--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -225,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -290,6 +290,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1373,7 +1377,7 @@
       </c>
       <c r="H6" s="20" t="inlineStr">
         <is>
-          <t>FUT_CONTRACT_DATE</t>
+          <t>Ref. start (FUT_DLV_DT_FIRST)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -1422,7 +1426,7 @@
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>IFERROR(BDP($A7,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A7,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I7" s="18">
@@ -1465,7 +1469,7 @@
         <v/>
       </c>
       <c r="H8" s="24">
-        <f>IFERROR(BDP($A8,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A8,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I8" s="24">
@@ -1508,7 +1512,7 @@
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>IFERROR(BDP($A9,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A9,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I9" s="18">
@@ -1551,7 +1555,7 @@
         <v/>
       </c>
       <c r="H10" s="24">
-        <f>IFERROR(BDP($A10,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A10,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I10" s="24">
@@ -1594,7 +1598,7 @@
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>IFERROR(BDP($A11,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A11,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I11" s="18">
@@ -1637,7 +1641,7 @@
         <v/>
       </c>
       <c r="H12" s="24">
-        <f>IFERROR(BDP($A12,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A12,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I12" s="24">
@@ -1680,7 +1684,7 @@
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>IFERROR(BDP($A13,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A13,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I13" s="18">
@@ -1723,7 +1727,7 @@
         <v/>
       </c>
       <c r="H14" s="24">
-        <f>IFERROR(BDP($A14,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A14,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I14" s="24">
@@ -1766,7 +1770,7 @@
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>IFERROR(BDP($A15,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A15,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I15" s="18">
@@ -1809,7 +1813,7 @@
         <v/>
       </c>
       <c r="H16" s="24">
-        <f>IFERROR(BDP($A16,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A16,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I16" s="24">
@@ -1852,7 +1856,7 @@
         <v/>
       </c>
       <c r="H17" s="18">
-        <f>IFERROR(BDP($A17,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A17,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I17" s="18">
@@ -1895,7 +1899,7 @@
         <v/>
       </c>
       <c r="H18" s="24">
-        <f>IFERROR(BDP($A18,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A18,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I18" s="24">
@@ -1938,7 +1942,7 @@
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>IFERROR(BDP($A19,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A19,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I19" s="18">
@@ -1981,7 +1985,7 @@
         <v/>
       </c>
       <c r="H20" s="24">
-        <f>IFERROR(BDP($A20,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A20,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I20" s="24">
@@ -2024,7 +2028,7 @@
         <v/>
       </c>
       <c r="H21" s="18">
-        <f>IFERROR(BDP($A21,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A21,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I21" s="18">
@@ -2067,7 +2071,7 @@
         <v/>
       </c>
       <c r="H22" s="24">
-        <f>IFERROR(BDP($A22,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A22,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I22" s="24">
@@ -2110,7 +2114,7 @@
         <v/>
       </c>
       <c r="H23" s="18">
-        <f>IFERROR(BDP($A23,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A23,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I23" s="18">
@@ -2153,7 +2157,7 @@
         <v/>
       </c>
       <c r="H24" s="24">
-        <f>IFERROR(BDP($A24,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A24,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I24" s="24">
@@ -2196,7 +2200,7 @@
         <v/>
       </c>
       <c r="H25" s="18">
-        <f>IFERROR(BDP($A25,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A25,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I25" s="18">
@@ -2239,7 +2243,7 @@
         <v/>
       </c>
       <c r="H26" s="24">
-        <f>IFERROR(BDP($A26,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A26,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I26" s="24">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="H31" s="20" t="inlineStr">
         <is>
-          <t>FUT_CONTRACT_DATE</t>
+          <t>Ref. start (FUT_DLV_DT_FIRST)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -2356,7 +2360,7 @@
         <v/>
       </c>
       <c r="H32" s="18">
-        <f>IFERROR(BDP($A32,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A32,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I32" s="18">
@@ -2399,7 +2403,7 @@
         <v/>
       </c>
       <c r="H33" s="24">
-        <f>IFERROR(BDP($A33,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A33,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I33" s="24">
@@ -2442,7 +2446,7 @@
         <v/>
       </c>
       <c r="H34" s="18">
-        <f>IFERROR(BDP($A34,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A34,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I34" s="18">
@@ -2485,7 +2489,7 @@
         <v/>
       </c>
       <c r="H35" s="24">
-        <f>IFERROR(BDP($A35,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A35,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I35" s="24">
@@ -2528,7 +2532,7 @@
         <v/>
       </c>
       <c r="H36" s="18">
-        <f>IFERROR(BDP($A36,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A36,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I36" s="18">
@@ -2571,7 +2575,7 @@
         <v/>
       </c>
       <c r="H37" s="24">
-        <f>IFERROR(BDP($A37,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A37,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I37" s="24">
@@ -2614,7 +2618,7 @@
         <v/>
       </c>
       <c r="H38" s="18">
-        <f>IFERROR(BDP($A38,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A38,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I38" s="18">
@@ -2657,7 +2661,7 @@
         <v/>
       </c>
       <c r="H39" s="24">
-        <f>IFERROR(BDP($A39,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A39,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I39" s="24">
@@ -2700,7 +2704,7 @@
         <v/>
       </c>
       <c r="H40" s="18">
-        <f>IFERROR(BDP($A40,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A40,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I40" s="18">
@@ -2743,7 +2747,7 @@
         <v/>
       </c>
       <c r="H41" s="24">
-        <f>IFERROR(BDP($A41,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A41,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I41" s="24">
@@ -2786,7 +2790,7 @@
         <v/>
       </c>
       <c r="H42" s="18">
-        <f>IFERROR(BDP($A42,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A42,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I42" s="18">
@@ -2829,7 +2833,7 @@
         <v/>
       </c>
       <c r="H43" s="24">
-        <f>IFERROR(BDP($A43,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A43,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I43" s="24">
@@ -2872,7 +2876,7 @@
         <v/>
       </c>
       <c r="H44" s="18">
-        <f>IFERROR(BDP($A44,"FUT_CONTRACT_DATE"),"")</f>
+        <f>IFERROR(BDP($A44,"FUT_DLV_DT_FIRST"),"")</f>
         <v/>
       </c>
       <c r="I44" s="18">
@@ -4565,7 +4569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4658,24 +4662,28 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>FLOATER_RESET_IDX</t>
-        </is>
-      </c>
-      <c r="C6" s="26">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","FLOATER_RESET_IDX"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D6" s="26">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","FLOATER_RESET_IDX"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E6" s="26">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","FLOATER_RESET_IDX"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","FLOATER_RESET_IDX"),"N/A — use FLDS")</f>
-        <v/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D6" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E6" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F6" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -4686,24 +4694,28 @@
       </c>
       <c r="B7" s="34" t="inlineStr">
         <is>
-          <t>DAYS_TO_SETTLE</t>
-        </is>
-      </c>
-      <c r="C7" s="35">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","DAYS_TO_SETTLE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D7" s="35">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","DAYS_TO_SETTLE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E7" s="35">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","DAYS_TO_SETTLE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F7" s="35">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","DAYS_TO_SETTLE"),"N/A — use FLDS")</f>
-        <v/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D7" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E7" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F7" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4719,22 +4731,22 @@
       </c>
       <c r="C8" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="D8" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="E8" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="F8" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
     </row>
@@ -4751,22 +4763,22 @@
       </c>
       <c r="C9" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="D9" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="E9" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
     </row>
@@ -4811,22 +4823,22 @@
       </c>
       <c r="C11" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="D11" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="E11" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="F11" s="35" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
     </row>
@@ -4866,24 +4878,28 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>CPN_FREQ</t>
-        </is>
-      </c>
-      <c r="C13" s="35">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","CPN_FREQ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D13" s="35">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CPN_FREQ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E13" s="35">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CPN_FREQ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F13" s="35">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CPN_FREQ"),"N/A — use FLDS")</f>
-        <v/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D13" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E13" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F13" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4894,24 +4910,28 @@
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
-          <t>FLOATING_DAY_COUNT</t>
-        </is>
-      </c>
-      <c r="C14" s="26">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","FLOATING_DAY_COUNT"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D14" s="26">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","FLOATING_DAY_COUNT"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E14" s="26">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","FLOATING_DAY_COUNT"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F14" s="26">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","FLOATING_DAY_COUNT"),"N/A — use FLDS")</f>
-        <v/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -4922,24 +4942,28 @@
       </c>
       <c r="B15" s="34" t="inlineStr">
         <is>
-          <t>FLOATING_PAY_FREQ</t>
-        </is>
-      </c>
-      <c r="C15" s="35">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","FLOATING_PAY_FREQ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D15" s="35">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","FLOATING_PAY_FREQ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E15" s="35">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","FLOATING_PAY_FREQ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F15" s="35">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","FLOATING_PAY_FREQ"),"N/A — use FLDS")</f>
-        <v/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D15" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F15" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -4955,22 +4979,22 @@
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="E16" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="F16" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
     </row>
@@ -4982,24 +5006,28 @@
       </c>
       <c r="B17" s="34" t="inlineStr">
         <is>
-          <t>PAY_LAG</t>
-        </is>
-      </c>
-      <c r="C17" s="35">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","PAY_LAG"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D17" s="35">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","PAY_LAG"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E17" s="35">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","PAY_LAG"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F17" s="35">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","PAY_LAG"),"N/A — use FLDS")</f>
-        <v/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D17" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E17" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F17" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -5015,22 +5043,22 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="E18" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
       <c r="F18" s="26" t="inlineStr">
         <is>
-          <t>(read from DES/SWPM)</t>
+          <t>— DES/SWPM —</t>
         </is>
       </c>
     </row>
@@ -5042,39 +5070,272 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>EOM_ADJ</t>
-        </is>
-      </c>
-      <c r="C19" s="35">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","EOM_ADJ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D19" s="35">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","EOM_ADJ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E19" s="35">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","EOM_ADJ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F19" s="35">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","EOM_ADJ"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>SWPM &lt;GO&gt;: build a representative SOFR OIS for 1Y, 5Y and 30Y and export the cashflow schedule — that gives an authoritative set of pay/accrual dates to test your own date generation against. Field mnemonics above are best-guess and entitlement-dependent: where a cell shows 'N/A — use FLDS', open FLDS &lt;GO&gt; on that security to find the enabled field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E19" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F19" s="35" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>USD SOFR OIS — MARKET-STANDARD CONVENTIONS  (confirm per-trade in DES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Reference index</t>
+        </is>
+      </c>
+      <c r="B22" s="36" t="inlineStr">
+        <is>
+          <t>USD-SOFR (compounded in arrears)</t>
+        </is>
+      </c>
+      <c r="C22" s="37" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="37" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Spot / settlement lag</t>
+        </is>
+      </c>
+      <c r="B23" s="36" t="inlineStr">
+        <is>
+          <t>T+2 US business days</t>
+        </is>
+      </c>
+      <c r="C23" s="37" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="37" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Effective date rule</t>
+        </is>
+      </c>
+      <c r="B24" s="36" t="inlineStr">
+        <is>
+          <t>Spot (T+2), modified following</t>
+        </is>
+      </c>
+      <c r="C24" s="37" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="37" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Maturity date rule</t>
+        </is>
+      </c>
+      <c r="B25" s="36" t="inlineStr">
+        <is>
+          <t>Effective + tenor, modified following</t>
+        </is>
+      </c>
+      <c r="C25" s="37" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="37" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Business-day convention</t>
+        </is>
+      </c>
+      <c r="B26" s="36" t="inlineStr">
+        <is>
+          <t>Modified Following</t>
+        </is>
+      </c>
+      <c r="C26" s="37" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="37" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Fixed-leg day count</t>
+        </is>
+      </c>
+      <c r="B27" s="36" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+      <c r="C27" s="37" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="37" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Fixed-leg pay frequency</t>
+        </is>
+      </c>
+      <c r="B28" s="36" t="inlineStr">
+        <is>
+          <t>Annual  (single payment if tenor ≤ 1Y)</t>
+        </is>
+      </c>
+      <c r="C28" s="37" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="37" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Floating-leg day count</t>
+        </is>
+      </c>
+      <c r="B29" s="36" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+      <c r="C29" s="37" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="37" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Floating-leg pay frequency</t>
+        </is>
+      </c>
+      <c r="B30" s="36" t="inlineStr">
+        <is>
+          <t>Annual  (single payment if tenor ≤ 1Y)</t>
+        </is>
+      </c>
+      <c r="C30" s="37" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="37" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>SOFR compounding method</t>
+        </is>
+      </c>
+      <c r="B31" s="36" t="inlineStr">
+        <is>
+          <t>Daily compounded, ACT/360</t>
+        </is>
+      </c>
+      <c r="C31" s="37" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="37" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>Payment lag</t>
+        </is>
+      </c>
+      <c r="B32" s="36" t="inlineStr">
+        <is>
+          <t>2 US business days</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="n"/>
+      <c r="D32" s="37" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="37" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Observation shift / lookback</t>
+        </is>
+      </c>
+      <c r="B33" s="36" t="inlineStr">
+        <is>
+          <t>None (payment-delay convention, 2 bd)</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="37" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>End-of-month treatment</t>
+        </is>
+      </c>
+      <c r="B34" s="36" t="inlineStr">
+        <is>
+          <t>EOM applies</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="37" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>SWPM &lt;GO&gt;: build a representative SOFR OIS for 1Y, 5Y and 30Y and export the cashflow schedule — that gives an authoritative set of pay/accrual dates to test your own date generation against. Rows marked '— DES/SWPM —' are leg-level conventions that a rate-quote ticker does not carry; read them from DES &lt;GO&gt; on an actual swap (the market-standard defaults above are the expected values). Where a BDP cell shows 'N/A — use FLDS', open FLDS &lt;GO&gt; to find the enabled field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="17">
+    <mergeCell ref="B30:F30"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B33:F33"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A21:F22"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A36:F37"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1019,108 +1019,191 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>BOOTSTRAP METHODOLOGY  —  one discount curve, three liquid segments</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>Short end (o/n – ~1Y)</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SOFR fixing + short OIS (1W,1M,3M,6M) anchor P(0,T) at the front — the modern LIBOR-deposit segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Mid (~3M – ~5Y)</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>SR3 3M-SOFR futures; implied rate = 100 − price, each covering one 3M IMM reference quarter — the modern Eurodollar-futures segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="28" customHeight="1">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>Long end (~2Y – 50Y)</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>SOFR OIS par swaps (mid = (bid+ask)/2) where deep liquidity lives — the modern LIBOR-swap segment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="28" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Bootstrap order</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Left → right: each instrument solves for the next discount-factor pillar given everything already solved to its left (sequential 1-D root find).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Three differences vs. Lehman 2002 (where 'modern' is not a literal copy):</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>•  Single-curve: the SOFR curve both projects forwards AND discounts. Lehman 2002 was also single-curve (LIBOR did both), so a SOFR OIS build is CLOSER to the paper than a modern LIBOR build would be.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>•  Compounding: SOFR is an overnight rate compounded daily in arrears over each period; LIBOR was a term rate set once. The OIS/futures legs carry a daily-compounding calc LIBOR did not need.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>•  Futures convexity: SR3 (like Eurodollar) futures need a small convexity adjustment before the implied rate enters the curve. A first pass can omit it and report the bias against the S490 benchmark.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>TABS IN THIS WORKBOOK</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>1. SOFR_Fixings</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Overnight SOFR fixing — current (BDP) + daily history (BDH).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>2. SOFR_Futures</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B37" s="3" t="inlineStr">
         <is>
           <t>SR3 (3M) and SR1 (1M) SOFR futures chains + fields + implied rate = 100 − price.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>3. SOFR_OIS_Quotes</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B38" s="3" t="inlineStr">
         <is>
           <t>Full USOSFR OIS strip (1W–50Y): bid / ask / last + mid. Bootstrap-set flagged.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>4. Bloomberg_S490_Validation</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>5. Conventions</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B40" s="3" t="inlineStr">
         <is>
           <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>DO NOT substitute these (wrong instruments):</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>•  Use PX midpoint (bid+ask)/2 for construction; use PX_LAST only where bid/ask are unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="28" customHeight="1">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>Licensing: Bloomberg data is licensed and entitlement-dependent — do NOT redistribute pulled values or commit them to a public repository. This template ships formulas only, no data. Some static convention fields may return N/A under your entitlement; use FLDS &lt;GO&gt; on the security to find the enabled mnemonic.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
+    <row r="48"/>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="50">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
@@ -1131,37 +1214,46 @@
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A42:F42"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A36:F37"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="B29:F29"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="A44:F44"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B37:F37"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A30:F30"/>
     <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B40:F40"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A45:F45"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B26:F26"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A47:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Fixings" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Futures" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_OIS_Quotes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -28,10 +29,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -225,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -281,9 +283,14 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -709,7 +716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1145,68 +1152,81 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>4. Bloomberg_S490_Validation</t>
+          <t>4. Bootstrap</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
+          <t>Live single-curve OIS bootstrap → discount factors, zero &amp; forward rates, S490 Δz check.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>5. Conventions</t>
+          <t>5. Bloomberg_S490_Validation</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
+          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>6. Conventions</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
           <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>DO NOT substitute these (wrong instruments):</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="11" t="inlineStr">
-        <is>
-          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
+          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
           <t>•  Use PX midpoint (bid+ask)/2 for construction; use PX_LAST only where bid/ask are unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="11" t="inlineStr">
+    <row r="48" ht="28" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>Licensing: Bloomberg data is licensed and entitlement-dependent — do NOT redistribute pulled values or commit them to a public repository. This template ships formulas only, no data. Some static convention fields may return N/A under your entitlement; use FLDS &lt;GO&gt; on the security to find the enabled mnemonic.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
+    <row r="49"/>
   </sheetData>
-  <mergeCells count="50">
+  <mergeCells count="51">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
+    <mergeCell ref="A46:F46"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="B27:F27"/>
@@ -1215,7 +1235,7 @@
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A48:F49"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="D12:F12"/>
@@ -1251,9 +1271,9 @@
     <mergeCell ref="A4:F5"/>
     <mergeCell ref="E18:F18"/>
     <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A47:F48"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4188,6 +4208,1544 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bootstrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Single-curve OIS bootstrap from the SOFR_OIS_Quotes mid strip → discount factors, zero &amp; forward rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Spot (T+2):</t>
+        </is>
+      </c>
+      <c r="B4" s="24">
+        <f>WORKDAY(VAL_DATE,2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Par-OIS recursive bootstrap on the quoted tenor grid:  DF_n = (1 − S_n·A_(n-1)) / (1 + S_n·τ_n),  with A_(n-1) = Σ τ_i·DF_i.  Exact for the sub-1Y money-market points and the annual 1Y–10Y section (pillars coincide with coupon dates); the sparse long end (12–50Y) uses the pillar grid AS the coupon schedule — a standard, transparent approximation (the openusdcurve engine does the exact interpolated-annuity build). Par rates are pulled live from the SOFR_OIS_Quotes mid column; paste Bloomberg S490 zero rates into column J for the Δz check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>T (yrs)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>τ ACT/360</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Par rate S (%)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>Annuity Στ·DF (prior)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Zero rate (%) cont.</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Fwd rate (%) simple</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>S490 zero (%) [paste]</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>Δ vs S490 (bp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>$B$4+7</f>
+        <v/>
+      </c>
+      <c r="C8" s="31">
+        <f>(B8-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D8" s="21">
+        <f>(B8-$B$4)/360</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
+        <f>'SOFR_OIS_Quotes'!$G5</f>
+        <v/>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="32">
+        <f>(1-(E8/100)*F8)/(1+(E8/100)*D8)</f>
+        <v/>
+      </c>
+      <c r="H8" s="21">
+        <f>-LN(G8)/C8*100</f>
+        <v/>
+      </c>
+      <c r="I8" s="21">
+        <f>(1/G8-1)/D8*100</f>
+        <v/>
+      </c>
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="34">
+        <f>IF(J8="","",(H8-J8)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="B9" s="24">
+        <f>$B$4+14</f>
+        <v/>
+      </c>
+      <c r="C9" s="35">
+        <f>(B9-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>(B9-B8)/360</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>'SOFR_OIS_Quotes'!$G6</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>F8+D8*G8</f>
+        <v/>
+      </c>
+      <c r="G9" s="36">
+        <f>(1-(E9/100)*F9)/(1+(E9/100)*D9)</f>
+        <v/>
+      </c>
+      <c r="H9" s="17">
+        <f>-LN(G9)/C9*100</f>
+        <v/>
+      </c>
+      <c r="I9" s="17">
+        <f>(G8/G9-1)/D9*100</f>
+        <v/>
+      </c>
+      <c r="J9" s="33" t="n"/>
+      <c r="K9" s="37">
+        <f>IF(J9="","",(H9-J9)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>3W</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>$B$4+21</f>
+        <v/>
+      </c>
+      <c r="C10" s="31">
+        <f>(B10-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
+        <f>(B10-B9)/360</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
+        <f>'SOFR_OIS_Quotes'!$G7</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>F9+D9*G9</f>
+        <v/>
+      </c>
+      <c r="G10" s="32">
+        <f>(1-(E10/100)*F10)/(1+(E10/100)*D10)</f>
+        <v/>
+      </c>
+      <c r="H10" s="21">
+        <f>-LN(G10)/C10*100</f>
+        <v/>
+      </c>
+      <c r="I10" s="21">
+        <f>(G9/G10-1)/D10*100</f>
+        <v/>
+      </c>
+      <c r="J10" s="33" t="n"/>
+      <c r="K10" s="34">
+        <f>IF(J10="","",(H10-J10)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="B11" s="24">
+        <f>EDATE($B$4,1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="35">
+        <f>(B11-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>(B11-B10)/360</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>'SOFR_OIS_Quotes'!$G8</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>F10+D10*G10</f>
+        <v/>
+      </c>
+      <c r="G11" s="36">
+        <f>(1-(E11/100)*F11)/(1+(E11/100)*D11)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>-LN(G11)/C11*100</f>
+        <v/>
+      </c>
+      <c r="I11" s="17">
+        <f>(G10/G11-1)/D11*100</f>
+        <v/>
+      </c>
+      <c r="J11" s="33" t="n"/>
+      <c r="K11" s="37">
+        <f>IF(J11="","",(H11-J11)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>EDATE($B$4,2)</f>
+        <v/>
+      </c>
+      <c r="C12" s="31">
+        <f>(B12-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D12" s="21">
+        <f>(B12-B11)/360</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
+        <f>'SOFR_OIS_Quotes'!$G9</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>F11+D11*G11</f>
+        <v/>
+      </c>
+      <c r="G12" s="32">
+        <f>(1-(E12/100)*F12)/(1+(E12/100)*D12)</f>
+        <v/>
+      </c>
+      <c r="H12" s="21">
+        <f>-LN(G12)/C12*100</f>
+        <v/>
+      </c>
+      <c r="I12" s="21">
+        <f>(G11/G12-1)/D12*100</f>
+        <v/>
+      </c>
+      <c r="J12" s="33" t="n"/>
+      <c r="K12" s="34">
+        <f>IF(J12="","",(H12-J12)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="B13" s="24">
+        <f>EDATE($B$4,3)</f>
+        <v/>
+      </c>
+      <c r="C13" s="35">
+        <f>(B13-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>(B13-B12)/360</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>'SOFR_OIS_Quotes'!$G10</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>F12+D12*G12</f>
+        <v/>
+      </c>
+      <c r="G13" s="36">
+        <f>(1-(E13/100)*F13)/(1+(E13/100)*D13)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>-LN(G13)/C13*100</f>
+        <v/>
+      </c>
+      <c r="I13" s="17">
+        <f>(G12/G13-1)/D13*100</f>
+        <v/>
+      </c>
+      <c r="J13" s="33" t="n"/>
+      <c r="K13" s="37">
+        <f>IF(J13="","",(H13-J13)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>4M</t>
+        </is>
+      </c>
+      <c r="B14" s="18">
+        <f>EDATE($B$4,4)</f>
+        <v/>
+      </c>
+      <c r="C14" s="31">
+        <f>(B14-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D14" s="21">
+        <f>(B14-B13)/360</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
+        <f>'SOFR_OIS_Quotes'!$G11</f>
+        <v/>
+      </c>
+      <c r="F14" s="21">
+        <f>F13+D13*G13</f>
+        <v/>
+      </c>
+      <c r="G14" s="32">
+        <f>(1-(E14/100)*F14)/(1+(E14/100)*D14)</f>
+        <v/>
+      </c>
+      <c r="H14" s="21">
+        <f>-LN(G14)/C14*100</f>
+        <v/>
+      </c>
+      <c r="I14" s="21">
+        <f>(G13/G14-1)/D14*100</f>
+        <v/>
+      </c>
+      <c r="J14" s="33" t="n"/>
+      <c r="K14" s="34">
+        <f>IF(J14="","",(H14-J14)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>5M</t>
+        </is>
+      </c>
+      <c r="B15" s="24">
+        <f>EDATE($B$4,5)</f>
+        <v/>
+      </c>
+      <c r="C15" s="35">
+        <f>(B15-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>(B15-B14)/360</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>'SOFR_OIS_Quotes'!$G12</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>F14+D14*G14</f>
+        <v/>
+      </c>
+      <c r="G15" s="36">
+        <f>(1-(E15/100)*F15)/(1+(E15/100)*D15)</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>-LN(G15)/C15*100</f>
+        <v/>
+      </c>
+      <c r="I15" s="17">
+        <f>(G14/G15-1)/D15*100</f>
+        <v/>
+      </c>
+      <c r="J15" s="33" t="n"/>
+      <c r="K15" s="37">
+        <f>IF(J15="","",(H15-J15)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="B16" s="18">
+        <f>EDATE($B$4,6)</f>
+        <v/>
+      </c>
+      <c r="C16" s="31">
+        <f>(B16-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>(B16-B15)/360</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
+        <f>'SOFR_OIS_Quotes'!$G13</f>
+        <v/>
+      </c>
+      <c r="F16" s="21">
+        <f>F15+D15*G15</f>
+        <v/>
+      </c>
+      <c r="G16" s="32">
+        <f>(1-(E16/100)*F16)/(1+(E16/100)*D16)</f>
+        <v/>
+      </c>
+      <c r="H16" s="21">
+        <f>-LN(G16)/C16*100</f>
+        <v/>
+      </c>
+      <c r="I16" s="21">
+        <f>(G15/G16-1)/D16*100</f>
+        <v/>
+      </c>
+      <c r="J16" s="33" t="n"/>
+      <c r="K16" s="34">
+        <f>IF(J16="","",(H16-J16)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>7M</t>
+        </is>
+      </c>
+      <c r="B17" s="24">
+        <f>EDATE($B$4,7)</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>(B17-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>(B17-B16)/360</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>'SOFR_OIS_Quotes'!$G14</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>F16+D16*G16</f>
+        <v/>
+      </c>
+      <c r="G17" s="36">
+        <f>(1-(E17/100)*F17)/(1+(E17/100)*D17)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>-LN(G17)/C17*100</f>
+        <v/>
+      </c>
+      <c r="I17" s="17">
+        <f>(G16/G17-1)/D17*100</f>
+        <v/>
+      </c>
+      <c r="J17" s="33" t="n"/>
+      <c r="K17" s="37">
+        <f>IF(J17="","",(H17-J17)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>8M</t>
+        </is>
+      </c>
+      <c r="B18" s="18">
+        <f>EDATE($B$4,8)</f>
+        <v/>
+      </c>
+      <c r="C18" s="31">
+        <f>(B18-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>(B18-B17)/360</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
+        <f>'SOFR_OIS_Quotes'!$G15</f>
+        <v/>
+      </c>
+      <c r="F18" s="21">
+        <f>F17+D17*G17</f>
+        <v/>
+      </c>
+      <c r="G18" s="32">
+        <f>(1-(E18/100)*F18)/(1+(E18/100)*D18)</f>
+        <v/>
+      </c>
+      <c r="H18" s="21">
+        <f>-LN(G18)/C18*100</f>
+        <v/>
+      </c>
+      <c r="I18" s="21">
+        <f>(G17/G18-1)/D18*100</f>
+        <v/>
+      </c>
+      <c r="J18" s="33" t="n"/>
+      <c r="K18" s="34">
+        <f>IF(J18="","",(H18-J18)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>EDATE($B$4,9)</f>
+        <v/>
+      </c>
+      <c r="C19" s="35">
+        <f>(B19-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>(B19-B18)/360</f>
+        <v/>
+      </c>
+      <c r="E19" s="17">
+        <f>'SOFR_OIS_Quotes'!$G16</f>
+        <v/>
+      </c>
+      <c r="F19" s="17">
+        <f>F18+D18*G18</f>
+        <v/>
+      </c>
+      <c r="G19" s="36">
+        <f>(1-(E19/100)*F19)/(1+(E19/100)*D19)</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>-LN(G19)/C19*100</f>
+        <v/>
+      </c>
+      <c r="I19" s="17">
+        <f>(G18/G19-1)/D19*100</f>
+        <v/>
+      </c>
+      <c r="J19" s="33" t="n"/>
+      <c r="K19" s="37">
+        <f>IF(J19="","",(H19-J19)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>10M</t>
+        </is>
+      </c>
+      <c r="B20" s="18">
+        <f>EDATE($B$4,10)</f>
+        <v/>
+      </c>
+      <c r="C20" s="31">
+        <f>(B20-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>(B20-B19)/360</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
+        <f>'SOFR_OIS_Quotes'!$G17</f>
+        <v/>
+      </c>
+      <c r="F20" s="21">
+        <f>F19+D19*G19</f>
+        <v/>
+      </c>
+      <c r="G20" s="32">
+        <f>(1-(E20/100)*F20)/(1+(E20/100)*D20)</f>
+        <v/>
+      </c>
+      <c r="H20" s="21">
+        <f>-LN(G20)/C20*100</f>
+        <v/>
+      </c>
+      <c r="I20" s="21">
+        <f>(G19/G20-1)/D20*100</f>
+        <v/>
+      </c>
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="34">
+        <f>IF(J20="","",(H20-J20)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>11M</t>
+        </is>
+      </c>
+      <c r="B21" s="24">
+        <f>EDATE($B$4,11)</f>
+        <v/>
+      </c>
+      <c r="C21" s="35">
+        <f>(B21-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>(B21-B20)/360</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>'SOFR_OIS_Quotes'!$G18</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>F20+D20*G20</f>
+        <v/>
+      </c>
+      <c r="G21" s="36">
+        <f>(1-(E21/100)*F21)/(1+(E21/100)*D21)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
+        <f>-LN(G21)/C21*100</f>
+        <v/>
+      </c>
+      <c r="I21" s="17">
+        <f>(G20/G21-1)/D21*100</f>
+        <v/>
+      </c>
+      <c r="J21" s="33" t="n"/>
+      <c r="K21" s="37">
+        <f>IF(J21="","",(H21-J21)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B22" s="18">
+        <f>EDATE($B$4,12)</f>
+        <v/>
+      </c>
+      <c r="C22" s="31">
+        <f>(B22-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D22" s="21">
+        <f>(B22-B21)/360</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
+        <f>'SOFR_OIS_Quotes'!$G19</f>
+        <v/>
+      </c>
+      <c r="F22" s="21">
+        <f>F21+D21*G21</f>
+        <v/>
+      </c>
+      <c r="G22" s="32">
+        <f>(1-(E22/100)*F22)/(1+(E22/100)*D22)</f>
+        <v/>
+      </c>
+      <c r="H22" s="21">
+        <f>-LN(G22)/C22*100</f>
+        <v/>
+      </c>
+      <c r="I22" s="21">
+        <f>(G21/G22-1)/D22*100</f>
+        <v/>
+      </c>
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="34">
+        <f>IF(J22="","",(H22-J22)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>18M</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>EDATE($B$4,18)</f>
+        <v/>
+      </c>
+      <c r="C23" s="35">
+        <f>(B23-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>(B23-B22)/360</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>'SOFR_OIS_Quotes'!$G20</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>F22+D22*G22</f>
+        <v/>
+      </c>
+      <c r="G23" s="36">
+        <f>(1-(E23/100)*F23)/(1+(E23/100)*D23)</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>-LN(G23)/C23*100</f>
+        <v/>
+      </c>
+      <c r="I23" s="17">
+        <f>(G22/G23-1)/D23*100</f>
+        <v/>
+      </c>
+      <c r="J23" s="33" t="n"/>
+      <c r="K23" s="37">
+        <f>IF(J23="","",(H23-J23)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B24" s="18">
+        <f>EDATE($B$4,24)</f>
+        <v/>
+      </c>
+      <c r="C24" s="31">
+        <f>(B24-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D24" s="21">
+        <f>(B24-B23)/360</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
+        <f>'SOFR_OIS_Quotes'!$G21</f>
+        <v/>
+      </c>
+      <c r="F24" s="21">
+        <f>F23+D23*G23</f>
+        <v/>
+      </c>
+      <c r="G24" s="32">
+        <f>(1-(E24/100)*F24)/(1+(E24/100)*D24)</f>
+        <v/>
+      </c>
+      <c r="H24" s="21">
+        <f>-LN(G24)/C24*100</f>
+        <v/>
+      </c>
+      <c r="I24" s="21">
+        <f>(G23/G24-1)/D24*100</f>
+        <v/>
+      </c>
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="34">
+        <f>IF(J24="","",(H24-J24)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B25" s="24">
+        <f>EDATE($B$4,36)</f>
+        <v/>
+      </c>
+      <c r="C25" s="35">
+        <f>(B25-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>(B25-B24)/360</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>'SOFR_OIS_Quotes'!$G22</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>F24+D24*G24</f>
+        <v/>
+      </c>
+      <c r="G25" s="36">
+        <f>(1-(E25/100)*F25)/(1+(E25/100)*D25)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>-LN(G25)/C25*100</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>(G24/G25-1)/D25*100</f>
+        <v/>
+      </c>
+      <c r="J25" s="33" t="n"/>
+      <c r="K25" s="37">
+        <f>IF(J25="","",(H25-J25)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>4Y</t>
+        </is>
+      </c>
+      <c r="B26" s="18">
+        <f>EDATE($B$4,48)</f>
+        <v/>
+      </c>
+      <c r="C26" s="31">
+        <f>(B26-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D26" s="21">
+        <f>(B26-B25)/360</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
+        <f>'SOFR_OIS_Quotes'!$G23</f>
+        <v/>
+      </c>
+      <c r="F26" s="21">
+        <f>F25+D25*G25</f>
+        <v/>
+      </c>
+      <c r="G26" s="32">
+        <f>(1-(E26/100)*F26)/(1+(E26/100)*D26)</f>
+        <v/>
+      </c>
+      <c r="H26" s="21">
+        <f>-LN(G26)/C26*100</f>
+        <v/>
+      </c>
+      <c r="I26" s="21">
+        <f>(G25/G26-1)/D26*100</f>
+        <v/>
+      </c>
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="34">
+        <f>IF(J26="","",(H26-J26)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B27" s="24">
+        <f>EDATE($B$4,60)</f>
+        <v/>
+      </c>
+      <c r="C27" s="35">
+        <f>(B27-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>(B27-B26)/360</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>'SOFR_OIS_Quotes'!$G24</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>F26+D26*G26</f>
+        <v/>
+      </c>
+      <c r="G27" s="36">
+        <f>(1-(E27/100)*F27)/(1+(E27/100)*D27)</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>-LN(G27)/C27*100</f>
+        <v/>
+      </c>
+      <c r="I27" s="17">
+        <f>(G26/G27-1)/D27*100</f>
+        <v/>
+      </c>
+      <c r="J27" s="33" t="n"/>
+      <c r="K27" s="37">
+        <f>IF(J27="","",(H27-J27)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>6Y</t>
+        </is>
+      </c>
+      <c r="B28" s="18">
+        <f>EDATE($B$4,72)</f>
+        <v/>
+      </c>
+      <c r="C28" s="31">
+        <f>(B28-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D28" s="21">
+        <f>(B28-B27)/360</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
+        <f>'SOFR_OIS_Quotes'!$G25</f>
+        <v/>
+      </c>
+      <c r="F28" s="21">
+        <f>F27+D27*G27</f>
+        <v/>
+      </c>
+      <c r="G28" s="32">
+        <f>(1-(E28/100)*F28)/(1+(E28/100)*D28)</f>
+        <v/>
+      </c>
+      <c r="H28" s="21">
+        <f>-LN(G28)/C28*100</f>
+        <v/>
+      </c>
+      <c r="I28" s="21">
+        <f>(G27/G28-1)/D28*100</f>
+        <v/>
+      </c>
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="34">
+        <f>IF(J28="","",(H28-J28)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="B29" s="24">
+        <f>EDATE($B$4,84)</f>
+        <v/>
+      </c>
+      <c r="C29" s="35">
+        <f>(B29-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>(B29-B28)/360</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>'SOFR_OIS_Quotes'!$G26</f>
+        <v/>
+      </c>
+      <c r="F29" s="17">
+        <f>F28+D28*G28</f>
+        <v/>
+      </c>
+      <c r="G29" s="36">
+        <f>(1-(E29/100)*F29)/(1+(E29/100)*D29)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>-LN(G29)/C29*100</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>(G28/G29-1)/D29*100</f>
+        <v/>
+      </c>
+      <c r="J29" s="33" t="n"/>
+      <c r="K29" s="37">
+        <f>IF(J29="","",(H29-J29)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>8Y</t>
+        </is>
+      </c>
+      <c r="B30" s="18">
+        <f>EDATE($B$4,96)</f>
+        <v/>
+      </c>
+      <c r="C30" s="31">
+        <f>(B30-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>(B30-B29)/360</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>'SOFR_OIS_Quotes'!$G27</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
+        <f>F29+D29*G29</f>
+        <v/>
+      </c>
+      <c r="G30" s="32">
+        <f>(1-(E30/100)*F30)/(1+(E30/100)*D30)</f>
+        <v/>
+      </c>
+      <c r="H30" s="21">
+        <f>-LN(G30)/C30*100</f>
+        <v/>
+      </c>
+      <c r="I30" s="21">
+        <f>(G29/G30-1)/D30*100</f>
+        <v/>
+      </c>
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="34">
+        <f>IF(J30="","",(H30-J30)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>9Y</t>
+        </is>
+      </c>
+      <c r="B31" s="24">
+        <f>EDATE($B$4,108)</f>
+        <v/>
+      </c>
+      <c r="C31" s="35">
+        <f>(B31-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>(B31-B30)/360</f>
+        <v/>
+      </c>
+      <c r="E31" s="17">
+        <f>'SOFR_OIS_Quotes'!$G28</f>
+        <v/>
+      </c>
+      <c r="F31" s="17">
+        <f>F30+D30*G30</f>
+        <v/>
+      </c>
+      <c r="G31" s="36">
+        <f>(1-(E31/100)*F31)/(1+(E31/100)*D31)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>-LN(G31)/C31*100</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>(G30/G31-1)/D31*100</f>
+        <v/>
+      </c>
+      <c r="J31" s="33" t="n"/>
+      <c r="K31" s="37">
+        <f>IF(J31="","",(H31-J31)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B32" s="18">
+        <f>EDATE($B$4,120)</f>
+        <v/>
+      </c>
+      <c r="C32" s="31">
+        <f>(B32-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>(B32-B31)/360</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>'SOFR_OIS_Quotes'!$G29</f>
+        <v/>
+      </c>
+      <c r="F32" s="21">
+        <f>F31+D31*G31</f>
+        <v/>
+      </c>
+      <c r="G32" s="32">
+        <f>(1-(E32/100)*F32)/(1+(E32/100)*D32)</f>
+        <v/>
+      </c>
+      <c r="H32" s="21">
+        <f>-LN(G32)/C32*100</f>
+        <v/>
+      </c>
+      <c r="I32" s="21">
+        <f>(G31/G32-1)/D32*100</f>
+        <v/>
+      </c>
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="34">
+        <f>IF(J32="","",(H32-J32)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>12Y</t>
+        </is>
+      </c>
+      <c r="B33" s="24">
+        <f>EDATE($B$4,144)</f>
+        <v/>
+      </c>
+      <c r="C33" s="35">
+        <f>(B33-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>(B33-B32)/360</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>'SOFR_OIS_Quotes'!$G30</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>F32+D32*G32</f>
+        <v/>
+      </c>
+      <c r="G33" s="36">
+        <f>(1-(E33/100)*F33)/(1+(E33/100)*D33)</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>-LN(G33)/C33*100</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>(G32/G33-1)/D33*100</f>
+        <v/>
+      </c>
+      <c r="J33" s="33" t="n"/>
+      <c r="K33" s="37">
+        <f>IF(J33="","",(H33-J33)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>15Y</t>
+        </is>
+      </c>
+      <c r="B34" s="18">
+        <f>EDATE($B$4,180)</f>
+        <v/>
+      </c>
+      <c r="C34" s="31">
+        <f>(B34-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D34" s="21">
+        <f>(B34-B33)/360</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
+        <f>'SOFR_OIS_Quotes'!$G31</f>
+        <v/>
+      </c>
+      <c r="F34" s="21">
+        <f>F33+D33*G33</f>
+        <v/>
+      </c>
+      <c r="G34" s="32">
+        <f>(1-(E34/100)*F34)/(1+(E34/100)*D34)</f>
+        <v/>
+      </c>
+      <c r="H34" s="21">
+        <f>-LN(G34)/C34*100</f>
+        <v/>
+      </c>
+      <c r="I34" s="21">
+        <f>(G33/G34-1)/D34*100</f>
+        <v/>
+      </c>
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="34">
+        <f>IF(J34="","",(H34-J34)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>20Y</t>
+        </is>
+      </c>
+      <c r="B35" s="24">
+        <f>EDATE($B$4,240)</f>
+        <v/>
+      </c>
+      <c r="C35" s="35">
+        <f>(B35-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>(B35-B34)/360</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>'SOFR_OIS_Quotes'!$G32</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>F34+D34*G34</f>
+        <v/>
+      </c>
+      <c r="G35" s="36">
+        <f>(1-(E35/100)*F35)/(1+(E35/100)*D35)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>-LN(G35)/C35*100</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>(G34/G35-1)/D35*100</f>
+        <v/>
+      </c>
+      <c r="J35" s="33" t="n"/>
+      <c r="K35" s="37">
+        <f>IF(J35="","",(H35-J35)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>25Y</t>
+        </is>
+      </c>
+      <c r="B36" s="18">
+        <f>EDATE($B$4,300)</f>
+        <v/>
+      </c>
+      <c r="C36" s="31">
+        <f>(B36-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f>(B36-B35)/360</f>
+        <v/>
+      </c>
+      <c r="E36" s="21">
+        <f>'SOFR_OIS_Quotes'!$G33</f>
+        <v/>
+      </c>
+      <c r="F36" s="21">
+        <f>F35+D35*G35</f>
+        <v/>
+      </c>
+      <c r="G36" s="32">
+        <f>(1-(E36/100)*F36)/(1+(E36/100)*D36)</f>
+        <v/>
+      </c>
+      <c r="H36" s="21">
+        <f>-LN(G36)/C36*100</f>
+        <v/>
+      </c>
+      <c r="I36" s="21">
+        <f>(G35/G36-1)/D36*100</f>
+        <v/>
+      </c>
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="34">
+        <f>IF(J36="","",(H36-J36)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>30Y</t>
+        </is>
+      </c>
+      <c r="B37" s="24">
+        <f>EDATE($B$4,360)</f>
+        <v/>
+      </c>
+      <c r="C37" s="35">
+        <f>(B37-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>(B37-B36)/360</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>'SOFR_OIS_Quotes'!$G34</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>F36+D36*G36</f>
+        <v/>
+      </c>
+      <c r="G37" s="36">
+        <f>(1-(E37/100)*F37)/(1+(E37/100)*D37)</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>-LN(G37)/C37*100</f>
+        <v/>
+      </c>
+      <c r="I37" s="17">
+        <f>(G36/G37-1)/D37*100</f>
+        <v/>
+      </c>
+      <c r="J37" s="33" t="n"/>
+      <c r="K37" s="37">
+        <f>IF(J37="","",(H37-J37)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>40Y</t>
+        </is>
+      </c>
+      <c r="B38" s="18">
+        <f>EDATE($B$4,480)</f>
+        <v/>
+      </c>
+      <c r="C38" s="31">
+        <f>(B38-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>(B38-B37)/360</f>
+        <v/>
+      </c>
+      <c r="E38" s="21">
+        <f>'SOFR_OIS_Quotes'!$G35</f>
+        <v/>
+      </c>
+      <c r="F38" s="21">
+        <f>F37+D37*G37</f>
+        <v/>
+      </c>
+      <c r="G38" s="32">
+        <f>(1-(E38/100)*F38)/(1+(E38/100)*D38)</f>
+        <v/>
+      </c>
+      <c r="H38" s="21">
+        <f>-LN(G38)/C38*100</f>
+        <v/>
+      </c>
+      <c r="I38" s="21">
+        <f>(G37/G38-1)/D38*100</f>
+        <v/>
+      </c>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="34">
+        <f>IF(J38="","",(H38-J38)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>50Y</t>
+        </is>
+      </c>
+      <c r="B39" s="24">
+        <f>EDATE($B$4,600)</f>
+        <v/>
+      </c>
+      <c r="C39" s="35">
+        <f>(B39-$B$4)/365</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>(B39-B38)/360</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>'SOFR_OIS_Quotes'!$G36</f>
+        <v/>
+      </c>
+      <c r="F39" s="17">
+        <f>F38+D38*G38</f>
+        <v/>
+      </c>
+      <c r="G39" s="36">
+        <f>(1-(E39/100)*F39)/(1+(E39/100)*D39)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>-LN(G39)/C39*100</f>
+        <v/>
+      </c>
+      <c r="I39" s="17">
+        <f>(G38/G39-1)/D39*100</f>
+        <v/>
+      </c>
+      <c r="J39" s="33" t="n"/>
+      <c r="K39" s="37">
+        <f>IF(J39="","",(H39-J39)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
+          <t>Discount factor is the deliverable curve P(0,T). Zero rate is continuously-compounded (ACT/365): z = −ln(DF)/T. Forward is the simple rate over each pillar interval. Yellow column J is for pasting the Bloomberg S490 zero rates; Δ (bp) then shows your bootstrap vs Bloomberg — the validation the Lehman paper does against the dealer curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A41:K42"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A5:K6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4231,417 +5789,393 @@
           <t>Curve date</t>
         </is>
       </c>
-      <c r="B5" s="31">
-        <f>IFERROR(BDP(S490_TKR,"CURVE_DT"),VAL_DATE)</f>
+      <c r="B5" s="38">
+        <f>VAL_DATE</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>Primary pull: the anchor cell A8 holds =BDS(S490_TKR,"CURVE_TENOR_RATES"), which spills Tenor + par rate. Zero rate, discount factor and forward rate are best exported from the curve screen (type YCSW0490 &lt;GO&gt;, or SWDF), because they are not all returned by a single BDS field under every entitlement — paste them into columns E:G alongside the spilled tenors. Compare your bootstrap's P(0,T), zero and forward against these.</t>
+          <t>The anchor cell A8 holds =BDS(S490_TKR,"CURVE_TENOR_RATES") and spills raw below in Bloomberg's own column order (typically tenor, curve member, maturity, mid rate). It is NOT pre-labeled, because forcing headers/date-formats mis-aligned the columns. Bloomberg's zero rates / discount factors are best read from the curve screen (YCSW0490 &lt;GO&gt;, or SWDF). The actual bootstrap + comparison lives on the Bootstrap tab: paste S490 zero rates into its column J to get Δz in bp.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Tenor</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Curve date</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>Maturity date</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>Market/par rate (%)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Zero rate (%)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr">
-        <is>
-          <t>Forward rate (%)</t>
-        </is>
-      </c>
+          <t>Raw CURVE_TENOR_RATES dump — Bloomberg-defined column order; verify on terminal, then paste S490 zero rates into the Bootstrap tab (column J) for the Δz check</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="20" t="inlineStr"/>
+      <c r="D7" s="20" t="inlineStr"/>
+      <c r="E7" s="20" t="inlineStr"/>
+      <c r="F7" s="20" t="inlineStr"/>
+      <c r="G7" s="20" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8">
         <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
         <v/>
       </c>
-      <c r="B8" s="18" t="n"/>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="21" t="n"/>
-      <c r="E8" s="21" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="21" t="n"/>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="8" t="n"/>
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="23" t="n"/>
-      <c r="B9" s="24" t="n"/>
-      <c r="C9" s="24" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="17" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n"/>
-      <c r="B10" s="18" t="n"/>
-      <c r="C10" s="18" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="21" t="n"/>
+      <c r="B10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n"/>
+      <c r="E10" s="8" t="n"/>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="23" t="n"/>
-      <c r="B11" s="24" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="17" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n"/>
-      <c r="B12" s="18" t="n"/>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="21" t="n"/>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
+      <c r="E12" s="8" t="n"/>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="23" t="n"/>
-      <c r="B13" s="24" t="n"/>
-      <c r="C13" s="24" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="17" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n"/>
-      <c r="B14" s="18" t="n"/>
-      <c r="C14" s="18" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="21" t="n"/>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="23" t="n"/>
-      <c r="B15" s="24" t="n"/>
-      <c r="C15" s="24" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="17" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n"/>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="21" t="n"/>
-      <c r="E16" s="21" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="21" t="n"/>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="23" t="n"/>
-      <c r="B17" s="24" t="n"/>
-      <c r="C17" s="24" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="33" t="n"/>
-      <c r="G17" s="17" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n"/>
-      <c r="B18" s="18" t="n"/>
-      <c r="C18" s="18" t="n"/>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="21" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="21" t="n"/>
+      <c r="B18" s="8" t="n"/>
+      <c r="C18" s="8" t="n"/>
+      <c r="D18" s="8" t="n"/>
+      <c r="E18" s="8" t="n"/>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="23" t="n"/>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="33" t="n"/>
-      <c r="G19" s="17" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n"/>
-      <c r="B20" s="18" t="n"/>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="21" t="n"/>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="21" t="n"/>
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="23" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="17" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n"/>
-      <c r="B22" s="18" t="n"/>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="21" t="n"/>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="21" t="n"/>
+      <c r="B22" s="8" t="n"/>
+      <c r="C22" s="8" t="n"/>
+      <c r="D22" s="8" t="n"/>
+      <c r="E22" s="8" t="n"/>
+      <c r="F22" s="8" t="n"/>
+      <c r="G22" s="8" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="23" t="n"/>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="33" t="n"/>
-      <c r="G23" s="17" t="n"/>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n"/>
-      <c r="B24" s="18" t="n"/>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="21" t="n"/>
-      <c r="E24" s="21" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="21" t="n"/>
+      <c r="B24" s="8" t="n"/>
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="8" t="n"/>
+      <c r="F24" s="8" t="n"/>
+      <c r="G24" s="8" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="23" t="n"/>
-      <c r="B25" s="24" t="n"/>
-      <c r="C25" s="24" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="17" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n"/>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="21" t="n"/>
-      <c r="E26" s="21" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="21" t="n"/>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="23" t="n"/>
-      <c r="B27" s="24" t="n"/>
-      <c r="C27" s="24" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="33" t="n"/>
-      <c r="G27" s="17" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n"/>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="21" t="n"/>
-      <c r="E28" s="21" t="n"/>
-      <c r="F28" s="32" t="n"/>
-      <c r="G28" s="21" t="n"/>
+      <c r="B28" s="8" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
+      <c r="G28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="23" t="n"/>
-      <c r="B29" s="24" t="n"/>
-      <c r="C29" s="24" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="33" t="n"/>
-      <c r="G29" s="17" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n"/>
-      <c r="B30" s="18" t="n"/>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="21" t="n"/>
-      <c r="E30" s="21" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="21" t="n"/>
+      <c r="B30" s="8" t="n"/>
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="8" t="n"/>
+      <c r="F30" s="8" t="n"/>
+      <c r="G30" s="8" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="23" t="n"/>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="33" t="n"/>
-      <c r="G31" s="17" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="23" t="n"/>
+      <c r="F31" s="23" t="n"/>
+      <c r="G31" s="23" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n"/>
-      <c r="B32" s="18" t="n"/>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="21" t="n"/>
-      <c r="E32" s="21" t="n"/>
-      <c r="F32" s="32" t="n"/>
-      <c r="G32" s="21" t="n"/>
+      <c r="B32" s="8" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="23" t="n"/>
-      <c r="B33" s="24" t="n"/>
-      <c r="C33" s="24" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="17" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="23" t="n"/>
+      <c r="F33" s="23" t="n"/>
+      <c r="G33" s="23" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n"/>
-      <c r="B34" s="18" t="n"/>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="21" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="21" t="n"/>
+      <c r="B34" s="8" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
+      <c r="E34" s="8" t="n"/>
+      <c r="F34" s="8" t="n"/>
+      <c r="G34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="23" t="n"/>
-      <c r="B35" s="24" t="n"/>
-      <c r="C35" s="24" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="33" t="n"/>
-      <c r="G35" s="17" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="23" t="n"/>
+      <c r="F35" s="23" t="n"/>
+      <c r="G35" s="23" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n"/>
-      <c r="B36" s="18" t="n"/>
-      <c r="C36" s="18" t="n"/>
-      <c r="D36" s="21" t="n"/>
-      <c r="E36" s="21" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="21" t="n"/>
+      <c r="B36" s="8" t="n"/>
+      <c r="C36" s="8" t="n"/>
+      <c r="D36" s="8" t="n"/>
+      <c r="E36" s="8" t="n"/>
+      <c r="F36" s="8" t="n"/>
+      <c r="G36" s="8" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="23" t="n"/>
-      <c r="B37" s="24" t="n"/>
-      <c r="C37" s="24" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="33" t="n"/>
-      <c r="G37" s="17" t="n"/>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="23" t="n"/>
+      <c r="F37" s="23" t="n"/>
+      <c r="G37" s="23" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n"/>
-      <c r="B38" s="18" t="n"/>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="21" t="n"/>
-      <c r="E38" s="21" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="21" t="n"/>
+      <c r="B38" s="8" t="n"/>
+      <c r="C38" s="8" t="n"/>
+      <c r="D38" s="8" t="n"/>
+      <c r="E38" s="8" t="n"/>
+      <c r="F38" s="8" t="n"/>
+      <c r="G38" s="8" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="23" t="n"/>
-      <c r="B39" s="24" t="n"/>
-      <c r="C39" s="24" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="33" t="n"/>
-      <c r="G39" s="17" t="n"/>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n"/>
-      <c r="B40" s="18" t="n"/>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="21" t="n"/>
-      <c r="E40" s="21" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="21" t="n"/>
+      <c r="B40" s="8" t="n"/>
+      <c r="C40" s="8" t="n"/>
+      <c r="D40" s="8" t="n"/>
+      <c r="E40" s="8" t="n"/>
+      <c r="F40" s="8" t="n"/>
+      <c r="G40" s="8" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="23" t="n"/>
-      <c r="B41" s="24" t="n"/>
-      <c r="C41" s="24" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="33" t="n"/>
-      <c r="G41" s="17" t="n"/>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n"/>
-      <c r="B42" s="18" t="n"/>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="21" t="n"/>
-      <c r="E42" s="21" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="21" t="n"/>
+      <c r="B42" s="8" t="n"/>
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="8" t="n"/>
+      <c r="E42" s="8" t="n"/>
+      <c r="F42" s="8" t="n"/>
+      <c r="G42" s="8" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n"/>
-      <c r="B43" s="24" t="n"/>
-      <c r="C43" s="24" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="33" t="n"/>
-      <c r="G43" s="17" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="23" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n"/>
-      <c r="B44" s="18" t="n"/>
-      <c r="C44" s="18" t="n"/>
-      <c r="D44" s="21" t="n"/>
-      <c r="E44" s="21" t="n"/>
-      <c r="F44" s="32" t="n"/>
-      <c r="G44" s="21" t="n"/>
+      <c r="B44" s="8" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="23" t="n"/>
-      <c r="B45" s="24" t="n"/>
-      <c r="C45" s="24" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="33" t="n"/>
-      <c r="G45" s="17" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="23" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="n"/>
-      <c r="B46" s="18" t="n"/>
-      <c r="C46" s="18" t="n"/>
-      <c r="D46" s="21" t="n"/>
-      <c r="E46" s="21" t="n"/>
-      <c r="F46" s="32" t="n"/>
-      <c r="G46" s="21" t="n"/>
+      <c r="B46" s="8" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
+      <c r="E46" s="8" t="n"/>
+      <c r="F46" s="8" t="n"/>
+      <c r="G46" s="8" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="23" t="n"/>
-      <c r="B47" s="24" t="n"/>
-      <c r="C47" s="24" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="33" t="n"/>
-      <c r="G47" s="17" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4655,7 +6189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4724,24 +6258,24 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>CRNCY</t>
         </is>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="40">
         <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="40">
         <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="40">
         <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="40">
         <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
@@ -4784,27 +6318,27 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -4848,27 +6382,27 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -4908,27 +6442,27 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -4968,27 +6502,27 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -5032,27 +6566,27 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B15" s="34" t="inlineStr">
+      <c r="B15" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -5096,27 +6630,27 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B17" s="34" t="inlineStr">
+      <c r="B17" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr">
+      <c r="F17" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -5160,27 +6694,27 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B19" s="34" t="inlineStr">
+      <c r="B19" s="39" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="40" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -5199,15 +6733,15 @@
           <t>Reference index</t>
         </is>
       </c>
-      <c r="B22" s="36" t="inlineStr">
+      <c r="B22" s="41" t="inlineStr">
         <is>
           <t>USD-SOFR (compounded in arrears)</t>
         </is>
       </c>
-      <c r="C22" s="37" t="n"/>
-      <c r="D22" s="37" t="n"/>
-      <c r="E22" s="37" t="n"/>
-      <c r="F22" s="37" t="n"/>
+      <c r="C22" s="42" t="n"/>
+      <c r="D22" s="42" t="n"/>
+      <c r="E22" s="42" t="n"/>
+      <c r="F22" s="42" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -5215,15 +6749,15 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B23" s="36" t="inlineStr">
+      <c r="B23" s="41" t="inlineStr">
         <is>
           <t>T+2 US business days</t>
         </is>
       </c>
-      <c r="C23" s="37" t="n"/>
-      <c r="D23" s="37" t="n"/>
-      <c r="E23" s="37" t="n"/>
-      <c r="F23" s="37" t="n"/>
+      <c r="C23" s="42" t="n"/>
+      <c r="D23" s="42" t="n"/>
+      <c r="E23" s="42" t="n"/>
+      <c r="F23" s="42" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -5231,15 +6765,15 @@
           <t>Effective date rule</t>
         </is>
       </c>
-      <c r="B24" s="36" t="inlineStr">
+      <c r="B24" s="41" t="inlineStr">
         <is>
           <t>Spot (T+2), modified following</t>
         </is>
       </c>
-      <c r="C24" s="37" t="n"/>
-      <c r="D24" s="37" t="n"/>
-      <c r="E24" s="37" t="n"/>
-      <c r="F24" s="37" t="n"/>
+      <c r="C24" s="42" t="n"/>
+      <c r="D24" s="42" t="n"/>
+      <c r="E24" s="42" t="n"/>
+      <c r="F24" s="42" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -5247,15 +6781,15 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B25" s="36" t="inlineStr">
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>Effective + tenor, modified following</t>
         </is>
       </c>
-      <c r="C25" s="37" t="n"/>
-      <c r="D25" s="37" t="n"/>
-      <c r="E25" s="37" t="n"/>
-      <c r="F25" s="37" t="n"/>
+      <c r="C25" s="42" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="42" t="n"/>
+      <c r="F25" s="42" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -5263,15 +6797,15 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B26" s="36" t="inlineStr">
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>Modified Following</t>
         </is>
       </c>
-      <c r="C26" s="37" t="n"/>
-      <c r="D26" s="37" t="n"/>
-      <c r="E26" s="37" t="n"/>
-      <c r="F26" s="37" t="n"/>
+      <c r="C26" s="42" t="n"/>
+      <c r="D26" s="42" t="n"/>
+      <c r="E26" s="42" t="n"/>
+      <c r="F26" s="42" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -5279,15 +6813,15 @@
           <t>Fixed-leg day count</t>
         </is>
       </c>
-      <c r="B27" s="36" t="inlineStr">
+      <c r="B27" s="41" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
       </c>
-      <c r="C27" s="37" t="n"/>
-      <c r="D27" s="37" t="n"/>
-      <c r="E27" s="37" t="n"/>
-      <c r="F27" s="37" t="n"/>
+      <c r="C27" s="42" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="42" t="n"/>
+      <c r="F27" s="42" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -5295,15 +6829,15 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B28" s="36" t="inlineStr">
+      <c r="B28" s="41" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
       </c>
-      <c r="C28" s="37" t="n"/>
-      <c r="D28" s="37" t="n"/>
-      <c r="E28" s="37" t="n"/>
-      <c r="F28" s="37" t="n"/>
+      <c r="C28" s="42" t="n"/>
+      <c r="D28" s="42" t="n"/>
+      <c r="E28" s="42" t="n"/>
+      <c r="F28" s="42" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -5311,15 +6845,15 @@
           <t>Floating-leg day count</t>
         </is>
       </c>
-      <c r="B29" s="36" t="inlineStr">
+      <c r="B29" s="41" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
       </c>
-      <c r="C29" s="37" t="n"/>
-      <c r="D29" s="37" t="n"/>
-      <c r="E29" s="37" t="n"/>
-      <c r="F29" s="37" t="n"/>
+      <c r="C29" s="42" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="42" t="n"/>
+      <c r="F29" s="42" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -5327,15 +6861,15 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B30" s="36" t="inlineStr">
+      <c r="B30" s="41" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
       </c>
-      <c r="C30" s="37" t="n"/>
-      <c r="D30" s="37" t="n"/>
-      <c r="E30" s="37" t="n"/>
-      <c r="F30" s="37" t="n"/>
+      <c r="C30" s="42" t="n"/>
+      <c r="D30" s="42" t="n"/>
+      <c r="E30" s="42" t="n"/>
+      <c r="F30" s="42" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -5343,15 +6877,15 @@
           <t>SOFR compounding method</t>
         </is>
       </c>
-      <c r="B31" s="36" t="inlineStr">
+      <c r="B31" s="41" t="inlineStr">
         <is>
           <t>Daily compounded, ACT/360</t>
         </is>
       </c>
-      <c r="C31" s="37" t="n"/>
-      <c r="D31" s="37" t="n"/>
-      <c r="E31" s="37" t="n"/>
-      <c r="F31" s="37" t="n"/>
+      <c r="C31" s="42" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="42" t="n"/>
+      <c r="F31" s="42" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -5359,15 +6893,15 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B32" s="36" t="inlineStr">
+      <c r="B32" s="41" t="inlineStr">
         <is>
           <t>2 US business days</t>
         </is>
       </c>
-      <c r="C32" s="37" t="n"/>
-      <c r="D32" s="37" t="n"/>
-      <c r="E32" s="37" t="n"/>
-      <c r="F32" s="37" t="n"/>
+      <c r="C32" s="42" t="n"/>
+      <c r="D32" s="42" t="n"/>
+      <c r="E32" s="42" t="n"/>
+      <c r="F32" s="42" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -5375,15 +6909,15 @@
           <t>Observation shift / lookback</t>
         </is>
       </c>
-      <c r="B33" s="36" t="inlineStr">
+      <c r="B33" s="41" t="inlineStr">
         <is>
           <t>None (payment-delay convention, 2 bd)</t>
         </is>
       </c>
-      <c r="C33" s="37" t="n"/>
-      <c r="D33" s="37" t="n"/>
-      <c r="E33" s="37" t="n"/>
-      <c r="F33" s="37" t="n"/>
+      <c r="C33" s="42" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="42" t="n"/>
+      <c r="F33" s="42" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -5391,15 +6925,15 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B34" s="36" t="inlineStr">
+      <c r="B34" s="41" t="inlineStr">
         <is>
           <t>EOM applies</t>
         </is>
       </c>
-      <c r="C34" s="37" t="n"/>
-      <c r="D34" s="37" t="n"/>
-      <c r="E34" s="37" t="n"/>
-      <c r="F34" s="37" t="n"/>
+      <c r="C34" s="42" t="n"/>
+      <c r="D34" s="42" t="n"/>
+      <c r="E34" s="42" t="n"/>
+      <c r="F34" s="42" t="n"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="11" t="inlineStr">

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Futures" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_OIS_Quotes" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -29,13 +30,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
+    <numFmt numFmtId="168" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,6 +114,12 @@
       <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="9">
@@ -227,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -290,6 +298,26 @@
     <xf numFmtId="2" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="13" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -4208,20 +4236,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -4249,10 +4279,10 @@
         <v/>
       </c>
     </row>
-    <row r="5" ht="46" customHeight="1">
+    <row r="5" ht="58" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
         <is>
-          <t>Par-OIS recursive bootstrap on the quoted tenor grid:  DF_n = (1 − S_n·A_(n-1)) / (1 + S_n·τ_n),  with A_(n-1) = Σ τ_i·DF_i.  Exact for the sub-1Y money-market points and the annual 1Y–10Y section (pillars coincide with coupon dates); the sparse long end (12–50Y) uses the pillar grid AS the coupon schedule — a standard, transparent approximation (the openusdcurve engine does the exact interpolated-annuity build). Par rates are pulled live from the SOFR_OIS_Quotes mid column; paste Bloomberg S490 zero rates into column J for the Δz check.</t>
+          <t>Proper single-curve OIS bootstrap that respects the payment convention: OIS ≤ 1Y pay a SINGLE coupon at maturity → DF = 1/(1 + S·τ0); OIS ≥ 18M pay ANNUAL coupons → DF = (1 − S·A_prior)/(1 + S·τcoupon), where A_prior = Σ τ·DF over prior annual coupon dates (column I accumulates these; sub-annual and 18M rows add 0 so only annual pillars enter the annuity). Exact through 10Y; the sparse long end (12–50Y) uses the pillar grid as the coupon schedule. Every input reprices to par to ~0 bp. Par rates pull live from SOFR_OIS_Quotes; paste S490 zeros into column L for the Δz check.</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4305,7 @@
       </c>
       <c r="D7" s="20" t="inlineStr">
         <is>
-          <t>τ ACT/360</t>
+          <t>τ0 spot→mat</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -4285,30 +4315,40 @@
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>Annuity Στ·DF (prior)</t>
+          <t>τ coupon</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
         <is>
+          <t>Annuity A(prior)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="H7" s="20" t="inlineStr">
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Ann.add τ·DF</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
         <is>
           <t>Zero rate (%) cont.</t>
         </is>
       </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>Fwd rate (%) simple</t>
-        </is>
-      </c>
-      <c r="J7" s="20" t="inlineStr">
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>Fwd rate (%)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
         <is>
           <t>S490 zero (%) [paste]</t>
         </is>
       </c>
-      <c r="K7" s="20" t="inlineStr">
+      <c r="M7" s="20" t="inlineStr">
         <is>
           <t>Δ vs S490 (bp)</t>
         </is>
@@ -4336,24 +4376,28 @@
         <f>'SOFR_OIS_Quotes'!$G5</f>
         <v/>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="8" t="n"/>
+      <c r="G8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="32">
-        <f>(1-(E8/100)*F8)/(1+(E8/100)*D8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="21">
-        <f>-LN(G8)/C8*100</f>
-        <v/>
-      </c>
-      <c r="I8" s="21">
-        <f>(1/G8-1)/D8*100</f>
-        <v/>
-      </c>
-      <c r="J8" s="33" t="n"/>
-      <c r="K8" s="34">
-        <f>IF(J8="","",(H8-J8)*100)</f>
+      <c r="H8" s="32">
+        <f>1/(1+(E8/100)*D8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="21">
+        <f>-LN(H8)/C8*100</f>
+        <v/>
+      </c>
+      <c r="K8" s="21">
+        <f>(1/H8-1)/D8*100</f>
+        <v/>
+      </c>
+      <c r="L8" s="33" t="n"/>
+      <c r="M8" s="34">
+        <f>IF(L8="","",(J8-L8)*100)</f>
         <v/>
       </c>
     </row>
@@ -4372,32 +4416,36 @@
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>(B9-B8)/360</f>
+        <f>(B9-$B$4)/360</f>
         <v/>
       </c>
       <c r="E9" s="17">
         <f>'SOFR_OIS_Quotes'!$G6</f>
         <v/>
       </c>
-      <c r="F9" s="17">
-        <f>F8+D8*G8</f>
-        <v/>
-      </c>
-      <c r="G9" s="36">
-        <f>(1-(E9/100)*F9)/(1+(E9/100)*D9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>-LN(G9)/C9*100</f>
-        <v/>
-      </c>
-      <c r="I9" s="17">
-        <f>(G8/G9-1)/D9*100</f>
-        <v/>
-      </c>
-      <c r="J9" s="33" t="n"/>
-      <c r="K9" s="37">
-        <f>IF(J9="","",(H9-J9)*100)</f>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="17">
+        <f>SUM($I$8:I8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="36">
+        <f>1/(1+(E9/100)*D9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="17">
+        <f>-LN(H9)/C9*100</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>(H8/H9-1)/((B9-B8)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L9" s="33" t="n"/>
+      <c r="M9" s="37">
+        <f>IF(L9="","",(J9-L9)*100)</f>
         <v/>
       </c>
     </row>
@@ -4416,32 +4464,36 @@
         <v/>
       </c>
       <c r="D10" s="21">
-        <f>(B10-B9)/360</f>
+        <f>(B10-$B$4)/360</f>
         <v/>
       </c>
       <c r="E10" s="21">
         <f>'SOFR_OIS_Quotes'!$G7</f>
         <v/>
       </c>
-      <c r="F10" s="21">
-        <f>F9+D9*G9</f>
-        <v/>
-      </c>
-      <c r="G10" s="32">
-        <f>(1-(E10/100)*F10)/(1+(E10/100)*D10)</f>
-        <v/>
-      </c>
-      <c r="H10" s="21">
-        <f>-LN(G10)/C10*100</f>
-        <v/>
-      </c>
-      <c r="I10" s="21">
-        <f>(G9/G10-1)/D10*100</f>
-        <v/>
-      </c>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="34">
-        <f>IF(J10="","",(H10-J10)*100)</f>
+      <c r="F10" s="8" t="n"/>
+      <c r="G10" s="21">
+        <f>SUM($I$8:I9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="32">
+        <f>1/(1+(E10/100)*D10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <f>-LN(H10)/C10*100</f>
+        <v/>
+      </c>
+      <c r="K10" s="21">
+        <f>(H9/H10-1)/((B10-B9)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L10" s="33" t="n"/>
+      <c r="M10" s="34">
+        <f>IF(L10="","",(J10-L10)*100)</f>
         <v/>
       </c>
     </row>
@@ -4460,32 +4512,36 @@
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>(B11-B10)/360</f>
+        <f>(B11-$B$4)/360</f>
         <v/>
       </c>
       <c r="E11" s="17">
         <f>'SOFR_OIS_Quotes'!$G8</f>
         <v/>
       </c>
-      <c r="F11" s="17">
-        <f>F10+D10*G10</f>
-        <v/>
-      </c>
-      <c r="G11" s="36">
-        <f>(1-(E11/100)*F11)/(1+(E11/100)*D11)</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
-        <f>-LN(G11)/C11*100</f>
-        <v/>
-      </c>
-      <c r="I11" s="17">
-        <f>(G10/G11-1)/D11*100</f>
-        <v/>
-      </c>
-      <c r="J11" s="33" t="n"/>
-      <c r="K11" s="37">
-        <f>IF(J11="","",(H11-J11)*100)</f>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="17">
+        <f>SUM($I$8:I10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="36">
+        <f>1/(1+(E11/100)*D11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17">
+        <f>-LN(H11)/C11*100</f>
+        <v/>
+      </c>
+      <c r="K11" s="17">
+        <f>(H10/H11-1)/((B11-B10)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L11" s="33" t="n"/>
+      <c r="M11" s="37">
+        <f>IF(L11="","",(J11-L11)*100)</f>
         <v/>
       </c>
     </row>
@@ -4504,32 +4560,36 @@
         <v/>
       </c>
       <c r="D12" s="21">
-        <f>(B12-B11)/360</f>
+        <f>(B12-$B$4)/360</f>
         <v/>
       </c>
       <c r="E12" s="21">
         <f>'SOFR_OIS_Quotes'!$G9</f>
         <v/>
       </c>
-      <c r="F12" s="21">
-        <f>F11+D11*G11</f>
-        <v/>
-      </c>
-      <c r="G12" s="32">
-        <f>(1-(E12/100)*F12)/(1+(E12/100)*D12)</f>
-        <v/>
-      </c>
-      <c r="H12" s="21">
-        <f>-LN(G12)/C12*100</f>
-        <v/>
-      </c>
-      <c r="I12" s="21">
-        <f>(G11/G12-1)/D12*100</f>
-        <v/>
-      </c>
-      <c r="J12" s="33" t="n"/>
-      <c r="K12" s="34">
-        <f>IF(J12="","",(H12-J12)*100)</f>
+      <c r="F12" s="8" t="n"/>
+      <c r="G12" s="21">
+        <f>SUM($I$8:I11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="32">
+        <f>1/(1+(E12/100)*D12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21">
+        <f>-LN(H12)/C12*100</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>(H11/H12-1)/((B12-B11)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L12" s="33" t="n"/>
+      <c r="M12" s="34">
+        <f>IF(L12="","",(J12-L12)*100)</f>
         <v/>
       </c>
     </row>
@@ -4548,32 +4608,36 @@
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>(B13-B12)/360</f>
+        <f>(B13-$B$4)/360</f>
         <v/>
       </c>
       <c r="E13" s="17">
         <f>'SOFR_OIS_Quotes'!$G10</f>
         <v/>
       </c>
-      <c r="F13" s="17">
-        <f>F12+D12*G12</f>
-        <v/>
-      </c>
-      <c r="G13" s="36">
-        <f>(1-(E13/100)*F13)/(1+(E13/100)*D13)</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>-LN(G13)/C13*100</f>
-        <v/>
-      </c>
-      <c r="I13" s="17">
-        <f>(G12/G13-1)/D13*100</f>
-        <v/>
-      </c>
-      <c r="J13" s="33" t="n"/>
-      <c r="K13" s="37">
-        <f>IF(J13="","",(H13-J13)*100)</f>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="17">
+        <f>SUM($I$8:I12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="36">
+        <f>1/(1+(E13/100)*D13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <f>-LN(H13)/C13*100</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>(H12/H13-1)/((B13-B12)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L13" s="33" t="n"/>
+      <c r="M13" s="37">
+        <f>IF(L13="","",(J13-L13)*100)</f>
         <v/>
       </c>
     </row>
@@ -4592,32 +4656,36 @@
         <v/>
       </c>
       <c r="D14" s="21">
-        <f>(B14-B13)/360</f>
+        <f>(B14-$B$4)/360</f>
         <v/>
       </c>
       <c r="E14" s="21">
         <f>'SOFR_OIS_Quotes'!$G11</f>
         <v/>
       </c>
-      <c r="F14" s="21">
-        <f>F13+D13*G13</f>
-        <v/>
-      </c>
-      <c r="G14" s="32">
-        <f>(1-(E14/100)*F14)/(1+(E14/100)*D14)</f>
-        <v/>
-      </c>
-      <c r="H14" s="21">
-        <f>-LN(G14)/C14*100</f>
-        <v/>
-      </c>
-      <c r="I14" s="21">
-        <f>(G13/G14-1)/D14*100</f>
-        <v/>
-      </c>
-      <c r="J14" s="33" t="n"/>
-      <c r="K14" s="34">
-        <f>IF(J14="","",(H14-J14)*100)</f>
+      <c r="F14" s="8" t="n"/>
+      <c r="G14" s="21">
+        <f>SUM($I$8:I13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="32">
+        <f>1/(1+(E14/100)*D14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <f>-LN(H14)/C14*100</f>
+        <v/>
+      </c>
+      <c r="K14" s="21">
+        <f>(H13/H14-1)/((B14-B13)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L14" s="33" t="n"/>
+      <c r="M14" s="34">
+        <f>IF(L14="","",(J14-L14)*100)</f>
         <v/>
       </c>
     </row>
@@ -4636,32 +4704,36 @@
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>(B15-B14)/360</f>
+        <f>(B15-$B$4)/360</f>
         <v/>
       </c>
       <c r="E15" s="17">
         <f>'SOFR_OIS_Quotes'!$G12</f>
         <v/>
       </c>
-      <c r="F15" s="17">
-        <f>F14+D14*G14</f>
-        <v/>
-      </c>
-      <c r="G15" s="36">
-        <f>(1-(E15/100)*F15)/(1+(E15/100)*D15)</f>
-        <v/>
-      </c>
-      <c r="H15" s="17">
-        <f>-LN(G15)/C15*100</f>
-        <v/>
-      </c>
-      <c r="I15" s="17">
-        <f>(G14/G15-1)/D15*100</f>
-        <v/>
-      </c>
-      <c r="J15" s="33" t="n"/>
-      <c r="K15" s="37">
-        <f>IF(J15="","",(H15-J15)*100)</f>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="17">
+        <f>SUM($I$8:I14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="36">
+        <f>1/(1+(E15/100)*D15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17">
+        <f>-LN(H15)/C15*100</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>(H14/H15-1)/((B15-B14)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L15" s="33" t="n"/>
+      <c r="M15" s="37">
+        <f>IF(L15="","",(J15-L15)*100)</f>
         <v/>
       </c>
     </row>
@@ -4680,32 +4752,36 @@
         <v/>
       </c>
       <c r="D16" s="21">
-        <f>(B16-B15)/360</f>
+        <f>(B16-$B$4)/360</f>
         <v/>
       </c>
       <c r="E16" s="21">
         <f>'SOFR_OIS_Quotes'!$G13</f>
         <v/>
       </c>
-      <c r="F16" s="21">
-        <f>F15+D15*G15</f>
-        <v/>
-      </c>
-      <c r="G16" s="32">
-        <f>(1-(E16/100)*F16)/(1+(E16/100)*D16)</f>
-        <v/>
-      </c>
-      <c r="H16" s="21">
-        <f>-LN(G16)/C16*100</f>
-        <v/>
-      </c>
-      <c r="I16" s="21">
-        <f>(G15/G16-1)/D16*100</f>
-        <v/>
-      </c>
-      <c r="J16" s="33" t="n"/>
-      <c r="K16" s="34">
-        <f>IF(J16="","",(H16-J16)*100)</f>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="21">
+        <f>SUM($I$8:I15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="32">
+        <f>1/(1+(E16/100)*D16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="21">
+        <f>-LN(H16)/C16*100</f>
+        <v/>
+      </c>
+      <c r="K16" s="21">
+        <f>(H15/H16-1)/((B16-B15)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L16" s="33" t="n"/>
+      <c r="M16" s="34">
+        <f>IF(L16="","",(J16-L16)*100)</f>
         <v/>
       </c>
     </row>
@@ -4724,32 +4800,36 @@
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>(B17-B16)/360</f>
+        <f>(B17-$B$4)/360</f>
         <v/>
       </c>
       <c r="E17" s="17">
         <f>'SOFR_OIS_Quotes'!$G14</f>
         <v/>
       </c>
-      <c r="F17" s="17">
-        <f>F16+D16*G16</f>
-        <v/>
-      </c>
-      <c r="G17" s="36">
-        <f>(1-(E17/100)*F17)/(1+(E17/100)*D17)</f>
-        <v/>
-      </c>
-      <c r="H17" s="17">
-        <f>-LN(G17)/C17*100</f>
-        <v/>
-      </c>
-      <c r="I17" s="17">
-        <f>(G16/G17-1)/D17*100</f>
-        <v/>
-      </c>
-      <c r="J17" s="33" t="n"/>
-      <c r="K17" s="37">
-        <f>IF(J17="","",(H17-J17)*100)</f>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="17">
+        <f>SUM($I$8:I16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="36">
+        <f>1/(1+(E17/100)*D17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="17">
+        <f>-LN(H17)/C17*100</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>(H16/H17-1)/((B17-B16)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L17" s="33" t="n"/>
+      <c r="M17" s="37">
+        <f>IF(L17="","",(J17-L17)*100)</f>
         <v/>
       </c>
     </row>
@@ -4768,32 +4848,36 @@
         <v/>
       </c>
       <c r="D18" s="21">
-        <f>(B18-B17)/360</f>
+        <f>(B18-$B$4)/360</f>
         <v/>
       </c>
       <c r="E18" s="21">
         <f>'SOFR_OIS_Quotes'!$G15</f>
         <v/>
       </c>
-      <c r="F18" s="21">
-        <f>F17+D17*G17</f>
-        <v/>
-      </c>
-      <c r="G18" s="32">
-        <f>(1-(E18/100)*F18)/(1+(E18/100)*D18)</f>
-        <v/>
-      </c>
-      <c r="H18" s="21">
-        <f>-LN(G18)/C18*100</f>
-        <v/>
-      </c>
-      <c r="I18" s="21">
-        <f>(G17/G18-1)/D18*100</f>
-        <v/>
-      </c>
-      <c r="J18" s="33" t="n"/>
-      <c r="K18" s="34">
-        <f>IF(J18="","",(H18-J18)*100)</f>
+      <c r="F18" s="8" t="n"/>
+      <c r="G18" s="21">
+        <f>SUM($I$8:I17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="32">
+        <f>1/(1+(E18/100)*D18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="21">
+        <f>-LN(H18)/C18*100</f>
+        <v/>
+      </c>
+      <c r="K18" s="21">
+        <f>(H17/H18-1)/((B18-B17)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L18" s="33" t="n"/>
+      <c r="M18" s="34">
+        <f>IF(L18="","",(J18-L18)*100)</f>
         <v/>
       </c>
     </row>
@@ -4812,32 +4896,36 @@
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>(B19-B18)/360</f>
+        <f>(B19-$B$4)/360</f>
         <v/>
       </c>
       <c r="E19" s="17">
         <f>'SOFR_OIS_Quotes'!$G16</f>
         <v/>
       </c>
-      <c r="F19" s="17">
-        <f>F18+D18*G18</f>
-        <v/>
-      </c>
-      <c r="G19" s="36">
-        <f>(1-(E19/100)*F19)/(1+(E19/100)*D19)</f>
-        <v/>
-      </c>
-      <c r="H19" s="17">
-        <f>-LN(G19)/C19*100</f>
-        <v/>
-      </c>
-      <c r="I19" s="17">
-        <f>(G18/G19-1)/D19*100</f>
-        <v/>
-      </c>
-      <c r="J19" s="33" t="n"/>
-      <c r="K19" s="37">
-        <f>IF(J19="","",(H19-J19)*100)</f>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="17">
+        <f>SUM($I$8:I18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="36">
+        <f>1/(1+(E19/100)*D19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="17">
+        <f>-LN(H19)/C19*100</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>(H18/H19-1)/((B19-B18)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L19" s="33" t="n"/>
+      <c r="M19" s="37">
+        <f>IF(L19="","",(J19-L19)*100)</f>
         <v/>
       </c>
     </row>
@@ -4856,32 +4944,36 @@
         <v/>
       </c>
       <c r="D20" s="21">
-        <f>(B20-B19)/360</f>
+        <f>(B20-$B$4)/360</f>
         <v/>
       </c>
       <c r="E20" s="21">
         <f>'SOFR_OIS_Quotes'!$G17</f>
         <v/>
       </c>
-      <c r="F20" s="21">
-        <f>F19+D19*G19</f>
-        <v/>
-      </c>
-      <c r="G20" s="32">
-        <f>(1-(E20/100)*F20)/(1+(E20/100)*D20)</f>
-        <v/>
-      </c>
-      <c r="H20" s="21">
-        <f>-LN(G20)/C20*100</f>
-        <v/>
-      </c>
-      <c r="I20" s="21">
-        <f>(G19/G20-1)/D20*100</f>
-        <v/>
-      </c>
-      <c r="J20" s="33" t="n"/>
-      <c r="K20" s="34">
-        <f>IF(J20="","",(H20-J20)*100)</f>
+      <c r="F20" s="8" t="n"/>
+      <c r="G20" s="21">
+        <f>SUM($I$8:I19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="32">
+        <f>1/(1+(E20/100)*D20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="21">
+        <f>-LN(H20)/C20*100</f>
+        <v/>
+      </c>
+      <c r="K20" s="21">
+        <f>(H19/H20-1)/((B20-B19)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L20" s="33" t="n"/>
+      <c r="M20" s="34">
+        <f>IF(L20="","",(J20-L20)*100)</f>
         <v/>
       </c>
     </row>
@@ -4900,32 +4992,36 @@
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>(B21-B20)/360</f>
+        <f>(B21-$B$4)/360</f>
         <v/>
       </c>
       <c r="E21" s="17">
         <f>'SOFR_OIS_Quotes'!$G18</f>
         <v/>
       </c>
-      <c r="F21" s="17">
-        <f>F20+D20*G20</f>
-        <v/>
-      </c>
-      <c r="G21" s="36">
-        <f>(1-(E21/100)*F21)/(1+(E21/100)*D21)</f>
-        <v/>
-      </c>
-      <c r="H21" s="17">
-        <f>-LN(G21)/C21*100</f>
-        <v/>
-      </c>
-      <c r="I21" s="17">
-        <f>(G20/G21-1)/D21*100</f>
-        <v/>
-      </c>
-      <c r="J21" s="33" t="n"/>
-      <c r="K21" s="37">
-        <f>IF(J21="","",(H21-J21)*100)</f>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="17">
+        <f>SUM($I$8:I20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="36">
+        <f>1/(1+(E21/100)*D21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="17">
+        <f>-LN(H21)/C21*100</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>(H20/H21-1)/((B21-B20)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L21" s="33" t="n"/>
+      <c r="M21" s="37">
+        <f>IF(L21="","",(J21-L21)*100)</f>
         <v/>
       </c>
     </row>
@@ -4944,7 +5040,7 @@
         <v/>
       </c>
       <c r="D22" s="21">
-        <f>(B22-B21)/360</f>
+        <f>(B22-$B$4)/360</f>
         <v/>
       </c>
       <c r="E22" s="21">
@@ -4952,24 +5048,32 @@
         <v/>
       </c>
       <c r="F22" s="21">
-        <f>F21+D21*G21</f>
-        <v/>
-      </c>
-      <c r="G22" s="32">
-        <f>(1-(E22/100)*F22)/(1+(E22/100)*D22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="21">
-        <f>-LN(G22)/C22*100</f>
+        <f>(B22-$B$4)/360</f>
+        <v/>
+      </c>
+      <c r="G22" s="21">
+        <f>SUM($I$8:I21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="32">
+        <f>1/(1+(E22/100)*D22)</f>
         <v/>
       </c>
       <c r="I22" s="21">
-        <f>(G21/G22-1)/D22*100</f>
-        <v/>
-      </c>
-      <c r="J22" s="33" t="n"/>
-      <c r="K22" s="34">
-        <f>IF(J22="","",(H22-J22)*100)</f>
+        <f>F22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="21">
+        <f>-LN(H22)/C22*100</f>
+        <v/>
+      </c>
+      <c r="K22" s="21">
+        <f>(H21/H22-1)/((B22-B21)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L22" s="33" t="n"/>
+      <c r="M22" s="34">
+        <f>IF(L22="","",(J22-L22)*100)</f>
         <v/>
       </c>
     </row>
@@ -4988,7 +5092,7 @@
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>(B23-B22)/360</f>
+        <f>(B23-$B$4)/360</f>
         <v/>
       </c>
       <c r="E23" s="17">
@@ -4996,24 +5100,31 @@
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>F22+D22*G22</f>
-        <v/>
-      </c>
-      <c r="G23" s="36">
-        <f>(1-(E23/100)*F23)/(1+(E23/100)*D23)</f>
-        <v/>
-      </c>
-      <c r="H23" s="17">
-        <f>-LN(G23)/C23*100</f>
-        <v/>
-      </c>
-      <c r="I23" s="17">
-        <f>(G22/G23-1)/D23*100</f>
-        <v/>
-      </c>
-      <c r="J23" s="33" t="n"/>
-      <c r="K23" s="37">
-        <f>IF(J23="","",(H23-J23)*100)</f>
+        <f>(B23-$B$22)/360</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>SUM($I$8:I22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="36">
+        <f>(1-(E23/100)*G23)/(1+(E23/100)*F23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="17">
+        <f>-LN(H23)/C23*100</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>(H22/H23-1)/((B23-B22)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L23" s="33" t="n"/>
+      <c r="M23" s="37">
+        <f>IF(L23="","",(J23-L23)*100)</f>
         <v/>
       </c>
     </row>
@@ -5032,7 +5143,7 @@
         <v/>
       </c>
       <c r="D24" s="21">
-        <f>(B24-B23)/360</f>
+        <f>(B24-$B$4)/360</f>
         <v/>
       </c>
       <c r="E24" s="21">
@@ -5040,24 +5151,32 @@
         <v/>
       </c>
       <c r="F24" s="21">
-        <f>F23+D23*G23</f>
-        <v/>
-      </c>
-      <c r="G24" s="32">
-        <f>(1-(E24/100)*F24)/(1+(E24/100)*D24)</f>
-        <v/>
-      </c>
-      <c r="H24" s="21">
-        <f>-LN(G24)/C24*100</f>
+        <f>(B24-$B$22)/360</f>
+        <v/>
+      </c>
+      <c r="G24" s="21">
+        <f>SUM($I$8:I23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="32">
+        <f>(1-(E24/100)*G24)/(1+(E24/100)*F24)</f>
         <v/>
       </c>
       <c r="I24" s="21">
-        <f>(G23/G24-1)/D24*100</f>
-        <v/>
-      </c>
-      <c r="J24" s="33" t="n"/>
-      <c r="K24" s="34">
-        <f>IF(J24="","",(H24-J24)*100)</f>
+        <f>F24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="21">
+        <f>-LN(H24)/C24*100</f>
+        <v/>
+      </c>
+      <c r="K24" s="21">
+        <f>(H23/H24-1)/((B24-B23)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="34">
+        <f>IF(L24="","",(J24-L24)*100)</f>
         <v/>
       </c>
     </row>
@@ -5076,7 +5195,7 @@
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>(B25-B24)/360</f>
+        <f>(B25-$B$4)/360</f>
         <v/>
       </c>
       <c r="E25" s="17">
@@ -5084,24 +5203,32 @@
         <v/>
       </c>
       <c r="F25" s="17">
-        <f>F24+D24*G24</f>
-        <v/>
-      </c>
-      <c r="G25" s="36">
-        <f>(1-(E25/100)*F25)/(1+(E25/100)*D25)</f>
-        <v/>
-      </c>
-      <c r="H25" s="17">
-        <f>-LN(G25)/C25*100</f>
+        <f>(B25-$B$24)/360</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>SUM($I$8:I24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="36">
+        <f>(1-(E25/100)*G25)/(1+(E25/100)*F25)</f>
         <v/>
       </c>
       <c r="I25" s="17">
-        <f>(G24/G25-1)/D25*100</f>
-        <v/>
-      </c>
-      <c r="J25" s="33" t="n"/>
-      <c r="K25" s="37">
-        <f>IF(J25="","",(H25-J25)*100)</f>
+        <f>F25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>-LN(H25)/C25*100</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>(H24/H25-1)/((B25-B24)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L25" s="33" t="n"/>
+      <c r="M25" s="37">
+        <f>IF(L25="","",(J25-L25)*100)</f>
         <v/>
       </c>
     </row>
@@ -5120,7 +5247,7 @@
         <v/>
       </c>
       <c r="D26" s="21">
-        <f>(B26-B25)/360</f>
+        <f>(B26-$B$4)/360</f>
         <v/>
       </c>
       <c r="E26" s="21">
@@ -5128,24 +5255,32 @@
         <v/>
       </c>
       <c r="F26" s="21">
-        <f>F25+D25*G25</f>
-        <v/>
-      </c>
-      <c r="G26" s="32">
-        <f>(1-(E26/100)*F26)/(1+(E26/100)*D26)</f>
-        <v/>
-      </c>
-      <c r="H26" s="21">
-        <f>-LN(G26)/C26*100</f>
+        <f>(B26-$B$25)/360</f>
+        <v/>
+      </c>
+      <c r="G26" s="21">
+        <f>SUM($I$8:I25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="32">
+        <f>(1-(E26/100)*G26)/(1+(E26/100)*F26)</f>
         <v/>
       </c>
       <c r="I26" s="21">
-        <f>(G25/G26-1)/D26*100</f>
-        <v/>
-      </c>
-      <c r="J26" s="33" t="n"/>
-      <c r="K26" s="34">
-        <f>IF(J26="","",(H26-J26)*100)</f>
+        <f>F26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="21">
+        <f>-LN(H26)/C26*100</f>
+        <v/>
+      </c>
+      <c r="K26" s="21">
+        <f>(H25/H26-1)/((B26-B25)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L26" s="33" t="n"/>
+      <c r="M26" s="34">
+        <f>IF(L26="","",(J26-L26)*100)</f>
         <v/>
       </c>
     </row>
@@ -5164,7 +5299,7 @@
         <v/>
       </c>
       <c r="D27" s="17">
-        <f>(B27-B26)/360</f>
+        <f>(B27-$B$4)/360</f>
         <v/>
       </c>
       <c r="E27" s="17">
@@ -5172,24 +5307,32 @@
         <v/>
       </c>
       <c r="F27" s="17">
-        <f>F26+D26*G26</f>
-        <v/>
-      </c>
-      <c r="G27" s="36">
-        <f>(1-(E27/100)*F27)/(1+(E27/100)*D27)</f>
-        <v/>
-      </c>
-      <c r="H27" s="17">
-        <f>-LN(G27)/C27*100</f>
+        <f>(B27-$B$26)/360</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>SUM($I$8:I26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="36">
+        <f>(1-(E27/100)*G27)/(1+(E27/100)*F27)</f>
         <v/>
       </c>
       <c r="I27" s="17">
-        <f>(G26/G27-1)/D27*100</f>
-        <v/>
-      </c>
-      <c r="J27" s="33" t="n"/>
-      <c r="K27" s="37">
-        <f>IF(J27="","",(H27-J27)*100)</f>
+        <f>F27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="17">
+        <f>-LN(H27)/C27*100</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>(H26/H27-1)/((B27-B26)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L27" s="33" t="n"/>
+      <c r="M27" s="37">
+        <f>IF(L27="","",(J27-L27)*100)</f>
         <v/>
       </c>
     </row>
@@ -5208,7 +5351,7 @@
         <v/>
       </c>
       <c r="D28" s="21">
-        <f>(B28-B27)/360</f>
+        <f>(B28-$B$4)/360</f>
         <v/>
       </c>
       <c r="E28" s="21">
@@ -5216,24 +5359,32 @@
         <v/>
       </c>
       <c r="F28" s="21">
-        <f>F27+D27*G27</f>
-        <v/>
-      </c>
-      <c r="G28" s="32">
-        <f>(1-(E28/100)*F28)/(1+(E28/100)*D28)</f>
-        <v/>
-      </c>
-      <c r="H28" s="21">
-        <f>-LN(G28)/C28*100</f>
+        <f>(B28-$B$27)/360</f>
+        <v/>
+      </c>
+      <c r="G28" s="21">
+        <f>SUM($I$8:I27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="32">
+        <f>(1-(E28/100)*G28)/(1+(E28/100)*F28)</f>
         <v/>
       </c>
       <c r="I28" s="21">
-        <f>(G27/G28-1)/D28*100</f>
-        <v/>
-      </c>
-      <c r="J28" s="33" t="n"/>
-      <c r="K28" s="34">
-        <f>IF(J28="","",(H28-J28)*100)</f>
+        <f>F28*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="21">
+        <f>-LN(H28)/C28*100</f>
+        <v/>
+      </c>
+      <c r="K28" s="21">
+        <f>(H27/H28-1)/((B28-B27)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L28" s="33" t="n"/>
+      <c r="M28" s="34">
+        <f>IF(L28="","",(J28-L28)*100)</f>
         <v/>
       </c>
     </row>
@@ -5252,7 +5403,7 @@
         <v/>
       </c>
       <c r="D29" s="17">
-        <f>(B29-B28)/360</f>
+        <f>(B29-$B$4)/360</f>
         <v/>
       </c>
       <c r="E29" s="17">
@@ -5260,24 +5411,32 @@
         <v/>
       </c>
       <c r="F29" s="17">
-        <f>F28+D28*G28</f>
-        <v/>
-      </c>
-      <c r="G29" s="36">
-        <f>(1-(E29/100)*F29)/(1+(E29/100)*D29)</f>
-        <v/>
-      </c>
-      <c r="H29" s="17">
-        <f>-LN(G29)/C29*100</f>
+        <f>(B29-$B$28)/360</f>
+        <v/>
+      </c>
+      <c r="G29" s="17">
+        <f>SUM($I$8:I28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="36">
+        <f>(1-(E29/100)*G29)/(1+(E29/100)*F29)</f>
         <v/>
       </c>
       <c r="I29" s="17">
-        <f>(G28/G29-1)/D29*100</f>
-        <v/>
-      </c>
-      <c r="J29" s="33" t="n"/>
-      <c r="K29" s="37">
-        <f>IF(J29="","",(H29-J29)*100)</f>
+        <f>F29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>-LN(H29)/C29*100</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>(H28/H29-1)/((B29-B28)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L29" s="33" t="n"/>
+      <c r="M29" s="37">
+        <f>IF(L29="","",(J29-L29)*100)</f>
         <v/>
       </c>
     </row>
@@ -5296,7 +5455,7 @@
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>(B30-B29)/360</f>
+        <f>(B30-$B$4)/360</f>
         <v/>
       </c>
       <c r="E30" s="21">
@@ -5304,24 +5463,32 @@
         <v/>
       </c>
       <c r="F30" s="21">
-        <f>F29+D29*G29</f>
-        <v/>
-      </c>
-      <c r="G30" s="32">
-        <f>(1-(E30/100)*F30)/(1+(E30/100)*D30)</f>
-        <v/>
-      </c>
-      <c r="H30" s="21">
-        <f>-LN(G30)/C30*100</f>
+        <f>(B30-$B$29)/360</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f>SUM($I$8:I29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="32">
+        <f>(1-(E30/100)*G30)/(1+(E30/100)*F30)</f>
         <v/>
       </c>
       <c r="I30" s="21">
-        <f>(G29/G30-1)/D30*100</f>
-        <v/>
-      </c>
-      <c r="J30" s="33" t="n"/>
-      <c r="K30" s="34">
-        <f>IF(J30="","",(H30-J30)*100)</f>
+        <f>F30*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="21">
+        <f>-LN(H30)/C30*100</f>
+        <v/>
+      </c>
+      <c r="K30" s="21">
+        <f>(H29/H30-1)/((B30-B29)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L30" s="33" t="n"/>
+      <c r="M30" s="34">
+        <f>IF(L30="","",(J30-L30)*100)</f>
         <v/>
       </c>
     </row>
@@ -5340,7 +5507,7 @@
         <v/>
       </c>
       <c r="D31" s="17">
-        <f>(B31-B30)/360</f>
+        <f>(B31-$B$4)/360</f>
         <v/>
       </c>
       <c r="E31" s="17">
@@ -5348,24 +5515,32 @@
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>F30+D30*G30</f>
-        <v/>
-      </c>
-      <c r="G31" s="36">
-        <f>(1-(E31/100)*F31)/(1+(E31/100)*D31)</f>
-        <v/>
-      </c>
-      <c r="H31" s="17">
-        <f>-LN(G31)/C31*100</f>
+        <f>(B31-$B$30)/360</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>SUM($I$8:I30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="36">
+        <f>(1-(E31/100)*G31)/(1+(E31/100)*F31)</f>
         <v/>
       </c>
       <c r="I31" s="17">
-        <f>(G30/G31-1)/D31*100</f>
-        <v/>
-      </c>
-      <c r="J31" s="33" t="n"/>
-      <c r="K31" s="37">
-        <f>IF(J31="","",(H31-J31)*100)</f>
+        <f>F31*H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>-LN(H31)/C31*100</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>(H30/H31-1)/((B31-B30)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L31" s="33" t="n"/>
+      <c r="M31" s="37">
+        <f>IF(L31="","",(J31-L31)*100)</f>
         <v/>
       </c>
     </row>
@@ -5384,7 +5559,7 @@
         <v/>
       </c>
       <c r="D32" s="21">
-        <f>(B32-B31)/360</f>
+        <f>(B32-$B$4)/360</f>
         <v/>
       </c>
       <c r="E32" s="21">
@@ -5392,24 +5567,32 @@
         <v/>
       </c>
       <c r="F32" s="21">
-        <f>F31+D31*G31</f>
-        <v/>
-      </c>
-      <c r="G32" s="32">
-        <f>(1-(E32/100)*F32)/(1+(E32/100)*D32)</f>
-        <v/>
-      </c>
-      <c r="H32" s="21">
-        <f>-LN(G32)/C32*100</f>
+        <f>(B32-$B$31)/360</f>
+        <v/>
+      </c>
+      <c r="G32" s="21">
+        <f>SUM($I$8:I31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="32">
+        <f>(1-(E32/100)*G32)/(1+(E32/100)*F32)</f>
         <v/>
       </c>
       <c r="I32" s="21">
-        <f>(G31/G32-1)/D32*100</f>
-        <v/>
-      </c>
-      <c r="J32" s="33" t="n"/>
-      <c r="K32" s="34">
-        <f>IF(J32="","",(H32-J32)*100)</f>
+        <f>F32*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="21">
+        <f>-LN(H32)/C32*100</f>
+        <v/>
+      </c>
+      <c r="K32" s="21">
+        <f>(H31/H32-1)/((B32-B31)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L32" s="33" t="n"/>
+      <c r="M32" s="34">
+        <f>IF(L32="","",(J32-L32)*100)</f>
         <v/>
       </c>
     </row>
@@ -5428,7 +5611,7 @@
         <v/>
       </c>
       <c r="D33" s="17">
-        <f>(B33-B32)/360</f>
+        <f>(B33-$B$4)/360</f>
         <v/>
       </c>
       <c r="E33" s="17">
@@ -5436,24 +5619,32 @@
         <v/>
       </c>
       <c r="F33" s="17">
-        <f>F32+D32*G32</f>
-        <v/>
-      </c>
-      <c r="G33" s="36">
-        <f>(1-(E33/100)*F33)/(1+(E33/100)*D33)</f>
-        <v/>
-      </c>
-      <c r="H33" s="17">
-        <f>-LN(G33)/C33*100</f>
+        <f>(B33-$B$32)/360</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>SUM($I$8:I32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="36">
+        <f>(1-(E33/100)*G33)/(1+(E33/100)*F33)</f>
         <v/>
       </c>
       <c r="I33" s="17">
-        <f>(G32/G33-1)/D33*100</f>
-        <v/>
-      </c>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="37">
-        <f>IF(J33="","",(H33-J33)*100)</f>
+        <f>F33*H33</f>
+        <v/>
+      </c>
+      <c r="J33" s="17">
+        <f>-LN(H33)/C33*100</f>
+        <v/>
+      </c>
+      <c r="K33" s="17">
+        <f>(H32/H33-1)/((B33-B32)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L33" s="33" t="n"/>
+      <c r="M33" s="37">
+        <f>IF(L33="","",(J33-L33)*100)</f>
         <v/>
       </c>
     </row>
@@ -5472,7 +5663,7 @@
         <v/>
       </c>
       <c r="D34" s="21">
-        <f>(B34-B33)/360</f>
+        <f>(B34-$B$4)/360</f>
         <v/>
       </c>
       <c r="E34" s="21">
@@ -5480,24 +5671,32 @@
         <v/>
       </c>
       <c r="F34" s="21">
-        <f>F33+D33*G33</f>
-        <v/>
-      </c>
-      <c r="G34" s="32">
-        <f>(1-(E34/100)*F34)/(1+(E34/100)*D34)</f>
-        <v/>
-      </c>
-      <c r="H34" s="21">
-        <f>-LN(G34)/C34*100</f>
+        <f>(B34-$B$33)/360</f>
+        <v/>
+      </c>
+      <c r="G34" s="21">
+        <f>SUM($I$8:I33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="32">
+        <f>(1-(E34/100)*G34)/(1+(E34/100)*F34)</f>
         <v/>
       </c>
       <c r="I34" s="21">
-        <f>(G33/G34-1)/D34*100</f>
-        <v/>
-      </c>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="34">
-        <f>IF(J34="","",(H34-J34)*100)</f>
+        <f>F34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="21">
+        <f>-LN(H34)/C34*100</f>
+        <v/>
+      </c>
+      <c r="K34" s="21">
+        <f>(H33/H34-1)/((B34-B33)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L34" s="33" t="n"/>
+      <c r="M34" s="34">
+        <f>IF(L34="","",(J34-L34)*100)</f>
         <v/>
       </c>
     </row>
@@ -5516,7 +5715,7 @@
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>(B35-B34)/360</f>
+        <f>(B35-$B$4)/360</f>
         <v/>
       </c>
       <c r="E35" s="17">
@@ -5524,24 +5723,32 @@
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>F34+D34*G34</f>
-        <v/>
-      </c>
-      <c r="G35" s="36">
-        <f>(1-(E35/100)*F35)/(1+(E35/100)*D35)</f>
-        <v/>
-      </c>
-      <c r="H35" s="17">
-        <f>-LN(G35)/C35*100</f>
+        <f>(B35-$B$34)/360</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>SUM($I$8:I34)</f>
+        <v/>
+      </c>
+      <c r="H35" s="36">
+        <f>(1-(E35/100)*G35)/(1+(E35/100)*F35)</f>
         <v/>
       </c>
       <c r="I35" s="17">
-        <f>(G34/G35-1)/D35*100</f>
-        <v/>
-      </c>
-      <c r="J35" s="33" t="n"/>
-      <c r="K35" s="37">
-        <f>IF(J35="","",(H35-J35)*100)</f>
+        <f>F35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="17">
+        <f>-LN(H35)/C35*100</f>
+        <v/>
+      </c>
+      <c r="K35" s="17">
+        <f>(H34/H35-1)/((B35-B34)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L35" s="33" t="n"/>
+      <c r="M35" s="37">
+        <f>IF(L35="","",(J35-L35)*100)</f>
         <v/>
       </c>
     </row>
@@ -5560,7 +5767,7 @@
         <v/>
       </c>
       <c r="D36" s="21">
-        <f>(B36-B35)/360</f>
+        <f>(B36-$B$4)/360</f>
         <v/>
       </c>
       <c r="E36" s="21">
@@ -5568,24 +5775,32 @@
         <v/>
       </c>
       <c r="F36" s="21">
-        <f>F35+D35*G35</f>
-        <v/>
-      </c>
-      <c r="G36" s="32">
-        <f>(1-(E36/100)*F36)/(1+(E36/100)*D36)</f>
-        <v/>
-      </c>
-      <c r="H36" s="21">
-        <f>-LN(G36)/C36*100</f>
+        <f>(B36-$B$35)/360</f>
+        <v/>
+      </c>
+      <c r="G36" s="21">
+        <f>SUM($I$8:I35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="32">
+        <f>(1-(E36/100)*G36)/(1+(E36/100)*F36)</f>
         <v/>
       </c>
       <c r="I36" s="21">
-        <f>(G35/G36-1)/D36*100</f>
-        <v/>
-      </c>
-      <c r="J36" s="33" t="n"/>
-      <c r="K36" s="34">
-        <f>IF(J36="","",(H36-J36)*100)</f>
+        <f>F36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="21">
+        <f>-LN(H36)/C36*100</f>
+        <v/>
+      </c>
+      <c r="K36" s="21">
+        <f>(H35/H36-1)/((B36-B35)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L36" s="33" t="n"/>
+      <c r="M36" s="34">
+        <f>IF(L36="","",(J36-L36)*100)</f>
         <v/>
       </c>
     </row>
@@ -5604,7 +5819,7 @@
         <v/>
       </c>
       <c r="D37" s="17">
-        <f>(B37-B36)/360</f>
+        <f>(B37-$B$4)/360</f>
         <v/>
       </c>
       <c r="E37" s="17">
@@ -5612,24 +5827,32 @@
         <v/>
       </c>
       <c r="F37" s="17">
-        <f>F36+D36*G36</f>
-        <v/>
-      </c>
-      <c r="G37" s="36">
-        <f>(1-(E37/100)*F37)/(1+(E37/100)*D37)</f>
-        <v/>
-      </c>
-      <c r="H37" s="17">
-        <f>-LN(G37)/C37*100</f>
+        <f>(B37-$B$36)/360</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>SUM($I$8:I36)</f>
+        <v/>
+      </c>
+      <c r="H37" s="36">
+        <f>(1-(E37/100)*G37)/(1+(E37/100)*F37)</f>
         <v/>
       </c>
       <c r="I37" s="17">
-        <f>(G36/G37-1)/D37*100</f>
-        <v/>
-      </c>
-      <c r="J37" s="33" t="n"/>
-      <c r="K37" s="37">
-        <f>IF(J37="","",(H37-J37)*100)</f>
+        <f>F37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="17">
+        <f>-LN(H37)/C37*100</f>
+        <v/>
+      </c>
+      <c r="K37" s="17">
+        <f>(H36/H37-1)/((B37-B36)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L37" s="33" t="n"/>
+      <c r="M37" s="37">
+        <f>IF(L37="","",(J37-L37)*100)</f>
         <v/>
       </c>
     </row>
@@ -5648,7 +5871,7 @@
         <v/>
       </c>
       <c r="D38" s="21">
-        <f>(B38-B37)/360</f>
+        <f>(B38-$B$4)/360</f>
         <v/>
       </c>
       <c r="E38" s="21">
@@ -5656,24 +5879,32 @@
         <v/>
       </c>
       <c r="F38" s="21">
-        <f>F37+D37*G37</f>
-        <v/>
-      </c>
-      <c r="G38" s="32">
-        <f>(1-(E38/100)*F38)/(1+(E38/100)*D38)</f>
-        <v/>
-      </c>
-      <c r="H38" s="21">
-        <f>-LN(G38)/C38*100</f>
+        <f>(B38-$B$37)/360</f>
+        <v/>
+      </c>
+      <c r="G38" s="21">
+        <f>SUM($I$8:I37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="32">
+        <f>(1-(E38/100)*G38)/(1+(E38/100)*F38)</f>
         <v/>
       </c>
       <c r="I38" s="21">
-        <f>(G37/G38-1)/D38*100</f>
-        <v/>
-      </c>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="34">
-        <f>IF(J38="","",(H38-J38)*100)</f>
+        <f>F38*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="21">
+        <f>-LN(H38)/C38*100</f>
+        <v/>
+      </c>
+      <c r="K38" s="21">
+        <f>(H37/H38-1)/((B38-B37)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L38" s="33" t="n"/>
+      <c r="M38" s="34">
+        <f>IF(L38="","",(J38-L38)*100)</f>
         <v/>
       </c>
     </row>
@@ -5692,7 +5923,7 @@
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>(B39-B38)/360</f>
+        <f>(B39-$B$4)/360</f>
         <v/>
       </c>
       <c r="E39" s="17">
@@ -5700,47 +5931,2514 @@
         <v/>
       </c>
       <c r="F39" s="17">
-        <f>F38+D38*G38</f>
-        <v/>
-      </c>
-      <c r="G39" s="36">
-        <f>(1-(E39/100)*F39)/(1+(E39/100)*D39)</f>
-        <v/>
-      </c>
-      <c r="H39" s="17">
-        <f>-LN(G39)/C39*100</f>
+        <f>(B39-$B$38)/360</f>
+        <v/>
+      </c>
+      <c r="G39" s="17">
+        <f>SUM($I$8:I38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="36">
+        <f>(1-(E39/100)*G39)/(1+(E39/100)*F39)</f>
         <v/>
       </c>
       <c r="I39" s="17">
-        <f>(G38/G39-1)/D39*100</f>
-        <v/>
-      </c>
-      <c r="J39" s="33" t="n"/>
-      <c r="K39" s="37">
-        <f>IF(J39="","",(H39-J39)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41" ht="40" customHeight="1">
+        <f>F39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="17">
+        <f>-LN(H39)/C39*100</f>
+        <v/>
+      </c>
+      <c r="K39" s="17">
+        <f>(H38/H39-1)/((B39-B38)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L39" s="33" t="n"/>
+      <c r="M39" s="37">
+        <f>IF(L39="","",(J39-L39)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="44" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Discount factor is the deliverable curve P(0,T). Zero rate is continuously-compounded (ACT/365): z = −ln(DF)/T. Forward is the simple rate over each pillar interval. Yellow column J is for pasting the Bloomberg S490 zero rates; Δ (bp) then shows your bootstrap vs Bloomberg — the validation the Lehman paper does against the dealer curve.</t>
+          <t>Column H (Discount factor) is the deliverable curve P(0,T). Zero rate is continuously-compounded (ACT/365): z = −ln(DF)/T. Column I (Ann.add) is τ·DF booked only at annual coupon dates, so column G sums exactly the coupons each swap actually pays. Yellow column L takes pasted Bloomberg S490 zeros; Δ (bp) is your bootstrap vs Bloomberg — the dealer-curve validation from the Lehman paper. The Swap_Pricer tab values any SOFR OIS off this curve.</t>
         </is>
       </c>
     </row>
     <row r="42"/>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A41:K42"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A5:K6"/>
+    <mergeCell ref="A5:M6"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A41:M42"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="1" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Swap_Pricer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Fixed-vs-SOFR OIS valuation (SWPM-style), priced off the Bootstrap curve — every cell is live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DEAL — Fixed vs SOFR OIS   (yellow = inputs; everything else is computed)</t>
+        </is>
+      </c>
+      <c r="K4" s="38" t="inlineStr">
+        <is>
+          <t>Discount curve (from Bootstrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>Direction (Leg 1 = Fixed)</t>
+        </is>
+      </c>
+      <c r="B5" s="40" t="inlineStr">
+        <is>
+          <t>Receive fixed</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
+        </is>
+      </c>
+      <c r="K5" s="42" t="inlineStr">
+        <is>
+          <t>Curve date</t>
+        </is>
+      </c>
+      <c r="L5" s="42" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="39" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
+      <c r="B6" s="43" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C6" s="41" t="inlineStr">
+        <is>
+          <t>Both legs, USD.</t>
+        </is>
+      </c>
+      <c r="K6" s="18">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="L6" s="44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K7" s="18">
+        <f>Bootstrap!B8</f>
+        <v/>
+      </c>
+      <c r="L7" s="44">
+        <f>Bootstrap!H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="39" t="inlineStr">
+        <is>
+          <t>Effective date</t>
+        </is>
+      </c>
+      <c r="B8" s="45">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="C8" s="41" t="inlineStr">
+        <is>
+          <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
+        </is>
+      </c>
+      <c r="K8" s="18">
+        <f>Bootstrap!B9</f>
+        <v/>
+      </c>
+      <c r="L8" s="44">
+        <f>Bootstrap!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39" t="inlineStr">
+        <is>
+          <t>Tenor (years)</t>
+        </is>
+      </c>
+      <c r="B9" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="41" t="inlineStr">
+        <is>
+          <t>Whole years; drives the annual coupon schedule below.</t>
+        </is>
+      </c>
+      <c r="K9" s="18">
+        <f>Bootstrap!B10</f>
+        <v/>
+      </c>
+      <c r="L9" s="44">
+        <f>Bootstrap!H10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39" t="inlineStr">
+        <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>EDATE(B8,12*B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="41">
+        <f> Effective + Tenor.</f>
+        <v/>
+      </c>
+      <c r="K10" s="18">
+        <f>Bootstrap!B11</f>
+        <v/>
+      </c>
+      <c r="L10" s="44">
+        <f>Bootstrap!H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39" t="inlineStr">
+        <is>
+          <t>Fixed coupon (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="47">
+        <f>B25</f>
+        <v/>
+      </c>
+      <c r="C11" s="41" t="inlineStr">
+        <is>
+          <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
+        </is>
+      </c>
+      <c r="K11" s="18">
+        <f>Bootstrap!B12</f>
+        <v/>
+      </c>
+      <c r="L11" s="44">
+        <f>Bootstrap!H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>Fixed pay frequency</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K12" s="18">
+        <f>Bootstrap!B13</f>
+        <v/>
+      </c>
+      <c r="L12" s="44">
+        <f>Bootstrap!H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39" t="inlineStr">
+        <is>
+          <t>Fixed day count</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+      <c r="K13" s="18">
+        <f>Bootstrap!B14</f>
+        <v/>
+      </c>
+      <c r="L13" s="44">
+        <f>Bootstrap!H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39" t="inlineStr">
+        <is>
+          <t>Float index</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>SOFR (daily compounded, single-curve)</t>
+        </is>
+      </c>
+      <c r="K14" s="18">
+        <f>Bootstrap!B15</f>
+        <v/>
+      </c>
+      <c r="L14" s="44">
+        <f>Bootstrap!H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>Curve / valuation date</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>VAL_DATE</f>
+        <v/>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Curve is discounted from spot = Bootstrap!B4.</t>
+        </is>
+      </c>
+      <c r="K15" s="18">
+        <f>Bootstrap!B16</f>
+        <v/>
+      </c>
+      <c r="L15" s="44">
+        <f>Bootstrap!H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>Direction sign (+recv / −pay)</t>
+        </is>
+      </c>
+      <c r="B16" s="48">
+        <f>IF($B$5="Receive fixed",1,-1)</f>
+        <v/>
+      </c>
+      <c r="K16" s="18">
+        <f>Bootstrap!B17</f>
+        <v/>
+      </c>
+      <c r="L16" s="44">
+        <f>Bootstrap!H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="K17" s="18">
+        <f>Bootstrap!B18</f>
+        <v/>
+      </c>
+      <c r="L17" s="44">
+        <f>Bootstrap!H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VALUATION RESULTS — single-curve OIS discounting</t>
+        </is>
+      </c>
+      <c r="K18" s="18">
+        <f>Bootstrap!B19</f>
+        <v/>
+      </c>
+      <c r="L18" s="44">
+        <f>Bootstrap!H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39" t="inlineStr">
+        <is>
+          <t>DF(effective)</t>
+        </is>
+      </c>
+      <c r="B19" s="44">
+        <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))^(($B$8-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))</f>
+        <v/>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Interpolated from the curve.</t>
+        </is>
+      </c>
+      <c r="K19" s="18">
+        <f>Bootstrap!B20</f>
+        <v/>
+      </c>
+      <c r="L19" s="44">
+        <f>Bootstrap!H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>DF(maturity)</t>
+        </is>
+      </c>
+      <c r="B20" s="44">
+        <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)))^(($B$10-INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="18">
+        <f>Bootstrap!B21</f>
+        <v/>
+      </c>
+      <c r="L20" s="44">
+        <f>Bootstrap!H21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39" t="inlineStr">
+        <is>
+          <t>Fixed annuity  Στ·DF</t>
+        </is>
+      </c>
+      <c r="B21" s="49">
+        <f>SUM(H36:H85)</f>
+        <v/>
+      </c>
+      <c r="C21" s="41" t="inlineStr">
+        <is>
+          <t>Sum of τ·DF over the fixed coupon dates.</t>
+        </is>
+      </c>
+      <c r="K21" s="18">
+        <f>Bootstrap!B22</f>
+        <v/>
+      </c>
+      <c r="L21" s="44">
+        <f>Bootstrap!H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39" t="inlineStr">
+        <is>
+          <t>Fixed leg PV (coupons)</t>
+        </is>
+      </c>
+      <c r="B22" s="50">
+        <f>SUM(G36:G85)</f>
+        <v/>
+      </c>
+      <c r="K22" s="18">
+        <f>Bootstrap!B23</f>
+        <v/>
+      </c>
+      <c r="L22" s="44">
+        <f>Bootstrap!H23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39" t="inlineStr">
+        <is>
+          <t>Float leg PV</t>
+        </is>
+      </c>
+      <c r="B23" s="50">
+        <f>B6*(B19-B20)</f>
+        <v/>
+      </c>
+      <c r="C23" s="41" t="inlineStr">
+        <is>
+          <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
+        </is>
+      </c>
+      <c r="K23" s="18">
+        <f>Bootstrap!B24</f>
+        <v/>
+      </c>
+      <c r="L23" s="44">
+        <f>Bootstrap!H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Notional PV @ maturity</t>
+        </is>
+      </c>
+      <c r="B24" s="50">
+        <f>B6*B20</f>
+        <v/>
+      </c>
+      <c r="C24" s="41" t="inlineStr">
+        <is>
+          <t>For the SWPM-style leg display only.</t>
+        </is>
+      </c>
+      <c r="K24" s="18">
+        <f>Bootstrap!B25</f>
+        <v/>
+      </c>
+      <c r="L24" s="44">
+        <f>Bootstrap!H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>Par coupon (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="49">
+        <f>(B19-B20)/B21*100</f>
+        <v/>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
+        </is>
+      </c>
+      <c r="K25" s="18">
+        <f>Bootstrap!B26</f>
+        <v/>
+      </c>
+      <c r="L25" s="44">
+        <f>Bootstrap!H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
+        <is>
+          <t>Leg 1 NPV  (fixed + notional)</t>
+        </is>
+      </c>
+      <c r="B26" s="50">
+        <f>B16*(B22+B24)</f>
+        <v/>
+      </c>
+      <c r="C26" s="41" t="inlineStr">
+        <is>
+          <t>SWPM shows each leg incl. a notional redemption.</t>
+        </is>
+      </c>
+      <c r="K26" s="18">
+        <f>Bootstrap!B27</f>
+        <v/>
+      </c>
+      <c r="L26" s="44">
+        <f>Bootstrap!H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Leg 2 NPV  (float + notional)</t>
+        </is>
+      </c>
+      <c r="B27" s="50">
+        <f>-B16*(B23+B24)</f>
+        <v/>
+      </c>
+      <c r="K27" s="18">
+        <f>Bootstrap!B28</f>
+        <v/>
+      </c>
+      <c r="L27" s="44">
+        <f>Bootstrap!H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39" t="inlineStr">
+        <is>
+          <t>Net swap NPV</t>
+        </is>
+      </c>
+      <c r="B28" s="51">
+        <f>B26+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="41">
+        <f> Fixed − Float (notionals cancel). ≈ 0 at par coupon.</f>
+        <v/>
+      </c>
+      <c r="K28" s="18">
+        <f>Bootstrap!B29</f>
+        <v/>
+      </c>
+      <c r="L28" s="44">
+        <f>Bootstrap!H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39" t="inlineStr">
+        <is>
+          <t>PV01 / DV01  (per 1bp)</t>
+        </is>
+      </c>
+      <c r="B29" s="50">
+        <f>B6*B21*0.0001</f>
+        <v/>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Annuity × notional × 1bp.</t>
+        </is>
+      </c>
+      <c r="K29" s="18">
+        <f>Bootstrap!B30</f>
+        <v/>
+      </c>
+      <c r="L29" s="44">
+        <f>Bootstrap!H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39" t="inlineStr">
+        <is>
+          <t>Accrued (at inception)</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="18">
+        <f>Bootstrap!B31</f>
+        <v/>
+      </c>
+      <c r="L30" s="44">
+        <f>Bootstrap!H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="K31" s="18">
+        <f>Bootstrap!B32</f>
+        <v/>
+      </c>
+      <c r="L31" s="44">
+        <f>Bootstrap!H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>Cross-check vs the SWPM screen: Par coupon and PV01 match (≈4.02%, ≈974 for a 10mm 1Y). SWPM's leg NPVs read ~9,995,534 rather than 10,000,000 because it discounts from curve date to a valuation date 2 business days after effective; here effective = spot so DF(effective) = 1 exactly. The net NPV, par coupon and DV01 are unaffected.</t>
+        </is>
+      </c>
+      <c r="K32" s="18">
+        <f>Bootstrap!B33</f>
+        <v/>
+      </c>
+      <c r="L32" s="44">
+        <f>Bootstrap!H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="K33" s="18">
+        <f>Bootstrap!B34</f>
+        <v/>
+      </c>
+      <c r="L33" s="44">
+        <f>Bootstrap!H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="K34" s="18">
+        <f>Bootstrap!B35</f>
+        <v/>
+      </c>
+      <c r="L34" s="44">
+        <f>Bootstrap!H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Pay date</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Prev date</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>τ ACT/360</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>DF (interp)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>Coupon CF</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>τ·DF</t>
+        </is>
+      </c>
+      <c r="K35" s="18">
+        <f>Bootstrap!B36</f>
+        <v/>
+      </c>
+      <c r="L35" s="44">
+        <f>Bootstrap!H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B36" s="18">
+        <f>IF(A36&lt;=$B$9,EDATE($B$8,12*A36),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="18">
+        <f>IF(A36&lt;=$B$9,$B$8,"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="21">
+        <f>IF(A36&lt;=$B$9,(B36-C36)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="44">
+        <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)))^((B36-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="50">
+        <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="50">
+        <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="49">
+        <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="18">
+        <f>Bootstrap!B37</f>
+        <v/>
+      </c>
+      <c r="L36" s="44">
+        <f>Bootstrap!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B37" s="24">
+        <f>IF(A37&lt;=$B$9,EDATE($B$8,12*A37),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="24">
+        <f>IF(A37&lt;=$B$9,B36,"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>IF(A37&lt;=$B$9,(B37-C37)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="53">
+        <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)))^((B37-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="54">
+        <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="54">
+        <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="55">
+        <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="18">
+        <f>Bootstrap!B38</f>
+        <v/>
+      </c>
+      <c r="L37" s="44">
+        <f>Bootstrap!H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B38" s="18">
+        <f>IF(A38&lt;=$B$9,EDATE($B$8,12*A38),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f>IF(A38&lt;=$B$9,B37,"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>IF(A38&lt;=$B$9,(B38-C38)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="44">
+        <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)))^((B38-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="50">
+        <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="50">
+        <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="49">
+        <f>IF(A38&lt;=$B$9,D38*E38,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="18">
+        <f>Bootstrap!B39</f>
+        <v/>
+      </c>
+      <c r="L38" s="44">
+        <f>Bootstrap!H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B39" s="24">
+        <f>IF(A39&lt;=$B$9,EDATE($B$8,12*A39),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="24">
+        <f>IF(A39&lt;=$B$9,B38,"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>IF(A39&lt;=$B$9,(B39-C39)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="53">
+        <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)))^((B39-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="54">
+        <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="54">
+        <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="55">
+        <f>IF(A39&lt;=$B$9,D39*E39,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>Log-linear DF interpolation on this grid (dates $K$6:$K$38, DFs $L$6:$L$38).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B40" s="18">
+        <f>IF(A40&lt;=$B$9,EDATE($B$8,12*A40),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="18">
+        <f>IF(A40&lt;=$B$9,B39,"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="21">
+        <f>IF(A40&lt;=$B$9,(B40-C40)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="44">
+        <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)))^((B40-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="50">
+        <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="50">
+        <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="49">
+        <f>IF(A40&lt;=$B$9,D40*E40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B41" s="24">
+        <f>IF(A41&lt;=$B$9,EDATE($B$8,12*A41),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="24">
+        <f>IF(A41&lt;=$B$9,B40,"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>IF(A41&lt;=$B$9,(B41-C41)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="53">
+        <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)))^((B41-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="54">
+        <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="54">
+        <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="55">
+        <f>IF(A41&lt;=$B$9,D41*E41,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B42" s="18">
+        <f>IF(A42&lt;=$B$9,EDATE($B$8,12*A42),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="18">
+        <f>IF(A42&lt;=$B$9,B41,"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="21">
+        <f>IF(A42&lt;=$B$9,(B42-C42)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="44">
+        <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)))^((B42-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="50">
+        <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="50">
+        <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="49">
+        <f>IF(A42&lt;=$B$9,D42*E42,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B43" s="24">
+        <f>IF(A43&lt;=$B$9,EDATE($B$8,12*A43),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="24">
+        <f>IF(A43&lt;=$B$9,B42,"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>IF(A43&lt;=$B$9,(B43-C43)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="53">
+        <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)))^((B43-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="54">
+        <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="54">
+        <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="55">
+        <f>IF(A43&lt;=$B$9,D43*E43,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B44" s="18">
+        <f>IF(A44&lt;=$B$9,EDATE($B$8,12*A44),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="18">
+        <f>IF(A44&lt;=$B$9,B43,"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="21">
+        <f>IF(A44&lt;=$B$9,(B44-C44)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="44">
+        <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)))^((B44-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="50">
+        <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="50">
+        <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="49">
+        <f>IF(A44&lt;=$B$9,D44*E44,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B45" s="24">
+        <f>IF(A45&lt;=$B$9,EDATE($B$8,12*A45),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="24">
+        <f>IF(A45&lt;=$B$9,B44,"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>IF(A45&lt;=$B$9,(B45-C45)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="53">
+        <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)))^((B45-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="54">
+        <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="54">
+        <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="55">
+        <f>IF(A45&lt;=$B$9,D45*E45,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B46" s="18">
+        <f>IF(A46&lt;=$B$9,EDATE($B$8,12*A46),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="18">
+        <f>IF(A46&lt;=$B$9,B45,"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="21">
+        <f>IF(A46&lt;=$B$9,(B46-C46)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="44">
+        <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)))^((B46-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="50">
+        <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="50">
+        <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="49">
+        <f>IF(A46&lt;=$B$9,D46*E46,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B47" s="24">
+        <f>IF(A47&lt;=$B$9,EDATE($B$8,12*A47),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="24">
+        <f>IF(A47&lt;=$B$9,B46,"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="17">
+        <f>IF(A47&lt;=$B$9,(B47-C47)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="53">
+        <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)))^((B47-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="54">
+        <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="54">
+        <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="55">
+        <f>IF(A47&lt;=$B$9,D47*E47,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B48" s="18">
+        <f>IF(A48&lt;=$B$9,EDATE($B$8,12*A48),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="18">
+        <f>IF(A48&lt;=$B$9,B47,"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="21">
+        <f>IF(A48&lt;=$B$9,(B48-C48)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="44">
+        <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)))^((B48-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="50">
+        <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="50">
+        <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="49">
+        <f>IF(A48&lt;=$B$9,D48*E48,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B49" s="24">
+        <f>IF(A49&lt;=$B$9,EDATE($B$8,12*A49),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="24">
+        <f>IF(A49&lt;=$B$9,B48,"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="17">
+        <f>IF(A49&lt;=$B$9,(B49-C49)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="53">
+        <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)))^((B49-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="54">
+        <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="54">
+        <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="55">
+        <f>IF(A49&lt;=$B$9,D49*E49,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B50" s="18">
+        <f>IF(A50&lt;=$B$9,EDATE($B$8,12*A50),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="18">
+        <f>IF(A50&lt;=$B$9,B49,"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="21">
+        <f>IF(A50&lt;=$B$9,(B50-C50)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="44">
+        <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)))^((B50-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="50">
+        <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="50">
+        <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="49">
+        <f>IF(A50&lt;=$B$9,D50*E50,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B51" s="24">
+        <f>IF(A51&lt;=$B$9,EDATE($B$8,12*A51),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="24">
+        <f>IF(A51&lt;=$B$9,B50,"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="17">
+        <f>IF(A51&lt;=$B$9,(B51-C51)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="53">
+        <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)))^((B51-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="54">
+        <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="54">
+        <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="55">
+        <f>IF(A51&lt;=$B$9,D51*E51,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B52" s="18">
+        <f>IF(A52&lt;=$B$9,EDATE($B$8,12*A52),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="18">
+        <f>IF(A52&lt;=$B$9,B51,"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="21">
+        <f>IF(A52&lt;=$B$9,(B52-C52)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="44">
+        <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)))^((B52-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="50">
+        <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="50">
+        <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="49">
+        <f>IF(A52&lt;=$B$9,D52*E52,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B53" s="24">
+        <f>IF(A53&lt;=$B$9,EDATE($B$8,12*A53),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="24">
+        <f>IF(A53&lt;=$B$9,B52,"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="17">
+        <f>IF(A53&lt;=$B$9,(B53-C53)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="53">
+        <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)))^((B53-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="54">
+        <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="54">
+        <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="55">
+        <f>IF(A53&lt;=$B$9,D53*E53,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B54" s="18">
+        <f>IF(A54&lt;=$B$9,EDATE($B$8,12*A54),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="18">
+        <f>IF(A54&lt;=$B$9,B53,"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="21">
+        <f>IF(A54&lt;=$B$9,(B54-C54)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="44">
+        <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)))^((B54-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="50">
+        <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="50">
+        <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="49">
+        <f>IF(A54&lt;=$B$9,D54*E54,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B55" s="24">
+        <f>IF(A55&lt;=$B$9,EDATE($B$8,12*A55),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="24">
+        <f>IF(A55&lt;=$B$9,B54,"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="17">
+        <f>IF(A55&lt;=$B$9,(B55-C55)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="53">
+        <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)))^((B55-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="54">
+        <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="54">
+        <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="55">
+        <f>IF(A55&lt;=$B$9,D55*E55,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B56" s="18">
+        <f>IF(A56&lt;=$B$9,EDATE($B$8,12*A56),"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="18">
+        <f>IF(A56&lt;=$B$9,B55,"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="21">
+        <f>IF(A56&lt;=$B$9,(B56-C56)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="44">
+        <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)))^((B56-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="50">
+        <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="50">
+        <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="49">
+        <f>IF(A56&lt;=$B$9,D56*E56,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B57" s="24">
+        <f>IF(A57&lt;=$B$9,EDATE($B$8,12*A57),"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="24">
+        <f>IF(A57&lt;=$B$9,B56,"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="17">
+        <f>IF(A57&lt;=$B$9,(B57-C57)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="53">
+        <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)))^((B57-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="54">
+        <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="54">
+        <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="55">
+        <f>IF(A57&lt;=$B$9,D57*E57,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B58" s="18">
+        <f>IF(A58&lt;=$B$9,EDATE($B$8,12*A58),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="18">
+        <f>IF(A58&lt;=$B$9,B57,"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="21">
+        <f>IF(A58&lt;=$B$9,(B58-C58)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="44">
+        <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)))^((B58-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="50">
+        <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="50">
+        <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="49">
+        <f>IF(A58&lt;=$B$9,D58*E58,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B59" s="24">
+        <f>IF(A59&lt;=$B$9,EDATE($B$8,12*A59),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="24">
+        <f>IF(A59&lt;=$B$9,B58,"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="17">
+        <f>IF(A59&lt;=$B$9,(B59-C59)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="53">
+        <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)))^((B59-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="54">
+        <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="54">
+        <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="55">
+        <f>IF(A59&lt;=$B$9,D59*E59,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B60" s="18">
+        <f>IF(A60&lt;=$B$9,EDATE($B$8,12*A60),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="18">
+        <f>IF(A60&lt;=$B$9,B59,"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="21">
+        <f>IF(A60&lt;=$B$9,(B60-C60)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="44">
+        <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)))^((B60-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="50">
+        <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="50">
+        <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="49">
+        <f>IF(A60&lt;=$B$9,D60*E60,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B61" s="24">
+        <f>IF(A61&lt;=$B$9,EDATE($B$8,12*A61),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="24">
+        <f>IF(A61&lt;=$B$9,B60,"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="17">
+        <f>IF(A61&lt;=$B$9,(B61-C61)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="53">
+        <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)))^((B61-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="54">
+        <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="54">
+        <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="55">
+        <f>IF(A61&lt;=$B$9,D61*E61,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B62" s="18">
+        <f>IF(A62&lt;=$B$9,EDATE($B$8,12*A62),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="18">
+        <f>IF(A62&lt;=$B$9,B61,"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="21">
+        <f>IF(A62&lt;=$B$9,(B62-C62)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E62" s="44">
+        <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)))^((B62-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F62" s="50">
+        <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="50">
+        <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="49">
+        <f>IF(A62&lt;=$B$9,D62*E62,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B63" s="24">
+        <f>IF(A63&lt;=$B$9,EDATE($B$8,12*A63),"")</f>
+        <v/>
+      </c>
+      <c r="C63" s="24">
+        <f>IF(A63&lt;=$B$9,B62,"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="17">
+        <f>IF(A63&lt;=$B$9,(B63-C63)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E63" s="53">
+        <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)))^((B63-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F63" s="54">
+        <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="54">
+        <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="55">
+        <f>IF(A63&lt;=$B$9,D63*E63,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B64" s="18">
+        <f>IF(A64&lt;=$B$9,EDATE($B$8,12*A64),"")</f>
+        <v/>
+      </c>
+      <c r="C64" s="18">
+        <f>IF(A64&lt;=$B$9,B63,"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="21">
+        <f>IF(A64&lt;=$B$9,(B64-C64)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E64" s="44">
+        <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)))^((B64-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F64" s="50">
+        <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="50">
+        <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="49">
+        <f>IF(A64&lt;=$B$9,D64*E64,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B65" s="24">
+        <f>IF(A65&lt;=$B$9,EDATE($B$8,12*A65),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="24">
+        <f>IF(A65&lt;=$B$9,B64,"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(A65&lt;=$B$9,(B65-C65)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E65" s="53">
+        <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)))^((B65-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F65" s="54">
+        <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="54">
+        <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="55">
+        <f>IF(A65&lt;=$B$9,D65*E65,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B66" s="18">
+        <f>IF(A66&lt;=$B$9,EDATE($B$8,12*A66),"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="18">
+        <f>IF(A66&lt;=$B$9,B65,"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="21">
+        <f>IF(A66&lt;=$B$9,(B66-C66)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="44">
+        <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)))^((B66-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F66" s="50">
+        <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="50">
+        <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="49">
+        <f>IF(A66&lt;=$B$9,D66*E66,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B67" s="24">
+        <f>IF(A67&lt;=$B$9,EDATE($B$8,12*A67),"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="24">
+        <f>IF(A67&lt;=$B$9,B66,"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="17">
+        <f>IF(A67&lt;=$B$9,(B67-C67)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="53">
+        <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)))^((B67-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="54">
+        <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
+        <v/>
+      </c>
+      <c r="G67" s="54">
+        <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="55">
+        <f>IF(A67&lt;=$B$9,D67*E67,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B68" s="18">
+        <f>IF(A68&lt;=$B$9,EDATE($B$8,12*A68),"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="18">
+        <f>IF(A68&lt;=$B$9,B67,"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="21">
+        <f>IF(A68&lt;=$B$9,(B68-C68)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E68" s="44">
+        <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)))^((B68-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F68" s="50">
+        <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="50">
+        <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="49">
+        <f>IF(A68&lt;=$B$9,D68*E68,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B69" s="24">
+        <f>IF(A69&lt;=$B$9,EDATE($B$8,12*A69),"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="24">
+        <f>IF(A69&lt;=$B$9,B68,"")</f>
+        <v/>
+      </c>
+      <c r="D69" s="17">
+        <f>IF(A69&lt;=$B$9,(B69-C69)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E69" s="53">
+        <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)))^((B69-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F69" s="54">
+        <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="54">
+        <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="55">
+        <f>IF(A69&lt;=$B$9,D69*E69,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B70" s="18">
+        <f>IF(A70&lt;=$B$9,EDATE($B$8,12*A70),"")</f>
+        <v/>
+      </c>
+      <c r="C70" s="18">
+        <f>IF(A70&lt;=$B$9,B69,"")</f>
+        <v/>
+      </c>
+      <c r="D70" s="21">
+        <f>IF(A70&lt;=$B$9,(B70-C70)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E70" s="44">
+        <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)))^((B70-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F70" s="50">
+        <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="50">
+        <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="49">
+        <f>IF(A70&lt;=$B$9,D70*E70,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B71" s="24">
+        <f>IF(A71&lt;=$B$9,EDATE($B$8,12*A71),"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="24">
+        <f>IF(A71&lt;=$B$9,B70,"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>IF(A71&lt;=$B$9,(B71-C71)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E71" s="53">
+        <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)))^((B71-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="54">
+        <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="54">
+        <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="55">
+        <f>IF(A71&lt;=$B$9,D71*E71,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B72" s="18">
+        <f>IF(A72&lt;=$B$9,EDATE($B$8,12*A72),"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="18">
+        <f>IF(A72&lt;=$B$9,B71,"")</f>
+        <v/>
+      </c>
+      <c r="D72" s="21">
+        <f>IF(A72&lt;=$B$9,(B72-C72)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E72" s="44">
+        <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)))^((B72-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F72" s="50">
+        <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
+        <v/>
+      </c>
+      <c r="G72" s="50">
+        <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
+        <v/>
+      </c>
+      <c r="H72" s="49">
+        <f>IF(A72&lt;=$B$9,D72*E72,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B73" s="24">
+        <f>IF(A73&lt;=$B$9,EDATE($B$8,12*A73),"")</f>
+        <v/>
+      </c>
+      <c r="C73" s="24">
+        <f>IF(A73&lt;=$B$9,B72,"")</f>
+        <v/>
+      </c>
+      <c r="D73" s="17">
+        <f>IF(A73&lt;=$B$9,(B73-C73)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E73" s="53">
+        <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)))^((B73-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F73" s="54">
+        <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
+        <v/>
+      </c>
+      <c r="G73" s="54">
+        <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
+        <v/>
+      </c>
+      <c r="H73" s="55">
+        <f>IF(A73&lt;=$B$9,D73*E73,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B74" s="18">
+        <f>IF(A74&lt;=$B$9,EDATE($B$8,12*A74),"")</f>
+        <v/>
+      </c>
+      <c r="C74" s="18">
+        <f>IF(A74&lt;=$B$9,B73,"")</f>
+        <v/>
+      </c>
+      <c r="D74" s="21">
+        <f>IF(A74&lt;=$B$9,(B74-C74)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E74" s="44">
+        <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)))^((B74-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F74" s="50">
+        <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
+        <v/>
+      </c>
+      <c r="G74" s="50">
+        <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
+        <v/>
+      </c>
+      <c r="H74" s="49">
+        <f>IF(A74&lt;=$B$9,D74*E74,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B75" s="24">
+        <f>IF(A75&lt;=$B$9,EDATE($B$8,12*A75),"")</f>
+        <v/>
+      </c>
+      <c r="C75" s="24">
+        <f>IF(A75&lt;=$B$9,B74,"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="17">
+        <f>IF(A75&lt;=$B$9,(B75-C75)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E75" s="53">
+        <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)))^((B75-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F75" s="54">
+        <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
+        <v/>
+      </c>
+      <c r="G75" s="54">
+        <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
+        <v/>
+      </c>
+      <c r="H75" s="55">
+        <f>IF(A75&lt;=$B$9,D75*E75,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B76" s="18">
+        <f>IF(A76&lt;=$B$9,EDATE($B$8,12*A76),"")</f>
+        <v/>
+      </c>
+      <c r="C76" s="18">
+        <f>IF(A76&lt;=$B$9,B75,"")</f>
+        <v/>
+      </c>
+      <c r="D76" s="21">
+        <f>IF(A76&lt;=$B$9,(B76-C76)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E76" s="44">
+        <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)))^((B76-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F76" s="50">
+        <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
+        <v/>
+      </c>
+      <c r="G76" s="50">
+        <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
+        <v/>
+      </c>
+      <c r="H76" s="49">
+        <f>IF(A76&lt;=$B$9,D76*E76,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B77" s="24">
+        <f>IF(A77&lt;=$B$9,EDATE($B$8,12*A77),"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="24">
+        <f>IF(A77&lt;=$B$9,B76,"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="17">
+        <f>IF(A77&lt;=$B$9,(B77-C77)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E77" s="53">
+        <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)))^((B77-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F77" s="54">
+        <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
+        <v/>
+      </c>
+      <c r="G77" s="54">
+        <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
+        <v/>
+      </c>
+      <c r="H77" s="55">
+        <f>IF(A77&lt;=$B$9,D77*E77,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B78" s="18">
+        <f>IF(A78&lt;=$B$9,EDATE($B$8,12*A78),"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="18">
+        <f>IF(A78&lt;=$B$9,B77,"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="21">
+        <f>IF(A78&lt;=$B$9,(B78-C78)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E78" s="44">
+        <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)))^((B78-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F78" s="50">
+        <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
+        <v/>
+      </c>
+      <c r="G78" s="50">
+        <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
+        <v/>
+      </c>
+      <c r="H78" s="49">
+        <f>IF(A78&lt;=$B$9,D78*E78,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B79" s="24">
+        <f>IF(A79&lt;=$B$9,EDATE($B$8,12*A79),"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="24">
+        <f>IF(A79&lt;=$B$9,B78,"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="17">
+        <f>IF(A79&lt;=$B$9,(B79-C79)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="53">
+        <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)))^((B79-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="54">
+        <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
+        <v/>
+      </c>
+      <c r="G79" s="54">
+        <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
+        <v/>
+      </c>
+      <c r="H79" s="55">
+        <f>IF(A79&lt;=$B$9,D79*E79,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B80" s="18">
+        <f>IF(A80&lt;=$B$9,EDATE($B$8,12*A80),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="18">
+        <f>IF(A80&lt;=$B$9,B79,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="21">
+        <f>IF(A80&lt;=$B$9,(B80-C80)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="44">
+        <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)))^((B80-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="50">
+        <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
+        <v/>
+      </c>
+      <c r="G80" s="50">
+        <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
+        <v/>
+      </c>
+      <c r="H80" s="49">
+        <f>IF(A80&lt;=$B$9,D80*E80,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B81" s="24">
+        <f>IF(A81&lt;=$B$9,EDATE($B$8,12*A81),"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="24">
+        <f>IF(A81&lt;=$B$9,B80,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="17">
+        <f>IF(A81&lt;=$B$9,(B81-C81)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="53">
+        <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)))^((B81-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="54">
+        <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
+        <v/>
+      </c>
+      <c r="G81" s="54">
+        <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
+        <v/>
+      </c>
+      <c r="H81" s="55">
+        <f>IF(A81&lt;=$B$9,D81*E81,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B82" s="18">
+        <f>IF(A82&lt;=$B$9,EDATE($B$8,12*A82),"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="18">
+        <f>IF(A82&lt;=$B$9,B81,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="21">
+        <f>IF(A82&lt;=$B$9,(B82-C82)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="44">
+        <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)))^((B82-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="50">
+        <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
+        <v/>
+      </c>
+      <c r="G82" s="50">
+        <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
+        <v/>
+      </c>
+      <c r="H82" s="49">
+        <f>IF(A82&lt;=$B$9,D82*E82,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B83" s="24">
+        <f>IF(A83&lt;=$B$9,EDATE($B$8,12*A83),"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="24">
+        <f>IF(A83&lt;=$B$9,B82,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="17">
+        <f>IF(A83&lt;=$B$9,(B83-C83)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="53">
+        <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)))^((B83-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="54">
+        <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
+        <v/>
+      </c>
+      <c r="G83" s="54">
+        <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
+        <v/>
+      </c>
+      <c r="H83" s="55">
+        <f>IF(A83&lt;=$B$9,D83*E83,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="48">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B84" s="18">
+        <f>IF(A84&lt;=$B$9,EDATE($B$8,12*A84),"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="18">
+        <f>IF(A84&lt;=$B$9,B83,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="21">
+        <f>IF(A84&lt;=$B$9,(B84-C84)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="44">
+        <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)))^((B84-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="50">
+        <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
+        <v/>
+      </c>
+      <c r="G84" s="50">
+        <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
+        <v/>
+      </c>
+      <c r="H84" s="49">
+        <f>IF(A84&lt;=$B$9,D84*E84,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="52">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B85" s="24">
+        <f>IF(A85&lt;=$B$9,EDATE($B$8,12*A85),"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="24">
+        <f>IF(A85&lt;=$B$9,B84,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(A85&lt;=$B$9,(B85-C85)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="53">
+        <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)))^((B85-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="54">
+        <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="54">
+        <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
+        <v/>
+      </c>
+      <c r="H85" s="55">
+        <f>IF(A85&lt;=$B$9,D85*E85,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A32:I33"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5789,7 +8487,7 @@
           <t>Curve date</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="56">
         <f>VAL_DATE</f>
         <v/>
       </c>
@@ -6189,7 +8887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6258,24 +8956,24 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="57" t="inlineStr">
         <is>
           <t>CRNCY</t>
         </is>
       </c>
-      <c r="C5" s="40">
+      <c r="C5" s="58">
         <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="D5" s="40">
+      <c r="D5" s="58">
         <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="58">
         <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="F5" s="40">
+      <c r="F5" s="58">
         <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
@@ -6318,27 +9016,27 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C7" s="40" t="inlineStr">
+      <c r="C7" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D7" s="40" t="inlineStr">
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E7" s="40" t="inlineStr">
+      <c r="E7" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F7" s="40" t="inlineStr">
+      <c r="F7" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6382,27 +9080,27 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B9" s="39" t="inlineStr">
+      <c r="B9" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C9" s="40" t="inlineStr">
+      <c r="C9" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D9" s="40" t="inlineStr">
+      <c r="D9" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E9" s="40" t="inlineStr">
+      <c r="E9" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F9" s="40" t="inlineStr">
+      <c r="F9" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6442,27 +9140,27 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B11" s="39" t="inlineStr">
+      <c r="B11" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C11" s="40" t="inlineStr">
+      <c r="C11" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D11" s="40" t="inlineStr">
+      <c r="D11" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E11" s="40" t="inlineStr">
+      <c r="E11" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F11" s="40" t="inlineStr">
+      <c r="F11" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6502,27 +9200,27 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B13" s="39" t="inlineStr">
+      <c r="B13" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C13" s="40" t="inlineStr">
+      <c r="C13" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D13" s="40" t="inlineStr">
+      <c r="D13" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E13" s="40" t="inlineStr">
+      <c r="E13" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F13" s="40" t="inlineStr">
+      <c r="F13" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6566,27 +9264,27 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C15" s="40" t="inlineStr">
+      <c r="C15" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D15" s="40" t="inlineStr">
+      <c r="D15" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E15" s="40" t="inlineStr">
+      <c r="E15" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F15" s="40" t="inlineStr">
+      <c r="F15" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6630,27 +9328,27 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B17" s="39" t="inlineStr">
+      <c r="B17" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C17" s="40" t="inlineStr">
+      <c r="C17" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D17" s="40" t="inlineStr">
+      <c r="D17" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E17" s="40" t="inlineStr">
+      <c r="E17" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F17" s="40" t="inlineStr">
+      <c r="F17" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6694,27 +9392,27 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B19" s="39" t="inlineStr">
+      <c r="B19" s="57" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C19" s="40" t="inlineStr">
+      <c r="C19" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D19" s="40" t="inlineStr">
+      <c r="D19" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E19" s="40" t="inlineStr">
+      <c r="E19" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F19" s="40" t="inlineStr">
+      <c r="F19" s="58" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -6733,15 +9431,15 @@
           <t>Reference index</t>
         </is>
       </c>
-      <c r="B22" s="41" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>USD-SOFR (compounded in arrears)</t>
         </is>
       </c>
-      <c r="C22" s="42" t="n"/>
-      <c r="D22" s="42" t="n"/>
-      <c r="E22" s="42" t="n"/>
-      <c r="F22" s="42" t="n"/>
+      <c r="C22" s="60" t="n"/>
+      <c r="D22" s="60" t="n"/>
+      <c r="E22" s="60" t="n"/>
+      <c r="F22" s="60" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -6749,15 +9447,15 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B23" s="41" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>T+2 US business days</t>
         </is>
       </c>
-      <c r="C23" s="42" t="n"/>
-      <c r="D23" s="42" t="n"/>
-      <c r="E23" s="42" t="n"/>
-      <c r="F23" s="42" t="n"/>
+      <c r="C23" s="60" t="n"/>
+      <c r="D23" s="60" t="n"/>
+      <c r="E23" s="60" t="n"/>
+      <c r="F23" s="60" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -6765,15 +9463,15 @@
           <t>Effective date rule</t>
         </is>
       </c>
-      <c r="B24" s="41" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>Spot (T+2), modified following</t>
         </is>
       </c>
-      <c r="C24" s="42" t="n"/>
-      <c r="D24" s="42" t="n"/>
-      <c r="E24" s="42" t="n"/>
-      <c r="F24" s="42" t="n"/>
+      <c r="C24" s="60" t="n"/>
+      <c r="D24" s="60" t="n"/>
+      <c r="E24" s="60" t="n"/>
+      <c r="F24" s="60" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -6781,15 +9479,15 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>Effective + tenor, modified following</t>
         </is>
       </c>
-      <c r="C25" s="42" t="n"/>
-      <c r="D25" s="42" t="n"/>
-      <c r="E25" s="42" t="n"/>
-      <c r="F25" s="42" t="n"/>
+      <c r="C25" s="60" t="n"/>
+      <c r="D25" s="60" t="n"/>
+      <c r="E25" s="60" t="n"/>
+      <c r="F25" s="60" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -6797,15 +9495,15 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B26" s="41" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>Modified Following</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n"/>
-      <c r="D26" s="42" t="n"/>
-      <c r="E26" s="42" t="n"/>
-      <c r="F26" s="42" t="n"/>
+      <c r="C26" s="60" t="n"/>
+      <c r="D26" s="60" t="n"/>
+      <c r="E26" s="60" t="n"/>
+      <c r="F26" s="60" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -6813,15 +9511,15 @@
           <t>Fixed-leg day count</t>
         </is>
       </c>
-      <c r="B27" s="41" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
       </c>
-      <c r="C27" s="42" t="n"/>
-      <c r="D27" s="42" t="n"/>
-      <c r="E27" s="42" t="n"/>
-      <c r="F27" s="42" t="n"/>
+      <c r="C27" s="60" t="n"/>
+      <c r="D27" s="60" t="n"/>
+      <c r="E27" s="60" t="n"/>
+      <c r="F27" s="60" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -6829,15 +9527,15 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B28" s="41" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
       </c>
-      <c r="C28" s="42" t="n"/>
-      <c r="D28" s="42" t="n"/>
-      <c r="E28" s="42" t="n"/>
-      <c r="F28" s="42" t="n"/>
+      <c r="C28" s="60" t="n"/>
+      <c r="D28" s="60" t="n"/>
+      <c r="E28" s="60" t="n"/>
+      <c r="F28" s="60" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -6845,15 +9543,15 @@
           <t>Floating-leg day count</t>
         </is>
       </c>
-      <c r="B29" s="41" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
       </c>
-      <c r="C29" s="42" t="n"/>
-      <c r="D29" s="42" t="n"/>
-      <c r="E29" s="42" t="n"/>
-      <c r="F29" s="42" t="n"/>
+      <c r="C29" s="60" t="n"/>
+      <c r="D29" s="60" t="n"/>
+      <c r="E29" s="60" t="n"/>
+      <c r="F29" s="60" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -6861,15 +9559,15 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B30" s="41" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
       </c>
-      <c r="C30" s="42" t="n"/>
-      <c r="D30" s="42" t="n"/>
-      <c r="E30" s="42" t="n"/>
-      <c r="F30" s="42" t="n"/>
+      <c r="C30" s="60" t="n"/>
+      <c r="D30" s="60" t="n"/>
+      <c r="E30" s="60" t="n"/>
+      <c r="F30" s="60" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -6877,15 +9575,15 @@
           <t>SOFR compounding method</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>Daily compounded, ACT/360</t>
         </is>
       </c>
-      <c r="C31" s="42" t="n"/>
-      <c r="D31" s="42" t="n"/>
-      <c r="E31" s="42" t="n"/>
-      <c r="F31" s="42" t="n"/>
+      <c r="C31" s="60" t="n"/>
+      <c r="D31" s="60" t="n"/>
+      <c r="E31" s="60" t="n"/>
+      <c r="F31" s="60" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -6893,15 +9591,15 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B32" s="41" t="inlineStr">
+      <c r="B32" s="59" t="inlineStr">
         <is>
           <t>2 US business days</t>
         </is>
       </c>
-      <c r="C32" s="42" t="n"/>
-      <c r="D32" s="42" t="n"/>
-      <c r="E32" s="42" t="n"/>
-      <c r="F32" s="42" t="n"/>
+      <c r="C32" s="60" t="n"/>
+      <c r="D32" s="60" t="n"/>
+      <c r="E32" s="60" t="n"/>
+      <c r="F32" s="60" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -6909,15 +9607,15 @@
           <t>Observation shift / lookback</t>
         </is>
       </c>
-      <c r="B33" s="41" t="inlineStr">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>None (payment-delay convention, 2 bd)</t>
         </is>
       </c>
-      <c r="C33" s="42" t="n"/>
-      <c r="D33" s="42" t="n"/>
-      <c r="E33" s="42" t="n"/>
-      <c r="F33" s="42" t="n"/>
+      <c r="C33" s="60" t="n"/>
+      <c r="D33" s="60" t="n"/>
+      <c r="E33" s="60" t="n"/>
+      <c r="F33" s="60" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -6925,15 +9623,15 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B34" s="41" t="inlineStr">
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>EOM applies</t>
         </is>
       </c>
-      <c r="C34" s="42" t="n"/>
-      <c r="D34" s="42" t="n"/>
-      <c r="E34" s="42" t="n"/>
-      <c r="F34" s="42" t="n"/>
+      <c r="C34" s="60" t="n"/>
+      <c r="D34" s="60" t="n"/>
+      <c r="E34" s="60" t="n"/>
+      <c r="F34" s="60" t="n"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="11" t="inlineStr">

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -405,56 +405,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>template</author>
-  </authors>
-  <commentList>
-    <comment ref="A12" authorId="0" shapeId="0">
-      <text>
-        <t>Array (spilling) formula. In Excel with Bloomberg it fills Date + PX_LAST down this block. If your Excel is pre-dynamic-array, it may need Ctrl+Shift+Enter across A:B.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>template</author>
-  </authors>
-  <commentList>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>Spilling chain. Fills contract tickers down this column in Excel+Bloomberg.</t>
-      </text>
-    </comment>
-    <comment ref="A32" authorId="0" shapeId="0">
-      <text>
-        <t>Spilling chain. Fills contract tickers down this column in Excel+Bloomberg.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>template</author>
-  </authors>
-  <commentList>
-    <comment ref="A8" authorId="0" shapeId="0">
-      <text>
-        <t>Spilling: Tenor in col A, par/market rate in col B (or D depending on Bloomberg's return order — verify and align). Fill zero/DF/forward from the curve screen.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -1425,7 +1375,6 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -3042,7 +2991,6 @@
     <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -8883,7 +8831,6 @@
     <mergeCell ref="B4:D4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -235,7 +235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -278,7 +278,11 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3000,17 +3004,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1">
@@ -3023,7 +3028,23 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>USD fixed-vs-SOFR OIS strip (USOSFR…, BGN) — 1W to 50Y.  Mid used for construction.</t>
+          <t>USD fixed-vs-SOFR OIS strip (USOSFR…, BGN) — 1W to 50Y.  Maturity &amp; years are derived live from the tenor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>Spot (T+2):</t>
+        </is>
+      </c>
+      <c r="B3" s="24">
+        <f>WORKDAY(VAL_DATE,2)</f>
+        <v/>
+      </c>
+      <c r="C3" s="26" t="inlineStr">
+        <is>
+          <t>Maturity &amp; Tenor(yrs) recompute from the tenor label + spot.</t>
         </is>
       </c>
     </row>
@@ -3040,30 +3061,35 @@
       </c>
       <c r="C4" s="20" t="inlineStr">
         <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
           <t>Tenor (yrs)</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="E4" s="20" t="inlineStr">
         <is>
           <t>PX_BID</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="F4" s="20" t="inlineStr">
         <is>
           <t>PX_ASK</t>
         </is>
       </c>
-      <c r="F4" s="20" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>PX_LAST</t>
         </is>
       </c>
-      <c r="G4" s="20" t="inlineStr">
+      <c r="H4" s="20" t="inlineStr">
         <is>
           <t>Mid = (Bid+Ask)/2</t>
         </is>
       </c>
-      <c r="H4" s="20" t="inlineStr">
+      <c r="I4" s="20" t="inlineStr">
         <is>
           <t>In bootstrap set</t>
         </is>
@@ -3075,31 +3101,36 @@
           <t>USOSFR1Z</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
-        <v>0.0192</v>
-      </c>
-      <c r="D5" s="21">
+      <c r="C5" s="28">
+        <f>IF(RIGHT(B5,1)="W",$B$3+7*VALUE(LEFT(B5,LEN(B5)-1)),IF(RIGHT(B5,1)="M",EDATE($B$3,VALUE(LEFT(B5,LEN(B5)-1))),EDATE($B$3,12*VALUE(LEFT(B5,LEN(B5)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D5" s="29">
+        <f>(C5-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E5" s="21">
         <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E5" s="21">
+      <c r="F5" s="21">
         <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F5" s="21">
+      <c r="G5" s="21">
         <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G5" s="28">
-        <f>IFERROR((D5+E5)/2,IFERROR(F5,""))</f>
-        <v/>
-      </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="30">
+        <f>IFERROR((E5+F5)/2,IFERROR(G5,""))</f>
+        <v/>
+      </c>
+      <c r="I5" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3111,31 +3142,36 @@
           <t>USOSFR2Z</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="27" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
-        <v>0.0385</v>
-      </c>
-      <c r="D6" s="21">
+      <c r="C6" s="28">
+        <f>IF(RIGHT(B6,1)="W",$B$3+7*VALUE(LEFT(B6,LEN(B6)-1)),IF(RIGHT(B6,1)="M",EDATE($B$3,VALUE(LEFT(B6,LEN(B6)-1))),EDATE($B$3,12*VALUE(LEFT(B6,LEN(B6)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D6" s="29">
+        <f>(C6-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E6" s="21">
         <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E6" s="21">
+      <c r="F6" s="21">
         <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F6" s="21">
+      <c r="G6" s="21">
         <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G6" s="28">
-        <f>IFERROR((D6+E6)/2,IFERROR(F6,""))</f>
-        <v/>
-      </c>
-      <c r="H6" s="30" t="inlineStr"/>
+      <c r="H6" s="30">
+        <f>IFERROR((E6+F6)/2,IFERROR(G6,""))</f>
+        <v/>
+      </c>
+      <c r="I6" s="32" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -3143,31 +3179,36 @@
           <t>USOSFR3Z</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
-        <v>0.0577</v>
-      </c>
-      <c r="D7" s="21">
+      <c r="C7" s="28">
+        <f>IF(RIGHT(B7,1)="W",$B$3+7*VALUE(LEFT(B7,LEN(B7)-1)),IF(RIGHT(B7,1)="M",EDATE($B$3,VALUE(LEFT(B7,LEN(B7)-1))),EDATE($B$3,12*VALUE(LEFT(B7,LEN(B7)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D7" s="29">
+        <f>(C7-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E7" s="21">
         <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E7" s="21">
+      <c r="F7" s="21">
         <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="G7" s="21">
         <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G7" s="28">
-        <f>IFERROR((D7+E7)/2,IFERROR(F7,""))</f>
-        <v/>
-      </c>
-      <c r="H7" s="30" t="inlineStr"/>
+      <c r="H7" s="30">
+        <f>IFERROR((E7+F7)/2,IFERROR(G7,""))</f>
+        <v/>
+      </c>
+      <c r="I7" s="32" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -3175,31 +3216,36 @@
           <t>USOSFRA</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="27" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
-        <v>0.0833</v>
-      </c>
-      <c r="D8" s="21">
+      <c r="C8" s="28">
+        <f>IF(RIGHT(B8,1)="W",$B$3+7*VALUE(LEFT(B8,LEN(B8)-1)),IF(RIGHT(B8,1)="M",EDATE($B$3,VALUE(LEFT(B8,LEN(B8)-1))),EDATE($B$3,12*VALUE(LEFT(B8,LEN(B8)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D8" s="29">
+        <f>(C8-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E8" s="21">
         <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E8" s="21">
+      <c r="F8" s="21">
         <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F8" s="21">
+      <c r="G8" s="21">
         <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G8" s="28">
-        <f>IFERROR((D8+E8)/2,IFERROR(F8,""))</f>
-        <v/>
-      </c>
-      <c r="H8" s="29" t="inlineStr">
+      <c r="H8" s="30">
+        <f>IFERROR((E8+F8)/2,IFERROR(G8,""))</f>
+        <v/>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3211,31 +3257,36 @@
           <t>USOSFRB</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="27" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="D9" s="21">
+      <c r="C9" s="28">
+        <f>IF(RIGHT(B9,1)="W",$B$3+7*VALUE(LEFT(B9,LEN(B9)-1)),IF(RIGHT(B9,1)="M",EDATE($B$3,VALUE(LEFT(B9,LEN(B9)-1))),EDATE($B$3,12*VALUE(LEFT(B9,LEN(B9)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D9" s="29">
+        <f>(C9-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E9" s="21">
         <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E9" s="21">
+      <c r="F9" s="21">
         <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F9" s="21">
+      <c r="G9" s="21">
         <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G9" s="28">
-        <f>IFERROR((D9+E9)/2,IFERROR(F9,""))</f>
-        <v/>
-      </c>
-      <c r="H9" s="30" t="inlineStr"/>
+      <c r="H9" s="30">
+        <f>IFERROR((E9+F9)/2,IFERROR(G9,""))</f>
+        <v/>
+      </c>
+      <c r="I9" s="32" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -3243,31 +3294,36 @@
           <t>USOSFRC</t>
         </is>
       </c>
-      <c r="B10" s="26" t="inlineStr">
+      <c r="B10" s="27" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D10" s="21">
+      <c r="C10" s="28">
+        <f>IF(RIGHT(B10,1)="W",$B$3+7*VALUE(LEFT(B10,LEN(B10)-1)),IF(RIGHT(B10,1)="M",EDATE($B$3,VALUE(LEFT(B10,LEN(B10)-1))),EDATE($B$3,12*VALUE(LEFT(B10,LEN(B10)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D10" s="29">
+        <f>(C10-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E10" s="21">
         <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E10" s="21">
+      <c r="F10" s="21">
         <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F10" s="21">
+      <c r="G10" s="21">
         <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G10" s="28">
-        <f>IFERROR((D10+E10)/2,IFERROR(F10,""))</f>
-        <v/>
-      </c>
-      <c r="H10" s="29" t="inlineStr">
+      <c r="H10" s="30">
+        <f>IFERROR((E10+F10)/2,IFERROR(G10,""))</f>
+        <v/>
+      </c>
+      <c r="I10" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3279,31 +3335,36 @@
           <t>USOSFRD</t>
         </is>
       </c>
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>4M</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="D11" s="21">
+      <c r="C11" s="28">
+        <f>IF(RIGHT(B11,1)="W",$B$3+7*VALUE(LEFT(B11,LEN(B11)-1)),IF(RIGHT(B11,1)="M",EDATE($B$3,VALUE(LEFT(B11,LEN(B11)-1))),EDATE($B$3,12*VALUE(LEFT(B11,LEN(B11)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D11" s="29">
+        <f>(C11-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E11" s="21">
         <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E11" s="21">
+      <c r="F11" s="21">
         <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F11" s="21">
+      <c r="G11" s="21">
         <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G11" s="28">
-        <f>IFERROR((D11+E11)/2,IFERROR(F11,""))</f>
-        <v/>
-      </c>
-      <c r="H11" s="30" t="inlineStr"/>
+      <c r="H11" s="30">
+        <f>IFERROR((E11+F11)/2,IFERROR(G11,""))</f>
+        <v/>
+      </c>
+      <c r="I11" s="32" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -3311,31 +3372,36 @@
           <t>USOSFRE</t>
         </is>
       </c>
-      <c r="B12" s="26" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>5M</t>
         </is>
       </c>
-      <c r="C12" s="27" t="n">
-        <v>0.4167</v>
-      </c>
-      <c r="D12" s="21">
+      <c r="C12" s="28">
+        <f>IF(RIGHT(B12,1)="W",$B$3+7*VALUE(LEFT(B12,LEN(B12)-1)),IF(RIGHT(B12,1)="M",EDATE($B$3,VALUE(LEFT(B12,LEN(B12)-1))),EDATE($B$3,12*VALUE(LEFT(B12,LEN(B12)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D12" s="29">
+        <f>(C12-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E12" s="21">
         <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E12" s="21">
+      <c r="F12" s="21">
         <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="G12" s="21">
         <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G12" s="28">
-        <f>IFERROR((D12+E12)/2,IFERROR(F12,""))</f>
-        <v/>
-      </c>
-      <c r="H12" s="30" t="inlineStr"/>
+      <c r="H12" s="30">
+        <f>IFERROR((E12+F12)/2,IFERROR(G12,""))</f>
+        <v/>
+      </c>
+      <c r="I12" s="32" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -3343,31 +3409,36 @@
           <t>USOSFRF</t>
         </is>
       </c>
-      <c r="B13" s="26" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="D13" s="21">
+      <c r="C13" s="28">
+        <f>IF(RIGHT(B13,1)="W",$B$3+7*VALUE(LEFT(B13,LEN(B13)-1)),IF(RIGHT(B13,1)="M",EDATE($B$3,VALUE(LEFT(B13,LEN(B13)-1))),EDATE($B$3,12*VALUE(LEFT(B13,LEN(B13)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D13" s="29">
+        <f>(C13-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E13" s="21">
         <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E13" s="21">
+      <c r="F13" s="21">
         <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F13" s="21">
+      <c r="G13" s="21">
         <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G13" s="28">
-        <f>IFERROR((D13+E13)/2,IFERROR(F13,""))</f>
-        <v/>
-      </c>
-      <c r="H13" s="29" t="inlineStr">
+      <c r="H13" s="30">
+        <f>IFERROR((E13+F13)/2,IFERROR(G13,""))</f>
+        <v/>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3379,31 +3450,36 @@
           <t>USOSFRG</t>
         </is>
       </c>
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>7M</t>
         </is>
       </c>
-      <c r="C14" s="27" t="n">
-        <v>0.5833</v>
-      </c>
-      <c r="D14" s="21">
+      <c r="C14" s="28">
+        <f>IF(RIGHT(B14,1)="W",$B$3+7*VALUE(LEFT(B14,LEN(B14)-1)),IF(RIGHT(B14,1)="M",EDATE($B$3,VALUE(LEFT(B14,LEN(B14)-1))),EDATE($B$3,12*VALUE(LEFT(B14,LEN(B14)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D14" s="29">
+        <f>(C14-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E14" s="21">
         <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E14" s="21">
+      <c r="F14" s="21">
         <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F14" s="21">
+      <c r="G14" s="21">
         <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G14" s="28">
-        <f>IFERROR((D14+E14)/2,IFERROR(F14,""))</f>
-        <v/>
-      </c>
-      <c r="H14" s="30" t="inlineStr"/>
+      <c r="H14" s="30">
+        <f>IFERROR((E14+F14)/2,IFERROR(G14,""))</f>
+        <v/>
+      </c>
+      <c r="I14" s="32" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -3411,31 +3487,36 @@
           <t>USOSFRH</t>
         </is>
       </c>
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>8M</t>
         </is>
       </c>
-      <c r="C15" s="27" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="C15" s="28">
+        <f>IF(RIGHT(B15,1)="W",$B$3+7*VALUE(LEFT(B15,LEN(B15)-1)),IF(RIGHT(B15,1)="M",EDATE($B$3,VALUE(LEFT(B15,LEN(B15)-1))),EDATE($B$3,12*VALUE(LEFT(B15,LEN(B15)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D15" s="29">
+        <f>(C15-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E15" s="21">
         <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E15" s="21">
+      <c r="F15" s="21">
         <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F15" s="21">
+      <c r="G15" s="21">
         <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G15" s="28">
-        <f>IFERROR((D15+E15)/2,IFERROR(F15,""))</f>
-        <v/>
-      </c>
-      <c r="H15" s="30" t="inlineStr"/>
+      <c r="H15" s="30">
+        <f>IFERROR((E15+F15)/2,IFERROR(G15,""))</f>
+        <v/>
+      </c>
+      <c r="I15" s="32" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -3443,31 +3524,36 @@
           <t>USOSFRI</t>
         </is>
       </c>
-      <c r="B16" s="26" t="inlineStr">
+      <c r="B16" s="27" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="C16" s="28">
+        <f>IF(RIGHT(B16,1)="W",$B$3+7*VALUE(LEFT(B16,LEN(B16)-1)),IF(RIGHT(B16,1)="M",EDATE($B$3,VALUE(LEFT(B16,LEN(B16)-1))),EDATE($B$3,12*VALUE(LEFT(B16,LEN(B16)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D16" s="29">
+        <f>(C16-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E16" s="21">
         <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E16" s="21">
+      <c r="F16" s="21">
         <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F16" s="21">
+      <c r="G16" s="21">
         <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G16" s="28">
-        <f>IFERROR((D16+E16)/2,IFERROR(F16,""))</f>
-        <v/>
-      </c>
-      <c r="H16" s="30" t="inlineStr"/>
+      <c r="H16" s="30">
+        <f>IFERROR((E16+F16)/2,IFERROR(G16,""))</f>
+        <v/>
+      </c>
+      <c r="I16" s="32" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -3475,31 +3561,36 @@
           <t>USOSFRJ</t>
         </is>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>10M</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="C17" s="28">
+        <f>IF(RIGHT(B17,1)="W",$B$3+7*VALUE(LEFT(B17,LEN(B17)-1)),IF(RIGHT(B17,1)="M",EDATE($B$3,VALUE(LEFT(B17,LEN(B17)-1))),EDATE($B$3,12*VALUE(LEFT(B17,LEN(B17)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D17" s="29">
+        <f>(C17-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E17" s="21">
         <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E17" s="21">
+      <c r="F17" s="21">
         <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F17" s="21">
+      <c r="G17" s="21">
         <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G17" s="28">
-        <f>IFERROR((D17+E17)/2,IFERROR(F17,""))</f>
-        <v/>
-      </c>
-      <c r="H17" s="30" t="inlineStr"/>
+      <c r="H17" s="30">
+        <f>IFERROR((E17+F17)/2,IFERROR(G17,""))</f>
+        <v/>
+      </c>
+      <c r="I17" s="32" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -3507,31 +3598,36 @@
           <t>USOSFRK</t>
         </is>
       </c>
-      <c r="B18" s="26" t="inlineStr">
+      <c r="B18" s="27" t="inlineStr">
         <is>
           <t>11M</t>
         </is>
       </c>
-      <c r="C18" s="27" t="n">
-        <v>0.9167</v>
-      </c>
-      <c r="D18" s="21">
+      <c r="C18" s="28">
+        <f>IF(RIGHT(B18,1)="W",$B$3+7*VALUE(LEFT(B18,LEN(B18)-1)),IF(RIGHT(B18,1)="M",EDATE($B$3,VALUE(LEFT(B18,LEN(B18)-1))),EDATE($B$3,12*VALUE(LEFT(B18,LEN(B18)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D18" s="29">
+        <f>(C18-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E18" s="21">
         <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E18" s="21">
+      <c r="F18" s="21">
         <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F18" s="21">
+      <c r="G18" s="21">
         <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G18" s="28">
-        <f>IFERROR((D18+E18)/2,IFERROR(F18,""))</f>
-        <v/>
-      </c>
-      <c r="H18" s="30" t="inlineStr"/>
+      <c r="H18" s="30">
+        <f>IFERROR((E18+F18)/2,IFERROR(G18,""))</f>
+        <v/>
+      </c>
+      <c r="I18" s="32" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -3539,31 +3635,36 @@
           <t>USOSFR1</t>
         </is>
       </c>
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="21">
+      <c r="C19" s="28">
+        <f>IF(RIGHT(B19,1)="W",$B$3+7*VALUE(LEFT(B19,LEN(B19)-1)),IF(RIGHT(B19,1)="M",EDATE($B$3,VALUE(LEFT(B19,LEN(B19)-1))),EDATE($B$3,12*VALUE(LEFT(B19,LEN(B19)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D19" s="29">
+        <f>(C19-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E19" s="21">
         <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E19" s="21">
+      <c r="F19" s="21">
         <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F19" s="21">
+      <c r="G19" s="21">
         <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G19" s="28">
-        <f>IFERROR((D19+E19)/2,IFERROR(F19,""))</f>
-        <v/>
-      </c>
-      <c r="H19" s="30" t="inlineStr"/>
+      <c r="H19" s="30">
+        <f>IFERROR((E19+F19)/2,IFERROR(G19,""))</f>
+        <v/>
+      </c>
+      <c r="I19" s="32" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -3571,31 +3672,36 @@
           <t>USOSFR1F</t>
         </is>
       </c>
-      <c r="B20" s="26" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>18M</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D20" s="21">
+      <c r="C20" s="28">
+        <f>IF(RIGHT(B20,1)="W",$B$3+7*VALUE(LEFT(B20,LEN(B20)-1)),IF(RIGHT(B20,1)="M",EDATE($B$3,VALUE(LEFT(B20,LEN(B20)-1))),EDATE($B$3,12*VALUE(LEFT(B20,LEN(B20)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D20" s="29">
+        <f>(C20-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E20" s="21">
         <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E20" s="21">
+      <c r="F20" s="21">
         <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F20" s="21">
+      <c r="G20" s="21">
         <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G20" s="28">
-        <f>IFERROR((D20+E20)/2,IFERROR(F20,""))</f>
-        <v/>
-      </c>
-      <c r="H20" s="30" t="inlineStr"/>
+      <c r="H20" s="30">
+        <f>IFERROR((E20+F20)/2,IFERROR(G20,""))</f>
+        <v/>
+      </c>
+      <c r="I20" s="32" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -3603,31 +3709,36 @@
           <t>USOSFR2</t>
         </is>
       </c>
-      <c r="B21" s="26" t="inlineStr">
+      <c r="B21" s="27" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="C21" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="21">
+      <c r="C21" s="28">
+        <f>IF(RIGHT(B21,1)="W",$B$3+7*VALUE(LEFT(B21,LEN(B21)-1)),IF(RIGHT(B21,1)="M",EDATE($B$3,VALUE(LEFT(B21,LEN(B21)-1))),EDATE($B$3,12*VALUE(LEFT(B21,LEN(B21)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D21" s="29">
+        <f>(C21-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E21" s="21">
         <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E21" s="21">
+      <c r="F21" s="21">
         <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F21" s="21">
+      <c r="G21" s="21">
         <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G21" s="28">
-        <f>IFERROR((D21+E21)/2,IFERROR(F21,""))</f>
-        <v/>
-      </c>
-      <c r="H21" s="30" t="inlineStr"/>
+      <c r="H21" s="30">
+        <f>IFERROR((E21+F21)/2,IFERROR(G21,""))</f>
+        <v/>
+      </c>
+      <c r="I21" s="32" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -3635,31 +3746,36 @@
           <t>USOSFR3</t>
         </is>
       </c>
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>3Y</t>
         </is>
       </c>
-      <c r="C22" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="21">
+      <c r="C22" s="28">
+        <f>IF(RIGHT(B22,1)="W",$B$3+7*VALUE(LEFT(B22,LEN(B22)-1)),IF(RIGHT(B22,1)="M",EDATE($B$3,VALUE(LEFT(B22,LEN(B22)-1))),EDATE($B$3,12*VALUE(LEFT(B22,LEN(B22)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D22" s="29">
+        <f>(C22-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E22" s="21">
         <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E22" s="21">
+      <c r="F22" s="21">
         <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F22" s="21">
+      <c r="G22" s="21">
         <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G22" s="28">
-        <f>IFERROR((D22+E22)/2,IFERROR(F22,""))</f>
-        <v/>
-      </c>
-      <c r="H22" s="30" t="inlineStr"/>
+      <c r="H22" s="30">
+        <f>IFERROR((E22+F22)/2,IFERROR(G22,""))</f>
+        <v/>
+      </c>
+      <c r="I22" s="32" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -3667,31 +3783,36 @@
           <t>USOSFR4</t>
         </is>
       </c>
-      <c r="B23" s="26" t="inlineStr">
+      <c r="B23" s="27" t="inlineStr">
         <is>
           <t>4Y</t>
         </is>
       </c>
-      <c r="C23" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="D23" s="21">
+      <c r="C23" s="28">
+        <f>IF(RIGHT(B23,1)="W",$B$3+7*VALUE(LEFT(B23,LEN(B23)-1)),IF(RIGHT(B23,1)="M",EDATE($B$3,VALUE(LEFT(B23,LEN(B23)-1))),EDATE($B$3,12*VALUE(LEFT(B23,LEN(B23)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D23" s="29">
+        <f>(C23-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E23" s="21">
         <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E23" s="21">
+      <c r="F23" s="21">
         <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F23" s="21">
+      <c r="G23" s="21">
         <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G23" s="28">
-        <f>IFERROR((D23+E23)/2,IFERROR(F23,""))</f>
-        <v/>
-      </c>
-      <c r="H23" s="30" t="inlineStr"/>
+      <c r="H23" s="30">
+        <f>IFERROR((E23+F23)/2,IFERROR(G23,""))</f>
+        <v/>
+      </c>
+      <c r="I23" s="32" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -3699,31 +3820,36 @@
           <t>USOSFR5</t>
         </is>
       </c>
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="27" t="inlineStr">
         <is>
           <t>5Y</t>
         </is>
       </c>
-      <c r="C24" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="21">
+      <c r="C24" s="28">
+        <f>IF(RIGHT(B24,1)="W",$B$3+7*VALUE(LEFT(B24,LEN(B24)-1)),IF(RIGHT(B24,1)="M",EDATE($B$3,VALUE(LEFT(B24,LEN(B24)-1))),EDATE($B$3,12*VALUE(LEFT(B24,LEN(B24)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D24" s="29">
+        <f>(C24-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E24" s="21">
         <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E24" s="21">
+      <c r="F24" s="21">
         <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F24" s="21">
+      <c r="G24" s="21">
         <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G24" s="28">
-        <f>IFERROR((D24+E24)/2,IFERROR(F24,""))</f>
-        <v/>
-      </c>
-      <c r="H24" s="29" t="inlineStr">
+      <c r="H24" s="30">
+        <f>IFERROR((E24+F24)/2,IFERROR(G24,""))</f>
+        <v/>
+      </c>
+      <c r="I24" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3735,31 +3861,36 @@
           <t>USOSFR6</t>
         </is>
       </c>
-      <c r="B25" s="26" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>6Y</t>
         </is>
       </c>
-      <c r="C25" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="D25" s="21">
+      <c r="C25" s="28">
+        <f>IF(RIGHT(B25,1)="W",$B$3+7*VALUE(LEFT(B25,LEN(B25)-1)),IF(RIGHT(B25,1)="M",EDATE($B$3,VALUE(LEFT(B25,LEN(B25)-1))),EDATE($B$3,12*VALUE(LEFT(B25,LEN(B25)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D25" s="29">
+        <f>(C25-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E25" s="21">
         <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E25" s="21">
+      <c r="F25" s="21">
         <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F25" s="21">
+      <c r="G25" s="21">
         <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G25" s="28">
-        <f>IFERROR((D25+E25)/2,IFERROR(F25,""))</f>
-        <v/>
-      </c>
-      <c r="H25" s="29" t="inlineStr">
+      <c r="H25" s="30">
+        <f>IFERROR((E25+F25)/2,IFERROR(G25,""))</f>
+        <v/>
+      </c>
+      <c r="I25" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3771,31 +3902,36 @@
           <t>USOSFR7</t>
         </is>
       </c>
-      <c r="B26" s="26" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>7Y</t>
         </is>
       </c>
-      <c r="C26" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="21">
+      <c r="C26" s="28">
+        <f>IF(RIGHT(B26,1)="W",$B$3+7*VALUE(LEFT(B26,LEN(B26)-1)),IF(RIGHT(B26,1)="M",EDATE($B$3,VALUE(LEFT(B26,LEN(B26)-1))),EDATE($B$3,12*VALUE(LEFT(B26,LEN(B26)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D26" s="29">
+        <f>(C26-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E26" s="21">
         <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E26" s="21">
+      <c r="F26" s="21">
         <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F26" s="21">
+      <c r="G26" s="21">
         <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G26" s="28">
-        <f>IFERROR((D26+E26)/2,IFERROR(F26,""))</f>
-        <v/>
-      </c>
-      <c r="H26" s="29" t="inlineStr">
+      <c r="H26" s="30">
+        <f>IFERROR((E26+F26)/2,IFERROR(G26,""))</f>
+        <v/>
+      </c>
+      <c r="I26" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3807,31 +3943,36 @@
           <t>USOSFR8</t>
         </is>
       </c>
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>8Y</t>
         </is>
       </c>
-      <c r="C27" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="D27" s="21">
+      <c r="C27" s="28">
+        <f>IF(RIGHT(B27,1)="W",$B$3+7*VALUE(LEFT(B27,LEN(B27)-1)),IF(RIGHT(B27,1)="M",EDATE($B$3,VALUE(LEFT(B27,LEN(B27)-1))),EDATE($B$3,12*VALUE(LEFT(B27,LEN(B27)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D27" s="29">
+        <f>(C27-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
         <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E27" s="21">
+      <c r="F27" s="21">
         <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F27" s="21">
+      <c r="G27" s="21">
         <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G27" s="28">
-        <f>IFERROR((D27+E27)/2,IFERROR(F27,""))</f>
-        <v/>
-      </c>
-      <c r="H27" s="29" t="inlineStr">
+      <c r="H27" s="30">
+        <f>IFERROR((E27+F27)/2,IFERROR(G27,""))</f>
+        <v/>
+      </c>
+      <c r="I27" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3843,31 +3984,36 @@
           <t>USOSFR9</t>
         </is>
       </c>
-      <c r="B28" s="26" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>9Y</t>
         </is>
       </c>
-      <c r="C28" s="27" t="n">
-        <v>9</v>
-      </c>
-      <c r="D28" s="21">
+      <c r="C28" s="28">
+        <f>IF(RIGHT(B28,1)="W",$B$3+7*VALUE(LEFT(B28,LEN(B28)-1)),IF(RIGHT(B28,1)="M",EDATE($B$3,VALUE(LEFT(B28,LEN(B28)-1))),EDATE($B$3,12*VALUE(LEFT(B28,LEN(B28)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D28" s="29">
+        <f>(C28-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
         <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E28" s="21">
+      <c r="F28" s="21">
         <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F28" s="21">
+      <c r="G28" s="21">
         <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G28" s="28">
-        <f>IFERROR((D28+E28)/2,IFERROR(F28,""))</f>
-        <v/>
-      </c>
-      <c r="H28" s="29" t="inlineStr">
+      <c r="H28" s="30">
+        <f>IFERROR((E28+F28)/2,IFERROR(G28,""))</f>
+        <v/>
+      </c>
+      <c r="I28" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3879,31 +4025,36 @@
           <t>USOSFR10</t>
         </is>
       </c>
-      <c r="B29" s="26" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>10Y</t>
         </is>
       </c>
-      <c r="C29" s="27" t="n">
-        <v>10</v>
-      </c>
-      <c r="D29" s="21">
+      <c r="C29" s="28">
+        <f>IF(RIGHT(B29,1)="W",$B$3+7*VALUE(LEFT(B29,LEN(B29)-1)),IF(RIGHT(B29,1)="M",EDATE($B$3,VALUE(LEFT(B29,LEN(B29)-1))),EDATE($B$3,12*VALUE(LEFT(B29,LEN(B29)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D29" s="29">
+        <f>(C29-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
         <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E29" s="21">
+      <c r="F29" s="21">
         <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F29" s="21">
+      <c r="G29" s="21">
         <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G29" s="28">
-        <f>IFERROR((D29+E29)/2,IFERROR(F29,""))</f>
-        <v/>
-      </c>
-      <c r="H29" s="29" t="inlineStr">
+      <c r="H29" s="30">
+        <f>IFERROR((E29+F29)/2,IFERROR(G29,""))</f>
+        <v/>
+      </c>
+      <c r="I29" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3915,31 +4066,36 @@
           <t>USOSFR12</t>
         </is>
       </c>
-      <c r="B30" s="26" t="inlineStr">
+      <c r="B30" s="27" t="inlineStr">
         <is>
           <t>12Y</t>
         </is>
       </c>
-      <c r="C30" s="27" t="n">
-        <v>12</v>
-      </c>
-      <c r="D30" s="21">
+      <c r="C30" s="28">
+        <f>IF(RIGHT(B30,1)="W",$B$3+7*VALUE(LEFT(B30,LEN(B30)-1)),IF(RIGHT(B30,1)="M",EDATE($B$3,VALUE(LEFT(B30,LEN(B30)-1))),EDATE($B$3,12*VALUE(LEFT(B30,LEN(B30)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D30" s="29">
+        <f>(C30-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
         <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E30" s="21">
+      <c r="F30" s="21">
         <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F30" s="21">
+      <c r="G30" s="21">
         <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G30" s="28">
-        <f>IFERROR((D30+E30)/2,IFERROR(F30,""))</f>
-        <v/>
-      </c>
-      <c r="H30" s="29" t="inlineStr">
+      <c r="H30" s="30">
+        <f>IFERROR((E30+F30)/2,IFERROR(G30,""))</f>
+        <v/>
+      </c>
+      <c r="I30" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3951,31 +4107,36 @@
           <t>USOSFR15</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>15Y</t>
         </is>
       </c>
-      <c r="C31" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="D31" s="21">
+      <c r="C31" s="28">
+        <f>IF(RIGHT(B31,1)="W",$B$3+7*VALUE(LEFT(B31,LEN(B31)-1)),IF(RIGHT(B31,1)="M",EDATE($B$3,VALUE(LEFT(B31,LEN(B31)-1))),EDATE($B$3,12*VALUE(LEFT(B31,LEN(B31)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D31" s="29">
+        <f>(C31-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
         <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E31" s="21">
+      <c r="F31" s="21">
         <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F31" s="21">
+      <c r="G31" s="21">
         <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G31" s="28">
-        <f>IFERROR((D31+E31)/2,IFERROR(F31,""))</f>
-        <v/>
-      </c>
-      <c r="H31" s="29" t="inlineStr">
+      <c r="H31" s="30">
+        <f>IFERROR((E31+F31)/2,IFERROR(G31,""))</f>
+        <v/>
+      </c>
+      <c r="I31" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -3987,31 +4148,36 @@
           <t>USOSFR20</t>
         </is>
       </c>
-      <c r="B32" s="26" t="inlineStr">
+      <c r="B32" s="27" t="inlineStr">
         <is>
           <t>20Y</t>
         </is>
       </c>
-      <c r="C32" s="27" t="n">
-        <v>20</v>
-      </c>
-      <c r="D32" s="21">
+      <c r="C32" s="28">
+        <f>IF(RIGHT(B32,1)="W",$B$3+7*VALUE(LEFT(B32,LEN(B32)-1)),IF(RIGHT(B32,1)="M",EDATE($B$3,VALUE(LEFT(B32,LEN(B32)-1))),EDATE($B$3,12*VALUE(LEFT(B32,LEN(B32)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D32" s="29">
+        <f>(C32-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
         <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E32" s="21">
+      <c r="F32" s="21">
         <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F32" s="21">
+      <c r="G32" s="21">
         <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G32" s="28">
-        <f>IFERROR((D32+E32)/2,IFERROR(F32,""))</f>
-        <v/>
-      </c>
-      <c r="H32" s="29" t="inlineStr">
+      <c r="H32" s="30">
+        <f>IFERROR((E32+F32)/2,IFERROR(G32,""))</f>
+        <v/>
+      </c>
+      <c r="I32" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4023,31 +4189,36 @@
           <t>USOSFR25</t>
         </is>
       </c>
-      <c r="B33" s="26" t="inlineStr">
+      <c r="B33" s="27" t="inlineStr">
         <is>
           <t>25Y</t>
         </is>
       </c>
-      <c r="C33" s="27" t="n">
-        <v>25</v>
-      </c>
-      <c r="D33" s="21">
+      <c r="C33" s="28">
+        <f>IF(RIGHT(B33,1)="W",$B$3+7*VALUE(LEFT(B33,LEN(B33)-1)),IF(RIGHT(B33,1)="M",EDATE($B$3,VALUE(LEFT(B33,LEN(B33)-1))),EDATE($B$3,12*VALUE(LEFT(B33,LEN(B33)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D33" s="29">
+        <f>(C33-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
         <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E33" s="21">
+      <c r="F33" s="21">
         <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F33" s="21">
+      <c r="G33" s="21">
         <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G33" s="28">
-        <f>IFERROR((D33+E33)/2,IFERROR(F33,""))</f>
-        <v/>
-      </c>
-      <c r="H33" s="29" t="inlineStr">
+      <c r="H33" s="30">
+        <f>IFERROR((E33+F33)/2,IFERROR(G33,""))</f>
+        <v/>
+      </c>
+      <c r="I33" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4059,31 +4230,36 @@
           <t>USOSFR30</t>
         </is>
       </c>
-      <c r="B34" s="26" t="inlineStr">
+      <c r="B34" s="27" t="inlineStr">
         <is>
           <t>30Y</t>
         </is>
       </c>
-      <c r="C34" s="27" t="n">
-        <v>30</v>
-      </c>
-      <c r="D34" s="21">
+      <c r="C34" s="28">
+        <f>IF(RIGHT(B34,1)="W",$B$3+7*VALUE(LEFT(B34,LEN(B34)-1)),IF(RIGHT(B34,1)="M",EDATE($B$3,VALUE(LEFT(B34,LEN(B34)-1))),EDATE($B$3,12*VALUE(LEFT(B34,LEN(B34)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D34" s="29">
+        <f>(C34-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E34" s="21">
         <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E34" s="21">
+      <c r="F34" s="21">
         <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F34" s="21">
+      <c r="G34" s="21">
         <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G34" s="28">
-        <f>IFERROR((D34+E34)/2,IFERROR(F34,""))</f>
-        <v/>
-      </c>
-      <c r="H34" s="29" t="inlineStr">
+      <c r="H34" s="30">
+        <f>IFERROR((E34+F34)/2,IFERROR(G34,""))</f>
+        <v/>
+      </c>
+      <c r="I34" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4095,31 +4271,36 @@
           <t>USOSFR40</t>
         </is>
       </c>
-      <c r="B35" s="26" t="inlineStr">
+      <c r="B35" s="27" t="inlineStr">
         <is>
           <t>40Y</t>
         </is>
       </c>
-      <c r="C35" s="27" t="n">
-        <v>40</v>
-      </c>
-      <c r="D35" s="21">
+      <c r="C35" s="28">
+        <f>IF(RIGHT(B35,1)="W",$B$3+7*VALUE(LEFT(B35,LEN(B35)-1)),IF(RIGHT(B35,1)="M",EDATE($B$3,VALUE(LEFT(B35,LEN(B35)-1))),EDATE($B$3,12*VALUE(LEFT(B35,LEN(B35)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D35" s="29">
+        <f>(C35-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E35" s="21">
         <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E35" s="21">
+      <c r="F35" s="21">
         <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F35" s="21">
+      <c r="G35" s="21">
         <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G35" s="28">
-        <f>IFERROR((D35+E35)/2,IFERROR(F35,""))</f>
-        <v/>
-      </c>
-      <c r="H35" s="29" t="inlineStr">
+      <c r="H35" s="30">
+        <f>IFERROR((E35+F35)/2,IFERROR(G35,""))</f>
+        <v/>
+      </c>
+      <c r="I35" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
@@ -4131,48 +4312,55 @@
           <t>USOSFR50</t>
         </is>
       </c>
-      <c r="B36" s="26" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>50Y</t>
         </is>
       </c>
-      <c r="C36" s="27" t="n">
-        <v>50</v>
-      </c>
-      <c r="D36" s="21">
+      <c r="C36" s="28">
+        <f>IF(RIGHT(B36,1)="W",$B$3+7*VALUE(LEFT(B36,LEN(B36)-1)),IF(RIGHT(B36,1)="M",EDATE($B$3,VALUE(LEFT(B36,LEN(B36)-1))),EDATE($B$3,12*VALUE(LEFT(B36,LEN(B36)-1)))))</f>
+        <v/>
+      </c>
+      <c r="D36" s="29">
+        <f>(C36-$B$3)/365</f>
+        <v/>
+      </c>
+      <c r="E36" s="21">
         <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
         <v/>
       </c>
-      <c r="E36" s="21">
+      <c r="F36" s="21">
         <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
         <v/>
       </c>
-      <c r="F36" s="21">
+      <c r="G36" s="21">
         <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
         <v/>
       </c>
-      <c r="G36" s="28">
-        <f>IFERROR((D36+E36)/2,IFERROR(F36,""))</f>
-        <v/>
-      </c>
-      <c r="H36" s="29" t="inlineStr">
+      <c r="H36" s="30">
+        <f>IFERROR((E36+F36)/2,IFERROR(G36,""))</f>
+        <v/>
+      </c>
+      <c r="I36" s="31" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="26" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="11" t="inlineStr">
         <is>
-          <t>"In bootstrap set" = Y marks the recommended restricted calibration set (front: 1W,1M,3M,6M ; long end: 5Y–50Y). The 3M–5Y gap is filled by SR3 futures on the SOFR_Futures tab.</t>
-        </is>
-      </c>
-    </row>
+          <t>Maturity date and Tenor (yrs) are live formulas parsed from the tenor label (e.g. "18M" → EDATE(spot,18)) — change the tenor or the valuation date and they update. "In bootstrap set" = Y marks the recommended restricted calibration set (front 1W,1M,3M,6M; long end 5Y–50Y); the 3M–5Y gap is filled by SR3 futures on the SOFR_Futures tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A38:H38"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="4">
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A38:I39"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4312,7 +4500,7 @@
         <f>$B$4+7</f>
         <v/>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="33">
         <f>(B8-$B$4)/365</f>
         <v/>
       </c>
@@ -4321,14 +4509,14 @@
         <v/>
       </c>
       <c r="E8" s="21">
-        <f>'SOFR_OIS_Quotes'!$G5</f>
+        <f>'SOFR_OIS_Quotes'!$H5</f>
         <v/>
       </c>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="34">
         <f>1/(1+(E8/100)*D8)</f>
         <v/>
       </c>
@@ -4343,8 +4531,8 @@
         <f>(1/H8-1)/D8*100</f>
         <v/>
       </c>
-      <c r="L8" s="33" t="n"/>
-      <c r="M8" s="34">
+      <c r="L8" s="35" t="n"/>
+      <c r="M8" s="36">
         <f>IF(L8="","",(J8-L8)*100)</f>
         <v/>
       </c>
@@ -4359,7 +4547,7 @@
         <f>$B$4+14</f>
         <v/>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="37">
         <f>(B9-$B$4)/365</f>
         <v/>
       </c>
@@ -4368,7 +4556,7 @@
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>'SOFR_OIS_Quotes'!$G6</f>
+        <f>'SOFR_OIS_Quotes'!$H6</f>
         <v/>
       </c>
       <c r="F9" s="23" t="n"/>
@@ -4376,7 +4564,7 @@
         <f>SUM($I$8:I8)</f>
         <v/>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="38">
         <f>1/(1+(E9/100)*D9)</f>
         <v/>
       </c>
@@ -4391,8 +4579,8 @@
         <f>(H8/H9-1)/((B9-B8)/360)*100</f>
         <v/>
       </c>
-      <c r="L9" s="33" t="n"/>
-      <c r="M9" s="37">
+      <c r="L9" s="35" t="n"/>
+      <c r="M9" s="39">
         <f>IF(L9="","",(J9-L9)*100)</f>
         <v/>
       </c>
@@ -4407,7 +4595,7 @@
         <f>$B$4+21</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="33">
         <f>(B10-$B$4)/365</f>
         <v/>
       </c>
@@ -4416,7 +4604,7 @@
         <v/>
       </c>
       <c r="E10" s="21">
-        <f>'SOFR_OIS_Quotes'!$G7</f>
+        <f>'SOFR_OIS_Quotes'!$H7</f>
         <v/>
       </c>
       <c r="F10" s="8" t="n"/>
@@ -4424,7 +4612,7 @@
         <f>SUM($I$8:I9)</f>
         <v/>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="34">
         <f>1/(1+(E10/100)*D10)</f>
         <v/>
       </c>
@@ -4439,8 +4627,8 @@
         <f>(H9/H10-1)/((B10-B9)/360)*100</f>
         <v/>
       </c>
-      <c r="L10" s="33" t="n"/>
-      <c r="M10" s="34">
+      <c r="L10" s="35" t="n"/>
+      <c r="M10" s="36">
         <f>IF(L10="","",(J10-L10)*100)</f>
         <v/>
       </c>
@@ -4455,7 +4643,7 @@
         <f>EDATE($B$4,1)</f>
         <v/>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="37">
         <f>(B11-$B$4)/365</f>
         <v/>
       </c>
@@ -4464,7 +4652,7 @@
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>'SOFR_OIS_Quotes'!$G8</f>
+        <f>'SOFR_OIS_Quotes'!$H8</f>
         <v/>
       </c>
       <c r="F11" s="23" t="n"/>
@@ -4472,7 +4660,7 @@
         <f>SUM($I$8:I10)</f>
         <v/>
       </c>
-      <c r="H11" s="36">
+      <c r="H11" s="38">
         <f>1/(1+(E11/100)*D11)</f>
         <v/>
       </c>
@@ -4487,8 +4675,8 @@
         <f>(H10/H11-1)/((B11-B10)/360)*100</f>
         <v/>
       </c>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="37">
+      <c r="L11" s="35" t="n"/>
+      <c r="M11" s="39">
         <f>IF(L11="","",(J11-L11)*100)</f>
         <v/>
       </c>
@@ -4503,7 +4691,7 @@
         <f>EDATE($B$4,2)</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="33">
         <f>(B12-$B$4)/365</f>
         <v/>
       </c>
@@ -4512,7 +4700,7 @@
         <v/>
       </c>
       <c r="E12" s="21">
-        <f>'SOFR_OIS_Quotes'!$G9</f>
+        <f>'SOFR_OIS_Quotes'!$H9</f>
         <v/>
       </c>
       <c r="F12" s="8" t="n"/>
@@ -4520,7 +4708,7 @@
         <f>SUM($I$8:I11)</f>
         <v/>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="34">
         <f>1/(1+(E12/100)*D12)</f>
         <v/>
       </c>
@@ -4535,8 +4723,8 @@
         <f>(H11/H12-1)/((B12-B11)/360)*100</f>
         <v/>
       </c>
-      <c r="L12" s="33" t="n"/>
-      <c r="M12" s="34">
+      <c r="L12" s="35" t="n"/>
+      <c r="M12" s="36">
         <f>IF(L12="","",(J12-L12)*100)</f>
         <v/>
       </c>
@@ -4551,7 +4739,7 @@
         <f>EDATE($B$4,3)</f>
         <v/>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="37">
         <f>(B13-$B$4)/365</f>
         <v/>
       </c>
@@ -4560,7 +4748,7 @@
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>'SOFR_OIS_Quotes'!$G10</f>
+        <f>'SOFR_OIS_Quotes'!$H10</f>
         <v/>
       </c>
       <c r="F13" s="23" t="n"/>
@@ -4568,7 +4756,7 @@
         <f>SUM($I$8:I12)</f>
         <v/>
       </c>
-      <c r="H13" s="36">
+      <c r="H13" s="38">
         <f>1/(1+(E13/100)*D13)</f>
         <v/>
       </c>
@@ -4583,8 +4771,8 @@
         <f>(H12/H13-1)/((B13-B12)/360)*100</f>
         <v/>
       </c>
-      <c r="L13" s="33" t="n"/>
-      <c r="M13" s="37">
+      <c r="L13" s="35" t="n"/>
+      <c r="M13" s="39">
         <f>IF(L13="","",(J13-L13)*100)</f>
         <v/>
       </c>
@@ -4599,7 +4787,7 @@
         <f>EDATE($B$4,4)</f>
         <v/>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="33">
         <f>(B14-$B$4)/365</f>
         <v/>
       </c>
@@ -4608,7 +4796,7 @@
         <v/>
       </c>
       <c r="E14" s="21">
-        <f>'SOFR_OIS_Quotes'!$G11</f>
+        <f>'SOFR_OIS_Quotes'!$H11</f>
         <v/>
       </c>
       <c r="F14" s="8" t="n"/>
@@ -4616,7 +4804,7 @@
         <f>SUM($I$8:I13)</f>
         <v/>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="34">
         <f>1/(1+(E14/100)*D14)</f>
         <v/>
       </c>
@@ -4631,8 +4819,8 @@
         <f>(H13/H14-1)/((B14-B13)/360)*100</f>
         <v/>
       </c>
-      <c r="L14" s="33" t="n"/>
-      <c r="M14" s="34">
+      <c r="L14" s="35" t="n"/>
+      <c r="M14" s="36">
         <f>IF(L14="","",(J14-L14)*100)</f>
         <v/>
       </c>
@@ -4647,7 +4835,7 @@
         <f>EDATE($B$4,5)</f>
         <v/>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="37">
         <f>(B15-$B$4)/365</f>
         <v/>
       </c>
@@ -4656,7 +4844,7 @@
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>'SOFR_OIS_Quotes'!$G12</f>
+        <f>'SOFR_OIS_Quotes'!$H12</f>
         <v/>
       </c>
       <c r="F15" s="23" t="n"/>
@@ -4664,7 +4852,7 @@
         <f>SUM($I$8:I14)</f>
         <v/>
       </c>
-      <c r="H15" s="36">
+      <c r="H15" s="38">
         <f>1/(1+(E15/100)*D15)</f>
         <v/>
       </c>
@@ -4679,8 +4867,8 @@
         <f>(H14/H15-1)/((B15-B14)/360)*100</f>
         <v/>
       </c>
-      <c r="L15" s="33" t="n"/>
-      <c r="M15" s="37">
+      <c r="L15" s="35" t="n"/>
+      <c r="M15" s="39">
         <f>IF(L15="","",(J15-L15)*100)</f>
         <v/>
       </c>
@@ -4695,7 +4883,7 @@
         <f>EDATE($B$4,6)</f>
         <v/>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="33">
         <f>(B16-$B$4)/365</f>
         <v/>
       </c>
@@ -4704,7 +4892,7 @@
         <v/>
       </c>
       <c r="E16" s="21">
-        <f>'SOFR_OIS_Quotes'!$G13</f>
+        <f>'SOFR_OIS_Quotes'!$H13</f>
         <v/>
       </c>
       <c r="F16" s="8" t="n"/>
@@ -4712,7 +4900,7 @@
         <f>SUM($I$8:I15)</f>
         <v/>
       </c>
-      <c r="H16" s="32">
+      <c r="H16" s="34">
         <f>1/(1+(E16/100)*D16)</f>
         <v/>
       </c>
@@ -4727,8 +4915,8 @@
         <f>(H15/H16-1)/((B16-B15)/360)*100</f>
         <v/>
       </c>
-      <c r="L16" s="33" t="n"/>
-      <c r="M16" s="34">
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="36">
         <f>IF(L16="","",(J16-L16)*100)</f>
         <v/>
       </c>
@@ -4743,7 +4931,7 @@
         <f>EDATE($B$4,7)</f>
         <v/>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="37">
         <f>(B17-$B$4)/365</f>
         <v/>
       </c>
@@ -4752,7 +4940,7 @@
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>'SOFR_OIS_Quotes'!$G14</f>
+        <f>'SOFR_OIS_Quotes'!$H14</f>
         <v/>
       </c>
       <c r="F17" s="23" t="n"/>
@@ -4760,7 +4948,7 @@
         <f>SUM($I$8:I16)</f>
         <v/>
       </c>
-      <c r="H17" s="36">
+      <c r="H17" s="38">
         <f>1/(1+(E17/100)*D17)</f>
         <v/>
       </c>
@@ -4775,8 +4963,8 @@
         <f>(H16/H17-1)/((B17-B16)/360)*100</f>
         <v/>
       </c>
-      <c r="L17" s="33" t="n"/>
-      <c r="M17" s="37">
+      <c r="L17" s="35" t="n"/>
+      <c r="M17" s="39">
         <f>IF(L17="","",(J17-L17)*100)</f>
         <v/>
       </c>
@@ -4791,7 +4979,7 @@
         <f>EDATE($B$4,8)</f>
         <v/>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="33">
         <f>(B18-$B$4)/365</f>
         <v/>
       </c>
@@ -4800,7 +4988,7 @@
         <v/>
       </c>
       <c r="E18" s="21">
-        <f>'SOFR_OIS_Quotes'!$G15</f>
+        <f>'SOFR_OIS_Quotes'!$H15</f>
         <v/>
       </c>
       <c r="F18" s="8" t="n"/>
@@ -4808,7 +4996,7 @@
         <f>SUM($I$8:I17)</f>
         <v/>
       </c>
-      <c r="H18" s="32">
+      <c r="H18" s="34">
         <f>1/(1+(E18/100)*D18)</f>
         <v/>
       </c>
@@ -4823,8 +5011,8 @@
         <f>(H17/H18-1)/((B18-B17)/360)*100</f>
         <v/>
       </c>
-      <c r="L18" s="33" t="n"/>
-      <c r="M18" s="34">
+      <c r="L18" s="35" t="n"/>
+      <c r="M18" s="36">
         <f>IF(L18="","",(J18-L18)*100)</f>
         <v/>
       </c>
@@ -4839,7 +5027,7 @@
         <f>EDATE($B$4,9)</f>
         <v/>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="37">
         <f>(B19-$B$4)/365</f>
         <v/>
       </c>
@@ -4848,7 +5036,7 @@
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>'SOFR_OIS_Quotes'!$G16</f>
+        <f>'SOFR_OIS_Quotes'!$H16</f>
         <v/>
       </c>
       <c r="F19" s="23" t="n"/>
@@ -4856,7 +5044,7 @@
         <f>SUM($I$8:I18)</f>
         <v/>
       </c>
-      <c r="H19" s="36">
+      <c r="H19" s="38">
         <f>1/(1+(E19/100)*D19)</f>
         <v/>
       </c>
@@ -4871,8 +5059,8 @@
         <f>(H18/H19-1)/((B19-B18)/360)*100</f>
         <v/>
       </c>
-      <c r="L19" s="33" t="n"/>
-      <c r="M19" s="37">
+      <c r="L19" s="35" t="n"/>
+      <c r="M19" s="39">
         <f>IF(L19="","",(J19-L19)*100)</f>
         <v/>
       </c>
@@ -4887,7 +5075,7 @@
         <f>EDATE($B$4,10)</f>
         <v/>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="33">
         <f>(B20-$B$4)/365</f>
         <v/>
       </c>
@@ -4896,7 +5084,7 @@
         <v/>
       </c>
       <c r="E20" s="21">
-        <f>'SOFR_OIS_Quotes'!$G17</f>
+        <f>'SOFR_OIS_Quotes'!$H17</f>
         <v/>
       </c>
       <c r="F20" s="8" t="n"/>
@@ -4904,7 +5092,7 @@
         <f>SUM($I$8:I19)</f>
         <v/>
       </c>
-      <c r="H20" s="32">
+      <c r="H20" s="34">
         <f>1/(1+(E20/100)*D20)</f>
         <v/>
       </c>
@@ -4919,8 +5107,8 @@
         <f>(H19/H20-1)/((B20-B19)/360)*100</f>
         <v/>
       </c>
-      <c r="L20" s="33" t="n"/>
-      <c r="M20" s="34">
+      <c r="L20" s="35" t="n"/>
+      <c r="M20" s="36">
         <f>IF(L20="","",(J20-L20)*100)</f>
         <v/>
       </c>
@@ -4935,7 +5123,7 @@
         <f>EDATE($B$4,11)</f>
         <v/>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="37">
         <f>(B21-$B$4)/365</f>
         <v/>
       </c>
@@ -4944,7 +5132,7 @@
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>'SOFR_OIS_Quotes'!$G18</f>
+        <f>'SOFR_OIS_Quotes'!$H18</f>
         <v/>
       </c>
       <c r="F21" s="23" t="n"/>
@@ -4952,7 +5140,7 @@
         <f>SUM($I$8:I20)</f>
         <v/>
       </c>
-      <c r="H21" s="36">
+      <c r="H21" s="38">
         <f>1/(1+(E21/100)*D21)</f>
         <v/>
       </c>
@@ -4967,8 +5155,8 @@
         <f>(H20/H21-1)/((B21-B20)/360)*100</f>
         <v/>
       </c>
-      <c r="L21" s="33" t="n"/>
-      <c r="M21" s="37">
+      <c r="L21" s="35" t="n"/>
+      <c r="M21" s="39">
         <f>IF(L21="","",(J21-L21)*100)</f>
         <v/>
       </c>
@@ -4983,7 +5171,7 @@
         <f>EDATE($B$4,12)</f>
         <v/>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="33">
         <f>(B22-$B$4)/365</f>
         <v/>
       </c>
@@ -4992,7 +5180,7 @@
         <v/>
       </c>
       <c r="E22" s="21">
-        <f>'SOFR_OIS_Quotes'!$G19</f>
+        <f>'SOFR_OIS_Quotes'!$H19</f>
         <v/>
       </c>
       <c r="F22" s="21">
@@ -5003,7 +5191,7 @@
         <f>SUM($I$8:I21)</f>
         <v/>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="34">
         <f>1/(1+(E22/100)*D22)</f>
         <v/>
       </c>
@@ -5019,8 +5207,8 @@
         <f>(H21/H22-1)/((B22-B21)/360)*100</f>
         <v/>
       </c>
-      <c r="L22" s="33" t="n"/>
-      <c r="M22" s="34">
+      <c r="L22" s="35" t="n"/>
+      <c r="M22" s="36">
         <f>IF(L22="","",(J22-L22)*100)</f>
         <v/>
       </c>
@@ -5035,7 +5223,7 @@
         <f>EDATE($B$4,18)</f>
         <v/>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="37">
         <f>(B23-$B$4)/365</f>
         <v/>
       </c>
@@ -5044,7 +5232,7 @@
         <v/>
       </c>
       <c r="E23" s="17">
-        <f>'SOFR_OIS_Quotes'!$G20</f>
+        <f>'SOFR_OIS_Quotes'!$H20</f>
         <v/>
       </c>
       <c r="F23" s="17">
@@ -5055,7 +5243,7 @@
         <f>SUM($I$8:I22)</f>
         <v/>
       </c>
-      <c r="H23" s="36">
+      <c r="H23" s="38">
         <f>(1-(E23/100)*G23)/(1+(E23/100)*F23)</f>
         <v/>
       </c>
@@ -5070,8 +5258,8 @@
         <f>(H22/H23-1)/((B23-B22)/360)*100</f>
         <v/>
       </c>
-      <c r="L23" s="33" t="n"/>
-      <c r="M23" s="37">
+      <c r="L23" s="35" t="n"/>
+      <c r="M23" s="39">
         <f>IF(L23="","",(J23-L23)*100)</f>
         <v/>
       </c>
@@ -5086,7 +5274,7 @@
         <f>EDATE($B$4,24)</f>
         <v/>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="33">
         <f>(B24-$B$4)/365</f>
         <v/>
       </c>
@@ -5095,7 +5283,7 @@
         <v/>
       </c>
       <c r="E24" s="21">
-        <f>'SOFR_OIS_Quotes'!$G21</f>
+        <f>'SOFR_OIS_Quotes'!$H21</f>
         <v/>
       </c>
       <c r="F24" s="21">
@@ -5106,7 +5294,7 @@
         <f>SUM($I$8:I23)</f>
         <v/>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="34">
         <f>(1-(E24/100)*G24)/(1+(E24/100)*F24)</f>
         <v/>
       </c>
@@ -5122,8 +5310,8 @@
         <f>(H23/H24-1)/((B24-B23)/360)*100</f>
         <v/>
       </c>
-      <c r="L24" s="33" t="n"/>
-      <c r="M24" s="34">
+      <c r="L24" s="35" t="n"/>
+      <c r="M24" s="36">
         <f>IF(L24="","",(J24-L24)*100)</f>
         <v/>
       </c>
@@ -5138,7 +5326,7 @@
         <f>EDATE($B$4,36)</f>
         <v/>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="37">
         <f>(B25-$B$4)/365</f>
         <v/>
       </c>
@@ -5147,7 +5335,7 @@
         <v/>
       </c>
       <c r="E25" s="17">
-        <f>'SOFR_OIS_Quotes'!$G22</f>
+        <f>'SOFR_OIS_Quotes'!$H22</f>
         <v/>
       </c>
       <c r="F25" s="17">
@@ -5158,7 +5346,7 @@
         <f>SUM($I$8:I24)</f>
         <v/>
       </c>
-      <c r="H25" s="36">
+      <c r="H25" s="38">
         <f>(1-(E25/100)*G25)/(1+(E25/100)*F25)</f>
         <v/>
       </c>
@@ -5174,8 +5362,8 @@
         <f>(H24/H25-1)/((B25-B24)/360)*100</f>
         <v/>
       </c>
-      <c r="L25" s="33" t="n"/>
-      <c r="M25" s="37">
+      <c r="L25" s="35" t="n"/>
+      <c r="M25" s="39">
         <f>IF(L25="","",(J25-L25)*100)</f>
         <v/>
       </c>
@@ -5190,7 +5378,7 @@
         <f>EDATE($B$4,48)</f>
         <v/>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="33">
         <f>(B26-$B$4)/365</f>
         <v/>
       </c>
@@ -5199,7 +5387,7 @@
         <v/>
       </c>
       <c r="E26" s="21">
-        <f>'SOFR_OIS_Quotes'!$G23</f>
+        <f>'SOFR_OIS_Quotes'!$H23</f>
         <v/>
       </c>
       <c r="F26" s="21">
@@ -5210,7 +5398,7 @@
         <f>SUM($I$8:I25)</f>
         <v/>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="34">
         <f>(1-(E26/100)*G26)/(1+(E26/100)*F26)</f>
         <v/>
       </c>
@@ -5226,8 +5414,8 @@
         <f>(H25/H26-1)/((B26-B25)/360)*100</f>
         <v/>
       </c>
-      <c r="L26" s="33" t="n"/>
-      <c r="M26" s="34">
+      <c r="L26" s="35" t="n"/>
+      <c r="M26" s="36">
         <f>IF(L26="","",(J26-L26)*100)</f>
         <v/>
       </c>
@@ -5242,7 +5430,7 @@
         <f>EDATE($B$4,60)</f>
         <v/>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="37">
         <f>(B27-$B$4)/365</f>
         <v/>
       </c>
@@ -5251,7 +5439,7 @@
         <v/>
       </c>
       <c r="E27" s="17">
-        <f>'SOFR_OIS_Quotes'!$G24</f>
+        <f>'SOFR_OIS_Quotes'!$H24</f>
         <v/>
       </c>
       <c r="F27" s="17">
@@ -5262,7 +5450,7 @@
         <f>SUM($I$8:I26)</f>
         <v/>
       </c>
-      <c r="H27" s="36">
+      <c r="H27" s="38">
         <f>(1-(E27/100)*G27)/(1+(E27/100)*F27)</f>
         <v/>
       </c>
@@ -5278,8 +5466,8 @@
         <f>(H26/H27-1)/((B27-B26)/360)*100</f>
         <v/>
       </c>
-      <c r="L27" s="33" t="n"/>
-      <c r="M27" s="37">
+      <c r="L27" s="35" t="n"/>
+      <c r="M27" s="39">
         <f>IF(L27="","",(J27-L27)*100)</f>
         <v/>
       </c>
@@ -5294,7 +5482,7 @@
         <f>EDATE($B$4,72)</f>
         <v/>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="33">
         <f>(B28-$B$4)/365</f>
         <v/>
       </c>
@@ -5303,7 +5491,7 @@
         <v/>
       </c>
       <c r="E28" s="21">
-        <f>'SOFR_OIS_Quotes'!$G25</f>
+        <f>'SOFR_OIS_Quotes'!$H25</f>
         <v/>
       </c>
       <c r="F28" s="21">
@@ -5314,7 +5502,7 @@
         <f>SUM($I$8:I27)</f>
         <v/>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="34">
         <f>(1-(E28/100)*G28)/(1+(E28/100)*F28)</f>
         <v/>
       </c>
@@ -5330,8 +5518,8 @@
         <f>(H27/H28-1)/((B28-B27)/360)*100</f>
         <v/>
       </c>
-      <c r="L28" s="33" t="n"/>
-      <c r="M28" s="34">
+      <c r="L28" s="35" t="n"/>
+      <c r="M28" s="36">
         <f>IF(L28="","",(J28-L28)*100)</f>
         <v/>
       </c>
@@ -5346,7 +5534,7 @@
         <f>EDATE($B$4,84)</f>
         <v/>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="37">
         <f>(B29-$B$4)/365</f>
         <v/>
       </c>
@@ -5355,7 +5543,7 @@
         <v/>
       </c>
       <c r="E29" s="17">
-        <f>'SOFR_OIS_Quotes'!$G26</f>
+        <f>'SOFR_OIS_Quotes'!$H26</f>
         <v/>
       </c>
       <c r="F29" s="17">
@@ -5366,7 +5554,7 @@
         <f>SUM($I$8:I28)</f>
         <v/>
       </c>
-      <c r="H29" s="36">
+      <c r="H29" s="38">
         <f>(1-(E29/100)*G29)/(1+(E29/100)*F29)</f>
         <v/>
       </c>
@@ -5382,8 +5570,8 @@
         <f>(H28/H29-1)/((B29-B28)/360)*100</f>
         <v/>
       </c>
-      <c r="L29" s="33" t="n"/>
-      <c r="M29" s="37">
+      <c r="L29" s="35" t="n"/>
+      <c r="M29" s="39">
         <f>IF(L29="","",(J29-L29)*100)</f>
         <v/>
       </c>
@@ -5398,7 +5586,7 @@
         <f>EDATE($B$4,96)</f>
         <v/>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="33">
         <f>(B30-$B$4)/365</f>
         <v/>
       </c>
@@ -5407,7 +5595,7 @@
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>'SOFR_OIS_Quotes'!$G27</f>
+        <f>'SOFR_OIS_Quotes'!$H27</f>
         <v/>
       </c>
       <c r="F30" s="21">
@@ -5418,7 +5606,7 @@
         <f>SUM($I$8:I29)</f>
         <v/>
       </c>
-      <c r="H30" s="32">
+      <c r="H30" s="34">
         <f>(1-(E30/100)*G30)/(1+(E30/100)*F30)</f>
         <v/>
       </c>
@@ -5434,8 +5622,8 @@
         <f>(H29/H30-1)/((B30-B29)/360)*100</f>
         <v/>
       </c>
-      <c r="L30" s="33" t="n"/>
-      <c r="M30" s="34">
+      <c r="L30" s="35" t="n"/>
+      <c r="M30" s="36">
         <f>IF(L30="","",(J30-L30)*100)</f>
         <v/>
       </c>
@@ -5450,7 +5638,7 @@
         <f>EDATE($B$4,108)</f>
         <v/>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="37">
         <f>(B31-$B$4)/365</f>
         <v/>
       </c>
@@ -5459,7 +5647,7 @@
         <v/>
       </c>
       <c r="E31" s="17">
-        <f>'SOFR_OIS_Quotes'!$G28</f>
+        <f>'SOFR_OIS_Quotes'!$H28</f>
         <v/>
       </c>
       <c r="F31" s="17">
@@ -5470,7 +5658,7 @@
         <f>SUM($I$8:I30)</f>
         <v/>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="38">
         <f>(1-(E31/100)*G31)/(1+(E31/100)*F31)</f>
         <v/>
       </c>
@@ -5486,8 +5674,8 @@
         <f>(H30/H31-1)/((B31-B30)/360)*100</f>
         <v/>
       </c>
-      <c r="L31" s="33" t="n"/>
-      <c r="M31" s="37">
+      <c r="L31" s="35" t="n"/>
+      <c r="M31" s="39">
         <f>IF(L31="","",(J31-L31)*100)</f>
         <v/>
       </c>
@@ -5502,7 +5690,7 @@
         <f>EDATE($B$4,120)</f>
         <v/>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="33">
         <f>(B32-$B$4)/365</f>
         <v/>
       </c>
@@ -5511,7 +5699,7 @@
         <v/>
       </c>
       <c r="E32" s="21">
-        <f>'SOFR_OIS_Quotes'!$G29</f>
+        <f>'SOFR_OIS_Quotes'!$H29</f>
         <v/>
       </c>
       <c r="F32" s="21">
@@ -5522,7 +5710,7 @@
         <f>SUM($I$8:I31)</f>
         <v/>
       </c>
-      <c r="H32" s="32">
+      <c r="H32" s="34">
         <f>(1-(E32/100)*G32)/(1+(E32/100)*F32)</f>
         <v/>
       </c>
@@ -5538,8 +5726,8 @@
         <f>(H31/H32-1)/((B32-B31)/360)*100</f>
         <v/>
       </c>
-      <c r="L32" s="33" t="n"/>
-      <c r="M32" s="34">
+      <c r="L32" s="35" t="n"/>
+      <c r="M32" s="36">
         <f>IF(L32="","",(J32-L32)*100)</f>
         <v/>
       </c>
@@ -5554,7 +5742,7 @@
         <f>EDATE($B$4,144)</f>
         <v/>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="37">
         <f>(B33-$B$4)/365</f>
         <v/>
       </c>
@@ -5563,7 +5751,7 @@
         <v/>
       </c>
       <c r="E33" s="17">
-        <f>'SOFR_OIS_Quotes'!$G30</f>
+        <f>'SOFR_OIS_Quotes'!$H30</f>
         <v/>
       </c>
       <c r="F33" s="17">
@@ -5574,7 +5762,7 @@
         <f>SUM($I$8:I32)</f>
         <v/>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="38">
         <f>(1-(E33/100)*G33)/(1+(E33/100)*F33)</f>
         <v/>
       </c>
@@ -5590,8 +5778,8 @@
         <f>(H32/H33-1)/((B33-B32)/360)*100</f>
         <v/>
       </c>
-      <c r="L33" s="33" t="n"/>
-      <c r="M33" s="37">
+      <c r="L33" s="35" t="n"/>
+      <c r="M33" s="39">
         <f>IF(L33="","",(J33-L33)*100)</f>
         <v/>
       </c>
@@ -5606,7 +5794,7 @@
         <f>EDATE($B$4,180)</f>
         <v/>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="33">
         <f>(B34-$B$4)/365</f>
         <v/>
       </c>
@@ -5615,7 +5803,7 @@
         <v/>
       </c>
       <c r="E34" s="21">
-        <f>'SOFR_OIS_Quotes'!$G31</f>
+        <f>'SOFR_OIS_Quotes'!$H31</f>
         <v/>
       </c>
       <c r="F34" s="21">
@@ -5626,7 +5814,7 @@
         <f>SUM($I$8:I33)</f>
         <v/>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="34">
         <f>(1-(E34/100)*G34)/(1+(E34/100)*F34)</f>
         <v/>
       </c>
@@ -5642,8 +5830,8 @@
         <f>(H33/H34-1)/((B34-B33)/360)*100</f>
         <v/>
       </c>
-      <c r="L34" s="33" t="n"/>
-      <c r="M34" s="34">
+      <c r="L34" s="35" t="n"/>
+      <c r="M34" s="36">
         <f>IF(L34="","",(J34-L34)*100)</f>
         <v/>
       </c>
@@ -5658,7 +5846,7 @@
         <f>EDATE($B$4,240)</f>
         <v/>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="37">
         <f>(B35-$B$4)/365</f>
         <v/>
       </c>
@@ -5667,7 +5855,7 @@
         <v/>
       </c>
       <c r="E35" s="17">
-        <f>'SOFR_OIS_Quotes'!$G32</f>
+        <f>'SOFR_OIS_Quotes'!$H32</f>
         <v/>
       </c>
       <c r="F35" s="17">
@@ -5678,7 +5866,7 @@
         <f>SUM($I$8:I34)</f>
         <v/>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="38">
         <f>(1-(E35/100)*G35)/(1+(E35/100)*F35)</f>
         <v/>
       </c>
@@ -5694,8 +5882,8 @@
         <f>(H34/H35-1)/((B35-B34)/360)*100</f>
         <v/>
       </c>
-      <c r="L35" s="33" t="n"/>
-      <c r="M35" s="37">
+      <c r="L35" s="35" t="n"/>
+      <c r="M35" s="39">
         <f>IF(L35="","",(J35-L35)*100)</f>
         <v/>
       </c>
@@ -5710,7 +5898,7 @@
         <f>EDATE($B$4,300)</f>
         <v/>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="33">
         <f>(B36-$B$4)/365</f>
         <v/>
       </c>
@@ -5719,7 +5907,7 @@
         <v/>
       </c>
       <c r="E36" s="21">
-        <f>'SOFR_OIS_Quotes'!$G33</f>
+        <f>'SOFR_OIS_Quotes'!$H33</f>
         <v/>
       </c>
       <c r="F36" s="21">
@@ -5730,7 +5918,7 @@
         <f>SUM($I$8:I35)</f>
         <v/>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="34">
         <f>(1-(E36/100)*G36)/(1+(E36/100)*F36)</f>
         <v/>
       </c>
@@ -5746,8 +5934,8 @@
         <f>(H35/H36-1)/((B36-B35)/360)*100</f>
         <v/>
       </c>
-      <c r="L36" s="33" t="n"/>
-      <c r="M36" s="34">
+      <c r="L36" s="35" t="n"/>
+      <c r="M36" s="36">
         <f>IF(L36="","",(J36-L36)*100)</f>
         <v/>
       </c>
@@ -5762,7 +5950,7 @@
         <f>EDATE($B$4,360)</f>
         <v/>
       </c>
-      <c r="C37" s="35">
+      <c r="C37" s="37">
         <f>(B37-$B$4)/365</f>
         <v/>
       </c>
@@ -5771,7 +5959,7 @@
         <v/>
       </c>
       <c r="E37" s="17">
-        <f>'SOFR_OIS_Quotes'!$G34</f>
+        <f>'SOFR_OIS_Quotes'!$H34</f>
         <v/>
       </c>
       <c r="F37" s="17">
@@ -5782,7 +5970,7 @@
         <f>SUM($I$8:I36)</f>
         <v/>
       </c>
-      <c r="H37" s="36">
+      <c r="H37" s="38">
         <f>(1-(E37/100)*G37)/(1+(E37/100)*F37)</f>
         <v/>
       </c>
@@ -5798,8 +5986,8 @@
         <f>(H36/H37-1)/((B37-B36)/360)*100</f>
         <v/>
       </c>
-      <c r="L37" s="33" t="n"/>
-      <c r="M37" s="37">
+      <c r="L37" s="35" t="n"/>
+      <c r="M37" s="39">
         <f>IF(L37="","",(J37-L37)*100)</f>
         <v/>
       </c>
@@ -5814,7 +6002,7 @@
         <f>EDATE($B$4,480)</f>
         <v/>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="33">
         <f>(B38-$B$4)/365</f>
         <v/>
       </c>
@@ -5823,7 +6011,7 @@
         <v/>
       </c>
       <c r="E38" s="21">
-        <f>'SOFR_OIS_Quotes'!$G35</f>
+        <f>'SOFR_OIS_Quotes'!$H35</f>
         <v/>
       </c>
       <c r="F38" s="21">
@@ -5834,7 +6022,7 @@
         <f>SUM($I$8:I37)</f>
         <v/>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="34">
         <f>(1-(E38/100)*G38)/(1+(E38/100)*F38)</f>
         <v/>
       </c>
@@ -5850,8 +6038,8 @@
         <f>(H37/H38-1)/((B38-B37)/360)*100</f>
         <v/>
       </c>
-      <c r="L38" s="33" t="n"/>
-      <c r="M38" s="34">
+      <c r="L38" s="35" t="n"/>
+      <c r="M38" s="36">
         <f>IF(L38="","",(J38-L38)*100)</f>
         <v/>
       </c>
@@ -5866,7 +6054,7 @@
         <f>EDATE($B$4,600)</f>
         <v/>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="37">
         <f>(B39-$B$4)/365</f>
         <v/>
       </c>
@@ -5875,7 +6063,7 @@
         <v/>
       </c>
       <c r="E39" s="17">
-        <f>'SOFR_OIS_Quotes'!$G36</f>
+        <f>'SOFR_OIS_Quotes'!$H36</f>
         <v/>
       </c>
       <c r="F39" s="17">
@@ -5886,7 +6074,7 @@
         <f>SUM($I$8:I38)</f>
         <v/>
       </c>
-      <c r="H39" s="36">
+      <c r="H39" s="38">
         <f>(1-(E39/100)*G39)/(1+(E39/100)*F39)</f>
         <v/>
       </c>
@@ -5902,8 +6090,8 @@
         <f>(H38/H39-1)/((B39-B38)/360)*100</f>
         <v/>
       </c>
-      <c r="L39" s="33" t="n"/>
-      <c r="M39" s="37">
+      <c r="L39" s="35" t="n"/>
+      <c r="M39" s="39">
         <f>IF(L39="","",(J39-L39)*100)</f>
         <v/>
       </c>
@@ -5970,49 +6158,49 @@
           <t>DEAL — Fixed vs SOFR OIS   (yellow = inputs; everything else is computed)</t>
         </is>
       </c>
-      <c r="K4" s="38" t="inlineStr">
+      <c r="K4" s="40" t="inlineStr">
         <is>
           <t>Discount curve (from Bootstrap)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>Direction (Leg 1 = Fixed)</t>
         </is>
       </c>
-      <c r="B5" s="40" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>Receive fixed</t>
         </is>
       </c>
-      <c r="C5" s="41" t="inlineStr">
+      <c r="C5" s="43" t="inlineStr">
         <is>
           <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
         </is>
       </c>
-      <c r="K5" s="42" t="inlineStr">
+      <c r="K5" s="44" t="inlineStr">
         <is>
           <t>Curve date</t>
         </is>
       </c>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="L5" s="44" t="inlineStr">
         <is>
           <t>DF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="39" t="inlineStr">
+      <c r="A6" s="41" t="inlineStr">
         <is>
           <t>Notional</t>
         </is>
       </c>
-      <c r="B6" s="43" t="n">
+      <c r="B6" s="45" t="n">
         <v>10000000</v>
       </c>
-      <c r="C6" s="41" t="inlineStr">
+      <c r="C6" s="43" t="inlineStr">
         <is>
           <t>Both legs, USD.</t>
         </is>
@@ -6021,12 +6209,12 @@
         <f>Bootstrap!$B$4</f>
         <v/>
       </c>
-      <c r="L6" s="44" t="n">
+      <c r="L6" s="46" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -6040,22 +6228,22 @@
         <f>Bootstrap!B8</f>
         <v/>
       </c>
-      <c r="L7" s="44">
+      <c r="L7" s="46">
         <f>Bootstrap!H8</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="39" t="inlineStr">
+      <c r="A8" s="41" t="inlineStr">
         <is>
           <t>Effective date</t>
         </is>
       </c>
-      <c r="B8" s="45">
+      <c r="B8" s="47">
         <f>Bootstrap!$B$4</f>
         <v/>
       </c>
-      <c r="C8" s="41" t="inlineStr">
+      <c r="C8" s="43" t="inlineStr">
         <is>
           <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
         </is>
@@ -6064,21 +6252,21 @@
         <f>Bootstrap!B9</f>
         <v/>
       </c>
-      <c r="L8" s="44">
+      <c r="L8" s="46">
         <f>Bootstrap!H9</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="39" t="inlineStr">
+      <c r="A9" s="41" t="inlineStr">
         <is>
           <t>Tenor (years)</t>
         </is>
       </c>
-      <c r="B9" s="46" t="n">
+      <c r="B9" s="48" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="43" t="inlineStr">
         <is>
           <t>Whole years; drives the annual coupon schedule below.</t>
         </is>
@@ -6087,13 +6275,13 @@
         <f>Bootstrap!B10</f>
         <v/>
       </c>
-      <c r="L9" s="44">
+      <c r="L9" s="46">
         <f>Bootstrap!H10</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39" t="inlineStr">
+      <c r="A10" s="41" t="inlineStr">
         <is>
           <t>Maturity date</t>
         </is>
@@ -6102,7 +6290,7 @@
         <f>EDATE(B8,12*B9)</f>
         <v/>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="43">
         <f> Effective + Tenor.</f>
         <v/>
       </c>
@@ -6110,22 +6298,22 @@
         <f>Bootstrap!B11</f>
         <v/>
       </c>
-      <c r="L10" s="44">
+      <c r="L10" s="46">
         <f>Bootstrap!H11</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39" t="inlineStr">
+      <c r="A11" s="41" t="inlineStr">
         <is>
           <t>Fixed coupon (%)</t>
         </is>
       </c>
-      <c r="B11" s="47">
+      <c r="B11" s="49">
         <f>B25</f>
         <v/>
       </c>
-      <c r="C11" s="41" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
         </is>
@@ -6134,13 +6322,13 @@
         <f>Bootstrap!B12</f>
         <v/>
       </c>
-      <c r="L11" s="44">
+      <c r="L11" s="46">
         <f>Bootstrap!H12</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>Fixed pay frequency</t>
         </is>
@@ -6154,13 +6342,13 @@
         <f>Bootstrap!B13</f>
         <v/>
       </c>
-      <c r="L12" s="44">
+      <c r="L12" s="46">
         <f>Bootstrap!H13</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39" t="inlineStr">
+      <c r="A13" s="41" t="inlineStr">
         <is>
           <t>Fixed day count</t>
         </is>
@@ -6174,13 +6362,13 @@
         <f>Bootstrap!B14</f>
         <v/>
       </c>
-      <c r="L13" s="44">
+      <c r="L13" s="46">
         <f>Bootstrap!H14</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39" t="inlineStr">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Float index</t>
         </is>
@@ -6194,13 +6382,13 @@
         <f>Bootstrap!B15</f>
         <v/>
       </c>
-      <c r="L14" s="44">
+      <c r="L14" s="46">
         <f>Bootstrap!H15</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39" t="inlineStr">
+      <c r="A15" s="41" t="inlineStr">
         <is>
           <t>Curve / valuation date</t>
         </is>
@@ -6209,7 +6397,7 @@
         <f>VAL_DATE</f>
         <v/>
       </c>
-      <c r="C15" s="41" t="inlineStr">
+      <c r="C15" s="43" t="inlineStr">
         <is>
           <t>Curve is discounted from spot = Bootstrap!B4.</t>
         </is>
@@ -6218,18 +6406,18 @@
         <f>Bootstrap!B16</f>
         <v/>
       </c>
-      <c r="L15" s="44">
+      <c r="L15" s="46">
         <f>Bootstrap!H16</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+      <c r="A16" s="41" t="inlineStr">
         <is>
           <t>Direction sign (+recv / −pay)</t>
         </is>
       </c>
-      <c r="B16" s="48">
+      <c r="B16" s="50">
         <f>IF($B$5="Receive fixed",1,-1)</f>
         <v/>
       </c>
@@ -6237,7 +6425,7 @@
         <f>Bootstrap!B17</f>
         <v/>
       </c>
-      <c r="L16" s="44">
+      <c r="L16" s="46">
         <f>Bootstrap!H17</f>
         <v/>
       </c>
@@ -6247,7 +6435,7 @@
         <f>Bootstrap!B18</f>
         <v/>
       </c>
-      <c r="L17" s="44">
+      <c r="L17" s="46">
         <f>Bootstrap!H18</f>
         <v/>
       </c>
@@ -6262,22 +6450,22 @@
         <f>Bootstrap!B19</f>
         <v/>
       </c>
-      <c r="L18" s="44">
+      <c r="L18" s="46">
         <f>Bootstrap!H19</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39" t="inlineStr">
+      <c r="A19" s="41" t="inlineStr">
         <is>
           <t>DF(effective)</t>
         </is>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="46">
         <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))^(($B$8-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))</f>
         <v/>
       </c>
-      <c r="C19" s="41" t="inlineStr">
+      <c r="C19" s="43" t="inlineStr">
         <is>
           <t>Interpolated from the curve.</t>
         </is>
@@ -6286,18 +6474,18 @@
         <f>Bootstrap!B20</f>
         <v/>
       </c>
-      <c r="L19" s="44">
+      <c r="L19" s="46">
         <f>Bootstrap!H20</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
+      <c r="A20" s="41" t="inlineStr">
         <is>
           <t>DF(maturity)</t>
         </is>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="46">
         <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)))^(($B$10-INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)))</f>
         <v/>
       </c>
@@ -6305,22 +6493,22 @@
         <f>Bootstrap!B21</f>
         <v/>
       </c>
-      <c r="L20" s="44">
+      <c r="L20" s="46">
         <f>Bootstrap!H21</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39" t="inlineStr">
+      <c r="A21" s="41" t="inlineStr">
         <is>
           <t>Fixed annuity  Στ·DF</t>
         </is>
       </c>
-      <c r="B21" s="49">
+      <c r="B21" s="51">
         <f>SUM(H36:H85)</f>
         <v/>
       </c>
-      <c r="C21" s="41" t="inlineStr">
+      <c r="C21" s="43" t="inlineStr">
         <is>
           <t>Sum of τ·DF over the fixed coupon dates.</t>
         </is>
@@ -6329,18 +6517,18 @@
         <f>Bootstrap!B22</f>
         <v/>
       </c>
-      <c r="L21" s="44">
+      <c r="L21" s="46">
         <f>Bootstrap!H22</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39" t="inlineStr">
+      <c r="A22" s="41" t="inlineStr">
         <is>
           <t>Fixed leg PV (coupons)</t>
         </is>
       </c>
-      <c r="B22" s="50">
+      <c r="B22" s="52">
         <f>SUM(G36:G85)</f>
         <v/>
       </c>
@@ -6348,22 +6536,22 @@
         <f>Bootstrap!B23</f>
         <v/>
       </c>
-      <c r="L22" s="44">
+      <c r="L22" s="46">
         <f>Bootstrap!H23</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39" t="inlineStr">
+      <c r="A23" s="41" t="inlineStr">
         <is>
           <t>Float leg PV</t>
         </is>
       </c>
-      <c r="B23" s="50">
+      <c r="B23" s="52">
         <f>B6*(B19-B20)</f>
         <v/>
       </c>
-      <c r="C23" s="41" t="inlineStr">
+      <c r="C23" s="43" t="inlineStr">
         <is>
           <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
         </is>
@@ -6372,22 +6560,22 @@
         <f>Bootstrap!B24</f>
         <v/>
       </c>
-      <c r="L23" s="44">
+      <c r="L23" s="46">
         <f>Bootstrap!H24</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39" t="inlineStr">
+      <c r="A24" s="41" t="inlineStr">
         <is>
           <t>Notional PV @ maturity</t>
         </is>
       </c>
-      <c r="B24" s="50">
+      <c r="B24" s="52">
         <f>B6*B20</f>
         <v/>
       </c>
-      <c r="C24" s="41" t="inlineStr">
+      <c r="C24" s="43" t="inlineStr">
         <is>
           <t>For the SWPM-style leg display only.</t>
         </is>
@@ -6396,22 +6584,22 @@
         <f>Bootstrap!B25</f>
         <v/>
       </c>
-      <c r="L24" s="44">
+      <c r="L24" s="46">
         <f>Bootstrap!H25</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39" t="inlineStr">
+      <c r="A25" s="41" t="inlineStr">
         <is>
           <t>Par coupon (%)</t>
         </is>
       </c>
-      <c r="B25" s="49">
+      <c r="B25" s="51">
         <f>(B19-B20)/B21*100</f>
         <v/>
       </c>
-      <c r="C25" s="41" t="inlineStr">
+      <c r="C25" s="43" t="inlineStr">
         <is>
           <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
         </is>
@@ -6420,22 +6608,22 @@
         <f>Bootstrap!B26</f>
         <v/>
       </c>
-      <c r="L25" s="44">
+      <c r="L25" s="46">
         <f>Bootstrap!H26</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
+      <c r="A26" s="41" t="inlineStr">
         <is>
           <t>Leg 1 NPV  (fixed + notional)</t>
         </is>
       </c>
-      <c r="B26" s="50">
+      <c r="B26" s="52">
         <f>B16*(B22+B24)</f>
         <v/>
       </c>
-      <c r="C26" s="41" t="inlineStr">
+      <c r="C26" s="43" t="inlineStr">
         <is>
           <t>SWPM shows each leg incl. a notional redemption.</t>
         </is>
@@ -6444,18 +6632,18 @@
         <f>Bootstrap!B27</f>
         <v/>
       </c>
-      <c r="L26" s="44">
+      <c r="L26" s="46">
         <f>Bootstrap!H27</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39" t="inlineStr">
+      <c r="A27" s="41" t="inlineStr">
         <is>
           <t>Leg 2 NPV  (float + notional)</t>
         </is>
       </c>
-      <c r="B27" s="50">
+      <c r="B27" s="52">
         <f>-B16*(B23+B24)</f>
         <v/>
       </c>
@@ -6463,22 +6651,22 @@
         <f>Bootstrap!B28</f>
         <v/>
       </c>
-      <c r="L27" s="44">
+      <c r="L27" s="46">
         <f>Bootstrap!H28</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39" t="inlineStr">
+      <c r="A28" s="41" t="inlineStr">
         <is>
           <t>Net swap NPV</t>
         </is>
       </c>
-      <c r="B28" s="51">
+      <c r="B28" s="53">
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="43">
         <f> Fixed − Float (notionals cancel). ≈ 0 at par coupon.</f>
         <v/>
       </c>
@@ -6486,22 +6674,22 @@
         <f>Bootstrap!B29</f>
         <v/>
       </c>
-      <c r="L28" s="44">
+      <c r="L28" s="46">
         <f>Bootstrap!H29</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39" t="inlineStr">
+      <c r="A29" s="41" t="inlineStr">
         <is>
           <t>PV01 / DV01  (per 1bp)</t>
         </is>
       </c>
-      <c r="B29" s="50">
+      <c r="B29" s="52">
         <f>B6*B21*0.0001</f>
         <v/>
       </c>
-      <c r="C29" s="41" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>Annuity × notional × 1bp.</t>
         </is>
@@ -6510,25 +6698,25 @@
         <f>Bootstrap!B30</f>
         <v/>
       </c>
-      <c r="L29" s="44">
+      <c r="L29" s="46">
         <f>Bootstrap!H30</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39" t="inlineStr">
+      <c r="A30" s="41" t="inlineStr">
         <is>
           <t>Accrued (at inception)</t>
         </is>
       </c>
-      <c r="B30" s="50" t="n">
+      <c r="B30" s="52" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="18">
         <f>Bootstrap!B31</f>
         <v/>
       </c>
-      <c r="L30" s="44">
+      <c r="L30" s="46">
         <f>Bootstrap!H31</f>
         <v/>
       </c>
@@ -6538,7 +6726,7 @@
         <f>Bootstrap!B32</f>
         <v/>
       </c>
-      <c r="L31" s="44">
+      <c r="L31" s="46">
         <f>Bootstrap!H32</f>
         <v/>
       </c>
@@ -6553,7 +6741,7 @@
         <f>Bootstrap!B33</f>
         <v/>
       </c>
-      <c r="L32" s="44">
+      <c r="L32" s="46">
         <f>Bootstrap!H33</f>
         <v/>
       </c>
@@ -6563,7 +6751,7 @@
         <f>Bootstrap!B34</f>
         <v/>
       </c>
-      <c r="L33" s="44">
+      <c r="L33" s="46">
         <f>Bootstrap!H34</f>
         <v/>
       </c>
@@ -6573,7 +6761,7 @@
         <f>Bootstrap!B35</f>
         <v/>
       </c>
-      <c r="L34" s="44">
+      <c r="L34" s="46">
         <f>Bootstrap!H35</f>
         <v/>
       </c>
@@ -6623,13 +6811,13 @@
         <f>Bootstrap!B36</f>
         <v/>
       </c>
-      <c r="L35" s="44">
+      <c r="L35" s="46">
         <f>Bootstrap!H36</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="48">
+      <c r="A36" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6645,19 +6833,19 @@
         <f>IF(A36&lt;=$B$9,(B36-C36)/360,"")</f>
         <v/>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="46">
         <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)))^((B36-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F36" s="50">
+      <c r="F36" s="52">
         <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
         <v/>
       </c>
-      <c r="G36" s="50">
+      <c r="G36" s="52">
         <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
         <v/>
       </c>
-      <c r="H36" s="49">
+      <c r="H36" s="51">
         <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
         <v/>
       </c>
@@ -6665,13 +6853,13 @@
         <f>Bootstrap!B37</f>
         <v/>
       </c>
-      <c r="L36" s="44">
+      <c r="L36" s="46">
         <f>Bootstrap!H37</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="52">
+      <c r="A37" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6687,19 +6875,19 @@
         <f>IF(A37&lt;=$B$9,(B37-C37)/360,"")</f>
         <v/>
       </c>
-      <c r="E37" s="53">
+      <c r="E37" s="55">
         <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)))^((B37-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F37" s="54">
+      <c r="F37" s="56">
         <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
         <v/>
       </c>
-      <c r="G37" s="54">
+      <c r="G37" s="56">
         <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
         <v/>
       </c>
-      <c r="H37" s="55">
+      <c r="H37" s="57">
         <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
         <v/>
       </c>
@@ -6707,13 +6895,13 @@
         <f>Bootstrap!B38</f>
         <v/>
       </c>
-      <c r="L37" s="44">
+      <c r="L37" s="46">
         <f>Bootstrap!H38</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="48">
+      <c r="A38" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6729,19 +6917,19 @@
         <f>IF(A38&lt;=$B$9,(B38-C38)/360,"")</f>
         <v/>
       </c>
-      <c r="E38" s="44">
+      <c r="E38" s="46">
         <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)))^((B38-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="50">
+      <c r="F38" s="52">
         <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
         <v/>
       </c>
-      <c r="G38" s="50">
+      <c r="G38" s="52">
         <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
         <v/>
       </c>
-      <c r="H38" s="49">
+      <c r="H38" s="51">
         <f>IF(A38&lt;=$B$9,D38*E38,"")</f>
         <v/>
       </c>
@@ -6749,13 +6937,13 @@
         <f>Bootstrap!B39</f>
         <v/>
       </c>
-      <c r="L38" s="44">
+      <c r="L38" s="46">
         <f>Bootstrap!H39</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="52">
+      <c r="A39" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6771,19 +6959,19 @@
         <f>IF(A39&lt;=$B$9,(B39-C39)/360,"")</f>
         <v/>
       </c>
-      <c r="E39" s="53">
+      <c r="E39" s="55">
         <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)))^((B39-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="56">
         <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
         <v/>
       </c>
-      <c r="G39" s="54">
+      <c r="G39" s="56">
         <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
         <v/>
       </c>
-      <c r="H39" s="55">
+      <c r="H39" s="57">
         <f>IF(A39&lt;=$B$9,D39*E39,"")</f>
         <v/>
       </c>
@@ -6794,7 +6982,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="48">
+      <c r="A40" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6810,25 +6998,25 @@
         <f>IF(A40&lt;=$B$9,(B40-C40)/360,"")</f>
         <v/>
       </c>
-      <c r="E40" s="44">
+      <c r="E40" s="46">
         <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)))^((B40-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F40" s="50">
+      <c r="F40" s="52">
         <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
         <v/>
       </c>
-      <c r="G40" s="50">
+      <c r="G40" s="52">
         <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
         <v/>
       </c>
-      <c r="H40" s="49">
+      <c r="H40" s="51">
         <f>IF(A40&lt;=$B$9,D40*E40,"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="52">
+      <c r="A41" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6844,25 +7032,25 @@
         <f>IF(A41&lt;=$B$9,(B41-C41)/360,"")</f>
         <v/>
       </c>
-      <c r="E41" s="53">
+      <c r="E41" s="55">
         <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)))^((B41-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="54">
+      <c r="F41" s="56">
         <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
         <v/>
       </c>
-      <c r="G41" s="54">
+      <c r="G41" s="56">
         <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
         <v/>
       </c>
-      <c r="H41" s="55">
+      <c r="H41" s="57">
         <f>IF(A41&lt;=$B$9,D41*E41,"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="48">
+      <c r="A42" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6878,25 +7066,25 @@
         <f>IF(A42&lt;=$B$9,(B42-C42)/360,"")</f>
         <v/>
       </c>
-      <c r="E42" s="44">
+      <c r="E42" s="46">
         <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)))^((B42-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F42" s="50">
+      <c r="F42" s="52">
         <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
         <v/>
       </c>
-      <c r="G42" s="50">
+      <c r="G42" s="52">
         <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
         <v/>
       </c>
-      <c r="H42" s="49">
+      <c r="H42" s="51">
         <f>IF(A42&lt;=$B$9,D42*E42,"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="52">
+      <c r="A43" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6912,25 +7100,25 @@
         <f>IF(A43&lt;=$B$9,(B43-C43)/360,"")</f>
         <v/>
       </c>
-      <c r="E43" s="53">
+      <c r="E43" s="55">
         <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)))^((B43-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="56">
         <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
         <v/>
       </c>
-      <c r="G43" s="54">
+      <c r="G43" s="56">
         <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
         <v/>
       </c>
-      <c r="H43" s="55">
+      <c r="H43" s="57">
         <f>IF(A43&lt;=$B$9,D43*E43,"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="48">
+      <c r="A44" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6946,25 +7134,25 @@
         <f>IF(A44&lt;=$B$9,(B44-C44)/360,"")</f>
         <v/>
       </c>
-      <c r="E44" s="44">
+      <c r="E44" s="46">
         <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)))^((B44-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F44" s="50">
+      <c r="F44" s="52">
         <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
         <v/>
       </c>
-      <c r="G44" s="50">
+      <c r="G44" s="52">
         <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
         <v/>
       </c>
-      <c r="H44" s="49">
+      <c r="H44" s="51">
         <f>IF(A44&lt;=$B$9,D44*E44,"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="52">
+      <c r="A45" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6980,25 +7168,25 @@
         <f>IF(A45&lt;=$B$9,(B45-C45)/360,"")</f>
         <v/>
       </c>
-      <c r="E45" s="53">
+      <c r="E45" s="55">
         <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)))^((B45-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="56">
         <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
         <v/>
       </c>
-      <c r="G45" s="54">
+      <c r="G45" s="56">
         <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
         <v/>
       </c>
-      <c r="H45" s="55">
+      <c r="H45" s="57">
         <f>IF(A45&lt;=$B$9,D45*E45,"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="48">
+      <c r="A46" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7014,25 +7202,25 @@
         <f>IF(A46&lt;=$B$9,(B46-C46)/360,"")</f>
         <v/>
       </c>
-      <c r="E46" s="44">
+      <c r="E46" s="46">
         <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)))^((B46-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F46" s="50">
+      <c r="F46" s="52">
         <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
         <v/>
       </c>
-      <c r="G46" s="50">
+      <c r="G46" s="52">
         <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
         <v/>
       </c>
-      <c r="H46" s="49">
+      <c r="H46" s="51">
         <f>IF(A46&lt;=$B$9,D46*E46,"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="52">
+      <c r="A47" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7048,25 +7236,25 @@
         <f>IF(A47&lt;=$B$9,(B47-C47)/360,"")</f>
         <v/>
       </c>
-      <c r="E47" s="53">
+      <c r="E47" s="55">
         <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)))^((B47-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F47" s="54">
+      <c r="F47" s="56">
         <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
         <v/>
       </c>
-      <c r="G47" s="54">
+      <c r="G47" s="56">
         <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
         <v/>
       </c>
-      <c r="H47" s="55">
+      <c r="H47" s="57">
         <f>IF(A47&lt;=$B$9,D47*E47,"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="48">
+      <c r="A48" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7082,25 +7270,25 @@
         <f>IF(A48&lt;=$B$9,(B48-C48)/360,"")</f>
         <v/>
       </c>
-      <c r="E48" s="44">
+      <c r="E48" s="46">
         <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)))^((B48-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F48" s="50">
+      <c r="F48" s="52">
         <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
         <v/>
       </c>
-      <c r="G48" s="50">
+      <c r="G48" s="52">
         <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
         <v/>
       </c>
-      <c r="H48" s="49">
+      <c r="H48" s="51">
         <f>IF(A48&lt;=$B$9,D48*E48,"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="52">
+      <c r="A49" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7116,25 +7304,25 @@
         <f>IF(A49&lt;=$B$9,(B49-C49)/360,"")</f>
         <v/>
       </c>
-      <c r="E49" s="53">
+      <c r="E49" s="55">
         <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)))^((B49-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="54">
+      <c r="F49" s="56">
         <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
         <v/>
       </c>
-      <c r="G49" s="54">
+      <c r="G49" s="56">
         <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
         <v/>
       </c>
-      <c r="H49" s="55">
+      <c r="H49" s="57">
         <f>IF(A49&lt;=$B$9,D49*E49,"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="48">
+      <c r="A50" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7150,25 +7338,25 @@
         <f>IF(A50&lt;=$B$9,(B50-C50)/360,"")</f>
         <v/>
       </c>
-      <c r="E50" s="44">
+      <c r="E50" s="46">
         <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)))^((B50-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F50" s="50">
+      <c r="F50" s="52">
         <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
         <v/>
       </c>
-      <c r="G50" s="50">
+      <c r="G50" s="52">
         <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
         <v/>
       </c>
-      <c r="H50" s="49">
+      <c r="H50" s="51">
         <f>IF(A50&lt;=$B$9,D50*E50,"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="52">
+      <c r="A51" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7184,25 +7372,25 @@
         <f>IF(A51&lt;=$B$9,(B51-C51)/360,"")</f>
         <v/>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="55">
         <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)))^((B51-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F51" s="54">
+      <c r="F51" s="56">
         <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
         <v/>
       </c>
-      <c r="G51" s="54">
+      <c r="G51" s="56">
         <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
         <v/>
       </c>
-      <c r="H51" s="55">
+      <c r="H51" s="57">
         <f>IF(A51&lt;=$B$9,D51*E51,"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="48">
+      <c r="A52" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7218,25 +7406,25 @@
         <f>IF(A52&lt;=$B$9,(B52-C52)/360,"")</f>
         <v/>
       </c>
-      <c r="E52" s="44">
+      <c r="E52" s="46">
         <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)))^((B52-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F52" s="50">
+      <c r="F52" s="52">
         <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
         <v/>
       </c>
-      <c r="G52" s="50">
+      <c r="G52" s="52">
         <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
         <v/>
       </c>
-      <c r="H52" s="49">
+      <c r="H52" s="51">
         <f>IF(A52&lt;=$B$9,D52*E52,"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="52">
+      <c r="A53" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7252,25 +7440,25 @@
         <f>IF(A53&lt;=$B$9,(B53-C53)/360,"")</f>
         <v/>
       </c>
-      <c r="E53" s="53">
+      <c r="E53" s="55">
         <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)))^((B53-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F53" s="54">
+      <c r="F53" s="56">
         <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
         <v/>
       </c>
-      <c r="G53" s="54">
+      <c r="G53" s="56">
         <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
         <v/>
       </c>
-      <c r="H53" s="55">
+      <c r="H53" s="57">
         <f>IF(A53&lt;=$B$9,D53*E53,"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="48">
+      <c r="A54" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7286,25 +7474,25 @@
         <f>IF(A54&lt;=$B$9,(B54-C54)/360,"")</f>
         <v/>
       </c>
-      <c r="E54" s="44">
+      <c r="E54" s="46">
         <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)))^((B54-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F54" s="50">
+      <c r="F54" s="52">
         <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
         <v/>
       </c>
-      <c r="G54" s="50">
+      <c r="G54" s="52">
         <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
         <v/>
       </c>
-      <c r="H54" s="49">
+      <c r="H54" s="51">
         <f>IF(A54&lt;=$B$9,D54*E54,"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="52">
+      <c r="A55" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7320,25 +7508,25 @@
         <f>IF(A55&lt;=$B$9,(B55-C55)/360,"")</f>
         <v/>
       </c>
-      <c r="E55" s="53">
+      <c r="E55" s="55">
         <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)))^((B55-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F55" s="54">
+      <c r="F55" s="56">
         <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
         <v/>
       </c>
-      <c r="G55" s="54">
+      <c r="G55" s="56">
         <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
         <v/>
       </c>
-      <c r="H55" s="55">
+      <c r="H55" s="57">
         <f>IF(A55&lt;=$B$9,D55*E55,"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="48">
+      <c r="A56" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7354,25 +7542,25 @@
         <f>IF(A56&lt;=$B$9,(B56-C56)/360,"")</f>
         <v/>
       </c>
-      <c r="E56" s="44">
+      <c r="E56" s="46">
         <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)))^((B56-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F56" s="50">
+      <c r="F56" s="52">
         <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
         <v/>
       </c>
-      <c r="G56" s="50">
+      <c r="G56" s="52">
         <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
         <v/>
       </c>
-      <c r="H56" s="49">
+      <c r="H56" s="51">
         <f>IF(A56&lt;=$B$9,D56*E56,"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="52">
+      <c r="A57" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7388,25 +7576,25 @@
         <f>IF(A57&lt;=$B$9,(B57-C57)/360,"")</f>
         <v/>
       </c>
-      <c r="E57" s="53">
+      <c r="E57" s="55">
         <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)))^((B57-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F57" s="54">
+      <c r="F57" s="56">
         <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
         <v/>
       </c>
-      <c r="G57" s="54">
+      <c r="G57" s="56">
         <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
         <v/>
       </c>
-      <c r="H57" s="55">
+      <c r="H57" s="57">
         <f>IF(A57&lt;=$B$9,D57*E57,"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="48">
+      <c r="A58" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7422,25 +7610,25 @@
         <f>IF(A58&lt;=$B$9,(B58-C58)/360,"")</f>
         <v/>
       </c>
-      <c r="E58" s="44">
+      <c r="E58" s="46">
         <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)))^((B58-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F58" s="50">
+      <c r="F58" s="52">
         <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
         <v/>
       </c>
-      <c r="G58" s="50">
+      <c r="G58" s="52">
         <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
         <v/>
       </c>
-      <c r="H58" s="49">
+      <c r="H58" s="51">
         <f>IF(A58&lt;=$B$9,D58*E58,"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="52">
+      <c r="A59" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7456,25 +7644,25 @@
         <f>IF(A59&lt;=$B$9,(B59-C59)/360,"")</f>
         <v/>
       </c>
-      <c r="E59" s="53">
+      <c r="E59" s="55">
         <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)))^((B59-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F59" s="54">
+      <c r="F59" s="56">
         <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
         <v/>
       </c>
-      <c r="G59" s="54">
+      <c r="G59" s="56">
         <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
         <v/>
       </c>
-      <c r="H59" s="55">
+      <c r="H59" s="57">
         <f>IF(A59&lt;=$B$9,D59*E59,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="48">
+      <c r="A60" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7490,25 +7678,25 @@
         <f>IF(A60&lt;=$B$9,(B60-C60)/360,"")</f>
         <v/>
       </c>
-      <c r="E60" s="44">
+      <c r="E60" s="46">
         <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)))^((B60-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="52">
         <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="52">
         <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="51">
         <f>IF(A60&lt;=$B$9,D60*E60,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="52">
+      <c r="A61" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7524,25 +7712,25 @@
         <f>IF(A61&lt;=$B$9,(B61-C61)/360,"")</f>
         <v/>
       </c>
-      <c r="E61" s="53">
+      <c r="E61" s="55">
         <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)))^((B61-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F61" s="54">
+      <c r="F61" s="56">
         <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
         <v/>
       </c>
-      <c r="G61" s="54">
+      <c r="G61" s="56">
         <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
         <v/>
       </c>
-      <c r="H61" s="55">
+      <c r="H61" s="57">
         <f>IF(A61&lt;=$B$9,D61*E61,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="48">
+      <c r="A62" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7558,25 +7746,25 @@
         <f>IF(A62&lt;=$B$9,(B62-C62)/360,"")</f>
         <v/>
       </c>
-      <c r="E62" s="44">
+      <c r="E62" s="46">
         <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)))^((B62-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="52">
         <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="52">
         <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="51">
         <f>IF(A62&lt;=$B$9,D62*E62,"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="52">
+      <c r="A63" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7592,25 +7780,25 @@
         <f>IF(A63&lt;=$B$9,(B63-C63)/360,"")</f>
         <v/>
       </c>
-      <c r="E63" s="53">
+      <c r="E63" s="55">
         <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)))^((B63-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F63" s="54">
+      <c r="F63" s="56">
         <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
         <v/>
       </c>
-      <c r="G63" s="54">
+      <c r="G63" s="56">
         <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
         <v/>
       </c>
-      <c r="H63" s="55">
+      <c r="H63" s="57">
         <f>IF(A63&lt;=$B$9,D63*E63,"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="48">
+      <c r="A64" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7626,25 +7814,25 @@
         <f>IF(A64&lt;=$B$9,(B64-C64)/360,"")</f>
         <v/>
       </c>
-      <c r="E64" s="44">
+      <c r="E64" s="46">
         <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)))^((B64-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F64" s="50">
+      <c r="F64" s="52">
         <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
         <v/>
       </c>
-      <c r="G64" s="50">
+      <c r="G64" s="52">
         <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
         <v/>
       </c>
-      <c r="H64" s="49">
+      <c r="H64" s="51">
         <f>IF(A64&lt;=$B$9,D64*E64,"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="52">
+      <c r="A65" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7660,25 +7848,25 @@
         <f>IF(A65&lt;=$B$9,(B65-C65)/360,"")</f>
         <v/>
       </c>
-      <c r="E65" s="53">
+      <c r="E65" s="55">
         <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)))^((B65-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F65" s="54">
+      <c r="F65" s="56">
         <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
         <v/>
       </c>
-      <c r="G65" s="54">
+      <c r="G65" s="56">
         <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
         <v/>
       </c>
-      <c r="H65" s="55">
+      <c r="H65" s="57">
         <f>IF(A65&lt;=$B$9,D65*E65,"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="48">
+      <c r="A66" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7694,25 +7882,25 @@
         <f>IF(A66&lt;=$B$9,(B66-C66)/360,"")</f>
         <v/>
       </c>
-      <c r="E66" s="44">
+      <c r="E66" s="46">
         <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)))^((B66-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F66" s="50">
+      <c r="F66" s="52">
         <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
         <v/>
       </c>
-      <c r="G66" s="50">
+      <c r="G66" s="52">
         <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
         <v/>
       </c>
-      <c r="H66" s="49">
+      <c r="H66" s="51">
         <f>IF(A66&lt;=$B$9,D66*E66,"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="52">
+      <c r="A67" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7728,25 +7916,25 @@
         <f>IF(A67&lt;=$B$9,(B67-C67)/360,"")</f>
         <v/>
       </c>
-      <c r="E67" s="53">
+      <c r="E67" s="55">
         <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)))^((B67-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F67" s="54">
+      <c r="F67" s="56">
         <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
         <v/>
       </c>
-      <c r="G67" s="54">
+      <c r="G67" s="56">
         <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
         <v/>
       </c>
-      <c r="H67" s="55">
+      <c r="H67" s="57">
         <f>IF(A67&lt;=$B$9,D67*E67,"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="48">
+      <c r="A68" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7762,25 +7950,25 @@
         <f>IF(A68&lt;=$B$9,(B68-C68)/360,"")</f>
         <v/>
       </c>
-      <c r="E68" s="44">
+      <c r="E68" s="46">
         <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)))^((B68-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F68" s="50">
+      <c r="F68" s="52">
         <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
         <v/>
       </c>
-      <c r="G68" s="50">
+      <c r="G68" s="52">
         <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
         <v/>
       </c>
-      <c r="H68" s="49">
+      <c r="H68" s="51">
         <f>IF(A68&lt;=$B$9,D68*E68,"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="52">
+      <c r="A69" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7796,25 +7984,25 @@
         <f>IF(A69&lt;=$B$9,(B69-C69)/360,"")</f>
         <v/>
       </c>
-      <c r="E69" s="53">
+      <c r="E69" s="55">
         <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)))^((B69-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F69" s="54">
+      <c r="F69" s="56">
         <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
         <v/>
       </c>
-      <c r="G69" s="54">
+      <c r="G69" s="56">
         <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
         <v/>
       </c>
-      <c r="H69" s="55">
+      <c r="H69" s="57">
         <f>IF(A69&lt;=$B$9,D69*E69,"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="48">
+      <c r="A70" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7830,25 +8018,25 @@
         <f>IF(A70&lt;=$B$9,(B70-C70)/360,"")</f>
         <v/>
       </c>
-      <c r="E70" s="44">
+      <c r="E70" s="46">
         <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)))^((B70-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F70" s="50">
+      <c r="F70" s="52">
         <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
         <v/>
       </c>
-      <c r="G70" s="50">
+      <c r="G70" s="52">
         <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
         <v/>
       </c>
-      <c r="H70" s="49">
+      <c r="H70" s="51">
         <f>IF(A70&lt;=$B$9,D70*E70,"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="52">
+      <c r="A71" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7864,25 +8052,25 @@
         <f>IF(A71&lt;=$B$9,(B71-C71)/360,"")</f>
         <v/>
       </c>
-      <c r="E71" s="53">
+      <c r="E71" s="55">
         <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)))^((B71-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F71" s="54">
+      <c r="F71" s="56">
         <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
         <v/>
       </c>
-      <c r="G71" s="54">
+      <c r="G71" s="56">
         <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
         <v/>
       </c>
-      <c r="H71" s="55">
+      <c r="H71" s="57">
         <f>IF(A71&lt;=$B$9,D71*E71,"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="48">
+      <c r="A72" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7898,25 +8086,25 @@
         <f>IF(A72&lt;=$B$9,(B72-C72)/360,"")</f>
         <v/>
       </c>
-      <c r="E72" s="44">
+      <c r="E72" s="46">
         <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)))^((B72-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F72" s="50">
+      <c r="F72" s="52">
         <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
         <v/>
       </c>
-      <c r="G72" s="50">
+      <c r="G72" s="52">
         <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
         <v/>
       </c>
-      <c r="H72" s="49">
+      <c r="H72" s="51">
         <f>IF(A72&lt;=$B$9,D72*E72,"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="52">
+      <c r="A73" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7932,25 +8120,25 @@
         <f>IF(A73&lt;=$B$9,(B73-C73)/360,"")</f>
         <v/>
       </c>
-      <c r="E73" s="53">
+      <c r="E73" s="55">
         <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)))^((B73-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F73" s="54">
+      <c r="F73" s="56">
         <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
         <v/>
       </c>
-      <c r="G73" s="54">
+      <c r="G73" s="56">
         <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
         <v/>
       </c>
-      <c r="H73" s="55">
+      <c r="H73" s="57">
         <f>IF(A73&lt;=$B$9,D73*E73,"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="48">
+      <c r="A74" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7966,25 +8154,25 @@
         <f>IF(A74&lt;=$B$9,(B74-C74)/360,"")</f>
         <v/>
       </c>
-      <c r="E74" s="44">
+      <c r="E74" s="46">
         <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)))^((B74-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F74" s="50">
+      <c r="F74" s="52">
         <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
         <v/>
       </c>
-      <c r="G74" s="50">
+      <c r="G74" s="52">
         <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
         <v/>
       </c>
-      <c r="H74" s="49">
+      <c r="H74" s="51">
         <f>IF(A74&lt;=$B$9,D74*E74,"")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="52">
+      <c r="A75" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8000,25 +8188,25 @@
         <f>IF(A75&lt;=$B$9,(B75-C75)/360,"")</f>
         <v/>
       </c>
-      <c r="E75" s="53">
+      <c r="E75" s="55">
         <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)))^((B75-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F75" s="54">
+      <c r="F75" s="56">
         <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
         <v/>
       </c>
-      <c r="G75" s="54">
+      <c r="G75" s="56">
         <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
         <v/>
       </c>
-      <c r="H75" s="55">
+      <c r="H75" s="57">
         <f>IF(A75&lt;=$B$9,D75*E75,"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="48">
+      <c r="A76" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8034,25 +8222,25 @@
         <f>IF(A76&lt;=$B$9,(B76-C76)/360,"")</f>
         <v/>
       </c>
-      <c r="E76" s="44">
+      <c r="E76" s="46">
         <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)))^((B76-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F76" s="50">
+      <c r="F76" s="52">
         <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
         <v/>
       </c>
-      <c r="G76" s="50">
+      <c r="G76" s="52">
         <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
         <v/>
       </c>
-      <c r="H76" s="49">
+      <c r="H76" s="51">
         <f>IF(A76&lt;=$B$9,D76*E76,"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="52">
+      <c r="A77" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8068,25 +8256,25 @@
         <f>IF(A77&lt;=$B$9,(B77-C77)/360,"")</f>
         <v/>
       </c>
-      <c r="E77" s="53">
+      <c r="E77" s="55">
         <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)))^((B77-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F77" s="54">
+      <c r="F77" s="56">
         <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
         <v/>
       </c>
-      <c r="G77" s="54">
+      <c r="G77" s="56">
         <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
         <v/>
       </c>
-      <c r="H77" s="55">
+      <c r="H77" s="57">
         <f>IF(A77&lt;=$B$9,D77*E77,"")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="48">
+      <c r="A78" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8102,25 +8290,25 @@
         <f>IF(A78&lt;=$B$9,(B78-C78)/360,"")</f>
         <v/>
       </c>
-      <c r="E78" s="44">
+      <c r="E78" s="46">
         <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)))^((B78-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F78" s="50">
+      <c r="F78" s="52">
         <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
         <v/>
       </c>
-      <c r="G78" s="50">
+      <c r="G78" s="52">
         <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
         <v/>
       </c>
-      <c r="H78" s="49">
+      <c r="H78" s="51">
         <f>IF(A78&lt;=$B$9,D78*E78,"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="52">
+      <c r="A79" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8136,25 +8324,25 @@
         <f>IF(A79&lt;=$B$9,(B79-C79)/360,"")</f>
         <v/>
       </c>
-      <c r="E79" s="53">
+      <c r="E79" s="55">
         <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)))^((B79-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F79" s="54">
+      <c r="F79" s="56">
         <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
         <v/>
       </c>
-      <c r="G79" s="54">
+      <c r="G79" s="56">
         <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
         <v/>
       </c>
-      <c r="H79" s="55">
+      <c r="H79" s="57">
         <f>IF(A79&lt;=$B$9,D79*E79,"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="48">
+      <c r="A80" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8170,25 +8358,25 @@
         <f>IF(A80&lt;=$B$9,(B80-C80)/360,"")</f>
         <v/>
       </c>
-      <c r="E80" s="44">
+      <c r="E80" s="46">
         <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)))^((B80-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F80" s="50">
+      <c r="F80" s="52">
         <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
         <v/>
       </c>
-      <c r="G80" s="50">
+      <c r="G80" s="52">
         <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
         <v/>
       </c>
-      <c r="H80" s="49">
+      <c r="H80" s="51">
         <f>IF(A80&lt;=$B$9,D80*E80,"")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="52">
+      <c r="A81" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8204,25 +8392,25 @@
         <f>IF(A81&lt;=$B$9,(B81-C81)/360,"")</f>
         <v/>
       </c>
-      <c r="E81" s="53">
+      <c r="E81" s="55">
         <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)))^((B81-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F81" s="54">
+      <c r="F81" s="56">
         <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
         <v/>
       </c>
-      <c r="G81" s="54">
+      <c r="G81" s="56">
         <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
         <v/>
       </c>
-      <c r="H81" s="55">
+      <c r="H81" s="57">
         <f>IF(A81&lt;=$B$9,D81*E81,"")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="48">
+      <c r="A82" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8238,25 +8426,25 @@
         <f>IF(A82&lt;=$B$9,(B82-C82)/360,"")</f>
         <v/>
       </c>
-      <c r="E82" s="44">
+      <c r="E82" s="46">
         <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)))^((B82-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F82" s="50">
+      <c r="F82" s="52">
         <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
         <v/>
       </c>
-      <c r="G82" s="50">
+      <c r="G82" s="52">
         <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
         <v/>
       </c>
-      <c r="H82" s="49">
+      <c r="H82" s="51">
         <f>IF(A82&lt;=$B$9,D82*E82,"")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="52">
+      <c r="A83" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8272,25 +8460,25 @@
         <f>IF(A83&lt;=$B$9,(B83-C83)/360,"")</f>
         <v/>
       </c>
-      <c r="E83" s="53">
+      <c r="E83" s="55">
         <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)))^((B83-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F83" s="54">
+      <c r="F83" s="56">
         <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
         <v/>
       </c>
-      <c r="G83" s="54">
+      <c r="G83" s="56">
         <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
         <v/>
       </c>
-      <c r="H83" s="55">
+      <c r="H83" s="57">
         <f>IF(A83&lt;=$B$9,D83*E83,"")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="48">
+      <c r="A84" s="50">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8306,25 +8494,25 @@
         <f>IF(A84&lt;=$B$9,(B84-C84)/360,"")</f>
         <v/>
       </c>
-      <c r="E84" s="44">
+      <c r="E84" s="46">
         <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)))^((B84-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F84" s="50">
+      <c r="F84" s="52">
         <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
         <v/>
       </c>
-      <c r="G84" s="50">
+      <c r="G84" s="52">
         <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
         <v/>
       </c>
-      <c r="H84" s="49">
+      <c r="H84" s="51">
         <f>IF(A84&lt;=$B$9,D84*E84,"")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="52">
+      <c r="A85" s="54">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8340,19 +8528,19 @@
         <f>IF(A85&lt;=$B$9,(B85-C85)/360,"")</f>
         <v/>
       </c>
-      <c r="E85" s="53">
+      <c r="E85" s="55">
         <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)))^((B85-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F85" s="54">
+      <c r="F85" s="56">
         <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
         <v/>
       </c>
-      <c r="G85" s="54">
+      <c r="G85" s="56">
         <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
         <v/>
       </c>
-      <c r="H85" s="55">
+      <c r="H85" s="57">
         <f>IF(A85&lt;=$B$9,D85*E85,"")</f>
         <v/>
       </c>
@@ -8435,7 +8623,7 @@
           <t>Curve date</t>
         </is>
       </c>
-      <c r="B5" s="56">
+      <c r="B5" s="58">
         <f>VAL_DATE</f>
         <v/>
       </c>
@@ -8903,24 +9091,24 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="B5" s="57" t="inlineStr">
+      <c r="B5" s="59" t="inlineStr">
         <is>
           <t>CRNCY</t>
         </is>
       </c>
-      <c r="C5" s="58">
+      <c r="C5" s="60">
         <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="D5" s="58">
+      <c r="D5" s="60">
         <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="E5" s="58">
+      <c r="E5" s="60">
         <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="F5" s="58">
+      <c r="F5" s="60">
         <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
         <v/>
       </c>
@@ -8936,22 +9124,22 @@
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="C6" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="D6" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="E6" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="F6" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -8963,27 +9151,27 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B7" s="57" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C7" s="58" t="inlineStr">
+      <c r="C7" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D7" s="58" t="inlineStr">
+      <c r="D7" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E7" s="58" t="inlineStr">
+      <c r="E7" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F7" s="58" t="inlineStr">
+      <c r="F7" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9000,22 +9188,22 @@
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C8" s="26" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D8" s="26" t="inlineStr">
+      <c r="D8" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E8" s="26" t="inlineStr">
+      <c r="E8" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F8" s="26" t="inlineStr">
+      <c r="F8" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9027,27 +9215,27 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B9" s="57" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C9" s="58" t="inlineStr">
+      <c r="C9" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D9" s="58" t="inlineStr">
+      <c r="D9" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E9" s="58" t="inlineStr">
+      <c r="E9" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F9" s="58" t="inlineStr">
+      <c r="F9" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9064,19 +9252,19 @@
           <t>CALENDAR_CODE</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="27">
         <f>IFERROR(BDP("USOSFRC BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="27">
         <f>IFERROR(BDP("USOSFR1 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f>IFERROR(BDP("USOSFR5 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>IFERROR(BDP("USOSFR30 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
         <v/>
       </c>
@@ -9087,27 +9275,27 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B11" s="57" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C11" s="58" t="inlineStr">
+      <c r="C11" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D11" s="58" t="inlineStr">
+      <c r="D11" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E11" s="58" t="inlineStr">
+      <c r="E11" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F11" s="58" t="inlineStr">
+      <c r="F11" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9124,19 +9312,19 @@
           <t>DAY_CNT_DES</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>IFERROR(BDP("USOSFRC BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>IFERROR(BDP("USOSFR1 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>IFERROR(BDP("USOSFR5 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>IFERROR(BDP("USOSFR30 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
         <v/>
       </c>
@@ -9147,27 +9335,27 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B13" s="57" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C13" s="58" t="inlineStr">
+      <c r="C13" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D13" s="58" t="inlineStr">
+      <c r="D13" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E13" s="58" t="inlineStr">
+      <c r="E13" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F13" s="58" t="inlineStr">
+      <c r="F13" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9184,22 +9372,22 @@
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D14" s="26" t="inlineStr">
+      <c r="D14" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F14" s="26" t="inlineStr">
+      <c r="F14" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9211,27 +9399,27 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B15" s="57" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C15" s="58" t="inlineStr">
+      <c r="C15" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D15" s="58" t="inlineStr">
+      <c r="D15" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E15" s="58" t="inlineStr">
+      <c r="E15" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F15" s="58" t="inlineStr">
+      <c r="F15" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9248,22 +9436,22 @@
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="C16" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E16" s="26" t="inlineStr">
+      <c r="E16" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F16" s="26" t="inlineStr">
+      <c r="F16" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9275,27 +9463,27 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B17" s="57" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C17" s="58" t="inlineStr">
+      <c r="C17" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D17" s="58" t="inlineStr">
+      <c r="D17" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E17" s="58" t="inlineStr">
+      <c r="E17" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F17" s="58" t="inlineStr">
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9312,22 +9500,22 @@
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E18" s="26" t="inlineStr">
+      <c r="E18" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F18" s="26" t="inlineStr">
+      <c r="F18" s="27" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9339,27 +9527,27 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B19" s="57" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>— DES/SWPM manual —</t>
         </is>
       </c>
-      <c r="C19" s="58" t="inlineStr">
+      <c r="C19" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="D19" s="58" t="inlineStr">
+      <c r="D19" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="E19" s="58" t="inlineStr">
+      <c r="E19" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
       </c>
-      <c r="F19" s="58" t="inlineStr">
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>— DES/SWPM —</t>
         </is>
@@ -9378,15 +9566,15 @@
           <t>Reference index</t>
         </is>
       </c>
-      <c r="B22" s="59" t="inlineStr">
+      <c r="B22" s="61" t="inlineStr">
         <is>
           <t>USD-SOFR (compounded in arrears)</t>
         </is>
       </c>
-      <c r="C22" s="60" t="n"/>
-      <c r="D22" s="60" t="n"/>
-      <c r="E22" s="60" t="n"/>
-      <c r="F22" s="60" t="n"/>
+      <c r="C22" s="62" t="n"/>
+      <c r="D22" s="62" t="n"/>
+      <c r="E22" s="62" t="n"/>
+      <c r="F22" s="62" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -9394,15 +9582,15 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B23" s="59" t="inlineStr">
+      <c r="B23" s="61" t="inlineStr">
         <is>
           <t>T+2 US business days</t>
         </is>
       </c>
-      <c r="C23" s="60" t="n"/>
-      <c r="D23" s="60" t="n"/>
-      <c r="E23" s="60" t="n"/>
-      <c r="F23" s="60" t="n"/>
+      <c r="C23" s="62" t="n"/>
+      <c r="D23" s="62" t="n"/>
+      <c r="E23" s="62" t="n"/>
+      <c r="F23" s="62" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -9410,15 +9598,15 @@
           <t>Effective date rule</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B24" s="61" t="inlineStr">
         <is>
           <t>Spot (T+2), modified following</t>
         </is>
       </c>
-      <c r="C24" s="60" t="n"/>
-      <c r="D24" s="60" t="n"/>
-      <c r="E24" s="60" t="n"/>
-      <c r="F24" s="60" t="n"/>
+      <c r="C24" s="62" t="n"/>
+      <c r="D24" s="62" t="n"/>
+      <c r="E24" s="62" t="n"/>
+      <c r="F24" s="62" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -9426,15 +9614,15 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B25" s="59" t="inlineStr">
+      <c r="B25" s="61" t="inlineStr">
         <is>
           <t>Effective + tenor, modified following</t>
         </is>
       </c>
-      <c r="C25" s="60" t="n"/>
-      <c r="D25" s="60" t="n"/>
-      <c r="E25" s="60" t="n"/>
-      <c r="F25" s="60" t="n"/>
+      <c r="C25" s="62" t="n"/>
+      <c r="D25" s="62" t="n"/>
+      <c r="E25" s="62" t="n"/>
+      <c r="F25" s="62" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -9442,15 +9630,15 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B26" s="59" t="inlineStr">
+      <c r="B26" s="61" t="inlineStr">
         <is>
           <t>Modified Following</t>
         </is>
       </c>
-      <c r="C26" s="60" t="n"/>
-      <c r="D26" s="60" t="n"/>
-      <c r="E26" s="60" t="n"/>
-      <c r="F26" s="60" t="n"/>
+      <c r="C26" s="62" t="n"/>
+      <c r="D26" s="62" t="n"/>
+      <c r="E26" s="62" t="n"/>
+      <c r="F26" s="62" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -9458,15 +9646,15 @@
           <t>Fixed-leg day count</t>
         </is>
       </c>
-      <c r="B27" s="59" t="inlineStr">
+      <c r="B27" s="61" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
       </c>
-      <c r="C27" s="60" t="n"/>
-      <c r="D27" s="60" t="n"/>
-      <c r="E27" s="60" t="n"/>
-      <c r="F27" s="60" t="n"/>
+      <c r="C27" s="62" t="n"/>
+      <c r="D27" s="62" t="n"/>
+      <c r="E27" s="62" t="n"/>
+      <c r="F27" s="62" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -9474,15 +9662,15 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B28" s="59" t="inlineStr">
+      <c r="B28" s="61" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
       </c>
-      <c r="C28" s="60" t="n"/>
-      <c r="D28" s="60" t="n"/>
-      <c r="E28" s="60" t="n"/>
-      <c r="F28" s="60" t="n"/>
+      <c r="C28" s="62" t="n"/>
+      <c r="D28" s="62" t="n"/>
+      <c r="E28" s="62" t="n"/>
+      <c r="F28" s="62" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -9490,15 +9678,15 @@
           <t>Floating-leg day count</t>
         </is>
       </c>
-      <c r="B29" s="59" t="inlineStr">
+      <c r="B29" s="61" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
       </c>
-      <c r="C29" s="60" t="n"/>
-      <c r="D29" s="60" t="n"/>
-      <c r="E29" s="60" t="n"/>
-      <c r="F29" s="60" t="n"/>
+      <c r="C29" s="62" t="n"/>
+      <c r="D29" s="62" t="n"/>
+      <c r="E29" s="62" t="n"/>
+      <c r="F29" s="62" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -9506,15 +9694,15 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B30" s="61" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
       </c>
-      <c r="C30" s="60" t="n"/>
-      <c r="D30" s="60" t="n"/>
-      <c r="E30" s="60" t="n"/>
-      <c r="F30" s="60" t="n"/>
+      <c r="C30" s="62" t="n"/>
+      <c r="D30" s="62" t="n"/>
+      <c r="E30" s="62" t="n"/>
+      <c r="F30" s="62" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -9522,15 +9710,15 @@
           <t>SOFR compounding method</t>
         </is>
       </c>
-      <c r="B31" s="59" t="inlineStr">
+      <c r="B31" s="61" t="inlineStr">
         <is>
           <t>Daily compounded, ACT/360</t>
         </is>
       </c>
-      <c r="C31" s="60" t="n"/>
-      <c r="D31" s="60" t="n"/>
-      <c r="E31" s="60" t="n"/>
-      <c r="F31" s="60" t="n"/>
+      <c r="C31" s="62" t="n"/>
+      <c r="D31" s="62" t="n"/>
+      <c r="E31" s="62" t="n"/>
+      <c r="F31" s="62" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -9538,15 +9726,15 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B32" s="59" t="inlineStr">
+      <c r="B32" s="61" t="inlineStr">
         <is>
           <t>2 US business days</t>
         </is>
       </c>
-      <c r="C32" s="60" t="n"/>
-      <c r="D32" s="60" t="n"/>
-      <c r="E32" s="60" t="n"/>
-      <c r="F32" s="60" t="n"/>
+      <c r="C32" s="62" t="n"/>
+      <c r="D32" s="62" t="n"/>
+      <c r="E32" s="62" t="n"/>
+      <c r="F32" s="62" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -9554,15 +9742,15 @@
           <t>Observation shift / lookback</t>
         </is>
       </c>
-      <c r="B33" s="59" t="inlineStr">
+      <c r="B33" s="61" t="inlineStr">
         <is>
           <t>None (payment-delay convention, 2 bd)</t>
         </is>
       </c>
-      <c r="C33" s="60" t="n"/>
-      <c r="D33" s="60" t="n"/>
-      <c r="E33" s="60" t="n"/>
-      <c r="F33" s="60" t="n"/>
+      <c r="C33" s="62" t="n"/>
+      <c r="D33" s="62" t="n"/>
+      <c r="E33" s="62" t="n"/>
+      <c r="F33" s="62" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -9570,15 +9758,15 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B34" s="59" t="inlineStr">
+      <c r="B34" s="61" t="inlineStr">
         <is>
           <t>EOM applies</t>
         </is>
       </c>
-      <c r="C34" s="60" t="n"/>
-      <c r="D34" s="60" t="n"/>
-      <c r="E34" s="60" t="n"/>
-      <c r="F34" s="60" t="n"/>
+      <c r="C34" s="62" t="n"/>
+      <c r="D34" s="62" t="n"/>
+      <c r="E34" s="62" t="n"/>
+      <c r="F34" s="62" t="n"/>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="11" t="inlineStr">

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -6144,9 +6144,10 @@
         <f>EDATE(B8,12*B9)</f>
         <v/>
       </c>
-      <c r="C10" s="32">
-        <f> Effective + Tenor.</f>
-        <v/>
+      <c r="C10" s="32" t="inlineStr">
+        <is>
+          <t>Effective + Tenor.</t>
+        </is>
       </c>
       <c r="K10" s="17">
         <f>Bootstrap!B11</f>
@@ -6520,9 +6521,10 @@
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="32">
-        <f> Fixed − Float (notionals cancel). ≈ 0 at par coupon.</f>
-        <v/>
+      <c r="C28" s="32" t="inlineStr">
+        <is>
+          <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
+        </is>
       </c>
       <c r="K28" s="17">
         <f>Bootstrap!B29</f>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -130,7 +130,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,17 +182,18 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -4228,7 +4229,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:Z42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4244,6 +4245,17 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="15" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4256,7 +4268,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Single-curve OIS bootstrap from the SOFR_OIS_Quotes mid strip → discount factors, zero &amp; forward rates</t>
+          <t>Three-segment USD curve (Zhou 2002): short OIS (≤1Y) · SR3 futures (1Y–5Y) · OIS swaps (5Y–50Y)</t>
         </is>
       </c>
     </row>
@@ -4274,11 +4286,22 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Proper single-curve OIS bootstrap that respects the payment convention: OIS ≤ 1Y pay a SINGLE coupon at maturity → DF = 1/(1 + S·τ0); OIS ≥ 18M pay ANNUAL coupons → DF = (1 − S·A_prior)/(1 + S·τcoupon), where A_prior = Σ τ·DF over prior annual coupon dates (column I accumulates these; sub-annual and 18M rows add 0 so only annual pillars enter the annuity). Exact through 10Y; the sparse long end (12–50Y) uses the pillar grid as the coupon schedule. Every input reprices to par to ~0 bp. Par rates pull live from SOFR_OIS_Quotes; paste S490 zeros into column L for the Δz check.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·τ0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which discounts each contract's forward rate forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is shown only for reference).  LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·τcoupon), with the annuity (col I) built from the short + futures DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>MIDDLE SEGMENT — SR3 futures chain (1Y→5Y)</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>Mid interp grid</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
@@ -4343,6 +4366,61 @@
       <c r="M7" s="19" t="inlineStr">
         <is>
           <t>Δ vs S490 (bp)</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P7" s="19" t="inlineStr">
+        <is>
+          <t>Fut start</t>
+        </is>
+      </c>
+      <c r="Q7" s="19" t="inlineStr">
+        <is>
+          <t>Fut end</t>
+        </is>
+      </c>
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>τ eff (post-1Y)</t>
+        </is>
+      </c>
+      <c r="S7" s="19" t="inlineStr">
+        <is>
+          <t>Implied %</t>
+        </is>
+      </c>
+      <c r="T7" s="19" t="inlineStr">
+        <is>
+          <t>Convexity bp</t>
+        </is>
+      </c>
+      <c r="U7" s="19" t="inlineStr">
+        <is>
+          <t>Fwd</t>
+        </is>
+      </c>
+      <c r="V7" s="19" t="inlineStr">
+        <is>
+          <t>DF before</t>
+        </is>
+      </c>
+      <c r="W7" s="19" t="inlineStr">
+        <is>
+          <t>DF after</t>
+        </is>
+      </c>
+      <c r="Y7" s="19" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="Z7" s="19" t="inlineStr">
+        <is>
+          <t>DF</t>
         </is>
       </c>
     </row>
@@ -4392,6 +4470,49 @@
         <f>IF(L8="","",(J8-L8)*100)</f>
         <v/>
       </c>
+      <c r="O8" s="6">
+        <f>'SOFR_Futures'!A7</f>
+        <v/>
+      </c>
+      <c r="P8" s="17">
+        <f>'SOFR_Futures'!H7</f>
+        <v/>
+      </c>
+      <c r="Q8" s="17">
+        <f>'SOFR_Futures'!H8</f>
+        <v/>
+      </c>
+      <c r="R8" s="16">
+        <f>MAX(0,(Q8-MAX(P8,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S8" s="16">
+        <f>'SOFR_Futures'!F7</f>
+        <v/>
+      </c>
+      <c r="T8" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="32">
+        <f>(S8-T8/100)/100</f>
+        <v/>
+      </c>
+      <c r="V8" s="33">
+        <f>$H$22</f>
+        <v/>
+      </c>
+      <c r="W8" s="33">
+        <f>V8/(1+U8*R8)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="17">
+        <f>$B$22</f>
+        <v/>
+      </c>
+      <c r="Z8" s="33">
+        <f>$H$22</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -4440,6 +4561,49 @@
         <f>IF(L9="","",(J9-L9)*100)</f>
         <v/>
       </c>
+      <c r="O9" s="6">
+        <f>'SOFR_Futures'!A8</f>
+        <v/>
+      </c>
+      <c r="P9" s="17">
+        <f>'SOFR_Futures'!H8</f>
+        <v/>
+      </c>
+      <c r="Q9" s="17">
+        <f>'SOFR_Futures'!H9</f>
+        <v/>
+      </c>
+      <c r="R9" s="16">
+        <f>MAX(0,(Q9-MAX(P9,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S9" s="16">
+        <f>'SOFR_Futures'!F8</f>
+        <v/>
+      </c>
+      <c r="T9" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="32">
+        <f>(S9-T9/100)/100</f>
+        <v/>
+      </c>
+      <c r="V9" s="33">
+        <f>W8</f>
+        <v/>
+      </c>
+      <c r="W9" s="33">
+        <f>V9/(1+U9*R9)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="17">
+        <f>MAX(Q8,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="33">
+        <f>W8</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -4488,6 +4652,49 @@
         <f>IF(L10="","",(J10-L10)*100)</f>
         <v/>
       </c>
+      <c r="O10" s="6">
+        <f>'SOFR_Futures'!A9</f>
+        <v/>
+      </c>
+      <c r="P10" s="17">
+        <f>'SOFR_Futures'!H9</f>
+        <v/>
+      </c>
+      <c r="Q10" s="17">
+        <f>'SOFR_Futures'!H10</f>
+        <v/>
+      </c>
+      <c r="R10" s="16">
+        <f>MAX(0,(Q10-MAX(P10,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S10" s="16">
+        <f>'SOFR_Futures'!F9</f>
+        <v/>
+      </c>
+      <c r="T10" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="32">
+        <f>(S10-T10/100)/100</f>
+        <v/>
+      </c>
+      <c r="V10" s="33">
+        <f>W9</f>
+        <v/>
+      </c>
+      <c r="W10" s="33">
+        <f>V10/(1+U10*R10)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="17">
+        <f>MAX(Q9,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="33">
+        <f>W9</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -4536,6 +4743,49 @@
         <f>IF(L11="","",(J11-L11)*100)</f>
         <v/>
       </c>
+      <c r="O11" s="6">
+        <f>'SOFR_Futures'!A10</f>
+        <v/>
+      </c>
+      <c r="P11" s="17">
+        <f>'SOFR_Futures'!H10</f>
+        <v/>
+      </c>
+      <c r="Q11" s="17">
+        <f>'SOFR_Futures'!H11</f>
+        <v/>
+      </c>
+      <c r="R11" s="16">
+        <f>MAX(0,(Q11-MAX(P11,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S11" s="16">
+        <f>'SOFR_Futures'!F10</f>
+        <v/>
+      </c>
+      <c r="T11" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="32">
+        <f>(S11-T11/100)/100</f>
+        <v/>
+      </c>
+      <c r="V11" s="33">
+        <f>W10</f>
+        <v/>
+      </c>
+      <c r="W11" s="33">
+        <f>V11/(1+U11*R11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="17">
+        <f>MAX(Q10,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="33">
+        <f>W10</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -4584,6 +4834,49 @@
         <f>IF(L12="","",(J12-L12)*100)</f>
         <v/>
       </c>
+      <c r="O12" s="6">
+        <f>'SOFR_Futures'!A11</f>
+        <v/>
+      </c>
+      <c r="P12" s="17">
+        <f>'SOFR_Futures'!H11</f>
+        <v/>
+      </c>
+      <c r="Q12" s="17">
+        <f>'SOFR_Futures'!H12</f>
+        <v/>
+      </c>
+      <c r="R12" s="16">
+        <f>MAX(0,(Q12-MAX(P12,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S12" s="16">
+        <f>'SOFR_Futures'!F11</f>
+        <v/>
+      </c>
+      <c r="T12" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="32">
+        <f>(S12-T12/100)/100</f>
+        <v/>
+      </c>
+      <c r="V12" s="33">
+        <f>W11</f>
+        <v/>
+      </c>
+      <c r="W12" s="33">
+        <f>V12/(1+U12*R12)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="17">
+        <f>MAX(Q11,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="33">
+        <f>W11</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -4632,6 +4925,49 @@
         <f>IF(L13="","",(J13-L13)*100)</f>
         <v/>
       </c>
+      <c r="O13" s="6">
+        <f>'SOFR_Futures'!A12</f>
+        <v/>
+      </c>
+      <c r="P13" s="17">
+        <f>'SOFR_Futures'!H12</f>
+        <v/>
+      </c>
+      <c r="Q13" s="17">
+        <f>'SOFR_Futures'!H13</f>
+        <v/>
+      </c>
+      <c r="R13" s="16">
+        <f>MAX(0,(Q13-MAX(P13,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S13" s="16">
+        <f>'SOFR_Futures'!F12</f>
+        <v/>
+      </c>
+      <c r="T13" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="32">
+        <f>(S13-T13/100)/100</f>
+        <v/>
+      </c>
+      <c r="V13" s="33">
+        <f>W12</f>
+        <v/>
+      </c>
+      <c r="W13" s="33">
+        <f>V13/(1+U13*R13)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="17">
+        <f>MAX(Q12,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="33">
+        <f>W12</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -4680,6 +5016,49 @@
         <f>IF(L14="","",(J14-L14)*100)</f>
         <v/>
       </c>
+      <c r="O14" s="6">
+        <f>'SOFR_Futures'!A13</f>
+        <v/>
+      </c>
+      <c r="P14" s="17">
+        <f>'SOFR_Futures'!H13</f>
+        <v/>
+      </c>
+      <c r="Q14" s="17">
+        <f>'SOFR_Futures'!H14</f>
+        <v/>
+      </c>
+      <c r="R14" s="16">
+        <f>MAX(0,(Q14-MAX(P14,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S14" s="16">
+        <f>'SOFR_Futures'!F13</f>
+        <v/>
+      </c>
+      <c r="T14" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="32">
+        <f>(S14-T14/100)/100</f>
+        <v/>
+      </c>
+      <c r="V14" s="33">
+        <f>W13</f>
+        <v/>
+      </c>
+      <c r="W14" s="33">
+        <f>V14/(1+U14*R14)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="17">
+        <f>MAX(Q13,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="33">
+        <f>W13</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -4728,6 +5107,49 @@
         <f>IF(L15="","",(J15-L15)*100)</f>
         <v/>
       </c>
+      <c r="O15" s="6">
+        <f>'SOFR_Futures'!A14</f>
+        <v/>
+      </c>
+      <c r="P15" s="17">
+        <f>'SOFR_Futures'!H14</f>
+        <v/>
+      </c>
+      <c r="Q15" s="17">
+        <f>'SOFR_Futures'!H15</f>
+        <v/>
+      </c>
+      <c r="R15" s="16">
+        <f>MAX(0,(Q15-MAX(P15,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S15" s="16">
+        <f>'SOFR_Futures'!F14</f>
+        <v/>
+      </c>
+      <c r="T15" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="32">
+        <f>(S15-T15/100)/100</f>
+        <v/>
+      </c>
+      <c r="V15" s="33">
+        <f>W14</f>
+        <v/>
+      </c>
+      <c r="W15" s="33">
+        <f>V15/(1+U15*R15)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="17">
+        <f>MAX(Q14,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="33">
+        <f>W14</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -4776,6 +5198,49 @@
         <f>IF(L16="","",(J16-L16)*100)</f>
         <v/>
       </c>
+      <c r="O16" s="6">
+        <f>'SOFR_Futures'!A15</f>
+        <v/>
+      </c>
+      <c r="P16" s="17">
+        <f>'SOFR_Futures'!H15</f>
+        <v/>
+      </c>
+      <c r="Q16" s="17">
+        <f>'SOFR_Futures'!H16</f>
+        <v/>
+      </c>
+      <c r="R16" s="16">
+        <f>MAX(0,(Q16-MAX(P16,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S16" s="16">
+        <f>'SOFR_Futures'!F15</f>
+        <v/>
+      </c>
+      <c r="T16" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="32">
+        <f>(S16-T16/100)/100</f>
+        <v/>
+      </c>
+      <c r="V16" s="33">
+        <f>W15</f>
+        <v/>
+      </c>
+      <c r="W16" s="33">
+        <f>V16/(1+U16*R16)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="17">
+        <f>MAX(Q15,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="33">
+        <f>W15</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -4824,6 +5289,49 @@
         <f>IF(L17="","",(J17-L17)*100)</f>
         <v/>
       </c>
+      <c r="O17" s="6">
+        <f>'SOFR_Futures'!A16</f>
+        <v/>
+      </c>
+      <c r="P17" s="17">
+        <f>'SOFR_Futures'!H16</f>
+        <v/>
+      </c>
+      <c r="Q17" s="17">
+        <f>'SOFR_Futures'!H17</f>
+        <v/>
+      </c>
+      <c r="R17" s="16">
+        <f>MAX(0,(Q17-MAX(P17,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S17" s="16">
+        <f>'SOFR_Futures'!F16</f>
+        <v/>
+      </c>
+      <c r="T17" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="32">
+        <f>(S17-T17/100)/100</f>
+        <v/>
+      </c>
+      <c r="V17" s="33">
+        <f>W16</f>
+        <v/>
+      </c>
+      <c r="W17" s="33">
+        <f>V17/(1+U17*R17)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="17">
+        <f>MAX(Q16,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="33">
+        <f>W16</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -4872,6 +5380,49 @@
         <f>IF(L18="","",(J18-L18)*100)</f>
         <v/>
       </c>
+      <c r="O18" s="6">
+        <f>'SOFR_Futures'!A17</f>
+        <v/>
+      </c>
+      <c r="P18" s="17">
+        <f>'SOFR_Futures'!H17</f>
+        <v/>
+      </c>
+      <c r="Q18" s="17">
+        <f>'SOFR_Futures'!H18</f>
+        <v/>
+      </c>
+      <c r="R18" s="16">
+        <f>MAX(0,(Q18-MAX(P18,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S18" s="16">
+        <f>'SOFR_Futures'!F17</f>
+        <v/>
+      </c>
+      <c r="T18" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="32">
+        <f>(S18-T18/100)/100</f>
+        <v/>
+      </c>
+      <c r="V18" s="33">
+        <f>W17</f>
+        <v/>
+      </c>
+      <c r="W18" s="33">
+        <f>V18/(1+U18*R18)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="17">
+        <f>MAX(Q17,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="33">
+        <f>W17</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -4920,6 +5471,49 @@
         <f>IF(L19="","",(J19-L19)*100)</f>
         <v/>
       </c>
+      <c r="O19" s="6">
+        <f>'SOFR_Futures'!A18</f>
+        <v/>
+      </c>
+      <c r="P19" s="17">
+        <f>'SOFR_Futures'!H18</f>
+        <v/>
+      </c>
+      <c r="Q19" s="17">
+        <f>'SOFR_Futures'!H19</f>
+        <v/>
+      </c>
+      <c r="R19" s="16">
+        <f>MAX(0,(Q19-MAX(P19,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S19" s="16">
+        <f>'SOFR_Futures'!F18</f>
+        <v/>
+      </c>
+      <c r="T19" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="32">
+        <f>(S19-T19/100)/100</f>
+        <v/>
+      </c>
+      <c r="V19" s="33">
+        <f>W18</f>
+        <v/>
+      </c>
+      <c r="W19" s="33">
+        <f>V19/(1+U19*R19)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="17">
+        <f>MAX(Q18,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="33">
+        <f>W18</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -4968,6 +5562,49 @@
         <f>IF(L20="","",(J20-L20)*100)</f>
         <v/>
       </c>
+      <c r="O20" s="6">
+        <f>'SOFR_Futures'!A19</f>
+        <v/>
+      </c>
+      <c r="P20" s="17">
+        <f>'SOFR_Futures'!H19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="17">
+        <f>'SOFR_Futures'!H20</f>
+        <v/>
+      </c>
+      <c r="R20" s="16">
+        <f>MAX(0,(Q20-MAX(P20,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S20" s="16">
+        <f>'SOFR_Futures'!F19</f>
+        <v/>
+      </c>
+      <c r="T20" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="32">
+        <f>(S20-T20/100)/100</f>
+        <v/>
+      </c>
+      <c r="V20" s="33">
+        <f>W19</f>
+        <v/>
+      </c>
+      <c r="W20" s="33">
+        <f>V20/(1+U20*R20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="17">
+        <f>MAX(Q19,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="33">
+        <f>W19</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -5016,6 +5653,49 @@
         <f>IF(L21="","",(J21-L21)*100)</f>
         <v/>
       </c>
+      <c r="O21" s="6">
+        <f>'SOFR_Futures'!A20</f>
+        <v/>
+      </c>
+      <c r="P21" s="17">
+        <f>'SOFR_Futures'!H20</f>
+        <v/>
+      </c>
+      <c r="Q21" s="17">
+        <f>'SOFR_Futures'!H21</f>
+        <v/>
+      </c>
+      <c r="R21" s="16">
+        <f>MAX(0,(Q21-MAX(P21,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S21" s="16">
+        <f>'SOFR_Futures'!F20</f>
+        <v/>
+      </c>
+      <c r="T21" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="32">
+        <f>(S21-T21/100)/100</f>
+        <v/>
+      </c>
+      <c r="V21" s="33">
+        <f>W20</f>
+        <v/>
+      </c>
+      <c r="W21" s="33">
+        <f>V21/(1+U21*R21)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="17">
+        <f>MAX(Q20,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="33">
+        <f>W20</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -5068,6 +5748,49 @@
         <f>IF(L22="","",(J22-L22)*100)</f>
         <v/>
       </c>
+      <c r="O22" s="6">
+        <f>'SOFR_Futures'!A21</f>
+        <v/>
+      </c>
+      <c r="P22" s="17">
+        <f>'SOFR_Futures'!H21</f>
+        <v/>
+      </c>
+      <c r="Q22" s="17">
+        <f>'SOFR_Futures'!H22</f>
+        <v/>
+      </c>
+      <c r="R22" s="16">
+        <f>MAX(0,(Q22-MAX(P22,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S22" s="16">
+        <f>'SOFR_Futures'!F21</f>
+        <v/>
+      </c>
+      <c r="T22" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="32">
+        <f>(S22-T22/100)/100</f>
+        <v/>
+      </c>
+      <c r="V22" s="33">
+        <f>W21</f>
+        <v/>
+      </c>
+      <c r="W22" s="33">
+        <f>V22/(1+U22*R22)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="17">
+        <f>MAX(Q21,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="33">
+        <f>W21</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -5100,7 +5823,7 @@
         <v/>
       </c>
       <c r="H23" s="28">
-        <f>(1-(E23/100)*G23)/(1+(E23/100)*F23)</f>
+        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))</f>
         <v/>
       </c>
       <c r="I23" s="16" t="n">
@@ -5119,6 +5842,49 @@
         <f>IF(L23="","",(J23-L23)*100)</f>
         <v/>
       </c>
+      <c r="O23" s="6">
+        <f>'SOFR_Futures'!A22</f>
+        <v/>
+      </c>
+      <c r="P23" s="17">
+        <f>'SOFR_Futures'!H22</f>
+        <v/>
+      </c>
+      <c r="Q23" s="17">
+        <f>'SOFR_Futures'!H23</f>
+        <v/>
+      </c>
+      <c r="R23" s="16">
+        <f>MAX(0,(Q23-MAX(P23,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S23" s="16">
+        <f>'SOFR_Futures'!F22</f>
+        <v/>
+      </c>
+      <c r="T23" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="32">
+        <f>(S23-T23/100)/100</f>
+        <v/>
+      </c>
+      <c r="V23" s="33">
+        <f>W22</f>
+        <v/>
+      </c>
+      <c r="W23" s="33">
+        <f>V23/(1+U23*R23)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="17">
+        <f>MAX(Q22,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="33">
+        <f>W22</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -5151,7 +5917,7 @@
         <v/>
       </c>
       <c r="H24" s="28">
-        <f>(1-(E24/100)*G24)/(1+(E24/100)*F24)</f>
+        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))</f>
         <v/>
       </c>
       <c r="I24" s="16">
@@ -5171,6 +5937,49 @@
         <f>IF(L24="","",(J24-L24)*100)</f>
         <v/>
       </c>
+      <c r="O24" s="6">
+        <f>'SOFR_Futures'!A23</f>
+        <v/>
+      </c>
+      <c r="P24" s="17">
+        <f>'SOFR_Futures'!H23</f>
+        <v/>
+      </c>
+      <c r="Q24" s="17">
+        <f>'SOFR_Futures'!H24</f>
+        <v/>
+      </c>
+      <c r="R24" s="16">
+        <f>MAX(0,(Q24-MAX(P24,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S24" s="16">
+        <f>'SOFR_Futures'!F23</f>
+        <v/>
+      </c>
+      <c r="T24" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="32">
+        <f>(S24-T24/100)/100</f>
+        <v/>
+      </c>
+      <c r="V24" s="33">
+        <f>W23</f>
+        <v/>
+      </c>
+      <c r="W24" s="33">
+        <f>V24/(1+U24*R24)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="17">
+        <f>MAX(Q23,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="33">
+        <f>W23</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -5203,7 +6012,7 @@
         <v/>
       </c>
       <c r="H25" s="28">
-        <f>(1-(E25/100)*G25)/(1+(E25/100)*F25)</f>
+        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))</f>
         <v/>
       </c>
       <c r="I25" s="16">
@@ -5223,6 +6032,49 @@
         <f>IF(L25="","",(J25-L25)*100)</f>
         <v/>
       </c>
+      <c r="O25" s="6">
+        <f>'SOFR_Futures'!A24</f>
+        <v/>
+      </c>
+      <c r="P25" s="17">
+        <f>'SOFR_Futures'!H24</f>
+        <v/>
+      </c>
+      <c r="Q25" s="17">
+        <f>'SOFR_Futures'!H25</f>
+        <v/>
+      </c>
+      <c r="R25" s="16">
+        <f>MAX(0,(Q25-MAX(P25,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S25" s="16">
+        <f>'SOFR_Futures'!F24</f>
+        <v/>
+      </c>
+      <c r="T25" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="32">
+        <f>(S25-T25/100)/100</f>
+        <v/>
+      </c>
+      <c r="V25" s="33">
+        <f>W24</f>
+        <v/>
+      </c>
+      <c r="W25" s="33">
+        <f>V25/(1+U25*R25)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="17">
+        <f>MAX(Q24,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="33">
+        <f>W24</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -5255,7 +6107,7 @@
         <v/>
       </c>
       <c r="H26" s="28">
-        <f>(1-(E26/100)*G26)/(1+(E26/100)*F26)</f>
+        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))</f>
         <v/>
       </c>
       <c r="I26" s="16">
@@ -5275,6 +6127,49 @@
         <f>IF(L26="","",(J26-L26)*100)</f>
         <v/>
       </c>
+      <c r="O26" s="6">
+        <f>'SOFR_Futures'!A25</f>
+        <v/>
+      </c>
+      <c r="P26" s="17">
+        <f>'SOFR_Futures'!H25</f>
+        <v/>
+      </c>
+      <c r="Q26" s="17">
+        <f>'SOFR_Futures'!H26</f>
+        <v/>
+      </c>
+      <c r="R26" s="16">
+        <f>MAX(0,(Q26-MAX(P26,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S26" s="16">
+        <f>'SOFR_Futures'!F25</f>
+        <v/>
+      </c>
+      <c r="T26" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="32">
+        <f>(S26-T26/100)/100</f>
+        <v/>
+      </c>
+      <c r="V26" s="33">
+        <f>W25</f>
+        <v/>
+      </c>
+      <c r="W26" s="33">
+        <f>V26/(1+U26*R26)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="17">
+        <f>MAX(Q25,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="33">
+        <f>W25</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -5307,7 +6202,7 @@
         <v/>
       </c>
       <c r="H27" s="28">
-        <f>(1-(E27/100)*G27)/(1+(E27/100)*F27)</f>
+        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))</f>
         <v/>
       </c>
       <c r="I27" s="16">
@@ -5327,6 +6222,49 @@
         <f>IF(L27="","",(J27-L27)*100)</f>
         <v/>
       </c>
+      <c r="O27" s="6">
+        <f>'SOFR_Futures'!A26</f>
+        <v/>
+      </c>
+      <c r="P27" s="17">
+        <f>'SOFR_Futures'!H26</f>
+        <v/>
+      </c>
+      <c r="Q27" s="17">
+        <f>EDATE(P27,3)</f>
+        <v/>
+      </c>
+      <c r="R27" s="16">
+        <f>MAX(0,(Q27-MAX(P27,$B$22))/360)</f>
+        <v/>
+      </c>
+      <c r="S27" s="16">
+        <f>'SOFR_Futures'!F26</f>
+        <v/>
+      </c>
+      <c r="T27" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="32">
+        <f>(S27-T27/100)/100</f>
+        <v/>
+      </c>
+      <c r="V27" s="33">
+        <f>W26</f>
+        <v/>
+      </c>
+      <c r="W27" s="33">
+        <f>V27/(1+U27*R27)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="17">
+        <f>MAX(Q26,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="33">
+        <f>W26</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -5379,6 +6317,14 @@
         <f>IF(L28="","",(J28-L28)*100)</f>
         <v/>
       </c>
+      <c r="Y28" s="17">
+        <f>MAX(Q27,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="33">
+        <f>W27</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -5955,14 +6901,16 @@
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>Column H (Discount factor) is the deliverable curve P(0,T). Zero rate is continuously-compounded (ACT/365): z = −ln(DF)/T. Column I (Ann.add) is τ·DF booked only at annual coupon dates, so column G sums exactly the coupons each swap actually pays. Yellow column L takes pasted Bloomberg S490 zeros; Δ (bp) is your bootstrap vs Bloomberg — the dealer-curve validation from the Lehman paper. The Swap_Pricer tab values any SOFR OIS off this curve.</t>
+          <t>THREE SEGMENTS (Zhou 2002 structure):  SHORT o/n–1Y = single-payment SOFR OIS  (DF=1/(1+S·τ0));  MIDDLE 1Y–5Y = SR3 futures chained from the 1Y DF (helper block to the right, cols O–W);  LONG 5Y–50Y = annual SOFR OIS swaps built off the futures-derived 5Y point. No overlap — each maturity is covered once. Column H is the curve P(0,T); zero z=−ln(DF)/T. The futures convexity column (T) defaults to 0 — enter an adjustment in bp to correct futures→forward. Paste S490 zeros into column L for the Δz check; the Swap_Pricer values any OIS off this curve.</t>
         </is>
       </c>
     </row>
     <row r="42"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="O6:W6"/>
     <mergeCell ref="A5:M6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="A41:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6024,12 +6972,12 @@
           <t>Direction (Leg 1 = Fixed)</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Receive fixed</t>
         </is>
       </c>
-      <c r="C5" s="32" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
         </is>
@@ -6051,10 +6999,10 @@
           <t>Notional</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="36" t="n">
         <v>10000000</v>
       </c>
-      <c r="C6" s="32" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Both legs, USD.</t>
         </is>
@@ -6063,7 +7011,7 @@
         <f>Bootstrap!$B$4</f>
         <v/>
       </c>
-      <c r="L6" s="34" t="n">
+      <c r="L6" s="33" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6082,7 +7030,7 @@
         <f>Bootstrap!B8</f>
         <v/>
       </c>
-      <c r="L7" s="34">
+      <c r="L7" s="33">
         <f>Bootstrap!H8</f>
         <v/>
       </c>
@@ -6093,11 +7041,11 @@
           <t>Effective date</t>
         </is>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="37">
         <f>Bootstrap!$B$4</f>
         <v/>
       </c>
-      <c r="C8" s="32" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
         </is>
@@ -6106,7 +7054,7 @@
         <f>Bootstrap!B9</f>
         <v/>
       </c>
-      <c r="L8" s="34">
+      <c r="L8" s="33">
         <f>Bootstrap!H9</f>
         <v/>
       </c>
@@ -6117,10 +7065,10 @@
           <t>Tenor (years)</t>
         </is>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="32" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Whole years; drives the annual coupon schedule below.</t>
         </is>
@@ -6129,7 +7077,7 @@
         <f>Bootstrap!B10</f>
         <v/>
       </c>
-      <c r="L9" s="34">
+      <c r="L9" s="33">
         <f>Bootstrap!H10</f>
         <v/>
       </c>
@@ -6144,7 +7092,7 @@
         <f>EDATE(B8,12*B9)</f>
         <v/>
       </c>
-      <c r="C10" s="32" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Effective + Tenor.</t>
         </is>
@@ -6153,7 +7101,7 @@
         <f>Bootstrap!B11</f>
         <v/>
       </c>
-      <c r="L10" s="34">
+      <c r="L10" s="33">
         <f>Bootstrap!H11</f>
         <v/>
       </c>
@@ -6164,11 +7112,11 @@
           <t>Fixed coupon (%)</t>
         </is>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="39">
         <f>B25</f>
         <v/>
       </c>
-      <c r="C11" s="32" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
         </is>
@@ -6177,7 +7125,7 @@
         <f>Bootstrap!B12</f>
         <v/>
       </c>
-      <c r="L11" s="34">
+      <c r="L11" s="33">
         <f>Bootstrap!H12</f>
         <v/>
       </c>
@@ -6197,7 +7145,7 @@
         <f>Bootstrap!B13</f>
         <v/>
       </c>
-      <c r="L12" s="34">
+      <c r="L12" s="33">
         <f>Bootstrap!H13</f>
         <v/>
       </c>
@@ -6217,7 +7165,7 @@
         <f>Bootstrap!B14</f>
         <v/>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="33">
         <f>Bootstrap!H14</f>
         <v/>
       </c>
@@ -6237,7 +7185,7 @@
         <f>Bootstrap!B15</f>
         <v/>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="33">
         <f>Bootstrap!H15</f>
         <v/>
       </c>
@@ -6252,7 +7200,7 @@
         <f>VAL_DATE</f>
         <v/>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Curve is discounted from spot = Bootstrap!B4.</t>
         </is>
@@ -6261,7 +7209,7 @@
         <f>Bootstrap!B16</f>
         <v/>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="33">
         <f>Bootstrap!H16</f>
         <v/>
       </c>
@@ -6272,7 +7220,7 @@
           <t>Direction sign (+recv / −pay)</t>
         </is>
       </c>
-      <c r="B16" s="38">
+      <c r="B16" s="40">
         <f>IF($B$5="Receive fixed",1,-1)</f>
         <v/>
       </c>
@@ -6280,7 +7228,7 @@
         <f>Bootstrap!B17</f>
         <v/>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="33">
         <f>Bootstrap!H17</f>
         <v/>
       </c>
@@ -6290,7 +7238,7 @@
         <f>Bootstrap!B18</f>
         <v/>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="33">
         <f>Bootstrap!H18</f>
         <v/>
       </c>
@@ -6305,7 +7253,7 @@
         <f>Bootstrap!B19</f>
         <v/>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="33">
         <f>Bootstrap!H19</f>
         <v/>
       </c>
@@ -6316,11 +7264,11 @@
           <t>DF(effective)</t>
         </is>
       </c>
-      <c r="B19" s="34">
+      <c r="B19" s="33">
         <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))^(($B$8-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))</f>
         <v/>
       </c>
-      <c r="C19" s="32" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Interpolated from the curve.</t>
         </is>
@@ -6329,7 +7277,7 @@
         <f>Bootstrap!B20</f>
         <v/>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="33">
         <f>Bootstrap!H20</f>
         <v/>
       </c>
@@ -6340,7 +7288,7 @@
           <t>DF(maturity)</t>
         </is>
       </c>
-      <c r="B20" s="34">
+      <c r="B20" s="33">
         <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)))^(($B$10-INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$10,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$10,$K$6:$K$38,1)))</f>
         <v/>
       </c>
@@ -6348,7 +7296,7 @@
         <f>Bootstrap!B21</f>
         <v/>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="33">
         <f>Bootstrap!H21</f>
         <v/>
       </c>
@@ -6359,11 +7307,11 @@
           <t>Fixed annuity  Στ·DF</t>
         </is>
       </c>
-      <c r="B21" s="39">
+      <c r="B21" s="32">
         <f>SUM(H36:H85)</f>
         <v/>
       </c>
-      <c r="C21" s="32" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Sum of τ·DF over the fixed coupon dates.</t>
         </is>
@@ -6372,7 +7320,7 @@
         <f>Bootstrap!B22</f>
         <v/>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="33">
         <f>Bootstrap!H22</f>
         <v/>
       </c>
@@ -6383,7 +7331,7 @@
           <t>Fixed leg PV (coupons)</t>
         </is>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="41">
         <f>SUM(G36:G85)</f>
         <v/>
       </c>
@@ -6391,7 +7339,7 @@
         <f>Bootstrap!B23</f>
         <v/>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="33">
         <f>Bootstrap!H23</f>
         <v/>
       </c>
@@ -6402,11 +7350,11 @@
           <t>Float leg PV</t>
         </is>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="41">
         <f>B6*(B19-B20)</f>
         <v/>
       </c>
-      <c r="C23" s="32" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
         </is>
@@ -6415,7 +7363,7 @@
         <f>Bootstrap!B24</f>
         <v/>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="33">
         <f>Bootstrap!H24</f>
         <v/>
       </c>
@@ -6426,11 +7374,11 @@
           <t>Notional PV @ maturity</t>
         </is>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="41">
         <f>B6*B20</f>
         <v/>
       </c>
-      <c r="C24" s="32" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>For the SWPM-style leg display only.</t>
         </is>
@@ -6439,7 +7387,7 @@
         <f>Bootstrap!B25</f>
         <v/>
       </c>
-      <c r="L24" s="34">
+      <c r="L24" s="33">
         <f>Bootstrap!H25</f>
         <v/>
       </c>
@@ -6450,11 +7398,11 @@
           <t>Par coupon (%)</t>
         </is>
       </c>
-      <c r="B25" s="39">
+      <c r="B25" s="32">
         <f>(B19-B20)/B21*100</f>
         <v/>
       </c>
-      <c r="C25" s="32" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
         </is>
@@ -6463,7 +7411,7 @@
         <f>Bootstrap!B26</f>
         <v/>
       </c>
-      <c r="L25" s="34">
+      <c r="L25" s="33">
         <f>Bootstrap!H26</f>
         <v/>
       </c>
@@ -6474,11 +7422,11 @@
           <t>Leg 1 NPV  (fixed + notional)</t>
         </is>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="41">
         <f>B16*(B22+B24)</f>
         <v/>
       </c>
-      <c r="C26" s="32" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>SWPM shows each leg incl. a notional redemption.</t>
         </is>
@@ -6487,7 +7435,7 @@
         <f>Bootstrap!B27</f>
         <v/>
       </c>
-      <c r="L26" s="34">
+      <c r="L26" s="33">
         <f>Bootstrap!H27</f>
         <v/>
       </c>
@@ -6498,7 +7446,7 @@
           <t>Leg 2 NPV  (float + notional)</t>
         </is>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="41">
         <f>-B16*(B23+B24)</f>
         <v/>
       </c>
@@ -6506,7 +7454,7 @@
         <f>Bootstrap!B28</f>
         <v/>
       </c>
-      <c r="L27" s="34">
+      <c r="L27" s="33">
         <f>Bootstrap!H28</f>
         <v/>
       </c>
@@ -6517,11 +7465,11 @@
           <t>Net swap NPV</t>
         </is>
       </c>
-      <c r="B28" s="41">
+      <c r="B28" s="42">
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="32" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
         </is>
@@ -6530,7 +7478,7 @@
         <f>Bootstrap!B29</f>
         <v/>
       </c>
-      <c r="L28" s="34">
+      <c r="L28" s="33">
         <f>Bootstrap!H29</f>
         <v/>
       </c>
@@ -6541,11 +7489,11 @@
           <t>PV01 / DV01  (per 1bp)</t>
         </is>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="41">
         <f>B6*B21*0.0001</f>
         <v/>
       </c>
-      <c r="C29" s="32" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>Annuity × notional × 1bp.</t>
         </is>
@@ -6554,7 +7502,7 @@
         <f>Bootstrap!B30</f>
         <v/>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="33">
         <f>Bootstrap!H30</f>
         <v/>
       </c>
@@ -6565,14 +7513,14 @@
           <t>Accrued (at inception)</t>
         </is>
       </c>
-      <c r="B30" s="40" t="n">
+      <c r="B30" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="17">
         <f>Bootstrap!B31</f>
         <v/>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="33">
         <f>Bootstrap!H31</f>
         <v/>
       </c>
@@ -6582,7 +7530,7 @@
         <f>Bootstrap!B32</f>
         <v/>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="33">
         <f>Bootstrap!H32</f>
         <v/>
       </c>
@@ -6597,7 +7545,7 @@
         <f>Bootstrap!B33</f>
         <v/>
       </c>
-      <c r="L32" s="34">
+      <c r="L32" s="33">
         <f>Bootstrap!H33</f>
         <v/>
       </c>
@@ -6607,7 +7555,7 @@
         <f>Bootstrap!B34</f>
         <v/>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="33">
         <f>Bootstrap!H34</f>
         <v/>
       </c>
@@ -6617,7 +7565,7 @@
         <f>Bootstrap!B35</f>
         <v/>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <f>Bootstrap!H35</f>
         <v/>
       </c>
@@ -6667,13 +7615,13 @@
         <f>Bootstrap!B36</f>
         <v/>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="33">
         <f>Bootstrap!H36</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38">
+      <c r="A36" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6689,19 +7637,19 @@
         <f>IF(A36&lt;=$B$9,(B36-C36)/360,"")</f>
         <v/>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="33">
         <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)))^((B36-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F36" s="40">
+      <c r="F36" s="41">
         <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
         <v/>
       </c>
-      <c r="G36" s="40">
+      <c r="G36" s="41">
         <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
         <v/>
       </c>
-      <c r="H36" s="39">
+      <c r="H36" s="32">
         <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
         <v/>
       </c>
@@ -6709,13 +7657,13 @@
         <f>Bootstrap!B37</f>
         <v/>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="33">
         <f>Bootstrap!H37</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="38">
+      <c r="A37" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6731,19 +7679,19 @@
         <f>IF(A37&lt;=$B$9,(B37-C37)/360,"")</f>
         <v/>
       </c>
-      <c r="E37" s="34">
+      <c r="E37" s="33">
         <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)))^((B37-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F37" s="40">
+      <c r="F37" s="41">
         <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
         <v/>
       </c>
-      <c r="G37" s="40">
+      <c r="G37" s="41">
         <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
         <v/>
       </c>
-      <c r="H37" s="39">
+      <c r="H37" s="32">
         <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
         <v/>
       </c>
@@ -6751,13 +7699,13 @@
         <f>Bootstrap!B38</f>
         <v/>
       </c>
-      <c r="L37" s="34">
+      <c r="L37" s="33">
         <f>Bootstrap!H38</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="38">
+      <c r="A38" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6773,19 +7721,19 @@
         <f>IF(A38&lt;=$B$9,(B38-C38)/360,"")</f>
         <v/>
       </c>
-      <c r="E38" s="34">
+      <c r="E38" s="33">
         <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)))^((B38-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="41">
         <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
         <v/>
       </c>
-      <c r="G38" s="40">
+      <c r="G38" s="41">
         <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
         <v/>
       </c>
-      <c r="H38" s="39">
+      <c r="H38" s="32">
         <f>IF(A38&lt;=$B$9,D38*E38,"")</f>
         <v/>
       </c>
@@ -6793,13 +7741,13 @@
         <f>Bootstrap!B39</f>
         <v/>
       </c>
-      <c r="L38" s="34">
+      <c r="L38" s="33">
         <f>Bootstrap!H39</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="38">
+      <c r="A39" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6815,19 +7763,19 @@
         <f>IF(A39&lt;=$B$9,(B39-C39)/360,"")</f>
         <v/>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="33">
         <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)))^((B39-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F39" s="40">
+      <c r="F39" s="41">
         <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
         <v/>
       </c>
-      <c r="G39" s="40">
+      <c r="G39" s="41">
         <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
         <v/>
       </c>
-      <c r="H39" s="39">
+      <c r="H39" s="32">
         <f>IF(A39&lt;=$B$9,D39*E39,"")</f>
         <v/>
       </c>
@@ -6838,7 +7786,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="38">
+      <c r="A40" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6854,25 +7802,25 @@
         <f>IF(A40&lt;=$B$9,(B40-C40)/360,"")</f>
         <v/>
       </c>
-      <c r="E40" s="34">
+      <c r="E40" s="33">
         <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)))^((B40-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F40" s="40">
+      <c r="F40" s="41">
         <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
         <v/>
       </c>
-      <c r="G40" s="40">
+      <c r="G40" s="41">
         <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
         <v/>
       </c>
-      <c r="H40" s="39">
+      <c r="H40" s="32">
         <f>IF(A40&lt;=$B$9,D40*E40,"")</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="38">
+      <c r="A41" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6888,25 +7836,25 @@
         <f>IF(A41&lt;=$B$9,(B41-C41)/360,"")</f>
         <v/>
       </c>
-      <c r="E41" s="34">
+      <c r="E41" s="33">
         <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)))^((B41-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="41">
         <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
         <v/>
       </c>
-      <c r="G41" s="40">
+      <c r="G41" s="41">
         <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
         <v/>
       </c>
-      <c r="H41" s="39">
+      <c r="H41" s="32">
         <f>IF(A41&lt;=$B$9,D41*E41,"")</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="38">
+      <c r="A42" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6922,25 +7870,25 @@
         <f>IF(A42&lt;=$B$9,(B42-C42)/360,"")</f>
         <v/>
       </c>
-      <c r="E42" s="34">
+      <c r="E42" s="33">
         <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)))^((B42-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="41">
         <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
         <v/>
       </c>
-      <c r="G42" s="40">
+      <c r="G42" s="41">
         <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
         <v/>
       </c>
-      <c r="H42" s="39">
+      <c r="H42" s="32">
         <f>IF(A42&lt;=$B$9,D42*E42,"")</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="38">
+      <c r="A43" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6956,25 +7904,25 @@
         <f>IF(A43&lt;=$B$9,(B43-C43)/360,"")</f>
         <v/>
       </c>
-      <c r="E43" s="34">
+      <c r="E43" s="33">
         <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)))^((B43-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="41">
         <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
         <v/>
       </c>
-      <c r="G43" s="40">
+      <c r="G43" s="41">
         <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
         <v/>
       </c>
-      <c r="H43" s="39">
+      <c r="H43" s="32">
         <f>IF(A43&lt;=$B$9,D43*E43,"")</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="38">
+      <c r="A44" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -6990,25 +7938,25 @@
         <f>IF(A44&lt;=$B$9,(B44-C44)/360,"")</f>
         <v/>
       </c>
-      <c r="E44" s="34">
+      <c r="E44" s="33">
         <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)))^((B44-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F44" s="40">
+      <c r="F44" s="41">
         <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
         <v/>
       </c>
-      <c r="G44" s="40">
+      <c r="G44" s="41">
         <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
         <v/>
       </c>
-      <c r="H44" s="39">
+      <c r="H44" s="32">
         <f>IF(A44&lt;=$B$9,D44*E44,"")</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="38">
+      <c r="A45" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7024,25 +7972,25 @@
         <f>IF(A45&lt;=$B$9,(B45-C45)/360,"")</f>
         <v/>
       </c>
-      <c r="E45" s="34">
+      <c r="E45" s="33">
         <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)))^((B45-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F45" s="40">
+      <c r="F45" s="41">
         <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
         <v/>
       </c>
-      <c r="G45" s="40">
+      <c r="G45" s="41">
         <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
         <v/>
       </c>
-      <c r="H45" s="39">
+      <c r="H45" s="32">
         <f>IF(A45&lt;=$B$9,D45*E45,"")</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="38">
+      <c r="A46" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7058,25 +8006,25 @@
         <f>IF(A46&lt;=$B$9,(B46-C46)/360,"")</f>
         <v/>
       </c>
-      <c r="E46" s="34">
+      <c r="E46" s="33">
         <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)))^((B46-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F46" s="40">
+      <c r="F46" s="41">
         <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
         <v/>
       </c>
-      <c r="G46" s="40">
+      <c r="G46" s="41">
         <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
         <v/>
       </c>
-      <c r="H46" s="39">
+      <c r="H46" s="32">
         <f>IF(A46&lt;=$B$9,D46*E46,"")</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="38">
+      <c r="A47" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7092,25 +8040,25 @@
         <f>IF(A47&lt;=$B$9,(B47-C47)/360,"")</f>
         <v/>
       </c>
-      <c r="E47" s="34">
+      <c r="E47" s="33">
         <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)))^((B47-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F47" s="40">
+      <c r="F47" s="41">
         <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
         <v/>
       </c>
-      <c r="G47" s="40">
+      <c r="G47" s="41">
         <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
         <v/>
       </c>
-      <c r="H47" s="39">
+      <c r="H47" s="32">
         <f>IF(A47&lt;=$B$9,D47*E47,"")</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="38">
+      <c r="A48" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7126,25 +8074,25 @@
         <f>IF(A48&lt;=$B$9,(B48-C48)/360,"")</f>
         <v/>
       </c>
-      <c r="E48" s="34">
+      <c r="E48" s="33">
         <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)))^((B48-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F48" s="40">
+      <c r="F48" s="41">
         <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
         <v/>
       </c>
-      <c r="G48" s="40">
+      <c r="G48" s="41">
         <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
         <v/>
       </c>
-      <c r="H48" s="39">
+      <c r="H48" s="32">
         <f>IF(A48&lt;=$B$9,D48*E48,"")</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="38">
+      <c r="A49" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7160,25 +8108,25 @@
         <f>IF(A49&lt;=$B$9,(B49-C49)/360,"")</f>
         <v/>
       </c>
-      <c r="E49" s="34">
+      <c r="E49" s="33">
         <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)))^((B49-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="40">
+      <c r="F49" s="41">
         <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
         <v/>
       </c>
-      <c r="G49" s="40">
+      <c r="G49" s="41">
         <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
         <v/>
       </c>
-      <c r="H49" s="39">
+      <c r="H49" s="32">
         <f>IF(A49&lt;=$B$9,D49*E49,"")</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="38">
+      <c r="A50" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7194,25 +8142,25 @@
         <f>IF(A50&lt;=$B$9,(B50-C50)/360,"")</f>
         <v/>
       </c>
-      <c r="E50" s="34">
+      <c r="E50" s="33">
         <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)))^((B50-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F50" s="40">
+      <c r="F50" s="41">
         <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
         <v/>
       </c>
-      <c r="G50" s="40">
+      <c r="G50" s="41">
         <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
         <v/>
       </c>
-      <c r="H50" s="39">
+      <c r="H50" s="32">
         <f>IF(A50&lt;=$B$9,D50*E50,"")</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="38">
+      <c r="A51" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7228,25 +8176,25 @@
         <f>IF(A51&lt;=$B$9,(B51-C51)/360,"")</f>
         <v/>
       </c>
-      <c r="E51" s="34">
+      <c r="E51" s="33">
         <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)))^((B51-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F51" s="40">
+      <c r="F51" s="41">
         <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
         <v/>
       </c>
-      <c r="G51" s="40">
+      <c r="G51" s="41">
         <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
         <v/>
       </c>
-      <c r="H51" s="39">
+      <c r="H51" s="32">
         <f>IF(A51&lt;=$B$9,D51*E51,"")</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="38">
+      <c r="A52" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7262,25 +8210,25 @@
         <f>IF(A52&lt;=$B$9,(B52-C52)/360,"")</f>
         <v/>
       </c>
-      <c r="E52" s="34">
+      <c r="E52" s="33">
         <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)))^((B52-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F52" s="40">
+      <c r="F52" s="41">
         <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
         <v/>
       </c>
-      <c r="G52" s="40">
+      <c r="G52" s="41">
         <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
         <v/>
       </c>
-      <c r="H52" s="39">
+      <c r="H52" s="32">
         <f>IF(A52&lt;=$B$9,D52*E52,"")</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="38">
+      <c r="A53" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7296,25 +8244,25 @@
         <f>IF(A53&lt;=$B$9,(B53-C53)/360,"")</f>
         <v/>
       </c>
-      <c r="E53" s="34">
+      <c r="E53" s="33">
         <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)))^((B53-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F53" s="40">
+      <c r="F53" s="41">
         <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
         <v/>
       </c>
-      <c r="G53" s="40">
+      <c r="G53" s="41">
         <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
         <v/>
       </c>
-      <c r="H53" s="39">
+      <c r="H53" s="32">
         <f>IF(A53&lt;=$B$9,D53*E53,"")</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="38">
+      <c r="A54" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7330,25 +8278,25 @@
         <f>IF(A54&lt;=$B$9,(B54-C54)/360,"")</f>
         <v/>
       </c>
-      <c r="E54" s="34">
+      <c r="E54" s="33">
         <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)))^((B54-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F54" s="40">
+      <c r="F54" s="41">
         <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
         <v/>
       </c>
-      <c r="G54" s="40">
+      <c r="G54" s="41">
         <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
         <v/>
       </c>
-      <c r="H54" s="39">
+      <c r="H54" s="32">
         <f>IF(A54&lt;=$B$9,D54*E54,"")</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="38">
+      <c r="A55" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7364,25 +8312,25 @@
         <f>IF(A55&lt;=$B$9,(B55-C55)/360,"")</f>
         <v/>
       </c>
-      <c r="E55" s="34">
+      <c r="E55" s="33">
         <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)))^((B55-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F55" s="40">
+      <c r="F55" s="41">
         <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
         <v/>
       </c>
-      <c r="G55" s="40">
+      <c r="G55" s="41">
         <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
         <v/>
       </c>
-      <c r="H55" s="39">
+      <c r="H55" s="32">
         <f>IF(A55&lt;=$B$9,D55*E55,"")</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="38">
+      <c r="A56" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7398,25 +8346,25 @@
         <f>IF(A56&lt;=$B$9,(B56-C56)/360,"")</f>
         <v/>
       </c>
-      <c r="E56" s="34">
+      <c r="E56" s="33">
         <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)))^((B56-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F56" s="40">
+      <c r="F56" s="41">
         <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
         <v/>
       </c>
-      <c r="G56" s="40">
+      <c r="G56" s="41">
         <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
         <v/>
       </c>
-      <c r="H56" s="39">
+      <c r="H56" s="32">
         <f>IF(A56&lt;=$B$9,D56*E56,"")</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="38">
+      <c r="A57" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7432,25 +8380,25 @@
         <f>IF(A57&lt;=$B$9,(B57-C57)/360,"")</f>
         <v/>
       </c>
-      <c r="E57" s="34">
+      <c r="E57" s="33">
         <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)))^((B57-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F57" s="40">
+      <c r="F57" s="41">
         <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
         <v/>
       </c>
-      <c r="G57" s="40">
+      <c r="G57" s="41">
         <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
         <v/>
       </c>
-      <c r="H57" s="39">
+      <c r="H57" s="32">
         <f>IF(A57&lt;=$B$9,D57*E57,"")</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="38">
+      <c r="A58" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7466,25 +8414,25 @@
         <f>IF(A58&lt;=$B$9,(B58-C58)/360,"")</f>
         <v/>
       </c>
-      <c r="E58" s="34">
+      <c r="E58" s="33">
         <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)))^((B58-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F58" s="40">
+      <c r="F58" s="41">
         <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
         <v/>
       </c>
-      <c r="G58" s="40">
+      <c r="G58" s="41">
         <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
         <v/>
       </c>
-      <c r="H58" s="39">
+      <c r="H58" s="32">
         <f>IF(A58&lt;=$B$9,D58*E58,"")</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="38">
+      <c r="A59" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7500,25 +8448,25 @@
         <f>IF(A59&lt;=$B$9,(B59-C59)/360,"")</f>
         <v/>
       </c>
-      <c r="E59" s="34">
+      <c r="E59" s="33">
         <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)))^((B59-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F59" s="40">
+      <c r="F59" s="41">
         <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
         <v/>
       </c>
-      <c r="G59" s="40">
+      <c r="G59" s="41">
         <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
         <v/>
       </c>
-      <c r="H59" s="39">
+      <c r="H59" s="32">
         <f>IF(A59&lt;=$B$9,D59*E59,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="38">
+      <c r="A60" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7534,25 +8482,25 @@
         <f>IF(A60&lt;=$B$9,(B60-C60)/360,"")</f>
         <v/>
       </c>
-      <c r="E60" s="34">
+      <c r="E60" s="33">
         <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)))^((B60-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F60" s="40">
+      <c r="F60" s="41">
         <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
         <v/>
       </c>
-      <c r="G60" s="40">
+      <c r="G60" s="41">
         <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
         <v/>
       </c>
-      <c r="H60" s="39">
+      <c r="H60" s="32">
         <f>IF(A60&lt;=$B$9,D60*E60,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="38">
+      <c r="A61" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7568,25 +8516,25 @@
         <f>IF(A61&lt;=$B$9,(B61-C61)/360,"")</f>
         <v/>
       </c>
-      <c r="E61" s="34">
+      <c r="E61" s="33">
         <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)))^((B61-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F61" s="40">
+      <c r="F61" s="41">
         <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
         <v/>
       </c>
-      <c r="G61" s="40">
+      <c r="G61" s="41">
         <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
         <v/>
       </c>
-      <c r="H61" s="39">
+      <c r="H61" s="32">
         <f>IF(A61&lt;=$B$9,D61*E61,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="38">
+      <c r="A62" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7602,25 +8550,25 @@
         <f>IF(A62&lt;=$B$9,(B62-C62)/360,"")</f>
         <v/>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="33">
         <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)))^((B62-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F62" s="40">
+      <c r="F62" s="41">
         <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
         <v/>
       </c>
-      <c r="G62" s="40">
+      <c r="G62" s="41">
         <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
         <v/>
       </c>
-      <c r="H62" s="39">
+      <c r="H62" s="32">
         <f>IF(A62&lt;=$B$9,D62*E62,"")</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="38">
+      <c r="A63" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7636,25 +8584,25 @@
         <f>IF(A63&lt;=$B$9,(B63-C63)/360,"")</f>
         <v/>
       </c>
-      <c r="E63" s="34">
+      <c r="E63" s="33">
         <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)))^((B63-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F63" s="40">
+      <c r="F63" s="41">
         <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
         <v/>
       </c>
-      <c r="G63" s="40">
+      <c r="G63" s="41">
         <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
         <v/>
       </c>
-      <c r="H63" s="39">
+      <c r="H63" s="32">
         <f>IF(A63&lt;=$B$9,D63*E63,"")</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="38">
+      <c r="A64" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7670,25 +8618,25 @@
         <f>IF(A64&lt;=$B$9,(B64-C64)/360,"")</f>
         <v/>
       </c>
-      <c r="E64" s="34">
+      <c r="E64" s="33">
         <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)))^((B64-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F64" s="40">
+      <c r="F64" s="41">
         <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
         <v/>
       </c>
-      <c r="G64" s="40">
+      <c r="G64" s="41">
         <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
         <v/>
       </c>
-      <c r="H64" s="39">
+      <c r="H64" s="32">
         <f>IF(A64&lt;=$B$9,D64*E64,"")</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="38">
+      <c r="A65" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7704,25 +8652,25 @@
         <f>IF(A65&lt;=$B$9,(B65-C65)/360,"")</f>
         <v/>
       </c>
-      <c r="E65" s="34">
+      <c r="E65" s="33">
         <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)))^((B65-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F65" s="40">
+      <c r="F65" s="41">
         <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
         <v/>
       </c>
-      <c r="G65" s="40">
+      <c r="G65" s="41">
         <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
         <v/>
       </c>
-      <c r="H65" s="39">
+      <c r="H65" s="32">
         <f>IF(A65&lt;=$B$9,D65*E65,"")</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="38">
+      <c r="A66" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7738,25 +8686,25 @@
         <f>IF(A66&lt;=$B$9,(B66-C66)/360,"")</f>
         <v/>
       </c>
-      <c r="E66" s="34">
+      <c r="E66" s="33">
         <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)))^((B66-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F66" s="40">
+      <c r="F66" s="41">
         <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
         <v/>
       </c>
-      <c r="G66" s="40">
+      <c r="G66" s="41">
         <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
         <v/>
       </c>
-      <c r="H66" s="39">
+      <c r="H66" s="32">
         <f>IF(A66&lt;=$B$9,D66*E66,"")</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="38">
+      <c r="A67" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7772,25 +8720,25 @@
         <f>IF(A67&lt;=$B$9,(B67-C67)/360,"")</f>
         <v/>
       </c>
-      <c r="E67" s="34">
+      <c r="E67" s="33">
         <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)))^((B67-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F67" s="40">
+      <c r="F67" s="41">
         <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
         <v/>
       </c>
-      <c r="G67" s="40">
+      <c r="G67" s="41">
         <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
         <v/>
       </c>
-      <c r="H67" s="39">
+      <c r="H67" s="32">
         <f>IF(A67&lt;=$B$9,D67*E67,"")</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="38">
+      <c r="A68" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7806,25 +8754,25 @@
         <f>IF(A68&lt;=$B$9,(B68-C68)/360,"")</f>
         <v/>
       </c>
-      <c r="E68" s="34">
+      <c r="E68" s="33">
         <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)))^((B68-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F68" s="40">
+      <c r="F68" s="41">
         <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
         <v/>
       </c>
-      <c r="G68" s="40">
+      <c r="G68" s="41">
         <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
         <v/>
       </c>
-      <c r="H68" s="39">
+      <c r="H68" s="32">
         <f>IF(A68&lt;=$B$9,D68*E68,"")</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="38">
+      <c r="A69" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7840,25 +8788,25 @@
         <f>IF(A69&lt;=$B$9,(B69-C69)/360,"")</f>
         <v/>
       </c>
-      <c r="E69" s="34">
+      <c r="E69" s="33">
         <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)))^((B69-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F69" s="40">
+      <c r="F69" s="41">
         <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
         <v/>
       </c>
-      <c r="G69" s="40">
+      <c r="G69" s="41">
         <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
         <v/>
       </c>
-      <c r="H69" s="39">
+      <c r="H69" s="32">
         <f>IF(A69&lt;=$B$9,D69*E69,"")</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="38">
+      <c r="A70" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7874,25 +8822,25 @@
         <f>IF(A70&lt;=$B$9,(B70-C70)/360,"")</f>
         <v/>
       </c>
-      <c r="E70" s="34">
+      <c r="E70" s="33">
         <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)))^((B70-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F70" s="40">
+      <c r="F70" s="41">
         <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
         <v/>
       </c>
-      <c r="G70" s="40">
+      <c r="G70" s="41">
         <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
         <v/>
       </c>
-      <c r="H70" s="39">
+      <c r="H70" s="32">
         <f>IF(A70&lt;=$B$9,D70*E70,"")</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="38">
+      <c r="A71" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7908,25 +8856,25 @@
         <f>IF(A71&lt;=$B$9,(B71-C71)/360,"")</f>
         <v/>
       </c>
-      <c r="E71" s="34">
+      <c r="E71" s="33">
         <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)))^((B71-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F71" s="40">
+      <c r="F71" s="41">
         <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
         <v/>
       </c>
-      <c r="G71" s="40">
+      <c r="G71" s="41">
         <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
         <v/>
       </c>
-      <c r="H71" s="39">
+      <c r="H71" s="32">
         <f>IF(A71&lt;=$B$9,D71*E71,"")</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="38">
+      <c r="A72" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7942,25 +8890,25 @@
         <f>IF(A72&lt;=$B$9,(B72-C72)/360,"")</f>
         <v/>
       </c>
-      <c r="E72" s="34">
+      <c r="E72" s="33">
         <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)))^((B72-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F72" s="40">
+      <c r="F72" s="41">
         <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
         <v/>
       </c>
-      <c r="G72" s="40">
+      <c r="G72" s="41">
         <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
         <v/>
       </c>
-      <c r="H72" s="39">
+      <c r="H72" s="32">
         <f>IF(A72&lt;=$B$9,D72*E72,"")</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="38">
+      <c r="A73" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -7976,25 +8924,25 @@
         <f>IF(A73&lt;=$B$9,(B73-C73)/360,"")</f>
         <v/>
       </c>
-      <c r="E73" s="34">
+      <c r="E73" s="33">
         <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)))^((B73-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F73" s="40">
+      <c r="F73" s="41">
         <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
         <v/>
       </c>
-      <c r="G73" s="40">
+      <c r="G73" s="41">
         <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
         <v/>
       </c>
-      <c r="H73" s="39">
+      <c r="H73" s="32">
         <f>IF(A73&lt;=$B$9,D73*E73,"")</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="38">
+      <c r="A74" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8010,25 +8958,25 @@
         <f>IF(A74&lt;=$B$9,(B74-C74)/360,"")</f>
         <v/>
       </c>
-      <c r="E74" s="34">
+      <c r="E74" s="33">
         <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)))^((B74-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F74" s="40">
+      <c r="F74" s="41">
         <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
         <v/>
       </c>
-      <c r="G74" s="40">
+      <c r="G74" s="41">
         <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
         <v/>
       </c>
-      <c r="H74" s="39">
+      <c r="H74" s="32">
         <f>IF(A74&lt;=$B$9,D74*E74,"")</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="38">
+      <c r="A75" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8044,25 +8992,25 @@
         <f>IF(A75&lt;=$B$9,(B75-C75)/360,"")</f>
         <v/>
       </c>
-      <c r="E75" s="34">
+      <c r="E75" s="33">
         <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)))^((B75-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F75" s="40">
+      <c r="F75" s="41">
         <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
         <v/>
       </c>
-      <c r="G75" s="40">
+      <c r="G75" s="41">
         <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
         <v/>
       </c>
-      <c r="H75" s="39">
+      <c r="H75" s="32">
         <f>IF(A75&lt;=$B$9,D75*E75,"")</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="38">
+      <c r="A76" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8078,25 +9026,25 @@
         <f>IF(A76&lt;=$B$9,(B76-C76)/360,"")</f>
         <v/>
       </c>
-      <c r="E76" s="34">
+      <c r="E76" s="33">
         <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)))^((B76-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F76" s="40">
+      <c r="F76" s="41">
         <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
         <v/>
       </c>
-      <c r="G76" s="40">
+      <c r="G76" s="41">
         <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
         <v/>
       </c>
-      <c r="H76" s="39">
+      <c r="H76" s="32">
         <f>IF(A76&lt;=$B$9,D76*E76,"")</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="38">
+      <c r="A77" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8112,25 +9060,25 @@
         <f>IF(A77&lt;=$B$9,(B77-C77)/360,"")</f>
         <v/>
       </c>
-      <c r="E77" s="34">
+      <c r="E77" s="33">
         <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)))^((B77-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F77" s="40">
+      <c r="F77" s="41">
         <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
         <v/>
       </c>
-      <c r="G77" s="40">
+      <c r="G77" s="41">
         <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
         <v/>
       </c>
-      <c r="H77" s="39">
+      <c r="H77" s="32">
         <f>IF(A77&lt;=$B$9,D77*E77,"")</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="38">
+      <c r="A78" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8146,25 +9094,25 @@
         <f>IF(A78&lt;=$B$9,(B78-C78)/360,"")</f>
         <v/>
       </c>
-      <c r="E78" s="34">
+      <c r="E78" s="33">
         <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)))^((B78-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F78" s="40">
+      <c r="F78" s="41">
         <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
         <v/>
       </c>
-      <c r="G78" s="40">
+      <c r="G78" s="41">
         <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
         <v/>
       </c>
-      <c r="H78" s="39">
+      <c r="H78" s="32">
         <f>IF(A78&lt;=$B$9,D78*E78,"")</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="38">
+      <c r="A79" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8180,25 +9128,25 @@
         <f>IF(A79&lt;=$B$9,(B79-C79)/360,"")</f>
         <v/>
       </c>
-      <c r="E79" s="34">
+      <c r="E79" s="33">
         <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)))^((B79-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F79" s="40">
+      <c r="F79" s="41">
         <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
         <v/>
       </c>
-      <c r="G79" s="40">
+      <c r="G79" s="41">
         <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
         <v/>
       </c>
-      <c r="H79" s="39">
+      <c r="H79" s="32">
         <f>IF(A79&lt;=$B$9,D79*E79,"")</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="38">
+      <c r="A80" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8214,25 +9162,25 @@
         <f>IF(A80&lt;=$B$9,(B80-C80)/360,"")</f>
         <v/>
       </c>
-      <c r="E80" s="34">
+      <c r="E80" s="33">
         <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)))^((B80-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F80" s="40">
+      <c r="F80" s="41">
         <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
         <v/>
       </c>
-      <c r="G80" s="40">
+      <c r="G80" s="41">
         <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
         <v/>
       </c>
-      <c r="H80" s="39">
+      <c r="H80" s="32">
         <f>IF(A80&lt;=$B$9,D80*E80,"")</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="38">
+      <c r="A81" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8248,25 +9196,25 @@
         <f>IF(A81&lt;=$B$9,(B81-C81)/360,"")</f>
         <v/>
       </c>
-      <c r="E81" s="34">
+      <c r="E81" s="33">
         <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)))^((B81-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F81" s="40">
+      <c r="F81" s="41">
         <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
         <v/>
       </c>
-      <c r="G81" s="40">
+      <c r="G81" s="41">
         <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
         <v/>
       </c>
-      <c r="H81" s="39">
+      <c r="H81" s="32">
         <f>IF(A81&lt;=$B$9,D81*E81,"")</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="38">
+      <c r="A82" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8282,25 +9230,25 @@
         <f>IF(A82&lt;=$B$9,(B82-C82)/360,"")</f>
         <v/>
       </c>
-      <c r="E82" s="34">
+      <c r="E82" s="33">
         <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)))^((B82-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F82" s="40">
+      <c r="F82" s="41">
         <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
         <v/>
       </c>
-      <c r="G82" s="40">
+      <c r="G82" s="41">
         <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
         <v/>
       </c>
-      <c r="H82" s="39">
+      <c r="H82" s="32">
         <f>IF(A82&lt;=$B$9,D82*E82,"")</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="38">
+      <c r="A83" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8316,25 +9264,25 @@
         <f>IF(A83&lt;=$B$9,(B83-C83)/360,"")</f>
         <v/>
       </c>
-      <c r="E83" s="34">
+      <c r="E83" s="33">
         <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)))^((B83-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F83" s="40">
+      <c r="F83" s="41">
         <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
         <v/>
       </c>
-      <c r="G83" s="40">
+      <c r="G83" s="41">
         <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
         <v/>
       </c>
-      <c r="H83" s="39">
+      <c r="H83" s="32">
         <f>IF(A83&lt;=$B$9,D83*E83,"")</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="38">
+      <c r="A84" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8350,25 +9298,25 @@
         <f>IF(A84&lt;=$B$9,(B84-C84)/360,"")</f>
         <v/>
       </c>
-      <c r="E84" s="34">
+      <c r="E84" s="33">
         <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)))^((B84-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F84" s="40">
+      <c r="F84" s="41">
         <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
         <v/>
       </c>
-      <c r="G84" s="40">
+      <c r="G84" s="41">
         <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
         <v/>
       </c>
-      <c r="H84" s="39">
+      <c r="H84" s="32">
         <f>IF(A84&lt;=$B$9,D84*E84,"")</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="38">
+      <c r="A85" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -8384,19 +9332,19 @@
         <f>IF(A85&lt;=$B$9,(B85-C85)/360,"")</f>
         <v/>
       </c>
-      <c r="E85" s="34">
+      <c r="E85" s="33">
         <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)))^((B85-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F85" s="40">
+      <c r="F85" s="41">
         <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
         <v/>
       </c>
-      <c r="G85" s="40">
+      <c r="G85" s="41">
         <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
         <v/>
       </c>
-      <c r="H85" s="39">
+      <c r="H85" s="32">
         <f>IF(A85&lt;=$B$9,D85*E85,"")</f>
         <v/>
       </c>
@@ -8477,7 +9425,7 @@
           <t>Curve date</t>
         </is>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="43">
         <f>VAL_DATE</f>
         <v/>
       </c>
@@ -9418,7 +10366,7 @@
           <t>Reference index</t>
         </is>
       </c>
-      <c r="B22" s="43" t="inlineStr">
+      <c r="B22" s="44" t="inlineStr">
         <is>
           <t>USD-SOFR (compounded in arrears)</t>
         </is>
@@ -9434,7 +10382,7 @@
           <t>Spot / settlement lag</t>
         </is>
       </c>
-      <c r="B23" s="43" t="inlineStr">
+      <c r="B23" s="44" t="inlineStr">
         <is>
           <t>T+2 US business days</t>
         </is>
@@ -9450,7 +10398,7 @@
           <t>Effective date rule</t>
         </is>
       </c>
-      <c r="B24" s="43" t="inlineStr">
+      <c r="B24" s="44" t="inlineStr">
         <is>
           <t>Spot (T+2), modified following</t>
         </is>
@@ -9466,7 +10414,7 @@
           <t>Maturity date rule</t>
         </is>
       </c>
-      <c r="B25" s="43" t="inlineStr">
+      <c r="B25" s="44" t="inlineStr">
         <is>
           <t>Effective + tenor, modified following</t>
         </is>
@@ -9482,7 +10430,7 @@
           <t>Business-day convention</t>
         </is>
       </c>
-      <c r="B26" s="43" t="inlineStr">
+      <c r="B26" s="44" t="inlineStr">
         <is>
           <t>Modified Following</t>
         </is>
@@ -9498,7 +10446,7 @@
           <t>Fixed-leg day count</t>
         </is>
       </c>
-      <c r="B27" s="43" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
@@ -9514,7 +10462,7 @@
           <t>Fixed-leg pay frequency</t>
         </is>
       </c>
-      <c r="B28" s="43" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
@@ -9530,7 +10478,7 @@
           <t>Floating-leg day count</t>
         </is>
       </c>
-      <c r="B29" s="43" t="inlineStr">
+      <c r="B29" s="44" t="inlineStr">
         <is>
           <t>ACT/360</t>
         </is>
@@ -9546,7 +10494,7 @@
           <t>Floating-leg pay frequency</t>
         </is>
       </c>
-      <c r="B30" s="43" t="inlineStr">
+      <c r="B30" s="44" t="inlineStr">
         <is>
           <t>Annual  (single payment if tenor ≤ 1Y)</t>
         </is>
@@ -9562,7 +10510,7 @@
           <t>SOFR compounding method</t>
         </is>
       </c>
-      <c r="B31" s="43" t="inlineStr">
+      <c r="B31" s="44" t="inlineStr">
         <is>
           <t>Daily compounded, ACT/360</t>
         </is>
@@ -9578,7 +10526,7 @@
           <t>Payment lag</t>
         </is>
       </c>
-      <c r="B32" s="43" t="inlineStr">
+      <c r="B32" s="44" t="inlineStr">
         <is>
           <t>2 US business days</t>
         </is>
@@ -9594,7 +10542,7 @@
           <t>Observation shift / lookback</t>
         </is>
       </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="B33" s="44" t="inlineStr">
         <is>
           <t>None (payment-delay convention, 2 bd)</t>
         </is>
@@ -9610,7 +10558,7 @@
           <t>End-of-month treatment</t>
         </is>
       </c>
-      <c r="B34" s="43" t="inlineStr">
+      <c r="B34" s="44" t="inlineStr">
         <is>
           <t>EOM applies</t>
         </is>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -15,6 +15,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -30,12 +31,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
+    <numFmt numFmtId="169" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -130,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,6 +202,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -565,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1032,44 +1039,56 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>7. Fwd_Interp</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>Zhou 2002 forward interpolation: V1 piecewise-flat vs V2 piecewise-quadratic forwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>DO NOT substitute these (wrong instruments):</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="9" t="inlineStr">
-        <is>
-          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="9" t="inlineStr">
         <is>
+          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
           <t>•  Use PX midpoint (bid+ask)/2 for construction; use PX_LAST only where bid/ask are unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="49" ht="28" customHeight="1">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Licensing: Bloomberg data is licensed and entitlement-dependent — do NOT redistribute pulled values or commit them to a public repository. This template ships formulas only, no data. Some static convention fields may return N/A under your entitlement; use FLDS &lt;GO&gt; on the security to find the enabled mnemonic.</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
+    <row r="50"/>
   </sheetData>
-  <mergeCells count="49">
+  <mergeCells count="50">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
@@ -1081,7 +1100,9 @@
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A48:F49"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A49:F50"/>
+    <mergeCell ref="B42:F42"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="A32:F32"/>
     <mergeCell ref="D12:F12"/>
@@ -1090,7 +1111,6 @@
     <mergeCell ref="A35:F35"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D8:F8"/>
-    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="C21:D21"/>
@@ -10596,4 +10616,1737 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fwd_Interp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Zhou 2002 forward interpolation — V1 piecewise-flat vs V2 piecewise-quadratic instantaneous forwards</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Both variants reprice the pillar DFs IDENTICALLY (same segment integral ∫f = −ln(DF_i/DF_(i-1))). V1 (Flat fwd) holds the instantaneous forward CONSTANT over each segment → a step curve; simplest &amp; most stable — Lehman's default. V2 makes the forward piecewise-QUADRATIC f(x)=a+bx+cx², CONTINUOUS across pillars (adjacent segments share the Node fwd) while still repricing exactly. a,b,c are closed-form from (f_left=node at left pillar, f_right=node at right pillar, ∫f) — no solver needed. Node fwd = average of the two adjacent flat forwards. 'reprice check' = ∫quad − ∫f ≈ 0 confirms V2 preserves every DF. The difference is intra-segment: compare Flat fwd (V1) vs V2 fwd @ mid — largest across the wide long-end gaps (10Y→15Y→20Y→30Y), which is exactly what V2 smooths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>Pillar</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>T (yrs)</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>Δ (yrs)</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="inlineStr">
+        <is>
+          <t>∫f (integral)</t>
+        </is>
+      </c>
+      <c r="F7" s="19" t="inlineStr">
+        <is>
+          <t>Flat fwd (V1)</t>
+        </is>
+      </c>
+      <c r="G7" s="19" t="inlineStr">
+        <is>
+          <t>Node fwd</t>
+        </is>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="K7" s="19" t="inlineStr">
+        <is>
+          <t>V2 fwd @ mid</t>
+        </is>
+      </c>
+      <c r="L7" s="19" t="inlineStr">
+        <is>
+          <t>reprice check</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="inlineStr">
+        <is>
+          <t>Spot</t>
+        </is>
+      </c>
+      <c r="B8" s="45" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="47">
+        <f>F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <f>'Bootstrap'!A8</f>
+        <v/>
+      </c>
+      <c r="B9" s="27">
+        <f>'Bootstrap'!C8</f>
+        <v/>
+      </c>
+      <c r="C9" s="33">
+        <f>'Bootstrap'!H8</f>
+        <v/>
+      </c>
+      <c r="D9" s="27">
+        <f>B9-B8</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>-LN(C9/C8)</f>
+        <v/>
+      </c>
+      <c r="F9" s="48">
+        <f>E9/D9</f>
+        <v/>
+      </c>
+      <c r="G9" s="48">
+        <f>(F9+F10)/2</f>
+        <v/>
+      </c>
+      <c r="H9" s="48">
+        <f>G8</f>
+        <v/>
+      </c>
+      <c r="I9" s="32">
+        <f>(G9-G8)/D9-J9*D9</f>
+        <v/>
+      </c>
+      <c r="J9" s="32">
+        <f>3*(G9-G8)/D9^2-6*(E9-G8*D9)/D9^3</f>
+        <v/>
+      </c>
+      <c r="K9" s="48">
+        <f>H9+I9*D9/2+J9*D9^2/4</f>
+        <v/>
+      </c>
+      <c r="L9" s="49">
+        <f>H9*D9+I9*D9^2/2+J9*D9^3/3-E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <f>'Bootstrap'!A9</f>
+        <v/>
+      </c>
+      <c r="B10" s="27">
+        <f>'Bootstrap'!C9</f>
+        <v/>
+      </c>
+      <c r="C10" s="33">
+        <f>'Bootstrap'!H9</f>
+        <v/>
+      </c>
+      <c r="D10" s="27">
+        <f>B10-B9</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>-LN(C10/C9)</f>
+        <v/>
+      </c>
+      <c r="F10" s="48">
+        <f>E10/D10</f>
+        <v/>
+      </c>
+      <c r="G10" s="48">
+        <f>(F10+F11)/2</f>
+        <v/>
+      </c>
+      <c r="H10" s="48">
+        <f>G9</f>
+        <v/>
+      </c>
+      <c r="I10" s="32">
+        <f>(G10-G9)/D10-J10*D10</f>
+        <v/>
+      </c>
+      <c r="J10" s="32">
+        <f>3*(G10-G9)/D10^2-6*(E10-G9*D10)/D10^3</f>
+        <v/>
+      </c>
+      <c r="K10" s="48">
+        <f>H10+I10*D10/2+J10*D10^2/4</f>
+        <v/>
+      </c>
+      <c r="L10" s="49">
+        <f>H10*D10+I10*D10^2/2+J10*D10^3/3-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <f>'Bootstrap'!A10</f>
+        <v/>
+      </c>
+      <c r="B11" s="27">
+        <f>'Bootstrap'!C10</f>
+        <v/>
+      </c>
+      <c r="C11" s="33">
+        <f>'Bootstrap'!H10</f>
+        <v/>
+      </c>
+      <c r="D11" s="27">
+        <f>B11-B10</f>
+        <v/>
+      </c>
+      <c r="E11" s="32">
+        <f>-LN(C11/C10)</f>
+        <v/>
+      </c>
+      <c r="F11" s="48">
+        <f>E11/D11</f>
+        <v/>
+      </c>
+      <c r="G11" s="48">
+        <f>(F11+F12)/2</f>
+        <v/>
+      </c>
+      <c r="H11" s="48">
+        <f>G10</f>
+        <v/>
+      </c>
+      <c r="I11" s="32">
+        <f>(G11-G10)/D11-J11*D11</f>
+        <v/>
+      </c>
+      <c r="J11" s="32">
+        <f>3*(G11-G10)/D11^2-6*(E11-G10*D11)/D11^3</f>
+        <v/>
+      </c>
+      <c r="K11" s="48">
+        <f>H11+I11*D11/2+J11*D11^2/4</f>
+        <v/>
+      </c>
+      <c r="L11" s="49">
+        <f>H11*D11+I11*D11^2/2+J11*D11^3/3-E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6">
+        <f>'Bootstrap'!A11</f>
+        <v/>
+      </c>
+      <c r="B12" s="27">
+        <f>'Bootstrap'!C11</f>
+        <v/>
+      </c>
+      <c r="C12" s="33">
+        <f>'Bootstrap'!H11</f>
+        <v/>
+      </c>
+      <c r="D12" s="27">
+        <f>B12-B11</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>-LN(C12/C11)</f>
+        <v/>
+      </c>
+      <c r="F12" s="48">
+        <f>E12/D12</f>
+        <v/>
+      </c>
+      <c r="G12" s="48">
+        <f>(F12+F13)/2</f>
+        <v/>
+      </c>
+      <c r="H12" s="48">
+        <f>G11</f>
+        <v/>
+      </c>
+      <c r="I12" s="32">
+        <f>(G12-G11)/D12-J12*D12</f>
+        <v/>
+      </c>
+      <c r="J12" s="32">
+        <f>3*(G12-G11)/D12^2-6*(E12-G11*D12)/D12^3</f>
+        <v/>
+      </c>
+      <c r="K12" s="48">
+        <f>H12+I12*D12/2+J12*D12^2/4</f>
+        <v/>
+      </c>
+      <c r="L12" s="49">
+        <f>H12*D12+I12*D12^2/2+J12*D12^3/3-E12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6">
+        <f>'Bootstrap'!A12</f>
+        <v/>
+      </c>
+      <c r="B13" s="27">
+        <f>'Bootstrap'!C12</f>
+        <v/>
+      </c>
+      <c r="C13" s="33">
+        <f>'Bootstrap'!H12</f>
+        <v/>
+      </c>
+      <c r="D13" s="27">
+        <f>B13-B12</f>
+        <v/>
+      </c>
+      <c r="E13" s="32">
+        <f>-LN(C13/C12)</f>
+        <v/>
+      </c>
+      <c r="F13" s="48">
+        <f>E13/D13</f>
+        <v/>
+      </c>
+      <c r="G13" s="48">
+        <f>(F13+F14)/2</f>
+        <v/>
+      </c>
+      <c r="H13" s="48">
+        <f>G12</f>
+        <v/>
+      </c>
+      <c r="I13" s="32">
+        <f>(G13-G12)/D13-J13*D13</f>
+        <v/>
+      </c>
+      <c r="J13" s="32">
+        <f>3*(G13-G12)/D13^2-6*(E13-G12*D13)/D13^3</f>
+        <v/>
+      </c>
+      <c r="K13" s="48">
+        <f>H13+I13*D13/2+J13*D13^2/4</f>
+        <v/>
+      </c>
+      <c r="L13" s="49">
+        <f>H13*D13+I13*D13^2/2+J13*D13^3/3-E13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6">
+        <f>'Bootstrap'!A13</f>
+        <v/>
+      </c>
+      <c r="B14" s="27">
+        <f>'Bootstrap'!C13</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
+        <f>'Bootstrap'!H13</f>
+        <v/>
+      </c>
+      <c r="D14" s="27">
+        <f>B14-B13</f>
+        <v/>
+      </c>
+      <c r="E14" s="32">
+        <f>-LN(C14/C13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="48">
+        <f>E14/D14</f>
+        <v/>
+      </c>
+      <c r="G14" s="48">
+        <f>(F14+F15)/2</f>
+        <v/>
+      </c>
+      <c r="H14" s="48">
+        <f>G13</f>
+        <v/>
+      </c>
+      <c r="I14" s="32">
+        <f>(G14-G13)/D14-J14*D14</f>
+        <v/>
+      </c>
+      <c r="J14" s="32">
+        <f>3*(G14-G13)/D14^2-6*(E14-G13*D14)/D14^3</f>
+        <v/>
+      </c>
+      <c r="K14" s="48">
+        <f>H14+I14*D14/2+J14*D14^2/4</f>
+        <v/>
+      </c>
+      <c r="L14" s="49">
+        <f>H14*D14+I14*D14^2/2+J14*D14^3/3-E14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6">
+        <f>'Bootstrap'!A14</f>
+        <v/>
+      </c>
+      <c r="B15" s="27">
+        <f>'Bootstrap'!C14</f>
+        <v/>
+      </c>
+      <c r="C15" s="33">
+        <f>'Bootstrap'!H14</f>
+        <v/>
+      </c>
+      <c r="D15" s="27">
+        <f>B15-B14</f>
+        <v/>
+      </c>
+      <c r="E15" s="32">
+        <f>-LN(C15/C14)</f>
+        <v/>
+      </c>
+      <c r="F15" s="48">
+        <f>E15/D15</f>
+        <v/>
+      </c>
+      <c r="G15" s="48">
+        <f>(F15+F16)/2</f>
+        <v/>
+      </c>
+      <c r="H15" s="48">
+        <f>G14</f>
+        <v/>
+      </c>
+      <c r="I15" s="32">
+        <f>(G15-G14)/D15-J15*D15</f>
+        <v/>
+      </c>
+      <c r="J15" s="32">
+        <f>3*(G15-G14)/D15^2-6*(E15-G14*D15)/D15^3</f>
+        <v/>
+      </c>
+      <c r="K15" s="48">
+        <f>H15+I15*D15/2+J15*D15^2/4</f>
+        <v/>
+      </c>
+      <c r="L15" s="49">
+        <f>H15*D15+I15*D15^2/2+J15*D15^3/3-E15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6">
+        <f>'Bootstrap'!A15</f>
+        <v/>
+      </c>
+      <c r="B16" s="27">
+        <f>'Bootstrap'!C15</f>
+        <v/>
+      </c>
+      <c r="C16" s="33">
+        <f>'Bootstrap'!H15</f>
+        <v/>
+      </c>
+      <c r="D16" s="27">
+        <f>B16-B15</f>
+        <v/>
+      </c>
+      <c r="E16" s="32">
+        <f>-LN(C16/C15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="48">
+        <f>E16/D16</f>
+        <v/>
+      </c>
+      <c r="G16" s="48">
+        <f>(F16+F17)/2</f>
+        <v/>
+      </c>
+      <c r="H16" s="48">
+        <f>G15</f>
+        <v/>
+      </c>
+      <c r="I16" s="32">
+        <f>(G16-G15)/D16-J16*D16</f>
+        <v/>
+      </c>
+      <c r="J16" s="32">
+        <f>3*(G16-G15)/D16^2-6*(E16-G15*D16)/D16^3</f>
+        <v/>
+      </c>
+      <c r="K16" s="48">
+        <f>H16+I16*D16/2+J16*D16^2/4</f>
+        <v/>
+      </c>
+      <c r="L16" s="49">
+        <f>H16*D16+I16*D16^2/2+J16*D16^3/3-E16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6">
+        <f>'Bootstrap'!A16</f>
+        <v/>
+      </c>
+      <c r="B17" s="27">
+        <f>'Bootstrap'!C16</f>
+        <v/>
+      </c>
+      <c r="C17" s="33">
+        <f>'Bootstrap'!H16</f>
+        <v/>
+      </c>
+      <c r="D17" s="27">
+        <f>B17-B16</f>
+        <v/>
+      </c>
+      <c r="E17" s="32">
+        <f>-LN(C17/C16)</f>
+        <v/>
+      </c>
+      <c r="F17" s="48">
+        <f>E17/D17</f>
+        <v/>
+      </c>
+      <c r="G17" s="48">
+        <f>(F17+F18)/2</f>
+        <v/>
+      </c>
+      <c r="H17" s="48">
+        <f>G16</f>
+        <v/>
+      </c>
+      <c r="I17" s="32">
+        <f>(G17-G16)/D17-J17*D17</f>
+        <v/>
+      </c>
+      <c r="J17" s="32">
+        <f>3*(G17-G16)/D17^2-6*(E17-G16*D17)/D17^3</f>
+        <v/>
+      </c>
+      <c r="K17" s="48">
+        <f>H17+I17*D17/2+J17*D17^2/4</f>
+        <v/>
+      </c>
+      <c r="L17" s="49">
+        <f>H17*D17+I17*D17^2/2+J17*D17^3/3-E17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6">
+        <f>'Bootstrap'!A17</f>
+        <v/>
+      </c>
+      <c r="B18" s="27">
+        <f>'Bootstrap'!C17</f>
+        <v/>
+      </c>
+      <c r="C18" s="33">
+        <f>'Bootstrap'!H17</f>
+        <v/>
+      </c>
+      <c r="D18" s="27">
+        <f>B18-B17</f>
+        <v/>
+      </c>
+      <c r="E18" s="32">
+        <f>-LN(C18/C17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="48">
+        <f>E18/D18</f>
+        <v/>
+      </c>
+      <c r="G18" s="48">
+        <f>(F18+F19)/2</f>
+        <v/>
+      </c>
+      <c r="H18" s="48">
+        <f>G17</f>
+        <v/>
+      </c>
+      <c r="I18" s="32">
+        <f>(G18-G17)/D18-J18*D18</f>
+        <v/>
+      </c>
+      <c r="J18" s="32">
+        <f>3*(G18-G17)/D18^2-6*(E18-G17*D18)/D18^3</f>
+        <v/>
+      </c>
+      <c r="K18" s="48">
+        <f>H18+I18*D18/2+J18*D18^2/4</f>
+        <v/>
+      </c>
+      <c r="L18" s="49">
+        <f>H18*D18+I18*D18^2/2+J18*D18^3/3-E18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6">
+        <f>'Bootstrap'!A18</f>
+        <v/>
+      </c>
+      <c r="B19" s="27">
+        <f>'Bootstrap'!C18</f>
+        <v/>
+      </c>
+      <c r="C19" s="33">
+        <f>'Bootstrap'!H18</f>
+        <v/>
+      </c>
+      <c r="D19" s="27">
+        <f>B19-B18</f>
+        <v/>
+      </c>
+      <c r="E19" s="32">
+        <f>-LN(C19/C18)</f>
+        <v/>
+      </c>
+      <c r="F19" s="48">
+        <f>E19/D19</f>
+        <v/>
+      </c>
+      <c r="G19" s="48">
+        <f>(F19+F20)/2</f>
+        <v/>
+      </c>
+      <c r="H19" s="48">
+        <f>G18</f>
+        <v/>
+      </c>
+      <c r="I19" s="32">
+        <f>(G19-G18)/D19-J19*D19</f>
+        <v/>
+      </c>
+      <c r="J19" s="32">
+        <f>3*(G19-G18)/D19^2-6*(E19-G18*D19)/D19^3</f>
+        <v/>
+      </c>
+      <c r="K19" s="48">
+        <f>H19+I19*D19/2+J19*D19^2/4</f>
+        <v/>
+      </c>
+      <c r="L19" s="49">
+        <f>H19*D19+I19*D19^2/2+J19*D19^3/3-E19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6">
+        <f>'Bootstrap'!A19</f>
+        <v/>
+      </c>
+      <c r="B20" s="27">
+        <f>'Bootstrap'!C19</f>
+        <v/>
+      </c>
+      <c r="C20" s="33">
+        <f>'Bootstrap'!H19</f>
+        <v/>
+      </c>
+      <c r="D20" s="27">
+        <f>B20-B19</f>
+        <v/>
+      </c>
+      <c r="E20" s="32">
+        <f>-LN(C20/C19)</f>
+        <v/>
+      </c>
+      <c r="F20" s="48">
+        <f>E20/D20</f>
+        <v/>
+      </c>
+      <c r="G20" s="48">
+        <f>(F20+F21)/2</f>
+        <v/>
+      </c>
+      <c r="H20" s="48">
+        <f>G19</f>
+        <v/>
+      </c>
+      <c r="I20" s="32">
+        <f>(G20-G19)/D20-J20*D20</f>
+        <v/>
+      </c>
+      <c r="J20" s="32">
+        <f>3*(G20-G19)/D20^2-6*(E20-G19*D20)/D20^3</f>
+        <v/>
+      </c>
+      <c r="K20" s="48">
+        <f>H20+I20*D20/2+J20*D20^2/4</f>
+        <v/>
+      </c>
+      <c r="L20" s="49">
+        <f>H20*D20+I20*D20^2/2+J20*D20^3/3-E20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6">
+        <f>'Bootstrap'!A20</f>
+        <v/>
+      </c>
+      <c r="B21" s="27">
+        <f>'Bootstrap'!C20</f>
+        <v/>
+      </c>
+      <c r="C21" s="33">
+        <f>'Bootstrap'!H20</f>
+        <v/>
+      </c>
+      <c r="D21" s="27">
+        <f>B21-B20</f>
+        <v/>
+      </c>
+      <c r="E21" s="32">
+        <f>-LN(C21/C20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="48">
+        <f>E21/D21</f>
+        <v/>
+      </c>
+      <c r="G21" s="48">
+        <f>(F21+F22)/2</f>
+        <v/>
+      </c>
+      <c r="H21" s="48">
+        <f>G20</f>
+        <v/>
+      </c>
+      <c r="I21" s="32">
+        <f>(G21-G20)/D21-J21*D21</f>
+        <v/>
+      </c>
+      <c r="J21" s="32">
+        <f>3*(G21-G20)/D21^2-6*(E21-G20*D21)/D21^3</f>
+        <v/>
+      </c>
+      <c r="K21" s="48">
+        <f>H21+I21*D21/2+J21*D21^2/4</f>
+        <v/>
+      </c>
+      <c r="L21" s="49">
+        <f>H21*D21+I21*D21^2/2+J21*D21^3/3-E21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6">
+        <f>'Bootstrap'!A21</f>
+        <v/>
+      </c>
+      <c r="B22" s="27">
+        <f>'Bootstrap'!C21</f>
+        <v/>
+      </c>
+      <c r="C22" s="33">
+        <f>'Bootstrap'!H21</f>
+        <v/>
+      </c>
+      <c r="D22" s="27">
+        <f>B22-B21</f>
+        <v/>
+      </c>
+      <c r="E22" s="32">
+        <f>-LN(C22/C21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="48">
+        <f>E22/D22</f>
+        <v/>
+      </c>
+      <c r="G22" s="48">
+        <f>(F22+F23)/2</f>
+        <v/>
+      </c>
+      <c r="H22" s="48">
+        <f>G21</f>
+        <v/>
+      </c>
+      <c r="I22" s="32">
+        <f>(G22-G21)/D22-J22*D22</f>
+        <v/>
+      </c>
+      <c r="J22" s="32">
+        <f>3*(G22-G21)/D22^2-6*(E22-G21*D22)/D22^3</f>
+        <v/>
+      </c>
+      <c r="K22" s="48">
+        <f>H22+I22*D22/2+J22*D22^2/4</f>
+        <v/>
+      </c>
+      <c r="L22" s="49">
+        <f>H22*D22+I22*D22^2/2+J22*D22^3/3-E22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6">
+        <f>'Bootstrap'!A22</f>
+        <v/>
+      </c>
+      <c r="B23" s="27">
+        <f>'Bootstrap'!C22</f>
+        <v/>
+      </c>
+      <c r="C23" s="33">
+        <f>'Bootstrap'!H22</f>
+        <v/>
+      </c>
+      <c r="D23" s="27">
+        <f>B23-B22</f>
+        <v/>
+      </c>
+      <c r="E23" s="32">
+        <f>-LN(C23/C22)</f>
+        <v/>
+      </c>
+      <c r="F23" s="48">
+        <f>E23/D23</f>
+        <v/>
+      </c>
+      <c r="G23" s="48">
+        <f>(F23+F24)/2</f>
+        <v/>
+      </c>
+      <c r="H23" s="48">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="I23" s="32">
+        <f>(G23-G22)/D23-J23*D23</f>
+        <v/>
+      </c>
+      <c r="J23" s="32">
+        <f>3*(G23-G22)/D23^2-6*(E23-G22*D23)/D23^3</f>
+        <v/>
+      </c>
+      <c r="K23" s="48">
+        <f>H23+I23*D23/2+J23*D23^2/4</f>
+        <v/>
+      </c>
+      <c r="L23" s="49">
+        <f>H23*D23+I23*D23^2/2+J23*D23^3/3-E23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6">
+        <f>'Bootstrap'!A23</f>
+        <v/>
+      </c>
+      <c r="B24" s="27">
+        <f>'Bootstrap'!C23</f>
+        <v/>
+      </c>
+      <c r="C24" s="33">
+        <f>'Bootstrap'!H23</f>
+        <v/>
+      </c>
+      <c r="D24" s="27">
+        <f>B24-B23</f>
+        <v/>
+      </c>
+      <c r="E24" s="32">
+        <f>-LN(C24/C23)</f>
+        <v/>
+      </c>
+      <c r="F24" s="48">
+        <f>E24/D24</f>
+        <v/>
+      </c>
+      <c r="G24" s="48">
+        <f>(F24+F25)/2</f>
+        <v/>
+      </c>
+      <c r="H24" s="48">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="I24" s="32">
+        <f>(G24-G23)/D24-J24*D24</f>
+        <v/>
+      </c>
+      <c r="J24" s="32">
+        <f>3*(G24-G23)/D24^2-6*(E24-G23*D24)/D24^3</f>
+        <v/>
+      </c>
+      <c r="K24" s="48">
+        <f>H24+I24*D24/2+J24*D24^2/4</f>
+        <v/>
+      </c>
+      <c r="L24" s="49">
+        <f>H24*D24+I24*D24^2/2+J24*D24^3/3-E24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6">
+        <f>'Bootstrap'!A24</f>
+        <v/>
+      </c>
+      <c r="B25" s="27">
+        <f>'Bootstrap'!C24</f>
+        <v/>
+      </c>
+      <c r="C25" s="33">
+        <f>'Bootstrap'!H24</f>
+        <v/>
+      </c>
+      <c r="D25" s="27">
+        <f>B25-B24</f>
+        <v/>
+      </c>
+      <c r="E25" s="32">
+        <f>-LN(C25/C24)</f>
+        <v/>
+      </c>
+      <c r="F25" s="48">
+        <f>E25/D25</f>
+        <v/>
+      </c>
+      <c r="G25" s="48">
+        <f>(F25+F26)/2</f>
+        <v/>
+      </c>
+      <c r="H25" s="48">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="I25" s="32">
+        <f>(G25-G24)/D25-J25*D25</f>
+        <v/>
+      </c>
+      <c r="J25" s="32">
+        <f>3*(G25-G24)/D25^2-6*(E25-G24*D25)/D25^3</f>
+        <v/>
+      </c>
+      <c r="K25" s="48">
+        <f>H25+I25*D25/2+J25*D25^2/4</f>
+        <v/>
+      </c>
+      <c r="L25" s="49">
+        <f>H25*D25+I25*D25^2/2+J25*D25^3/3-E25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6">
+        <f>'Bootstrap'!A25</f>
+        <v/>
+      </c>
+      <c r="B26" s="27">
+        <f>'Bootstrap'!C25</f>
+        <v/>
+      </c>
+      <c r="C26" s="33">
+        <f>'Bootstrap'!H25</f>
+        <v/>
+      </c>
+      <c r="D26" s="27">
+        <f>B26-B25</f>
+        <v/>
+      </c>
+      <c r="E26" s="32">
+        <f>-LN(C26/C25)</f>
+        <v/>
+      </c>
+      <c r="F26" s="48">
+        <f>E26/D26</f>
+        <v/>
+      </c>
+      <c r="G26" s="48">
+        <f>(F26+F27)/2</f>
+        <v/>
+      </c>
+      <c r="H26" s="48">
+        <f>G25</f>
+        <v/>
+      </c>
+      <c r="I26" s="32">
+        <f>(G26-G25)/D26-J26*D26</f>
+        <v/>
+      </c>
+      <c r="J26" s="32">
+        <f>3*(G26-G25)/D26^2-6*(E26-G25*D26)/D26^3</f>
+        <v/>
+      </c>
+      <c r="K26" s="48">
+        <f>H26+I26*D26/2+J26*D26^2/4</f>
+        <v/>
+      </c>
+      <c r="L26" s="49">
+        <f>H26*D26+I26*D26^2/2+J26*D26^3/3-E26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6">
+        <f>'Bootstrap'!A26</f>
+        <v/>
+      </c>
+      <c r="B27" s="27">
+        <f>'Bootstrap'!C26</f>
+        <v/>
+      </c>
+      <c r="C27" s="33">
+        <f>'Bootstrap'!H26</f>
+        <v/>
+      </c>
+      <c r="D27" s="27">
+        <f>B27-B26</f>
+        <v/>
+      </c>
+      <c r="E27" s="32">
+        <f>-LN(C27/C26)</f>
+        <v/>
+      </c>
+      <c r="F27" s="48">
+        <f>E27/D27</f>
+        <v/>
+      </c>
+      <c r="G27" s="48">
+        <f>(F27+F28)/2</f>
+        <v/>
+      </c>
+      <c r="H27" s="48">
+        <f>G26</f>
+        <v/>
+      </c>
+      <c r="I27" s="32">
+        <f>(G27-G26)/D27-J27*D27</f>
+        <v/>
+      </c>
+      <c r="J27" s="32">
+        <f>3*(G27-G26)/D27^2-6*(E27-G26*D27)/D27^3</f>
+        <v/>
+      </c>
+      <c r="K27" s="48">
+        <f>H27+I27*D27/2+J27*D27^2/4</f>
+        <v/>
+      </c>
+      <c r="L27" s="49">
+        <f>H27*D27+I27*D27^2/2+J27*D27^3/3-E27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6">
+        <f>'Bootstrap'!A27</f>
+        <v/>
+      </c>
+      <c r="B28" s="27">
+        <f>'Bootstrap'!C27</f>
+        <v/>
+      </c>
+      <c r="C28" s="33">
+        <f>'Bootstrap'!H27</f>
+        <v/>
+      </c>
+      <c r="D28" s="27">
+        <f>B28-B27</f>
+        <v/>
+      </c>
+      <c r="E28" s="32">
+        <f>-LN(C28/C27)</f>
+        <v/>
+      </c>
+      <c r="F28" s="48">
+        <f>E28/D28</f>
+        <v/>
+      </c>
+      <c r="G28" s="48">
+        <f>(F28+F29)/2</f>
+        <v/>
+      </c>
+      <c r="H28" s="48">
+        <f>G27</f>
+        <v/>
+      </c>
+      <c r="I28" s="32">
+        <f>(G28-G27)/D28-J28*D28</f>
+        <v/>
+      </c>
+      <c r="J28" s="32">
+        <f>3*(G28-G27)/D28^2-6*(E28-G27*D28)/D28^3</f>
+        <v/>
+      </c>
+      <c r="K28" s="48">
+        <f>H28+I28*D28/2+J28*D28^2/4</f>
+        <v/>
+      </c>
+      <c r="L28" s="49">
+        <f>H28*D28+I28*D28^2/2+J28*D28^3/3-E28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6">
+        <f>'Bootstrap'!A28</f>
+        <v/>
+      </c>
+      <c r="B29" s="27">
+        <f>'Bootstrap'!C28</f>
+        <v/>
+      </c>
+      <c r="C29" s="33">
+        <f>'Bootstrap'!H28</f>
+        <v/>
+      </c>
+      <c r="D29" s="27">
+        <f>B29-B28</f>
+        <v/>
+      </c>
+      <c r="E29" s="32">
+        <f>-LN(C29/C28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="48">
+        <f>E29/D29</f>
+        <v/>
+      </c>
+      <c r="G29" s="48">
+        <f>(F29+F30)/2</f>
+        <v/>
+      </c>
+      <c r="H29" s="48">
+        <f>G28</f>
+        <v/>
+      </c>
+      <c r="I29" s="32">
+        <f>(G29-G28)/D29-J29*D29</f>
+        <v/>
+      </c>
+      <c r="J29" s="32">
+        <f>3*(G29-G28)/D29^2-6*(E29-G28*D29)/D29^3</f>
+        <v/>
+      </c>
+      <c r="K29" s="48">
+        <f>H29+I29*D29/2+J29*D29^2/4</f>
+        <v/>
+      </c>
+      <c r="L29" s="49">
+        <f>H29*D29+I29*D29^2/2+J29*D29^3/3-E29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6">
+        <f>'Bootstrap'!A29</f>
+        <v/>
+      </c>
+      <c r="B30" s="27">
+        <f>'Bootstrap'!C29</f>
+        <v/>
+      </c>
+      <c r="C30" s="33">
+        <f>'Bootstrap'!H29</f>
+        <v/>
+      </c>
+      <c r="D30" s="27">
+        <f>B30-B29</f>
+        <v/>
+      </c>
+      <c r="E30" s="32">
+        <f>-LN(C30/C29)</f>
+        <v/>
+      </c>
+      <c r="F30" s="48">
+        <f>E30/D30</f>
+        <v/>
+      </c>
+      <c r="G30" s="48">
+        <f>(F30+F31)/2</f>
+        <v/>
+      </c>
+      <c r="H30" s="48">
+        <f>G29</f>
+        <v/>
+      </c>
+      <c r="I30" s="32">
+        <f>(G30-G29)/D30-J30*D30</f>
+        <v/>
+      </c>
+      <c r="J30" s="32">
+        <f>3*(G30-G29)/D30^2-6*(E30-G29*D30)/D30^3</f>
+        <v/>
+      </c>
+      <c r="K30" s="48">
+        <f>H30+I30*D30/2+J30*D30^2/4</f>
+        <v/>
+      </c>
+      <c r="L30" s="49">
+        <f>H30*D30+I30*D30^2/2+J30*D30^3/3-E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6">
+        <f>'Bootstrap'!A30</f>
+        <v/>
+      </c>
+      <c r="B31" s="27">
+        <f>'Bootstrap'!C30</f>
+        <v/>
+      </c>
+      <c r="C31" s="33">
+        <f>'Bootstrap'!H30</f>
+        <v/>
+      </c>
+      <c r="D31" s="27">
+        <f>B31-B30</f>
+        <v/>
+      </c>
+      <c r="E31" s="32">
+        <f>-LN(C31/C30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="48">
+        <f>E31/D31</f>
+        <v/>
+      </c>
+      <c r="G31" s="48">
+        <f>(F31+F32)/2</f>
+        <v/>
+      </c>
+      <c r="H31" s="48">
+        <f>G30</f>
+        <v/>
+      </c>
+      <c r="I31" s="32">
+        <f>(G31-G30)/D31-J31*D31</f>
+        <v/>
+      </c>
+      <c r="J31" s="32">
+        <f>3*(G31-G30)/D31^2-6*(E31-G30*D31)/D31^3</f>
+        <v/>
+      </c>
+      <c r="K31" s="48">
+        <f>H31+I31*D31/2+J31*D31^2/4</f>
+        <v/>
+      </c>
+      <c r="L31" s="49">
+        <f>H31*D31+I31*D31^2/2+J31*D31^3/3-E31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6">
+        <f>'Bootstrap'!A31</f>
+        <v/>
+      </c>
+      <c r="B32" s="27">
+        <f>'Bootstrap'!C31</f>
+        <v/>
+      </c>
+      <c r="C32" s="33">
+        <f>'Bootstrap'!H31</f>
+        <v/>
+      </c>
+      <c r="D32" s="27">
+        <f>B32-B31</f>
+        <v/>
+      </c>
+      <c r="E32" s="32">
+        <f>-LN(C32/C31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="48">
+        <f>E32/D32</f>
+        <v/>
+      </c>
+      <c r="G32" s="48">
+        <f>(F32+F33)/2</f>
+        <v/>
+      </c>
+      <c r="H32" s="48">
+        <f>G31</f>
+        <v/>
+      </c>
+      <c r="I32" s="32">
+        <f>(G32-G31)/D32-J32*D32</f>
+        <v/>
+      </c>
+      <c r="J32" s="32">
+        <f>3*(G32-G31)/D32^2-6*(E32-G31*D32)/D32^3</f>
+        <v/>
+      </c>
+      <c r="K32" s="48">
+        <f>H32+I32*D32/2+J32*D32^2/4</f>
+        <v/>
+      </c>
+      <c r="L32" s="49">
+        <f>H32*D32+I32*D32^2/2+J32*D32^3/3-E32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6">
+        <f>'Bootstrap'!A32</f>
+        <v/>
+      </c>
+      <c r="B33" s="27">
+        <f>'Bootstrap'!C32</f>
+        <v/>
+      </c>
+      <c r="C33" s="33">
+        <f>'Bootstrap'!H32</f>
+        <v/>
+      </c>
+      <c r="D33" s="27">
+        <f>B33-B32</f>
+        <v/>
+      </c>
+      <c r="E33" s="32">
+        <f>-LN(C33/C32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="48">
+        <f>E33/D33</f>
+        <v/>
+      </c>
+      <c r="G33" s="48">
+        <f>(F33+F34)/2</f>
+        <v/>
+      </c>
+      <c r="H33" s="48">
+        <f>G32</f>
+        <v/>
+      </c>
+      <c r="I33" s="32">
+        <f>(G33-G32)/D33-J33*D33</f>
+        <v/>
+      </c>
+      <c r="J33" s="32">
+        <f>3*(G33-G32)/D33^2-6*(E33-G32*D33)/D33^3</f>
+        <v/>
+      </c>
+      <c r="K33" s="48">
+        <f>H33+I33*D33/2+J33*D33^2/4</f>
+        <v/>
+      </c>
+      <c r="L33" s="49">
+        <f>H33*D33+I33*D33^2/2+J33*D33^3/3-E33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6">
+        <f>'Bootstrap'!A33</f>
+        <v/>
+      </c>
+      <c r="B34" s="27">
+        <f>'Bootstrap'!C33</f>
+        <v/>
+      </c>
+      <c r="C34" s="33">
+        <f>'Bootstrap'!H33</f>
+        <v/>
+      </c>
+      <c r="D34" s="27">
+        <f>B34-B33</f>
+        <v/>
+      </c>
+      <c r="E34" s="32">
+        <f>-LN(C34/C33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="48">
+        <f>E34/D34</f>
+        <v/>
+      </c>
+      <c r="G34" s="48">
+        <f>(F34+F35)/2</f>
+        <v/>
+      </c>
+      <c r="H34" s="48">
+        <f>G33</f>
+        <v/>
+      </c>
+      <c r="I34" s="32">
+        <f>(G34-G33)/D34-J34*D34</f>
+        <v/>
+      </c>
+      <c r="J34" s="32">
+        <f>3*(G34-G33)/D34^2-6*(E34-G33*D34)/D34^3</f>
+        <v/>
+      </c>
+      <c r="K34" s="48">
+        <f>H34+I34*D34/2+J34*D34^2/4</f>
+        <v/>
+      </c>
+      <c r="L34" s="49">
+        <f>H34*D34+I34*D34^2/2+J34*D34^3/3-E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6">
+        <f>'Bootstrap'!A34</f>
+        <v/>
+      </c>
+      <c r="B35" s="27">
+        <f>'Bootstrap'!C34</f>
+        <v/>
+      </c>
+      <c r="C35" s="33">
+        <f>'Bootstrap'!H34</f>
+        <v/>
+      </c>
+      <c r="D35" s="27">
+        <f>B35-B34</f>
+        <v/>
+      </c>
+      <c r="E35" s="32">
+        <f>-LN(C35/C34)</f>
+        <v/>
+      </c>
+      <c r="F35" s="48">
+        <f>E35/D35</f>
+        <v/>
+      </c>
+      <c r="G35" s="48">
+        <f>(F35+F36)/2</f>
+        <v/>
+      </c>
+      <c r="H35" s="48">
+        <f>G34</f>
+        <v/>
+      </c>
+      <c r="I35" s="32">
+        <f>(G35-G34)/D35-J35*D35</f>
+        <v/>
+      </c>
+      <c r="J35" s="32">
+        <f>3*(G35-G34)/D35^2-6*(E35-G34*D35)/D35^3</f>
+        <v/>
+      </c>
+      <c r="K35" s="48">
+        <f>H35+I35*D35/2+J35*D35^2/4</f>
+        <v/>
+      </c>
+      <c r="L35" s="49">
+        <f>H35*D35+I35*D35^2/2+J35*D35^3/3-E35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6">
+        <f>'Bootstrap'!A35</f>
+        <v/>
+      </c>
+      <c r="B36" s="27">
+        <f>'Bootstrap'!C35</f>
+        <v/>
+      </c>
+      <c r="C36" s="33">
+        <f>'Bootstrap'!H35</f>
+        <v/>
+      </c>
+      <c r="D36" s="27">
+        <f>B36-B35</f>
+        <v/>
+      </c>
+      <c r="E36" s="32">
+        <f>-LN(C36/C35)</f>
+        <v/>
+      </c>
+      <c r="F36" s="48">
+        <f>E36/D36</f>
+        <v/>
+      </c>
+      <c r="G36" s="48">
+        <f>(F36+F37)/2</f>
+        <v/>
+      </c>
+      <c r="H36" s="48">
+        <f>G35</f>
+        <v/>
+      </c>
+      <c r="I36" s="32">
+        <f>(G36-G35)/D36-J36*D36</f>
+        <v/>
+      </c>
+      <c r="J36" s="32">
+        <f>3*(G36-G35)/D36^2-6*(E36-G35*D36)/D36^3</f>
+        <v/>
+      </c>
+      <c r="K36" s="48">
+        <f>H36+I36*D36/2+J36*D36^2/4</f>
+        <v/>
+      </c>
+      <c r="L36" s="49">
+        <f>H36*D36+I36*D36^2/2+J36*D36^3/3-E36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6">
+        <f>'Bootstrap'!A36</f>
+        <v/>
+      </c>
+      <c r="B37" s="27">
+        <f>'Bootstrap'!C36</f>
+        <v/>
+      </c>
+      <c r="C37" s="33">
+        <f>'Bootstrap'!H36</f>
+        <v/>
+      </c>
+      <c r="D37" s="27">
+        <f>B37-B36</f>
+        <v/>
+      </c>
+      <c r="E37" s="32">
+        <f>-LN(C37/C36)</f>
+        <v/>
+      </c>
+      <c r="F37" s="48">
+        <f>E37/D37</f>
+        <v/>
+      </c>
+      <c r="G37" s="48">
+        <f>(F37+F38)/2</f>
+        <v/>
+      </c>
+      <c r="H37" s="48">
+        <f>G36</f>
+        <v/>
+      </c>
+      <c r="I37" s="32">
+        <f>(G37-G36)/D37-J37*D37</f>
+        <v/>
+      </c>
+      <c r="J37" s="32">
+        <f>3*(G37-G36)/D37^2-6*(E37-G36*D37)/D37^3</f>
+        <v/>
+      </c>
+      <c r="K37" s="48">
+        <f>H37+I37*D37/2+J37*D37^2/4</f>
+        <v/>
+      </c>
+      <c r="L37" s="49">
+        <f>H37*D37+I37*D37^2/2+J37*D37^3/3-E37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6">
+        <f>'Bootstrap'!A37</f>
+        <v/>
+      </c>
+      <c r="B38" s="27">
+        <f>'Bootstrap'!C37</f>
+        <v/>
+      </c>
+      <c r="C38" s="33">
+        <f>'Bootstrap'!H37</f>
+        <v/>
+      </c>
+      <c r="D38" s="27">
+        <f>B38-B37</f>
+        <v/>
+      </c>
+      <c r="E38" s="32">
+        <f>-LN(C38/C37)</f>
+        <v/>
+      </c>
+      <c r="F38" s="48">
+        <f>E38/D38</f>
+        <v/>
+      </c>
+      <c r="G38" s="48">
+        <f>(F38+F39)/2</f>
+        <v/>
+      </c>
+      <c r="H38" s="48">
+        <f>G37</f>
+        <v/>
+      </c>
+      <c r="I38" s="32">
+        <f>(G38-G37)/D38-J38*D38</f>
+        <v/>
+      </c>
+      <c r="J38" s="32">
+        <f>3*(G38-G37)/D38^2-6*(E38-G37*D38)/D38^3</f>
+        <v/>
+      </c>
+      <c r="K38" s="48">
+        <f>H38+I38*D38/2+J38*D38^2/4</f>
+        <v/>
+      </c>
+      <c r="L38" s="49">
+        <f>H38*D38+I38*D38^2/2+J38*D38^3/3-E38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6">
+        <f>'Bootstrap'!A38</f>
+        <v/>
+      </c>
+      <c r="B39" s="27">
+        <f>'Bootstrap'!C38</f>
+        <v/>
+      </c>
+      <c r="C39" s="33">
+        <f>'Bootstrap'!H38</f>
+        <v/>
+      </c>
+      <c r="D39" s="27">
+        <f>B39-B38</f>
+        <v/>
+      </c>
+      <c r="E39" s="32">
+        <f>-LN(C39/C38)</f>
+        <v/>
+      </c>
+      <c r="F39" s="48">
+        <f>E39/D39</f>
+        <v/>
+      </c>
+      <c r="G39" s="48">
+        <f>(F39+F40)/2</f>
+        <v/>
+      </c>
+      <c r="H39" s="48">
+        <f>G38</f>
+        <v/>
+      </c>
+      <c r="I39" s="32">
+        <f>(G39-G38)/D39-J39*D39</f>
+        <v/>
+      </c>
+      <c r="J39" s="32">
+        <f>3*(G39-G38)/D39^2-6*(E39-G38*D39)/D39^3</f>
+        <v/>
+      </c>
+      <c r="K39" s="48">
+        <f>H39+I39*D39/2+J39*D39^2/4</f>
+        <v/>
+      </c>
+      <c r="L39" s="49">
+        <f>H39*D39+I39*D39^2/2+J39*D39^3/3-E39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6">
+        <f>'Bootstrap'!A39</f>
+        <v/>
+      </c>
+      <c r="B40" s="27">
+        <f>'Bootstrap'!C39</f>
+        <v/>
+      </c>
+      <c r="C40" s="33">
+        <f>'Bootstrap'!H39</f>
+        <v/>
+      </c>
+      <c r="D40" s="27">
+        <f>B40-B39</f>
+        <v/>
+      </c>
+      <c r="E40" s="32">
+        <f>-LN(C40/C39)</f>
+        <v/>
+      </c>
+      <c r="F40" s="48">
+        <f>E40/D40</f>
+        <v/>
+      </c>
+      <c r="G40" s="48">
+        <f>F40</f>
+        <v/>
+      </c>
+      <c r="H40" s="48">
+        <f>G39</f>
+        <v/>
+      </c>
+      <c r="I40" s="32">
+        <f>(G40-G39)/D40-J40*D40</f>
+        <v/>
+      </c>
+      <c r="J40" s="32">
+        <f>3*(G40-G39)/D40^2-6*(E40-G39*D40)/D40^3</f>
+        <v/>
+      </c>
+      <c r="K40" s="48">
+        <f>H40+I40*D40/2+J40*D40^2/4</f>
+        <v/>
+      </c>
+      <c r="L40" s="49">
+        <f>H40*D40+I40*D40^2/2+J40*D40^3/3-E40</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:L6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -4265,6 +4265,7 @@
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="12" customWidth="1" min="16" max="16"/>
     <col width="12" customWidth="1" min="17" max="17"/>
@@ -4306,7 +4307,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·τ0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which discounts each contract's forward rate forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is shown only for reference).  LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·τcoupon), with the annuity (col I) built from the short + futures DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
+          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·tau0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which discounts each contract's forward rate forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is shown only for reference).  LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·taucoupon), with the annuity (col I) built from the short + futures DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4341,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>τ0 spot→mat</t>
+          <t>tau0 spot→mat</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -4350,7 +4351,7 @@
       </c>
       <c r="F7" s="19" t="inlineStr">
         <is>
-          <t>τ coupon</t>
+          <t>tau coupon</t>
         </is>
       </c>
       <c r="G7" s="19" t="inlineStr">
@@ -4365,7 +4366,7 @@
       </c>
       <c r="I7" s="19" t="inlineStr">
         <is>
-          <t>Ann.add τ·DF</t>
+          <t>Ann.add tau·DF</t>
         </is>
       </c>
       <c r="J7" s="19" t="inlineStr">
@@ -4388,6 +4389,11 @@
           <t>Δ vs S490 (bp)</t>
         </is>
       </c>
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>DF source</t>
+        </is>
+      </c>
       <c r="O7" s="19" t="inlineStr">
         <is>
           <t>Contract</t>
@@ -4405,7 +4411,7 @@
       </c>
       <c r="R7" s="19" t="inlineStr">
         <is>
-          <t>τ eff (post-1Y)</t>
+          <t>tau eff (post-1Y)</t>
         </is>
       </c>
       <c r="S7" s="19" t="inlineStr">
@@ -4490,6 +4496,11 @@
         <f>IF(L8="","",(J8-L8)*100)</f>
         <v/>
       </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O8" s="6">
         <f>'SOFR_Futures'!A7</f>
         <v/>
@@ -4581,6 +4592,11 @@
         <f>IF(L9="","",(J9-L9)*100)</f>
         <v/>
       </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O9" s="6">
         <f>'SOFR_Futures'!A8</f>
         <v/>
@@ -4672,6 +4688,11 @@
         <f>IF(L10="","",(J10-L10)*100)</f>
         <v/>
       </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O10" s="6">
         <f>'SOFR_Futures'!A9</f>
         <v/>
@@ -4763,6 +4784,11 @@
         <f>IF(L11="","",(J11-L11)*100)</f>
         <v/>
       </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O11" s="6">
         <f>'SOFR_Futures'!A10</f>
         <v/>
@@ -4854,6 +4880,11 @@
         <f>IF(L12="","",(J12-L12)*100)</f>
         <v/>
       </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O12" s="6">
         <f>'SOFR_Futures'!A11</f>
         <v/>
@@ -4945,6 +4976,11 @@
         <f>IF(L13="","",(J13-L13)*100)</f>
         <v/>
       </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O13" s="6">
         <f>'SOFR_Futures'!A12</f>
         <v/>
@@ -5036,6 +5072,11 @@
         <f>IF(L14="","",(J14-L14)*100)</f>
         <v/>
       </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O14" s="6">
         <f>'SOFR_Futures'!A13</f>
         <v/>
@@ -5127,6 +5168,11 @@
         <f>IF(L15="","",(J15-L15)*100)</f>
         <v/>
       </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O15" s="6">
         <f>'SOFR_Futures'!A14</f>
         <v/>
@@ -5218,6 +5264,11 @@
         <f>IF(L16="","",(J16-L16)*100)</f>
         <v/>
       </c>
+      <c r="N16" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O16" s="6">
         <f>'SOFR_Futures'!A15</f>
         <v/>
@@ -5309,6 +5360,11 @@
         <f>IF(L17="","",(J17-L17)*100)</f>
         <v/>
       </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O17" s="6">
         <f>'SOFR_Futures'!A16</f>
         <v/>
@@ -5400,6 +5456,11 @@
         <f>IF(L18="","",(J18-L18)*100)</f>
         <v/>
       </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O18" s="6">
         <f>'SOFR_Futures'!A17</f>
         <v/>
@@ -5491,6 +5552,11 @@
         <f>IF(L19="","",(J19-L19)*100)</f>
         <v/>
       </c>
+      <c r="N19" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O19" s="6">
         <f>'SOFR_Futures'!A18</f>
         <v/>
@@ -5582,6 +5648,11 @@
         <f>IF(L20="","",(J20-L20)*100)</f>
         <v/>
       </c>
+      <c r="N20" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O20" s="6">
         <f>'SOFR_Futures'!A19</f>
         <v/>
@@ -5673,6 +5744,11 @@
         <f>IF(L21="","",(J21-L21)*100)</f>
         <v/>
       </c>
+      <c r="N21" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O21" s="6">
         <f>'SOFR_Futures'!A20</f>
         <v/>
@@ -5768,6 +5844,11 @@
         <f>IF(L22="","",(J22-L22)*100)</f>
         <v/>
       </c>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
+      </c>
       <c r="O22" s="6">
         <f>'SOFR_Futures'!A21</f>
         <v/>
@@ -5862,6 +5943,11 @@
         <f>IF(L23="","",(J23-L23)*100)</f>
         <v/>
       </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
       <c r="O23" s="6">
         <f>'SOFR_Futures'!A22</f>
         <v/>
@@ -5957,6 +6043,11 @@
         <f>IF(L24="","",(J24-L24)*100)</f>
         <v/>
       </c>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
       <c r="O24" s="6">
         <f>'SOFR_Futures'!A23</f>
         <v/>
@@ -6052,6 +6143,11 @@
         <f>IF(L25="","",(J25-L25)*100)</f>
         <v/>
       </c>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
       <c r="O25" s="6">
         <f>'SOFR_Futures'!A24</f>
         <v/>
@@ -6147,6 +6243,11 @@
         <f>IF(L26="","",(J26-L26)*100)</f>
         <v/>
       </c>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
       <c r="O26" s="6">
         <f>'SOFR_Futures'!A25</f>
         <v/>
@@ -6242,6 +6343,11 @@
         <f>IF(L27="","",(J27-L27)*100)</f>
         <v/>
       </c>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
       <c r="O27" s="6">
         <f>'SOFR_Futures'!A26</f>
         <v/>
@@ -6337,6 +6443,11 @@
         <f>IF(L28="","",(J28-L28)*100)</f>
         <v/>
       </c>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
       <c r="Y28" s="17">
         <f>MAX(Q27,$B$22)</f>
         <v/>
@@ -6397,6 +6508,11 @@
         <f>IF(L29="","",(J29-L29)*100)</f>
         <v/>
       </c>
+      <c r="N29" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -6449,6 +6565,11 @@
         <f>IF(L30="","",(J30-L30)*100)</f>
         <v/>
       </c>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -6501,6 +6622,11 @@
         <f>IF(L31="","",(J31-L31)*100)</f>
         <v/>
       </c>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -6553,6 +6679,11 @@
         <f>IF(L32="","",(J32-L32)*100)</f>
         <v/>
       </c>
+      <c r="N32" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -6605,6 +6736,11 @@
         <f>IF(L33="","",(J33-L33)*100)</f>
         <v/>
       </c>
+      <c r="N33" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -6657,6 +6793,11 @@
         <f>IF(L34="","",(J34-L34)*100)</f>
         <v/>
       </c>
+      <c r="N34" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -6709,6 +6850,11 @@
         <f>IF(L35="","",(J35-L35)*100)</f>
         <v/>
       </c>
+      <c r="N35" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -6761,6 +6907,11 @@
         <f>IF(L36="","",(J36-L36)*100)</f>
         <v/>
       </c>
+      <c r="N36" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -6813,6 +6964,11 @@
         <f>IF(L37="","",(J37-L37)*100)</f>
         <v/>
       </c>
+      <c r="N37" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -6865,6 +7021,11 @@
         <f>IF(L38="","",(J38-L38)*100)</f>
         <v/>
       </c>
+      <c r="N38" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -6917,11 +7078,16 @@
         <f>IF(L39="","",(J39-L39)*100)</f>
         <v/>
       </c>
+      <c r="N39" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>THREE SEGMENTS (Zhou 2002 structure):  SHORT o/n–1Y = single-payment SOFR OIS  (DF=1/(1+S·τ0));  MIDDLE 1Y–5Y = SR3 futures chained from the 1Y DF (helper block to the right, cols O–W);  LONG 5Y–50Y = annual SOFR OIS swaps built off the futures-derived 5Y point. No overlap — each maturity is covered once. Column H is the curve P(0,T); zero z=−ln(DF)/T. The futures convexity column (T) defaults to 0 — enter an adjustment in bp to correct futures→forward. Paste S490 zeros into column L for the Δz check; the Swap_Pricer values any OIS off this curve.</t>
+          <t>THREE SEGMENTS (Zhou 2002 structure):  SHORT o/n–1Y = single-payment SOFR OIS  (DF=1/(1+S·tau0));  MIDDLE 1Y–5Y = SR3 futures chained from the 1Y DF (helper block to the right, cols O–W);  LONG 5Y–50Y = annual SOFR OIS swaps built off the futures-derived 5Y point. No overlap — each maturity is covered once. Column H is the curve P(0,T); zero z=−ln(DF)/T. The futures convexity column (T) defaults to 0 — enter an adjustment in bp to correct futures→forward. Paste S490 zeros into column L for the Δz check; the Swap_Pricer values any OIS off this curve.</t>
         </is>
       </c>
     </row>
@@ -6929,9 +7095,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="O6:W6"/>
-    <mergeCell ref="A5:M6"/>
     <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="A41:M42"/>
+    <mergeCell ref="A5:N6"/>
+    <mergeCell ref="A41:N42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7324,7 +7490,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Fixed annuity  Στ·DF</t>
+          <t>Fixed annuity  Sum tau·DF</t>
         </is>
       </c>
       <c r="B21" s="32">
@@ -7333,7 +7499,7 @@
       </c>
       <c r="C21" s="35" t="inlineStr">
         <is>
-          <t>Sum of τ·DF over the fixed coupon dates.</t>
+          <t>Sum of tau·DF over the fixed coupon dates.</t>
         </is>
       </c>
       <c r="K21" s="17">
@@ -7608,7 +7774,7 @@
       </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
-          <t>τ ACT/360</t>
+          <t>tau ACT/360</t>
         </is>
       </c>
       <c r="E35" s="19" t="inlineStr">
@@ -7628,7 +7794,7 @@
       </c>
       <c r="H35" s="19" t="inlineStr">
         <is>
-          <t>τ·DF</t>
+          <t>tau·DF</t>
         </is>
       </c>
       <c r="K35" s="17">

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -13,10 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Futures" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_OIS_Quotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -133,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -188,6 +189,8 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -196,7 +199,6 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1020,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1478,77 +1480,89 @@
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>5. Bloomberg_S490_Validation</t>
+          <t>Curve_Interface</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
+          <t>Shared D(0,t): interpolates the SOFR curve to ANY date (quarterly CDS dates demo). Used by Swap_Pricer + CDS.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>6. Conventions</t>
+          <t>5. Bloomberg_S490_Validation</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
+          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
+          <t>6. Conventions</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="inlineStr">
+        <is>
           <t>7. Fwd_Interp</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B44" s="3" t="inlineStr">
         <is>
           <t>Zhou 2002 forward interpolation: V1 piecewise-flat vs V2 piecewise-quadratic forwards.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>DO NOT substitute these (wrong instruments):</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
-        <is>
-          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="9" t="inlineStr">
         <is>
+          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
           <t>•  Use PX midpoint (bid+ask)/2 for construction; use PX_LAST only where bid/ask are unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="51" ht="28" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Licensing: Bloomberg data is licensed and entitlement-dependent — do NOT redistribute pulled values or commit them to a public repository. This template ships formulas only, no data. Some static convention fields may return N/A under your entitlement; use FLDS &lt;GO&gt; on the security to find the enabled mnemonic.</t>
         </is>
       </c>
     </row>
-    <row r="51"/>
+    <row r="52"/>
   </sheetData>
-  <mergeCells count="51">
+  <mergeCells count="52">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
@@ -1569,13 +1583,14 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A51:F52"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D14:F14"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="B38:F38"/>
-    <mergeCell ref="A50:F51"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="B37:F37"/>
@@ -1588,8 +1603,8 @@
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="A24:F24"/>
     <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A45:F45"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E22:F22"/>
     <mergeCell ref="B36:F36"/>
@@ -1606,6 +1621,782 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Conventions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>OIS quote conventions (DES/FLDS) for representative tenors — record before you bootstrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>Convention attribute</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>BDP field (verify via FLDS)</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>USOSFRC  (3M)</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>USOSFR1  (1Y)</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="inlineStr">
+        <is>
+          <t>USOSFR5  (5Y)</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>USOSFR30  (30Y)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>CRNCY</t>
+        </is>
+      </c>
+      <c r="C5" s="22">
+        <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="D5" s="22">
+        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="E5" s="22">
+        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="F5" s="22">
+        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Reference index</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D6" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Spot / settlement lag</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Effective date rule</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Maturity date rule</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Business-day calendar</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>CALENDAR_CODE</t>
+        </is>
+      </c>
+      <c r="C10" s="22">
+        <f>IFERROR(BDP("USOSFRC BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="D10" s="22">
+        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="E10" s="22">
+        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="F10" s="22">
+        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Business-day convention</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F11" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Fixed-leg day count</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>DAY_CNT_DES</t>
+        </is>
+      </c>
+      <c r="C12" s="22">
+        <f>IFERROR(BDP("USOSFRC BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="D12" s="22">
+        <f>IFERROR(BDP("USOSFR1 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="E12" s="22">
+        <f>IFERROR(BDP("USOSFR5 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+      <c r="F12" s="22">
+        <f>IFERROR(BDP("USOSFR30 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Fixed-leg pay frequency</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F13" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Floating-leg day count</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F14" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Floating-leg pay frequency</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>SOFR compounding method</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Payment lag</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E17" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Observation shift / lookback</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>End-of-month treatment</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>— DES/SWPM manual —</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+      <c r="F19" s="22" t="inlineStr">
+        <is>
+          <t>— DES/SWPM —</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>USD SOFR OIS — MARKET-STANDARD CONVENTIONS  (confirm per-trade in DES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Reference index</t>
+        </is>
+      </c>
+      <c r="B22" s="45" t="inlineStr">
+        <is>
+          <t>USD-SOFR (compounded in arrears)</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Spot / settlement lag</t>
+        </is>
+      </c>
+      <c r="B23" s="45" t="inlineStr">
+        <is>
+          <t>T+2 US business days</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Effective date rule</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="inlineStr">
+        <is>
+          <t>Spot (T+2), modified following</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Maturity date rule</t>
+        </is>
+      </c>
+      <c r="B25" s="45" t="inlineStr">
+        <is>
+          <t>Effective + tenor, modified following</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Business-day convention</t>
+        </is>
+      </c>
+      <c r="B26" s="45" t="inlineStr">
+        <is>
+          <t>Modified Following</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Fixed-leg day count</t>
+        </is>
+      </c>
+      <c r="B27" s="45" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Fixed-leg pay frequency</t>
+        </is>
+      </c>
+      <c r="B28" s="45" t="inlineStr">
+        <is>
+          <t>Annual  (single payment if tenor ≤ 1Y)</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Floating-leg day count</t>
+        </is>
+      </c>
+      <c r="B29" s="45" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Floating-leg pay frequency</t>
+        </is>
+      </c>
+      <c r="B30" s="45" t="inlineStr">
+        <is>
+          <t>Annual  (single payment if tenor ≤ 1Y)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>SOFR compounding method</t>
+        </is>
+      </c>
+      <c r="B31" s="45" t="inlineStr">
+        <is>
+          <t>Daily compounded, ACT/360</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Payment lag</t>
+        </is>
+      </c>
+      <c r="B32" s="45" t="inlineStr">
+        <is>
+          <t>2 US business days</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Observation shift / lookback</t>
+        </is>
+      </c>
+      <c r="B33" s="45" t="inlineStr">
+        <is>
+          <t>None (payment-delay convention, 2 bd)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>End-of-month treatment</t>
+        </is>
+      </c>
+      <c r="B34" s="45" t="inlineStr">
+        <is>
+          <t>EOM applies</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+    </row>
+    <row r="36" ht="44" customHeight="1">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>SWPM &lt;GO&gt;: build a representative SOFR OIS for 1Y, 5Y and 30Y and export the cashflow schedule — that gives an authoritative set of pay/accrual dates to test your own date generation against. Rows marked '— DES/SWPM —' are leg-level conventions that a rate-quote ticker does not carry; read them from DES &lt;GO&gt; on an actual swap (the market-standard defaults above are the expected values). Where a BDP cell shows 'N/A — use FLDS', open FLDS &lt;GO&gt; to find the enabled field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="A36:F37"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="B26:F26"/>
+    <mergeCell ref="B27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1719,13 +2510,13 @@
           <t>Spot</t>
         </is>
       </c>
-      <c r="B8" s="45" t="n">
+      <c r="B8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="46" t="n">
+      <c r="C8" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="48">
         <f>F9</f>
         <v/>
       </c>
@@ -1751,15 +2542,15 @@
         <f>-LN(C9/C8)</f>
         <v/>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="49">
         <f>E9/D9</f>
         <v/>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="49">
         <f>(F9+F10)/2</f>
         <v/>
       </c>
-      <c r="H9" s="48">
+      <c r="H9" s="49">
         <f>G8</f>
         <v/>
       </c>
@@ -1771,11 +2562,11 @@
         <f>3*(G9-G8)/D9^2-6*(E9-G8*D9)/D9^3</f>
         <v/>
       </c>
-      <c r="K9" s="48">
+      <c r="K9" s="49">
         <f>H9+I9*D9/2+J9*D9^2/4</f>
         <v/>
       </c>
-      <c r="L9" s="49">
+      <c r="L9" s="50">
         <f>H9*D9+I9*D9^2/2+J9*D9^3/3-E9</f>
         <v/>
       </c>
@@ -1801,15 +2592,15 @@
         <f>-LN(C10/C9)</f>
         <v/>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="49">
         <f>E10/D10</f>
         <v/>
       </c>
-      <c r="G10" s="48">
+      <c r="G10" s="49">
         <f>(F10+F11)/2</f>
         <v/>
       </c>
-      <c r="H10" s="48">
+      <c r="H10" s="49">
         <f>G9</f>
         <v/>
       </c>
@@ -1821,11 +2612,11 @@
         <f>3*(G10-G9)/D10^2-6*(E10-G9*D10)/D10^3</f>
         <v/>
       </c>
-      <c r="K10" s="48">
+      <c r="K10" s="49">
         <f>H10+I10*D10/2+J10*D10^2/4</f>
         <v/>
       </c>
-      <c r="L10" s="49">
+      <c r="L10" s="50">
         <f>H10*D10+I10*D10^2/2+J10*D10^3/3-E10</f>
         <v/>
       </c>
@@ -1851,15 +2642,15 @@
         <f>-LN(C11/C10)</f>
         <v/>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="49">
         <f>E11/D11</f>
         <v/>
       </c>
-      <c r="G11" s="48">
+      <c r="G11" s="49">
         <f>(F11+F12)/2</f>
         <v/>
       </c>
-      <c r="H11" s="48">
+      <c r="H11" s="49">
         <f>G10</f>
         <v/>
       </c>
@@ -1871,11 +2662,11 @@
         <f>3*(G11-G10)/D11^2-6*(E11-G10*D11)/D11^3</f>
         <v/>
       </c>
-      <c r="K11" s="48">
+      <c r="K11" s="49">
         <f>H11+I11*D11/2+J11*D11^2/4</f>
         <v/>
       </c>
-      <c r="L11" s="49">
+      <c r="L11" s="50">
         <f>H11*D11+I11*D11^2/2+J11*D11^3/3-E11</f>
         <v/>
       </c>
@@ -1901,15 +2692,15 @@
         <f>-LN(C12/C11)</f>
         <v/>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="49">
         <f>E12/D12</f>
         <v/>
       </c>
-      <c r="G12" s="48">
+      <c r="G12" s="49">
         <f>(F12+F13)/2</f>
         <v/>
       </c>
-      <c r="H12" s="48">
+      <c r="H12" s="49">
         <f>G11</f>
         <v/>
       </c>
@@ -1921,11 +2712,11 @@
         <f>3*(G12-G11)/D12^2-6*(E12-G11*D12)/D12^3</f>
         <v/>
       </c>
-      <c r="K12" s="48">
+      <c r="K12" s="49">
         <f>H12+I12*D12/2+J12*D12^2/4</f>
         <v/>
       </c>
-      <c r="L12" s="49">
+      <c r="L12" s="50">
         <f>H12*D12+I12*D12^2/2+J12*D12^3/3-E12</f>
         <v/>
       </c>
@@ -1951,15 +2742,15 @@
         <f>-LN(C13/C12)</f>
         <v/>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="49">
         <f>E13/D13</f>
         <v/>
       </c>
-      <c r="G13" s="48">
+      <c r="G13" s="49">
         <f>(F13+F14)/2</f>
         <v/>
       </c>
-      <c r="H13" s="48">
+      <c r="H13" s="49">
         <f>G12</f>
         <v/>
       </c>
@@ -1971,11 +2762,11 @@
         <f>3*(G13-G12)/D13^2-6*(E13-G12*D13)/D13^3</f>
         <v/>
       </c>
-      <c r="K13" s="48">
+      <c r="K13" s="49">
         <f>H13+I13*D13/2+J13*D13^2/4</f>
         <v/>
       </c>
-      <c r="L13" s="49">
+      <c r="L13" s="50">
         <f>H13*D13+I13*D13^2/2+J13*D13^3/3-E13</f>
         <v/>
       </c>
@@ -2001,15 +2792,15 @@
         <f>-LN(C14/C13)</f>
         <v/>
       </c>
-      <c r="F14" s="48">
+      <c r="F14" s="49">
         <f>E14/D14</f>
         <v/>
       </c>
-      <c r="G14" s="48">
+      <c r="G14" s="49">
         <f>(F14+F15)/2</f>
         <v/>
       </c>
-      <c r="H14" s="48">
+      <c r="H14" s="49">
         <f>G13</f>
         <v/>
       </c>
@@ -2021,11 +2812,11 @@
         <f>3*(G14-G13)/D14^2-6*(E14-G13*D14)/D14^3</f>
         <v/>
       </c>
-      <c r="K14" s="48">
+      <c r="K14" s="49">
         <f>H14+I14*D14/2+J14*D14^2/4</f>
         <v/>
       </c>
-      <c r="L14" s="49">
+      <c r="L14" s="50">
         <f>H14*D14+I14*D14^2/2+J14*D14^3/3-E14</f>
         <v/>
       </c>
@@ -2051,15 +2842,15 @@
         <f>-LN(C15/C14)</f>
         <v/>
       </c>
-      <c r="F15" s="48">
+      <c r="F15" s="49">
         <f>E15/D15</f>
         <v/>
       </c>
-      <c r="G15" s="48">
+      <c r="G15" s="49">
         <f>(F15+F16)/2</f>
         <v/>
       </c>
-      <c r="H15" s="48">
+      <c r="H15" s="49">
         <f>G14</f>
         <v/>
       </c>
@@ -2071,11 +2862,11 @@
         <f>3*(G15-G14)/D15^2-6*(E15-G14*D15)/D15^3</f>
         <v/>
       </c>
-      <c r="K15" s="48">
+      <c r="K15" s="49">
         <f>H15+I15*D15/2+J15*D15^2/4</f>
         <v/>
       </c>
-      <c r="L15" s="49">
+      <c r="L15" s="50">
         <f>H15*D15+I15*D15^2/2+J15*D15^3/3-E15</f>
         <v/>
       </c>
@@ -2101,15 +2892,15 @@
         <f>-LN(C16/C15)</f>
         <v/>
       </c>
-      <c r="F16" s="48">
+      <c r="F16" s="49">
         <f>E16/D16</f>
         <v/>
       </c>
-      <c r="G16" s="48">
+      <c r="G16" s="49">
         <f>(F16+F17)/2</f>
         <v/>
       </c>
-      <c r="H16" s="48">
+      <c r="H16" s="49">
         <f>G15</f>
         <v/>
       </c>
@@ -2121,11 +2912,11 @@
         <f>3*(G16-G15)/D16^2-6*(E16-G15*D16)/D16^3</f>
         <v/>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="49">
         <f>H16+I16*D16/2+J16*D16^2/4</f>
         <v/>
       </c>
-      <c r="L16" s="49">
+      <c r="L16" s="50">
         <f>H16*D16+I16*D16^2/2+J16*D16^3/3-E16</f>
         <v/>
       </c>
@@ -2151,15 +2942,15 @@
         <f>-LN(C17/C16)</f>
         <v/>
       </c>
-      <c r="F17" s="48">
+      <c r="F17" s="49">
         <f>E17/D17</f>
         <v/>
       </c>
-      <c r="G17" s="48">
+      <c r="G17" s="49">
         <f>(F17+F18)/2</f>
         <v/>
       </c>
-      <c r="H17" s="48">
+      <c r="H17" s="49">
         <f>G16</f>
         <v/>
       </c>
@@ -2171,11 +2962,11 @@
         <f>3*(G17-G16)/D17^2-6*(E17-G16*D17)/D17^3</f>
         <v/>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="49">
         <f>H17+I17*D17/2+J17*D17^2/4</f>
         <v/>
       </c>
-      <c r="L17" s="49">
+      <c r="L17" s="50">
         <f>H17*D17+I17*D17^2/2+J17*D17^3/3-E17</f>
         <v/>
       </c>
@@ -2201,15 +2992,15 @@
         <f>-LN(C18/C17)</f>
         <v/>
       </c>
-      <c r="F18" s="48">
+      <c r="F18" s="49">
         <f>E18/D18</f>
         <v/>
       </c>
-      <c r="G18" s="48">
+      <c r="G18" s="49">
         <f>(F18+F19)/2</f>
         <v/>
       </c>
-      <c r="H18" s="48">
+      <c r="H18" s="49">
         <f>G17</f>
         <v/>
       </c>
@@ -2221,11 +3012,11 @@
         <f>3*(G18-G17)/D18^2-6*(E18-G17*D18)/D18^3</f>
         <v/>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="49">
         <f>H18+I18*D18/2+J18*D18^2/4</f>
         <v/>
       </c>
-      <c r="L18" s="49">
+      <c r="L18" s="50">
         <f>H18*D18+I18*D18^2/2+J18*D18^3/3-E18</f>
         <v/>
       </c>
@@ -2251,15 +3042,15 @@
         <f>-LN(C19/C18)</f>
         <v/>
       </c>
-      <c r="F19" s="48">
+      <c r="F19" s="49">
         <f>E19/D19</f>
         <v/>
       </c>
-      <c r="G19" s="48">
+      <c r="G19" s="49">
         <f>(F19+F20)/2</f>
         <v/>
       </c>
-      <c r="H19" s="48">
+      <c r="H19" s="49">
         <f>G18</f>
         <v/>
       </c>
@@ -2271,11 +3062,11 @@
         <f>3*(G19-G18)/D19^2-6*(E19-G18*D19)/D19^3</f>
         <v/>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="49">
         <f>H19+I19*D19/2+J19*D19^2/4</f>
         <v/>
       </c>
-      <c r="L19" s="49">
+      <c r="L19" s="50">
         <f>H19*D19+I19*D19^2/2+J19*D19^3/3-E19</f>
         <v/>
       </c>
@@ -2301,15 +3092,15 @@
         <f>-LN(C20/C19)</f>
         <v/>
       </c>
-      <c r="F20" s="48">
+      <c r="F20" s="49">
         <f>E20/D20</f>
         <v/>
       </c>
-      <c r="G20" s="48">
+      <c r="G20" s="49">
         <f>(F20+F21)/2</f>
         <v/>
       </c>
-      <c r="H20" s="48">
+      <c r="H20" s="49">
         <f>G19</f>
         <v/>
       </c>
@@ -2321,11 +3112,11 @@
         <f>3*(G20-G19)/D20^2-6*(E20-G19*D20)/D20^3</f>
         <v/>
       </c>
-      <c r="K20" s="48">
+      <c r="K20" s="49">
         <f>H20+I20*D20/2+J20*D20^2/4</f>
         <v/>
       </c>
-      <c r="L20" s="49">
+      <c r="L20" s="50">
         <f>H20*D20+I20*D20^2/2+J20*D20^3/3-E20</f>
         <v/>
       </c>
@@ -2351,15 +3142,15 @@
         <f>-LN(C21/C20)</f>
         <v/>
       </c>
-      <c r="F21" s="48">
+      <c r="F21" s="49">
         <f>E21/D21</f>
         <v/>
       </c>
-      <c r="G21" s="48">
+      <c r="G21" s="49">
         <f>(F21+F22)/2</f>
         <v/>
       </c>
-      <c r="H21" s="48">
+      <c r="H21" s="49">
         <f>G20</f>
         <v/>
       </c>
@@ -2371,11 +3162,11 @@
         <f>3*(G21-G20)/D21^2-6*(E21-G20*D21)/D21^3</f>
         <v/>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="49">
         <f>H21+I21*D21/2+J21*D21^2/4</f>
         <v/>
       </c>
-      <c r="L21" s="49">
+      <c r="L21" s="50">
         <f>H21*D21+I21*D21^2/2+J21*D21^3/3-E21</f>
         <v/>
       </c>
@@ -2401,15 +3192,15 @@
         <f>-LN(C22/C21)</f>
         <v/>
       </c>
-      <c r="F22" s="48">
+      <c r="F22" s="49">
         <f>E22/D22</f>
         <v/>
       </c>
-      <c r="G22" s="48">
+      <c r="G22" s="49">
         <f>(F22+F23)/2</f>
         <v/>
       </c>
-      <c r="H22" s="48">
+      <c r="H22" s="49">
         <f>G21</f>
         <v/>
       </c>
@@ -2421,11 +3212,11 @@
         <f>3*(G22-G21)/D22^2-6*(E22-G21*D22)/D22^3</f>
         <v/>
       </c>
-      <c r="K22" s="48">
+      <c r="K22" s="49">
         <f>H22+I22*D22/2+J22*D22^2/4</f>
         <v/>
       </c>
-      <c r="L22" s="49">
+      <c r="L22" s="50">
         <f>H22*D22+I22*D22^2/2+J22*D22^3/3-E22</f>
         <v/>
       </c>
@@ -2451,15 +3242,15 @@
         <f>-LN(C23/C22)</f>
         <v/>
       </c>
-      <c r="F23" s="48">
+      <c r="F23" s="49">
         <f>E23/D23</f>
         <v/>
       </c>
-      <c r="G23" s="48">
+      <c r="G23" s="49">
         <f>(F23+F24)/2</f>
         <v/>
       </c>
-      <c r="H23" s="48">
+      <c r="H23" s="49">
         <f>G22</f>
         <v/>
       </c>
@@ -2471,11 +3262,11 @@
         <f>3*(G23-G22)/D23^2-6*(E23-G22*D23)/D23^3</f>
         <v/>
       </c>
-      <c r="K23" s="48">
+      <c r="K23" s="49">
         <f>H23+I23*D23/2+J23*D23^2/4</f>
         <v/>
       </c>
-      <c r="L23" s="49">
+      <c r="L23" s="50">
         <f>H23*D23+I23*D23^2/2+J23*D23^3/3-E23</f>
         <v/>
       </c>
@@ -2501,15 +3292,15 @@
         <f>-LN(C24/C23)</f>
         <v/>
       </c>
-      <c r="F24" s="48">
+      <c r="F24" s="49">
         <f>E24/D24</f>
         <v/>
       </c>
-      <c r="G24" s="48">
+      <c r="G24" s="49">
         <f>(F24+F25)/2</f>
         <v/>
       </c>
-      <c r="H24" s="48">
+      <c r="H24" s="49">
         <f>G23</f>
         <v/>
       </c>
@@ -2521,11 +3312,11 @@
         <f>3*(G24-G23)/D24^2-6*(E24-G23*D24)/D24^3</f>
         <v/>
       </c>
-      <c r="K24" s="48">
+      <c r="K24" s="49">
         <f>H24+I24*D24/2+J24*D24^2/4</f>
         <v/>
       </c>
-      <c r="L24" s="49">
+      <c r="L24" s="50">
         <f>H24*D24+I24*D24^2/2+J24*D24^3/3-E24</f>
         <v/>
       </c>
@@ -2551,15 +3342,15 @@
         <f>-LN(C25/C24)</f>
         <v/>
       </c>
-      <c r="F25" s="48">
+      <c r="F25" s="49">
         <f>E25/D25</f>
         <v/>
       </c>
-      <c r="G25" s="48">
+      <c r="G25" s="49">
         <f>(F25+F26)/2</f>
         <v/>
       </c>
-      <c r="H25" s="48">
+      <c r="H25" s="49">
         <f>G24</f>
         <v/>
       </c>
@@ -2571,11 +3362,11 @@
         <f>3*(G25-G24)/D25^2-6*(E25-G24*D25)/D25^3</f>
         <v/>
       </c>
-      <c r="K25" s="48">
+      <c r="K25" s="49">
         <f>H25+I25*D25/2+J25*D25^2/4</f>
         <v/>
       </c>
-      <c r="L25" s="49">
+      <c r="L25" s="50">
         <f>H25*D25+I25*D25^2/2+J25*D25^3/3-E25</f>
         <v/>
       </c>
@@ -2601,15 +3392,15 @@
         <f>-LN(C26/C25)</f>
         <v/>
       </c>
-      <c r="F26" s="48">
+      <c r="F26" s="49">
         <f>E26/D26</f>
         <v/>
       </c>
-      <c r="G26" s="48">
+      <c r="G26" s="49">
         <f>(F26+F27)/2</f>
         <v/>
       </c>
-      <c r="H26" s="48">
+      <c r="H26" s="49">
         <f>G25</f>
         <v/>
       </c>
@@ -2621,11 +3412,11 @@
         <f>3*(G26-G25)/D26^2-6*(E26-G25*D26)/D26^3</f>
         <v/>
       </c>
-      <c r="K26" s="48">
+      <c r="K26" s="49">
         <f>H26+I26*D26/2+J26*D26^2/4</f>
         <v/>
       </c>
-      <c r="L26" s="49">
+      <c r="L26" s="50">
         <f>H26*D26+I26*D26^2/2+J26*D26^3/3-E26</f>
         <v/>
       </c>
@@ -2651,15 +3442,15 @@
         <f>-LN(C27/C26)</f>
         <v/>
       </c>
-      <c r="F27" s="48">
+      <c r="F27" s="49">
         <f>E27/D27</f>
         <v/>
       </c>
-      <c r="G27" s="48">
+      <c r="G27" s="49">
         <f>(F27+F28)/2</f>
         <v/>
       </c>
-      <c r="H27" s="48">
+      <c r="H27" s="49">
         <f>G26</f>
         <v/>
       </c>
@@ -2671,11 +3462,11 @@
         <f>3*(G27-G26)/D27^2-6*(E27-G26*D27)/D27^3</f>
         <v/>
       </c>
-      <c r="K27" s="48">
+      <c r="K27" s="49">
         <f>H27+I27*D27/2+J27*D27^2/4</f>
         <v/>
       </c>
-      <c r="L27" s="49">
+      <c r="L27" s="50">
         <f>H27*D27+I27*D27^2/2+J27*D27^3/3-E27</f>
         <v/>
       </c>
@@ -2701,15 +3492,15 @@
         <f>-LN(C28/C27)</f>
         <v/>
       </c>
-      <c r="F28" s="48">
+      <c r="F28" s="49">
         <f>E28/D28</f>
         <v/>
       </c>
-      <c r="G28" s="48">
+      <c r="G28" s="49">
         <f>(F28+F29)/2</f>
         <v/>
       </c>
-      <c r="H28" s="48">
+      <c r="H28" s="49">
         <f>G27</f>
         <v/>
       </c>
@@ -2721,11 +3512,11 @@
         <f>3*(G28-G27)/D28^2-6*(E28-G27*D28)/D28^3</f>
         <v/>
       </c>
-      <c r="K28" s="48">
+      <c r="K28" s="49">
         <f>H28+I28*D28/2+J28*D28^2/4</f>
         <v/>
       </c>
-      <c r="L28" s="49">
+      <c r="L28" s="50">
         <f>H28*D28+I28*D28^2/2+J28*D28^3/3-E28</f>
         <v/>
       </c>
@@ -2751,15 +3542,15 @@
         <f>-LN(C29/C28)</f>
         <v/>
       </c>
-      <c r="F29" s="48">
+      <c r="F29" s="49">
         <f>E29/D29</f>
         <v/>
       </c>
-      <c r="G29" s="48">
+      <c r="G29" s="49">
         <f>(F29+F30)/2</f>
         <v/>
       </c>
-      <c r="H29" s="48">
+      <c r="H29" s="49">
         <f>G28</f>
         <v/>
       </c>
@@ -2771,11 +3562,11 @@
         <f>3*(G29-G28)/D29^2-6*(E29-G28*D29)/D29^3</f>
         <v/>
       </c>
-      <c r="K29" s="48">
+      <c r="K29" s="49">
         <f>H29+I29*D29/2+J29*D29^2/4</f>
         <v/>
       </c>
-      <c r="L29" s="49">
+      <c r="L29" s="50">
         <f>H29*D29+I29*D29^2/2+J29*D29^3/3-E29</f>
         <v/>
       </c>
@@ -2801,15 +3592,15 @@
         <f>-LN(C30/C29)</f>
         <v/>
       </c>
-      <c r="F30" s="48">
+      <c r="F30" s="49">
         <f>E30/D30</f>
         <v/>
       </c>
-      <c r="G30" s="48">
+      <c r="G30" s="49">
         <f>(F30+F31)/2</f>
         <v/>
       </c>
-      <c r="H30" s="48">
+      <c r="H30" s="49">
         <f>G29</f>
         <v/>
       </c>
@@ -2821,11 +3612,11 @@
         <f>3*(G30-G29)/D30^2-6*(E30-G29*D30)/D30^3</f>
         <v/>
       </c>
-      <c r="K30" s="48">
+      <c r="K30" s="49">
         <f>H30+I30*D30/2+J30*D30^2/4</f>
         <v/>
       </c>
-      <c r="L30" s="49">
+      <c r="L30" s="50">
         <f>H30*D30+I30*D30^2/2+J30*D30^3/3-E30</f>
         <v/>
       </c>
@@ -2851,15 +3642,15 @@
         <f>-LN(C31/C30)</f>
         <v/>
       </c>
-      <c r="F31" s="48">
+      <c r="F31" s="49">
         <f>E31/D31</f>
         <v/>
       </c>
-      <c r="G31" s="48">
+      <c r="G31" s="49">
         <f>(F31+F32)/2</f>
         <v/>
       </c>
-      <c r="H31" s="48">
+      <c r="H31" s="49">
         <f>G30</f>
         <v/>
       </c>
@@ -2871,11 +3662,11 @@
         <f>3*(G31-G30)/D31^2-6*(E31-G30*D31)/D31^3</f>
         <v/>
       </c>
-      <c r="K31" s="48">
+      <c r="K31" s="49">
         <f>H31+I31*D31/2+J31*D31^2/4</f>
         <v/>
       </c>
-      <c r="L31" s="49">
+      <c r="L31" s="50">
         <f>H31*D31+I31*D31^2/2+J31*D31^3/3-E31</f>
         <v/>
       </c>
@@ -2901,15 +3692,15 @@
         <f>-LN(C32/C31)</f>
         <v/>
       </c>
-      <c r="F32" s="48">
+      <c r="F32" s="49">
         <f>E32/D32</f>
         <v/>
       </c>
-      <c r="G32" s="48">
+      <c r="G32" s="49">
         <f>(F32+F33)/2</f>
         <v/>
       </c>
-      <c r="H32" s="48">
+      <c r="H32" s="49">
         <f>G31</f>
         <v/>
       </c>
@@ -2921,11 +3712,11 @@
         <f>3*(G32-G31)/D32^2-6*(E32-G31*D32)/D32^3</f>
         <v/>
       </c>
-      <c r="K32" s="48">
+      <c r="K32" s="49">
         <f>H32+I32*D32/2+J32*D32^2/4</f>
         <v/>
       </c>
-      <c r="L32" s="49">
+      <c r="L32" s="50">
         <f>H32*D32+I32*D32^2/2+J32*D32^3/3-E32</f>
         <v/>
       </c>
@@ -2951,15 +3742,15 @@
         <f>-LN(C33/C32)</f>
         <v/>
       </c>
-      <c r="F33" s="48">
+      <c r="F33" s="49">
         <f>E33/D33</f>
         <v/>
       </c>
-      <c r="G33" s="48">
+      <c r="G33" s="49">
         <f>(F33+F34)/2</f>
         <v/>
       </c>
-      <c r="H33" s="48">
+      <c r="H33" s="49">
         <f>G32</f>
         <v/>
       </c>
@@ -2971,11 +3762,11 @@
         <f>3*(G33-G32)/D33^2-6*(E33-G32*D33)/D33^3</f>
         <v/>
       </c>
-      <c r="K33" s="48">
+      <c r="K33" s="49">
         <f>H33+I33*D33/2+J33*D33^2/4</f>
         <v/>
       </c>
-      <c r="L33" s="49">
+      <c r="L33" s="50">
         <f>H33*D33+I33*D33^2/2+J33*D33^3/3-E33</f>
         <v/>
       </c>
@@ -3001,15 +3792,15 @@
         <f>-LN(C34/C33)</f>
         <v/>
       </c>
-      <c r="F34" s="48">
+      <c r="F34" s="49">
         <f>E34/D34</f>
         <v/>
       </c>
-      <c r="G34" s="48">
+      <c r="G34" s="49">
         <f>(F34+F35)/2</f>
         <v/>
       </c>
-      <c r="H34" s="48">
+      <c r="H34" s="49">
         <f>G33</f>
         <v/>
       </c>
@@ -3021,11 +3812,11 @@
         <f>3*(G34-G33)/D34^2-6*(E34-G33*D34)/D34^3</f>
         <v/>
       </c>
-      <c r="K34" s="48">
+      <c r="K34" s="49">
         <f>H34+I34*D34/2+J34*D34^2/4</f>
         <v/>
       </c>
-      <c r="L34" s="49">
+      <c r="L34" s="50">
         <f>H34*D34+I34*D34^2/2+J34*D34^3/3-E34</f>
         <v/>
       </c>
@@ -3051,15 +3842,15 @@
         <f>-LN(C35/C34)</f>
         <v/>
       </c>
-      <c r="F35" s="48">
+      <c r="F35" s="49">
         <f>E35/D35</f>
         <v/>
       </c>
-      <c r="G35" s="48">
+      <c r="G35" s="49">
         <f>(F35+F36)/2</f>
         <v/>
       </c>
-      <c r="H35" s="48">
+      <c r="H35" s="49">
         <f>G34</f>
         <v/>
       </c>
@@ -3071,11 +3862,11 @@
         <f>3*(G35-G34)/D35^2-6*(E35-G34*D35)/D35^3</f>
         <v/>
       </c>
-      <c r="K35" s="48">
+      <c r="K35" s="49">
         <f>H35+I35*D35/2+J35*D35^2/4</f>
         <v/>
       </c>
-      <c r="L35" s="49">
+      <c r="L35" s="50">
         <f>H35*D35+I35*D35^2/2+J35*D35^3/3-E35</f>
         <v/>
       </c>
@@ -3101,15 +3892,15 @@
         <f>-LN(C36/C35)</f>
         <v/>
       </c>
-      <c r="F36" s="48">
+      <c r="F36" s="49">
         <f>E36/D36</f>
         <v/>
       </c>
-      <c r="G36" s="48">
+      <c r="G36" s="49">
         <f>(F36+F37)/2</f>
         <v/>
       </c>
-      <c r="H36" s="48">
+      <c r="H36" s="49">
         <f>G35</f>
         <v/>
       </c>
@@ -3121,11 +3912,11 @@
         <f>3*(G36-G35)/D36^2-6*(E36-G35*D36)/D36^3</f>
         <v/>
       </c>
-      <c r="K36" s="48">
+      <c r="K36" s="49">
         <f>H36+I36*D36/2+J36*D36^2/4</f>
         <v/>
       </c>
-      <c r="L36" s="49">
+      <c r="L36" s="50">
         <f>H36*D36+I36*D36^2/2+J36*D36^3/3-E36</f>
         <v/>
       </c>
@@ -3151,15 +3942,15 @@
         <f>-LN(C37/C36)</f>
         <v/>
       </c>
-      <c r="F37" s="48">
+      <c r="F37" s="49">
         <f>E37/D37</f>
         <v/>
       </c>
-      <c r="G37" s="48">
+      <c r="G37" s="49">
         <f>(F37+F38)/2</f>
         <v/>
       </c>
-      <c r="H37" s="48">
+      <c r="H37" s="49">
         <f>G36</f>
         <v/>
       </c>
@@ -3171,11 +3962,11 @@
         <f>3*(G37-G36)/D37^2-6*(E37-G36*D37)/D37^3</f>
         <v/>
       </c>
-      <c r="K37" s="48">
+      <c r="K37" s="49">
         <f>H37+I37*D37/2+J37*D37^2/4</f>
         <v/>
       </c>
-      <c r="L37" s="49">
+      <c r="L37" s="50">
         <f>H37*D37+I37*D37^2/2+J37*D37^3/3-E37</f>
         <v/>
       </c>
@@ -3201,15 +3992,15 @@
         <f>-LN(C38/C37)</f>
         <v/>
       </c>
-      <c r="F38" s="48">
+      <c r="F38" s="49">
         <f>E38/D38</f>
         <v/>
       </c>
-      <c r="G38" s="48">
+      <c r="G38" s="49">
         <f>(F38+F39)/2</f>
         <v/>
       </c>
-      <c r="H38" s="48">
+      <c r="H38" s="49">
         <f>G37</f>
         <v/>
       </c>
@@ -3221,11 +4012,11 @@
         <f>3*(G38-G37)/D38^2-6*(E38-G37*D38)/D38^3</f>
         <v/>
       </c>
-      <c r="K38" s="48">
+      <c r="K38" s="49">
         <f>H38+I38*D38/2+J38*D38^2/4</f>
         <v/>
       </c>
-      <c r="L38" s="49">
+      <c r="L38" s="50">
         <f>H38*D38+I38*D38^2/2+J38*D38^3/3-E38</f>
         <v/>
       </c>
@@ -3251,15 +4042,15 @@
         <f>-LN(C39/C38)</f>
         <v/>
       </c>
-      <c r="F39" s="48">
+      <c r="F39" s="49">
         <f>E39/D39</f>
         <v/>
       </c>
-      <c r="G39" s="48">
+      <c r="G39" s="49">
         <f>(F39+F40)/2</f>
         <v/>
       </c>
-      <c r="H39" s="48">
+      <c r="H39" s="49">
         <f>G38</f>
         <v/>
       </c>
@@ -3271,11 +4062,11 @@
         <f>3*(G39-G38)/D39^2-6*(E39-G38*D39)/D39^3</f>
         <v/>
       </c>
-      <c r="K39" s="48">
+      <c r="K39" s="49">
         <f>H39+I39*D39/2+J39*D39^2/4</f>
         <v/>
       </c>
-      <c r="L39" s="49">
+      <c r="L39" s="50">
         <f>H39*D39+I39*D39^2/2+J39*D39^3/3-E39</f>
         <v/>
       </c>
@@ -3301,15 +4092,15 @@
         <f>-LN(C40/C39)</f>
         <v/>
       </c>
-      <c r="F40" s="48">
+      <c r="F40" s="49">
         <f>E40/D40</f>
         <v/>
       </c>
-      <c r="G40" s="48">
+      <c r="G40" s="49">
         <f>F40</f>
         <v/>
       </c>
-      <c r="H40" s="48">
+      <c r="H40" s="49">
         <f>G39</f>
         <v/>
       </c>
@@ -3321,11 +4112,11 @@
         <f>3*(G40-G39)/D40^2-6*(E40-G39*D40)/D40^3</f>
         <v/>
       </c>
-      <c r="K40" s="48">
+      <c r="K40" s="49">
         <f>H40+I40*D40/2+J40*D40^2/4</f>
         <v/>
       </c>
-      <c r="L40" s="49">
+      <c r="L40" s="50">
         <f>H40*D40+I40*D40^2/2+J40*D40^3/3-E40</f>
         <v/>
       </c>
@@ -9369,6 +10160,1731 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L49"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Curve_Interface</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Shared discounting D(0,t): interpolates the SOFR Bootstrap curve to ANY date (piecewise-flat forward). One function used by both Swap_Pricer and the CDS module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Piecewise-flat instantaneous-forward interpolation — the SOFR curve's own baseline method. For t in (T_prev, T_next]: f = −ln(D_next/D_prev)/(T_next−T_prev), then D(0,t) = D_prev·exp(−f·(t−T_prev)). The demo rows are the STANDARD quarterly CDS dates (20 Mar/Jun/Sep/Dec) out to 10Y — proving the curve returns a discount factor on every CDS payment date even though those dates don't coincide with the SOFR pillars. A CDS schedule just references this same formula, so any change to fixings/futures/OIS/interpolation flows straight through. Curve grid (spot + Bootstrap pillars) is in cols K:L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Curve grid (from Bootstrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Valuation:</t>
+        </is>
+      </c>
+      <c r="B7" s="34">
+        <f>VAL_DATE</f>
+        <v/>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Spot:</t>
+        </is>
+      </c>
+      <c r="D7" s="34">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>1st CDS date:</t>
+        </is>
+      </c>
+      <c r="F7" s="34">
+        <f>IF(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20)&gt;=VAL_DATE,DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),EDATE(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),3))</f>
+        <v/>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="K8" s="18">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="L8" s="33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Coupon #</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Time from val (yrs)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Prev SOFR pillar</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Next SOFR pillar</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Segment fwd (%)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Interp DF  D(0,t)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>Interp zero (%)</t>
+        </is>
+      </c>
+      <c r="K9" s="18">
+        <f>Bootstrap!B8</f>
+        <v/>
+      </c>
+      <c r="L9" s="33">
+        <f>Bootstrap!H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="18">
+        <f>EDATE($F$7,3*0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="28">
+        <f>(B10-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D10" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B10,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B10,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1)))/((E10-D10)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G10" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1))*EXP(-(F10/100)*(B10-D10)/365)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>-LN(G10)/C10*100</f>
+        <v/>
+      </c>
+      <c r="K10" s="18">
+        <f>Bootstrap!B9</f>
+        <v/>
+      </c>
+      <c r="L10" s="33">
+        <f>Bootstrap!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="18">
+        <f>EDATE($F$7,3*1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="28">
+        <f>(B11-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D11" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B11,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E11" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B11,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1)))/((E11-D11)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G11" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1))*EXP(-(F11/100)*(B11-D11)/365)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>-LN(G11)/C11*100</f>
+        <v/>
+      </c>
+      <c r="K11" s="18">
+        <f>Bootstrap!B10</f>
+        <v/>
+      </c>
+      <c r="L11" s="33">
+        <f>Bootstrap!H10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18">
+        <f>EDATE($F$7,3*2)</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>(B12-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B12,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B12,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1)))/((E12-D12)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G12" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1))*EXP(-(F12/100)*(B12-D12)/365)</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>-LN(G12)/C12*100</f>
+        <v/>
+      </c>
+      <c r="K12" s="18">
+        <f>Bootstrap!B11</f>
+        <v/>
+      </c>
+      <c r="L12" s="33">
+        <f>Bootstrap!H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="18">
+        <f>EDATE($F$7,3*3)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>(B13-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D13" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B13,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B13,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1)))/((E13-D13)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G13" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1))*EXP(-(F13/100)*(B13-D13)/365)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>-LN(G13)/C13*100</f>
+        <v/>
+      </c>
+      <c r="K13" s="18">
+        <f>Bootstrap!B12</f>
+        <v/>
+      </c>
+      <c r="L13" s="33">
+        <f>Bootstrap!H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="18">
+        <f>EDATE($F$7,3*4)</f>
+        <v/>
+      </c>
+      <c r="C14" s="28">
+        <f>(B14-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B14,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B14,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1)))/((E14-D14)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1))*EXP(-(F14/100)*(B14-D14)/365)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>-LN(G14)/C14*100</f>
+        <v/>
+      </c>
+      <c r="K14" s="18">
+        <f>Bootstrap!B13</f>
+        <v/>
+      </c>
+      <c r="L14" s="33">
+        <f>Bootstrap!H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="18">
+        <f>EDATE($F$7,3*5)</f>
+        <v/>
+      </c>
+      <c r="C15" s="28">
+        <f>(B15-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D15" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B15,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B15,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1)))/((E15-D15)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1))*EXP(-(F15/100)*(B15-D15)/365)</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>-LN(G15)/C15*100</f>
+        <v/>
+      </c>
+      <c r="K15" s="18">
+        <f>Bootstrap!B14</f>
+        <v/>
+      </c>
+      <c r="L15" s="33">
+        <f>Bootstrap!H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="18">
+        <f>EDATE($F$7,3*6)</f>
+        <v/>
+      </c>
+      <c r="C16" s="28">
+        <f>(B16-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B16,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B16,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1)))/((E16-D16)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1))*EXP(-(F16/100)*(B16-D16)/365)</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>-LN(G16)/C16*100</f>
+        <v/>
+      </c>
+      <c r="K16" s="18">
+        <f>Bootstrap!B15</f>
+        <v/>
+      </c>
+      <c r="L16" s="33">
+        <f>Bootstrap!H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="18">
+        <f>EDATE($F$7,3*7)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>(B17-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D17" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B17,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E17" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B17,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1)))/((E17-D17)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1))*EXP(-(F17/100)*(B17-D17)/365)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>-LN(G17)/C17*100</f>
+        <v/>
+      </c>
+      <c r="K17" s="18">
+        <f>Bootstrap!B16</f>
+        <v/>
+      </c>
+      <c r="L17" s="33">
+        <f>Bootstrap!H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="18">
+        <f>EDATE($F$7,3*8)</f>
+        <v/>
+      </c>
+      <c r="C18" s="28">
+        <f>(B18-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B18,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E18" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B18,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1)))/((E18-D18)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G18" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1))*EXP(-(F18/100)*(B18-D18)/365)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>-LN(G18)/C18*100</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
+        <f>Bootstrap!B17</f>
+        <v/>
+      </c>
+      <c r="L18" s="33">
+        <f>Bootstrap!H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="18">
+        <f>EDATE($F$7,3*9)</f>
+        <v/>
+      </c>
+      <c r="C19" s="28">
+        <f>(B19-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D19" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B19,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E19" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B19,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F19" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1)))/((E19-D19)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G19" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1))*EXP(-(F19/100)*(B19-D19)/365)</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>-LN(G19)/C19*100</f>
+        <v/>
+      </c>
+      <c r="K19" s="18">
+        <f>Bootstrap!B18</f>
+        <v/>
+      </c>
+      <c r="L19" s="33">
+        <f>Bootstrap!H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="18">
+        <f>EDATE($F$7,3*10)</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>(B20-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B20,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B20,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1)))/((E20-D20)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1))*EXP(-(F20/100)*(B20-D20)/365)</f>
+        <v/>
+      </c>
+      <c r="H20" s="17">
+        <f>-LN(G20)/C20*100</f>
+        <v/>
+      </c>
+      <c r="K20" s="18">
+        <f>Bootstrap!B19</f>
+        <v/>
+      </c>
+      <c r="L20" s="33">
+        <f>Bootstrap!H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="18">
+        <f>EDATE($F$7,3*11)</f>
+        <v/>
+      </c>
+      <c r="C21" s="28">
+        <f>(B21-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D21" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B21,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E21" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B21,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1)))/((E21-D21)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1))*EXP(-(F21/100)*(B21-D21)/365)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
+        <f>-LN(G21)/C21*100</f>
+        <v/>
+      </c>
+      <c r="K21" s="18">
+        <f>Bootstrap!B20</f>
+        <v/>
+      </c>
+      <c r="L21" s="33">
+        <f>Bootstrap!H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="18">
+        <f>EDATE($F$7,3*12)</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>(B22-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D22" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B22,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E22" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B22,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1)))/((E22-D22)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1))*EXP(-(F22/100)*(B22-D22)/365)</f>
+        <v/>
+      </c>
+      <c r="H22" s="17">
+        <f>-LN(G22)/C22*100</f>
+        <v/>
+      </c>
+      <c r="K22" s="18">
+        <f>Bootstrap!B21</f>
+        <v/>
+      </c>
+      <c r="L22" s="33">
+        <f>Bootstrap!H21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="18">
+        <f>EDATE($F$7,3*13)</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>(B23-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B23,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E23" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B23,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1)))/((E23-D23)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1))*EXP(-(F23/100)*(B23-D23)/365)</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>-LN(G23)/C23*100</f>
+        <v/>
+      </c>
+      <c r="K23" s="18">
+        <f>Bootstrap!B22</f>
+        <v/>
+      </c>
+      <c r="L23" s="33">
+        <f>Bootstrap!H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="18">
+        <f>EDATE($F$7,3*14)</f>
+        <v/>
+      </c>
+      <c r="C24" s="28">
+        <f>(B24-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D24" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B24,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E24" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B24,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1)))/((E24-D24)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1))*EXP(-(F24/100)*(B24-D24)/365)</f>
+        <v/>
+      </c>
+      <c r="H24" s="17">
+        <f>-LN(G24)/C24*100</f>
+        <v/>
+      </c>
+      <c r="K24" s="18">
+        <f>Bootstrap!B23</f>
+        <v/>
+      </c>
+      <c r="L24" s="33">
+        <f>Bootstrap!H23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="18">
+        <f>EDATE($F$7,3*15)</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>(B25-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D25" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B25,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B25,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1)))/((E25-D25)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G25" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1))*EXP(-(F25/100)*(B25-D25)/365)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>-LN(G25)/C25*100</f>
+        <v/>
+      </c>
+      <c r="K25" s="18">
+        <f>Bootstrap!B24</f>
+        <v/>
+      </c>
+      <c r="L25" s="33">
+        <f>Bootstrap!H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="18">
+        <f>EDATE($F$7,3*16)</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>(B26-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D26" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B26,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E26" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B26,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F26" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1)))/((E26-D26)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G26" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1))*EXP(-(F26/100)*(B26-D26)/365)</f>
+        <v/>
+      </c>
+      <c r="H26" s="17">
+        <f>-LN(G26)/C26*100</f>
+        <v/>
+      </c>
+      <c r="K26" s="18">
+        <f>Bootstrap!B25</f>
+        <v/>
+      </c>
+      <c r="L26" s="33">
+        <f>Bootstrap!H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="18">
+        <f>EDATE($F$7,3*17)</f>
+        <v/>
+      </c>
+      <c r="C27" s="28">
+        <f>(B27-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B27,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E27" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B27,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1)))/((E27-D27)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1))*EXP(-(F27/100)*(B27-D27)/365)</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>-LN(G27)/C27*100</f>
+        <v/>
+      </c>
+      <c r="K27" s="18">
+        <f>Bootstrap!B26</f>
+        <v/>
+      </c>
+      <c r="L27" s="33">
+        <f>Bootstrap!H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="18">
+        <f>EDATE($F$7,3*18)</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>(B28-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D28" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B28,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E28" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B28,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1)))/((E28-D28)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G28" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1))*EXP(-(F28/100)*(B28-D28)/365)</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
+        <f>-LN(G28)/C28*100</f>
+        <v/>
+      </c>
+      <c r="K28" s="18">
+        <f>Bootstrap!B27</f>
+        <v/>
+      </c>
+      <c r="L28" s="33">
+        <f>Bootstrap!H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="18">
+        <f>EDATE($F$7,3*19)</f>
+        <v/>
+      </c>
+      <c r="C29" s="28">
+        <f>(B29-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D29" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B29,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E29" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B29,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1)))/((E29-D29)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G29" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1))*EXP(-(F29/100)*(B29-D29)/365)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>-LN(G29)/C29*100</f>
+        <v/>
+      </c>
+      <c r="K29" s="18">
+        <f>Bootstrap!B28</f>
+        <v/>
+      </c>
+      <c r="L29" s="33">
+        <f>Bootstrap!H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="18">
+        <f>EDATE($F$7,3*20)</f>
+        <v/>
+      </c>
+      <c r="C30" s="28">
+        <f>(B30-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B30,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E30" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B30,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F30" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1)))/((E30-D30)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G30" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1))*EXP(-(F30/100)*(B30-D30)/365)</f>
+        <v/>
+      </c>
+      <c r="H30" s="17">
+        <f>-LN(G30)/C30*100</f>
+        <v/>
+      </c>
+      <c r="K30" s="18">
+        <f>Bootstrap!B29</f>
+        <v/>
+      </c>
+      <c r="L30" s="33">
+        <f>Bootstrap!H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="18">
+        <f>EDATE($F$7,3*21)</f>
+        <v/>
+      </c>
+      <c r="C31" s="28">
+        <f>(B31-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D31" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B31,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E31" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B31,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1)))/((E31-D31)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G31" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1))*EXP(-(F31/100)*(B31-D31)/365)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>-LN(G31)/C31*100</f>
+        <v/>
+      </c>
+      <c r="K31" s="18">
+        <f>Bootstrap!B30</f>
+        <v/>
+      </c>
+      <c r="L31" s="33">
+        <f>Bootstrap!H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="18">
+        <f>EDATE($F$7,3*22)</f>
+        <v/>
+      </c>
+      <c r="C32" s="28">
+        <f>(B32-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D32" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B32,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B32,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1)))/((E32-D32)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G32" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1))*EXP(-(F32/100)*(B32-D32)/365)</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>-LN(G32)/C32*100</f>
+        <v/>
+      </c>
+      <c r="K32" s="18">
+        <f>Bootstrap!B31</f>
+        <v/>
+      </c>
+      <c r="L32" s="33">
+        <f>Bootstrap!H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="18">
+        <f>EDATE($F$7,3*23)</f>
+        <v/>
+      </c>
+      <c r="C33" s="28">
+        <f>(B33-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D33" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B33,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E33" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B33,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1)))/((E33-D33)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G33" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1))*EXP(-(F33/100)*(B33-D33)/365)</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>-LN(G33)/C33*100</f>
+        <v/>
+      </c>
+      <c r="K33" s="18">
+        <f>Bootstrap!B32</f>
+        <v/>
+      </c>
+      <c r="L33" s="33">
+        <f>Bootstrap!H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="18">
+        <f>EDATE($F$7,3*24)</f>
+        <v/>
+      </c>
+      <c r="C34" s="28">
+        <f>(B34-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D34" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B34,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B34,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1)))/((E34-D34)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G34" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1))*EXP(-(F34/100)*(B34-D34)/365)</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>-LN(G34)/C34*100</f>
+        <v/>
+      </c>
+      <c r="K34" s="18">
+        <f>Bootstrap!B33</f>
+        <v/>
+      </c>
+      <c r="L34" s="33">
+        <f>Bootstrap!H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="18">
+        <f>EDATE($F$7,3*25)</f>
+        <v/>
+      </c>
+      <c r="C35" s="28">
+        <f>(B35-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D35" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B35,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E35" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B35,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1)))/((E35-D35)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G35" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1))*EXP(-(F35/100)*(B35-D35)/365)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>-LN(G35)/C35*100</f>
+        <v/>
+      </c>
+      <c r="K35" s="18">
+        <f>Bootstrap!B34</f>
+        <v/>
+      </c>
+      <c r="L35" s="33">
+        <f>Bootstrap!H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="18">
+        <f>EDATE($F$7,3*26)</f>
+        <v/>
+      </c>
+      <c r="C36" s="28">
+        <f>(B36-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D36" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B36,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E36" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B36,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1)))/((E36-D36)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G36" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1))*EXP(-(F36/100)*(B36-D36)/365)</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>-LN(G36)/C36*100</f>
+        <v/>
+      </c>
+      <c r="K36" s="18">
+        <f>Bootstrap!B35</f>
+        <v/>
+      </c>
+      <c r="L36" s="33">
+        <f>Bootstrap!H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="18">
+        <f>EDATE($F$7,3*27)</f>
+        <v/>
+      </c>
+      <c r="C37" s="28">
+        <f>(B37-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D37" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B37,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E37" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B37,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1)))/((E37-D37)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G37" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1))*EXP(-(F37/100)*(B37-D37)/365)</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>-LN(G37)/C37*100</f>
+        <v/>
+      </c>
+      <c r="K37" s="18">
+        <f>Bootstrap!B36</f>
+        <v/>
+      </c>
+      <c r="L37" s="33">
+        <f>Bootstrap!H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="18">
+        <f>EDATE($F$7,3*28)</f>
+        <v/>
+      </c>
+      <c r="C38" s="28">
+        <f>(B38-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B38,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E38" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B38,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1)))/((E38-D38)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G38" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1))*EXP(-(F38/100)*(B38-D38)/365)</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>-LN(G38)/C38*100</f>
+        <v/>
+      </c>
+      <c r="K38" s="18">
+        <f>Bootstrap!B37</f>
+        <v/>
+      </c>
+      <c r="L38" s="33">
+        <f>Bootstrap!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="18">
+        <f>EDATE($F$7,3*29)</f>
+        <v/>
+      </c>
+      <c r="C39" s="28">
+        <f>(B39-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D39" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B39,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B39,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F39" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1)))/((E39-D39)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G39" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1))*EXP(-(F39/100)*(B39-D39)/365)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>-LN(G39)/C39*100</f>
+        <v/>
+      </c>
+      <c r="K39" s="18">
+        <f>Bootstrap!B38</f>
+        <v/>
+      </c>
+      <c r="L39" s="33">
+        <f>Bootstrap!H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="18">
+        <f>EDATE($F$7,3*30)</f>
+        <v/>
+      </c>
+      <c r="C40" s="28">
+        <f>(B40-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D40" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B40,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E40" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B40,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1)))/((E40-D40)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G40" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1))*EXP(-(F40/100)*(B40-D40)/365)</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
+        <f>-LN(G40)/C40*100</f>
+        <v/>
+      </c>
+      <c r="K40" s="18">
+        <f>Bootstrap!B39</f>
+        <v/>
+      </c>
+      <c r="L40" s="33">
+        <f>Bootstrap!H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="18">
+        <f>EDATE($F$7,3*31)</f>
+        <v/>
+      </c>
+      <c r="C41" s="28">
+        <f>(B41-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D41" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B41,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E41" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B41,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1)))/((E41-D41)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G41" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1))*EXP(-(F41/100)*(B41-D41)/365)</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>-LN(G41)/C41*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="18">
+        <f>EDATE($F$7,3*32)</f>
+        <v/>
+      </c>
+      <c r="C42" s="28">
+        <f>(B42-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D42" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B42,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E42" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B42,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F42" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1)))/((E42-D42)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G42" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1))*EXP(-(F42/100)*(B42-D42)/365)</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>-LN(G42)/C42*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="18">
+        <f>EDATE($F$7,3*33)</f>
+        <v/>
+      </c>
+      <c r="C43" s="28">
+        <f>(B43-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D43" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B43,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E43" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B43,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1)))/((E43-D43)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G43" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1))*EXP(-(F43/100)*(B43-D43)/365)</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>-LN(G43)/C43*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="18">
+        <f>EDATE($F$7,3*34)</f>
+        <v/>
+      </c>
+      <c r="C44" s="28">
+        <f>(B44-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B44,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E44" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B44,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1)))/((E44-D44)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G44" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1))*EXP(-(F44/100)*(B44-D44)/365)</f>
+        <v/>
+      </c>
+      <c r="H44" s="17">
+        <f>-LN(G44)/C44*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="18">
+        <f>EDATE($F$7,3*35)</f>
+        <v/>
+      </c>
+      <c r="C45" s="28">
+        <f>(B45-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B45,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E45" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B45,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1)))/((E45-D45)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G45" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1))*EXP(-(F45/100)*(B45-D45)/365)</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>-LN(G45)/C45*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="B46" s="18">
+        <f>EDATE($F$7,3*36)</f>
+        <v/>
+      </c>
+      <c r="C46" s="28">
+        <f>(B46-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D46" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B46,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E46" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B46,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1)))/((E46-D46)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G46" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1))*EXP(-(F46/100)*(B46-D46)/365)</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>-LN(G46)/C46*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" s="18">
+        <f>EDATE($F$7,3*37)</f>
+        <v/>
+      </c>
+      <c r="C47" s="28">
+        <f>(B47-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D47" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B47,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E47" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B47,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1)))/((E47-D47)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G47" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1))*EXP(-(F47/100)*(B47-D47)/365)</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>-LN(G47)/C47*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="35" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" s="18">
+        <f>EDATE($F$7,3*38)</f>
+        <v/>
+      </c>
+      <c r="C48" s="28">
+        <f>(B48-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D48" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B48,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E48" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B48,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F48" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1)))/((E48-D48)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G48" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1))*EXP(-(F48/100)*(B48-D48)/365)</f>
+        <v/>
+      </c>
+      <c r="H48" s="17">
+        <f>-LN(G48)/C48*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="18">
+        <f>EDATE($F$7,3*39)</f>
+        <v/>
+      </c>
+      <c r="C49" s="28">
+        <f>(B49-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D49" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B49,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E49" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B49,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1)))/((E49-D49)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G49" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1))*EXP(-(F49/100)*(B49-D49)/365)</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>-LN(G49)/C49*100</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A4:H6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9418,12 +11934,12 @@
           <t>Direction (Leg 1 = Fixed)</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="36" t="inlineStr">
         <is>
           <t>Receive fixed</t>
         </is>
       </c>
-      <c r="C5" s="35" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
         </is>
@@ -9445,10 +11961,10 @@
           <t>Notional</t>
         </is>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="38" t="n">
         <v>10000000</v>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>Both legs, USD.</t>
         </is>
@@ -9487,11 +12003,11 @@
           <t>Effective date</t>
         </is>
       </c>
-      <c r="B8" s="37">
+      <c r="B8" s="39">
         <f>Bootstrap!$B$4</f>
         <v/>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="37" t="inlineStr">
         <is>
           <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
         </is>
@@ -9511,10 +12027,10 @@
           <t>Tenor (years)</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n">
+      <c r="B9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>Whole years; drives the annual coupon schedule below.</t>
         </is>
@@ -9538,7 +12054,7 @@
         <f>EDATE(B8,12*B9)</f>
         <v/>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="37" t="inlineStr">
         <is>
           <t>Effective + Tenor.</t>
         </is>
@@ -9558,11 +12074,11 @@
           <t>Fixed coupon (%)</t>
         </is>
       </c>
-      <c r="B11" s="39">
+      <c r="B11" s="41">
         <f>B25</f>
         <v/>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="37" t="inlineStr">
         <is>
           <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
         </is>
@@ -9646,7 +12162,7 @@
         <f>VAL_DATE</f>
         <v/>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="37" t="inlineStr">
         <is>
           <t>Curve is discounted from spot = Bootstrap!B4.</t>
         </is>
@@ -9666,7 +12182,7 @@
           <t>Direction sign (+recv / −pay)</t>
         </is>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="35">
         <f>IF($B$5="Receive fixed",1,-1)</f>
         <v/>
       </c>
@@ -9714,7 +12230,7 @@
         <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))^(($B$8-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))</f>
         <v/>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="37" t="inlineStr">
         <is>
           <t>Interpolated from the curve.</t>
         </is>
@@ -9757,7 +12273,7 @@
         <f>SUM(H36:H85)</f>
         <v/>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="37" t="inlineStr">
         <is>
           <t>Sum of tau·DF over the fixed coupon dates.</t>
         </is>
@@ -9777,7 +12293,7 @@
           <t>Fixed leg PV (coupons)</t>
         </is>
       </c>
-      <c r="B22" s="41">
+      <c r="B22" s="42">
         <f>SUM(G36:G85)</f>
         <v/>
       </c>
@@ -9796,11 +12312,11 @@
           <t>Float leg PV</t>
         </is>
       </c>
-      <c r="B23" s="41">
+      <c r="B23" s="42">
         <f>B6*(B19-B20)</f>
         <v/>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="37" t="inlineStr">
         <is>
           <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
         </is>
@@ -9820,11 +12336,11 @@
           <t>Notional PV @ maturity</t>
         </is>
       </c>
-      <c r="B24" s="41">
+      <c r="B24" s="42">
         <f>B6*B20</f>
         <v/>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="37" t="inlineStr">
         <is>
           <t>For the SWPM-style leg display only.</t>
         </is>
@@ -9848,7 +12364,7 @@
         <f>(B19-B20)/B21*100</f>
         <v/>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="37" t="inlineStr">
         <is>
           <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
         </is>
@@ -9868,11 +12384,11 @@
           <t>Leg 1 NPV  (fixed + notional)</t>
         </is>
       </c>
-      <c r="B26" s="41">
+      <c r="B26" s="42">
         <f>B16*(B22+B24)</f>
         <v/>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="37" t="inlineStr">
         <is>
           <t>SWPM shows each leg incl. a notional redemption.</t>
         </is>
@@ -9892,7 +12408,7 @@
           <t>Leg 2 NPV  (float + notional)</t>
         </is>
       </c>
-      <c r="B27" s="41">
+      <c r="B27" s="42">
         <f>-B16*(B23+B24)</f>
         <v/>
       </c>
@@ -9911,11 +12427,11 @@
           <t>Net swap NPV</t>
         </is>
       </c>
-      <c r="B28" s="42">
+      <c r="B28" s="43">
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="37" t="inlineStr">
         <is>
           <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
         </is>
@@ -9935,11 +12451,11 @@
           <t>PV01 / DV01  (per 1bp)</t>
         </is>
       </c>
-      <c r="B29" s="41">
+      <c r="B29" s="42">
         <f>B6*B21*0.0001</f>
         <v/>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="37" t="inlineStr">
         <is>
           <t>Annuity × notional × 1bp.</t>
         </is>
@@ -9959,7 +12475,7 @@
           <t>Accrued (at inception)</t>
         </is>
       </c>
-      <c r="B30" s="41" t="n">
+      <c r="B30" s="42" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="18">
@@ -10067,7 +12583,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="40">
+      <c r="A36" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10087,11 +12603,11 @@
         <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)))^((B36-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F36" s="41">
+      <c r="F36" s="42">
         <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
         <v/>
       </c>
-      <c r="G36" s="41">
+      <c r="G36" s="42">
         <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
         <v/>
       </c>
@@ -10109,7 +12625,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="40">
+      <c r="A37" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10129,11 +12645,11 @@
         <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)))^((B37-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F37" s="41">
+      <c r="F37" s="42">
         <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
         <v/>
       </c>
-      <c r="G37" s="41">
+      <c r="G37" s="42">
         <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
         <v/>
       </c>
@@ -10151,7 +12667,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="40">
+      <c r="A38" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10171,11 +12687,11 @@
         <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)))^((B38-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="41">
+      <c r="F38" s="42">
         <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
         <v/>
       </c>
-      <c r="G38" s="41">
+      <c r="G38" s="42">
         <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
         <v/>
       </c>
@@ -10193,7 +12709,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="40">
+      <c r="A39" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10213,11 +12729,11 @@
         <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)))^((B39-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F39" s="41">
+      <c r="F39" s="42">
         <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
         <v/>
       </c>
-      <c r="G39" s="41">
+      <c r="G39" s="42">
         <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
         <v/>
       </c>
@@ -10232,7 +12748,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="40">
+      <c r="A40" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10252,11 +12768,11 @@
         <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)))^((B40-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F40" s="41">
+      <c r="F40" s="42">
         <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
         <v/>
       </c>
-      <c r="G40" s="41">
+      <c r="G40" s="42">
         <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
         <v/>
       </c>
@@ -10266,7 +12782,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="40">
+      <c r="A41" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10286,11 +12802,11 @@
         <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)))^((B41-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="41">
+      <c r="F41" s="42">
         <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
         <v/>
       </c>
-      <c r="G41" s="41">
+      <c r="G41" s="42">
         <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
         <v/>
       </c>
@@ -10300,7 +12816,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="40">
+      <c r="A42" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10320,11 +12836,11 @@
         <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)))^((B42-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F42" s="41">
+      <c r="F42" s="42">
         <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
         <v/>
       </c>
-      <c r="G42" s="41">
+      <c r="G42" s="42">
         <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
         <v/>
       </c>
@@ -10334,7 +12850,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="40">
+      <c r="A43" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10354,11 +12870,11 @@
         <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)))^((B43-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F43" s="41">
+      <c r="F43" s="42">
         <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
         <v/>
       </c>
-      <c r="G43" s="41">
+      <c r="G43" s="42">
         <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
         <v/>
       </c>
@@ -10368,7 +12884,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="40">
+      <c r="A44" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10388,11 +12904,11 @@
         <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)))^((B44-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F44" s="41">
+      <c r="F44" s="42">
         <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
         <v/>
       </c>
-      <c r="G44" s="41">
+      <c r="G44" s="42">
         <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
         <v/>
       </c>
@@ -10402,7 +12918,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="40">
+      <c r="A45" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10422,11 +12938,11 @@
         <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)))^((B45-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F45" s="41">
+      <c r="F45" s="42">
         <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
         <v/>
       </c>
-      <c r="G45" s="41">
+      <c r="G45" s="42">
         <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
         <v/>
       </c>
@@ -10436,7 +12952,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="40">
+      <c r="A46" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10456,11 +12972,11 @@
         <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)))^((B46-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F46" s="41">
+      <c r="F46" s="42">
         <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
         <v/>
       </c>
-      <c r="G46" s="41">
+      <c r="G46" s="42">
         <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
         <v/>
       </c>
@@ -10470,7 +12986,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="40">
+      <c r="A47" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10490,11 +13006,11 @@
         <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)))^((B47-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F47" s="41">
+      <c r="F47" s="42">
         <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
         <v/>
       </c>
-      <c r="G47" s="41">
+      <c r="G47" s="42">
         <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
         <v/>
       </c>
@@ -10504,7 +13020,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="40">
+      <c r="A48" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10524,11 +13040,11 @@
         <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)))^((B48-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F48" s="41">
+      <c r="F48" s="42">
         <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
         <v/>
       </c>
-      <c r="G48" s="41">
+      <c r="G48" s="42">
         <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
         <v/>
       </c>
@@ -10538,7 +13054,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="40">
+      <c r="A49" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10558,11 +13074,11 @@
         <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)))^((B49-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="41">
+      <c r="F49" s="42">
         <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
         <v/>
       </c>
-      <c r="G49" s="41">
+      <c r="G49" s="42">
         <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
         <v/>
       </c>
@@ -10572,7 +13088,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="40">
+      <c r="A50" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10592,11 +13108,11 @@
         <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)))^((B50-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F50" s="41">
+      <c r="F50" s="42">
         <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
         <v/>
       </c>
-      <c r="G50" s="41">
+      <c r="G50" s="42">
         <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
         <v/>
       </c>
@@ -10606,7 +13122,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="40">
+      <c r="A51" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10626,11 +13142,11 @@
         <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)))^((B51-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F51" s="41">
+      <c r="F51" s="42">
         <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
         <v/>
       </c>
-      <c r="G51" s="41">
+      <c r="G51" s="42">
         <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
         <v/>
       </c>
@@ -10640,7 +13156,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="40">
+      <c r="A52" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10660,11 +13176,11 @@
         <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)))^((B52-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F52" s="41">
+      <c r="F52" s="42">
         <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
         <v/>
       </c>
-      <c r="G52" s="41">
+      <c r="G52" s="42">
         <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
         <v/>
       </c>
@@ -10674,7 +13190,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="40">
+      <c r="A53" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10694,11 +13210,11 @@
         <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)))^((B53-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F53" s="41">
+      <c r="F53" s="42">
         <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
         <v/>
       </c>
-      <c r="G53" s="41">
+      <c r="G53" s="42">
         <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
         <v/>
       </c>
@@ -10708,7 +13224,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="40">
+      <c r="A54" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10728,11 +13244,11 @@
         <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)))^((B54-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F54" s="41">
+      <c r="F54" s="42">
         <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
         <v/>
       </c>
-      <c r="G54" s="41">
+      <c r="G54" s="42">
         <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
         <v/>
       </c>
@@ -10742,7 +13258,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="40">
+      <c r="A55" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10762,11 +13278,11 @@
         <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)))^((B55-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F55" s="41">
+      <c r="F55" s="42">
         <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
         <v/>
       </c>
-      <c r="G55" s="41">
+      <c r="G55" s="42">
         <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
         <v/>
       </c>
@@ -10776,7 +13292,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="40">
+      <c r="A56" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10796,11 +13312,11 @@
         <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)))^((B56-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F56" s="41">
+      <c r="F56" s="42">
         <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
         <v/>
       </c>
-      <c r="G56" s="41">
+      <c r="G56" s="42">
         <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
         <v/>
       </c>
@@ -10810,7 +13326,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="40">
+      <c r="A57" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10830,11 +13346,11 @@
         <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)))^((B57-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F57" s="41">
+      <c r="F57" s="42">
         <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
         <v/>
       </c>
-      <c r="G57" s="41">
+      <c r="G57" s="42">
         <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
         <v/>
       </c>
@@ -10844,7 +13360,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="40">
+      <c r="A58" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10864,11 +13380,11 @@
         <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)))^((B58-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F58" s="41">
+      <c r="F58" s="42">
         <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
         <v/>
       </c>
-      <c r="G58" s="41">
+      <c r="G58" s="42">
         <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
         <v/>
       </c>
@@ -10878,7 +13394,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="40">
+      <c r="A59" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10898,11 +13414,11 @@
         <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)))^((B59-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F59" s="41">
+      <c r="F59" s="42">
         <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
         <v/>
       </c>
-      <c r="G59" s="41">
+      <c r="G59" s="42">
         <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
         <v/>
       </c>
@@ -10912,7 +13428,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="40">
+      <c r="A60" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10932,11 +13448,11 @@
         <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)))^((B60-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F60" s="41">
+      <c r="F60" s="42">
         <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
         <v/>
       </c>
-      <c r="G60" s="41">
+      <c r="G60" s="42">
         <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
         <v/>
       </c>
@@ -10946,7 +13462,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="40">
+      <c r="A61" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -10966,11 +13482,11 @@
         <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)))^((B61-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F61" s="41">
+      <c r="F61" s="42">
         <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
         <v/>
       </c>
-      <c r="G61" s="41">
+      <c r="G61" s="42">
         <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
         <v/>
       </c>
@@ -10980,7 +13496,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="40">
+      <c r="A62" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11000,11 +13516,11 @@
         <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)))^((B62-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F62" s="41">
+      <c r="F62" s="42">
         <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
         <v/>
       </c>
-      <c r="G62" s="41">
+      <c r="G62" s="42">
         <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
         <v/>
       </c>
@@ -11014,7 +13530,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="40">
+      <c r="A63" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11034,11 +13550,11 @@
         <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)))^((B63-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F63" s="41">
+      <c r="F63" s="42">
         <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
         <v/>
       </c>
-      <c r="G63" s="41">
+      <c r="G63" s="42">
         <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
         <v/>
       </c>
@@ -11048,7 +13564,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="40">
+      <c r="A64" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11068,11 +13584,11 @@
         <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)))^((B64-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F64" s="41">
+      <c r="F64" s="42">
         <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
         <v/>
       </c>
-      <c r="G64" s="41">
+      <c r="G64" s="42">
         <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
         <v/>
       </c>
@@ -11082,7 +13598,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="40">
+      <c r="A65" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11102,11 +13618,11 @@
         <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)))^((B65-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F65" s="41">
+      <c r="F65" s="42">
         <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
         <v/>
       </c>
-      <c r="G65" s="41">
+      <c r="G65" s="42">
         <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
         <v/>
       </c>
@@ -11116,7 +13632,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="40">
+      <c r="A66" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11136,11 +13652,11 @@
         <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)))^((B66-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F66" s="41">
+      <c r="F66" s="42">
         <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
         <v/>
       </c>
-      <c r="G66" s="41">
+      <c r="G66" s="42">
         <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
         <v/>
       </c>
@@ -11150,7 +13666,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="40">
+      <c r="A67" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11170,11 +13686,11 @@
         <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)))^((B67-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F67" s="41">
+      <c r="F67" s="42">
         <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
         <v/>
       </c>
-      <c r="G67" s="41">
+      <c r="G67" s="42">
         <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
         <v/>
       </c>
@@ -11184,7 +13700,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="40">
+      <c r="A68" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11204,11 +13720,11 @@
         <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)))^((B68-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F68" s="41">
+      <c r="F68" s="42">
         <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
         <v/>
       </c>
-      <c r="G68" s="41">
+      <c r="G68" s="42">
         <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
         <v/>
       </c>
@@ -11218,7 +13734,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="40">
+      <c r="A69" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11238,11 +13754,11 @@
         <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)))^((B69-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F69" s="41">
+      <c r="F69" s="42">
         <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
         <v/>
       </c>
-      <c r="G69" s="41">
+      <c r="G69" s="42">
         <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
         <v/>
       </c>
@@ -11252,7 +13768,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="40">
+      <c r="A70" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11272,11 +13788,11 @@
         <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)))^((B70-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F70" s="41">
+      <c r="F70" s="42">
         <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
         <v/>
       </c>
-      <c r="G70" s="41">
+      <c r="G70" s="42">
         <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
         <v/>
       </c>
@@ -11286,7 +13802,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="40">
+      <c r="A71" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11306,11 +13822,11 @@
         <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)))^((B71-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F71" s="41">
+      <c r="F71" s="42">
         <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
         <v/>
       </c>
-      <c r="G71" s="41">
+      <c r="G71" s="42">
         <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
         <v/>
       </c>
@@ -11320,7 +13836,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="40">
+      <c r="A72" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11340,11 +13856,11 @@
         <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)))^((B72-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F72" s="41">
+      <c r="F72" s="42">
         <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
         <v/>
       </c>
-      <c r="G72" s="41">
+      <c r="G72" s="42">
         <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
         <v/>
       </c>
@@ -11354,7 +13870,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="40">
+      <c r="A73" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11374,11 +13890,11 @@
         <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)))^((B73-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F73" s="41">
+      <c r="F73" s="42">
         <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
         <v/>
       </c>
-      <c r="G73" s="41">
+      <c r="G73" s="42">
         <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
         <v/>
       </c>
@@ -11388,7 +13904,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="40">
+      <c r="A74" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11408,11 +13924,11 @@
         <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)))^((B74-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F74" s="41">
+      <c r="F74" s="42">
         <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
         <v/>
       </c>
-      <c r="G74" s="41">
+      <c r="G74" s="42">
         <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
         <v/>
       </c>
@@ -11422,7 +13938,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="40">
+      <c r="A75" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11442,11 +13958,11 @@
         <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)))^((B75-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F75" s="41">
+      <c r="F75" s="42">
         <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
         <v/>
       </c>
-      <c r="G75" s="41">
+      <c r="G75" s="42">
         <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
         <v/>
       </c>
@@ -11456,7 +13972,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="40">
+      <c r="A76" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11476,11 +13992,11 @@
         <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)))^((B76-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F76" s="41">
+      <c r="F76" s="42">
         <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
         <v/>
       </c>
-      <c r="G76" s="41">
+      <c r="G76" s="42">
         <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
         <v/>
       </c>
@@ -11490,7 +14006,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="40">
+      <c r="A77" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11510,11 +14026,11 @@
         <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)))^((B77-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F77" s="41">
+      <c r="F77" s="42">
         <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
         <v/>
       </c>
-      <c r="G77" s="41">
+      <c r="G77" s="42">
         <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
         <v/>
       </c>
@@ -11524,7 +14040,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="40">
+      <c r="A78" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11544,11 +14060,11 @@
         <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)))^((B78-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F78" s="41">
+      <c r="F78" s="42">
         <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
         <v/>
       </c>
-      <c r="G78" s="41">
+      <c r="G78" s="42">
         <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
         <v/>
       </c>
@@ -11558,7 +14074,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="40">
+      <c r="A79" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11578,11 +14094,11 @@
         <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)))^((B79-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F79" s="41">
+      <c r="F79" s="42">
         <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
         <v/>
       </c>
-      <c r="G79" s="41">
+      <c r="G79" s="42">
         <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
         <v/>
       </c>
@@ -11592,7 +14108,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="40">
+      <c r="A80" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11612,11 +14128,11 @@
         <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)))^((B80-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F80" s="41">
+      <c r="F80" s="42">
         <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
         <v/>
       </c>
-      <c r="G80" s="41">
+      <c r="G80" s="42">
         <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
         <v/>
       </c>
@@ -11626,7 +14142,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="40">
+      <c r="A81" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11646,11 +14162,11 @@
         <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)))^((B81-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F81" s="41">
+      <c r="F81" s="42">
         <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
         <v/>
       </c>
-      <c r="G81" s="41">
+      <c r="G81" s="42">
         <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
         <v/>
       </c>
@@ -11660,7 +14176,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="40">
+      <c r="A82" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11680,11 +14196,11 @@
         <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)))^((B82-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F82" s="41">
+      <c r="F82" s="42">
         <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
         <v/>
       </c>
-      <c r="G82" s="41">
+      <c r="G82" s="42">
         <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
         <v/>
       </c>
@@ -11694,7 +14210,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="40">
+      <c r="A83" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11714,11 +14230,11 @@
         <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)))^((B83-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F83" s="41">
+      <c r="F83" s="42">
         <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
         <v/>
       </c>
-      <c r="G83" s="41">
+      <c r="G83" s="42">
         <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
         <v/>
       </c>
@@ -11728,7 +14244,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="40">
+      <c r="A84" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11748,11 +14264,11 @@
         <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)))^((B84-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F84" s="41">
+      <c r="F84" s="42">
         <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
         <v/>
       </c>
-      <c r="G84" s="41">
+      <c r="G84" s="42">
         <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
         <v/>
       </c>
@@ -11762,7 +14278,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="40">
+      <c r="A85" s="35">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -11782,11 +14298,11 @@
         <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)))^((B85-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F85" s="41">
+      <c r="F85" s="42">
         <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
         <v/>
       </c>
-      <c r="G85" s="41">
+      <c r="G85" s="42">
         <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
         <v/>
       </c>
@@ -11822,7 +14338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11871,7 +14387,7 @@
           <t>Curve date</t>
         </is>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="44">
         <f>VAL_DATE</f>
         <v/>
       </c>
@@ -12266,780 +14782,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F37"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Conventions</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>OIS quote conventions (DES/FLDS) for representative tenors — record before you bootstrap</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>Convention attribute</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr">
-        <is>
-          <t>BDP field (verify via FLDS)</t>
-        </is>
-      </c>
-      <c r="C4" s="20" t="inlineStr">
-        <is>
-          <t>USOSFRC  (3M)</t>
-        </is>
-      </c>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>USOSFR1  (1Y)</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="inlineStr">
-        <is>
-          <t>USOSFR5  (5Y)</t>
-        </is>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>USOSFR30  (30Y)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>CRNCY</t>
-        </is>
-      </c>
-      <c r="C5" s="22">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D5" s="22">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E5" s="22">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F5" s="22">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Reference index</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C6" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E6" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Spot / settlement lag</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F7" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Effective date rule</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F8" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>Maturity date rule</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E9" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F9" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Business-day calendar</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>CALENDAR_CODE</t>
-        </is>
-      </c>
-      <c r="C10" s="22">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D10" s="22">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E10" s="22">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Business-day convention</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E11" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F11" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Fixed-leg day count</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>DAY_CNT_DES</t>
-        </is>
-      </c>
-      <c r="C12" s="22">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="D12" s="22">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="E12" s="22">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-      <c r="F12" s="22">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Fixed-leg pay frequency</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E13" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Floating-leg day count</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Floating-leg pay frequency</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>SOFR compounding method</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Payment lag</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Observation shift / lookback</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>End-of-month treatment</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>— DES/SWPM manual —</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-      <c r="F19" s="22" t="inlineStr">
-        <is>
-          <t>— DES/SWPM —</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>USD SOFR OIS — MARKET-STANDARD CONVENTIONS  (confirm per-trade in DES)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Reference index</t>
-        </is>
-      </c>
-      <c r="B22" s="44" t="inlineStr">
-        <is>
-          <t>USD-SOFR (compounded in arrears)</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Spot / settlement lag</t>
-        </is>
-      </c>
-      <c r="B23" s="44" t="inlineStr">
-        <is>
-          <t>T+2 US business days</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Effective date rule</t>
-        </is>
-      </c>
-      <c r="B24" s="44" t="inlineStr">
-        <is>
-          <t>Spot (T+2), modified following</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>Maturity date rule</t>
-        </is>
-      </c>
-      <c r="B25" s="44" t="inlineStr">
-        <is>
-          <t>Effective + tenor, modified following</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Business-day convention</t>
-        </is>
-      </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>Modified Following</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Fixed-leg day count</t>
-        </is>
-      </c>
-      <c r="B27" s="44" t="inlineStr">
-        <is>
-          <t>ACT/360</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>Fixed-leg pay frequency</t>
-        </is>
-      </c>
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>Annual  (single payment if tenor ≤ 1Y)</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>Floating-leg day count</t>
-        </is>
-      </c>
-      <c r="B29" s="44" t="inlineStr">
-        <is>
-          <t>ACT/360</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Floating-leg pay frequency</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="inlineStr">
-        <is>
-          <t>Annual  (single payment if tenor ≤ 1Y)</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>SOFR compounding method</t>
-        </is>
-      </c>
-      <c r="B31" s="44" t="inlineStr">
-        <is>
-          <t>Daily compounded, ACT/360</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Payment lag</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>2 US business days</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="6" t="inlineStr">
-        <is>
-          <t>Observation shift / lookback</t>
-        </is>
-      </c>
-      <c r="B33" s="44" t="inlineStr">
-        <is>
-          <t>None (payment-delay convention, 2 bd)</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>End-of-month treatment</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>EOM applies</t>
-        </is>
-      </c>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-    </row>
-    <row r="36" ht="44" customHeight="1">
-      <c r="A36" s="9" t="inlineStr">
-        <is>
-          <t>SWPM &lt;GO&gt;: build a representative SOFR OIS for 1Y, 5Y and 30Y and export the cashflow schedule — that gives an authoritative set of pay/accrual dates to test your own date generation against. Rows marked '— DES/SWPM —' are leg-level conventions that a rate-quote ticker does not carry; read them from DES &lt;GO&gt; on an actual swap (the market-standard defaults above are the expected values). Where a BDP cell shows 'N/A — use FLDS', open FLDS &lt;GO&gt; to find the enabled field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-  </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="A36:F37"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B27:F27"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -1695,19 +1695,19 @@
         </is>
       </c>
       <c r="C5" s="22">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFRC BGN Curncy","CRNCY"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D5" s="22">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CRNCY"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E5" s="22">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CRNCY"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F5" s="22">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CRNCY"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -1851,19 +1851,19 @@
         </is>
       </c>
       <c r="C10" s="22">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFRC BGN Curncy","CALENDAR_CODE"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D10" s="22">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR1 BGN Curncy","CALENDAR_CODE"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E10" s="22">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR5 BGN Curncy","CALENDAR_CODE"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F10" s="22">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CALENDAR_CODE"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR30 BGN Curncy","CALENDAR_CODE"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -1911,19 +1911,19 @@
         </is>
       </c>
       <c r="C12" s="22">
-        <f>IFERROR(BDP("USOSFRC BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFRC BGN Curncy","DAY_CNT_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D12" s="22">
-        <f>IFERROR(BDP("USOSFR1 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR1 BGN Curncy","DAY_CNT_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E12" s="22">
-        <f>IFERROR(BDP("USOSFR5 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR5 BGN Curncy","DAY_CNT_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F12" s="22">
-        <f>IFERROR(BDP("USOSFR30 BGN Curncy","DAY_CNT_DES"),"N/A — use FLDS")</f>
+        <f>IFERROR(BDP("USOSFR30 BGN Curncy","DAY_CNT_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -4230,11 +4230,11 @@
         </is>
       </c>
       <c r="C6" s="17">
-        <f>IFERROR(BDP(SOFR_TKR,"PX_LAST"),"open in Bloomberg")</f>
+        <f>IFERROR(BDP(SOFR_TKR,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D6" s="18">
-        <f>IFERROR(BDP(SOFR_TKR,"LAST_UPDATE_DT"),"—")</f>
+        <f>IFERROR(BDP(SOFR_TKR,"LAST_UPDATE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19">
-        <f>IFERROR(BDH(SOFR_TKR,"PX_LAST",TEXT(HIST_START,"mm/dd/yyyy"),TEXT(HIST_END,"mm/dd/yyyy")),"open in Bloomberg")</f>
+        <f>IFERROR(BDH(SOFR_TKR,"PX_LAST",TEXT(HIST_START,"mm/dd/yyyy"),TEXT(HIST_END,"mm/dd/yyyy")),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -4393,860 +4393,860 @@
         <v/>
       </c>
       <c r="B7" s="6">
-        <f>IFERROR(BDP($A7,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A7,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C7" s="17">
-        <f>IFERROR(BDP($A7,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A7,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D7" s="17">
-        <f>IFERROR(BDP($A7,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A7,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>IFERROR(BDP($A7,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A7,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>IFERROR(100-C7,"")</f>
+        <f>IFERROR(100-C7,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G7" s="6">
-        <f>IFERROR(BDP($A7,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A7,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>IFERROR(BDP($A7,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A7,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I7" s="18">
-        <f>IFERROR(BDP($A7,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A7,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J7" s="21">
-        <f>IFERROR(BDP($A7,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A7,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K7" s="21">
-        <f>IFERROR(BDP($A7,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A7,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6">
-        <f>IFERROR(BDP($A8,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A8,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C8" s="17">
-        <f>IFERROR(BDP($A8,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A8,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D8" s="17">
-        <f>IFERROR(BDP($A8,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A8,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>IFERROR(BDP($A8,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A8,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>IFERROR(100-C8,"")</f>
+        <f>IFERROR(100-C8,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G8" s="6">
-        <f>IFERROR(BDP($A8,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A8,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>IFERROR(BDP($A8,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A8,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I8" s="18">
-        <f>IFERROR(BDP($A8,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A8,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J8" s="21">
-        <f>IFERROR(BDP($A8,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A8,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K8" s="21">
-        <f>IFERROR(BDP($A8,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A8,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n"/>
       <c r="B9" s="6">
-        <f>IFERROR(BDP($A9,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A9,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C9" s="17">
-        <f>IFERROR(BDP($A9,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A9,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D9" s="17">
-        <f>IFERROR(BDP($A9,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A9,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>IFERROR(BDP($A9,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A9,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>IFERROR(100-C9,"")</f>
+        <f>IFERROR(100-C9,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G9" s="6">
-        <f>IFERROR(BDP($A9,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A9,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>IFERROR(BDP($A9,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A9,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I9" s="18">
-        <f>IFERROR(BDP($A9,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A9,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J9" s="21">
-        <f>IFERROR(BDP($A9,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A9,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K9" s="21">
-        <f>IFERROR(BDP($A9,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A9,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6">
-        <f>IFERROR(BDP($A10,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A10,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C10" s="17">
-        <f>IFERROR(BDP($A10,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A10,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D10" s="17">
-        <f>IFERROR(BDP($A10,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A10,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>IFERROR(BDP($A10,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A10,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>IFERROR(100-C10,"")</f>
+        <f>IFERROR(100-C10,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G10" s="6">
-        <f>IFERROR(BDP($A10,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A10,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>IFERROR(BDP($A10,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A10,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I10" s="18">
-        <f>IFERROR(BDP($A10,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A10,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J10" s="21">
-        <f>IFERROR(BDP($A10,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A10,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K10" s="21">
-        <f>IFERROR(BDP($A10,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A10,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n"/>
       <c r="B11" s="6">
-        <f>IFERROR(BDP($A11,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A11,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C11" s="17">
-        <f>IFERROR(BDP($A11,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A11,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D11" s="17">
-        <f>IFERROR(BDP($A11,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A11,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>IFERROR(BDP($A11,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A11,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>IFERROR(100-C11,"")</f>
+        <f>IFERROR(100-C11,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G11" s="6">
-        <f>IFERROR(BDP($A11,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A11,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>IFERROR(BDP($A11,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A11,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I11" s="18">
-        <f>IFERROR(BDP($A11,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A11,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J11" s="21">
-        <f>IFERROR(BDP($A11,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A11,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K11" s="21">
-        <f>IFERROR(BDP($A11,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A11,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6">
-        <f>IFERROR(BDP($A12,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A12,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C12" s="17">
-        <f>IFERROR(BDP($A12,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A12,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D12" s="17">
-        <f>IFERROR(BDP($A12,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A12,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>IFERROR(BDP($A12,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A12,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>IFERROR(100-C12,"")</f>
+        <f>IFERROR(100-C12,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G12" s="6">
-        <f>IFERROR(BDP($A12,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A12,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H12" s="18">
-        <f>IFERROR(BDP($A12,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A12,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I12" s="18">
-        <f>IFERROR(BDP($A12,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A12,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J12" s="21">
-        <f>IFERROR(BDP($A12,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A12,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K12" s="21">
-        <f>IFERROR(BDP($A12,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A12,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="6">
-        <f>IFERROR(BDP($A13,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A13,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C13" s="17">
-        <f>IFERROR(BDP($A13,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A13,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D13" s="17">
-        <f>IFERROR(BDP($A13,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A13,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>IFERROR(BDP($A13,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A13,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>IFERROR(100-C13,"")</f>
+        <f>IFERROR(100-C13,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G13" s="6">
-        <f>IFERROR(BDP($A13,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A13,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H13" s="18">
-        <f>IFERROR(BDP($A13,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A13,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I13" s="18">
-        <f>IFERROR(BDP($A13,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A13,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J13" s="21">
-        <f>IFERROR(BDP($A13,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A13,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K13" s="21">
-        <f>IFERROR(BDP($A13,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A13,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6">
-        <f>IFERROR(BDP($A14,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A14,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C14" s="17">
-        <f>IFERROR(BDP($A14,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A14,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D14" s="17">
-        <f>IFERROR(BDP($A14,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A14,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>IFERROR(BDP($A14,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A14,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>IFERROR(100-C14,"")</f>
+        <f>IFERROR(100-C14,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G14" s="6">
-        <f>IFERROR(BDP($A14,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A14,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H14" s="18">
-        <f>IFERROR(BDP($A14,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A14,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I14" s="18">
-        <f>IFERROR(BDP($A14,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A14,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J14" s="21">
-        <f>IFERROR(BDP($A14,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A14,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K14" s="21">
-        <f>IFERROR(BDP($A14,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A14,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="n"/>
       <c r="B15" s="6">
-        <f>IFERROR(BDP($A15,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A15,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C15" s="17">
-        <f>IFERROR(BDP($A15,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A15,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D15" s="17">
-        <f>IFERROR(BDP($A15,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A15,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>IFERROR(BDP($A15,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A15,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>IFERROR(100-C15,"")</f>
+        <f>IFERROR(100-C15,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G15" s="6">
-        <f>IFERROR(BDP($A15,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A15,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H15" s="18">
-        <f>IFERROR(BDP($A15,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A15,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I15" s="18">
-        <f>IFERROR(BDP($A15,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A15,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J15" s="21">
-        <f>IFERROR(BDP($A15,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A15,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K15" s="21">
-        <f>IFERROR(BDP($A15,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A15,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6">
-        <f>IFERROR(BDP($A16,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A16,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C16" s="17">
-        <f>IFERROR(BDP($A16,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A16,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D16" s="17">
-        <f>IFERROR(BDP($A16,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A16,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>IFERROR(BDP($A16,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A16,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>IFERROR(100-C16,"")</f>
+        <f>IFERROR(100-C16,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G16" s="6">
-        <f>IFERROR(BDP($A16,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A16,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H16" s="18">
-        <f>IFERROR(BDP($A16,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A16,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I16" s="18">
-        <f>IFERROR(BDP($A16,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A16,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J16" s="21">
-        <f>IFERROR(BDP($A16,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A16,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K16" s="21">
-        <f>IFERROR(BDP($A16,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A16,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n"/>
       <c r="B17" s="6">
-        <f>IFERROR(BDP($A17,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A17,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C17" s="17">
-        <f>IFERROR(BDP($A17,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A17,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D17" s="17">
-        <f>IFERROR(BDP($A17,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A17,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>IFERROR(BDP($A17,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A17,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>IFERROR(100-C17,"")</f>
+        <f>IFERROR(100-C17,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G17" s="6">
-        <f>IFERROR(BDP($A17,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A17,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H17" s="18">
-        <f>IFERROR(BDP($A17,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A17,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I17" s="18">
-        <f>IFERROR(BDP($A17,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A17,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J17" s="21">
-        <f>IFERROR(BDP($A17,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A17,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K17" s="21">
-        <f>IFERROR(BDP($A17,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A17,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n"/>
       <c r="B18" s="6">
-        <f>IFERROR(BDP($A18,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A18,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C18" s="17">
-        <f>IFERROR(BDP($A18,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A18,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>IFERROR(BDP($A18,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A18,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>IFERROR(BDP($A18,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A18,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>IFERROR(100-C18,"")</f>
+        <f>IFERROR(100-C18,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G18" s="6">
-        <f>IFERROR(BDP($A18,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A18,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H18" s="18">
-        <f>IFERROR(BDP($A18,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A18,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I18" s="18">
-        <f>IFERROR(BDP($A18,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A18,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J18" s="21">
-        <f>IFERROR(BDP($A18,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A18,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K18" s="21">
-        <f>IFERROR(BDP($A18,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A18,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="n"/>
       <c r="B19" s="6">
-        <f>IFERROR(BDP($A19,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A19,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C19" s="17">
-        <f>IFERROR(BDP($A19,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A19,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D19" s="17">
-        <f>IFERROR(BDP($A19,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A19,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>IFERROR(BDP($A19,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A19,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F19" s="17">
-        <f>IFERROR(100-C19,"")</f>
+        <f>IFERROR(100-C19,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G19" s="6">
-        <f>IFERROR(BDP($A19,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A19,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>IFERROR(BDP($A19,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A19,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I19" s="18">
-        <f>IFERROR(BDP($A19,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A19,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J19" s="21">
-        <f>IFERROR(BDP($A19,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A19,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K19" s="21">
-        <f>IFERROR(BDP($A19,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A19,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n"/>
       <c r="B20" s="6">
-        <f>IFERROR(BDP($A20,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A20,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C20" s="17">
-        <f>IFERROR(BDP($A20,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A20,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D20" s="17">
-        <f>IFERROR(BDP($A20,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A20,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E20" s="17">
-        <f>IFERROR(BDP($A20,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A20,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>IFERROR(100-C20,"")</f>
+        <f>IFERROR(100-C20,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G20" s="6">
-        <f>IFERROR(BDP($A20,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A20,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H20" s="18">
-        <f>IFERROR(BDP($A20,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A20,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I20" s="18">
-        <f>IFERROR(BDP($A20,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A20,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J20" s="21">
-        <f>IFERROR(BDP($A20,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A20,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K20" s="21">
-        <f>IFERROR(BDP($A20,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A20,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="n"/>
       <c r="B21" s="6">
-        <f>IFERROR(BDP($A21,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A21,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C21" s="17">
-        <f>IFERROR(BDP($A21,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A21,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D21" s="17">
-        <f>IFERROR(BDP($A21,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A21,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>IFERROR(BDP($A21,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A21,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>IFERROR(100-C21,"")</f>
+        <f>IFERROR(100-C21,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G21" s="6">
-        <f>IFERROR(BDP($A21,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A21,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H21" s="18">
-        <f>IFERROR(BDP($A21,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A21,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I21" s="18">
-        <f>IFERROR(BDP($A21,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A21,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J21" s="21">
-        <f>IFERROR(BDP($A21,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A21,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K21" s="21">
-        <f>IFERROR(BDP($A21,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A21,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n"/>
       <c r="B22" s="6">
-        <f>IFERROR(BDP($A22,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A22,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C22" s="17">
-        <f>IFERROR(BDP($A22,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A22,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>IFERROR(BDP($A22,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A22,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E22" s="17">
-        <f>IFERROR(BDP($A22,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A22,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>IFERROR(100-C22,"")</f>
+        <f>IFERROR(100-C22,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G22" s="6">
-        <f>IFERROR(BDP($A22,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A22,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H22" s="18">
-        <f>IFERROR(BDP($A22,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A22,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I22" s="18">
-        <f>IFERROR(BDP($A22,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A22,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J22" s="21">
-        <f>IFERROR(BDP($A22,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A22,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K22" s="21">
-        <f>IFERROR(BDP($A22,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A22,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n"/>
       <c r="B23" s="6">
-        <f>IFERROR(BDP($A23,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A23,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C23" s="17">
-        <f>IFERROR(BDP($A23,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A23,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D23" s="17">
-        <f>IFERROR(BDP($A23,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A23,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E23" s="17">
-        <f>IFERROR(BDP($A23,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A23,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>IFERROR(100-C23,"")</f>
+        <f>IFERROR(100-C23,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G23" s="6">
-        <f>IFERROR(BDP($A23,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A23,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H23" s="18">
-        <f>IFERROR(BDP($A23,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A23,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I23" s="18">
-        <f>IFERROR(BDP($A23,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A23,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J23" s="21">
-        <f>IFERROR(BDP($A23,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A23,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K23" s="21">
-        <f>IFERROR(BDP($A23,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A23,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="n"/>
       <c r="B24" s="6">
-        <f>IFERROR(BDP($A24,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A24,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C24" s="17">
-        <f>IFERROR(BDP($A24,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A24,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D24" s="17">
-        <f>IFERROR(BDP($A24,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A24,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E24" s="17">
-        <f>IFERROR(BDP($A24,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A24,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>IFERROR(100-C24,"")</f>
+        <f>IFERROR(100-C24,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G24" s="6">
-        <f>IFERROR(BDP($A24,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A24,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H24" s="18">
-        <f>IFERROR(BDP($A24,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A24,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I24" s="18">
-        <f>IFERROR(BDP($A24,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A24,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J24" s="21">
-        <f>IFERROR(BDP($A24,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A24,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K24" s="21">
-        <f>IFERROR(BDP($A24,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A24,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n"/>
       <c r="B25" s="6">
-        <f>IFERROR(BDP($A25,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A25,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C25" s="17">
-        <f>IFERROR(BDP($A25,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A25,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D25" s="17">
-        <f>IFERROR(BDP($A25,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A25,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E25" s="17">
-        <f>IFERROR(BDP($A25,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A25,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F25" s="17">
-        <f>IFERROR(100-C25,"")</f>
+        <f>IFERROR(100-C25,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G25" s="6">
-        <f>IFERROR(BDP($A25,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A25,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H25" s="18">
-        <f>IFERROR(BDP($A25,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A25,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I25" s="18">
-        <f>IFERROR(BDP($A25,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A25,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J25" s="21">
-        <f>IFERROR(BDP($A25,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A25,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K25" s="21">
-        <f>IFERROR(BDP($A25,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A25,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="n"/>
       <c r="B26" s="6">
-        <f>IFERROR(BDP($A26,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A26,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C26" s="17">
-        <f>IFERROR(BDP($A26,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A26,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D26" s="17">
-        <f>IFERROR(BDP($A26,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A26,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E26" s="17">
-        <f>IFERROR(BDP($A26,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A26,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F26" s="17">
-        <f>IFERROR(100-C26,"")</f>
+        <f>IFERROR(100-C26,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G26" s="6">
-        <f>IFERROR(BDP($A26,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A26,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H26" s="18">
-        <f>IFERROR(BDP($A26,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A26,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I26" s="18">
-        <f>IFERROR(BDP($A26,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A26,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J26" s="21">
-        <f>IFERROR(BDP($A26,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A26,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K26" s="21">
-        <f>IFERROR(BDP($A26,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A26,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -5327,559 +5327,559 @@
         <v/>
       </c>
       <c r="B32" s="6">
-        <f>IFERROR(BDP($A32,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A32,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C32" s="17">
-        <f>IFERROR(BDP($A32,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A32,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D32" s="17">
-        <f>IFERROR(BDP($A32,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A32,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E32" s="17">
-        <f>IFERROR(BDP($A32,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A32,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>IFERROR(100-C32,"")</f>
+        <f>IFERROR(100-C32,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G32" s="6">
-        <f>IFERROR(BDP($A32,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A32,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H32" s="18">
-        <f>IFERROR(BDP($A32,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A32,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I32" s="18">
-        <f>IFERROR(BDP($A32,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A32,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J32" s="21">
-        <f>IFERROR(BDP($A32,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A32,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K32" s="21">
-        <f>IFERROR(BDP($A32,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A32,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="n"/>
       <c r="B33" s="6">
-        <f>IFERROR(BDP($A33,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A33,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C33" s="17">
-        <f>IFERROR(BDP($A33,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A33,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D33" s="17">
-        <f>IFERROR(BDP($A33,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A33,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E33" s="17">
-        <f>IFERROR(BDP($A33,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A33,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F33" s="17">
-        <f>IFERROR(100-C33,"")</f>
+        <f>IFERROR(100-C33,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G33" s="6">
-        <f>IFERROR(BDP($A33,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A33,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H33" s="18">
-        <f>IFERROR(BDP($A33,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A33,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I33" s="18">
-        <f>IFERROR(BDP($A33,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A33,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J33" s="21">
-        <f>IFERROR(BDP($A33,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A33,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K33" s="21">
-        <f>IFERROR(BDP($A33,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A33,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="n"/>
       <c r="B34" s="6">
-        <f>IFERROR(BDP($A34,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A34,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C34" s="17">
-        <f>IFERROR(BDP($A34,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A34,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D34" s="17">
-        <f>IFERROR(BDP($A34,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A34,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E34" s="17">
-        <f>IFERROR(BDP($A34,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A34,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F34" s="17">
-        <f>IFERROR(100-C34,"")</f>
+        <f>IFERROR(100-C34,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G34" s="6">
-        <f>IFERROR(BDP($A34,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A34,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H34" s="18">
-        <f>IFERROR(BDP($A34,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A34,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I34" s="18">
-        <f>IFERROR(BDP($A34,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A34,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J34" s="21">
-        <f>IFERROR(BDP($A34,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A34,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K34" s="21">
-        <f>IFERROR(BDP($A34,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A34,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="n"/>
       <c r="B35" s="6">
-        <f>IFERROR(BDP($A35,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A35,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C35" s="17">
-        <f>IFERROR(BDP($A35,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A35,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D35" s="17">
-        <f>IFERROR(BDP($A35,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A35,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E35" s="17">
-        <f>IFERROR(BDP($A35,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A35,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>IFERROR(100-C35,"")</f>
+        <f>IFERROR(100-C35,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G35" s="6">
-        <f>IFERROR(BDP($A35,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A35,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H35" s="18">
-        <f>IFERROR(BDP($A35,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A35,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I35" s="18">
-        <f>IFERROR(BDP($A35,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A35,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J35" s="21">
-        <f>IFERROR(BDP($A35,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A35,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K35" s="21">
-        <f>IFERROR(BDP($A35,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A35,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="n"/>
       <c r="B36" s="6">
-        <f>IFERROR(BDP($A36,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A36,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C36" s="17">
-        <f>IFERROR(BDP($A36,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A36,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D36" s="17">
-        <f>IFERROR(BDP($A36,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A36,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E36" s="17">
-        <f>IFERROR(BDP($A36,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A36,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F36" s="17">
-        <f>IFERROR(100-C36,"")</f>
+        <f>IFERROR(100-C36,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G36" s="6">
-        <f>IFERROR(BDP($A36,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A36,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H36" s="18">
-        <f>IFERROR(BDP($A36,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A36,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I36" s="18">
-        <f>IFERROR(BDP($A36,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A36,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J36" s="21">
-        <f>IFERROR(BDP($A36,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A36,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K36" s="21">
-        <f>IFERROR(BDP($A36,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A36,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="n"/>
       <c r="B37" s="6">
-        <f>IFERROR(BDP($A37,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A37,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C37" s="17">
-        <f>IFERROR(BDP($A37,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A37,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D37" s="17">
-        <f>IFERROR(BDP($A37,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A37,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E37" s="17">
-        <f>IFERROR(BDP($A37,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A37,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F37" s="17">
-        <f>IFERROR(100-C37,"")</f>
+        <f>IFERROR(100-C37,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G37" s="6">
-        <f>IFERROR(BDP($A37,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A37,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H37" s="18">
-        <f>IFERROR(BDP($A37,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A37,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I37" s="18">
-        <f>IFERROR(BDP($A37,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A37,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J37" s="21">
-        <f>IFERROR(BDP($A37,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A37,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K37" s="21">
-        <f>IFERROR(BDP($A37,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A37,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="n"/>
       <c r="B38" s="6">
-        <f>IFERROR(BDP($A38,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A38,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C38" s="17">
-        <f>IFERROR(BDP($A38,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A38,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D38" s="17">
-        <f>IFERROR(BDP($A38,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A38,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E38" s="17">
-        <f>IFERROR(BDP($A38,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A38,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F38" s="17">
-        <f>IFERROR(100-C38,"")</f>
+        <f>IFERROR(100-C38,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G38" s="6">
-        <f>IFERROR(BDP($A38,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A38,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H38" s="18">
-        <f>IFERROR(BDP($A38,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A38,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I38" s="18">
-        <f>IFERROR(BDP($A38,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A38,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J38" s="21">
-        <f>IFERROR(BDP($A38,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A38,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K38" s="21">
-        <f>IFERROR(BDP($A38,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A38,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n"/>
       <c r="B39" s="6">
-        <f>IFERROR(BDP($A39,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A39,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C39" s="17">
-        <f>IFERROR(BDP($A39,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A39,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D39" s="17">
-        <f>IFERROR(BDP($A39,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A39,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E39" s="17">
-        <f>IFERROR(BDP($A39,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A39,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F39" s="17">
-        <f>IFERROR(100-C39,"")</f>
+        <f>IFERROR(100-C39,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G39" s="6">
-        <f>IFERROR(BDP($A39,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A39,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H39" s="18">
-        <f>IFERROR(BDP($A39,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A39,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I39" s="18">
-        <f>IFERROR(BDP($A39,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A39,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J39" s="21">
-        <f>IFERROR(BDP($A39,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A39,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K39" s="21">
-        <f>IFERROR(BDP($A39,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A39,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="n"/>
       <c r="B40" s="6">
-        <f>IFERROR(BDP($A40,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A40,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C40" s="17">
-        <f>IFERROR(BDP($A40,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A40,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D40" s="17">
-        <f>IFERROR(BDP($A40,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A40,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E40" s="17">
-        <f>IFERROR(BDP($A40,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A40,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F40" s="17">
-        <f>IFERROR(100-C40,"")</f>
+        <f>IFERROR(100-C40,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G40" s="6">
-        <f>IFERROR(BDP($A40,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A40,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H40" s="18">
-        <f>IFERROR(BDP($A40,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A40,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I40" s="18">
-        <f>IFERROR(BDP($A40,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A40,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J40" s="21">
-        <f>IFERROR(BDP($A40,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A40,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K40" s="21">
-        <f>IFERROR(BDP($A40,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A40,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n"/>
       <c r="B41" s="6">
-        <f>IFERROR(BDP($A41,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A41,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C41" s="17">
-        <f>IFERROR(BDP($A41,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A41,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D41" s="17">
-        <f>IFERROR(BDP($A41,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A41,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E41" s="17">
-        <f>IFERROR(BDP($A41,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A41,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F41" s="17">
-        <f>IFERROR(100-C41,"")</f>
+        <f>IFERROR(100-C41,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G41" s="6">
-        <f>IFERROR(BDP($A41,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A41,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H41" s="18">
-        <f>IFERROR(BDP($A41,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A41,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I41" s="18">
-        <f>IFERROR(BDP($A41,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A41,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J41" s="21">
-        <f>IFERROR(BDP($A41,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A41,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K41" s="21">
-        <f>IFERROR(BDP($A41,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A41,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="n"/>
       <c r="B42" s="6">
-        <f>IFERROR(BDP($A42,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A42,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C42" s="17">
-        <f>IFERROR(BDP($A42,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A42,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D42" s="17">
-        <f>IFERROR(BDP($A42,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A42,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E42" s="17">
-        <f>IFERROR(BDP($A42,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A42,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F42" s="17">
-        <f>IFERROR(100-C42,"")</f>
+        <f>IFERROR(100-C42,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G42" s="6">
-        <f>IFERROR(BDP($A42,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A42,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H42" s="18">
-        <f>IFERROR(BDP($A42,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A42,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I42" s="18">
-        <f>IFERROR(BDP($A42,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A42,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J42" s="21">
-        <f>IFERROR(BDP($A42,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A42,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K42" s="21">
-        <f>IFERROR(BDP($A42,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A42,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n"/>
       <c r="B43" s="6">
-        <f>IFERROR(BDP($A43,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A43,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C43" s="17">
-        <f>IFERROR(BDP($A43,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A43,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D43" s="17">
-        <f>IFERROR(BDP($A43,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A43,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E43" s="17">
-        <f>IFERROR(BDP($A43,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A43,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F43" s="17">
-        <f>IFERROR(100-C43,"")</f>
+        <f>IFERROR(100-C43,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G43" s="6">
-        <f>IFERROR(BDP($A43,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A43,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H43" s="18">
-        <f>IFERROR(BDP($A43,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A43,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I43" s="18">
-        <f>IFERROR(BDP($A43,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A43,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J43" s="21">
-        <f>IFERROR(BDP($A43,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A43,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K43" s="21">
-        <f>IFERROR(BDP($A43,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A43,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n"/>
       <c r="B44" s="6">
-        <f>IFERROR(BDP($A44,"SECURITY_DES"),"")</f>
+        <f>IFERROR(BDP($A44,"SECURITY_DES"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="C44" s="17">
-        <f>IFERROR(BDP($A44,"PX_LAST"),"")</f>
+        <f>IFERROR(BDP($A44,"PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="D44" s="17">
-        <f>IFERROR(BDP($A44,"PX_BID"),"")</f>
+        <f>IFERROR(BDP($A44,"PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="E44" s="17">
-        <f>IFERROR(BDP($A44,"PX_ASK"),"")</f>
+        <f>IFERROR(BDP($A44,"PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F44" s="17">
-        <f>IFERROR(100-C44,"")</f>
+        <f>IFERROR(100-C44,"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G44" s="6">
-        <f>IFERROR(BDP($A44,"FUT_MONTH_YR"),"")</f>
+        <f>IFERROR(BDP($A44,"FUT_MONTH_YR"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H44" s="18">
-        <f>IFERROR(BDP($A44,"FUT_DLV_DT_FIRST"),"")</f>
+        <f>IFERROR(BDP($A44,"FUT_DLV_DT_FIRST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="I44" s="18">
-        <f>IFERROR(BDP($A44,"LAST_TRADEABLE_DT"),"")</f>
+        <f>IFERROR(BDP($A44,"LAST_TRADEABLE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="J44" s="21">
-        <f>IFERROR(BDP($A44,"VOLUME"),"")</f>
+        <f>IFERROR(BDP($A44,"VOLUME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="K44" s="21">
-        <f>IFERROR(BDP($A44,"OPEN_INT"),"")</f>
+        <f>IFERROR(BDP($A44,"OPEN_INT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>
@@ -6011,19 +6011,19 @@
         <v/>
       </c>
       <c r="E5" s="17">
-        <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F5" s="17">
-        <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G5" s="17">
-        <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H5" s="25">
-        <f>IFERROR((E5+F5)/2,IFERROR(G5,""))</f>
+        <f>IFERROR((E5+F5)/2,IFERROR(G5,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I5" s="26" t="inlineStr">
@@ -6052,19 +6052,19 @@
         <v/>
       </c>
       <c r="E6" s="17">
-        <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F6" s="17">
-        <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G6" s="17">
-        <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H6" s="25">
-        <f>IFERROR((E6+F6)/2,IFERROR(G6,""))</f>
+        <f>IFERROR((E6+F6)/2,IFERROR(G6,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I6" s="26" t="inlineStr"/>
@@ -6089,19 +6089,19 @@
         <v/>
       </c>
       <c r="E7" s="17">
-        <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F7" s="17">
-        <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G7" s="17">
-        <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H7" s="25">
-        <f>IFERROR((E7+F7)/2,IFERROR(G7,""))</f>
+        <f>IFERROR((E7+F7)/2,IFERROR(G7,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I7" s="26" t="inlineStr"/>
@@ -6126,19 +6126,19 @@
         <v/>
       </c>
       <c r="E8" s="17">
-        <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F8" s="17">
-        <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G8" s="17">
-        <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H8" s="25">
-        <f>IFERROR((E8+F8)/2,IFERROR(G8,""))</f>
+        <f>IFERROR((E8+F8)/2,IFERROR(G8,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I8" s="26" t="inlineStr">
@@ -6167,19 +6167,19 @@
         <v/>
       </c>
       <c r="E9" s="17">
-        <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F9" s="17">
-        <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G9" s="17">
-        <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H9" s="25">
-        <f>IFERROR((E9+F9)/2,IFERROR(G9,""))</f>
+        <f>IFERROR((E9+F9)/2,IFERROR(G9,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I9" s="26" t="inlineStr"/>
@@ -6204,19 +6204,19 @@
         <v/>
       </c>
       <c r="E10" s="17">
-        <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G10" s="17">
-        <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H10" s="25">
-        <f>IFERROR((E10+F10)/2,IFERROR(G10,""))</f>
+        <f>IFERROR((E10+F10)/2,IFERROR(G10,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I10" s="26" t="inlineStr">
@@ -6245,19 +6245,19 @@
         <v/>
       </c>
       <c r="E11" s="17">
-        <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G11" s="17">
-        <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H11" s="25">
-        <f>IFERROR((E11+F11)/2,IFERROR(G11,""))</f>
+        <f>IFERROR((E11+F11)/2,IFERROR(G11,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I11" s="26" t="inlineStr"/>
@@ -6282,19 +6282,19 @@
         <v/>
       </c>
       <c r="E12" s="17">
-        <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G12" s="17">
-        <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H12" s="25">
-        <f>IFERROR((E12+F12)/2,IFERROR(G12,""))</f>
+        <f>IFERROR((E12+F12)/2,IFERROR(G12,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I12" s="26" t="inlineStr"/>
@@ -6319,19 +6319,19 @@
         <v/>
       </c>
       <c r="E13" s="17">
-        <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H13" s="25">
-        <f>IFERROR((E13+F13)/2,IFERROR(G13,""))</f>
+        <f>IFERROR((E13+F13)/2,IFERROR(G13,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I13" s="26" t="inlineStr">
@@ -6360,19 +6360,19 @@
         <v/>
       </c>
       <c r="E14" s="17">
-        <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H14" s="25">
-        <f>IFERROR((E14+F14)/2,IFERROR(G14,""))</f>
+        <f>IFERROR((E14+F14)/2,IFERROR(G14,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I14" s="26" t="inlineStr"/>
@@ -6397,19 +6397,19 @@
         <v/>
       </c>
       <c r="E15" s="17">
-        <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G15" s="17">
-        <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H15" s="25">
-        <f>IFERROR((E15+F15)/2,IFERROR(G15,""))</f>
+        <f>IFERROR((E15+F15)/2,IFERROR(G15,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I15" s="26" t="inlineStr"/>
@@ -6434,19 +6434,19 @@
         <v/>
       </c>
       <c r="E16" s="17">
-        <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G16" s="17">
-        <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H16" s="25">
-        <f>IFERROR((E16+F16)/2,IFERROR(G16,""))</f>
+        <f>IFERROR((E16+F16)/2,IFERROR(G16,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I16" s="26" t="inlineStr"/>
@@ -6471,19 +6471,19 @@
         <v/>
       </c>
       <c r="E17" s="17">
-        <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G17" s="17">
-        <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H17" s="25">
-        <f>IFERROR((E17+F17)/2,IFERROR(G17,""))</f>
+        <f>IFERROR((E17+F17)/2,IFERROR(G17,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I17" s="26" t="inlineStr"/>
@@ -6508,19 +6508,19 @@
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H18" s="25">
-        <f>IFERROR((E18+F18)/2,IFERROR(G18,""))</f>
+        <f>IFERROR((E18+F18)/2,IFERROR(G18,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I18" s="26" t="inlineStr"/>
@@ -6545,19 +6545,19 @@
         <v/>
       </c>
       <c r="E19" s="17">
-        <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F19" s="17">
-        <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G19" s="17">
-        <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H19" s="25">
-        <f>IFERROR((E19+F19)/2,IFERROR(G19,""))</f>
+        <f>IFERROR((E19+F19)/2,IFERROR(G19,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I19" s="26" t="inlineStr"/>
@@ -6582,19 +6582,19 @@
         <v/>
       </c>
       <c r="E20" s="17">
-        <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G20" s="17">
-        <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H20" s="25">
-        <f>IFERROR((E20+F20)/2,IFERROR(G20,""))</f>
+        <f>IFERROR((E20+F20)/2,IFERROR(G20,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I20" s="26" t="inlineStr"/>
@@ -6619,19 +6619,19 @@
         <v/>
       </c>
       <c r="E21" s="17">
-        <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G21" s="17">
-        <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H21" s="25">
-        <f>IFERROR((E21+F21)/2,IFERROR(G21,""))</f>
+        <f>IFERROR((E21+F21)/2,IFERROR(G21,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I21" s="26" t="inlineStr"/>
@@ -6656,19 +6656,19 @@
         <v/>
       </c>
       <c r="E22" s="17">
-        <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H22" s="25">
-        <f>IFERROR((E22+F22)/2,IFERROR(G22,""))</f>
+        <f>IFERROR((E22+F22)/2,IFERROR(G22,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I22" s="26" t="inlineStr"/>
@@ -6693,19 +6693,19 @@
         <v/>
       </c>
       <c r="E23" s="17">
-        <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G23" s="17">
-        <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H23" s="25">
-        <f>IFERROR((E23+F23)/2,IFERROR(G23,""))</f>
+        <f>IFERROR((E23+F23)/2,IFERROR(G23,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I23" s="26" t="inlineStr"/>
@@ -6730,19 +6730,19 @@
         <v/>
       </c>
       <c r="E24" s="17">
-        <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G24" s="17">
-        <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H24" s="25">
-        <f>IFERROR((E24+F24)/2,IFERROR(G24,""))</f>
+        <f>IFERROR((E24+F24)/2,IFERROR(G24,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I24" s="26" t="inlineStr">
@@ -6771,19 +6771,19 @@
         <v/>
       </c>
       <c r="E25" s="17">
-        <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F25" s="17">
-        <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G25" s="17">
-        <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H25" s="25">
-        <f>IFERROR((E25+F25)/2,IFERROR(G25,""))</f>
+        <f>IFERROR((E25+F25)/2,IFERROR(G25,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I25" s="26" t="inlineStr">
@@ -6812,19 +6812,19 @@
         <v/>
       </c>
       <c r="E26" s="17">
-        <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F26" s="17">
-        <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G26" s="17">
-        <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H26" s="25">
-        <f>IFERROR((E26+F26)/2,IFERROR(G26,""))</f>
+        <f>IFERROR((E26+F26)/2,IFERROR(G26,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I26" s="26" t="inlineStr">
@@ -6853,19 +6853,19 @@
         <v/>
       </c>
       <c r="E27" s="17">
-        <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F27" s="17">
-        <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G27" s="17">
-        <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H27" s="25">
-        <f>IFERROR((E27+F27)/2,IFERROR(G27,""))</f>
+        <f>IFERROR((E27+F27)/2,IFERROR(G27,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I27" s="26" t="inlineStr">
@@ -6894,19 +6894,19 @@
         <v/>
       </c>
       <c r="E28" s="17">
-        <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F28" s="17">
-        <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G28" s="17">
-        <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H28" s="25">
-        <f>IFERROR((E28+F28)/2,IFERROR(G28,""))</f>
+        <f>IFERROR((E28+F28)/2,IFERROR(G28,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I28" s="26" t="inlineStr">
@@ -6935,19 +6935,19 @@
         <v/>
       </c>
       <c r="E29" s="17">
-        <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F29" s="17">
-        <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G29" s="17">
-        <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H29" s="25">
-        <f>IFERROR((E29+F29)/2,IFERROR(G29,""))</f>
+        <f>IFERROR((E29+F29)/2,IFERROR(G29,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I29" s="26" t="inlineStr">
@@ -6976,19 +6976,19 @@
         <v/>
       </c>
       <c r="E30" s="17">
-        <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F30" s="17">
-        <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G30" s="17">
-        <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H30" s="25">
-        <f>IFERROR((E30+F30)/2,IFERROR(G30,""))</f>
+        <f>IFERROR((E30+F30)/2,IFERROR(G30,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I30" s="26" t="inlineStr">
@@ -7017,19 +7017,19 @@
         <v/>
       </c>
       <c r="E31" s="17">
-        <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G31" s="17">
-        <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H31" s="25">
-        <f>IFERROR((E31+F31)/2,IFERROR(G31,""))</f>
+        <f>IFERROR((E31+F31)/2,IFERROR(G31,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I31" s="26" t="inlineStr">
@@ -7058,19 +7058,19 @@
         <v/>
       </c>
       <c r="E32" s="17">
-        <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G32" s="17">
-        <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H32" s="25">
-        <f>IFERROR((E32+F32)/2,IFERROR(G32,""))</f>
+        <f>IFERROR((E32+F32)/2,IFERROR(G32,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I32" s="26" t="inlineStr">
@@ -7099,19 +7099,19 @@
         <v/>
       </c>
       <c r="E33" s="17">
-        <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F33" s="17">
-        <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G33" s="17">
-        <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H33" s="25">
-        <f>IFERROR((E33+F33)/2,IFERROR(G33,""))</f>
+        <f>IFERROR((E33+F33)/2,IFERROR(G33,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I33" s="26" t="inlineStr">
@@ -7140,19 +7140,19 @@
         <v/>
       </c>
       <c r="E34" s="17">
-        <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F34" s="17">
-        <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G34" s="17">
-        <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H34" s="25">
-        <f>IFERROR((E34+F34)/2,IFERROR(G34,""))</f>
+        <f>IFERROR((E34+F34)/2,IFERROR(G34,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I34" s="26" t="inlineStr">
@@ -7181,19 +7181,19 @@
         <v/>
       </c>
       <c r="E35" s="17">
-        <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G35" s="17">
-        <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H35" s="25">
-        <f>IFERROR((E35+F35)/2,IFERROR(G35,""))</f>
+        <f>IFERROR((E35+F35)/2,IFERROR(G35,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I35" s="26" t="inlineStr">
@@ -7222,19 +7222,19 @@
         <v/>
       </c>
       <c r="E36" s="17">
-        <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"")</f>
+        <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_BID"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="F36" s="17">
-        <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"")</f>
+        <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_ASK"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="G36" s="17">
-        <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"")</f>
+        <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
       <c r="H36" s="25">
-        <f>IFERROR((E36+F36)/2,IFERROR(G36,""))</f>
+        <f>IFERROR((E36+F36)/2,IFERROR(G36,"ERROR PLZ FIX"))</f>
         <v/>
       </c>
       <c r="I36" s="26" t="inlineStr">
@@ -14377,7 +14377,7 @@
         </is>
       </c>
       <c r="B4" s="19">
-        <f>IFERROR(BDP(S490_TKR,"NAME"),"open in Bloomberg")</f>
+        <f>IFERROR(BDP(S490_TKR,"NAME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
     </row>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -7324,7 +7324,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·tau0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which discounts each contract's forward rate forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is shown only for reference).  LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·taucoupon), with the annuity (col I) built from the short + futures DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
+          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·tau0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which discounts each contract's forward rate forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is shown only for reference). If the SR3 chain is unavailable the middle DFs FALL BACK to the OIS bootstrap so the curve never breaks — col N shows which is live per pillar. LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·taucoupon), annuity (col I) built from the short + middle DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
         </is>
       </c>
       <c r="O5" s="13" t="inlineStr">
@@ -8969,7 +8969,7 @@
         <v/>
       </c>
       <c r="H23" s="29">
-        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))</f>
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))),(1-(E23/100)*G23)/(1+(E23/100)*F23))</f>
         <v/>
       </c>
       <c r="I23" s="17" t="n">
@@ -8988,10 +8988,9 @@
         <f>IF(L23="","",(J23-L23)*100)</f>
         <v/>
       </c>
-      <c r="N23" s="6" t="inlineStr">
-        <is>
-          <t>SR3 futures</t>
-        </is>
+      <c r="N23" s="6">
+        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <v/>
       </c>
       <c r="O23" s="6">
         <f>'SOFR_Futures'!A22</f>
@@ -9069,7 +9068,7 @@
         <v/>
       </c>
       <c r="H24" s="29">
-        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))</f>
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))),(1-(E24/100)*G24)/(1+(E24/100)*F24))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -9089,10 +9088,9 @@
         <f>IF(L24="","",(J24-L24)*100)</f>
         <v/>
       </c>
-      <c r="N24" s="6" t="inlineStr">
-        <is>
-          <t>SR3 futures</t>
-        </is>
+      <c r="N24" s="6">
+        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <v/>
       </c>
       <c r="O24" s="6">
         <f>'SOFR_Futures'!A23</f>
@@ -9170,7 +9168,7 @@
         <v/>
       </c>
       <c r="H25" s="29">
-        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))</f>
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))),(1-(E25/100)*G25)/(1+(E25/100)*F25))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -9190,10 +9188,9 @@
         <f>IF(L25="","",(J25-L25)*100)</f>
         <v/>
       </c>
-      <c r="N25" s="6" t="inlineStr">
-        <is>
-          <t>SR3 futures</t>
-        </is>
+      <c r="N25" s="6">
+        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <v/>
       </c>
       <c r="O25" s="6">
         <f>'SOFR_Futures'!A24</f>
@@ -9271,7 +9268,7 @@
         <v/>
       </c>
       <c r="H26" s="29">
-        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))</f>
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))),(1-(E26/100)*G26)/(1+(E26/100)*F26))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -9291,10 +9288,9 @@
         <f>IF(L26="","",(J26-L26)*100)</f>
         <v/>
       </c>
-      <c r="N26" s="6" t="inlineStr">
-        <is>
-          <t>SR3 futures</t>
-        </is>
+      <c r="N26" s="6">
+        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <v/>
       </c>
       <c r="O26" s="6">
         <f>'SOFR_Futures'!A25</f>
@@ -9372,7 +9368,7 @@
         <v/>
       </c>
       <c r="H27" s="29">
-        <f>IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))</f>
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))),(1-(E27/100)*G27)/(1+(E27/100)*F27))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -9392,10 +9388,9 @@
         <f>IF(L27="","",(J27-L27)*100)</f>
         <v/>
       </c>
-      <c r="N27" s="6" t="inlineStr">
-        <is>
-          <t>SR3 futures</t>
-        </is>
+      <c r="N27" s="6">
+        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <v/>
       </c>
       <c r="O27" s="6">
         <f>'SOFR_Futures'!A26</f>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -18,6 +18,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -33,13 +39,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000000"/>
     <numFmt numFmtId="169" formatCode="0.0000%"/>
+    <numFmt numFmtId="170" formatCode="0.000"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -134,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -210,6 +217,14 @@
     <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1022,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1492,90 +1507,165 @@
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>5. Bloomberg_S490_Validation</t>
+          <t>CDS_Parameters</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
+          <t>Credit assumptions: recovery, notional, coupon, direction (recovery is an INPUT).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>6. Conventions</t>
+          <t>CDS_Quotes</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
+          <t>Single-name CDS par spreads (BDP ticker, or manual demo). One entity, one seniority.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
+          <t>CDS_Schedule</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>Quarterly premium/default schedule to 10Y; DF from the SOFR curve, survival from hazards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="inlineStr">
+        <is>
+          <t>Hazard_Bootstrap</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>Piecewise-constant hazard curve; s/(1-R) default, Goal-Seek the error to 0 for exact fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>CDS_Pricer</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>Prices a CDS off both curves: protection − premium, par spread, upfront, CS01.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>CDS_Validation</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Survival/hazard sanity checks + the s ≈ (1-R)·lambda approximation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>5. Bloomberg_S490_Validation</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="inlineStr">
+        <is>
+          <t>6. Conventions</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
           <t>7. Fwd_Interp</t>
         </is>
       </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Zhou 2002 forward interpolation: V1 piecewise-flat vs V2 piecewise-quadratic forwards.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>DO NOT substitute these (wrong instruments):</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="9" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="9" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>•  Use PX midpoint (bid+ask)/2 for construction; use PX_LAST only where bid/ask are unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
+    <row r="57" ht="28" customHeight="1">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>Licensing: Bloomberg data is licensed and entitlement-dependent — do NOT redistribute pulled values or commit them to a public repository. This template ships formulas only, no data. Some static convention fields may return N/A under your entitlement; use FLDS &lt;GO&gt; on the security to find the enabled mnemonic.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
+    <row r="58"/>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="58">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A54:F54"/>
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="D13:F13"/>
-    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="B47:F47"/>
     <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A55:F55"/>
     <mergeCell ref="B27:F27"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A33:F33"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B39:F39"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="B48:F48"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="E19:F19"/>
     <mergeCell ref="A32:F32"/>
@@ -1583,30 +1673,33 @@
     <mergeCell ref="D9:F9"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="A35:F35"/>
-    <mergeCell ref="A51:F52"/>
     <mergeCell ref="A18:B18"/>
     <mergeCell ref="D8:F8"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A53:F53"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A52:F52"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B28:F28"/>
     <mergeCell ref="A31:F31"/>
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="D10:F10"/>
     <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B49:F49"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B45:F45"/>
     <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A57:F58"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A4:F5"/>
@@ -4129,6 +4222,3905 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CDS_Parameters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Credit-default-swap assumptions (recovery is an INPUT, not bootstrapped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Valuation date</t>
+        </is>
+      </c>
+      <c r="B4" s="18">
+        <f>VAL_DATE</f>
+        <v/>
+      </c>
+      <c r="C4" s="16" t="inlineStr">
+        <is>
+          <t>Linked to the Parameters/Instructions tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1st CDS date (roll)</t>
+        </is>
+      </c>
+      <c r="B5" s="18">
+        <f>'Curve_Interface'!$F$7</f>
+        <v/>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Next 20 Mar/Jun/Sep/Dec.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Reference entity</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="inlineStr">
+        <is>
+          <t>EXAMPLE CORP</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>Type your reference entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Recovery rate R</t>
+        </is>
+      </c>
+      <c r="B8" s="51" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>Assumed. Changing R re-fits every hazard.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
+      <c r="B9" s="38" t="n">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Standard coupon (bp)</t>
+        </is>
+      </c>
+      <c r="B10" s="40" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Fixed running coupon (IG=100, HY=500).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Premium frequency</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Premium day count</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Hazard interpolation</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Piecewise-constant</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Discount curve</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>SOFR OIS (Curve_Interface)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Protection direction</t>
+        </is>
+      </c>
+      <c r="B15" s="36" t="inlineStr">
+        <is>
+          <t>Buy protection</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>"Buy protection" or "Sell protection".</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Accrual-on-default</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Included (midpoint approx.)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C10:H10"/>
+    <mergeCell ref="C5:H5"/>
+    <mergeCell ref="C8:H8"/>
+    <mergeCell ref="C4:H4"/>
+    <mergeCell ref="C7:H7"/>
+    <mergeCell ref="C15:H15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CDS_Quotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Single-name CDS par spreads — one entity, one seniority/clause. Live BDP overrides the manual demo values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Enter each tenor's Bloomberg CDS ticker in col D (e.g. the entity's par-spread series); Market spread = BDP(ticker,"PX_LAST") when it resolves, else the yellow Manual spread so the module still runs. Do NOT mix seniorities, currencies, or restructuring clauses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Tenor (yrs)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>CDS ticker</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Manual spread (bp)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Market spread (bp)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>Approx hazard s/(1-R)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(4-1))</f>
+        <v/>
+      </c>
+      <c r="D7" s="36" t="inlineStr"/>
+      <c r="E7" s="52" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" s="31">
+        <f>IFERROR(BDP(D7,"PX_LAST"),E7)</f>
+        <v/>
+      </c>
+      <c r="G7" s="49">
+        <f>(F7/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(8-1))</f>
+        <v/>
+      </c>
+      <c r="D8" s="36" t="inlineStr"/>
+      <c r="E8" s="52" t="n">
+        <v>55</v>
+      </c>
+      <c r="F8" s="31">
+        <f>IFERROR(BDP(D8,"PX_LAST"),E8)</f>
+        <v/>
+      </c>
+      <c r="G8" s="49">
+        <f>(F8/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(12-1))</f>
+        <v/>
+      </c>
+      <c r="D9" s="36" t="inlineStr"/>
+      <c r="E9" s="52" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="31">
+        <f>IFERROR(BDP(D9,"PX_LAST"),E9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="49">
+        <f>(F9/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B10" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(20-1))</f>
+        <v/>
+      </c>
+      <c r="D10" s="36" t="inlineStr"/>
+      <c r="E10" s="52" t="n">
+        <v>95</v>
+      </c>
+      <c r="F10" s="31">
+        <f>IFERROR(BDP(D10,"PX_LAST"),E10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="49">
+        <f>(F10/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="B11" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(28-1))</f>
+        <v/>
+      </c>
+      <c r="D11" s="36" t="inlineStr"/>
+      <c r="E11" s="52" t="n">
+        <v>115</v>
+      </c>
+      <c r="F11" s="31">
+        <f>IFERROR(BDP(D11,"PX_LAST"),E11)</f>
+        <v/>
+      </c>
+      <c r="G11" s="49">
+        <f>(F11/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B12" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(40-1))</f>
+        <v/>
+      </c>
+      <c r="D12" s="36" t="inlineStr"/>
+      <c r="E12" s="52" t="n">
+        <v>135</v>
+      </c>
+      <c r="F12" s="31">
+        <f>IFERROR(BDP(D12,"PX_LAST"),E12)</f>
+        <v/>
+      </c>
+      <c r="G12" s="49">
+        <f>(F12/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hazard_Bootstrap</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Piecewise-constant hazard curve. Col D pre-filled with s/(1-R); Goal Seek col J (error)=0 by changing col D for EXACT fit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Bootstrap maturity by maturity: hold earlier hazards fixed, solve the current segment so model spread = market. Col D defaults to the s/(1-R) approximation (module runs immediately). For an exact fit (|error|&lt;0.01bp), Goal Seek EACH row: Data &gt; What-If &gt; Goal Seek, Set cell = col J, To value 0, By changing = col D — top row first, then down. Survival/PVs come from the CDS_Schedule tab, which discounts on the shared SOFR Curve_Interface.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Market spread (bp)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>Hazard lambda (solve)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>Cum. survival Q(T)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>Cum. default 1-Q</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>RPV01 (risky annuity)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>Protection PV factor</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Model spread (bp)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>Repricing error (bp)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>CDS_Quotes!C7</f>
+        <v/>
+      </c>
+      <c r="C7" s="31">
+        <f>CDS_Quotes!F7</f>
+        <v/>
+      </c>
+      <c r="D7" s="53">
+        <f>(C7/10000)/(1-CDS_Parameters!$B$8)</f>
+        <v/>
+      </c>
+      <c r="E7" s="32">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B7,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F7" s="32">
+        <f>1-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I7" s="28">
+        <f>(1-CDS_Parameters!$B$8)*H7/G7*10000</f>
+        <v/>
+      </c>
+      <c r="J7" s="54">
+        <f>I7-C7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>CDS_Quotes!C8</f>
+        <v/>
+      </c>
+      <c r="C8" s="31">
+        <f>CDS_Quotes!F8</f>
+        <v/>
+      </c>
+      <c r="D8" s="53">
+        <f>((C8/10000)*(B8-VAL_DATE)/365-(C7/10000)*(B7-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B8-VAL_DATE)/365-(B7-VAL_DATE)/365))</f>
+        <v/>
+      </c>
+      <c r="E8" s="32">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B8,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F8" s="32">
+        <f>1-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H8" s="32">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I8" s="28">
+        <f>(1-CDS_Parameters!$B$8)*H8/G8*10000</f>
+        <v/>
+      </c>
+      <c r="J8" s="54">
+        <f>I8-C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>CDS_Quotes!C9</f>
+        <v/>
+      </c>
+      <c r="C9" s="31">
+        <f>CDS_Quotes!F9</f>
+        <v/>
+      </c>
+      <c r="D9" s="53">
+        <f>((C9/10000)*(B9-VAL_DATE)/365-(C8/10000)*(B8-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B9-VAL_DATE)/365-(B8-VAL_DATE)/365))</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B9,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F9" s="32">
+        <f>1-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H9" s="32">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I9" s="28">
+        <f>(1-CDS_Parameters!$B$8)*H9/G9*10000</f>
+        <v/>
+      </c>
+      <c r="J9" s="54">
+        <f>I9-C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>CDS_Quotes!C10</f>
+        <v/>
+      </c>
+      <c r="C10" s="31">
+        <f>CDS_Quotes!F10</f>
+        <v/>
+      </c>
+      <c r="D10" s="53">
+        <f>((C10/10000)*(B10-VAL_DATE)/365-(C9/10000)*(B9-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B10-VAL_DATE)/365-(B9-VAL_DATE)/365))</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B10,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F10" s="32">
+        <f>1-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H10" s="32">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I10" s="28">
+        <f>(1-CDS_Parameters!$B$8)*H10/G10*10000</f>
+        <v/>
+      </c>
+      <c r="J10" s="54">
+        <f>I10-C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>CDS_Quotes!C11</f>
+        <v/>
+      </c>
+      <c r="C11" s="31">
+        <f>CDS_Quotes!F11</f>
+        <v/>
+      </c>
+      <c r="D11" s="53">
+        <f>((C11/10000)*(B11-VAL_DATE)/365-(C10/10000)*(B10-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B11-VAL_DATE)/365-(B10-VAL_DATE)/365))</f>
+        <v/>
+      </c>
+      <c r="E11" s="32">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B11,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F11" s="32">
+        <f>1-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H11" s="32">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I11" s="28">
+        <f>(1-CDS_Parameters!$B$8)*H11/G11*10000</f>
+        <v/>
+      </c>
+      <c r="J11" s="54">
+        <f>I11-C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>CDS_Quotes!C12</f>
+        <v/>
+      </c>
+      <c r="C12" s="31">
+        <f>CDS_Quotes!F12</f>
+        <v/>
+      </c>
+      <c r="D12" s="53">
+        <f>((C12/10000)*(B12-VAL_DATE)/365-(C11/10000)*(B11-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B12-VAL_DATE)/365-(B11-VAL_DATE)/365))</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B12,CDS_Schedule!$C$7:$C$46,1))</f>
+        <v/>
+      </c>
+      <c r="F12" s="32">
+        <f>1-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="H12" s="32">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+      <c r="I12" s="28">
+        <f>(1-CDS_Parameters!$B$8)*H12/G12*10000</f>
+        <v/>
+      </c>
+      <c r="J12" s="54">
+        <f>I12-C12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:J5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CDS_Schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Quarterly premium &amp; default schedule to 10Y. DF from the shared SOFR curve; survival from the hazard curve.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Each row is one quarterly coupon period. DF(end)/DF(mid) interpolate the SOFR Curve_Interface; hazard is the piecewise-constant Hazard_Bootstrap lambda for the segment (by pay date); Q(end)=Q(prev)*exp(-hazard*dt). Premium factor = alpha*DF*Q ; Accrual factor = (alpha/2)*DF(mid)*deltaPD ; Protection factor = DF(mid)*deltaPD. Front period is a stub from valuation to the first roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Accrual start</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Pay date</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>alpha ACT/360</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>dt ACT/365</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>T (yrs)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>DF(end)</t>
+        </is>
+      </c>
+      <c r="H6" s="20" t="inlineStr">
+        <is>
+          <t>DF(mid)</t>
+        </is>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>Q(prev)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>Q(end)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>delta PD</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>Premium factor</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>Accrual factor</t>
+        </is>
+      </c>
+      <c r="O6" s="20" t="inlineStr">
+        <is>
+          <t>Protection factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="18">
+        <f>VAL_DATE</f>
+        <v/>
+      </c>
+      <c r="C7" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>(C7-B7)/360</f>
+        <v/>
+      </c>
+      <c r="E7" s="17">
+        <f>(C7-B7)/365</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>(C7-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G7" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1)))^((C7-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C7,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H7" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B7+C7)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B7+C7)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C7)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>J7*EXP(-I7*E7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="32">
+        <f>J7-K7</f>
+        <v/>
+      </c>
+      <c r="M7" s="32">
+        <f>D7*G7*K7</f>
+        <v/>
+      </c>
+      <c r="N7" s="32">
+        <f>(D7/2)*H7*L7</f>
+        <v/>
+      </c>
+      <c r="O7" s="32">
+        <f>H7*L7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="35" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="18">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="C8" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*1)</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>(C8-B8)/360</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>(C8-B8)/365</f>
+        <v/>
+      </c>
+      <c r="F8" s="28">
+        <f>(C8-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G8" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1)))^((C8-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C8,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H8" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B8+C8)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B8+C8)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C8)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J8" s="32">
+        <f>K7</f>
+        <v/>
+      </c>
+      <c r="K8" s="32">
+        <f>J8*EXP(-I8*E8)</f>
+        <v/>
+      </c>
+      <c r="L8" s="32">
+        <f>J8-K8</f>
+        <v/>
+      </c>
+      <c r="M8" s="32">
+        <f>D8*G8*K8</f>
+        <v/>
+      </c>
+      <c r="N8" s="32">
+        <f>(D8/2)*H8*L8</f>
+        <v/>
+      </c>
+      <c r="O8" s="32">
+        <f>H8*L8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="35" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="18">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="C9" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*2)</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>(C9-B9)/360</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>(C9-B9)/365</f>
+        <v/>
+      </c>
+      <c r="F9" s="28">
+        <f>(C9-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G9" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1)))^((C9-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C9,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H9" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B9+C9)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B9+C9)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C9)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J9" s="32">
+        <f>K8</f>
+        <v/>
+      </c>
+      <c r="K9" s="32">
+        <f>J9*EXP(-I9*E9)</f>
+        <v/>
+      </c>
+      <c r="L9" s="32">
+        <f>J9-K9</f>
+        <v/>
+      </c>
+      <c r="M9" s="32">
+        <f>D9*G9*K9</f>
+        <v/>
+      </c>
+      <c r="N9" s="32">
+        <f>(D9/2)*H9*L9</f>
+        <v/>
+      </c>
+      <c r="O9" s="32">
+        <f>H9*L9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="18">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="C10" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*3)</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>(C10-B10)/360</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>(C10-B10)/365</f>
+        <v/>
+      </c>
+      <c r="F10" s="28">
+        <f>(C10-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G10" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1)))^((C10-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C10,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H10" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B10+C10)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B10+C10)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C10)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J10" s="32">
+        <f>K9</f>
+        <v/>
+      </c>
+      <c r="K10" s="32">
+        <f>J10*EXP(-I10*E10)</f>
+        <v/>
+      </c>
+      <c r="L10" s="32">
+        <f>J10-K10</f>
+        <v/>
+      </c>
+      <c r="M10" s="32">
+        <f>D10*G10*K10</f>
+        <v/>
+      </c>
+      <c r="N10" s="32">
+        <f>(D10/2)*H10*L10</f>
+        <v/>
+      </c>
+      <c r="O10" s="32">
+        <f>H10*L10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="B11" s="18">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="C11" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*4)</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>(C11-B11)/360</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>(C11-B11)/365</f>
+        <v/>
+      </c>
+      <c r="F11" s="28">
+        <f>(C11-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G11" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1)))^((C11-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C11,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H11" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B11+C11)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B11+C11)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C11)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J11" s="32">
+        <f>K10</f>
+        <v/>
+      </c>
+      <c r="K11" s="32">
+        <f>J11*EXP(-I11*E11)</f>
+        <v/>
+      </c>
+      <c r="L11" s="32">
+        <f>J11-K11</f>
+        <v/>
+      </c>
+      <c r="M11" s="32">
+        <f>D11*G11*K11</f>
+        <v/>
+      </c>
+      <c r="N11" s="32">
+        <f>(D11/2)*H11*L11</f>
+        <v/>
+      </c>
+      <c r="O11" s="32">
+        <f>H11*L11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="35" t="n">
+        <v>6</v>
+      </c>
+      <c r="B12" s="18">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="C12" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*5)</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>(C12-B12)/360</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>(C12-B12)/365</f>
+        <v/>
+      </c>
+      <c r="F12" s="28">
+        <f>(C12-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G12" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1)))^((C12-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C12,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H12" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B12+C12)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B12+C12)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C12)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J12" s="32">
+        <f>K11</f>
+        <v/>
+      </c>
+      <c r="K12" s="32">
+        <f>J12*EXP(-I12*E12)</f>
+        <v/>
+      </c>
+      <c r="L12" s="32">
+        <f>J12-K12</f>
+        <v/>
+      </c>
+      <c r="M12" s="32">
+        <f>D12*G12*K12</f>
+        <v/>
+      </c>
+      <c r="N12" s="32">
+        <f>(D12/2)*H12*L12</f>
+        <v/>
+      </c>
+      <c r="O12" s="32">
+        <f>H12*L12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="18">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="C13" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*6)</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>(C13-B13)/360</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>(C13-B13)/365</f>
+        <v/>
+      </c>
+      <c r="F13" s="28">
+        <f>(C13-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G13" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1)))^((C13-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C13,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H13" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B13+C13)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B13+C13)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C13)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J13" s="32">
+        <f>K12</f>
+        <v/>
+      </c>
+      <c r="K13" s="32">
+        <f>J13*EXP(-I13*E13)</f>
+        <v/>
+      </c>
+      <c r="L13" s="32">
+        <f>J13-K13</f>
+        <v/>
+      </c>
+      <c r="M13" s="32">
+        <f>D13*G13*K13</f>
+        <v/>
+      </c>
+      <c r="N13" s="32">
+        <f>(D13/2)*H13*L13</f>
+        <v/>
+      </c>
+      <c r="O13" s="32">
+        <f>H13*L13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="18">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="C14" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*7)</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>(C14-B14)/360</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>(C14-B14)/365</f>
+        <v/>
+      </c>
+      <c r="F14" s="28">
+        <f>(C14-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1)))^((C14-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C14,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H14" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B14+C14)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B14+C14)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C14)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J14" s="32">
+        <f>K13</f>
+        <v/>
+      </c>
+      <c r="K14" s="32">
+        <f>J14*EXP(-I14*E14)</f>
+        <v/>
+      </c>
+      <c r="L14" s="32">
+        <f>J14-K14</f>
+        <v/>
+      </c>
+      <c r="M14" s="32">
+        <f>D14*G14*K14</f>
+        <v/>
+      </c>
+      <c r="N14" s="32">
+        <f>(D14/2)*H14*L14</f>
+        <v/>
+      </c>
+      <c r="O14" s="32">
+        <f>H14*L14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="35" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="18">
+        <f>C14</f>
+        <v/>
+      </c>
+      <c r="C15" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*8)</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>(C15-B15)/360</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>(C15-B15)/365</f>
+        <v/>
+      </c>
+      <c r="F15" s="28">
+        <f>(C15-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1)))^((C15-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C15,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H15" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B15+C15)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B15+C15)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C15)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J15" s="32">
+        <f>K14</f>
+        <v/>
+      </c>
+      <c r="K15" s="32">
+        <f>J15*EXP(-I15*E15)</f>
+        <v/>
+      </c>
+      <c r="L15" s="32">
+        <f>J15-K15</f>
+        <v/>
+      </c>
+      <c r="M15" s="32">
+        <f>D15*G15*K15</f>
+        <v/>
+      </c>
+      <c r="N15" s="32">
+        <f>(D15/2)*H15*L15</f>
+        <v/>
+      </c>
+      <c r="O15" s="32">
+        <f>H15*L15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="18">
+        <f>C15</f>
+        <v/>
+      </c>
+      <c r="C16" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*9)</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>(C16-B16)/360</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>(C16-B16)/365</f>
+        <v/>
+      </c>
+      <c r="F16" s="28">
+        <f>(C16-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1)))^((C16-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C16,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H16" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B16+C16)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B16+C16)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I16" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C16)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J16" s="32">
+        <f>K15</f>
+        <v/>
+      </c>
+      <c r="K16" s="32">
+        <f>J16*EXP(-I16*E16)</f>
+        <v/>
+      </c>
+      <c r="L16" s="32">
+        <f>J16-K16</f>
+        <v/>
+      </c>
+      <c r="M16" s="32">
+        <f>D16*G16*K16</f>
+        <v/>
+      </c>
+      <c r="N16" s="32">
+        <f>(D16/2)*H16*L16</f>
+        <v/>
+      </c>
+      <c r="O16" s="32">
+        <f>H16*L16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="35" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="18">
+        <f>C16</f>
+        <v/>
+      </c>
+      <c r="C17" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*10)</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>(C17-B17)/360</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>(C17-B17)/365</f>
+        <v/>
+      </c>
+      <c r="F17" s="28">
+        <f>(C17-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1)))^((C17-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C17,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H17" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B17+C17)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B17+C17)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I17" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C17)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J17" s="32">
+        <f>K16</f>
+        <v/>
+      </c>
+      <c r="K17" s="32">
+        <f>J17*EXP(-I17*E17)</f>
+        <v/>
+      </c>
+      <c r="L17" s="32">
+        <f>J17-K17</f>
+        <v/>
+      </c>
+      <c r="M17" s="32">
+        <f>D17*G17*K17</f>
+        <v/>
+      </c>
+      <c r="N17" s="32">
+        <f>(D17/2)*H17*L17</f>
+        <v/>
+      </c>
+      <c r="O17" s="32">
+        <f>H17*L17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="35" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="18">
+        <f>C17</f>
+        <v/>
+      </c>
+      <c r="C18" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*11)</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>(C18-B18)/360</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>(C18-B18)/365</f>
+        <v/>
+      </c>
+      <c r="F18" s="28">
+        <f>(C18-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G18" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1)))^((C18-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C18,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H18" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B18+C18)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B18+C18)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I18" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C18)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J18" s="32">
+        <f>K17</f>
+        <v/>
+      </c>
+      <c r="K18" s="32">
+        <f>J18*EXP(-I18*E18)</f>
+        <v/>
+      </c>
+      <c r="L18" s="32">
+        <f>J18-K18</f>
+        <v/>
+      </c>
+      <c r="M18" s="32">
+        <f>D18*G18*K18</f>
+        <v/>
+      </c>
+      <c r="N18" s="32">
+        <f>(D18/2)*H18*L18</f>
+        <v/>
+      </c>
+      <c r="O18" s="32">
+        <f>H18*L18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="35" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="18">
+        <f>C18</f>
+        <v/>
+      </c>
+      <c r="C19" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*12)</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>(C19-B19)/360</f>
+        <v/>
+      </c>
+      <c r="E19" s="17">
+        <f>(C19-B19)/365</f>
+        <v/>
+      </c>
+      <c r="F19" s="28">
+        <f>(C19-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G19" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1)))^((C19-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C19,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H19" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B19+C19)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B19+C19)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I19" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C19)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J19" s="32">
+        <f>K18</f>
+        <v/>
+      </c>
+      <c r="K19" s="32">
+        <f>J19*EXP(-I19*E19)</f>
+        <v/>
+      </c>
+      <c r="L19" s="32">
+        <f>J19-K19</f>
+        <v/>
+      </c>
+      <c r="M19" s="32">
+        <f>D19*G19*K19</f>
+        <v/>
+      </c>
+      <c r="N19" s="32">
+        <f>(D19/2)*H19*L19</f>
+        <v/>
+      </c>
+      <c r="O19" s="32">
+        <f>H19*L19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="35" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="18">
+        <f>C19</f>
+        <v/>
+      </c>
+      <c r="C20" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*13)</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>(C20-B20)/360</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>(C20-B20)/365</f>
+        <v/>
+      </c>
+      <c r="F20" s="28">
+        <f>(C20-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1)))^((C20-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C20,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H20" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B20+C20)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B20+C20)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I20" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C20)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J20" s="32">
+        <f>K19</f>
+        <v/>
+      </c>
+      <c r="K20" s="32">
+        <f>J20*EXP(-I20*E20)</f>
+        <v/>
+      </c>
+      <c r="L20" s="32">
+        <f>J20-K20</f>
+        <v/>
+      </c>
+      <c r="M20" s="32">
+        <f>D20*G20*K20</f>
+        <v/>
+      </c>
+      <c r="N20" s="32">
+        <f>(D20/2)*H20*L20</f>
+        <v/>
+      </c>
+      <c r="O20" s="32">
+        <f>H20*L20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="35" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" s="18">
+        <f>C20</f>
+        <v/>
+      </c>
+      <c r="C21" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*14)</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>(C21-B21)/360</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>(C21-B21)/365</f>
+        <v/>
+      </c>
+      <c r="F21" s="28">
+        <f>(C21-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1)))^((C21-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C21,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H21" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B21+C21)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B21+C21)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I21" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C21)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J21" s="32">
+        <f>K20</f>
+        <v/>
+      </c>
+      <c r="K21" s="32">
+        <f>J21*EXP(-I21*E21)</f>
+        <v/>
+      </c>
+      <c r="L21" s="32">
+        <f>J21-K21</f>
+        <v/>
+      </c>
+      <c r="M21" s="32">
+        <f>D21*G21*K21</f>
+        <v/>
+      </c>
+      <c r="N21" s="32">
+        <f>(D21/2)*H21*L21</f>
+        <v/>
+      </c>
+      <c r="O21" s="32">
+        <f>H21*L21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="B22" s="18">
+        <f>C21</f>
+        <v/>
+      </c>
+      <c r="C22" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*15)</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>(C22-B22)/360</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>(C22-B22)/365</f>
+        <v/>
+      </c>
+      <c r="F22" s="28">
+        <f>(C22-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1)))^((C22-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C22,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H22" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B22+C22)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B22+C22)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I22" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C22)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J22" s="32">
+        <f>K21</f>
+        <v/>
+      </c>
+      <c r="K22" s="32">
+        <f>J22*EXP(-I22*E22)</f>
+        <v/>
+      </c>
+      <c r="L22" s="32">
+        <f>J22-K22</f>
+        <v/>
+      </c>
+      <c r="M22" s="32">
+        <f>D22*G22*K22</f>
+        <v/>
+      </c>
+      <c r="N22" s="32">
+        <f>(D22/2)*H22*L22</f>
+        <v/>
+      </c>
+      <c r="O22" s="32">
+        <f>H22*L22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="B23" s="18">
+        <f>C22</f>
+        <v/>
+      </c>
+      <c r="C23" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*16)</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>(C23-B23)/360</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>(C23-B23)/365</f>
+        <v/>
+      </c>
+      <c r="F23" s="28">
+        <f>(C23-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1)))^((C23-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C23,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H23" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B23+C23)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B23+C23)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I23" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C23)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J23" s="32">
+        <f>K22</f>
+        <v/>
+      </c>
+      <c r="K23" s="32">
+        <f>J23*EXP(-I23*E23)</f>
+        <v/>
+      </c>
+      <c r="L23" s="32">
+        <f>J23-K23</f>
+        <v/>
+      </c>
+      <c r="M23" s="32">
+        <f>D23*G23*K23</f>
+        <v/>
+      </c>
+      <c r="N23" s="32">
+        <f>(D23/2)*H23*L23</f>
+        <v/>
+      </c>
+      <c r="O23" s="32">
+        <f>H23*L23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="35" t="n">
+        <v>18</v>
+      </c>
+      <c r="B24" s="18">
+        <f>C23</f>
+        <v/>
+      </c>
+      <c r="C24" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*17)</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>(C24-B24)/360</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>(C24-B24)/365</f>
+        <v/>
+      </c>
+      <c r="F24" s="28">
+        <f>(C24-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1)))^((C24-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C24,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H24" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B24+C24)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B24+C24)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I24" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C24)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J24" s="32">
+        <f>K23</f>
+        <v/>
+      </c>
+      <c r="K24" s="32">
+        <f>J24*EXP(-I24*E24)</f>
+        <v/>
+      </c>
+      <c r="L24" s="32">
+        <f>J24-K24</f>
+        <v/>
+      </c>
+      <c r="M24" s="32">
+        <f>D24*G24*K24</f>
+        <v/>
+      </c>
+      <c r="N24" s="32">
+        <f>(D24/2)*H24*L24</f>
+        <v/>
+      </c>
+      <c r="O24" s="32">
+        <f>H24*L24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="B25" s="18">
+        <f>C24</f>
+        <v/>
+      </c>
+      <c r="C25" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*18)</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>(C25-B25)/360</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>(C25-B25)/365</f>
+        <v/>
+      </c>
+      <c r="F25" s="28">
+        <f>(C25-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G25" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1)))^((C25-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C25,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H25" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B25+C25)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B25+C25)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I25" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C25)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J25" s="32">
+        <f>K24</f>
+        <v/>
+      </c>
+      <c r="K25" s="32">
+        <f>J25*EXP(-I25*E25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="32">
+        <f>J25-K25</f>
+        <v/>
+      </c>
+      <c r="M25" s="32">
+        <f>D25*G25*K25</f>
+        <v/>
+      </c>
+      <c r="N25" s="32">
+        <f>(D25/2)*H25*L25</f>
+        <v/>
+      </c>
+      <c r="O25" s="32">
+        <f>H25*L25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="B26" s="18">
+        <f>C25</f>
+        <v/>
+      </c>
+      <c r="C26" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*19)</f>
+        <v/>
+      </c>
+      <c r="D26" s="17">
+        <f>(C26-B26)/360</f>
+        <v/>
+      </c>
+      <c r="E26" s="17">
+        <f>(C26-B26)/365</f>
+        <v/>
+      </c>
+      <c r="F26" s="28">
+        <f>(C26-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G26" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1)))^((C26-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C26,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H26" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B26+C26)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B26+C26)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I26" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C26)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J26" s="32">
+        <f>K25</f>
+        <v/>
+      </c>
+      <c r="K26" s="32">
+        <f>J26*EXP(-I26*E26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="32">
+        <f>J26-K26</f>
+        <v/>
+      </c>
+      <c r="M26" s="32">
+        <f>D26*G26*K26</f>
+        <v/>
+      </c>
+      <c r="N26" s="32">
+        <f>(D26/2)*H26*L26</f>
+        <v/>
+      </c>
+      <c r="O26" s="32">
+        <f>H26*L26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="35" t="n">
+        <v>21</v>
+      </c>
+      <c r="B27" s="18">
+        <f>C26</f>
+        <v/>
+      </c>
+      <c r="C27" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*20)</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>(C27-B27)/360</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>(C27-B27)/365</f>
+        <v/>
+      </c>
+      <c r="F27" s="28">
+        <f>(C27-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1)))^((C27-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C27,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H27" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B27+C27)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B27+C27)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I27" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C27)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J27" s="32">
+        <f>K26</f>
+        <v/>
+      </c>
+      <c r="K27" s="32">
+        <f>J27*EXP(-I27*E27)</f>
+        <v/>
+      </c>
+      <c r="L27" s="32">
+        <f>J27-K27</f>
+        <v/>
+      </c>
+      <c r="M27" s="32">
+        <f>D27*G27*K27</f>
+        <v/>
+      </c>
+      <c r="N27" s="32">
+        <f>(D27/2)*H27*L27</f>
+        <v/>
+      </c>
+      <c r="O27" s="32">
+        <f>H27*L27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="B28" s="18">
+        <f>C27</f>
+        <v/>
+      </c>
+      <c r="C28" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*21)</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>(C28-B28)/360</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>(C28-B28)/365</f>
+        <v/>
+      </c>
+      <c r="F28" s="28">
+        <f>(C28-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G28" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1)))^((C28-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C28,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H28" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B28+C28)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B28+C28)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I28" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C28)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J28" s="32">
+        <f>K27</f>
+        <v/>
+      </c>
+      <c r="K28" s="32">
+        <f>J28*EXP(-I28*E28)</f>
+        <v/>
+      </c>
+      <c r="L28" s="32">
+        <f>J28-K28</f>
+        <v/>
+      </c>
+      <c r="M28" s="32">
+        <f>D28*G28*K28</f>
+        <v/>
+      </c>
+      <c r="N28" s="32">
+        <f>(D28/2)*H28*L28</f>
+        <v/>
+      </c>
+      <c r="O28" s="32">
+        <f>H28*L28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n">
+        <v>23</v>
+      </c>
+      <c r="B29" s="18">
+        <f>C28</f>
+        <v/>
+      </c>
+      <c r="C29" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*22)</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>(C29-B29)/360</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>(C29-B29)/365</f>
+        <v/>
+      </c>
+      <c r="F29" s="28">
+        <f>(C29-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G29" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1)))^((C29-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C29,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H29" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B29+C29)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B29+C29)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I29" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C29)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J29" s="32">
+        <f>K28</f>
+        <v/>
+      </c>
+      <c r="K29" s="32">
+        <f>J29*EXP(-I29*E29)</f>
+        <v/>
+      </c>
+      <c r="L29" s="32">
+        <f>J29-K29</f>
+        <v/>
+      </c>
+      <c r="M29" s="32">
+        <f>D29*G29*K29</f>
+        <v/>
+      </c>
+      <c r="N29" s="32">
+        <f>(D29/2)*H29*L29</f>
+        <v/>
+      </c>
+      <c r="O29" s="32">
+        <f>H29*L29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="B30" s="18">
+        <f>C29</f>
+        <v/>
+      </c>
+      <c r="C30" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*23)</f>
+        <v/>
+      </c>
+      <c r="D30" s="17">
+        <f>(C30-B30)/360</f>
+        <v/>
+      </c>
+      <c r="E30" s="17">
+        <f>(C30-B30)/365</f>
+        <v/>
+      </c>
+      <c r="F30" s="28">
+        <f>(C30-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G30" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1)))^((C30-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C30,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H30" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B30+C30)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B30+C30)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I30" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C30)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J30" s="32">
+        <f>K29</f>
+        <v/>
+      </c>
+      <c r="K30" s="32">
+        <f>J30*EXP(-I30*E30)</f>
+        <v/>
+      </c>
+      <c r="L30" s="32">
+        <f>J30-K30</f>
+        <v/>
+      </c>
+      <c r="M30" s="32">
+        <f>D30*G30*K30</f>
+        <v/>
+      </c>
+      <c r="N30" s="32">
+        <f>(D30/2)*H30*L30</f>
+        <v/>
+      </c>
+      <c r="O30" s="32">
+        <f>H30*L30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="B31" s="18">
+        <f>C30</f>
+        <v/>
+      </c>
+      <c r="C31" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*24)</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>(C31-B31)/360</f>
+        <v/>
+      </c>
+      <c r="E31" s="17">
+        <f>(C31-B31)/365</f>
+        <v/>
+      </c>
+      <c r="F31" s="28">
+        <f>(C31-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G31" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1)))^((C31-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C31,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H31" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B31+C31)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B31+C31)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I31" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C31)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J31" s="32">
+        <f>K30</f>
+        <v/>
+      </c>
+      <c r="K31" s="32">
+        <f>J31*EXP(-I31*E31)</f>
+        <v/>
+      </c>
+      <c r="L31" s="32">
+        <f>J31-K31</f>
+        <v/>
+      </c>
+      <c r="M31" s="32">
+        <f>D31*G31*K31</f>
+        <v/>
+      </c>
+      <c r="N31" s="32">
+        <f>(D31/2)*H31*L31</f>
+        <v/>
+      </c>
+      <c r="O31" s="32">
+        <f>H31*L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="B32" s="18">
+        <f>C31</f>
+        <v/>
+      </c>
+      <c r="C32" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*25)</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>(C32-B32)/360</f>
+        <v/>
+      </c>
+      <c r="E32" s="17">
+        <f>(C32-B32)/365</f>
+        <v/>
+      </c>
+      <c r="F32" s="28">
+        <f>(C32-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G32" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1)))^((C32-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C32,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H32" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B32+C32)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B32+C32)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I32" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C32)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J32" s="32">
+        <f>K31</f>
+        <v/>
+      </c>
+      <c r="K32" s="32">
+        <f>J32*EXP(-I32*E32)</f>
+        <v/>
+      </c>
+      <c r="L32" s="32">
+        <f>J32-K32</f>
+        <v/>
+      </c>
+      <c r="M32" s="32">
+        <f>D32*G32*K32</f>
+        <v/>
+      </c>
+      <c r="N32" s="32">
+        <f>(D32/2)*H32*L32</f>
+        <v/>
+      </c>
+      <c r="O32" s="32">
+        <f>H32*L32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="B33" s="18">
+        <f>C32</f>
+        <v/>
+      </c>
+      <c r="C33" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*26)</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>(C33-B33)/360</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>(C33-B33)/365</f>
+        <v/>
+      </c>
+      <c r="F33" s="28">
+        <f>(C33-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G33" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1)))^((C33-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C33,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H33" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B33+C33)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B33+C33)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I33" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C33)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J33" s="32">
+        <f>K32</f>
+        <v/>
+      </c>
+      <c r="K33" s="32">
+        <f>J33*EXP(-I33*E33)</f>
+        <v/>
+      </c>
+      <c r="L33" s="32">
+        <f>J33-K33</f>
+        <v/>
+      </c>
+      <c r="M33" s="32">
+        <f>D33*G33*K33</f>
+        <v/>
+      </c>
+      <c r="N33" s="32">
+        <f>(D33/2)*H33*L33</f>
+        <v/>
+      </c>
+      <c r="O33" s="32">
+        <f>H33*L33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="35" t="n">
+        <v>28</v>
+      </c>
+      <c r="B34" s="18">
+        <f>C33</f>
+        <v/>
+      </c>
+      <c r="C34" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*27)</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>(C34-B34)/360</f>
+        <v/>
+      </c>
+      <c r="E34" s="17">
+        <f>(C34-B34)/365</f>
+        <v/>
+      </c>
+      <c r="F34" s="28">
+        <f>(C34-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G34" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1)))^((C34-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C34,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H34" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B34+C34)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B34+C34)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I34" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C34)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J34" s="32">
+        <f>K33</f>
+        <v/>
+      </c>
+      <c r="K34" s="32">
+        <f>J34*EXP(-I34*E34)</f>
+        <v/>
+      </c>
+      <c r="L34" s="32">
+        <f>J34-K34</f>
+        <v/>
+      </c>
+      <c r="M34" s="32">
+        <f>D34*G34*K34</f>
+        <v/>
+      </c>
+      <c r="N34" s="32">
+        <f>(D34/2)*H34*L34</f>
+        <v/>
+      </c>
+      <c r="O34" s="32">
+        <f>H34*L34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="35" t="n">
+        <v>29</v>
+      </c>
+      <c r="B35" s="18">
+        <f>C34</f>
+        <v/>
+      </c>
+      <c r="C35" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*28)</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>(C35-B35)/360</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>(C35-B35)/365</f>
+        <v/>
+      </c>
+      <c r="F35" s="28">
+        <f>(C35-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G35" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1)))^((C35-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C35,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H35" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B35+C35)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B35+C35)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I35" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C35)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J35" s="32">
+        <f>K34</f>
+        <v/>
+      </c>
+      <c r="K35" s="32">
+        <f>J35*EXP(-I35*E35)</f>
+        <v/>
+      </c>
+      <c r="L35" s="32">
+        <f>J35-K35</f>
+        <v/>
+      </c>
+      <c r="M35" s="32">
+        <f>D35*G35*K35</f>
+        <v/>
+      </c>
+      <c r="N35" s="32">
+        <f>(D35/2)*H35*L35</f>
+        <v/>
+      </c>
+      <c r="O35" s="32">
+        <f>H35*L35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="B36" s="18">
+        <f>C35</f>
+        <v/>
+      </c>
+      <c r="C36" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*29)</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>(C36-B36)/360</f>
+        <v/>
+      </c>
+      <c r="E36" s="17">
+        <f>(C36-B36)/365</f>
+        <v/>
+      </c>
+      <c r="F36" s="28">
+        <f>(C36-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G36" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1)))^((C36-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C36,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H36" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B36+C36)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B36+C36)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I36" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C36)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J36" s="32">
+        <f>K35</f>
+        <v/>
+      </c>
+      <c r="K36" s="32">
+        <f>J36*EXP(-I36*E36)</f>
+        <v/>
+      </c>
+      <c r="L36" s="32">
+        <f>J36-K36</f>
+        <v/>
+      </c>
+      <c r="M36" s="32">
+        <f>D36*G36*K36</f>
+        <v/>
+      </c>
+      <c r="N36" s="32">
+        <f>(D36/2)*H36*L36</f>
+        <v/>
+      </c>
+      <c r="O36" s="32">
+        <f>H36*L36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="B37" s="18">
+        <f>C36</f>
+        <v/>
+      </c>
+      <c r="C37" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*30)</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>(C37-B37)/360</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>(C37-B37)/365</f>
+        <v/>
+      </c>
+      <c r="F37" s="28">
+        <f>(C37-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G37" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1)))^((C37-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C37,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H37" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B37+C37)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B37+C37)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I37" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C37)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J37" s="32">
+        <f>K36</f>
+        <v/>
+      </c>
+      <c r="K37" s="32">
+        <f>J37*EXP(-I37*E37)</f>
+        <v/>
+      </c>
+      <c r="L37" s="32">
+        <f>J37-K37</f>
+        <v/>
+      </c>
+      <c r="M37" s="32">
+        <f>D37*G37*K37</f>
+        <v/>
+      </c>
+      <c r="N37" s="32">
+        <f>(D37/2)*H37*L37</f>
+        <v/>
+      </c>
+      <c r="O37" s="32">
+        <f>H37*L37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="35" t="n">
+        <v>32</v>
+      </c>
+      <c r="B38" s="18">
+        <f>C37</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*31)</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>(C38-B38)/360</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>(C38-B38)/365</f>
+        <v/>
+      </c>
+      <c r="F38" s="28">
+        <f>(C38-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G38" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1)))^((C38-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C38,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H38" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B38+C38)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B38+C38)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I38" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C38)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J38" s="32">
+        <f>K37</f>
+        <v/>
+      </c>
+      <c r="K38" s="32">
+        <f>J38*EXP(-I38*E38)</f>
+        <v/>
+      </c>
+      <c r="L38" s="32">
+        <f>J38-K38</f>
+        <v/>
+      </c>
+      <c r="M38" s="32">
+        <f>D38*G38*K38</f>
+        <v/>
+      </c>
+      <c r="N38" s="32">
+        <f>(D38/2)*H38*L38</f>
+        <v/>
+      </c>
+      <c r="O38" s="32">
+        <f>H38*L38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B39" s="18">
+        <f>C38</f>
+        <v/>
+      </c>
+      <c r="C39" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*32)</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>(C39-B39)/360</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>(C39-B39)/365</f>
+        <v/>
+      </c>
+      <c r="F39" s="28">
+        <f>(C39-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G39" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1)))^((C39-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C39,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H39" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B39+C39)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B39+C39)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I39" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C39)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J39" s="32">
+        <f>K38</f>
+        <v/>
+      </c>
+      <c r="K39" s="32">
+        <f>J39*EXP(-I39*E39)</f>
+        <v/>
+      </c>
+      <c r="L39" s="32">
+        <f>J39-K39</f>
+        <v/>
+      </c>
+      <c r="M39" s="32">
+        <f>D39*G39*K39</f>
+        <v/>
+      </c>
+      <c r="N39" s="32">
+        <f>(D39/2)*H39*L39</f>
+        <v/>
+      </c>
+      <c r="O39" s="32">
+        <f>H39*L39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B40" s="18">
+        <f>C39</f>
+        <v/>
+      </c>
+      <c r="C40" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*33)</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>(C40-B40)/360</f>
+        <v/>
+      </c>
+      <c r="E40" s="17">
+        <f>(C40-B40)/365</f>
+        <v/>
+      </c>
+      <c r="F40" s="28">
+        <f>(C40-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G40" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1)))^((C40-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C40,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H40" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B40+C40)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B40+C40)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I40" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C40)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J40" s="32">
+        <f>K39</f>
+        <v/>
+      </c>
+      <c r="K40" s="32">
+        <f>J40*EXP(-I40*E40)</f>
+        <v/>
+      </c>
+      <c r="L40" s="32">
+        <f>J40-K40</f>
+        <v/>
+      </c>
+      <c r="M40" s="32">
+        <f>D40*G40*K40</f>
+        <v/>
+      </c>
+      <c r="N40" s="32">
+        <f>(D40/2)*H40*L40</f>
+        <v/>
+      </c>
+      <c r="O40" s="32">
+        <f>H40*L40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="35" t="n">
+        <v>35</v>
+      </c>
+      <c r="B41" s="18">
+        <f>C40</f>
+        <v/>
+      </c>
+      <c r="C41" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*34)</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>(C41-B41)/360</f>
+        <v/>
+      </c>
+      <c r="E41" s="17">
+        <f>(C41-B41)/365</f>
+        <v/>
+      </c>
+      <c r="F41" s="28">
+        <f>(C41-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G41" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1)))^((C41-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C41,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H41" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B41+C41)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B41+C41)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I41" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C41)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J41" s="32">
+        <f>K40</f>
+        <v/>
+      </c>
+      <c r="K41" s="32">
+        <f>J41*EXP(-I41*E41)</f>
+        <v/>
+      </c>
+      <c r="L41" s="32">
+        <f>J41-K41</f>
+        <v/>
+      </c>
+      <c r="M41" s="32">
+        <f>D41*G41*K41</f>
+        <v/>
+      </c>
+      <c r="N41" s="32">
+        <f>(D41/2)*H41*L41</f>
+        <v/>
+      </c>
+      <c r="O41" s="32">
+        <f>H41*L41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="35" t="n">
+        <v>36</v>
+      </c>
+      <c r="B42" s="18">
+        <f>C41</f>
+        <v/>
+      </c>
+      <c r="C42" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*35)</f>
+        <v/>
+      </c>
+      <c r="D42" s="17">
+        <f>(C42-B42)/360</f>
+        <v/>
+      </c>
+      <c r="E42" s="17">
+        <f>(C42-B42)/365</f>
+        <v/>
+      </c>
+      <c r="F42" s="28">
+        <f>(C42-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G42" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1)))^((C42-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C42,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H42" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B42+C42)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B42+C42)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I42" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C42)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J42" s="32">
+        <f>K41</f>
+        <v/>
+      </c>
+      <c r="K42" s="32">
+        <f>J42*EXP(-I42*E42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="32">
+        <f>J42-K42</f>
+        <v/>
+      </c>
+      <c r="M42" s="32">
+        <f>D42*G42*K42</f>
+        <v/>
+      </c>
+      <c r="N42" s="32">
+        <f>(D42/2)*H42*L42</f>
+        <v/>
+      </c>
+      <c r="O42" s="32">
+        <f>H42*L42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="35" t="n">
+        <v>37</v>
+      </c>
+      <c r="B43" s="18">
+        <f>C42</f>
+        <v/>
+      </c>
+      <c r="C43" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*36)</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>(C43-B43)/360</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>(C43-B43)/365</f>
+        <v/>
+      </c>
+      <c r="F43" s="28">
+        <f>(C43-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G43" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1)))^((C43-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C43,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H43" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B43+C43)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B43+C43)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I43" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C43)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J43" s="32">
+        <f>K42</f>
+        <v/>
+      </c>
+      <c r="K43" s="32">
+        <f>J43*EXP(-I43*E43)</f>
+        <v/>
+      </c>
+      <c r="L43" s="32">
+        <f>J43-K43</f>
+        <v/>
+      </c>
+      <c r="M43" s="32">
+        <f>D43*G43*K43</f>
+        <v/>
+      </c>
+      <c r="N43" s="32">
+        <f>(D43/2)*H43*L43</f>
+        <v/>
+      </c>
+      <c r="O43" s="32">
+        <f>H43*L43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="35" t="n">
+        <v>38</v>
+      </c>
+      <c r="B44" s="18">
+        <f>C43</f>
+        <v/>
+      </c>
+      <c r="C44" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*37)</f>
+        <v/>
+      </c>
+      <c r="D44" s="17">
+        <f>(C44-B44)/360</f>
+        <v/>
+      </c>
+      <c r="E44" s="17">
+        <f>(C44-B44)/365</f>
+        <v/>
+      </c>
+      <c r="F44" s="28">
+        <f>(C44-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G44" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1)))^((C44-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C44,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H44" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B44+C44)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B44+C44)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I44" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C44)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J44" s="32">
+        <f>K43</f>
+        <v/>
+      </c>
+      <c r="K44" s="32">
+        <f>J44*EXP(-I44*E44)</f>
+        <v/>
+      </c>
+      <c r="L44" s="32">
+        <f>J44-K44</f>
+        <v/>
+      </c>
+      <c r="M44" s="32">
+        <f>D44*G44*K44</f>
+        <v/>
+      </c>
+      <c r="N44" s="32">
+        <f>(D44/2)*H44*L44</f>
+        <v/>
+      </c>
+      <c r="O44" s="32">
+        <f>H44*L44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="35" t="n">
+        <v>39</v>
+      </c>
+      <c r="B45" s="18">
+        <f>C44</f>
+        <v/>
+      </c>
+      <c r="C45" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*38)</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>(C45-B45)/360</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>(C45-B45)/365</f>
+        <v/>
+      </c>
+      <c r="F45" s="28">
+        <f>(C45-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G45" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1)))^((C45-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C45,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H45" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B45+C45)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B45+C45)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I45" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C45)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J45" s="32">
+        <f>K44</f>
+        <v/>
+      </c>
+      <c r="K45" s="32">
+        <f>J45*EXP(-I45*E45)</f>
+        <v/>
+      </c>
+      <c r="L45" s="32">
+        <f>J45-K45</f>
+        <v/>
+      </c>
+      <c r="M45" s="32">
+        <f>D45*G45*K45</f>
+        <v/>
+      </c>
+      <c r="N45" s="32">
+        <f>(D45/2)*H45*L45</f>
+        <v/>
+      </c>
+      <c r="O45" s="32">
+        <f>H45*L45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="35" t="n">
+        <v>40</v>
+      </c>
+      <c r="B46" s="18">
+        <f>C45</f>
+        <v/>
+      </c>
+      <c r="C46" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*39)</f>
+        <v/>
+      </c>
+      <c r="D46" s="17">
+        <f>(C46-B46)/360</f>
+        <v/>
+      </c>
+      <c r="E46" s="17">
+        <f>(C46-B46)/365</f>
+        <v/>
+      </c>
+      <c r="F46" s="28">
+        <f>(C46-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="G46" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1)))^((C46-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH(C46,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="H46" s="33">
+        <f>IFERROR(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1))*(INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1)+1)/INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1)))^(((B46+C46)/2-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1)))/(INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1)+1)-INDEX('Curve_Interface'!$K$8:$K$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1)))),INDEX('Curve_Interface'!$L$8:$L$40,MATCH((B46+C46)/2,'Curve_Interface'!$K$8:$K$40,1)))</f>
+        <v/>
+      </c>
+      <c r="I46" s="49">
+        <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C46)+1,6))</f>
+        <v/>
+      </c>
+      <c r="J46" s="32">
+        <f>K45</f>
+        <v/>
+      </c>
+      <c r="K46" s="32">
+        <f>J46*EXP(-I46*E46)</f>
+        <v/>
+      </c>
+      <c r="L46" s="32">
+        <f>J46-K46</f>
+        <v/>
+      </c>
+      <c r="M46" s="32">
+        <f>D46*G46*K46</f>
+        <v/>
+      </c>
+      <c r="N46" s="32">
+        <f>(D46/2)*H46*L46</f>
+        <v/>
+      </c>
+      <c r="O46" s="32">
+        <f>H46*L46</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:O5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CDS_Pricer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Price a CDS off the SOFR + hazard curves (protection − premium legs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
+      <c r="B4" s="21">
+        <f>CDS_Parameters!$B$9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Recovery R</t>
+        </is>
+      </c>
+      <c r="B5" s="55">
+        <f>CDS_Parameters!$B$8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Contractual coupon (bp)</t>
+        </is>
+      </c>
+      <c r="B6" s="40">
+        <f>CDS_Parameters!$B$10</f>
+        <v/>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Overtype to price an off-market coupon.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Maturity (tenor yrs)</t>
+        </is>
+      </c>
+      <c r="B7" s="40" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>EDATE('Curve_Interface'!$F$7,3*(4*B7-1))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="B9" s="6">
+        <f>CDS_Parameters!$B$15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="56" t="inlineStr">
+        <is>
+          <t>RESULTS</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>RPV01 (risky annuity)</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
+        <v/>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>Scheduled + accrual-on-default.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Protection PV</t>
+        </is>
+      </c>
+      <c r="B13" s="42">
+        <f>B4*(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Premium PV (@ coupon)</t>
+        </is>
+      </c>
+      <c r="B14" s="42">
+        <f>B4*(B6/10000)*B12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Par spread (bp)</t>
+        </is>
+      </c>
+      <c r="B15" s="28">
+        <f>(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)/B12*10000</f>
+        <v/>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>Coupon that makes PV=0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>PV — protection buyer</t>
+        </is>
+      </c>
+      <c r="B16" s="42">
+        <f>B13-B14</f>
+        <v/>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
+        <is>
+          <t>Protection − Premium.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>PV to your direction</t>
+        </is>
+      </c>
+      <c r="B17" s="42">
+        <f>IF(B9="Buy protection",B13-B14,B14-B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Upfront (% notional)</t>
+        </is>
+      </c>
+      <c r="B18" s="57">
+        <f>B17/B4*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>CS01 (per 1bp spread)</t>
+        </is>
+      </c>
+      <c r="B19" s="42">
+        <f>B4*(B6/10000+0.0001)*B12-B4*(B6/10000)*B12</f>
+        <v/>
+      </c>
+      <c r="C19" s="16" t="inlineStr">
+        <is>
+          <t>≈ Notional*RPV01*1bp.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C6:H6"/>
+    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C12:H12"/>
+    <mergeCell ref="C15:H15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CDS_Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Internal checks + the flat-curve approximation s ≈ (1-R)·lambda</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>Q(0) = 1</t>
+        </is>
+      </c>
+      <c r="B5" s="58">
+        <f>CDS_Schedule!J7</f>
+        <v/>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>1 (exact)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>Survival monotone (min ΔPD ≥ 0)</t>
+        </is>
+      </c>
+      <c r="B6" s="58">
+        <f>MIN(CDS_Schedule!$L$7:$L$46)</f>
+        <v/>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>≥ 0 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>All hazards ≥ 0</t>
+        </is>
+      </c>
+      <c r="B7" s="58">
+        <f>MIN(Hazard_Bootstrap!$D$7:$D$12)</f>
+        <v/>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>≥ 0 ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>Q(T) in (0,1]</t>
+        </is>
+      </c>
+      <c r="B8" s="58">
+        <f>AND(MIN(CDS_Schedule!$K$7:$K$46)&gt;0,MAX(CDS_Schedule!$K$7:$K$46)&lt;=1)</f>
+        <v/>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>TRUE ✓</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>Max |repricing error| (bp)</t>
+        </is>
+      </c>
+      <c r="B9" s="58">
+        <f>MAX(ABS(Hazard_Bootstrap!$J$7:$J$12))</f>
+        <v/>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>→0 after Goal Seek (&lt;0.01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Approx check:  lambda ≈ s/(1-R)   (exact only for a flat curve)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>Bootstrapped lambda</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>s/(1-R)</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="B13" s="48">
+        <f>Hazard_Bootstrap!D7</f>
+        <v/>
+      </c>
+      <c r="C13" s="48">
+        <f>CDS_Quotes!G7</f>
+        <v/>
+      </c>
+      <c r="D13" s="48">
+        <f>B13-C13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="B14" s="48">
+        <f>Hazard_Bootstrap!D8</f>
+        <v/>
+      </c>
+      <c r="C14" s="48">
+        <f>CDS_Quotes!G8</f>
+        <v/>
+      </c>
+      <c r="D14" s="48">
+        <f>B14-C14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="B15" s="48">
+        <f>Hazard_Bootstrap!D9</f>
+        <v/>
+      </c>
+      <c r="C15" s="48">
+        <f>CDS_Quotes!G9</f>
+        <v/>
+      </c>
+      <c r="D15" s="48">
+        <f>B15-C15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>5Y</t>
+        </is>
+      </c>
+      <c r="B16" s="48">
+        <f>Hazard_Bootstrap!D10</f>
+        <v/>
+      </c>
+      <c r="C16" s="48">
+        <f>CDS_Quotes!G10</f>
+        <v/>
+      </c>
+      <c r="D16" s="48">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>7Y</t>
+        </is>
+      </c>
+      <c r="B17" s="48">
+        <f>Hazard_Bootstrap!D11</f>
+        <v/>
+      </c>
+      <c r="C17" s="48">
+        <f>CDS_Quotes!G11</f>
+        <v/>
+      </c>
+      <c r="D17" s="48">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>10Y</t>
+        </is>
+      </c>
+      <c r="B18" s="48">
+        <f>Hazard_Bootstrap!D12</f>
+        <v/>
+      </c>
+      <c r="C18" s="48">
+        <f>CDS_Quotes!G12</f>
+        <v/>
+      </c>
+      <c r="D18" s="48">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:F11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -7621,7 +7621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7817,26 +7817,89 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>CS01 (per 1bp spread)</t>
-        </is>
-      </c>
-      <c r="B19" s="42">
-        <f>B4*(B6/10000+0.0001)*B12-B4*(B6/10000)*B12</f>
-        <v/>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>≈ Notional*RPV01*1bp.</t>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>RISK MEASURES (analytic, first-order)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>CS01  (per +1bp spread)</t>
+        </is>
+      </c>
+      <c r="B22" s="42">
+        <f>B4*B12*0.0001</f>
+        <v/>
+      </c>
+      <c r="C22" s="16" t="inlineStr">
+        <is>
+          <t>Spread DV01 = Notional*RPV01*1bp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>IR01 / DV01  (per +1bp SOFR)</t>
+        </is>
+      </c>
+      <c r="B23" s="42">
+        <f>-(B4*(1-B5)*SUMPRODUCT((CDS_Schedule!$C$7:$C$46&lt;=B8)*CDS_Schedule!$O$7:$O$46*CDS_Schedule!$F$7:$F$46)-B4*(B6/10000)*SUMPRODUCT((CDS_Schedule!$C$7:$C$46&lt;=B8)*(CDS_Schedule!$M$7:$M$46+CDS_Schedule!$N$7:$N$46)*CDS_Schedule!$F$7:$F$46))*0.0001</f>
+        <v/>
+      </c>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>Net-leg dollar duration x 1bp (small for CDS).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Rec01  (per +1% recovery)</t>
+        </is>
+      </c>
+      <c r="B24" s="42">
+        <f>-B4*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)*0.01</f>
+        <v/>
+      </c>
+      <c r="C24" s="16" t="inlineStr">
+        <is>
+          <t>Sticky-hazard (hazards held; proper Rec01 re-fits spreads).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Jump-to-default (immediate)</t>
+        </is>
+      </c>
+      <c r="B25" s="43">
+        <f>IF(B9="Buy protection",B4*(1-B5),-B4*(1-B5))-B17</f>
+        <v/>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>Default-now P&amp;L to your direction: LGD payout - current PV.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="9">
+    <mergeCell ref="C25:H25"/>
     <mergeCell ref="C6:H6"/>
-    <mergeCell ref="C19:H19"/>
+    <mergeCell ref="C24:H24"/>
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="C16:H16"/>
+    <mergeCell ref="C22:H22"/>
+    <mergeCell ref="C23:H23"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="C15:H15"/>
   </mergeCells>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -4535,7 +4535,7 @@
         <v>40</v>
       </c>
       <c r="F7" s="31">
-        <f>IFERROR(BDP(D7,"PX_LAST"),E7)</f>
+        <f>IF(D7="",E7,IFERROR(BDP(D7,"PX_LAST"),E7))</f>
         <v/>
       </c>
       <c r="G7" s="49">
@@ -4561,7 +4561,7 @@
         <v>55</v>
       </c>
       <c r="F8" s="31">
-        <f>IFERROR(BDP(D8,"PX_LAST"),E8)</f>
+        <f>IF(D8="",E8,IFERROR(BDP(D8,"PX_LAST"),E8))</f>
         <v/>
       </c>
       <c r="G8" s="49">
@@ -4587,7 +4587,7 @@
         <v>70</v>
       </c>
       <c r="F9" s="31">
-        <f>IFERROR(BDP(D9,"PX_LAST"),E9)</f>
+        <f>IF(D9="",E9,IFERROR(BDP(D9,"PX_LAST"),E9))</f>
         <v/>
       </c>
       <c r="G9" s="49">
@@ -4613,7 +4613,7 @@
         <v>95</v>
       </c>
       <c r="F10" s="31">
-        <f>IFERROR(BDP(D10,"PX_LAST"),E10)</f>
+        <f>IF(D10="",E10,IFERROR(BDP(D10,"PX_LAST"),E10))</f>
         <v/>
       </c>
       <c r="G10" s="49">
@@ -4639,7 +4639,7 @@
         <v>115</v>
       </c>
       <c r="F11" s="31">
-        <f>IFERROR(BDP(D11,"PX_LAST"),E11)</f>
+        <f>IF(D11="",E11,IFERROR(BDP(D11,"PX_LAST"),E11))</f>
         <v/>
       </c>
       <c r="G11" s="49">
@@ -4665,7 +4665,7 @@
         <v>135</v>
       </c>
       <c r="F12" s="31">
-        <f>IFERROR(BDP(D12,"PX_LAST"),E12)</f>
+        <f>IF(D12="",E12,IFERROR(BDP(D12,"PX_LAST"),E12))</f>
         <v/>
       </c>
       <c r="G12" s="49">
@@ -13024,7 +13024,7 @@
         <v/>
       </c>
       <c r="H23" s="29">
-        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))),(1-(E23/100)*G23)/(1+(E23/100)*F23))</f>
+        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))))-((1-(E23/100)*G23)/(1+(E23/100)*F23)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))),((1-(E23/100)*G23)/(1+(E23/100)*F23))),((1-(E23/100)*G23)/(1+(E23/100)*F23)))</f>
         <v/>
       </c>
       <c r="I23" s="17" t="n">
@@ -13044,7 +13044,7 @@
         <v/>
       </c>
       <c r="N23" s="6">
-        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))))-((1-(E23/100)*G23)/(1+(E23/100)*F23)))&lt;0.03),"SR3 futures","OIS fallback")</f>
         <v/>
       </c>
       <c r="O23" s="6">
@@ -13123,7 +13123,7 @@
         <v/>
       </c>
       <c r="H24" s="29">
-        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))),(1-(E24/100)*G24)/(1+(E24/100)*F24))</f>
+        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))))-((1-(E24/100)*G24)/(1+(E24/100)*F24)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))),((1-(E24/100)*G24)/(1+(E24/100)*F24))),((1-(E24/100)*G24)/(1+(E24/100)*F24)))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -13144,7 +13144,7 @@
         <v/>
       </c>
       <c r="N24" s="6">
-        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))))-((1-(E24/100)*G24)/(1+(E24/100)*F24)))&lt;0.03),"SR3 futures","OIS fallback")</f>
         <v/>
       </c>
       <c r="O24" s="6">
@@ -13223,7 +13223,7 @@
         <v/>
       </c>
       <c r="H25" s="29">
-        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))),(1-(E25/100)*G25)/(1+(E25/100)*F25))</f>
+        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))))-((1-(E25/100)*G25)/(1+(E25/100)*F25)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))),((1-(E25/100)*G25)/(1+(E25/100)*F25))),((1-(E25/100)*G25)/(1+(E25/100)*F25)))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -13244,7 +13244,7 @@
         <v/>
       </c>
       <c r="N25" s="6">
-        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))))-((1-(E25/100)*G25)/(1+(E25/100)*F25)))&lt;0.03),"SR3 futures","OIS fallback")</f>
         <v/>
       </c>
       <c r="O25" s="6">
@@ -13323,7 +13323,7 @@
         <v/>
       </c>
       <c r="H26" s="29">
-        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))),(1-(E26/100)*G26)/(1+(E26/100)*F26))</f>
+        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))))-((1-(E26/100)*G26)/(1+(E26/100)*F26)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))),((1-(E26/100)*G26)/(1+(E26/100)*F26))),((1-(E26/100)*G26)/(1+(E26/100)*F26)))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -13344,7 +13344,7 @@
         <v/>
       </c>
       <c r="N26" s="6">
-        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))))-((1-(E26/100)*G26)/(1+(E26/100)*F26)))&lt;0.03),"SR3 futures","OIS fallback")</f>
         <v/>
       </c>
       <c r="O26" s="6">
@@ -13423,7 +13423,7 @@
         <v/>
       </c>
       <c r="H27" s="29">
-        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))),(1-(E27/100)*G27)/(1+(E27/100)*F27))</f>
+        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))))-((1-(E27/100)*G27)/(1+(E27/100)*F27)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))),((1-(E27/100)*G27)/(1+(E27/100)*F27))),((1-(E27/100)*G27)/(1+(E27/100)*F27)))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -13444,7 +13444,7 @@
         <v/>
       </c>
       <c r="N27" s="6">
-        <f>IF(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))),"SR3 futures","OIS fallback")</f>
+        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))))-((1-(E27/100)*G27)/(1+(E27/100)*F27)))&lt;0.03),"SR3 futures","OIS fallback")</f>
         <v/>
       </c>
       <c r="O27" s="6">
@@ -18394,16 +18394,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -18423,7 +18421,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Curve name</t>
+          <t>Curve name:</t>
         </is>
       </c>
       <c r="B4" s="19">
@@ -18434,7 +18432,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Curve date</t>
+          <t>Curve date:</t>
         </is>
       </c>
       <c r="B5" s="44">
@@ -18442,393 +18440,662 @@
         <v/>
       </c>
     </row>
-    <row r="6" ht="46" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>The anchor cell A8 holds =BDS(S490_TKR,"CURVE_TENOR_RATES") and spills raw below in Bloomberg's own column order (typically tenor, curve member, maturity, mid rate). It is NOT pre-labeled, because forcing headers/date-formats mis-aligned the columns. Bloomberg's zero rates / discount factors are best read from the curve screen (YCSW0490 &lt;GO&gt;, or SWDF). The actual bootstrap + comparison lives on the Bootstrap tab: paste S490 zero rates into its column J to get Δz in bp.</t>
+          <t>Paste Bloomberg's S490 zero rates (from YCSW0490 &lt;GO&gt; or SWDF) into the yellow column D, tenor for tenor; column E then shows Δz = your bootstrap − Bloomberg in bp (single digits = agreement). The raw BDS(CURVE_TENOR_RATES) dump is off to the right (cols H:I) as an optional live pull — its column order is Bloomberg-defined, so verify before relying on it.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
-          <t>Raw CURVE_TENOR_RATES dump — Bloomberg-defined column order; verify on terminal, then paste S490 zero rates into the Bootstrap tab (column J) for the Δz check</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="20" t="inlineStr"/>
-      <c r="E7" s="20" t="inlineStr"/>
-      <c r="F7" s="20" t="inlineStr"/>
-      <c r="G7" s="20" t="inlineStr"/>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Your zero (%)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>S490 zero (%) [paste]</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Δz (bp)</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Raw CURVE_TENOR_RATES (verify order)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6">
+        <f>Bootstrap!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="18">
+        <f>Bootstrap!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>Bootstrap!J8</f>
+        <v/>
+      </c>
+      <c r="D8" s="30" t="n"/>
+      <c r="E8" s="31">
+        <f>IF(D8="","",(C8-D8)*100)</f>
+        <v/>
+      </c>
+      <c r="H8">
         <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
         <v/>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="A9" s="6">
+        <f>Bootstrap!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="18">
+        <f>Bootstrap!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>Bootstrap!J9</f>
+        <v/>
+      </c>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="31">
+        <f>IF(D9="","",(C9-D9)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="n"/>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="A10" s="6">
+        <f>Bootstrap!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="18">
+        <f>Bootstrap!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>Bootstrap!J10</f>
+        <v/>
+      </c>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="31">
+        <f>IF(D10="","",(C10-D10)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="A11" s="6">
+        <f>Bootstrap!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="18">
+        <f>Bootstrap!B11</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>Bootstrap!J11</f>
+        <v/>
+      </c>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="31">
+        <f>IF(D11="","",(C11-D11)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="A12" s="6">
+        <f>Bootstrap!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="18">
+        <f>Bootstrap!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>Bootstrap!J12</f>
+        <v/>
+      </c>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="31">
+        <f>IF(D12="","",(C12-D12)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="A13" s="6">
+        <f>Bootstrap!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="18">
+        <f>Bootstrap!B13</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
+        <f>Bootstrap!J13</f>
+        <v/>
+      </c>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="31">
+        <f>IF(D13="","",(C13-D13)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="A14" s="6">
+        <f>Bootstrap!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="18">
+        <f>Bootstrap!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>Bootstrap!J14</f>
+        <v/>
+      </c>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="31">
+        <f>IF(D14="","",(C14-D14)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n"/>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="6" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="A15" s="6">
+        <f>Bootstrap!A15</f>
+        <v/>
+      </c>
+      <c r="B15" s="18">
+        <f>Bootstrap!B15</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>Bootstrap!J15</f>
+        <v/>
+      </c>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="31">
+        <f>IF(D15="","",(C15-D15)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="6" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="A16" s="6">
+        <f>Bootstrap!A16</f>
+        <v/>
+      </c>
+      <c r="B16" s="18">
+        <f>Bootstrap!B16</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
+        <f>Bootstrap!J16</f>
+        <v/>
+      </c>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="31">
+        <f>IF(D16="","",(C16-D16)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="n"/>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="6" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="A17" s="6">
+        <f>Bootstrap!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="18">
+        <f>Bootstrap!B17</f>
+        <v/>
+      </c>
+      <c r="C17" s="17">
+        <f>Bootstrap!J17</f>
+        <v/>
+      </c>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="31">
+        <f>IF(D17="","",(C17-D17)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="n"/>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="6" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="A18" s="6">
+        <f>Bootstrap!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="18">
+        <f>Bootstrap!B18</f>
+        <v/>
+      </c>
+      <c r="C18" s="17">
+        <f>Bootstrap!J18</f>
+        <v/>
+      </c>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="31">
+        <f>IF(D18="","",(C18-D18)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="n"/>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="6" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="A19" s="6">
+        <f>Bootstrap!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="18">
+        <f>Bootstrap!B19</f>
+        <v/>
+      </c>
+      <c r="C19" s="17">
+        <f>Bootstrap!J19</f>
+        <v/>
+      </c>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="31">
+        <f>IF(D19="","",(C19-D19)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="A20" s="6">
+        <f>Bootstrap!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="18">
+        <f>Bootstrap!B20</f>
+        <v/>
+      </c>
+      <c r="C20" s="17">
+        <f>Bootstrap!J20</f>
+        <v/>
+      </c>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="31">
+        <f>IF(D20="","",(C20-D20)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="A21" s="6">
+        <f>Bootstrap!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="18">
+        <f>Bootstrap!B21</f>
+        <v/>
+      </c>
+      <c r="C21" s="17">
+        <f>Bootstrap!J21</f>
+        <v/>
+      </c>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="31">
+        <f>IF(D21="","",(C21-D21)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="A22" s="6">
+        <f>Bootstrap!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="18">
+        <f>Bootstrap!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="17">
+        <f>Bootstrap!J22</f>
+        <v/>
+      </c>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="31">
+        <f>IF(D22="","",(C22-D22)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="6" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="A23" s="6">
+        <f>Bootstrap!A23</f>
+        <v/>
+      </c>
+      <c r="B23" s="18">
+        <f>Bootstrap!B23</f>
+        <v/>
+      </c>
+      <c r="C23" s="17">
+        <f>Bootstrap!J23</f>
+        <v/>
+      </c>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="31">
+        <f>IF(D23="","",(C23-D23)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="6" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="A24" s="6">
+        <f>Bootstrap!A24</f>
+        <v/>
+      </c>
+      <c r="B24" s="18">
+        <f>Bootstrap!B24</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>Bootstrap!J24</f>
+        <v/>
+      </c>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="31">
+        <f>IF(D24="","",(C24-D24)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="6" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="A25" s="6">
+        <f>Bootstrap!A25</f>
+        <v/>
+      </c>
+      <c r="B25" s="18">
+        <f>Bootstrap!B25</f>
+        <v/>
+      </c>
+      <c r="C25" s="17">
+        <f>Bootstrap!J25</f>
+        <v/>
+      </c>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="31">
+        <f>IF(D25="","",(C25-D25)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="n"/>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="A26" s="6">
+        <f>Bootstrap!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="18">
+        <f>Bootstrap!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="17">
+        <f>Bootstrap!J26</f>
+        <v/>
+      </c>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="31">
+        <f>IF(D26="","",(C26-D26)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="n"/>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
+      <c r="A27" s="6">
+        <f>Bootstrap!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="18">
+        <f>Bootstrap!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="17">
+        <f>Bootstrap!J27</f>
+        <v/>
+      </c>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="31">
+        <f>IF(D27="","",(C27-D27)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="n"/>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="6" t="n"/>
-      <c r="G28" s="6" t="n"/>
+      <c r="A28" s="6">
+        <f>Bootstrap!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="18">
+        <f>Bootstrap!B28</f>
+        <v/>
+      </c>
+      <c r="C28" s="17">
+        <f>Bootstrap!J28</f>
+        <v/>
+      </c>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="31">
+        <f>IF(D28="","",(C28-D28)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="6" t="n"/>
-      <c r="G29" s="6" t="n"/>
+      <c r="A29" s="6">
+        <f>Bootstrap!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="18">
+        <f>Bootstrap!B29</f>
+        <v/>
+      </c>
+      <c r="C29" s="17">
+        <f>Bootstrap!J29</f>
+        <v/>
+      </c>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="31">
+        <f>IF(D29="","",(C29-D29)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n"/>
-      <c r="B30" s="6" t="n"/>
-      <c r="C30" s="6" t="n"/>
-      <c r="D30" s="6" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="6" t="n"/>
-      <c r="G30" s="6" t="n"/>
+      <c r="A30" s="6">
+        <f>Bootstrap!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="18">
+        <f>Bootstrap!B30</f>
+        <v/>
+      </c>
+      <c r="C30" s="17">
+        <f>Bootstrap!J30</f>
+        <v/>
+      </c>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="31">
+        <f>IF(D30="","",(C30-D30)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="6" t="n"/>
-      <c r="G31" s="6" t="n"/>
+      <c r="A31" s="6">
+        <f>Bootstrap!A31</f>
+        <v/>
+      </c>
+      <c r="B31" s="18">
+        <f>Bootstrap!B31</f>
+        <v/>
+      </c>
+      <c r="C31" s="17">
+        <f>Bootstrap!J31</f>
+        <v/>
+      </c>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="31">
+        <f>IF(D31="","",(C31-D31)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="n"/>
-      <c r="B32" s="6" t="n"/>
-      <c r="C32" s="6" t="n"/>
-      <c r="D32" s="6" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
-      <c r="G32" s="6" t="n"/>
+      <c r="A32" s="6">
+        <f>Bootstrap!A32</f>
+        <v/>
+      </c>
+      <c r="B32" s="18">
+        <f>Bootstrap!B32</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>Bootstrap!J32</f>
+        <v/>
+      </c>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="31">
+        <f>IF(D32="","",(C32-D32)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
+      <c r="A33" s="6">
+        <f>Bootstrap!A33</f>
+        <v/>
+      </c>
+      <c r="B33" s="18">
+        <f>Bootstrap!B33</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>Bootstrap!J33</f>
+        <v/>
+      </c>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="31">
+        <f>IF(D33="","",(C33-D33)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="n"/>
-      <c r="B34" s="6" t="n"/>
-      <c r="C34" s="6" t="n"/>
-      <c r="D34" s="6" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
-      <c r="G34" s="6" t="n"/>
+      <c r="A34" s="6">
+        <f>Bootstrap!A34</f>
+        <v/>
+      </c>
+      <c r="B34" s="18">
+        <f>Bootstrap!B34</f>
+        <v/>
+      </c>
+      <c r="C34" s="17">
+        <f>Bootstrap!J34</f>
+        <v/>
+      </c>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="31">
+        <f>IF(D34="","",(C34-D34)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="n"/>
-      <c r="B35" s="6" t="n"/>
-      <c r="C35" s="6" t="n"/>
-      <c r="D35" s="6" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
-      <c r="G35" s="6" t="n"/>
+      <c r="A35" s="6">
+        <f>Bootstrap!A35</f>
+        <v/>
+      </c>
+      <c r="B35" s="18">
+        <f>Bootstrap!B35</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>Bootstrap!J35</f>
+        <v/>
+      </c>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="31">
+        <f>IF(D35="","",(C35-D35)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="n"/>
-      <c r="B36" s="6" t="n"/>
-      <c r="C36" s="6" t="n"/>
-      <c r="D36" s="6" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
-      <c r="G36" s="6" t="n"/>
+      <c r="A36" s="6">
+        <f>Bootstrap!A36</f>
+        <v/>
+      </c>
+      <c r="B36" s="18">
+        <f>Bootstrap!B36</f>
+        <v/>
+      </c>
+      <c r="C36" s="17">
+        <f>Bootstrap!J36</f>
+        <v/>
+      </c>
+      <c r="D36" s="30" t="n"/>
+      <c r="E36" s="31">
+        <f>IF(D36="","",(C36-D36)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n"/>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
+      <c r="A37" s="6">
+        <f>Bootstrap!A37</f>
+        <v/>
+      </c>
+      <c r="B37" s="18">
+        <f>Bootstrap!B37</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>Bootstrap!J37</f>
+        <v/>
+      </c>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="31">
+        <f>IF(D37="","",(C37-D37)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="n"/>
-      <c r="B38" s="6" t="n"/>
-      <c r="C38" s="6" t="n"/>
-      <c r="D38" s="6" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
-      <c r="G38" s="6" t="n"/>
+      <c r="A38" s="6">
+        <f>Bootstrap!A38</f>
+        <v/>
+      </c>
+      <c r="B38" s="18">
+        <f>Bootstrap!B38</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>Bootstrap!J38</f>
+        <v/>
+      </c>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="31">
+        <f>IF(D38="","",(C38-D38)*100)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="n"/>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
-      <c r="G39" s="6" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="n"/>
-      <c r="B40" s="6" t="n"/>
-      <c r="C40" s="6" t="n"/>
-      <c r="D40" s="6" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
-      <c r="G40" s="6" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n"/>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="6" t="n"/>
-      <c r="G41" s="6" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n"/>
-      <c r="B42" s="6" t="n"/>
-      <c r="C42" s="6" t="n"/>
-      <c r="D42" s="6" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n"/>
-      <c r="B43" s="6" t="n"/>
-      <c r="C43" s="6" t="n"/>
-      <c r="D43" s="6" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="n"/>
-      <c r="B44" s="6" t="n"/>
-      <c r="C44" s="6" t="n"/>
-      <c r="D44" s="6" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
-      <c r="G44" s="6" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="6" t="n"/>
-      <c r="B45" s="6" t="n"/>
-      <c r="C45" s="6" t="n"/>
-      <c r="D45" s="6" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
-      <c r="G45" s="6" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="n"/>
-      <c r="B46" s="6" t="n"/>
-      <c r="C46" s="6" t="n"/>
-      <c r="D46" s="6" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="6" t="n"/>
-      <c r="G46" s="6" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="6" t="n"/>
-      <c r="B47" s="6" t="n"/>
-      <c r="C47" s="6" t="n"/>
-      <c r="D47" s="6" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
-      <c r="G47" s="6" t="n"/>
+      <c r="A39" s="6">
+        <f>Bootstrap!A39</f>
+        <v/>
+      </c>
+      <c r="B39" s="18">
+        <f>Bootstrap!B39</f>
+        <v/>
+      </c>
+      <c r="C39" s="17">
+        <f>Bootstrap!J39</f>
+        <v/>
+      </c>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="31">
+        <f>IF(D39="","",(C39-D39)*100)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A6:G6"/>
-    <mergeCell ref="B4:D4"/>
+  <mergeCells count="3">
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B4:E4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -11379,7 +11379,7 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·tau0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which discounts each contract's forward rate forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is shown only for reference). If the SR3 chain is unavailable the middle DFs FALL BACK to the OIS bootstrap so the curve never breaks — col N shows which is live per pillar. LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·taucoupon), annuity (col I) built from the short + middle DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
+          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·tau0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which chains the QUARTERLY contracts only (ref start Mar/Jun/Sep/Dec; monthly serials skipped) forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is reference only). The middle DF uses the futures value only if it agrees with the OIS bootstrap (|diff|&lt;0.03), else it FALLS BACK to OIS so bad/mixed futures data can never break the curve — col N shows which is live per pillar. LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·taucoupon), annuity (col I) built from the short + middle DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
         </is>
       </c>
       <c r="O5" s="13" t="inlineStr">
@@ -11595,11 +11595,11 @@
         <v/>
       </c>
       <c r="Q8" s="18">
-        <f>'SOFR_Futures'!H8</f>
+        <f>EDATE(P8,3)</f>
         <v/>
       </c>
       <c r="R8" s="17">
-        <f>MAX(0,(Q8-MAX(P8,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P8)=3,MONTH(P8)=6,MONTH(P8)=9,MONTH(P8)=12),MAX(0,(Q8-MAX(P8,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S8" s="17">
@@ -11692,11 +11692,11 @@
         <v/>
       </c>
       <c r="Q9" s="18">
-        <f>'SOFR_Futures'!H9</f>
+        <f>EDATE(P9,3)</f>
         <v/>
       </c>
       <c r="R9" s="17">
-        <f>MAX(0,(Q9-MAX(P9,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P9)=3,MONTH(P9)=6,MONTH(P9)=9,MONTH(P9)=12),MAX(0,(Q9-MAX(P9,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S9" s="17">
@@ -11789,11 +11789,11 @@
         <v/>
       </c>
       <c r="Q10" s="18">
-        <f>'SOFR_Futures'!H10</f>
+        <f>EDATE(P10,3)</f>
         <v/>
       </c>
       <c r="R10" s="17">
-        <f>MAX(0,(Q10-MAX(P10,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P10)=3,MONTH(P10)=6,MONTH(P10)=9,MONTH(P10)=12),MAX(0,(Q10-MAX(P10,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S10" s="17">
@@ -11886,11 +11886,11 @@
         <v/>
       </c>
       <c r="Q11" s="18">
-        <f>'SOFR_Futures'!H11</f>
+        <f>EDATE(P11,3)</f>
         <v/>
       </c>
       <c r="R11" s="17">
-        <f>MAX(0,(Q11-MAX(P11,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P11)=3,MONTH(P11)=6,MONTH(P11)=9,MONTH(P11)=12),MAX(0,(Q11-MAX(P11,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S11" s="17">
@@ -11983,11 +11983,11 @@
         <v/>
       </c>
       <c r="Q12" s="18">
-        <f>'SOFR_Futures'!H12</f>
+        <f>EDATE(P12,3)</f>
         <v/>
       </c>
       <c r="R12" s="17">
-        <f>MAX(0,(Q12-MAX(P12,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P12)=3,MONTH(P12)=6,MONTH(P12)=9,MONTH(P12)=12),MAX(0,(Q12-MAX(P12,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S12" s="17">
@@ -12080,11 +12080,11 @@
         <v/>
       </c>
       <c r="Q13" s="18">
-        <f>'SOFR_Futures'!H13</f>
+        <f>EDATE(P13,3)</f>
         <v/>
       </c>
       <c r="R13" s="17">
-        <f>MAX(0,(Q13-MAX(P13,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P13)=3,MONTH(P13)=6,MONTH(P13)=9,MONTH(P13)=12),MAX(0,(Q13-MAX(P13,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S13" s="17">
@@ -12177,11 +12177,11 @@
         <v/>
       </c>
       <c r="Q14" s="18">
-        <f>'SOFR_Futures'!H14</f>
+        <f>EDATE(P14,3)</f>
         <v/>
       </c>
       <c r="R14" s="17">
-        <f>MAX(0,(Q14-MAX(P14,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P14)=3,MONTH(P14)=6,MONTH(P14)=9,MONTH(P14)=12),MAX(0,(Q14-MAX(P14,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S14" s="17">
@@ -12274,11 +12274,11 @@
         <v/>
       </c>
       <c r="Q15" s="18">
-        <f>'SOFR_Futures'!H15</f>
+        <f>EDATE(P15,3)</f>
         <v/>
       </c>
       <c r="R15" s="17">
-        <f>MAX(0,(Q15-MAX(P15,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P15)=3,MONTH(P15)=6,MONTH(P15)=9,MONTH(P15)=12),MAX(0,(Q15-MAX(P15,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S15" s="17">
@@ -12371,11 +12371,11 @@
         <v/>
       </c>
       <c r="Q16" s="18">
-        <f>'SOFR_Futures'!H16</f>
+        <f>EDATE(P16,3)</f>
         <v/>
       </c>
       <c r="R16" s="17">
-        <f>MAX(0,(Q16-MAX(P16,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P16)=3,MONTH(P16)=6,MONTH(P16)=9,MONTH(P16)=12),MAX(0,(Q16-MAX(P16,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S16" s="17">
@@ -12468,11 +12468,11 @@
         <v/>
       </c>
       <c r="Q17" s="18">
-        <f>'SOFR_Futures'!H17</f>
+        <f>EDATE(P17,3)</f>
         <v/>
       </c>
       <c r="R17" s="17">
-        <f>MAX(0,(Q17-MAX(P17,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P17)=3,MONTH(P17)=6,MONTH(P17)=9,MONTH(P17)=12),MAX(0,(Q17-MAX(P17,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S17" s="17">
@@ -12565,11 +12565,11 @@
         <v/>
       </c>
       <c r="Q18" s="18">
-        <f>'SOFR_Futures'!H18</f>
+        <f>EDATE(P18,3)</f>
         <v/>
       </c>
       <c r="R18" s="17">
-        <f>MAX(0,(Q18-MAX(P18,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P18)=3,MONTH(P18)=6,MONTH(P18)=9,MONTH(P18)=12),MAX(0,(Q18-MAX(P18,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S18" s="17">
@@ -12662,11 +12662,11 @@
         <v/>
       </c>
       <c r="Q19" s="18">
-        <f>'SOFR_Futures'!H19</f>
+        <f>EDATE(P19,3)</f>
         <v/>
       </c>
       <c r="R19" s="17">
-        <f>MAX(0,(Q19-MAX(P19,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P19)=3,MONTH(P19)=6,MONTH(P19)=9,MONTH(P19)=12),MAX(0,(Q19-MAX(P19,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S19" s="17">
@@ -12759,11 +12759,11 @@
         <v/>
       </c>
       <c r="Q20" s="18">
-        <f>'SOFR_Futures'!H20</f>
+        <f>EDATE(P20,3)</f>
         <v/>
       </c>
       <c r="R20" s="17">
-        <f>MAX(0,(Q20-MAX(P20,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P20)=3,MONTH(P20)=6,MONTH(P20)=9,MONTH(P20)=12),MAX(0,(Q20-MAX(P20,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S20" s="17">
@@ -12856,11 +12856,11 @@
         <v/>
       </c>
       <c r="Q21" s="18">
-        <f>'SOFR_Futures'!H21</f>
+        <f>EDATE(P21,3)</f>
         <v/>
       </c>
       <c r="R21" s="17">
-        <f>MAX(0,(Q21-MAX(P21,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P21)=3,MONTH(P21)=6,MONTH(P21)=9,MONTH(P21)=12),MAX(0,(Q21-MAX(P21,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S21" s="17">
@@ -12957,11 +12957,11 @@
         <v/>
       </c>
       <c r="Q22" s="18">
-        <f>'SOFR_Futures'!H22</f>
+        <f>EDATE(P22,3)</f>
         <v/>
       </c>
       <c r="R22" s="17">
-        <f>MAX(0,(Q22-MAX(P22,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P22)=3,MONTH(P22)=6,MONTH(P22)=9,MONTH(P22)=12),MAX(0,(Q22-MAX(P22,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S22" s="17">
@@ -13056,11 +13056,11 @@
         <v/>
       </c>
       <c r="Q23" s="18">
-        <f>'SOFR_Futures'!H23</f>
+        <f>EDATE(P23,3)</f>
         <v/>
       </c>
       <c r="R23" s="17">
-        <f>MAX(0,(Q23-MAX(P23,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P23)=3,MONTH(P23)=6,MONTH(P23)=9,MONTH(P23)=12),MAX(0,(Q23-MAX(P23,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S23" s="17">
@@ -13156,11 +13156,11 @@
         <v/>
       </c>
       <c r="Q24" s="18">
-        <f>'SOFR_Futures'!H24</f>
+        <f>EDATE(P24,3)</f>
         <v/>
       </c>
       <c r="R24" s="17">
-        <f>MAX(0,(Q24-MAX(P24,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P24)=3,MONTH(P24)=6,MONTH(P24)=9,MONTH(P24)=12),MAX(0,(Q24-MAX(P24,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S24" s="17">
@@ -13256,11 +13256,11 @@
         <v/>
       </c>
       <c r="Q25" s="18">
-        <f>'SOFR_Futures'!H25</f>
+        <f>EDATE(P25,3)</f>
         <v/>
       </c>
       <c r="R25" s="17">
-        <f>MAX(0,(Q25-MAX(P25,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P25)=3,MONTH(P25)=6,MONTH(P25)=9,MONTH(P25)=12),MAX(0,(Q25-MAX(P25,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S25" s="17">
@@ -13356,11 +13356,11 @@
         <v/>
       </c>
       <c r="Q26" s="18">
-        <f>'SOFR_Futures'!H26</f>
+        <f>EDATE(P26,3)</f>
         <v/>
       </c>
       <c r="R26" s="17">
-        <f>MAX(0,(Q26-MAX(P26,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P26)=3,MONTH(P26)=6,MONTH(P26)=9,MONTH(P26)=12),MAX(0,(Q26-MAX(P26,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S26" s="17">
@@ -13460,7 +13460,7 @@
         <v/>
       </c>
       <c r="R27" s="17">
-        <f>MAX(0,(Q27-MAX(P27,$B$22))/360)</f>
+        <f>IF(OR(MONTH(P27)=3,MONTH(P27)=6,MONTH(P27)=9,MONTH(P27)=12),MAX(0,(Q27-MAX(P27,$B$22))/360),0)</f>
         <v/>
       </c>
       <c r="S27" s="17">

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -13,17 +13,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Futures" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_OIS_Quotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap_Futures" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -196,8 +197,6 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -206,8 +205,10 @@
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1037,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1488,168 +1489,180 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Live single-curve OIS bootstrap → discount factors, zero &amp; forward rates, S490 Δz check.</t>
+          <t>Robust 3-segment bootstrap (futures-if-agree-else-OIS). The curve everything downstream uses.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Curve_Interface</t>
+          <t>Bootstrap_Futures</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Shared D(0,t): interpolates the SOFR curve to ANY date (quarterly CDS dates demo). Used by Swap_Pricer + CDS.</t>
+          <t>Second copy — FORCES the SR3 futures in the middle (no guard). Compare col H vs Bootstrap.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="13" t="inlineStr">
         <is>
-          <t>CDS_Parameters</t>
+          <t>Curve_Interface</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Credit assumptions: recovery, notional, coupon, direction (recovery is an INPUT).</t>
+          <t>Shared D(0,t): interpolates the SOFR curve to ANY date (quarterly CDS dates demo). Used by Swap_Pricer + CDS.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="13" t="inlineStr">
         <is>
-          <t>CDS_Quotes</t>
+          <t>CDS_Parameters</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Single-name CDS par spreads (BDP ticker, or manual demo). One entity, one seniority.</t>
+          <t>Credit assumptions: recovery, notional, coupon, direction (recovery is an INPUT).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="13" t="inlineStr">
         <is>
-          <t>CDS_Schedule</t>
+          <t>CDS_Quotes</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Quarterly premium/default schedule to 10Y; DF from the SOFR curve, survival from hazards.</t>
+          <t>Single-name CDS par spreads (BDP ticker, or manual demo). One entity, one seniority.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="13" t="inlineStr">
         <is>
-          <t>Hazard_Bootstrap</t>
+          <t>CDS_Schedule</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Piecewise-constant hazard curve; s/(1-R) default, Goal-Seek the error to 0 for exact fit.</t>
+          <t>Quarterly premium/default schedule to 10Y; DF from the SOFR curve, survival from hazards.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="13" t="inlineStr">
         <is>
-          <t>CDS_Pricer</t>
+          <t>Hazard_Bootstrap</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Prices a CDS off both curves: protection − premium, par spread, upfront, CS01.</t>
+          <t>Piecewise-constant hazard curve; s/(1-R) default, Goal-Seek the error to 0 for exact fit.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="13" t="inlineStr">
         <is>
-          <t>CDS_Validation</t>
+          <t>CDS_Pricer</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Survival/hazard sanity checks + the s ≈ (1-R)·lambda approximation.</t>
+          <t>Prices a CDS off both curves: protection − premium, par spread, upfront, CS01.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="13" t="inlineStr">
         <is>
-          <t>5. Bloomberg_S490_Validation</t>
+          <t>CDS_Validation</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
+          <t>Survival/hazard sanity checks + the s ≈ (1-R)·lambda approximation.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="13" t="inlineStr">
         <is>
-          <t>6. Conventions</t>
+          <t>5. Bloomberg_S490_Validation</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
+          <t>Bloomberg's own USD SOFR curve (S490) for benchmarking your bootstrap.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="13" t="inlineStr">
         <is>
+          <t>6. Conventions</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>DES/SWPM conventions for representative OIS (spot lag, day counts, compounding, EOM…).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
           <t>7. Fwd_Interp</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Zhou 2002 forward interpolation: V1 piecewise-flat vs V2 piecewise-quadratic forwards.</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>DO NOT substitute these (wrong instruments):</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+          <t>•  TSFR1M/3M/6M/12M Index  — Term SOFR benchmarks, NOT overnight-SOFR OIS calibration instruments.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="9" t="inlineStr">
         <is>
+          <t>•  USISSO02/05/10/30 Index — ICE Swap Rate fixings, NOT the live OIS quote strip needed to bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
           <t>•  Use PX midpoint (bid+ask)/2 for construction; use PX_LAST only where bid/ask are unavailable.</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>Licensing: Bloomberg data is licensed and entitlement-dependent — do NOT redistribute pulled values or commit them to a public repository. This template ships formulas only, no data. Some static convention fields may return N/A under your entitlement; use FLDS &lt;GO&gt; on the security to find the enabled mnemonic.</t>
         </is>
       </c>
     </row>
-    <row r="58"/>
+    <row r="59"/>
   </sheetData>
-  <mergeCells count="58">
+  <mergeCells count="59">
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="A54:F54"/>
     <mergeCell ref="D11:F11"/>
@@ -1657,6 +1670,7 @@
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A56:F56"/>
     <mergeCell ref="E17:F17"/>
     <mergeCell ref="A55:F55"/>
     <mergeCell ref="B27:F27"/>
@@ -1665,6 +1679,7 @@
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B39:F39"/>
+    <mergeCell ref="A58:F59"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B42:F42"/>
     <mergeCell ref="E19:F19"/>
@@ -1680,7 +1695,6 @@
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="D14:F14"/>
-    <mergeCell ref="A52:F52"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="B38:F38"/>
     <mergeCell ref="B28:F28"/>
@@ -1697,9 +1711,9 @@
     <mergeCell ref="A20:B20"/>
     <mergeCell ref="A19:B19"/>
     <mergeCell ref="C19:D19"/>
+    <mergeCell ref="B51:F51"/>
     <mergeCell ref="B45:F45"/>
     <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A57:F58"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="A4:F5"/>
@@ -1714,6 +1728,719 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Bloomberg_S490_Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bloomberg's own USD SOFR curve (S490 / YCSW0490 Index) — benchmark for your bootstrap, not an input</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Curve name:</t>
+        </is>
+      </c>
+      <c r="B4" s="19">
+        <f>IFERROR(BDP(S490_TKR,"NAME"),"ERROR PLZ FIX")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t>Curve date:</t>
+        </is>
+      </c>
+      <c r="B5" s="44">
+        <f>VAL_DATE</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Paste Bloomberg's S490 zero rates (from YCSW0490 &lt;GO&gt; or SWDF) into the yellow column D, tenor for tenor; column E then shows Δz = your bootstrap − Bloomberg in bp (single digits = agreement). The raw BDS(CURVE_TENOR_RATES) dump is off to the right (cols H:I) as an optional live pull — its column order is Bloomberg-defined, so verify before relying on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Your zero (%)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>S490 zero (%) [paste]</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Δz (bp)</t>
+        </is>
+      </c>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>Raw CURVE_TENOR_RATES (verify order)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6">
+        <f>Bootstrap!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="18">
+        <f>Bootstrap!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>Bootstrap!J8</f>
+        <v/>
+      </c>
+      <c r="D8" s="30" t="n"/>
+      <c r="E8" s="31">
+        <f>IF(D8="","",(C8-D8)*100)</f>
+        <v/>
+      </c>
+      <c r="H8">
+        <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <f>Bootstrap!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="18">
+        <f>Bootstrap!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="17">
+        <f>Bootstrap!J9</f>
+        <v/>
+      </c>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="31">
+        <f>IF(D9="","",(C9-D9)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6">
+        <f>Bootstrap!A10</f>
+        <v/>
+      </c>
+      <c r="B10" s="18">
+        <f>Bootstrap!B10</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>Bootstrap!J10</f>
+        <v/>
+      </c>
+      <c r="D10" s="30" t="n"/>
+      <c r="E10" s="31">
+        <f>IF(D10="","",(C10-D10)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <f>Bootstrap!A11</f>
+        <v/>
+      </c>
+      <c r="B11" s="18">
+        <f>Bootstrap!B11</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>Bootstrap!J11</f>
+        <v/>
+      </c>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="31">
+        <f>IF(D11="","",(C11-D11)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6">
+        <f>Bootstrap!A12</f>
+        <v/>
+      </c>
+      <c r="B12" s="18">
+        <f>Bootstrap!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>Bootstrap!J12</f>
+        <v/>
+      </c>
+      <c r="D12" s="30" t="n"/>
+      <c r="E12" s="31">
+        <f>IF(D12="","",(C12-D12)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6">
+        <f>Bootstrap!A13</f>
+        <v/>
+      </c>
+      <c r="B13" s="18">
+        <f>Bootstrap!B13</f>
+        <v/>
+      </c>
+      <c r="C13" s="17">
+        <f>Bootstrap!J13</f>
+        <v/>
+      </c>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="31">
+        <f>IF(D13="","",(C13-D13)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6">
+        <f>Bootstrap!A14</f>
+        <v/>
+      </c>
+      <c r="B14" s="18">
+        <f>Bootstrap!B14</f>
+        <v/>
+      </c>
+      <c r="C14" s="17">
+        <f>Bootstrap!J14</f>
+        <v/>
+      </c>
+      <c r="D14" s="30" t="n"/>
+      <c r="E14" s="31">
+        <f>IF(D14="","",(C14-D14)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6">
+        <f>Bootstrap!A15</f>
+        <v/>
+      </c>
+      <c r="B15" s="18">
+        <f>Bootstrap!B15</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>Bootstrap!J15</f>
+        <v/>
+      </c>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="31">
+        <f>IF(D15="","",(C15-D15)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6">
+        <f>Bootstrap!A16</f>
+        <v/>
+      </c>
+      <c r="B16" s="18">
+        <f>Bootstrap!B16</f>
+        <v/>
+      </c>
+      <c r="C16" s="17">
+        <f>Bootstrap!J16</f>
+        <v/>
+      </c>
+      <c r="D16" s="30" t="n"/>
+      <c r="E16" s="31">
+        <f>IF(D16="","",(C16-D16)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6">
+        <f>Bootstrap!A17</f>
+        <v/>
+      </c>
+      <c r="B17" s="18">
+        <f>Bootstrap!B17</f>
+        <v/>
+      </c>
+      <c r="C17" s="17">
+        <f>Bootstrap!J17</f>
+        <v/>
+      </c>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="31">
+        <f>IF(D17="","",(C17-D17)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6">
+        <f>Bootstrap!A18</f>
+        <v/>
+      </c>
+      <c r="B18" s="18">
+        <f>Bootstrap!B18</f>
+        <v/>
+      </c>
+      <c r="C18" s="17">
+        <f>Bootstrap!J18</f>
+        <v/>
+      </c>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="31">
+        <f>IF(D18="","",(C18-D18)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6">
+        <f>Bootstrap!A19</f>
+        <v/>
+      </c>
+      <c r="B19" s="18">
+        <f>Bootstrap!B19</f>
+        <v/>
+      </c>
+      <c r="C19" s="17">
+        <f>Bootstrap!J19</f>
+        <v/>
+      </c>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="31">
+        <f>IF(D19="","",(C19-D19)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6">
+        <f>Bootstrap!A20</f>
+        <v/>
+      </c>
+      <c r="B20" s="18">
+        <f>Bootstrap!B20</f>
+        <v/>
+      </c>
+      <c r="C20" s="17">
+        <f>Bootstrap!J20</f>
+        <v/>
+      </c>
+      <c r="D20" s="30" t="n"/>
+      <c r="E20" s="31">
+        <f>IF(D20="","",(C20-D20)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6">
+        <f>Bootstrap!A21</f>
+        <v/>
+      </c>
+      <c r="B21" s="18">
+        <f>Bootstrap!B21</f>
+        <v/>
+      </c>
+      <c r="C21" s="17">
+        <f>Bootstrap!J21</f>
+        <v/>
+      </c>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="31">
+        <f>IF(D21="","",(C21-D21)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6">
+        <f>Bootstrap!A22</f>
+        <v/>
+      </c>
+      <c r="B22" s="18">
+        <f>Bootstrap!B22</f>
+        <v/>
+      </c>
+      <c r="C22" s="17">
+        <f>Bootstrap!J22</f>
+        <v/>
+      </c>
+      <c r="D22" s="30" t="n"/>
+      <c r="E22" s="31">
+        <f>IF(D22="","",(C22-D22)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6">
+        <f>Bootstrap!A23</f>
+        <v/>
+      </c>
+      <c r="B23" s="18">
+        <f>Bootstrap!B23</f>
+        <v/>
+      </c>
+      <c r="C23" s="17">
+        <f>Bootstrap!J23</f>
+        <v/>
+      </c>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="31">
+        <f>IF(D23="","",(C23-D23)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6">
+        <f>Bootstrap!A24</f>
+        <v/>
+      </c>
+      <c r="B24" s="18">
+        <f>Bootstrap!B24</f>
+        <v/>
+      </c>
+      <c r="C24" s="17">
+        <f>Bootstrap!J24</f>
+        <v/>
+      </c>
+      <c r="D24" s="30" t="n"/>
+      <c r="E24" s="31">
+        <f>IF(D24="","",(C24-D24)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6">
+        <f>Bootstrap!A25</f>
+        <v/>
+      </c>
+      <c r="B25" s="18">
+        <f>Bootstrap!B25</f>
+        <v/>
+      </c>
+      <c r="C25" s="17">
+        <f>Bootstrap!J25</f>
+        <v/>
+      </c>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="31">
+        <f>IF(D25="","",(C25-D25)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6">
+        <f>Bootstrap!A26</f>
+        <v/>
+      </c>
+      <c r="B26" s="18">
+        <f>Bootstrap!B26</f>
+        <v/>
+      </c>
+      <c r="C26" s="17">
+        <f>Bootstrap!J26</f>
+        <v/>
+      </c>
+      <c r="D26" s="30" t="n"/>
+      <c r="E26" s="31">
+        <f>IF(D26="","",(C26-D26)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6">
+        <f>Bootstrap!A27</f>
+        <v/>
+      </c>
+      <c r="B27" s="18">
+        <f>Bootstrap!B27</f>
+        <v/>
+      </c>
+      <c r="C27" s="17">
+        <f>Bootstrap!J27</f>
+        <v/>
+      </c>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="31">
+        <f>IF(D27="","",(C27-D27)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6">
+        <f>Bootstrap!A28</f>
+        <v/>
+      </c>
+      <c r="B28" s="18">
+        <f>Bootstrap!B28</f>
+        <v/>
+      </c>
+      <c r="C28" s="17">
+        <f>Bootstrap!J28</f>
+        <v/>
+      </c>
+      <c r="D28" s="30" t="n"/>
+      <c r="E28" s="31">
+        <f>IF(D28="","",(C28-D28)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6">
+        <f>Bootstrap!A29</f>
+        <v/>
+      </c>
+      <c r="B29" s="18">
+        <f>Bootstrap!B29</f>
+        <v/>
+      </c>
+      <c r="C29" s="17">
+        <f>Bootstrap!J29</f>
+        <v/>
+      </c>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="31">
+        <f>IF(D29="","",(C29-D29)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6">
+        <f>Bootstrap!A30</f>
+        <v/>
+      </c>
+      <c r="B30" s="18">
+        <f>Bootstrap!B30</f>
+        <v/>
+      </c>
+      <c r="C30" s="17">
+        <f>Bootstrap!J30</f>
+        <v/>
+      </c>
+      <c r="D30" s="30" t="n"/>
+      <c r="E30" s="31">
+        <f>IF(D30="","",(C30-D30)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6">
+        <f>Bootstrap!A31</f>
+        <v/>
+      </c>
+      <c r="B31" s="18">
+        <f>Bootstrap!B31</f>
+        <v/>
+      </c>
+      <c r="C31" s="17">
+        <f>Bootstrap!J31</f>
+        <v/>
+      </c>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="31">
+        <f>IF(D31="","",(C31-D31)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6">
+        <f>Bootstrap!A32</f>
+        <v/>
+      </c>
+      <c r="B32" s="18">
+        <f>Bootstrap!B32</f>
+        <v/>
+      </c>
+      <c r="C32" s="17">
+        <f>Bootstrap!J32</f>
+        <v/>
+      </c>
+      <c r="D32" s="30" t="n"/>
+      <c r="E32" s="31">
+        <f>IF(D32="","",(C32-D32)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6">
+        <f>Bootstrap!A33</f>
+        <v/>
+      </c>
+      <c r="B33" s="18">
+        <f>Bootstrap!B33</f>
+        <v/>
+      </c>
+      <c r="C33" s="17">
+        <f>Bootstrap!J33</f>
+        <v/>
+      </c>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="31">
+        <f>IF(D33="","",(C33-D33)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6">
+        <f>Bootstrap!A34</f>
+        <v/>
+      </c>
+      <c r="B34" s="18">
+        <f>Bootstrap!B34</f>
+        <v/>
+      </c>
+      <c r="C34" s="17">
+        <f>Bootstrap!J34</f>
+        <v/>
+      </c>
+      <c r="D34" s="30" t="n"/>
+      <c r="E34" s="31">
+        <f>IF(D34="","",(C34-D34)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6">
+        <f>Bootstrap!A35</f>
+        <v/>
+      </c>
+      <c r="B35" s="18">
+        <f>Bootstrap!B35</f>
+        <v/>
+      </c>
+      <c r="C35" s="17">
+        <f>Bootstrap!J35</f>
+        <v/>
+      </c>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="31">
+        <f>IF(D35="","",(C35-D35)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6">
+        <f>Bootstrap!A36</f>
+        <v/>
+      </c>
+      <c r="B36" s="18">
+        <f>Bootstrap!B36</f>
+        <v/>
+      </c>
+      <c r="C36" s="17">
+        <f>Bootstrap!J36</f>
+        <v/>
+      </c>
+      <c r="D36" s="30" t="n"/>
+      <c r="E36" s="31">
+        <f>IF(D36="","",(C36-D36)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6">
+        <f>Bootstrap!A37</f>
+        <v/>
+      </c>
+      <c r="B37" s="18">
+        <f>Bootstrap!B37</f>
+        <v/>
+      </c>
+      <c r="C37" s="17">
+        <f>Bootstrap!J37</f>
+        <v/>
+      </c>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="31">
+        <f>IF(D37="","",(C37-D37)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6">
+        <f>Bootstrap!A38</f>
+        <v/>
+      </c>
+      <c r="B38" s="18">
+        <f>Bootstrap!B38</f>
+        <v/>
+      </c>
+      <c r="C38" s="17">
+        <f>Bootstrap!J38</f>
+        <v/>
+      </c>
+      <c r="D38" s="30" t="n"/>
+      <c r="E38" s="31">
+        <f>IF(D38="","",(C38-D38)*100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6">
+        <f>Bootstrap!A39</f>
+        <v/>
+      </c>
+      <c r="B39" s="18">
+        <f>Bootstrap!B39</f>
+        <v/>
+      </c>
+      <c r="C39" s="17">
+        <f>Bootstrap!J39</f>
+        <v/>
+      </c>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="31">
+        <f>IF(D39="","",(C39-D39)*100)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="H7:L7"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="B4:E4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2489,7 +3216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4222,7 +4949,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4299,7 +5026,7 @@
           <t>Reference entity</t>
         </is>
       </c>
-      <c r="B7" s="36" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
         <is>
           <t>EXAMPLE CORP</t>
         </is>
@@ -4331,7 +5058,7 @@
           <t>Notional</t>
         </is>
       </c>
-      <c r="B9" s="38" t="n">
+      <c r="B9" s="36" t="n">
         <v>10000000</v>
       </c>
     </row>
@@ -4341,7 +5068,7 @@
           <t>Standard coupon (bp)</t>
         </is>
       </c>
-      <c r="B10" s="40" t="n">
+      <c r="B10" s="38" t="n">
         <v>100</v>
       </c>
       <c r="C10" s="16" t="inlineStr">
@@ -4404,7 +5131,7 @@
           <t>Protection direction</t>
         </is>
       </c>
-      <c r="B15" s="36" t="inlineStr">
+      <c r="B15" s="34" t="inlineStr">
         <is>
           <t>Buy protection</t>
         </is>
@@ -4440,7 +5167,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4523,14 +5250,14 @@
           <t>1Y</t>
         </is>
       </c>
-      <c r="B7" s="35" t="n">
+      <c r="B7" s="40" t="n">
         <v>1</v>
       </c>
       <c r="C7" s="18">
         <f>EDATE('Curve_Interface'!$F$7,3*(4-1))</f>
         <v/>
       </c>
-      <c r="D7" s="36" t="inlineStr"/>
+      <c r="D7" s="34" t="inlineStr"/>
       <c r="E7" s="52" t="n">
         <v>40</v>
       </c>
@@ -4549,14 +5276,14 @@
           <t>2Y</t>
         </is>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="40" t="n">
         <v>2</v>
       </c>
       <c r="C8" s="18">
         <f>EDATE('Curve_Interface'!$F$7,3*(8-1))</f>
         <v/>
       </c>
-      <c r="D8" s="36" t="inlineStr"/>
+      <c r="D8" s="34" t="inlineStr"/>
       <c r="E8" s="52" t="n">
         <v>55</v>
       </c>
@@ -4575,14 +5302,14 @@
           <t>3Y</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="40" t="n">
         <v>3</v>
       </c>
       <c r="C9" s="18">
         <f>EDATE('Curve_Interface'!$F$7,3*(12-1))</f>
         <v/>
       </c>
-      <c r="D9" s="36" t="inlineStr"/>
+      <c r="D9" s="34" t="inlineStr"/>
       <c r="E9" s="52" t="n">
         <v>70</v>
       </c>
@@ -4601,14 +5328,14 @@
           <t>5Y</t>
         </is>
       </c>
-      <c r="B10" s="35" t="n">
+      <c r="B10" s="40" t="n">
         <v>5</v>
       </c>
       <c r="C10" s="18">
         <f>EDATE('Curve_Interface'!$F$7,3*(20-1))</f>
         <v/>
       </c>
-      <c r="D10" s="36" t="inlineStr"/>
+      <c r="D10" s="34" t="inlineStr"/>
       <c r="E10" s="52" t="n">
         <v>95</v>
       </c>
@@ -4627,14 +5354,14 @@
           <t>7Y</t>
         </is>
       </c>
-      <c r="B11" s="35" t="n">
+      <c r="B11" s="40" t="n">
         <v>7</v>
       </c>
       <c r="C11" s="18">
         <f>EDATE('Curve_Interface'!$F$7,3*(28-1))</f>
         <v/>
       </c>
-      <c r="D11" s="36" t="inlineStr"/>
+      <c r="D11" s="34" t="inlineStr"/>
       <c r="E11" s="52" t="n">
         <v>115</v>
       </c>
@@ -4653,14 +5380,14 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="B12" s="35" t="n">
+      <c r="B12" s="40" t="n">
         <v>10</v>
       </c>
       <c r="C12" s="18">
         <f>EDATE('Curve_Interface'!$F$7,3*(40-1))</f>
         <v/>
       </c>
-      <c r="D12" s="36" t="inlineStr"/>
+      <c r="D12" s="34" t="inlineStr"/>
       <c r="E12" s="52" t="n">
         <v>135</v>
       </c>
@@ -4681,7 +5408,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5042,7 +5769,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5168,7 +5895,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="35" t="n">
+      <c r="A7" s="40" t="n">
         <v>1</v>
       </c>
       <c r="B7" s="18">
@@ -5229,7 +5956,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="35" t="n">
+      <c r="A8" s="40" t="n">
         <v>2</v>
       </c>
       <c r="B8" s="18">
@@ -5290,7 +6017,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="35" t="n">
+      <c r="A9" s="40" t="n">
         <v>3</v>
       </c>
       <c r="B9" s="18">
@@ -5351,7 +6078,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n">
+      <c r="A10" s="40" t="n">
         <v>4</v>
       </c>
       <c r="B10" s="18">
@@ -5412,7 +6139,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n">
+      <c r="A11" s="40" t="n">
         <v>5</v>
       </c>
       <c r="B11" s="18">
@@ -5473,7 +6200,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n">
+      <c r="A12" s="40" t="n">
         <v>6</v>
       </c>
       <c r="B12" s="18">
@@ -5534,7 +6261,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n">
+      <c r="A13" s="40" t="n">
         <v>7</v>
       </c>
       <c r="B13" s="18">
@@ -5595,7 +6322,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n">
+      <c r="A14" s="40" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="18">
@@ -5656,7 +6383,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n">
+      <c r="A15" s="40" t="n">
         <v>9</v>
       </c>
       <c r="B15" s="18">
@@ -5717,7 +6444,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n">
+      <c r="A16" s="40" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="18">
@@ -5778,7 +6505,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n">
+      <c r="A17" s="40" t="n">
         <v>11</v>
       </c>
       <c r="B17" s="18">
@@ -5839,7 +6566,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n">
+      <c r="A18" s="40" t="n">
         <v>12</v>
       </c>
       <c r="B18" s="18">
@@ -5900,7 +6627,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n">
+      <c r="A19" s="40" t="n">
         <v>13</v>
       </c>
       <c r="B19" s="18">
@@ -5961,7 +6688,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n">
+      <c r="A20" s="40" t="n">
         <v>14</v>
       </c>
       <c r="B20" s="18">
@@ -6022,7 +6749,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n">
+      <c r="A21" s="40" t="n">
         <v>15</v>
       </c>
       <c r="B21" s="18">
@@ -6083,7 +6810,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="n">
+      <c r="A22" s="40" t="n">
         <v>16</v>
       </c>
       <c r="B22" s="18">
@@ -6144,7 +6871,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n">
+      <c r="A23" s="40" t="n">
         <v>17</v>
       </c>
       <c r="B23" s="18">
@@ -6205,7 +6932,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="n">
+      <c r="A24" s="40" t="n">
         <v>18</v>
       </c>
       <c r="B24" s="18">
@@ -6266,7 +6993,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="n">
+      <c r="A25" s="40" t="n">
         <v>19</v>
       </c>
       <c r="B25" s="18">
@@ -6327,7 +7054,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="n">
+      <c r="A26" s="40" t="n">
         <v>20</v>
       </c>
       <c r="B26" s="18">
@@ -6388,7 +7115,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="n">
+      <c r="A27" s="40" t="n">
         <v>21</v>
       </c>
       <c r="B27" s="18">
@@ -6449,7 +7176,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="n">
+      <c r="A28" s="40" t="n">
         <v>22</v>
       </c>
       <c r="B28" s="18">
@@ -6510,7 +7237,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="n">
+      <c r="A29" s="40" t="n">
         <v>23</v>
       </c>
       <c r="B29" s="18">
@@ -6571,7 +7298,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="n">
+      <c r="A30" s="40" t="n">
         <v>24</v>
       </c>
       <c r="B30" s="18">
@@ -6632,7 +7359,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="n">
+      <c r="A31" s="40" t="n">
         <v>25</v>
       </c>
       <c r="B31" s="18">
@@ -6693,7 +7420,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="n">
+      <c r="A32" s="40" t="n">
         <v>26</v>
       </c>
       <c r="B32" s="18">
@@ -6754,7 +7481,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="n">
+      <c r="A33" s="40" t="n">
         <v>27</v>
       </c>
       <c r="B33" s="18">
@@ -6815,7 +7542,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="n">
+      <c r="A34" s="40" t="n">
         <v>28</v>
       </c>
       <c r="B34" s="18">
@@ -6876,7 +7603,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="n">
+      <c r="A35" s="40" t="n">
         <v>29</v>
       </c>
       <c r="B35" s="18">
@@ -6937,7 +7664,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="n">
+      <c r="A36" s="40" t="n">
         <v>30</v>
       </c>
       <c r="B36" s="18">
@@ -6998,7 +7725,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="n">
+      <c r="A37" s="40" t="n">
         <v>31</v>
       </c>
       <c r="B37" s="18">
@@ -7059,7 +7786,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="n">
+      <c r="A38" s="40" t="n">
         <v>32</v>
       </c>
       <c r="B38" s="18">
@@ -7120,7 +7847,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="n">
+      <c r="A39" s="40" t="n">
         <v>33</v>
       </c>
       <c r="B39" s="18">
@@ -7181,7 +7908,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35" t="n">
+      <c r="A40" s="40" t="n">
         <v>34</v>
       </c>
       <c r="B40" s="18">
@@ -7242,7 +7969,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35" t="n">
+      <c r="A41" s="40" t="n">
         <v>35</v>
       </c>
       <c r="B41" s="18">
@@ -7303,7 +8030,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35" t="n">
+      <c r="A42" s="40" t="n">
         <v>36</v>
       </c>
       <c r="B42" s="18">
@@ -7364,7 +8091,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35" t="n">
+      <c r="A43" s="40" t="n">
         <v>37</v>
       </c>
       <c r="B43" s="18">
@@ -7425,7 +8152,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35" t="n">
+      <c r="A44" s="40" t="n">
         <v>38</v>
       </c>
       <c r="B44" s="18">
@@ -7486,7 +8213,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35" t="n">
+      <c r="A45" s="40" t="n">
         <v>39</v>
       </c>
       <c r="B45" s="18">
@@ -7547,7 +8274,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35" t="n">
+      <c r="A46" s="40" t="n">
         <v>40</v>
       </c>
       <c r="B46" s="18">
@@ -7615,7 +8342,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7670,7 +8397,7 @@
           <t>Contractual coupon (bp)</t>
         </is>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="38">
         <f>CDS_Parameters!$B$10</f>
         <v/>
       </c>
@@ -7686,7 +8413,7 @@
           <t>Maturity (tenor yrs)</t>
         </is>
       </c>
-      <c r="B7" s="40" t="n">
+      <c r="B7" s="38" t="n">
         <v>5</v>
       </c>
     </row>
@@ -7746,7 +8473,7 @@
           <t>Protection PV</t>
         </is>
       </c>
-      <c r="B13" s="42">
+      <c r="B13" s="41">
         <f>B4*(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -7757,7 +8484,7 @@
           <t>Premium PV (@ coupon)</t>
         </is>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="41">
         <f>B4*(B6/10000)*B12</f>
         <v/>
       </c>
@@ -7784,7 +8511,7 @@
           <t>PV — protection buyer</t>
         </is>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="41">
         <f>B13-B14</f>
         <v/>
       </c>
@@ -7800,7 +8527,7 @@
           <t>PV to your direction</t>
         </is>
       </c>
-      <c r="B17" s="42">
+      <c r="B17" s="41">
         <f>IF(B9="Buy protection",B13-B14,B14-B13)</f>
         <v/>
       </c>
@@ -7833,7 +8560,7 @@
           <t>CS01  (per +1bp spread)</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="41">
         <f>B4*B12*0.0001</f>
         <v/>
       </c>
@@ -7849,7 +8576,7 @@
           <t>IR01 / DV01  (per +1bp SOFR)</t>
         </is>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="41">
         <f>-(B4*(1-B5)*SUMPRODUCT((CDS_Schedule!$C$7:$C$46&lt;=B8)*CDS_Schedule!$O$7:$O$46*CDS_Schedule!$F$7:$F$46)-B4*(B6/10000)*SUMPRODUCT((CDS_Schedule!$C$7:$C$46&lt;=B8)*(CDS_Schedule!$M$7:$M$46+CDS_Schedule!$N$7:$N$46)*CDS_Schedule!$F$7:$F$46))*0.0001</f>
         <v/>
       </c>
@@ -7865,7 +8592,7 @@
           <t>Rec01  (per +1% recovery)</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="41">
         <f>-B4*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)*0.01</f>
         <v/>
       </c>
@@ -7881,7 +8608,7 @@
           <t>Jump-to-default (immediate)</t>
         </is>
       </c>
-      <c r="B25" s="43">
+      <c r="B25" s="42">
         <f>IF(B9="Buy protection",B4*(1-B5),-B4*(1-B5))-B17</f>
         <v/>
       </c>
@@ -7907,7 +8634,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14210,1720 +14937,1727 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L49"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Curve_Interface</t>
+          <t>Bootstrap_Futures</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Shared discounting D(0,t): interpolates the SOFR Bootstrap curve to ANY date (piecewise-flat forward). One function used by both Swap_Pricer and the CDS module.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="66" customHeight="1">
+          <t>Second copy — same 3-segment build, but the MIDDLE (1Y–5Y) FORCES the SR3 futures (no OIS-agreement guard). The pure futures-driven curve, to compare against the robust Bootstrap tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Piecewise-flat instantaneous-forward interpolation — the SOFR curve's own baseline method. For t in (T_prev, T_next]: f = −ln(D_next/D_prev)/(T_next−T_prev), then D(0,t) = D_prev·exp(−f·(t−T_prev)). The demo rows are the STANDARD quarterly CDS dates (20 Mar/Jun/Sep/Dec) out to 10Y — proving the curve returns a discount factor on every CDS payment date even though those dates don't coincide with the SOFR pillars. A CDS schedule just references this same formula, so any change to fixings/futures/OIS/interpolation flows straight through. Curve grid (spot + Bootstrap pillars) is in cols K:L.</t>
+          <t>Identical to Bootstrap except the middle DFs use the SR3 futures chain DIRECTLY (interpolated off Bootstrap's futures grid Y8:Z28), falling back to OIS only on a hard error — NOT on disagreement. So 18M/2Y…5Y are always futures here. Cols A–F mirror Bootstrap; the long end re-bootstraps off these forced-futures middle DFs. Downstream tabs (Curve_Interface, Swap_Pricer, CDS) still use the robust Bootstrap tab; this one is for comparison. Watch the DF-source column and compare col H side by side.</t>
         </is>
       </c>
     </row>
     <row r="5"/>
-    <row r="6">
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>Curve grid (from Bootstrap)</t>
-        </is>
-      </c>
-    </row>
+    <row r="6"/>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Valuation:</t>
-        </is>
-      </c>
-      <c r="B7" s="34">
-        <f>VAL_DATE</f>
-        <v/>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>Spot:</t>
-        </is>
-      </c>
-      <c r="D7" s="34">
-        <f>Bootstrap!$B$4</f>
-        <v/>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>1st CDS date:</t>
-        </is>
-      </c>
-      <c r="F7" s="34">
-        <f>IF(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20)&gt;=VAL_DATE,DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),EDATE(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),3))</f>
-        <v/>
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>Tenor</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>Maturity</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>T (yrs)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>tau0</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>Par S (%)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>tau cpn</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>Annuity A(prior)</t>
+        </is>
+      </c>
+      <c r="H7" s="20" t="inlineStr">
+        <is>
+          <t>Discount factor</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Ann.add tau·DF</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>Zero (%)</t>
+        </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Fwd (%)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>DF source</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="K8" s="18">
-        <f>Bootstrap!$B$4</f>
-        <v/>
-      </c>
-      <c r="L8" s="33" t="n">
-        <v>1</v>
+      <c r="A8" s="17">
+        <f>'Bootstrap'!A8</f>
+        <v/>
+      </c>
+      <c r="B8" s="18">
+        <f>'Bootstrap'!B8</f>
+        <v/>
+      </c>
+      <c r="C8" s="28">
+        <f>'Bootstrap'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>'Bootstrap'!D8</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>'Bootstrap'!E8</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>'Bootstrap'!F8</f>
+        <v/>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="29">
+        <f>1/(1+(E8/100)*D8)</f>
+        <v/>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="17">
+        <f>-LN(H8)/C8*100</f>
+        <v/>
+      </c>
+      <c r="K8" s="17">
+        <f>(1/H8-1)/D8*100</f>
+        <v/>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Coupon #</t>
-        </is>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>Time from val (yrs)</t>
-        </is>
-      </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>Prev SOFR pillar</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr">
-        <is>
-          <t>Next SOFR pillar</t>
-        </is>
-      </c>
-      <c r="F9" s="20" t="inlineStr">
-        <is>
-          <t>Segment fwd (%)</t>
-        </is>
-      </c>
-      <c r="G9" s="20" t="inlineStr">
-        <is>
-          <t>Interp DF  D(0,t)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>Interp zero (%)</t>
-        </is>
-      </c>
-      <c r="K9" s="18">
-        <f>Bootstrap!B8</f>
-        <v/>
-      </c>
-      <c r="L9" s="33">
-        <f>Bootstrap!H8</f>
-        <v/>
+      <c r="A9" s="17">
+        <f>'Bootstrap'!A9</f>
+        <v/>
+      </c>
+      <c r="B9" s="18">
+        <f>'Bootstrap'!B9</f>
+        <v/>
+      </c>
+      <c r="C9" s="28">
+        <f>'Bootstrap'!C9</f>
+        <v/>
+      </c>
+      <c r="D9" s="17">
+        <f>'Bootstrap'!D9</f>
+        <v/>
+      </c>
+      <c r="E9" s="17">
+        <f>'Bootstrap'!E9</f>
+        <v/>
+      </c>
+      <c r="F9" s="17">
+        <f>'Bootstrap'!F9</f>
+        <v/>
+      </c>
+      <c r="G9" s="17">
+        <f>SUM($I$8:I8)</f>
+        <v/>
+      </c>
+      <c r="H9" s="29">
+        <f>1/(1+(E9/100)*D9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="17">
+        <f>-LN(H9)/C9*100</f>
+        <v/>
+      </c>
+      <c r="K9" s="17">
+        <f>(H8/H9-1)/((B9-B8)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="35" t="n">
-        <v>1</v>
+      <c r="A10" s="17">
+        <f>'Bootstrap'!A10</f>
+        <v/>
       </c>
       <c r="B10" s="18">
-        <f>EDATE($F$7,3*0)</f>
+        <f>'Bootstrap'!B10</f>
         <v/>
       </c>
       <c r="C10" s="28">
-        <f>(B10-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B10,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E10" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B10,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C10</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>'Bootstrap'!D10</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>'Bootstrap'!E10</f>
         <v/>
       </c>
       <c r="F10" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1)))/((E10-D10)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G10" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1))*EXP(-(F10/100)*(B10-D10)/365)</f>
-        <v/>
-      </c>
-      <c r="H10" s="17">
-        <f>-LN(G10)/C10*100</f>
-        <v/>
-      </c>
-      <c r="K10" s="18">
-        <f>Bootstrap!B9</f>
-        <v/>
-      </c>
-      <c r="L10" s="33">
-        <f>Bootstrap!H9</f>
-        <v/>
+        <f>'Bootstrap'!F10</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>SUM($I$8:I9)</f>
+        <v/>
+      </c>
+      <c r="H10" s="29">
+        <f>1/(1+(E10/100)*D10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="17">
+        <f>-LN(H10)/C10*100</f>
+        <v/>
+      </c>
+      <c r="K10" s="17">
+        <f>(H9/H10-1)/((B10-B9)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="35" t="n">
-        <v>2</v>
+      <c r="A11" s="17">
+        <f>'Bootstrap'!A11</f>
+        <v/>
       </c>
       <c r="B11" s="18">
-        <f>EDATE($F$7,3*1)</f>
+        <f>'Bootstrap'!B11</f>
         <v/>
       </c>
       <c r="C11" s="28">
-        <f>(B11-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D11" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B11,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E11" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B11,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C11</f>
+        <v/>
+      </c>
+      <c r="D11" s="17">
+        <f>'Bootstrap'!D11</f>
+        <v/>
+      </c>
+      <c r="E11" s="17">
+        <f>'Bootstrap'!E11</f>
         <v/>
       </c>
       <c r="F11" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1)))/((E11-D11)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G11" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1))*EXP(-(F11/100)*(B11-D11)/365)</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
-        <f>-LN(G11)/C11*100</f>
-        <v/>
-      </c>
-      <c r="K11" s="18">
-        <f>Bootstrap!B10</f>
-        <v/>
-      </c>
-      <c r="L11" s="33">
-        <f>Bootstrap!H10</f>
-        <v/>
+        <f>'Bootstrap'!F11</f>
+        <v/>
+      </c>
+      <c r="G11" s="17">
+        <f>SUM($I$8:I10)</f>
+        <v/>
+      </c>
+      <c r="H11" s="29">
+        <f>1/(1+(E11/100)*D11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17">
+        <f>-LN(H11)/C11*100</f>
+        <v/>
+      </c>
+      <c r="K11" s="17">
+        <f>(H10/H11-1)/((B11-B10)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L11" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="35" t="n">
-        <v>3</v>
+      <c r="A12" s="17">
+        <f>'Bootstrap'!A12</f>
+        <v/>
       </c>
       <c r="B12" s="18">
-        <f>EDATE($F$7,3*2)</f>
+        <f>'Bootstrap'!B12</f>
         <v/>
       </c>
       <c r="C12" s="28">
-        <f>(B12-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D12" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B12,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E12" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B12,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C12</f>
+        <v/>
+      </c>
+      <c r="D12" s="17">
+        <f>'Bootstrap'!D12</f>
+        <v/>
+      </c>
+      <c r="E12" s="17">
+        <f>'Bootstrap'!E12</f>
         <v/>
       </c>
       <c r="F12" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1)))/((E12-D12)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G12" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1))*EXP(-(F12/100)*(B12-D12)/365)</f>
-        <v/>
-      </c>
-      <c r="H12" s="17">
-        <f>-LN(G12)/C12*100</f>
-        <v/>
-      </c>
-      <c r="K12" s="18">
-        <f>Bootstrap!B11</f>
-        <v/>
-      </c>
-      <c r="L12" s="33">
-        <f>Bootstrap!H11</f>
-        <v/>
+        <f>'Bootstrap'!F12</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>SUM($I$8:I11)</f>
+        <v/>
+      </c>
+      <c r="H12" s="29">
+        <f>1/(1+(E12/100)*D12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17">
+        <f>-LN(H12)/C12*100</f>
+        <v/>
+      </c>
+      <c r="K12" s="17">
+        <f>(H11/H12-1)/((B12-B11)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="35" t="n">
-        <v>4</v>
+      <c r="A13" s="17">
+        <f>'Bootstrap'!A13</f>
+        <v/>
       </c>
       <c r="B13" s="18">
-        <f>EDATE($F$7,3*3)</f>
+        <f>'Bootstrap'!B13</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>(B13-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D13" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B13,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E13" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B13,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C13</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>'Bootstrap'!D13</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>'Bootstrap'!E13</f>
         <v/>
       </c>
       <c r="F13" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1)))/((E13-D13)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G13" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1))*EXP(-(F13/100)*(B13-D13)/365)</f>
-        <v/>
-      </c>
-      <c r="H13" s="17">
-        <f>-LN(G13)/C13*100</f>
-        <v/>
-      </c>
-      <c r="K13" s="18">
-        <f>Bootstrap!B12</f>
-        <v/>
-      </c>
-      <c r="L13" s="33">
-        <f>Bootstrap!H12</f>
-        <v/>
+        <f>'Bootstrap'!F13</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>SUM($I$8:I12)</f>
+        <v/>
+      </c>
+      <c r="H13" s="29">
+        <f>1/(1+(E13/100)*D13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <f>-LN(H13)/C13*100</f>
+        <v/>
+      </c>
+      <c r="K13" s="17">
+        <f>(H12/H13-1)/((B13-B12)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L13" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="35" t="n">
-        <v>5</v>
+      <c r="A14" s="17">
+        <f>'Bootstrap'!A14</f>
+        <v/>
       </c>
       <c r="B14" s="18">
-        <f>EDATE($F$7,3*4)</f>
+        <f>'Bootstrap'!B14</f>
         <v/>
       </c>
       <c r="C14" s="28">
-        <f>(B14-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D14" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B14,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E14" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B14,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C14</f>
+        <v/>
+      </c>
+      <c r="D14" s="17">
+        <f>'Bootstrap'!D14</f>
+        <v/>
+      </c>
+      <c r="E14" s="17">
+        <f>'Bootstrap'!E14</f>
         <v/>
       </c>
       <c r="F14" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1)))/((E14-D14)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G14" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1))*EXP(-(F14/100)*(B14-D14)/365)</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>-LN(G14)/C14*100</f>
-        <v/>
-      </c>
-      <c r="K14" s="18">
-        <f>Bootstrap!B13</f>
-        <v/>
-      </c>
-      <c r="L14" s="33">
-        <f>Bootstrap!H13</f>
-        <v/>
+        <f>'Bootstrap'!F14</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>SUM($I$8:I13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="29">
+        <f>1/(1+(E14/100)*D14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="17">
+        <f>-LN(H14)/C14*100</f>
+        <v/>
+      </c>
+      <c r="K14" s="17">
+        <f>(H13/H14-1)/((B14-B13)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="35" t="n">
-        <v>6</v>
+      <c r="A15" s="17">
+        <f>'Bootstrap'!A15</f>
+        <v/>
       </c>
       <c r="B15" s="18">
-        <f>EDATE($F$7,3*5)</f>
+        <f>'Bootstrap'!B15</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>(B15-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B15,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E15" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B15,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C15</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>'Bootstrap'!D15</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>'Bootstrap'!E15</f>
         <v/>
       </c>
       <c r="F15" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1)))/((E15-D15)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G15" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1))*EXP(-(F15/100)*(B15-D15)/365)</f>
-        <v/>
-      </c>
-      <c r="H15" s="17">
-        <f>-LN(G15)/C15*100</f>
-        <v/>
-      </c>
-      <c r="K15" s="18">
-        <f>Bootstrap!B14</f>
-        <v/>
-      </c>
-      <c r="L15" s="33">
-        <f>Bootstrap!H14</f>
-        <v/>
+        <f>'Bootstrap'!F15</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>SUM($I$8:I14)</f>
+        <v/>
+      </c>
+      <c r="H15" s="29">
+        <f>1/(1+(E15/100)*D15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="17">
+        <f>-LN(H15)/C15*100</f>
+        <v/>
+      </c>
+      <c r="K15" s="17">
+        <f>(H14/H15-1)/((B15-B14)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="35" t="n">
-        <v>7</v>
+      <c r="A16" s="17">
+        <f>'Bootstrap'!A16</f>
+        <v/>
       </c>
       <c r="B16" s="18">
-        <f>EDATE($F$7,3*6)</f>
+        <f>'Bootstrap'!B16</f>
         <v/>
       </c>
       <c r="C16" s="28">
-        <f>(B16-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D16" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B16,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E16" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B16,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C16</f>
+        <v/>
+      </c>
+      <c r="D16" s="17">
+        <f>'Bootstrap'!D16</f>
+        <v/>
+      </c>
+      <c r="E16" s="17">
+        <f>'Bootstrap'!E16</f>
         <v/>
       </c>
       <c r="F16" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1)))/((E16-D16)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G16" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1))*EXP(-(F16/100)*(B16-D16)/365)</f>
-        <v/>
-      </c>
-      <c r="H16" s="17">
-        <f>-LN(G16)/C16*100</f>
-        <v/>
-      </c>
-      <c r="K16" s="18">
-        <f>Bootstrap!B15</f>
-        <v/>
-      </c>
-      <c r="L16" s="33">
-        <f>Bootstrap!H15</f>
-        <v/>
+        <f>'Bootstrap'!F16</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>SUM($I$8:I15)</f>
+        <v/>
+      </c>
+      <c r="H16" s="29">
+        <f>1/(1+(E16/100)*D16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <f>-LN(H16)/C16*100</f>
+        <v/>
+      </c>
+      <c r="K16" s="17">
+        <f>(H15/H16-1)/((B16-B15)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="35" t="n">
-        <v>8</v>
+      <c r="A17" s="17">
+        <f>'Bootstrap'!A17</f>
+        <v/>
       </c>
       <c r="B17" s="18">
-        <f>EDATE($F$7,3*7)</f>
+        <f>'Bootstrap'!B17</f>
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>(B17-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D17" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B17,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E17" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B17,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C17</f>
+        <v/>
+      </c>
+      <c r="D17" s="17">
+        <f>'Bootstrap'!D17</f>
+        <v/>
+      </c>
+      <c r="E17" s="17">
+        <f>'Bootstrap'!E17</f>
         <v/>
       </c>
       <c r="F17" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1)))/((E17-D17)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G17" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1))*EXP(-(F17/100)*(B17-D17)/365)</f>
-        <v/>
-      </c>
-      <c r="H17" s="17">
-        <f>-LN(G17)/C17*100</f>
-        <v/>
-      </c>
-      <c r="K17" s="18">
-        <f>Bootstrap!B16</f>
-        <v/>
-      </c>
-      <c r="L17" s="33">
-        <f>Bootstrap!H16</f>
-        <v/>
+        <f>'Bootstrap'!F17</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>SUM($I$8:I16)</f>
+        <v/>
+      </c>
+      <c r="H17" s="29">
+        <f>1/(1+(E17/100)*D17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="17">
+        <f>-LN(H17)/C17*100</f>
+        <v/>
+      </c>
+      <c r="K17" s="17">
+        <f>(H16/H17-1)/((B17-B16)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L17" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="35" t="n">
-        <v>9</v>
+      <c r="A18" s="17">
+        <f>'Bootstrap'!A18</f>
+        <v/>
       </c>
       <c r="B18" s="18">
-        <f>EDATE($F$7,3*8)</f>
+        <f>'Bootstrap'!B18</f>
         <v/>
       </c>
       <c r="C18" s="28">
-        <f>(B18-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D18" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B18,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E18" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B18,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C18</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>'Bootstrap'!D18</f>
+        <v/>
+      </c>
+      <c r="E18" s="17">
+        <f>'Bootstrap'!E18</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1)))/((E18-D18)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G18" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1))*EXP(-(F18/100)*(B18-D18)/365)</f>
-        <v/>
-      </c>
-      <c r="H18" s="17">
-        <f>-LN(G18)/C18*100</f>
-        <v/>
-      </c>
-      <c r="K18" s="18">
-        <f>Bootstrap!B17</f>
-        <v/>
-      </c>
-      <c r="L18" s="33">
-        <f>Bootstrap!H17</f>
-        <v/>
+        <f>'Bootstrap'!F18</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>SUM($I$8:I17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="29">
+        <f>1/(1+(E18/100)*D18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="17">
+        <f>-LN(H18)/C18*100</f>
+        <v/>
+      </c>
+      <c r="K18" s="17">
+        <f>(H17/H18-1)/((B18-B17)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="35" t="n">
-        <v>10</v>
+      <c r="A19" s="17">
+        <f>'Bootstrap'!A19</f>
+        <v/>
       </c>
       <c r="B19" s="18">
-        <f>EDATE($F$7,3*9)</f>
+        <f>'Bootstrap'!B19</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>(B19-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D19" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B19,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E19" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B19,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C19</f>
+        <v/>
+      </c>
+      <c r="D19" s="17">
+        <f>'Bootstrap'!D19</f>
+        <v/>
+      </c>
+      <c r="E19" s="17">
+        <f>'Bootstrap'!E19</f>
         <v/>
       </c>
       <c r="F19" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1)))/((E19-D19)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G19" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1))*EXP(-(F19/100)*(B19-D19)/365)</f>
-        <v/>
-      </c>
-      <c r="H19" s="17">
-        <f>-LN(G19)/C19*100</f>
-        <v/>
-      </c>
-      <c r="K19" s="18">
-        <f>Bootstrap!B18</f>
-        <v/>
-      </c>
-      <c r="L19" s="33">
-        <f>Bootstrap!H18</f>
-        <v/>
+        <f>'Bootstrap'!F19</f>
+        <v/>
+      </c>
+      <c r="G19" s="17">
+        <f>SUM($I$8:I18)</f>
+        <v/>
+      </c>
+      <c r="H19" s="29">
+        <f>1/(1+(E19/100)*D19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="17">
+        <f>-LN(H19)/C19*100</f>
+        <v/>
+      </c>
+      <c r="K19" s="17">
+        <f>(H18/H19-1)/((B19-B18)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L19" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="35" t="n">
-        <v>11</v>
+      <c r="A20" s="17">
+        <f>'Bootstrap'!A20</f>
+        <v/>
       </c>
       <c r="B20" s="18">
-        <f>EDATE($F$7,3*10)</f>
+        <f>'Bootstrap'!B20</f>
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>(B20-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D20" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B20,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E20" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B20,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C20</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>'Bootstrap'!D20</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>'Bootstrap'!E20</f>
         <v/>
       </c>
       <c r="F20" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1)))/((E20-D20)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G20" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1))*EXP(-(F20/100)*(B20-D20)/365)</f>
-        <v/>
-      </c>
-      <c r="H20" s="17">
-        <f>-LN(G20)/C20*100</f>
-        <v/>
-      </c>
-      <c r="K20" s="18">
-        <f>Bootstrap!B19</f>
-        <v/>
-      </c>
-      <c r="L20" s="33">
-        <f>Bootstrap!H19</f>
-        <v/>
+        <f>'Bootstrap'!F20</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>SUM($I$8:I19)</f>
+        <v/>
+      </c>
+      <c r="H20" s="29">
+        <f>1/(1+(E20/100)*D20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="17">
+        <f>-LN(H20)/C20*100</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>(H19/H20-1)/((B20-B19)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L20" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="35" t="n">
-        <v>12</v>
+      <c r="A21" s="17">
+        <f>'Bootstrap'!A21</f>
+        <v/>
       </c>
       <c r="B21" s="18">
-        <f>EDATE($F$7,3*11)</f>
+        <f>'Bootstrap'!B21</f>
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>(B21-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D21" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B21,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E21" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B21,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C21</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>'Bootstrap'!D21</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>'Bootstrap'!E21</f>
         <v/>
       </c>
       <c r="F21" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1)))/((E21-D21)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G21" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1))*EXP(-(F21/100)*(B21-D21)/365)</f>
-        <v/>
-      </c>
-      <c r="H21" s="17">
-        <f>-LN(G21)/C21*100</f>
-        <v/>
-      </c>
-      <c r="K21" s="18">
-        <f>Bootstrap!B20</f>
-        <v/>
-      </c>
-      <c r="L21" s="33">
-        <f>Bootstrap!H20</f>
-        <v/>
+        <f>'Bootstrap'!F21</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f>SUM($I$8:I20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="29">
+        <f>1/(1+(E21/100)*D21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="17">
+        <f>-LN(H21)/C21*100</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>(H20/H21-1)/((B21-B20)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L21" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="35" t="n">
-        <v>13</v>
+      <c r="A22" s="17">
+        <f>'Bootstrap'!A22</f>
+        <v/>
       </c>
       <c r="B22" s="18">
-        <f>EDATE($F$7,3*12)</f>
+        <f>'Bootstrap'!B22</f>
         <v/>
       </c>
       <c r="C22" s="28">
-        <f>(B22-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D22" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B22,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E22" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B22,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C22</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>'Bootstrap'!D22</f>
+        <v/>
+      </c>
+      <c r="E22" s="17">
+        <f>'Bootstrap'!E22</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1)))/((E22-D22)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G22" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1))*EXP(-(F22/100)*(B22-D22)/365)</f>
-        <v/>
-      </c>
-      <c r="H22" s="17">
-        <f>-LN(G22)/C22*100</f>
-        <v/>
-      </c>
-      <c r="K22" s="18">
-        <f>Bootstrap!B21</f>
-        <v/>
-      </c>
-      <c r="L22" s="33">
-        <f>Bootstrap!H21</f>
-        <v/>
+        <f>'Bootstrap'!F22</f>
+        <v/>
+      </c>
+      <c r="G22" s="17">
+        <f>SUM($I$8:I21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="29">
+        <f>1/(1+(E22/100)*D22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="17">
+        <f>F22*H22</f>
+        <v/>
+      </c>
+      <c r="J22" s="17">
+        <f>-LN(H22)/C22*100</f>
+        <v/>
+      </c>
+      <c r="K22" s="17">
+        <f>(H21/H22-1)/((B22-B21)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L22" s="6" t="inlineStr">
+        <is>
+          <t>short OIS</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="35" t="n">
-        <v>14</v>
+      <c r="A23" s="17">
+        <f>'Bootstrap'!A23</f>
+        <v/>
       </c>
       <c r="B23" s="18">
-        <f>EDATE($F$7,3*13)</f>
+        <f>'Bootstrap'!B23</f>
         <v/>
       </c>
       <c r="C23" s="28">
-        <f>(B23-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D23" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B23,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E23" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B23,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C23</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>'Bootstrap'!D23</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>'Bootstrap'!E23</f>
         <v/>
       </c>
       <c r="F23" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1)))/((E23-D23)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G23" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1))*EXP(-(F23/100)*(B23-D23)/365)</f>
-        <v/>
-      </c>
-      <c r="H23" s="17">
-        <f>-LN(G23)/C23*100</f>
-        <v/>
-      </c>
-      <c r="K23" s="18">
-        <f>Bootstrap!B22</f>
-        <v/>
-      </c>
-      <c r="L23" s="33">
-        <f>Bootstrap!H22</f>
-        <v/>
+        <f>'Bootstrap'!F23</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>SUM($I$8:I22)</f>
+        <v/>
+      </c>
+      <c r="H23" s="29">
+        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)))^((B23-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E23/100)*G23)/(1+(E23/100)*F23))</f>
+        <v/>
+      </c>
+      <c r="I23" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="17">
+        <f>-LN(H23)/C23*100</f>
+        <v/>
+      </c>
+      <c r="K23" s="17">
+        <f>(H22/H23-1)/((B23-B22)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures (forced)</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="35" t="n">
-        <v>15</v>
+      <c r="A24" s="17">
+        <f>'Bootstrap'!A24</f>
+        <v/>
       </c>
       <c r="B24" s="18">
-        <f>EDATE($F$7,3*14)</f>
+        <f>'Bootstrap'!B24</f>
         <v/>
       </c>
       <c r="C24" s="28">
-        <f>(B24-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D24" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B24,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E24" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B24,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C24</f>
+        <v/>
+      </c>
+      <c r="D24" s="17">
+        <f>'Bootstrap'!D24</f>
+        <v/>
+      </c>
+      <c r="E24" s="17">
+        <f>'Bootstrap'!E24</f>
         <v/>
       </c>
       <c r="F24" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1)))/((E24-D24)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G24" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1))*EXP(-(F24/100)*(B24-D24)/365)</f>
-        <v/>
-      </c>
-      <c r="H24" s="17">
-        <f>-LN(G24)/C24*100</f>
-        <v/>
-      </c>
-      <c r="K24" s="18">
-        <f>Bootstrap!B23</f>
-        <v/>
-      </c>
-      <c r="L24" s="33">
-        <f>Bootstrap!H23</f>
-        <v/>
+        <f>'Bootstrap'!F24</f>
+        <v/>
+      </c>
+      <c r="G24" s="17">
+        <f>SUM($I$8:I23)</f>
+        <v/>
+      </c>
+      <c r="H24" s="29">
+        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)))^((B24-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E24/100)*G24)/(1+(E24/100)*F24))</f>
+        <v/>
+      </c>
+      <c r="I24" s="17">
+        <f>F24*H24</f>
+        <v/>
+      </c>
+      <c r="J24" s="17">
+        <f>-LN(H24)/C24*100</f>
+        <v/>
+      </c>
+      <c r="K24" s="17">
+        <f>(H23/H24-1)/((B24-B23)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L24" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures (forced)</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="35" t="n">
-        <v>16</v>
+      <c r="A25" s="17">
+        <f>'Bootstrap'!A25</f>
+        <v/>
       </c>
       <c r="B25" s="18">
-        <f>EDATE($F$7,3*15)</f>
+        <f>'Bootstrap'!B25</f>
         <v/>
       </c>
       <c r="C25" s="28">
-        <f>(B25-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D25" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B25,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E25" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B25,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C25</f>
+        <v/>
+      </c>
+      <c r="D25" s="17">
+        <f>'Bootstrap'!D25</f>
+        <v/>
+      </c>
+      <c r="E25" s="17">
+        <f>'Bootstrap'!E25</f>
         <v/>
       </c>
       <c r="F25" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1)))/((E25-D25)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G25" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1))*EXP(-(F25/100)*(B25-D25)/365)</f>
-        <v/>
-      </c>
-      <c r="H25" s="17">
-        <f>-LN(G25)/C25*100</f>
-        <v/>
-      </c>
-      <c r="K25" s="18">
-        <f>Bootstrap!B24</f>
-        <v/>
-      </c>
-      <c r="L25" s="33">
-        <f>Bootstrap!H24</f>
-        <v/>
+        <f>'Bootstrap'!F25</f>
+        <v/>
+      </c>
+      <c r="G25" s="17">
+        <f>SUM($I$8:I24)</f>
+        <v/>
+      </c>
+      <c r="H25" s="29">
+        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)))^((B25-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E25/100)*G25)/(1+(E25/100)*F25))</f>
+        <v/>
+      </c>
+      <c r="I25" s="17">
+        <f>F25*H25</f>
+        <v/>
+      </c>
+      <c r="J25" s="17">
+        <f>-LN(H25)/C25*100</f>
+        <v/>
+      </c>
+      <c r="K25" s="17">
+        <f>(H24/H25-1)/((B25-B24)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L25" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures (forced)</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="35" t="n">
-        <v>17</v>
+      <c r="A26" s="17">
+        <f>'Bootstrap'!A26</f>
+        <v/>
       </c>
       <c r="B26" s="18">
-        <f>EDATE($F$7,3*16)</f>
+        <f>'Bootstrap'!B26</f>
         <v/>
       </c>
       <c r="C26" s="28">
-        <f>(B26-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D26" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B26,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E26" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B26,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C26</f>
+        <v/>
+      </c>
+      <c r="D26" s="17">
+        <f>'Bootstrap'!D26</f>
+        <v/>
+      </c>
+      <c r="E26" s="17">
+        <f>'Bootstrap'!E26</f>
         <v/>
       </c>
       <c r="F26" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1)))/((E26-D26)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G26" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1))*EXP(-(F26/100)*(B26-D26)/365)</f>
-        <v/>
-      </c>
-      <c r="H26" s="17">
-        <f>-LN(G26)/C26*100</f>
-        <v/>
-      </c>
-      <c r="K26" s="18">
-        <f>Bootstrap!B25</f>
-        <v/>
-      </c>
-      <c r="L26" s="33">
-        <f>Bootstrap!H25</f>
-        <v/>
+        <f>'Bootstrap'!F26</f>
+        <v/>
+      </c>
+      <c r="G26" s="17">
+        <f>SUM($I$8:I25)</f>
+        <v/>
+      </c>
+      <c r="H26" s="29">
+        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)))^((B26-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E26/100)*G26)/(1+(E26/100)*F26))</f>
+        <v/>
+      </c>
+      <c r="I26" s="17">
+        <f>F26*H26</f>
+        <v/>
+      </c>
+      <c r="J26" s="17">
+        <f>-LN(H26)/C26*100</f>
+        <v/>
+      </c>
+      <c r="K26" s="17">
+        <f>(H25/H26-1)/((B26-B25)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L26" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures (forced)</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="35" t="n">
-        <v>18</v>
+      <c r="A27" s="17">
+        <f>'Bootstrap'!A27</f>
+        <v/>
       </c>
       <c r="B27" s="18">
-        <f>EDATE($F$7,3*17)</f>
+        <f>'Bootstrap'!B27</f>
         <v/>
       </c>
       <c r="C27" s="28">
-        <f>(B27-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D27" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B27,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E27" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B27,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C27</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>'Bootstrap'!D27</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>'Bootstrap'!E27</f>
         <v/>
       </c>
       <c r="F27" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1)))/((E27-D27)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G27" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1))*EXP(-(F27/100)*(B27-D27)/365)</f>
-        <v/>
-      </c>
-      <c r="H27" s="17">
-        <f>-LN(G27)/C27*100</f>
-        <v/>
-      </c>
-      <c r="K27" s="18">
-        <f>Bootstrap!B26</f>
-        <v/>
-      </c>
-      <c r="L27" s="33">
-        <f>Bootstrap!H26</f>
-        <v/>
+        <f>'Bootstrap'!F27</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>SUM($I$8:I26)</f>
+        <v/>
+      </c>
+      <c r="H27" s="29">
+        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)))^((B27-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E27/100)*G27)/(1+(E27/100)*F27))</f>
+        <v/>
+      </c>
+      <c r="I27" s="17">
+        <f>F27*H27</f>
+        <v/>
+      </c>
+      <c r="J27" s="17">
+        <f>-LN(H27)/C27*100</f>
+        <v/>
+      </c>
+      <c r="K27" s="17">
+        <f>(H26/H27-1)/((B27-B26)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L27" s="6" t="inlineStr">
+        <is>
+          <t>SR3 futures (forced)</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="35" t="n">
-        <v>19</v>
+      <c r="A28" s="17">
+        <f>'Bootstrap'!A28</f>
+        <v/>
       </c>
       <c r="B28" s="18">
-        <f>EDATE($F$7,3*18)</f>
+        <f>'Bootstrap'!B28</f>
         <v/>
       </c>
       <c r="C28" s="28">
-        <f>(B28-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D28" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B28,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E28" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B28,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C28</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>'Bootstrap'!D28</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>'Bootstrap'!E28</f>
         <v/>
       </c>
       <c r="F28" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1)))/((E28-D28)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G28" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1))*EXP(-(F28/100)*(B28-D28)/365)</f>
-        <v/>
-      </c>
-      <c r="H28" s="17">
-        <f>-LN(G28)/C28*100</f>
-        <v/>
-      </c>
-      <c r="K28" s="18">
-        <f>Bootstrap!B27</f>
-        <v/>
-      </c>
-      <c r="L28" s="33">
-        <f>Bootstrap!H27</f>
-        <v/>
+        <f>'Bootstrap'!F28</f>
+        <v/>
+      </c>
+      <c r="G28" s="17">
+        <f>SUM($I$8:I27)</f>
+        <v/>
+      </c>
+      <c r="H28" s="29">
+        <f>(1-(E28/100)*G28)/(1+(E28/100)*F28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>F28*H28</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>-LN(H28)/C28*100</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>(H27/H28-1)/((B28-B27)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L28" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="35" t="n">
-        <v>20</v>
+      <c r="A29" s="17">
+        <f>'Bootstrap'!A29</f>
+        <v/>
       </c>
       <c r="B29" s="18">
-        <f>EDATE($F$7,3*19)</f>
+        <f>'Bootstrap'!B29</f>
         <v/>
       </c>
       <c r="C29" s="28">
-        <f>(B29-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D29" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B29,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E29" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B29,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C29</f>
+        <v/>
+      </c>
+      <c r="D29" s="17">
+        <f>'Bootstrap'!D29</f>
+        <v/>
+      </c>
+      <c r="E29" s="17">
+        <f>'Bootstrap'!E29</f>
         <v/>
       </c>
       <c r="F29" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1)))/((E29-D29)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G29" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1))*EXP(-(F29/100)*(B29-D29)/365)</f>
-        <v/>
-      </c>
-      <c r="H29" s="17">
-        <f>-LN(G29)/C29*100</f>
-        <v/>
-      </c>
-      <c r="K29" s="18">
-        <f>Bootstrap!B28</f>
-        <v/>
-      </c>
-      <c r="L29" s="33">
-        <f>Bootstrap!H28</f>
-        <v/>
+        <f>'Bootstrap'!F29</f>
+        <v/>
+      </c>
+      <c r="G29" s="17">
+        <f>SUM($I$8:I28)</f>
+        <v/>
+      </c>
+      <c r="H29" s="29">
+        <f>(1-(E29/100)*G29)/(1+(E29/100)*F29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="17">
+        <f>F29*H29</f>
+        <v/>
+      </c>
+      <c r="J29" s="17">
+        <f>-LN(H29)/C29*100</f>
+        <v/>
+      </c>
+      <c r="K29" s="17">
+        <f>(H28/H29-1)/((B29-B28)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="35" t="n">
-        <v>21</v>
+      <c r="A30" s="17">
+        <f>'Bootstrap'!A30</f>
+        <v/>
       </c>
       <c r="B30" s="18">
-        <f>EDATE($F$7,3*20)</f>
+        <f>'Bootstrap'!B30</f>
         <v/>
       </c>
       <c r="C30" s="28">
-        <f>(B30-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D30" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B30,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E30" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B30,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C30</f>
+        <v/>
+      </c>
+      <c r="D30" s="17">
+        <f>'Bootstrap'!D30</f>
+        <v/>
+      </c>
+      <c r="E30" s="17">
+        <f>'Bootstrap'!E30</f>
         <v/>
       </c>
       <c r="F30" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1)))/((E30-D30)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G30" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1))*EXP(-(F30/100)*(B30-D30)/365)</f>
-        <v/>
-      </c>
-      <c r="H30" s="17">
-        <f>-LN(G30)/C30*100</f>
-        <v/>
-      </c>
-      <c r="K30" s="18">
-        <f>Bootstrap!B29</f>
-        <v/>
-      </c>
-      <c r="L30" s="33">
-        <f>Bootstrap!H29</f>
-        <v/>
+        <f>'Bootstrap'!F30</f>
+        <v/>
+      </c>
+      <c r="G30" s="17">
+        <f>SUM($I$8:I29)</f>
+        <v/>
+      </c>
+      <c r="H30" s="29">
+        <f>(1-(E30/100)*G30)/(1+(E30/100)*F30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="17">
+        <f>F30*H30</f>
+        <v/>
+      </c>
+      <c r="J30" s="17">
+        <f>-LN(H30)/C30*100</f>
+        <v/>
+      </c>
+      <c r="K30" s="17">
+        <f>(H29/H30-1)/((B30-B29)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="35" t="n">
-        <v>22</v>
+      <c r="A31" s="17">
+        <f>'Bootstrap'!A31</f>
+        <v/>
       </c>
       <c r="B31" s="18">
-        <f>EDATE($F$7,3*21)</f>
+        <f>'Bootstrap'!B31</f>
         <v/>
       </c>
       <c r="C31" s="28">
-        <f>(B31-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D31" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B31,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E31" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B31,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C31</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>'Bootstrap'!D31</f>
+        <v/>
+      </c>
+      <c r="E31" s="17">
+        <f>'Bootstrap'!E31</f>
         <v/>
       </c>
       <c r="F31" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1)))/((E31-D31)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G31" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1))*EXP(-(F31/100)*(B31-D31)/365)</f>
-        <v/>
-      </c>
-      <c r="H31" s="17">
-        <f>-LN(G31)/C31*100</f>
-        <v/>
-      </c>
-      <c r="K31" s="18">
-        <f>Bootstrap!B30</f>
-        <v/>
-      </c>
-      <c r="L31" s="33">
-        <f>Bootstrap!H30</f>
-        <v/>
+        <f>'Bootstrap'!F31</f>
+        <v/>
+      </c>
+      <c r="G31" s="17">
+        <f>SUM($I$8:I30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="29">
+        <f>(1-(E31/100)*G31)/(1+(E31/100)*F31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="17">
+        <f>F31*H31</f>
+        <v/>
+      </c>
+      <c r="J31" s="17">
+        <f>-LN(H31)/C31*100</f>
+        <v/>
+      </c>
+      <c r="K31" s="17">
+        <f>(H30/H31-1)/((B31-B30)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="35" t="n">
-        <v>23</v>
+      <c r="A32" s="17">
+        <f>'Bootstrap'!A32</f>
+        <v/>
       </c>
       <c r="B32" s="18">
-        <f>EDATE($F$7,3*22)</f>
+        <f>'Bootstrap'!B32</f>
         <v/>
       </c>
       <c r="C32" s="28">
-        <f>(B32-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D32" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B32,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E32" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B32,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C32</f>
+        <v/>
+      </c>
+      <c r="D32" s="17">
+        <f>'Bootstrap'!D32</f>
+        <v/>
+      </c>
+      <c r="E32" s="17">
+        <f>'Bootstrap'!E32</f>
         <v/>
       </c>
       <c r="F32" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1)))/((E32-D32)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G32" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1))*EXP(-(F32/100)*(B32-D32)/365)</f>
-        <v/>
-      </c>
-      <c r="H32" s="17">
-        <f>-LN(G32)/C32*100</f>
-        <v/>
-      </c>
-      <c r="K32" s="18">
-        <f>Bootstrap!B31</f>
-        <v/>
-      </c>
-      <c r="L32" s="33">
-        <f>Bootstrap!H31</f>
-        <v/>
+        <f>'Bootstrap'!F32</f>
+        <v/>
+      </c>
+      <c r="G32" s="17">
+        <f>SUM($I$8:I31)</f>
+        <v/>
+      </c>
+      <c r="H32" s="29">
+        <f>(1-(E32/100)*G32)/(1+(E32/100)*F32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="17">
+        <f>F32*H32</f>
+        <v/>
+      </c>
+      <c r="J32" s="17">
+        <f>-LN(H32)/C32*100</f>
+        <v/>
+      </c>
+      <c r="K32" s="17">
+        <f>(H31/H32-1)/((B32-B31)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L32" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="35" t="n">
-        <v>24</v>
+      <c r="A33" s="17">
+        <f>'Bootstrap'!A33</f>
+        <v/>
       </c>
       <c r="B33" s="18">
-        <f>EDATE($F$7,3*23)</f>
+        <f>'Bootstrap'!B33</f>
         <v/>
       </c>
       <c r="C33" s="28">
-        <f>(B33-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D33" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B33,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E33" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B33,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C33</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>'Bootstrap'!D33</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>'Bootstrap'!E33</f>
         <v/>
       </c>
       <c r="F33" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1)))/((E33-D33)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G33" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1))*EXP(-(F33/100)*(B33-D33)/365)</f>
-        <v/>
-      </c>
-      <c r="H33" s="17">
-        <f>-LN(G33)/C33*100</f>
-        <v/>
-      </c>
-      <c r="K33" s="18">
-        <f>Bootstrap!B32</f>
-        <v/>
-      </c>
-      <c r="L33" s="33">
-        <f>Bootstrap!H32</f>
-        <v/>
+        <f>'Bootstrap'!F33</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>SUM($I$8:I32)</f>
+        <v/>
+      </c>
+      <c r="H33" s="29">
+        <f>(1-(E33/100)*G33)/(1+(E33/100)*F33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="17">
+        <f>F33*H33</f>
+        <v/>
+      </c>
+      <c r="J33" s="17">
+        <f>-LN(H33)/C33*100</f>
+        <v/>
+      </c>
+      <c r="K33" s="17">
+        <f>(H32/H33-1)/((B33-B32)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L33" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="35" t="n">
-        <v>25</v>
+      <c r="A34" s="17">
+        <f>'Bootstrap'!A34</f>
+        <v/>
       </c>
       <c r="B34" s="18">
-        <f>EDATE($F$7,3*24)</f>
+        <f>'Bootstrap'!B34</f>
         <v/>
       </c>
       <c r="C34" s="28">
-        <f>(B34-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D34" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B34,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E34" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B34,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C34</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>'Bootstrap'!D34</f>
+        <v/>
+      </c>
+      <c r="E34" s="17">
+        <f>'Bootstrap'!E34</f>
         <v/>
       </c>
       <c r="F34" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1)))/((E34-D34)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G34" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1))*EXP(-(F34/100)*(B34-D34)/365)</f>
-        <v/>
-      </c>
-      <c r="H34" s="17">
-        <f>-LN(G34)/C34*100</f>
-        <v/>
-      </c>
-      <c r="K34" s="18">
-        <f>Bootstrap!B33</f>
-        <v/>
-      </c>
-      <c r="L34" s="33">
-        <f>Bootstrap!H33</f>
-        <v/>
+        <f>'Bootstrap'!F34</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>SUM($I$8:I33)</f>
+        <v/>
+      </c>
+      <c r="H34" s="29">
+        <f>(1-(E34/100)*G34)/(1+(E34/100)*F34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="17">
+        <f>F34*H34</f>
+        <v/>
+      </c>
+      <c r="J34" s="17">
+        <f>-LN(H34)/C34*100</f>
+        <v/>
+      </c>
+      <c r="K34" s="17">
+        <f>(H33/H34-1)/((B34-B33)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L34" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="35" t="n">
-        <v>26</v>
+      <c r="A35" s="17">
+        <f>'Bootstrap'!A35</f>
+        <v/>
       </c>
       <c r="B35" s="18">
-        <f>EDATE($F$7,3*25)</f>
+        <f>'Bootstrap'!B35</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>(B35-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D35" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B35,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E35" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B35,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C35</f>
+        <v/>
+      </c>
+      <c r="D35" s="17">
+        <f>'Bootstrap'!D35</f>
+        <v/>
+      </c>
+      <c r="E35" s="17">
+        <f>'Bootstrap'!E35</f>
         <v/>
       </c>
       <c r="F35" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1)))/((E35-D35)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G35" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1))*EXP(-(F35/100)*(B35-D35)/365)</f>
-        <v/>
-      </c>
-      <c r="H35" s="17">
-        <f>-LN(G35)/C35*100</f>
-        <v/>
-      </c>
-      <c r="K35" s="18">
-        <f>Bootstrap!B34</f>
-        <v/>
-      </c>
-      <c r="L35" s="33">
-        <f>Bootstrap!H34</f>
-        <v/>
+        <f>'Bootstrap'!F35</f>
+        <v/>
+      </c>
+      <c r="G35" s="17">
+        <f>SUM($I$8:I34)</f>
+        <v/>
+      </c>
+      <c r="H35" s="29">
+        <f>(1-(E35/100)*G35)/(1+(E35/100)*F35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="17">
+        <f>F35*H35</f>
+        <v/>
+      </c>
+      <c r="J35" s="17">
+        <f>-LN(H35)/C35*100</f>
+        <v/>
+      </c>
+      <c r="K35" s="17">
+        <f>(H34/H35-1)/((B35-B34)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L35" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35" t="n">
-        <v>27</v>
+      <c r="A36" s="17">
+        <f>'Bootstrap'!A36</f>
+        <v/>
       </c>
       <c r="B36" s="18">
-        <f>EDATE($F$7,3*26)</f>
+        <f>'Bootstrap'!B36</f>
         <v/>
       </c>
       <c r="C36" s="28">
-        <f>(B36-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D36" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B36,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E36" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B36,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C36</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>'Bootstrap'!D36</f>
+        <v/>
+      </c>
+      <c r="E36" s="17">
+        <f>'Bootstrap'!E36</f>
         <v/>
       </c>
       <c r="F36" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1)))/((E36-D36)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G36" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1))*EXP(-(F36/100)*(B36-D36)/365)</f>
-        <v/>
-      </c>
-      <c r="H36" s="17">
-        <f>-LN(G36)/C36*100</f>
-        <v/>
-      </c>
-      <c r="K36" s="18">
-        <f>Bootstrap!B35</f>
-        <v/>
-      </c>
-      <c r="L36" s="33">
-        <f>Bootstrap!H35</f>
-        <v/>
+        <f>'Bootstrap'!F36</f>
+        <v/>
+      </c>
+      <c r="G36" s="17">
+        <f>SUM($I$8:I35)</f>
+        <v/>
+      </c>
+      <c r="H36" s="29">
+        <f>(1-(E36/100)*G36)/(1+(E36/100)*F36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="17">
+        <f>F36*H36</f>
+        <v/>
+      </c>
+      <c r="J36" s="17">
+        <f>-LN(H36)/C36*100</f>
+        <v/>
+      </c>
+      <c r="K36" s="17">
+        <f>(H35/H36-1)/((B36-B35)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L36" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35" t="n">
-        <v>28</v>
+      <c r="A37" s="17">
+        <f>'Bootstrap'!A37</f>
+        <v/>
       </c>
       <c r="B37" s="18">
-        <f>EDATE($F$7,3*27)</f>
+        <f>'Bootstrap'!B37</f>
         <v/>
       </c>
       <c r="C37" s="28">
-        <f>(B37-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D37" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B37,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E37" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B37,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C37</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>'Bootstrap'!D37</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>'Bootstrap'!E37</f>
         <v/>
       </c>
       <c r="F37" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1)))/((E37-D37)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G37" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1))*EXP(-(F37/100)*(B37-D37)/365)</f>
-        <v/>
-      </c>
-      <c r="H37" s="17">
-        <f>-LN(G37)/C37*100</f>
-        <v/>
-      </c>
-      <c r="K37" s="18">
-        <f>Bootstrap!B36</f>
-        <v/>
-      </c>
-      <c r="L37" s="33">
-        <f>Bootstrap!H36</f>
-        <v/>
+        <f>'Bootstrap'!F37</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>SUM($I$8:I36)</f>
+        <v/>
+      </c>
+      <c r="H37" s="29">
+        <f>(1-(E37/100)*G37)/(1+(E37/100)*F37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="17">
+        <f>F37*H37</f>
+        <v/>
+      </c>
+      <c r="J37" s="17">
+        <f>-LN(H37)/C37*100</f>
+        <v/>
+      </c>
+      <c r="K37" s="17">
+        <f>(H36/H37-1)/((B37-B36)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L37" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35" t="n">
-        <v>29</v>
+      <c r="A38" s="17">
+        <f>'Bootstrap'!A38</f>
+        <v/>
       </c>
       <c r="B38" s="18">
-        <f>EDATE($F$7,3*28)</f>
+        <f>'Bootstrap'!B38</f>
         <v/>
       </c>
       <c r="C38" s="28">
-        <f>(B38-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D38" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B38,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E38" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B38,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C38</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>'Bootstrap'!D38</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>'Bootstrap'!E38</f>
         <v/>
       </c>
       <c r="F38" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1)))/((E38-D38)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G38" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1))*EXP(-(F38/100)*(B38-D38)/365)</f>
-        <v/>
-      </c>
-      <c r="H38" s="17">
-        <f>-LN(G38)/C38*100</f>
-        <v/>
-      </c>
-      <c r="K38" s="18">
-        <f>Bootstrap!B37</f>
-        <v/>
-      </c>
-      <c r="L38" s="33">
-        <f>Bootstrap!H37</f>
-        <v/>
+        <f>'Bootstrap'!F38</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>SUM($I$8:I37)</f>
+        <v/>
+      </c>
+      <c r="H38" s="29">
+        <f>(1-(E38/100)*G38)/(1+(E38/100)*F38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="17">
+        <f>F38*H38</f>
+        <v/>
+      </c>
+      <c r="J38" s="17">
+        <f>-LN(H38)/C38*100</f>
+        <v/>
+      </c>
+      <c r="K38" s="17">
+        <f>(H37/H38-1)/((B38-B37)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L38" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35" t="n">
-        <v>30</v>
+      <c r="A39" s="17">
+        <f>'Bootstrap'!A39</f>
+        <v/>
       </c>
       <c r="B39" s="18">
-        <f>EDATE($F$7,3*29)</f>
+        <f>'Bootstrap'!B39</f>
         <v/>
       </c>
       <c r="C39" s="28">
-        <f>(B39-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D39" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B39,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E39" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B39,$K$8:$K$40,1)+1)</f>
+        <f>'Bootstrap'!C39</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>'Bootstrap'!D39</f>
+        <v/>
+      </c>
+      <c r="E39" s="17">
+        <f>'Bootstrap'!E39</f>
         <v/>
       </c>
       <c r="F39" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1)))/((E39-D39)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G39" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1))*EXP(-(F39/100)*(B39-D39)/365)</f>
-        <v/>
-      </c>
-      <c r="H39" s="17">
-        <f>-LN(G39)/C39*100</f>
-        <v/>
-      </c>
-      <c r="K39" s="18">
-        <f>Bootstrap!B38</f>
-        <v/>
-      </c>
-      <c r="L39" s="33">
-        <f>Bootstrap!H38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="35" t="n">
-        <v>31</v>
-      </c>
-      <c r="B40" s="18">
-        <f>EDATE($F$7,3*30)</f>
-        <v/>
-      </c>
-      <c r="C40" s="28">
-        <f>(B40-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D40" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B40,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E40" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B40,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F40" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1)))/((E40-D40)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G40" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1))*EXP(-(F40/100)*(B40-D40)/365)</f>
-        <v/>
-      </c>
-      <c r="H40" s="17">
-        <f>-LN(G40)/C40*100</f>
-        <v/>
-      </c>
-      <c r="K40" s="18">
-        <f>Bootstrap!B39</f>
-        <v/>
-      </c>
-      <c r="L40" s="33">
-        <f>Bootstrap!H39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="35" t="n">
-        <v>32</v>
-      </c>
-      <c r="B41" s="18">
-        <f>EDATE($F$7,3*31)</f>
-        <v/>
-      </c>
-      <c r="C41" s="28">
-        <f>(B41-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D41" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B41,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E41" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B41,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F41" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1)))/((E41-D41)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G41" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1))*EXP(-(F41/100)*(B41-D41)/365)</f>
-        <v/>
-      </c>
-      <c r="H41" s="17">
-        <f>-LN(G41)/C41*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="35" t="n">
-        <v>33</v>
-      </c>
-      <c r="B42" s="18">
-        <f>EDATE($F$7,3*32)</f>
-        <v/>
-      </c>
-      <c r="C42" s="28">
-        <f>(B42-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D42" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B42,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E42" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B42,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F42" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1)))/((E42-D42)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G42" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1))*EXP(-(F42/100)*(B42-D42)/365)</f>
-        <v/>
-      </c>
-      <c r="H42" s="17">
-        <f>-LN(G42)/C42*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="35" t="n">
-        <v>34</v>
-      </c>
-      <c r="B43" s="18">
-        <f>EDATE($F$7,3*33)</f>
-        <v/>
-      </c>
-      <c r="C43" s="28">
-        <f>(B43-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D43" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B43,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E43" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B43,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F43" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1)))/((E43-D43)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G43" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1))*EXP(-(F43/100)*(B43-D43)/365)</f>
-        <v/>
-      </c>
-      <c r="H43" s="17">
-        <f>-LN(G43)/C43*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="35" t="n">
-        <v>35</v>
-      </c>
-      <c r="B44" s="18">
-        <f>EDATE($F$7,3*34)</f>
-        <v/>
-      </c>
-      <c r="C44" s="28">
-        <f>(B44-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D44" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B44,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E44" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B44,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F44" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1)))/((E44-D44)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G44" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1))*EXP(-(F44/100)*(B44-D44)/365)</f>
-        <v/>
-      </c>
-      <c r="H44" s="17">
-        <f>-LN(G44)/C44*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="35" t="n">
-        <v>36</v>
-      </c>
-      <c r="B45" s="18">
-        <f>EDATE($F$7,3*35)</f>
-        <v/>
-      </c>
-      <c r="C45" s="28">
-        <f>(B45-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D45" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B45,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E45" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B45,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F45" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1)))/((E45-D45)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G45" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1))*EXP(-(F45/100)*(B45-D45)/365)</f>
-        <v/>
-      </c>
-      <c r="H45" s="17">
-        <f>-LN(G45)/C45*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="35" t="n">
-        <v>37</v>
-      </c>
-      <c r="B46" s="18">
-        <f>EDATE($F$7,3*36)</f>
-        <v/>
-      </c>
-      <c r="C46" s="28">
-        <f>(B46-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D46" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B46,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E46" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B46,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F46" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1)))/((E46-D46)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G46" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1))*EXP(-(F46/100)*(B46-D46)/365)</f>
-        <v/>
-      </c>
-      <c r="H46" s="17">
-        <f>-LN(G46)/C46*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="35" t="n">
-        <v>38</v>
-      </c>
-      <c r="B47" s="18">
-        <f>EDATE($F$7,3*37)</f>
-        <v/>
-      </c>
-      <c r="C47" s="28">
-        <f>(B47-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D47" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B47,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E47" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B47,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F47" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1)))/((E47-D47)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G47" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1))*EXP(-(F47/100)*(B47-D47)/365)</f>
-        <v/>
-      </c>
-      <c r="H47" s="17">
-        <f>-LN(G47)/C47*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="35" t="n">
-        <v>39</v>
-      </c>
-      <c r="B48" s="18">
-        <f>EDATE($F$7,3*38)</f>
-        <v/>
-      </c>
-      <c r="C48" s="28">
-        <f>(B48-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D48" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B48,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E48" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B48,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F48" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1)))/((E48-D48)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G48" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1))*EXP(-(F48/100)*(B48-D48)/365)</f>
-        <v/>
-      </c>
-      <c r="H48" s="17">
-        <f>-LN(G48)/C48*100</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="35" t="n">
-        <v>40</v>
-      </c>
-      <c r="B49" s="18">
-        <f>EDATE($F$7,3*39)</f>
-        <v/>
-      </c>
-      <c r="C49" s="28">
-        <f>(B49-VAL_DATE)/365</f>
-        <v/>
-      </c>
-      <c r="D49" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B49,$K$8:$K$40,1))</f>
-        <v/>
-      </c>
-      <c r="E49" s="18">
-        <f>INDEX($K$8:$K$40,MATCH(B49,$K$8:$K$40,1)+1)</f>
-        <v/>
-      </c>
-      <c r="F49" s="17">
-        <f>-LN(INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1)))/((E49-D49)/365)*100</f>
-        <v/>
-      </c>
-      <c r="G49" s="33">
-        <f>INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1))*EXP(-(F49/100)*(B49-D49)/365)</f>
-        <v/>
-      </c>
-      <c r="H49" s="17">
-        <f>-LN(G49)/C49*100</f>
-        <v/>
+        <f>'Bootstrap'!F39</f>
+        <v/>
+      </c>
+      <c r="G39" s="17">
+        <f>SUM($I$8:I38)</f>
+        <v/>
+      </c>
+      <c r="H39" s="29">
+        <f>(1-(E39/100)*G39)/(1+(E39/100)*F39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="17">
+        <f>F39*H39</f>
+        <v/>
+      </c>
+      <c r="J39" s="17">
+        <f>-LN(H39)/C39*100</f>
+        <v/>
+      </c>
+      <c r="K39" s="17">
+        <f>(H38/H39-1)/((B39-B38)/360)*100</f>
+        <v/>
+      </c>
+      <c r="L39" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="A4:H6"/>
+  <mergeCells count="1">
+    <mergeCell ref="A4:L6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15984,12 +16718,12 @@
           <t>Direction (Leg 1 = Fixed)</t>
         </is>
       </c>
-      <c r="B5" s="36" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Receive fixed</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
         </is>
@@ -16011,10 +16745,10 @@
           <t>Notional</t>
         </is>
       </c>
-      <c r="B6" s="38" t="n">
+      <c r="B6" s="36" t="n">
         <v>10000000</v>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>Both legs, USD.</t>
         </is>
@@ -16053,11 +16787,11 @@
           <t>Effective date</t>
         </is>
       </c>
-      <c r="B8" s="39">
+      <c r="B8" s="37">
         <f>Bootstrap!$B$4</f>
         <v/>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="C8" s="35" t="inlineStr">
         <is>
           <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
         </is>
@@ -16077,10 +16811,10 @@
           <t>Tenor (years)</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n">
+      <c r="B9" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="37" t="inlineStr">
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>Whole years; drives the annual coupon schedule below.</t>
         </is>
@@ -16104,7 +16838,7 @@
         <f>EDATE(B8,12*B9)</f>
         <v/>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="C10" s="35" t="inlineStr">
         <is>
           <t>Effective + Tenor.</t>
         </is>
@@ -16124,11 +16858,11 @@
           <t>Fixed coupon (%)</t>
         </is>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="39">
         <f>B25</f>
         <v/>
       </c>
-      <c r="C11" s="37" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
         </is>
@@ -16212,7 +16946,7 @@
         <f>VAL_DATE</f>
         <v/>
       </c>
-      <c r="C15" s="37" t="inlineStr">
+      <c r="C15" s="35" t="inlineStr">
         <is>
           <t>Curve is discounted from spot = Bootstrap!B4.</t>
         </is>
@@ -16232,7 +16966,7 @@
           <t>Direction sign (+recv / −pay)</t>
         </is>
       </c>
-      <c r="B16" s="35">
+      <c r="B16" s="40">
         <f>IF($B$5="Receive fixed",1,-1)</f>
         <v/>
       </c>
@@ -16280,7 +17014,7 @@
         <f>IFERROR(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))^(($B$8-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH($B$8,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH($B$8,$K$6:$K$38,1)))</f>
         <v/>
       </c>
-      <c r="C19" s="37" t="inlineStr">
+      <c r="C19" s="35" t="inlineStr">
         <is>
           <t>Interpolated from the curve.</t>
         </is>
@@ -16323,7 +17057,7 @@
         <f>SUM(H36:H85)</f>
         <v/>
       </c>
-      <c r="C21" s="37" t="inlineStr">
+      <c r="C21" s="35" t="inlineStr">
         <is>
           <t>Sum of tau·DF over the fixed coupon dates.</t>
         </is>
@@ -16343,7 +17077,7 @@
           <t>Fixed leg PV (coupons)</t>
         </is>
       </c>
-      <c r="B22" s="42">
+      <c r="B22" s="41">
         <f>SUM(G36:G85)</f>
         <v/>
       </c>
@@ -16362,11 +17096,11 @@
           <t>Float leg PV</t>
         </is>
       </c>
-      <c r="B23" s="42">
+      <c r="B23" s="41">
         <f>B6*(B19-B20)</f>
         <v/>
       </c>
-      <c r="C23" s="37" t="inlineStr">
+      <c r="C23" s="35" t="inlineStr">
         <is>
           <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
         </is>
@@ -16386,11 +17120,11 @@
           <t>Notional PV @ maturity</t>
         </is>
       </c>
-      <c r="B24" s="42">
+      <c r="B24" s="41">
         <f>B6*B20</f>
         <v/>
       </c>
-      <c r="C24" s="37" t="inlineStr">
+      <c r="C24" s="35" t="inlineStr">
         <is>
           <t>For the SWPM-style leg display only.</t>
         </is>
@@ -16414,7 +17148,7 @@
         <f>(B19-B20)/B21*100</f>
         <v/>
       </c>
-      <c r="C25" s="37" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
         </is>
@@ -16434,11 +17168,11 @@
           <t>Leg 1 NPV  (fixed + notional)</t>
         </is>
       </c>
-      <c r="B26" s="42">
+      <c r="B26" s="41">
         <f>B16*(B22+B24)</f>
         <v/>
       </c>
-      <c r="C26" s="37" t="inlineStr">
+      <c r="C26" s="35" t="inlineStr">
         <is>
           <t>SWPM shows each leg incl. a notional redemption.</t>
         </is>
@@ -16458,7 +17192,7 @@
           <t>Leg 2 NPV  (float + notional)</t>
         </is>
       </c>
-      <c r="B27" s="42">
+      <c r="B27" s="41">
         <f>-B16*(B23+B24)</f>
         <v/>
       </c>
@@ -16477,11 +17211,11 @@
           <t>Net swap NPV</t>
         </is>
       </c>
-      <c r="B28" s="43">
+      <c r="B28" s="42">
         <f>B26+B27</f>
         <v/>
       </c>
-      <c r="C28" s="37" t="inlineStr">
+      <c r="C28" s="35" t="inlineStr">
         <is>
           <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
         </is>
@@ -16501,11 +17235,11 @@
           <t>PV01 / DV01  (per 1bp)</t>
         </is>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="41">
         <f>B6*B21*0.0001</f>
         <v/>
       </c>
-      <c r="C29" s="37" t="inlineStr">
+      <c r="C29" s="35" t="inlineStr">
         <is>
           <t>Annuity × notional × 1bp.</t>
         </is>
@@ -16525,7 +17259,7 @@
           <t>Accrued (at inception)</t>
         </is>
       </c>
-      <c r="B30" s="42" t="n">
+      <c r="B30" s="41" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="18">
@@ -16633,7 +17367,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="35">
+      <c r="A36" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16653,11 +17387,11 @@
         <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1)))^((B36-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B36,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B36,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F36" s="42">
+      <c r="F36" s="41">
         <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
         <v/>
       </c>
-      <c r="G36" s="42">
+      <c r="G36" s="41">
         <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
         <v/>
       </c>
@@ -16675,7 +17409,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="35">
+      <c r="A37" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16695,11 +17429,11 @@
         <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1)))^((B37-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B37,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B37,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F37" s="42">
+      <c r="F37" s="41">
         <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
         <v/>
       </c>
-      <c r="G37" s="42">
+      <c r="G37" s="41">
         <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
         <v/>
       </c>
@@ -16717,7 +17451,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="35">
+      <c r="A38" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16737,11 +17471,11 @@
         <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1)))^((B38-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B38,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B38,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F38" s="42">
+      <c r="F38" s="41">
         <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
         <v/>
       </c>
-      <c r="G38" s="42">
+      <c r="G38" s="41">
         <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
         <v/>
       </c>
@@ -16759,7 +17493,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="35">
+      <c r="A39" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16779,11 +17513,11 @@
         <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1)))^((B39-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B39,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B39,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F39" s="42">
+      <c r="F39" s="41">
         <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
         <v/>
       </c>
-      <c r="G39" s="42">
+      <c r="G39" s="41">
         <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
         <v/>
       </c>
@@ -16798,7 +17532,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="35">
+      <c r="A40" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16818,11 +17552,11 @@
         <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1)))^((B40-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B40,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B40,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F40" s="42">
+      <c r="F40" s="41">
         <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
         <v/>
       </c>
-      <c r="G40" s="42">
+      <c r="G40" s="41">
         <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
         <v/>
       </c>
@@ -16832,7 +17566,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="35">
+      <c r="A41" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16852,11 +17586,11 @@
         <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1)))^((B41-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B41,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B41,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F41" s="42">
+      <c r="F41" s="41">
         <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
         <v/>
       </c>
-      <c r="G41" s="42">
+      <c r="G41" s="41">
         <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
         <v/>
       </c>
@@ -16866,7 +17600,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="35">
+      <c r="A42" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16886,11 +17620,11 @@
         <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1)))^((B42-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B42,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B42,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F42" s="42">
+      <c r="F42" s="41">
         <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
         <v/>
       </c>
-      <c r="G42" s="42">
+      <c r="G42" s="41">
         <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
         <v/>
       </c>
@@ -16900,7 +17634,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="35">
+      <c r="A43" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16920,11 +17654,11 @@
         <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1)))^((B43-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B43,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B43,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F43" s="42">
+      <c r="F43" s="41">
         <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
         <v/>
       </c>
-      <c r="G43" s="42">
+      <c r="G43" s="41">
         <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
         <v/>
       </c>
@@ -16934,7 +17668,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="35">
+      <c r="A44" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16954,11 +17688,11 @@
         <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1)))^((B44-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B44,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B44,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F44" s="42">
+      <c r="F44" s="41">
         <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
         <v/>
       </c>
-      <c r="G44" s="42">
+      <c r="G44" s="41">
         <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
         <v/>
       </c>
@@ -16968,7 +17702,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="35">
+      <c r="A45" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -16988,11 +17722,11 @@
         <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1)))^((B45-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B45,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B45,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F45" s="42">
+      <c r="F45" s="41">
         <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
         <v/>
       </c>
-      <c r="G45" s="42">
+      <c r="G45" s="41">
         <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
         <v/>
       </c>
@@ -17002,7 +17736,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="35">
+      <c r="A46" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17022,11 +17756,11 @@
         <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1)))^((B46-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B46,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B46,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F46" s="42">
+      <c r="F46" s="41">
         <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
         <v/>
       </c>
-      <c r="G46" s="42">
+      <c r="G46" s="41">
         <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
         <v/>
       </c>
@@ -17036,7 +17770,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="35">
+      <c r="A47" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17056,11 +17790,11 @@
         <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1)))^((B47-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B47,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B47,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F47" s="42">
+      <c r="F47" s="41">
         <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
         <v/>
       </c>
-      <c r="G47" s="42">
+      <c r="G47" s="41">
         <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
         <v/>
       </c>
@@ -17070,7 +17804,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="35">
+      <c r="A48" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17090,11 +17824,11 @@
         <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1)))^((B48-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B48,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B48,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F48" s="42">
+      <c r="F48" s="41">
         <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
         <v/>
       </c>
-      <c r="G48" s="42">
+      <c r="G48" s="41">
         <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
         <v/>
       </c>
@@ -17104,7 +17838,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="35">
+      <c r="A49" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17124,11 +17858,11 @@
         <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1)))^((B49-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B49,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B49,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="42">
+      <c r="F49" s="41">
         <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
         <v/>
       </c>
-      <c r="G49" s="42">
+      <c r="G49" s="41">
         <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
         <v/>
       </c>
@@ -17138,7 +17872,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="35">
+      <c r="A50" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17158,11 +17892,11 @@
         <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1)))^((B50-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B50,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B50,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F50" s="42">
+      <c r="F50" s="41">
         <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
         <v/>
       </c>
-      <c r="G50" s="42">
+      <c r="G50" s="41">
         <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
         <v/>
       </c>
@@ -17172,7 +17906,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="35">
+      <c r="A51" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17192,11 +17926,11 @@
         <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1)))^((B51-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B51,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B51,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F51" s="42">
+      <c r="F51" s="41">
         <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
         <v/>
       </c>
-      <c r="G51" s="42">
+      <c r="G51" s="41">
         <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
         <v/>
       </c>
@@ -17206,7 +17940,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="35">
+      <c r="A52" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17226,11 +17960,11 @@
         <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1)))^((B52-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B52,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B52,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F52" s="42">
+      <c r="F52" s="41">
         <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
         <v/>
       </c>
-      <c r="G52" s="42">
+      <c r="G52" s="41">
         <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
         <v/>
       </c>
@@ -17240,7 +17974,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="35">
+      <c r="A53" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17260,11 +17994,11 @@
         <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1)))^((B53-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B53,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B53,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F53" s="42">
+      <c r="F53" s="41">
         <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
         <v/>
       </c>
-      <c r="G53" s="42">
+      <c r="G53" s="41">
         <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
         <v/>
       </c>
@@ -17274,7 +18008,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="35">
+      <c r="A54" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17294,11 +18028,11 @@
         <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1)))^((B54-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B54,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B54,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F54" s="42">
+      <c r="F54" s="41">
         <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
         <v/>
       </c>
-      <c r="G54" s="42">
+      <c r="G54" s="41">
         <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
         <v/>
       </c>
@@ -17308,7 +18042,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="35">
+      <c r="A55" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17328,11 +18062,11 @@
         <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1)))^((B55-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B55,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B55,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F55" s="42">
+      <c r="F55" s="41">
         <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
         <v/>
       </c>
-      <c r="G55" s="42">
+      <c r="G55" s="41">
         <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
         <v/>
       </c>
@@ -17342,7 +18076,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="35">
+      <c r="A56" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17362,11 +18096,11 @@
         <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1)))^((B56-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B56,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B56,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F56" s="42">
+      <c r="F56" s="41">
         <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
         <v/>
       </c>
-      <c r="G56" s="42">
+      <c r="G56" s="41">
         <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
         <v/>
       </c>
@@ -17376,7 +18110,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="35">
+      <c r="A57" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17396,11 +18130,11 @@
         <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1)))^((B57-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B57,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B57,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F57" s="42">
+      <c r="F57" s="41">
         <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
         <v/>
       </c>
-      <c r="G57" s="42">
+      <c r="G57" s="41">
         <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
         <v/>
       </c>
@@ -17410,7 +18144,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="35">
+      <c r="A58" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17430,11 +18164,11 @@
         <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1)))^((B58-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B58,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B58,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F58" s="42">
+      <c r="F58" s="41">
         <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
         <v/>
       </c>
-      <c r="G58" s="42">
+      <c r="G58" s="41">
         <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
         <v/>
       </c>
@@ -17444,7 +18178,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="35">
+      <c r="A59" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17464,11 +18198,11 @@
         <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1)))^((B59-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B59,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B59,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F59" s="42">
+      <c r="F59" s="41">
         <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
         <v/>
       </c>
-      <c r="G59" s="42">
+      <c r="G59" s="41">
         <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
         <v/>
       </c>
@@ -17478,7 +18212,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="35">
+      <c r="A60" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17498,11 +18232,11 @@
         <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1)))^((B60-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B60,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B60,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F60" s="42">
+      <c r="F60" s="41">
         <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
         <v/>
       </c>
-      <c r="G60" s="42">
+      <c r="G60" s="41">
         <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
         <v/>
       </c>
@@ -17512,7 +18246,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="35">
+      <c r="A61" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17532,11 +18266,11 @@
         <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1)))^((B61-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B61,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B61,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F61" s="42">
+      <c r="F61" s="41">
         <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
         <v/>
       </c>
-      <c r="G61" s="42">
+      <c r="G61" s="41">
         <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
         <v/>
       </c>
@@ -17546,7 +18280,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="35">
+      <c r="A62" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17566,11 +18300,11 @@
         <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1)))^((B62-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B62,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B62,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F62" s="42">
+      <c r="F62" s="41">
         <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
         <v/>
       </c>
-      <c r="G62" s="42">
+      <c r="G62" s="41">
         <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
         <v/>
       </c>
@@ -17580,7 +18314,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="35">
+      <c r="A63" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17600,11 +18334,11 @@
         <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1)))^((B63-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B63,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B63,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F63" s="42">
+      <c r="F63" s="41">
         <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
         <v/>
       </c>
-      <c r="G63" s="42">
+      <c r="G63" s="41">
         <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
         <v/>
       </c>
@@ -17614,7 +18348,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="35">
+      <c r="A64" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17634,11 +18368,11 @@
         <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1)))^((B64-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B64,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B64,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F64" s="42">
+      <c r="F64" s="41">
         <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
         <v/>
       </c>
-      <c r="G64" s="42">
+      <c r="G64" s="41">
         <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
         <v/>
       </c>
@@ -17648,7 +18382,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="35">
+      <c r="A65" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17668,11 +18402,11 @@
         <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1)))^((B65-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B65,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B65,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F65" s="42">
+      <c r="F65" s="41">
         <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
         <v/>
       </c>
-      <c r="G65" s="42">
+      <c r="G65" s="41">
         <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
         <v/>
       </c>
@@ -17682,7 +18416,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="35">
+      <c r="A66" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17702,11 +18436,11 @@
         <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1)))^((B66-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B66,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B66,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F66" s="42">
+      <c r="F66" s="41">
         <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
         <v/>
       </c>
-      <c r="G66" s="42">
+      <c r="G66" s="41">
         <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
         <v/>
       </c>
@@ -17716,7 +18450,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="35">
+      <c r="A67" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17736,11 +18470,11 @@
         <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1)))^((B67-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B67,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B67,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F67" s="42">
+      <c r="F67" s="41">
         <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
         <v/>
       </c>
-      <c r="G67" s="42">
+      <c r="G67" s="41">
         <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
         <v/>
       </c>
@@ -17750,7 +18484,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="35">
+      <c r="A68" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17770,11 +18504,11 @@
         <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1)))^((B68-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B68,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B68,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F68" s="42">
+      <c r="F68" s="41">
         <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
         <v/>
       </c>
-      <c r="G68" s="42">
+      <c r="G68" s="41">
         <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
         <v/>
       </c>
@@ -17784,7 +18518,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="35">
+      <c r="A69" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17804,11 +18538,11 @@
         <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1)))^((B69-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B69,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B69,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F69" s="42">
+      <c r="F69" s="41">
         <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
         <v/>
       </c>
-      <c r="G69" s="42">
+      <c r="G69" s="41">
         <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
         <v/>
       </c>
@@ -17818,7 +18552,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="35">
+      <c r="A70" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17838,11 +18572,11 @@
         <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1)))^((B70-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B70,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B70,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F70" s="42">
+      <c r="F70" s="41">
         <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
         <v/>
       </c>
-      <c r="G70" s="42">
+      <c r="G70" s="41">
         <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
         <v/>
       </c>
@@ -17852,7 +18586,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="35">
+      <c r="A71" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17872,11 +18606,11 @@
         <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1)))^((B71-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B71,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B71,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F71" s="42">
+      <c r="F71" s="41">
         <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
         <v/>
       </c>
-      <c r="G71" s="42">
+      <c r="G71" s="41">
         <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
         <v/>
       </c>
@@ -17886,7 +18620,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="35">
+      <c r="A72" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17906,11 +18640,11 @@
         <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1)))^((B72-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B72,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B72,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F72" s="42">
+      <c r="F72" s="41">
         <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
         <v/>
       </c>
-      <c r="G72" s="42">
+      <c r="G72" s="41">
         <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
         <v/>
       </c>
@@ -17920,7 +18654,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="35">
+      <c r="A73" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17940,11 +18674,11 @@
         <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1)))^((B73-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B73,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B73,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F73" s="42">
+      <c r="F73" s="41">
         <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
         <v/>
       </c>
-      <c r="G73" s="42">
+      <c r="G73" s="41">
         <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
         <v/>
       </c>
@@ -17954,7 +18688,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="35">
+      <c r="A74" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -17974,11 +18708,11 @@
         <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1)))^((B74-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B74,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B74,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F74" s="42">
+      <c r="F74" s="41">
         <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
         <v/>
       </c>
-      <c r="G74" s="42">
+      <c r="G74" s="41">
         <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
         <v/>
       </c>
@@ -17988,7 +18722,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="35">
+      <c r="A75" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18008,11 +18742,11 @@
         <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1)))^((B75-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B75,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B75,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F75" s="42">
+      <c r="F75" s="41">
         <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
         <v/>
       </c>
-      <c r="G75" s="42">
+      <c r="G75" s="41">
         <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
         <v/>
       </c>
@@ -18022,7 +18756,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="35">
+      <c r="A76" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18042,11 +18776,11 @@
         <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1)))^((B76-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B76,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B76,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F76" s="42">
+      <c r="F76" s="41">
         <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
         <v/>
       </c>
-      <c r="G76" s="42">
+      <c r="G76" s="41">
         <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
         <v/>
       </c>
@@ -18056,7 +18790,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="35">
+      <c r="A77" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18076,11 +18810,11 @@
         <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1)))^((B77-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B77,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B77,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F77" s="42">
+      <c r="F77" s="41">
         <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
         <v/>
       </c>
-      <c r="G77" s="42">
+      <c r="G77" s="41">
         <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
         <v/>
       </c>
@@ -18090,7 +18824,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="35">
+      <c r="A78" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18110,11 +18844,11 @@
         <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1)))^((B78-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B78,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B78,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F78" s="42">
+      <c r="F78" s="41">
         <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
         <v/>
       </c>
-      <c r="G78" s="42">
+      <c r="G78" s="41">
         <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
         <v/>
       </c>
@@ -18124,7 +18858,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="35">
+      <c r="A79" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18144,11 +18878,11 @@
         <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1)))^((B79-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B79,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B79,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F79" s="42">
+      <c r="F79" s="41">
         <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
         <v/>
       </c>
-      <c r="G79" s="42">
+      <c r="G79" s="41">
         <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
         <v/>
       </c>
@@ -18158,7 +18892,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="35">
+      <c r="A80" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18178,11 +18912,11 @@
         <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1)))^((B80-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B80,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B80,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F80" s="42">
+      <c r="F80" s="41">
         <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
         <v/>
       </c>
-      <c r="G80" s="42">
+      <c r="G80" s="41">
         <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
         <v/>
       </c>
@@ -18192,7 +18926,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="35">
+      <c r="A81" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18212,11 +18946,11 @@
         <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1)))^((B81-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B81,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B81,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F81" s="42">
+      <c r="F81" s="41">
         <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
         <v/>
       </c>
-      <c r="G81" s="42">
+      <c r="G81" s="41">
         <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
         <v/>
       </c>
@@ -18226,7 +18960,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="35">
+      <c r="A82" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18246,11 +18980,11 @@
         <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1)))^((B82-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B82,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B82,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F82" s="42">
+      <c r="F82" s="41">
         <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
         <v/>
       </c>
-      <c r="G82" s="42">
+      <c r="G82" s="41">
         <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
         <v/>
       </c>
@@ -18260,7 +18994,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="35">
+      <c r="A83" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18280,11 +19014,11 @@
         <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1)))^((B83-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B83,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B83,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F83" s="42">
+      <c r="F83" s="41">
         <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
         <v/>
       </c>
-      <c r="G83" s="42">
+      <c r="G83" s="41">
         <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
         <v/>
       </c>
@@ -18294,7 +19028,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="35">
+      <c r="A84" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18314,11 +19048,11 @@
         <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1)))^((B84-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B84,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B84,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F84" s="42">
+      <c r="F84" s="41">
         <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
         <v/>
       </c>
-      <c r="G84" s="42">
+      <c r="G84" s="41">
         <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
         <v/>
       </c>
@@ -18328,7 +19062,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="35">
+      <c r="A85" s="40">
         <f>ROW()-35</f>
         <v/>
       </c>
@@ -18348,11 +19082,11 @@
         <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))*(INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)+1)/INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1)))^((B85-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))/(INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)+1)-INDEX($K$6:$K$38,MATCH(B85,$K$6:$K$38,1)))),INDEX($L$6:$L$38,MATCH(B85,$K$6:$K$38,1))),"")</f>
         <v/>
       </c>
-      <c r="F85" s="42">
+      <c r="F85" s="41">
         <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
         <v/>
       </c>
-      <c r="G85" s="42">
+      <c r="G85" s="41">
         <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
         <v/>
       </c>
@@ -18394,708 +19128,1720 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bloomberg_S490_Validation</t>
+          <t>Curve_Interface</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Bloomberg's own USD SOFR curve (S490 / YCSW0490 Index) — benchmark for your bootstrap, not an input</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>Curve name:</t>
-        </is>
-      </c>
-      <c r="B4" s="19">
-        <f>IFERROR(BDP(S490_TKR,"NAME"),"ERROR PLZ FIX")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Curve date:</t>
-        </is>
-      </c>
-      <c r="B5" s="44">
+          <t>Shared discounting D(0,t): interpolates the SOFR Bootstrap curve to ANY date (piecewise-flat forward). One function used by both Swap_Pricer and the CDS module.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Piecewise-flat instantaneous-forward interpolation — the SOFR curve's own baseline method. For t in (T_prev, T_next]: f = −ln(D_next/D_prev)/(T_next−T_prev), then D(0,t) = D_prev·exp(−f·(t−T_prev)). The demo rows are the STANDARD quarterly CDS dates (20 Mar/Jun/Sep/Dec) out to 10Y — proving the curve returns a discount factor on every CDS payment date even though those dates don't coincide with the SOFR pillars. A CDS schedule just references this same formula, so any change to fixings/futures/OIS/interpolation flows straight through. Curve grid (spot + Bootstrap pillars) is in cols K:L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Curve grid (from Bootstrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Valuation:</t>
+        </is>
+      </c>
+      <c r="B7" s="43">
         <f>VAL_DATE</f>
         <v/>
       </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Paste Bloomberg's S490 zero rates (from YCSW0490 &lt;GO&gt; or SWDF) into the yellow column D, tenor for tenor; column E then shows Δz = your bootstrap − Bloomberg in bp (single digits = agreement). The raw BDS(CURVE_TENOR_RATES) dump is off to the right (cols H:I) as an optional live pull — its column order is Bloomberg-defined, so verify before relying on it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>Tenor</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>Maturity</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>Your zero (%)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>S490 zero (%) [paste]</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>Δz (bp)</t>
-        </is>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Raw CURVE_TENOR_RATES (verify order)</t>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>Spot:</t>
+        </is>
+      </c>
+      <c r="D7" s="43">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>1st CDS date:</t>
+        </is>
+      </c>
+      <c r="F7" s="43">
+        <f>IF(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20)&gt;=VAL_DATE,DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),EDATE(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),3))</f>
+        <v/>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>DF</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6">
-        <f>Bootstrap!A8</f>
-        <v/>
-      </c>
-      <c r="B8" s="18">
+      <c r="K8" s="18">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="L8" s="33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>Coupon #</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Time from val (yrs)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>Prev SOFR pillar</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>Next SOFR pillar</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>Segment fwd (%)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>Interp DF  D(0,t)</t>
+        </is>
+      </c>
+      <c r="H9" s="20" t="inlineStr">
+        <is>
+          <t>Interp zero (%)</t>
+        </is>
+      </c>
+      <c r="K9" s="18">
         <f>Bootstrap!B8</f>
         <v/>
       </c>
-      <c r="C8" s="17">
-        <f>Bootstrap!J8</f>
-        <v/>
-      </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31">
-        <f>IF(D8="","",(C8-D8)*100)</f>
-        <v/>
-      </c>
-      <c r="H8">
-        <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="6">
-        <f>Bootstrap!A9</f>
-        <v/>
-      </c>
-      <c r="B9" s="18">
+      <c r="L9" s="33">
+        <f>Bootstrap!H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="18">
+        <f>EDATE($F$7,3*0)</f>
+        <v/>
+      </c>
+      <c r="C10" s="28">
+        <f>(B10-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D10" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B10,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E10" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B10,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1)))/((E10-D10)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G10" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B10,$K$8:$K$40,1))*EXP(-(F10/100)*(B10-D10)/365)</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>-LN(G10)/C10*100</f>
+        <v/>
+      </c>
+      <c r="K10" s="18">
         <f>Bootstrap!B9</f>
         <v/>
       </c>
-      <c r="C9" s="17">
-        <f>Bootstrap!J9</f>
-        <v/>
-      </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31">
-        <f>IF(D9="","",(C9-D9)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6">
-        <f>Bootstrap!A10</f>
-        <v/>
-      </c>
-      <c r="B10" s="18">
+      <c r="L10" s="33">
+        <f>Bootstrap!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" s="18">
+        <f>EDATE($F$7,3*1)</f>
+        <v/>
+      </c>
+      <c r="C11" s="28">
+        <f>(B11-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D11" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B11,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E11" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B11,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F11" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1)))/((E11-D11)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G11" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B11,$K$8:$K$40,1))*EXP(-(F11/100)*(B11-D11)/365)</f>
+        <v/>
+      </c>
+      <c r="H11" s="17">
+        <f>-LN(G11)/C11*100</f>
+        <v/>
+      </c>
+      <c r="K11" s="18">
         <f>Bootstrap!B10</f>
         <v/>
       </c>
-      <c r="C10" s="17">
-        <f>Bootstrap!J10</f>
-        <v/>
-      </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="31">
-        <f>IF(D10="","",(C10-D10)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6">
-        <f>Bootstrap!A11</f>
-        <v/>
-      </c>
-      <c r="B11" s="18">
+      <c r="L11" s="33">
+        <f>Bootstrap!H10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="40" t="n">
+        <v>3</v>
+      </c>
+      <c r="B12" s="18">
+        <f>EDATE($F$7,3*2)</f>
+        <v/>
+      </c>
+      <c r="C12" s="28">
+        <f>(B12-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D12" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B12,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E12" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B12,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1)))/((E12-D12)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G12" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B12,$K$8:$K$40,1))*EXP(-(F12/100)*(B12-D12)/365)</f>
+        <v/>
+      </c>
+      <c r="H12" s="17">
+        <f>-LN(G12)/C12*100</f>
+        <v/>
+      </c>
+      <c r="K12" s="18">
         <f>Bootstrap!B11</f>
         <v/>
       </c>
-      <c r="C11" s="17">
-        <f>Bootstrap!J11</f>
-        <v/>
-      </c>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31">
-        <f>IF(D11="","",(C11-D11)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6">
-        <f>Bootstrap!A12</f>
-        <v/>
-      </c>
-      <c r="B12" s="18">
+      <c r="L12" s="33">
+        <f>Bootstrap!H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="40" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" s="18">
+        <f>EDATE($F$7,3*3)</f>
+        <v/>
+      </c>
+      <c r="C13" s="28">
+        <f>(B13-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D13" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B13,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E13" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B13,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1)))/((E13-D13)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G13" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B13,$K$8:$K$40,1))*EXP(-(F13/100)*(B13-D13)/365)</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>-LN(G13)/C13*100</f>
+        <v/>
+      </c>
+      <c r="K13" s="18">
         <f>Bootstrap!B12</f>
         <v/>
       </c>
-      <c r="C12" s="17">
-        <f>Bootstrap!J12</f>
-        <v/>
-      </c>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="31">
-        <f>IF(D12="","",(C12-D12)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6">
-        <f>Bootstrap!A13</f>
-        <v/>
-      </c>
-      <c r="B13" s="18">
+      <c r="L13" s="33">
+        <f>Bootstrap!H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="18">
+        <f>EDATE($F$7,3*4)</f>
+        <v/>
+      </c>
+      <c r="C14" s="28">
+        <f>(B14-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B14,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B14,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1)))/((E14-D14)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B14,$K$8:$K$40,1))*EXP(-(F14/100)*(B14-D14)/365)</f>
+        <v/>
+      </c>
+      <c r="H14" s="17">
+        <f>-LN(G14)/C14*100</f>
+        <v/>
+      </c>
+      <c r="K14" s="18">
         <f>Bootstrap!B13</f>
         <v/>
       </c>
-      <c r="C13" s="17">
-        <f>Bootstrap!J13</f>
-        <v/>
-      </c>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="31">
-        <f>IF(D13="","",(C13-D13)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6">
-        <f>Bootstrap!A14</f>
-        <v/>
-      </c>
-      <c r="B14" s="18">
+      <c r="L14" s="33">
+        <f>Bootstrap!H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" s="18">
+        <f>EDATE($F$7,3*5)</f>
+        <v/>
+      </c>
+      <c r="C15" s="28">
+        <f>(B15-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D15" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B15,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E15" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B15,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1)))/((E15-D15)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G15" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B15,$K$8:$K$40,1))*EXP(-(F15/100)*(B15-D15)/365)</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>-LN(G15)/C15*100</f>
+        <v/>
+      </c>
+      <c r="K15" s="18">
         <f>Bootstrap!B14</f>
         <v/>
       </c>
-      <c r="C14" s="17">
-        <f>Bootstrap!J14</f>
-        <v/>
-      </c>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="31">
-        <f>IF(D14="","",(C14-D14)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6">
-        <f>Bootstrap!A15</f>
-        <v/>
-      </c>
-      <c r="B15" s="18">
+      <c r="L15" s="33">
+        <f>Bootstrap!H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="n">
+        <v>7</v>
+      </c>
+      <c r="B16" s="18">
+        <f>EDATE($F$7,3*6)</f>
+        <v/>
+      </c>
+      <c r="C16" s="28">
+        <f>(B16-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B16,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B16,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1)))/((E16-D16)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G16" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B16,$K$8:$K$40,1))*EXP(-(F16/100)*(B16-D16)/365)</f>
+        <v/>
+      </c>
+      <c r="H16" s="17">
+        <f>-LN(G16)/C16*100</f>
+        <v/>
+      </c>
+      <c r="K16" s="18">
         <f>Bootstrap!B15</f>
         <v/>
       </c>
-      <c r="C15" s="17">
-        <f>Bootstrap!J15</f>
-        <v/>
-      </c>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="31">
-        <f>IF(D15="","",(C15-D15)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6">
-        <f>Bootstrap!A16</f>
-        <v/>
-      </c>
-      <c r="B16" s="18">
+      <c r="L16" s="33">
+        <f>Bootstrap!H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="40" t="n">
+        <v>8</v>
+      </c>
+      <c r="B17" s="18">
+        <f>EDATE($F$7,3*7)</f>
+        <v/>
+      </c>
+      <c r="C17" s="28">
+        <f>(B17-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D17" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B17,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E17" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B17,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F17" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1)))/((E17-D17)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G17" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B17,$K$8:$K$40,1))*EXP(-(F17/100)*(B17-D17)/365)</f>
+        <v/>
+      </c>
+      <c r="H17" s="17">
+        <f>-LN(G17)/C17*100</f>
+        <v/>
+      </c>
+      <c r="K17" s="18">
         <f>Bootstrap!B16</f>
         <v/>
       </c>
-      <c r="C16" s="17">
-        <f>Bootstrap!J16</f>
-        <v/>
-      </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="31">
-        <f>IF(D16="","",(C16-D16)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6">
-        <f>Bootstrap!A17</f>
-        <v/>
-      </c>
-      <c r="B17" s="18">
+      <c r="L17" s="33">
+        <f>Bootstrap!H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="18">
+        <f>EDATE($F$7,3*8)</f>
+        <v/>
+      </c>
+      <c r="C18" s="28">
+        <f>(B18-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B18,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E18" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B18,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F18" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1)))/((E18-D18)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G18" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B18,$K$8:$K$40,1))*EXP(-(F18/100)*(B18-D18)/365)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>-LN(G18)/C18*100</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
         <f>Bootstrap!B17</f>
         <v/>
       </c>
-      <c r="C17" s="17">
-        <f>Bootstrap!J17</f>
-        <v/>
-      </c>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="31">
-        <f>IF(D17="","",(C17-D17)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6">
-        <f>Bootstrap!A18</f>
-        <v/>
-      </c>
-      <c r="B18" s="18">
+      <c r="L18" s="33">
+        <f>Bootstrap!H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="40" t="n">
+        <v>10</v>
+      </c>
+      <c r="B19" s="18">
+        <f>EDATE($F$7,3*9)</f>
+        <v/>
+      </c>
+      <c r="C19" s="28">
+        <f>(B19-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D19" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B19,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E19" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B19,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F19" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1)))/((E19-D19)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G19" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B19,$K$8:$K$40,1))*EXP(-(F19/100)*(B19-D19)/365)</f>
+        <v/>
+      </c>
+      <c r="H19" s="17">
+        <f>-LN(G19)/C19*100</f>
+        <v/>
+      </c>
+      <c r="K19" s="18">
         <f>Bootstrap!B18</f>
         <v/>
       </c>
-      <c r="C18" s="17">
-        <f>Bootstrap!J18</f>
-        <v/>
-      </c>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="31">
-        <f>IF(D18="","",(C18-D18)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6">
-        <f>Bootstrap!A19</f>
-        <v/>
-      </c>
-      <c r="B19" s="18">
+      <c r="L19" s="33">
+        <f>Bootstrap!H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="40" t="n">
+        <v>11</v>
+      </c>
+      <c r="B20" s="18">
+        <f>EDATE($F$7,3*10)</f>
+        <v/>
+      </c>
+      <c r="C20" s="28">
+        <f>(B20-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D20" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B20,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E20" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B20,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1)))/((E20-D20)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G20" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B20,$K$8:$K$40,1))*EXP(-(F20/100)*(B20-D20)/365)</f>
+        <v/>
+      </c>
+      <c r="H20" s="17">
+        <f>-LN(G20)/C20*100</f>
+        <v/>
+      </c>
+      <c r="K20" s="18">
         <f>Bootstrap!B19</f>
         <v/>
       </c>
-      <c r="C19" s="17">
-        <f>Bootstrap!J19</f>
-        <v/>
-      </c>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="31">
-        <f>IF(D19="","",(C19-D19)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6">
-        <f>Bootstrap!A20</f>
-        <v/>
-      </c>
-      <c r="B20" s="18">
+      <c r="L20" s="33">
+        <f>Bootstrap!H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="40" t="n">
+        <v>12</v>
+      </c>
+      <c r="B21" s="18">
+        <f>EDATE($F$7,3*11)</f>
+        <v/>
+      </c>
+      <c r="C21" s="28">
+        <f>(B21-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D21" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B21,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E21" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B21,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1)))/((E21-D21)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G21" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B21,$K$8:$K$40,1))*EXP(-(F21/100)*(B21-D21)/365)</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
+        <f>-LN(G21)/C21*100</f>
+        <v/>
+      </c>
+      <c r="K21" s="18">
         <f>Bootstrap!B20</f>
         <v/>
       </c>
-      <c r="C20" s="17">
-        <f>Bootstrap!J20</f>
-        <v/>
-      </c>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="31">
-        <f>IF(D20="","",(C20-D20)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6">
-        <f>Bootstrap!A21</f>
-        <v/>
-      </c>
-      <c r="B21" s="18">
+      <c r="L21" s="33">
+        <f>Bootstrap!H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B22" s="18">
+        <f>EDATE($F$7,3*12)</f>
+        <v/>
+      </c>
+      <c r="C22" s="28">
+        <f>(B22-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D22" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B22,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E22" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B22,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F22" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1)))/((E22-D22)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G22" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B22,$K$8:$K$40,1))*EXP(-(F22/100)*(B22-D22)/365)</f>
+        <v/>
+      </c>
+      <c r="H22" s="17">
+        <f>-LN(G22)/C22*100</f>
+        <v/>
+      </c>
+      <c r="K22" s="18">
         <f>Bootstrap!B21</f>
         <v/>
       </c>
-      <c r="C21" s="17">
-        <f>Bootstrap!J21</f>
-        <v/>
-      </c>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="31">
-        <f>IF(D21="","",(C21-D21)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6">
-        <f>Bootstrap!A22</f>
-        <v/>
-      </c>
-      <c r="B22" s="18">
+      <c r="L22" s="33">
+        <f>Bootstrap!H21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="n">
+        <v>14</v>
+      </c>
+      <c r="B23" s="18">
+        <f>EDATE($F$7,3*13)</f>
+        <v/>
+      </c>
+      <c r="C23" s="28">
+        <f>(B23-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D23" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B23,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E23" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B23,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1)))/((E23-D23)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G23" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B23,$K$8:$K$40,1))*EXP(-(F23/100)*(B23-D23)/365)</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>-LN(G23)/C23*100</f>
+        <v/>
+      </c>
+      <c r="K23" s="18">
         <f>Bootstrap!B22</f>
         <v/>
       </c>
-      <c r="C22" s="17">
-        <f>Bootstrap!J22</f>
-        <v/>
-      </c>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="31">
-        <f>IF(D22="","",(C22-D22)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6">
-        <f>Bootstrap!A23</f>
-        <v/>
-      </c>
-      <c r="B23" s="18">
+      <c r="L23" s="33">
+        <f>Bootstrap!H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="40" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="18">
+        <f>EDATE($F$7,3*14)</f>
+        <v/>
+      </c>
+      <c r="C24" s="28">
+        <f>(B24-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D24" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B24,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E24" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B24,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F24" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1)))/((E24-D24)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G24" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B24,$K$8:$K$40,1))*EXP(-(F24/100)*(B24-D24)/365)</f>
+        <v/>
+      </c>
+      <c r="H24" s="17">
+        <f>-LN(G24)/C24*100</f>
+        <v/>
+      </c>
+      <c r="K24" s="18">
         <f>Bootstrap!B23</f>
         <v/>
       </c>
-      <c r="C23" s="17">
-        <f>Bootstrap!J23</f>
-        <v/>
-      </c>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="31">
-        <f>IF(D23="","",(C23-D23)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6">
-        <f>Bootstrap!A24</f>
-        <v/>
-      </c>
-      <c r="B24" s="18">
+      <c r="L24" s="33">
+        <f>Bootstrap!H23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="40" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="18">
+        <f>EDATE($F$7,3*15)</f>
+        <v/>
+      </c>
+      <c r="C25" s="28">
+        <f>(B25-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D25" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B25,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E25" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B25,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F25" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1)))/((E25-D25)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G25" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B25,$K$8:$K$40,1))*EXP(-(F25/100)*(B25-D25)/365)</f>
+        <v/>
+      </c>
+      <c r="H25" s="17">
+        <f>-LN(G25)/C25*100</f>
+        <v/>
+      </c>
+      <c r="K25" s="18">
         <f>Bootstrap!B24</f>
         <v/>
       </c>
-      <c r="C24" s="17">
-        <f>Bootstrap!J24</f>
-        <v/>
-      </c>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="31">
-        <f>IF(D24="","",(C24-D24)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6">
-        <f>Bootstrap!A25</f>
-        <v/>
-      </c>
-      <c r="B25" s="18">
+      <c r="L25" s="33">
+        <f>Bootstrap!H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="18">
+        <f>EDATE($F$7,3*16)</f>
+        <v/>
+      </c>
+      <c r="C26" s="28">
+        <f>(B26-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D26" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B26,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E26" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B26,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F26" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1)))/((E26-D26)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G26" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B26,$K$8:$K$40,1))*EXP(-(F26/100)*(B26-D26)/365)</f>
+        <v/>
+      </c>
+      <c r="H26" s="17">
+        <f>-LN(G26)/C26*100</f>
+        <v/>
+      </c>
+      <c r="K26" s="18">
         <f>Bootstrap!B25</f>
         <v/>
       </c>
-      <c r="C25" s="17">
-        <f>Bootstrap!J25</f>
-        <v/>
-      </c>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="31">
-        <f>IF(D25="","",(C25-D25)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6">
-        <f>Bootstrap!A26</f>
-        <v/>
-      </c>
-      <c r="B26" s="18">
+      <c r="L26" s="33">
+        <f>Bootstrap!H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="40" t="n">
+        <v>18</v>
+      </c>
+      <c r="B27" s="18">
+        <f>EDATE($F$7,3*17)</f>
+        <v/>
+      </c>
+      <c r="C27" s="28">
+        <f>(B27-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D27" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B27,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E27" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B27,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1)))/((E27-D27)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G27" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B27,$K$8:$K$40,1))*EXP(-(F27/100)*(B27-D27)/365)</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>-LN(G27)/C27*100</f>
+        <v/>
+      </c>
+      <c r="K27" s="18">
         <f>Bootstrap!B26</f>
         <v/>
       </c>
-      <c r="C26" s="17">
-        <f>Bootstrap!J26</f>
-        <v/>
-      </c>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="31">
-        <f>IF(D26="","",(C26-D26)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6">
-        <f>Bootstrap!A27</f>
-        <v/>
-      </c>
-      <c r="B27" s="18">
+      <c r="L27" s="33">
+        <f>Bootstrap!H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="40" t="n">
+        <v>19</v>
+      </c>
+      <c r="B28" s="18">
+        <f>EDATE($F$7,3*18)</f>
+        <v/>
+      </c>
+      <c r="C28" s="28">
+        <f>(B28-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D28" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B28,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E28" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B28,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F28" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1)))/((E28-D28)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G28" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B28,$K$8:$K$40,1))*EXP(-(F28/100)*(B28-D28)/365)</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
+        <f>-LN(G28)/C28*100</f>
+        <v/>
+      </c>
+      <c r="K28" s="18">
         <f>Bootstrap!B27</f>
         <v/>
       </c>
-      <c r="C27" s="17">
-        <f>Bootstrap!J27</f>
-        <v/>
-      </c>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="31">
-        <f>IF(D27="","",(C27-D27)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6">
-        <f>Bootstrap!A28</f>
-        <v/>
-      </c>
-      <c r="B28" s="18">
+      <c r="L28" s="33">
+        <f>Bootstrap!H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="n">
+        <v>20</v>
+      </c>
+      <c r="B29" s="18">
+        <f>EDATE($F$7,3*19)</f>
+        <v/>
+      </c>
+      <c r="C29" s="28">
+        <f>(B29-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D29" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B29,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E29" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B29,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F29" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1)))/((E29-D29)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G29" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B29,$K$8:$K$40,1))*EXP(-(F29/100)*(B29-D29)/365)</f>
+        <v/>
+      </c>
+      <c r="H29" s="17">
+        <f>-LN(G29)/C29*100</f>
+        <v/>
+      </c>
+      <c r="K29" s="18">
         <f>Bootstrap!B28</f>
         <v/>
       </c>
-      <c r="C28" s="17">
-        <f>Bootstrap!J28</f>
-        <v/>
-      </c>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="31">
-        <f>IF(D28="","",(C28-D28)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6">
-        <f>Bootstrap!A29</f>
-        <v/>
-      </c>
-      <c r="B29" s="18">
+      <c r="L29" s="33">
+        <f>Bootstrap!H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="n">
+        <v>21</v>
+      </c>
+      <c r="B30" s="18">
+        <f>EDATE($F$7,3*20)</f>
+        <v/>
+      </c>
+      <c r="C30" s="28">
+        <f>(B30-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D30" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B30,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E30" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B30,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F30" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1)))/((E30-D30)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G30" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B30,$K$8:$K$40,1))*EXP(-(F30/100)*(B30-D30)/365)</f>
+        <v/>
+      </c>
+      <c r="H30" s="17">
+        <f>-LN(G30)/C30*100</f>
+        <v/>
+      </c>
+      <c r="K30" s="18">
         <f>Bootstrap!B29</f>
         <v/>
       </c>
-      <c r="C29" s="17">
-        <f>Bootstrap!J29</f>
-        <v/>
-      </c>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="31">
-        <f>IF(D29="","",(C29-D29)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6">
-        <f>Bootstrap!A30</f>
-        <v/>
-      </c>
-      <c r="B30" s="18">
+      <c r="L30" s="33">
+        <f>Bootstrap!H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="40" t="n">
+        <v>22</v>
+      </c>
+      <c r="B31" s="18">
+        <f>EDATE($F$7,3*21)</f>
+        <v/>
+      </c>
+      <c r="C31" s="28">
+        <f>(B31-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D31" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B31,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E31" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B31,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F31" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1)))/((E31-D31)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G31" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B31,$K$8:$K$40,1))*EXP(-(F31/100)*(B31-D31)/365)</f>
+        <v/>
+      </c>
+      <c r="H31" s="17">
+        <f>-LN(G31)/C31*100</f>
+        <v/>
+      </c>
+      <c r="K31" s="18">
         <f>Bootstrap!B30</f>
         <v/>
       </c>
-      <c r="C30" s="17">
-        <f>Bootstrap!J30</f>
-        <v/>
-      </c>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="31">
-        <f>IF(D30="","",(C30-D30)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="6">
-        <f>Bootstrap!A31</f>
-        <v/>
-      </c>
-      <c r="B31" s="18">
+      <c r="L31" s="33">
+        <f>Bootstrap!H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="n">
+        <v>23</v>
+      </c>
+      <c r="B32" s="18">
+        <f>EDATE($F$7,3*22)</f>
+        <v/>
+      </c>
+      <c r="C32" s="28">
+        <f>(B32-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D32" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B32,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E32" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B32,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F32" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1)))/((E32-D32)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G32" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B32,$K$8:$K$40,1))*EXP(-(F32/100)*(B32-D32)/365)</f>
+        <v/>
+      </c>
+      <c r="H32" s="17">
+        <f>-LN(G32)/C32*100</f>
+        <v/>
+      </c>
+      <c r="K32" s="18">
         <f>Bootstrap!B31</f>
         <v/>
       </c>
-      <c r="C31" s="17">
-        <f>Bootstrap!J31</f>
-        <v/>
-      </c>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="31">
-        <f>IF(D31="","",(C31-D31)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6">
-        <f>Bootstrap!A32</f>
-        <v/>
-      </c>
-      <c r="B32" s="18">
+      <c r="L32" s="33">
+        <f>Bootstrap!H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="40" t="n">
+        <v>24</v>
+      </c>
+      <c r="B33" s="18">
+        <f>EDATE($F$7,3*23)</f>
+        <v/>
+      </c>
+      <c r="C33" s="28">
+        <f>(B33-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D33" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B33,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E33" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B33,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1)))/((E33-D33)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G33" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B33,$K$8:$K$40,1))*EXP(-(F33/100)*(B33-D33)/365)</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>-LN(G33)/C33*100</f>
+        <v/>
+      </c>
+      <c r="K33" s="18">
         <f>Bootstrap!B32</f>
         <v/>
       </c>
-      <c r="C32" s="17">
-        <f>Bootstrap!J32</f>
-        <v/>
-      </c>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="31">
-        <f>IF(D32="","",(C32-D32)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="6">
-        <f>Bootstrap!A33</f>
-        <v/>
-      </c>
-      <c r="B33" s="18">
+      <c r="L33" s="33">
+        <f>Bootstrap!H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="40" t="n">
+        <v>25</v>
+      </c>
+      <c r="B34" s="18">
+        <f>EDATE($F$7,3*24)</f>
+        <v/>
+      </c>
+      <c r="C34" s="28">
+        <f>(B34-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D34" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B34,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E34" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B34,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1)))/((E34-D34)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G34" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B34,$K$8:$K$40,1))*EXP(-(F34/100)*(B34-D34)/365)</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>-LN(G34)/C34*100</f>
+        <v/>
+      </c>
+      <c r="K34" s="18">
         <f>Bootstrap!B33</f>
         <v/>
       </c>
-      <c r="C33" s="17">
-        <f>Bootstrap!J33</f>
-        <v/>
-      </c>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="31">
-        <f>IF(D33="","",(C33-D33)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6">
-        <f>Bootstrap!A34</f>
-        <v/>
-      </c>
-      <c r="B34" s="18">
+      <c r="L34" s="33">
+        <f>Bootstrap!H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="n">
+        <v>26</v>
+      </c>
+      <c r="B35" s="18">
+        <f>EDATE($F$7,3*25)</f>
+        <v/>
+      </c>
+      <c r="C35" s="28">
+        <f>(B35-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D35" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B35,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E35" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B35,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F35" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1)))/((E35-D35)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G35" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B35,$K$8:$K$40,1))*EXP(-(F35/100)*(B35-D35)/365)</f>
+        <v/>
+      </c>
+      <c r="H35" s="17">
+        <f>-LN(G35)/C35*100</f>
+        <v/>
+      </c>
+      <c r="K35" s="18">
         <f>Bootstrap!B34</f>
         <v/>
       </c>
-      <c r="C34" s="17">
-        <f>Bootstrap!J34</f>
-        <v/>
-      </c>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="31">
-        <f>IF(D34="","",(C34-D34)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6">
-        <f>Bootstrap!A35</f>
-        <v/>
-      </c>
-      <c r="B35" s="18">
+      <c r="L35" s="33">
+        <f>Bootstrap!H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="40" t="n">
+        <v>27</v>
+      </c>
+      <c r="B36" s="18">
+        <f>EDATE($F$7,3*26)</f>
+        <v/>
+      </c>
+      <c r="C36" s="28">
+        <f>(B36-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D36" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B36,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E36" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B36,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F36" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1)))/((E36-D36)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G36" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B36,$K$8:$K$40,1))*EXP(-(F36/100)*(B36-D36)/365)</f>
+        <v/>
+      </c>
+      <c r="H36" s="17">
+        <f>-LN(G36)/C36*100</f>
+        <v/>
+      </c>
+      <c r="K36" s="18">
         <f>Bootstrap!B35</f>
         <v/>
       </c>
-      <c r="C35" s="17">
-        <f>Bootstrap!J35</f>
-        <v/>
-      </c>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31">
-        <f>IF(D35="","",(C35-D35)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6">
-        <f>Bootstrap!A36</f>
-        <v/>
-      </c>
-      <c r="B36" s="18">
+      <c r="L36" s="33">
+        <f>Bootstrap!H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="n">
+        <v>28</v>
+      </c>
+      <c r="B37" s="18">
+        <f>EDATE($F$7,3*27)</f>
+        <v/>
+      </c>
+      <c r="C37" s="28">
+        <f>(B37-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D37" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B37,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E37" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B37,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1)))/((E37-D37)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G37" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B37,$K$8:$K$40,1))*EXP(-(F37/100)*(B37-D37)/365)</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>-LN(G37)/C37*100</f>
+        <v/>
+      </c>
+      <c r="K37" s="18">
         <f>Bootstrap!B36</f>
         <v/>
       </c>
-      <c r="C36" s="17">
-        <f>Bootstrap!J36</f>
-        <v/>
-      </c>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="31">
-        <f>IF(D36="","",(C36-D36)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6">
-        <f>Bootstrap!A37</f>
-        <v/>
-      </c>
-      <c r="B37" s="18">
+      <c r="L37" s="33">
+        <f>Bootstrap!H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="n">
+        <v>29</v>
+      </c>
+      <c r="B38" s="18">
+        <f>EDATE($F$7,3*28)</f>
+        <v/>
+      </c>
+      <c r="C38" s="28">
+        <f>(B38-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D38" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B38,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E38" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B38,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F38" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1)))/((E38-D38)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G38" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B38,$K$8:$K$40,1))*EXP(-(F38/100)*(B38-D38)/365)</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>-LN(G38)/C38*100</f>
+        <v/>
+      </c>
+      <c r="K38" s="18">
         <f>Bootstrap!B37</f>
         <v/>
       </c>
-      <c r="C37" s="17">
-        <f>Bootstrap!J37</f>
-        <v/>
-      </c>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31">
-        <f>IF(D37="","",(C37-D37)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6">
-        <f>Bootstrap!A38</f>
-        <v/>
-      </c>
-      <c r="B38" s="18">
+      <c r="L38" s="33">
+        <f>Bootstrap!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="40" t="n">
+        <v>30</v>
+      </c>
+      <c r="B39" s="18">
+        <f>EDATE($F$7,3*29)</f>
+        <v/>
+      </c>
+      <c r="C39" s="28">
+        <f>(B39-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D39" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B39,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E39" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B39,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F39" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1)))/((E39-D39)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G39" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B39,$K$8:$K$40,1))*EXP(-(F39/100)*(B39-D39)/365)</f>
+        <v/>
+      </c>
+      <c r="H39" s="17">
+        <f>-LN(G39)/C39*100</f>
+        <v/>
+      </c>
+      <c r="K39" s="18">
         <f>Bootstrap!B38</f>
         <v/>
       </c>
-      <c r="C38" s="17">
-        <f>Bootstrap!J38</f>
-        <v/>
-      </c>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="31">
-        <f>IF(D38="","",(C38-D38)*100)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="6">
-        <f>Bootstrap!A39</f>
-        <v/>
-      </c>
-      <c r="B39" s="18">
+      <c r="L39" s="33">
+        <f>Bootstrap!H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="40" t="n">
+        <v>31</v>
+      </c>
+      <c r="B40" s="18">
+        <f>EDATE($F$7,3*30)</f>
+        <v/>
+      </c>
+      <c r="C40" s="28">
+        <f>(B40-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D40" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B40,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E40" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B40,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F40" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1)))/((E40-D40)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G40" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B40,$K$8:$K$40,1))*EXP(-(F40/100)*(B40-D40)/365)</f>
+        <v/>
+      </c>
+      <c r="H40" s="17">
+        <f>-LN(G40)/C40*100</f>
+        <v/>
+      </c>
+      <c r="K40" s="18">
         <f>Bootstrap!B39</f>
         <v/>
       </c>
-      <c r="C39" s="17">
-        <f>Bootstrap!J39</f>
-        <v/>
-      </c>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="31">
-        <f>IF(D39="","",(C39-D39)*100)</f>
+      <c r="L40" s="33">
+        <f>Bootstrap!H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="n">
+        <v>32</v>
+      </c>
+      <c r="B41" s="18">
+        <f>EDATE($F$7,3*31)</f>
+        <v/>
+      </c>
+      <c r="C41" s="28">
+        <f>(B41-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D41" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B41,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E41" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B41,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F41" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1)))/((E41-D41)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G41" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B41,$K$8:$K$40,1))*EXP(-(F41/100)*(B41-D41)/365)</f>
+        <v/>
+      </c>
+      <c r="H41" s="17">
+        <f>-LN(G41)/C41*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="40" t="n">
+        <v>33</v>
+      </c>
+      <c r="B42" s="18">
+        <f>EDATE($F$7,3*32)</f>
+        <v/>
+      </c>
+      <c r="C42" s="28">
+        <f>(B42-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D42" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B42,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E42" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B42,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F42" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1)))/((E42-D42)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G42" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B42,$K$8:$K$40,1))*EXP(-(F42/100)*(B42-D42)/365)</f>
+        <v/>
+      </c>
+      <c r="H42" s="17">
+        <f>-LN(G42)/C42*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="n">
+        <v>34</v>
+      </c>
+      <c r="B43" s="18">
+        <f>EDATE($F$7,3*33)</f>
+        <v/>
+      </c>
+      <c r="C43" s="28">
+        <f>(B43-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D43" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B43,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E43" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B43,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1)))/((E43-D43)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G43" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B43,$K$8:$K$40,1))*EXP(-(F43/100)*(B43-D43)/365)</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>-LN(G43)/C43*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="40" t="n">
+        <v>35</v>
+      </c>
+      <c r="B44" s="18">
+        <f>EDATE($F$7,3*34)</f>
+        <v/>
+      </c>
+      <c r="C44" s="28">
+        <f>(B44-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D44" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B44,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E44" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B44,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F44" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1)))/((E44-D44)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G44" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B44,$K$8:$K$40,1))*EXP(-(F44/100)*(B44-D44)/365)</f>
+        <v/>
+      </c>
+      <c r="H44" s="17">
+        <f>-LN(G44)/C44*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="n">
+        <v>36</v>
+      </c>
+      <c r="B45" s="18">
+        <f>EDATE($F$7,3*35)</f>
+        <v/>
+      </c>
+      <c r="C45" s="28">
+        <f>(B45-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D45" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B45,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E45" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B45,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1)))/((E45-D45)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G45" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B45,$K$8:$K$40,1))*EXP(-(F45/100)*(B45-D45)/365)</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>-LN(G45)/C45*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="40" t="n">
+        <v>37</v>
+      </c>
+      <c r="B46" s="18">
+        <f>EDATE($F$7,3*36)</f>
+        <v/>
+      </c>
+      <c r="C46" s="28">
+        <f>(B46-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D46" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B46,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E46" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B46,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1)))/((E46-D46)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G46" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B46,$K$8:$K$40,1))*EXP(-(F46/100)*(B46-D46)/365)</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>-LN(G46)/C46*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B47" s="18">
+        <f>EDATE($F$7,3*37)</f>
+        <v/>
+      </c>
+      <c r="C47" s="28">
+        <f>(B47-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D47" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B47,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E47" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B47,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1)))/((E47-D47)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G47" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B47,$K$8:$K$40,1))*EXP(-(F47/100)*(B47-D47)/365)</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>-LN(G47)/C47*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B48" s="18">
+        <f>EDATE($F$7,3*38)</f>
+        <v/>
+      </c>
+      <c r="C48" s="28">
+        <f>(B48-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D48" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B48,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E48" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B48,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F48" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1)))/((E48-D48)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G48" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B48,$K$8:$K$40,1))*EXP(-(F48/100)*(B48-D48)/365)</f>
+        <v/>
+      </c>
+      <c r="H48" s="17">
+        <f>-LN(G48)/C48*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="40" t="n">
+        <v>40</v>
+      </c>
+      <c r="B49" s="18">
+        <f>EDATE($F$7,3*39)</f>
+        <v/>
+      </c>
+      <c r="C49" s="28">
+        <f>(B49-VAL_DATE)/365</f>
+        <v/>
+      </c>
+      <c r="D49" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B49,$K$8:$K$40,1))</f>
+        <v/>
+      </c>
+      <c r="E49" s="18">
+        <f>INDEX($K$8:$K$40,MATCH(B49,$K$8:$K$40,1)+1)</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>-LN(INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1)+1)/INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1)))/((E49-D49)/365)*100</f>
+        <v/>
+      </c>
+      <c r="G49" s="33">
+        <f>INDEX($L$8:$L$40,MATCH(B49,$K$8:$K$40,1))*EXP(-(F49/100)*(B49-D49)/365)</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>-LN(G49)/C49*100</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="H7:L7"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="B4:E4"/>
+  <mergeCells count="2">
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="A4:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Futures" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_OIS_Quotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap_Futures" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap_Lehman" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="10" state="visible" r:id="rId10"/>
@@ -190,11 +190,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1489,19 +1489,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Robust 3-segment bootstrap (futures-if-agree-else-OIS). The curve everything downstream uses.</t>
+          <t>Purely-OIS bootstrap. The production curve — Swap_Pricer, Curve_Interface, and CDS all use it.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="13" t="inlineStr">
         <is>
-          <t>Bootstrap_Futures</t>
+          <t>Bootstrap_Lehman</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Second copy — FORCES the SR3 futures in the middle (no guard). Compare col H vs Bootstrap.</t>
+          <t>Lehman methodology: short OIS + SR3 futures (1Y–5Y) + OIS swaps. Compare col H vs the OIS Bootstrap.</t>
         </is>
       </c>
     </row>
@@ -1831,8 +1831,8 @@
         <f>Bootstrap!J8</f>
         <v/>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31">
+      <c r="D8" s="29" t="n"/>
+      <c r="E8" s="30">
         <f>IF(D8="","",(C8-D8)*100)</f>
         <v/>
       </c>
@@ -1854,8 +1854,8 @@
         <f>Bootstrap!J9</f>
         <v/>
       </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31">
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="30">
         <f>IF(D9="","",(C9-D9)*100)</f>
         <v/>
       </c>
@@ -1873,8 +1873,8 @@
         <f>Bootstrap!J10</f>
         <v/>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="31">
+      <c r="D10" s="29" t="n"/>
+      <c r="E10" s="30">
         <f>IF(D10="","",(C10-D10)*100)</f>
         <v/>
       </c>
@@ -1892,8 +1892,8 @@
         <f>Bootstrap!J11</f>
         <v/>
       </c>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31">
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="30">
         <f>IF(D11="","",(C11-D11)*100)</f>
         <v/>
       </c>
@@ -1911,8 +1911,8 @@
         <f>Bootstrap!J12</f>
         <v/>
       </c>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="31">
+      <c r="D12" s="29" t="n"/>
+      <c r="E12" s="30">
         <f>IF(D12="","",(C12-D12)*100)</f>
         <v/>
       </c>
@@ -1930,8 +1930,8 @@
         <f>Bootstrap!J13</f>
         <v/>
       </c>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="31">
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="30">
         <f>IF(D13="","",(C13-D13)*100)</f>
         <v/>
       </c>
@@ -1949,8 +1949,8 @@
         <f>Bootstrap!J14</f>
         <v/>
       </c>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="31">
+      <c r="D14" s="29" t="n"/>
+      <c r="E14" s="30">
         <f>IF(D14="","",(C14-D14)*100)</f>
         <v/>
       </c>
@@ -1968,8 +1968,8 @@
         <f>Bootstrap!J15</f>
         <v/>
       </c>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="31">
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="30">
         <f>IF(D15="","",(C15-D15)*100)</f>
         <v/>
       </c>
@@ -1987,8 +1987,8 @@
         <f>Bootstrap!J16</f>
         <v/>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="31">
+      <c r="D16" s="29" t="n"/>
+      <c r="E16" s="30">
         <f>IF(D16="","",(C16-D16)*100)</f>
         <v/>
       </c>
@@ -2006,8 +2006,8 @@
         <f>Bootstrap!J17</f>
         <v/>
       </c>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="31">
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="30">
         <f>IF(D17="","",(C17-D17)*100)</f>
         <v/>
       </c>
@@ -2025,8 +2025,8 @@
         <f>Bootstrap!J18</f>
         <v/>
       </c>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="31">
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="30">
         <f>IF(D18="","",(C18-D18)*100)</f>
         <v/>
       </c>
@@ -2044,8 +2044,8 @@
         <f>Bootstrap!J19</f>
         <v/>
       </c>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="31">
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="30">
         <f>IF(D19="","",(C19-D19)*100)</f>
         <v/>
       </c>
@@ -2063,8 +2063,8 @@
         <f>Bootstrap!J20</f>
         <v/>
       </c>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="31">
+      <c r="D20" s="29" t="n"/>
+      <c r="E20" s="30">
         <f>IF(D20="","",(C20-D20)*100)</f>
         <v/>
       </c>
@@ -2082,8 +2082,8 @@
         <f>Bootstrap!J21</f>
         <v/>
       </c>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="31">
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="30">
         <f>IF(D21="","",(C21-D21)*100)</f>
         <v/>
       </c>
@@ -2101,8 +2101,8 @@
         <f>Bootstrap!J22</f>
         <v/>
       </c>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="31">
+      <c r="D22" s="29" t="n"/>
+      <c r="E22" s="30">
         <f>IF(D22="","",(C22-D22)*100)</f>
         <v/>
       </c>
@@ -2120,8 +2120,8 @@
         <f>Bootstrap!J23</f>
         <v/>
       </c>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="31">
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="30">
         <f>IF(D23="","",(C23-D23)*100)</f>
         <v/>
       </c>
@@ -2139,8 +2139,8 @@
         <f>Bootstrap!J24</f>
         <v/>
       </c>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="31">
+      <c r="D24" s="29" t="n"/>
+      <c r="E24" s="30">
         <f>IF(D24="","",(C24-D24)*100)</f>
         <v/>
       </c>
@@ -2158,8 +2158,8 @@
         <f>Bootstrap!J25</f>
         <v/>
       </c>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="31">
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="30">
         <f>IF(D25="","",(C25-D25)*100)</f>
         <v/>
       </c>
@@ -2177,8 +2177,8 @@
         <f>Bootstrap!J26</f>
         <v/>
       </c>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="31">
+      <c r="D26" s="29" t="n"/>
+      <c r="E26" s="30">
         <f>IF(D26="","",(C26-D26)*100)</f>
         <v/>
       </c>
@@ -2196,8 +2196,8 @@
         <f>Bootstrap!J27</f>
         <v/>
       </c>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="31">
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="30">
         <f>IF(D27="","",(C27-D27)*100)</f>
         <v/>
       </c>
@@ -2215,8 +2215,8 @@
         <f>Bootstrap!J28</f>
         <v/>
       </c>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="31">
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="30">
         <f>IF(D28="","",(C28-D28)*100)</f>
         <v/>
       </c>
@@ -2234,8 +2234,8 @@
         <f>Bootstrap!J29</f>
         <v/>
       </c>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="31">
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="30">
         <f>IF(D29="","",(C29-D29)*100)</f>
         <v/>
       </c>
@@ -2253,8 +2253,8 @@
         <f>Bootstrap!J30</f>
         <v/>
       </c>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="31">
+      <c r="D30" s="29" t="n"/>
+      <c r="E30" s="30">
         <f>IF(D30="","",(C30-D30)*100)</f>
         <v/>
       </c>
@@ -2272,8 +2272,8 @@
         <f>Bootstrap!J31</f>
         <v/>
       </c>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="31">
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="30">
         <f>IF(D31="","",(C31-D31)*100)</f>
         <v/>
       </c>
@@ -2291,8 +2291,8 @@
         <f>Bootstrap!J32</f>
         <v/>
       </c>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="31">
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="30">
         <f>IF(D32="","",(C32-D32)*100)</f>
         <v/>
       </c>
@@ -2310,8 +2310,8 @@
         <f>Bootstrap!J33</f>
         <v/>
       </c>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="31">
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="30">
         <f>IF(D33="","",(C33-D33)*100)</f>
         <v/>
       </c>
@@ -2329,8 +2329,8 @@
         <f>Bootstrap!J34</f>
         <v/>
       </c>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="31">
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="30">
         <f>IF(D34="","",(C34-D34)*100)</f>
         <v/>
       </c>
@@ -2348,8 +2348,8 @@
         <f>Bootstrap!J35</f>
         <v/>
       </c>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31">
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="30">
         <f>IF(D35="","",(C35-D35)*100)</f>
         <v/>
       </c>
@@ -2367,8 +2367,8 @@
         <f>Bootstrap!J36</f>
         <v/>
       </c>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="31">
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="30">
         <f>IF(D36="","",(C36-D36)*100)</f>
         <v/>
       </c>
@@ -2386,8 +2386,8 @@
         <f>Bootstrap!J37</f>
         <v/>
       </c>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31">
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="30">
         <f>IF(D37="","",(C37-D37)*100)</f>
         <v/>
       </c>
@@ -2405,8 +2405,8 @@
         <f>Bootstrap!J38</f>
         <v/>
       </c>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="31">
+      <c r="D38" s="29" t="n"/>
+      <c r="E38" s="30">
         <f>IF(D38="","",(C38-D38)*100)</f>
         <v/>
       </c>
@@ -2424,8 +2424,8 @@
         <f>Bootstrap!J39</f>
         <v/>
       </c>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="31">
+      <c r="D39" s="29" t="n"/>
+      <c r="E39" s="30">
         <f>IF(D39="","",(C39-D39)*100)</f>
         <v/>
       </c>
@@ -3346,7 +3346,7 @@
         <f>'Bootstrap'!A8</f>
         <v/>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <f>'Bootstrap'!C8</f>
         <v/>
       </c>
@@ -3354,7 +3354,7 @@
         <f>'Bootstrap'!H8</f>
         <v/>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <f>B9-B8</f>
         <v/>
       </c>
@@ -3396,7 +3396,7 @@
         <f>'Bootstrap'!A9</f>
         <v/>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="27">
         <f>'Bootstrap'!C9</f>
         <v/>
       </c>
@@ -3404,7 +3404,7 @@
         <f>'Bootstrap'!H9</f>
         <v/>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="27">
         <f>B10-B9</f>
         <v/>
       </c>
@@ -3446,7 +3446,7 @@
         <f>'Bootstrap'!A10</f>
         <v/>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="27">
         <f>'Bootstrap'!C10</f>
         <v/>
       </c>
@@ -3454,7 +3454,7 @@
         <f>'Bootstrap'!H10</f>
         <v/>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="27">
         <f>B11-B10</f>
         <v/>
       </c>
@@ -3496,7 +3496,7 @@
         <f>'Bootstrap'!A11</f>
         <v/>
       </c>
-      <c r="B12" s="28">
+      <c r="B12" s="27">
         <f>'Bootstrap'!C11</f>
         <v/>
       </c>
@@ -3504,7 +3504,7 @@
         <f>'Bootstrap'!H11</f>
         <v/>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="27">
         <f>B12-B11</f>
         <v/>
       </c>
@@ -3546,7 +3546,7 @@
         <f>'Bootstrap'!A12</f>
         <v/>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="27">
         <f>'Bootstrap'!C12</f>
         <v/>
       </c>
@@ -3554,7 +3554,7 @@
         <f>'Bootstrap'!H12</f>
         <v/>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <f>B13-B12</f>
         <v/>
       </c>
@@ -3596,7 +3596,7 @@
         <f>'Bootstrap'!A13</f>
         <v/>
       </c>
-      <c r="B14" s="28">
+      <c r="B14" s="27">
         <f>'Bootstrap'!C13</f>
         <v/>
       </c>
@@ -3604,7 +3604,7 @@
         <f>'Bootstrap'!H13</f>
         <v/>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="27">
         <f>B14-B13</f>
         <v/>
       </c>
@@ -3646,7 +3646,7 @@
         <f>'Bootstrap'!A14</f>
         <v/>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <f>'Bootstrap'!C14</f>
         <v/>
       </c>
@@ -3654,7 +3654,7 @@
         <f>'Bootstrap'!H14</f>
         <v/>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <f>B15-B14</f>
         <v/>
       </c>
@@ -3696,7 +3696,7 @@
         <f>'Bootstrap'!A15</f>
         <v/>
       </c>
-      <c r="B16" s="28">
+      <c r="B16" s="27">
         <f>'Bootstrap'!C15</f>
         <v/>
       </c>
@@ -3704,7 +3704,7 @@
         <f>'Bootstrap'!H15</f>
         <v/>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <f>B16-B15</f>
         <v/>
       </c>
@@ -3746,7 +3746,7 @@
         <f>'Bootstrap'!A16</f>
         <v/>
       </c>
-      <c r="B17" s="28">
+      <c r="B17" s="27">
         <f>'Bootstrap'!C16</f>
         <v/>
       </c>
@@ -3754,7 +3754,7 @@
         <f>'Bootstrap'!H16</f>
         <v/>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <f>B17-B16</f>
         <v/>
       </c>
@@ -3796,7 +3796,7 @@
         <f>'Bootstrap'!A17</f>
         <v/>
       </c>
-      <c r="B18" s="28">
+      <c r="B18" s="27">
         <f>'Bootstrap'!C17</f>
         <v/>
       </c>
@@ -3804,7 +3804,7 @@
         <f>'Bootstrap'!H17</f>
         <v/>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <f>B18-B17</f>
         <v/>
       </c>
@@ -3846,7 +3846,7 @@
         <f>'Bootstrap'!A18</f>
         <v/>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="27">
         <f>'Bootstrap'!C18</f>
         <v/>
       </c>
@@ -3854,7 +3854,7 @@
         <f>'Bootstrap'!H18</f>
         <v/>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="27">
         <f>B19-B18</f>
         <v/>
       </c>
@@ -3896,7 +3896,7 @@
         <f>'Bootstrap'!A19</f>
         <v/>
       </c>
-      <c r="B20" s="28">
+      <c r="B20" s="27">
         <f>'Bootstrap'!C19</f>
         <v/>
       </c>
@@ -3904,7 +3904,7 @@
         <f>'Bootstrap'!H19</f>
         <v/>
       </c>
-      <c r="D20" s="28">
+      <c r="D20" s="27">
         <f>B20-B19</f>
         <v/>
       </c>
@@ -3946,7 +3946,7 @@
         <f>'Bootstrap'!A20</f>
         <v/>
       </c>
-      <c r="B21" s="28">
+      <c r="B21" s="27">
         <f>'Bootstrap'!C20</f>
         <v/>
       </c>
@@ -3954,7 +3954,7 @@
         <f>'Bootstrap'!H20</f>
         <v/>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="27">
         <f>B21-B20</f>
         <v/>
       </c>
@@ -3996,7 +3996,7 @@
         <f>'Bootstrap'!A21</f>
         <v/>
       </c>
-      <c r="B22" s="28">
+      <c r="B22" s="27">
         <f>'Bootstrap'!C21</f>
         <v/>
       </c>
@@ -4004,7 +4004,7 @@
         <f>'Bootstrap'!H21</f>
         <v/>
       </c>
-      <c r="D22" s="28">
+      <c r="D22" s="27">
         <f>B22-B21</f>
         <v/>
       </c>
@@ -4046,7 +4046,7 @@
         <f>'Bootstrap'!A22</f>
         <v/>
       </c>
-      <c r="B23" s="28">
+      <c r="B23" s="27">
         <f>'Bootstrap'!C22</f>
         <v/>
       </c>
@@ -4054,7 +4054,7 @@
         <f>'Bootstrap'!H22</f>
         <v/>
       </c>
-      <c r="D23" s="28">
+      <c r="D23" s="27">
         <f>B23-B22</f>
         <v/>
       </c>
@@ -4096,7 +4096,7 @@
         <f>'Bootstrap'!A23</f>
         <v/>
       </c>
-      <c r="B24" s="28">
+      <c r="B24" s="27">
         <f>'Bootstrap'!C23</f>
         <v/>
       </c>
@@ -4104,7 +4104,7 @@
         <f>'Bootstrap'!H23</f>
         <v/>
       </c>
-      <c r="D24" s="28">
+      <c r="D24" s="27">
         <f>B24-B23</f>
         <v/>
       </c>
@@ -4146,7 +4146,7 @@
         <f>'Bootstrap'!A24</f>
         <v/>
       </c>
-      <c r="B25" s="28">
+      <c r="B25" s="27">
         <f>'Bootstrap'!C24</f>
         <v/>
       </c>
@@ -4154,7 +4154,7 @@
         <f>'Bootstrap'!H24</f>
         <v/>
       </c>
-      <c r="D25" s="28">
+      <c r="D25" s="27">
         <f>B25-B24</f>
         <v/>
       </c>
@@ -4196,7 +4196,7 @@
         <f>'Bootstrap'!A25</f>
         <v/>
       </c>
-      <c r="B26" s="28">
+      <c r="B26" s="27">
         <f>'Bootstrap'!C25</f>
         <v/>
       </c>
@@ -4204,7 +4204,7 @@
         <f>'Bootstrap'!H25</f>
         <v/>
       </c>
-      <c r="D26" s="28">
+      <c r="D26" s="27">
         <f>B26-B25</f>
         <v/>
       </c>
@@ -4246,7 +4246,7 @@
         <f>'Bootstrap'!A26</f>
         <v/>
       </c>
-      <c r="B27" s="28">
+      <c r="B27" s="27">
         <f>'Bootstrap'!C26</f>
         <v/>
       </c>
@@ -4254,7 +4254,7 @@
         <f>'Bootstrap'!H26</f>
         <v/>
       </c>
-      <c r="D27" s="28">
+      <c r="D27" s="27">
         <f>B27-B26</f>
         <v/>
       </c>
@@ -4296,7 +4296,7 @@
         <f>'Bootstrap'!A27</f>
         <v/>
       </c>
-      <c r="B28" s="28">
+      <c r="B28" s="27">
         <f>'Bootstrap'!C27</f>
         <v/>
       </c>
@@ -4304,7 +4304,7 @@
         <f>'Bootstrap'!H27</f>
         <v/>
       </c>
-      <c r="D28" s="28">
+      <c r="D28" s="27">
         <f>B28-B27</f>
         <v/>
       </c>
@@ -4346,7 +4346,7 @@
         <f>'Bootstrap'!A28</f>
         <v/>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <f>'Bootstrap'!C28</f>
         <v/>
       </c>
@@ -4354,7 +4354,7 @@
         <f>'Bootstrap'!H28</f>
         <v/>
       </c>
-      <c r="D29" s="28">
+      <c r="D29" s="27">
         <f>B29-B28</f>
         <v/>
       </c>
@@ -4396,7 +4396,7 @@
         <f>'Bootstrap'!A29</f>
         <v/>
       </c>
-      <c r="B30" s="28">
+      <c r="B30" s="27">
         <f>'Bootstrap'!C29</f>
         <v/>
       </c>
@@ -4404,7 +4404,7 @@
         <f>'Bootstrap'!H29</f>
         <v/>
       </c>
-      <c r="D30" s="28">
+      <c r="D30" s="27">
         <f>B30-B29</f>
         <v/>
       </c>
@@ -4446,7 +4446,7 @@
         <f>'Bootstrap'!A30</f>
         <v/>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <f>'Bootstrap'!C30</f>
         <v/>
       </c>
@@ -4454,7 +4454,7 @@
         <f>'Bootstrap'!H30</f>
         <v/>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="27">
         <f>B31-B30</f>
         <v/>
       </c>
@@ -4496,7 +4496,7 @@
         <f>'Bootstrap'!A31</f>
         <v/>
       </c>
-      <c r="B32" s="28">
+      <c r="B32" s="27">
         <f>'Bootstrap'!C31</f>
         <v/>
       </c>
@@ -4504,7 +4504,7 @@
         <f>'Bootstrap'!H31</f>
         <v/>
       </c>
-      <c r="D32" s="28">
+      <c r="D32" s="27">
         <f>B32-B31</f>
         <v/>
       </c>
@@ -4546,7 +4546,7 @@
         <f>'Bootstrap'!A32</f>
         <v/>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <f>'Bootstrap'!C32</f>
         <v/>
       </c>
@@ -4554,7 +4554,7 @@
         <f>'Bootstrap'!H32</f>
         <v/>
       </c>
-      <c r="D33" s="28">
+      <c r="D33" s="27">
         <f>B33-B32</f>
         <v/>
       </c>
@@ -4596,7 +4596,7 @@
         <f>'Bootstrap'!A33</f>
         <v/>
       </c>
-      <c r="B34" s="28">
+      <c r="B34" s="27">
         <f>'Bootstrap'!C33</f>
         <v/>
       </c>
@@ -4604,7 +4604,7 @@
         <f>'Bootstrap'!H33</f>
         <v/>
       </c>
-      <c r="D34" s="28">
+      <c r="D34" s="27">
         <f>B34-B33</f>
         <v/>
       </c>
@@ -4646,7 +4646,7 @@
         <f>'Bootstrap'!A34</f>
         <v/>
       </c>
-      <c r="B35" s="28">
+      <c r="B35" s="27">
         <f>'Bootstrap'!C34</f>
         <v/>
       </c>
@@ -4654,7 +4654,7 @@
         <f>'Bootstrap'!H34</f>
         <v/>
       </c>
-      <c r="D35" s="28">
+      <c r="D35" s="27">
         <f>B35-B34</f>
         <v/>
       </c>
@@ -4696,7 +4696,7 @@
         <f>'Bootstrap'!A35</f>
         <v/>
       </c>
-      <c r="B36" s="28">
+      <c r="B36" s="27">
         <f>'Bootstrap'!C35</f>
         <v/>
       </c>
@@ -4704,7 +4704,7 @@
         <f>'Bootstrap'!H35</f>
         <v/>
       </c>
-      <c r="D36" s="28">
+      <c r="D36" s="27">
         <f>B36-B35</f>
         <v/>
       </c>
@@ -4746,7 +4746,7 @@
         <f>'Bootstrap'!A36</f>
         <v/>
       </c>
-      <c r="B37" s="28">
+      <c r="B37" s="27">
         <f>'Bootstrap'!C36</f>
         <v/>
       </c>
@@ -4754,7 +4754,7 @@
         <f>'Bootstrap'!H36</f>
         <v/>
       </c>
-      <c r="D37" s="28">
+      <c r="D37" s="27">
         <f>B37-B36</f>
         <v/>
       </c>
@@ -4796,7 +4796,7 @@
         <f>'Bootstrap'!A37</f>
         <v/>
       </c>
-      <c r="B38" s="28">
+      <c r="B38" s="27">
         <f>'Bootstrap'!C37</f>
         <v/>
       </c>
@@ -4804,7 +4804,7 @@
         <f>'Bootstrap'!H37</f>
         <v/>
       </c>
-      <c r="D38" s="28">
+      <c r="D38" s="27">
         <f>B38-B37</f>
         <v/>
       </c>
@@ -4846,7 +4846,7 @@
         <f>'Bootstrap'!A38</f>
         <v/>
       </c>
-      <c r="B39" s="28">
+      <c r="B39" s="27">
         <f>'Bootstrap'!C38</f>
         <v/>
       </c>
@@ -4854,7 +4854,7 @@
         <f>'Bootstrap'!H38</f>
         <v/>
       </c>
-      <c r="D39" s="28">
+      <c r="D39" s="27">
         <f>B39-B38</f>
         <v/>
       </c>
@@ -4896,7 +4896,7 @@
         <f>'Bootstrap'!A39</f>
         <v/>
       </c>
-      <c r="B40" s="28">
+      <c r="B40" s="27">
         <f>'Bootstrap'!C39</f>
         <v/>
       </c>
@@ -4904,7 +4904,7 @@
         <f>'Bootstrap'!H39</f>
         <v/>
       </c>
-      <c r="D40" s="28">
+      <c r="D40" s="27">
         <f>B40-B39</f>
         <v/>
       </c>
@@ -5261,7 +5261,7 @@
       <c r="E7" s="52" t="n">
         <v>40</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <f>IF(D7="",E7,IFERROR(BDP(D7,"PX_LAST"),E7))</f>
         <v/>
       </c>
@@ -5287,7 +5287,7 @@
       <c r="E8" s="52" t="n">
         <v>55</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <f>IF(D8="",E8,IFERROR(BDP(D8,"PX_LAST"),E8))</f>
         <v/>
       </c>
@@ -5313,7 +5313,7 @@
       <c r="E9" s="52" t="n">
         <v>70</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f>IF(D9="",E9,IFERROR(BDP(D9,"PX_LAST"),E9))</f>
         <v/>
       </c>
@@ -5339,7 +5339,7 @@
       <c r="E10" s="52" t="n">
         <v>95</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <f>IF(D10="",E10,IFERROR(BDP(D10,"PX_LAST"),E10))</f>
         <v/>
       </c>
@@ -5365,7 +5365,7 @@
       <c r="E11" s="52" t="n">
         <v>115</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <f>IF(D11="",E11,IFERROR(BDP(D11,"PX_LAST"),E11))</f>
         <v/>
       </c>
@@ -5391,7 +5391,7 @@
       <c r="E12" s="52" t="n">
         <v>135</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <f>IF(D12="",E12,IFERROR(BDP(D12,"PX_LAST"),E12))</f>
         <v/>
       </c>
@@ -5513,7 +5513,7 @@
         <f>CDS_Quotes!C7</f>
         <v/>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <f>CDS_Quotes!F7</f>
         <v/>
       </c>
@@ -5537,7 +5537,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <f>(1-CDS_Parameters!$B$8)*H7/G7*10000</f>
         <v/>
       </c>
@@ -5556,7 +5556,7 @@
         <f>CDS_Quotes!C8</f>
         <v/>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <f>CDS_Quotes!F8</f>
         <v/>
       </c>
@@ -5580,7 +5580,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <f>(1-CDS_Parameters!$B$8)*H8/G8*10000</f>
         <v/>
       </c>
@@ -5599,7 +5599,7 @@
         <f>CDS_Quotes!C9</f>
         <v/>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <f>CDS_Quotes!F9</f>
         <v/>
       </c>
@@ -5623,7 +5623,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="27">
         <f>(1-CDS_Parameters!$B$8)*H9/G9*10000</f>
         <v/>
       </c>
@@ -5642,7 +5642,7 @@
         <f>CDS_Quotes!C10</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <f>CDS_Quotes!F10</f>
         <v/>
       </c>
@@ -5666,7 +5666,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <f>(1-CDS_Parameters!$B$8)*H10/G10*10000</f>
         <v/>
       </c>
@@ -5685,7 +5685,7 @@
         <f>CDS_Quotes!C11</f>
         <v/>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <f>CDS_Quotes!F11</f>
         <v/>
       </c>
@@ -5709,7 +5709,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="27">
         <f>(1-CDS_Parameters!$B$8)*H11/G11*10000</f>
         <v/>
       </c>
@@ -5728,7 +5728,7 @@
         <f>CDS_Quotes!C12</f>
         <v/>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <f>CDS_Quotes!F12</f>
         <v/>
       </c>
@@ -5752,7 +5752,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="27">
         <f>(1-CDS_Parameters!$B$8)*H12/G12*10000</f>
         <v/>
       </c>
@@ -5914,7 +5914,7 @@
         <f>(C7-B7)/365</f>
         <v/>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="27">
         <f>(C7-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -5975,7 +5975,7 @@
         <f>(C8-B8)/365</f>
         <v/>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
         <f>(C8-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6036,7 +6036,7 @@
         <f>(C9-B9)/365</f>
         <v/>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="27">
         <f>(C9-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6097,7 +6097,7 @@
         <f>(C10-B10)/365</f>
         <v/>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="27">
         <f>(C10-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6158,7 +6158,7 @@
         <f>(C11-B11)/365</f>
         <v/>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="27">
         <f>(C11-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6219,7 +6219,7 @@
         <f>(C12-B12)/365</f>
         <v/>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="27">
         <f>(C12-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6280,7 +6280,7 @@
         <f>(C13-B13)/365</f>
         <v/>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="27">
         <f>(C13-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6341,7 +6341,7 @@
         <f>(C14-B14)/365</f>
         <v/>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="27">
         <f>(C14-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6402,7 +6402,7 @@
         <f>(C15-B15)/365</f>
         <v/>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="27">
         <f>(C15-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6463,7 +6463,7 @@
         <f>(C16-B16)/365</f>
         <v/>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="27">
         <f>(C16-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6524,7 +6524,7 @@
         <f>(C17-B17)/365</f>
         <v/>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="27">
         <f>(C17-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6585,7 +6585,7 @@
         <f>(C18-B18)/365</f>
         <v/>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="27">
         <f>(C18-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6646,7 +6646,7 @@
         <f>(C19-B19)/365</f>
         <v/>
       </c>
-      <c r="F19" s="28">
+      <c r="F19" s="27">
         <f>(C19-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6707,7 +6707,7 @@
         <f>(C20-B20)/365</f>
         <v/>
       </c>
-      <c r="F20" s="28">
+      <c r="F20" s="27">
         <f>(C20-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6768,7 +6768,7 @@
         <f>(C21-B21)/365</f>
         <v/>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="27">
         <f>(C21-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6829,7 +6829,7 @@
         <f>(C22-B22)/365</f>
         <v/>
       </c>
-      <c r="F22" s="28">
+      <c r="F22" s="27">
         <f>(C22-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6890,7 +6890,7 @@
         <f>(C23-B23)/365</f>
         <v/>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="27">
         <f>(C23-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -6951,7 +6951,7 @@
         <f>(C24-B24)/365</f>
         <v/>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="27">
         <f>(C24-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7012,7 +7012,7 @@
         <f>(C25-B25)/365</f>
         <v/>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="27">
         <f>(C25-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7073,7 +7073,7 @@
         <f>(C26-B26)/365</f>
         <v/>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="27">
         <f>(C26-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7134,7 +7134,7 @@
         <f>(C27-B27)/365</f>
         <v/>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="27">
         <f>(C27-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7195,7 +7195,7 @@
         <f>(C28-B28)/365</f>
         <v/>
       </c>
-      <c r="F28" s="28">
+      <c r="F28" s="27">
         <f>(C28-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7256,7 +7256,7 @@
         <f>(C29-B29)/365</f>
         <v/>
       </c>
-      <c r="F29" s="28">
+      <c r="F29" s="27">
         <f>(C29-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7317,7 +7317,7 @@
         <f>(C30-B30)/365</f>
         <v/>
       </c>
-      <c r="F30" s="28">
+      <c r="F30" s="27">
         <f>(C30-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7378,7 +7378,7 @@
         <f>(C31-B31)/365</f>
         <v/>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="27">
         <f>(C31-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7439,7 +7439,7 @@
         <f>(C32-B32)/365</f>
         <v/>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="27">
         <f>(C32-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7500,7 +7500,7 @@
         <f>(C33-B33)/365</f>
         <v/>
       </c>
-      <c r="F33" s="28">
+      <c r="F33" s="27">
         <f>(C33-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7561,7 +7561,7 @@
         <f>(C34-B34)/365</f>
         <v/>
       </c>
-      <c r="F34" s="28">
+      <c r="F34" s="27">
         <f>(C34-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7622,7 +7622,7 @@
         <f>(C35-B35)/365</f>
         <v/>
       </c>
-      <c r="F35" s="28">
+      <c r="F35" s="27">
         <f>(C35-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7683,7 +7683,7 @@
         <f>(C36-B36)/365</f>
         <v/>
       </c>
-      <c r="F36" s="28">
+      <c r="F36" s="27">
         <f>(C36-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7744,7 +7744,7 @@
         <f>(C37-B37)/365</f>
         <v/>
       </c>
-      <c r="F37" s="28">
+      <c r="F37" s="27">
         <f>(C37-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7805,7 +7805,7 @@
         <f>(C38-B38)/365</f>
         <v/>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="27">
         <f>(C38-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7866,7 +7866,7 @@
         <f>(C39-B39)/365</f>
         <v/>
       </c>
-      <c r="F39" s="28">
+      <c r="F39" s="27">
         <f>(C39-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7927,7 +7927,7 @@
         <f>(C40-B40)/365</f>
         <v/>
       </c>
-      <c r="F40" s="28">
+      <c r="F40" s="27">
         <f>(C40-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -7988,7 +7988,7 @@
         <f>(C41-B41)/365</f>
         <v/>
       </c>
-      <c r="F41" s="28">
+      <c r="F41" s="27">
         <f>(C41-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -8049,7 +8049,7 @@
         <f>(C42-B42)/365</f>
         <v/>
       </c>
-      <c r="F42" s="28">
+      <c r="F42" s="27">
         <f>(C42-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -8110,7 +8110,7 @@
         <f>(C43-B43)/365</f>
         <v/>
       </c>
-      <c r="F43" s="28">
+      <c r="F43" s="27">
         <f>(C43-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -8171,7 +8171,7 @@
         <f>(C44-B44)/365</f>
         <v/>
       </c>
-      <c r="F44" s="28">
+      <c r="F44" s="27">
         <f>(C44-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -8232,7 +8232,7 @@
         <f>(C45-B45)/365</f>
         <v/>
       </c>
-      <c r="F45" s="28">
+      <c r="F45" s="27">
         <f>(C45-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -8293,7 +8293,7 @@
         <f>(C46-B46)/365</f>
         <v/>
       </c>
-      <c r="F46" s="28">
+      <c r="F46" s="27">
         <f>(C46-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -8495,7 +8495,7 @@
           <t>Par spread (bp)</t>
         </is>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="27">
         <f>(1-B5)*SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)/B12*10000</f>
         <v/>
       </c>
@@ -12048,7 +12048,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z42"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12065,17 +12065,6 @@
     <col width="16" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="12" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="13" customWidth="1" min="22" max="22"/>
-    <col width="13" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -12088,7 +12077,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Three-segment USD curve (Zhou 2002): short OIS (≤1Y) · SR3 futures (1Y–5Y) · OIS swaps (5Y–50Y)</t>
+          <t>Purely-OIS USD SOFR curve: short single-payment OIS (≤1Y) + annual OIS swaps (18M–50Y). The production curve — used by Swap_Pricer, Curve_Interface and the CDS module.</t>
         </is>
       </c>
     </row>
@@ -12106,35 +12095,11 @@
     <row r="5" ht="58" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>SHORT (o/n–1Y): single-payment SOFR OIS, DF = 1/(1+S·tau0).  MIDDLE (1Y–5Y): the DF at 18M/2Y/3Y/4Y/5Y is interpolated off the SR3 futures chain (helper block cols O–W), which chains the QUARTERLY contracts only (ref start Mar/Jun/Sep/Dec; monthly serials skipped) forward from the OIS 1Y DF — so 18M/2Y…5Y here are driven by FUTURES, not the OIS pars (col E is reference only). The middle DF uses the futures value only if it agrees with the OIS bootstrap (|diff|&lt;0.03), else it FALLS BACK to OIS so bad/mixed futures data can never break the curve — col N shows which is live per pillar. LONG (5Y–50Y): annual SOFR OIS swaps, DF = (1−S·A_prior)/(1+S·taucoupon), annuity (col I) built from the short + middle DFs. Cutovers at 1Y and 5Y mean nothing overlaps. Paste S490 zeros into column L for the Δz check.</t>
-        </is>
-      </c>
-      <c r="O5" s="13" t="inlineStr">
-        <is>
-          <t>sigma (bp/yr):</t>
-        </is>
-      </c>
-      <c r="P5" s="27" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q5" s="16" t="inlineStr">
-        <is>
-          <t>futures convexity CA = 0.5·sigma^2·t1·t2 (col T, bp)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="O6" s="4" t="inlineStr">
-        <is>
-          <t>MIDDLE SEGMENT — SR3 futures chain (1Y→5Y)</t>
-        </is>
-      </c>
-      <c r="Y6" s="4" t="inlineStr">
-        <is>
-          <t>Mid interp grid</t>
-        </is>
-      </c>
-    </row>
+          <t>Purely from the SOFR OIS quotes — no futures. SHORT (o/n–1Y): each OIS pays a single coupon, so DF = 1/(1+S·tau0). 18M–50Y: annual coupons, DF = (1−S·A_prior)/(1+S·taucoupon), where A_prior (col G) sums tau·DF over prior annual coupon dates (col I books this only at annual pillars; sub-annual and 18M add 0). Every input reprices to par. Col E par rates pull live from SOFR_OIS_Quotes. Paste Bloomberg S490 zeros into column L for the Δz check. For the Lehman-style build that puts SR3 futures in the 1Y–5Y middle, see the Bootstrap_Lehman tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -12206,61 +12171,6 @@
           <t>DF source</t>
         </is>
       </c>
-      <c r="O7" s="20" t="inlineStr">
-        <is>
-          <t>Contract</t>
-        </is>
-      </c>
-      <c r="P7" s="20" t="inlineStr">
-        <is>
-          <t>Fut start</t>
-        </is>
-      </c>
-      <c r="Q7" s="20" t="inlineStr">
-        <is>
-          <t>Fut end</t>
-        </is>
-      </c>
-      <c r="R7" s="20" t="inlineStr">
-        <is>
-          <t>tau eff (post-1Y)</t>
-        </is>
-      </c>
-      <c r="S7" s="20" t="inlineStr">
-        <is>
-          <t>Implied %</t>
-        </is>
-      </c>
-      <c r="T7" s="20" t="inlineStr">
-        <is>
-          <t>Convexity bp</t>
-        </is>
-      </c>
-      <c r="U7" s="20" t="inlineStr">
-        <is>
-          <t>Fwd</t>
-        </is>
-      </c>
-      <c r="V7" s="20" t="inlineStr">
-        <is>
-          <t>DF before</t>
-        </is>
-      </c>
-      <c r="W7" s="20" t="inlineStr">
-        <is>
-          <t>DF after</t>
-        </is>
-      </c>
-      <c r="Y7" s="20" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="Z7" s="20" t="inlineStr">
-        <is>
-          <t>DF</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -12272,7 +12182,7 @@
         <f>$B$4+7</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
         <f>(B8-$B$4)/365</f>
         <v/>
       </c>
@@ -12288,7 +12198,7 @@
       <c r="G8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <f>1/(1+(E8/100)*D8)</f>
         <v/>
       </c>
@@ -12303,8 +12213,8 @@
         <f>(1/H8-1)/D8*100</f>
         <v/>
       </c>
-      <c r="L8" s="30" t="n"/>
-      <c r="M8" s="31">
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="30">
         <f>IF(L8="","",(J8-L8)*100)</f>
         <v/>
       </c>
@@ -12312,50 +12222,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O8" s="6">
-        <f>'SOFR_Futures'!A7</f>
-        <v/>
-      </c>
-      <c r="P8" s="18">
-        <f>'SOFR_Futures'!H7</f>
-        <v/>
-      </c>
-      <c r="Q8" s="18">
-        <f>EDATE(P8,3)</f>
-        <v/>
-      </c>
-      <c r="R8" s="17">
-        <f>IF(OR(MONTH(P8)=3,MONTH(P8)=6,MONTH(P8)=9,MONTH(P8)=12),MAX(0,(Q8-MAX(P8,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S8" s="17">
-        <f>'SOFR_Futures'!F7</f>
-        <v/>
-      </c>
-      <c r="T8" s="28">
-        <f>0.5*$P$5^2*((P8-$B$4)/365)*((Q8-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U8" s="32">
-        <f>(S8-T8/100)/100</f>
-        <v/>
-      </c>
-      <c r="V8" s="33">
-        <f>$H$22</f>
-        <v/>
-      </c>
-      <c r="W8" s="33">
-        <f>V8/(1+U8*R8)</f>
-        <v/>
-      </c>
-      <c r="Y8" s="18">
-        <f>$B$22</f>
-        <v/>
-      </c>
-      <c r="Z8" s="33">
-        <f>$H$22</f>
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -12368,7 +12234,7 @@
         <f>$B$4+14</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <f>(B9-$B$4)/365</f>
         <v/>
       </c>
@@ -12385,7 +12251,7 @@
         <f>SUM($I$8:I8)</f>
         <v/>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <f>1/(1+(E9/100)*D9)</f>
         <v/>
       </c>
@@ -12400,8 +12266,8 @@
         <f>(H8/H9-1)/((B9-B8)/360)*100</f>
         <v/>
       </c>
-      <c r="L9" s="30" t="n"/>
-      <c r="M9" s="31">
+      <c r="L9" s="29" t="n"/>
+      <c r="M9" s="30">
         <f>IF(L9="","",(J9-L9)*100)</f>
         <v/>
       </c>
@@ -12409,50 +12275,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O9" s="6">
-        <f>'SOFR_Futures'!A8</f>
-        <v/>
-      </c>
-      <c r="P9" s="18">
-        <f>'SOFR_Futures'!H8</f>
-        <v/>
-      </c>
-      <c r="Q9" s="18">
-        <f>EDATE(P9,3)</f>
-        <v/>
-      </c>
-      <c r="R9" s="17">
-        <f>IF(OR(MONTH(P9)=3,MONTH(P9)=6,MONTH(P9)=9,MONTH(P9)=12),MAX(0,(Q9-MAX(P9,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S9" s="17">
-        <f>'SOFR_Futures'!F8</f>
-        <v/>
-      </c>
-      <c r="T9" s="28">
-        <f>0.5*$P$5^2*((P9-$B$4)/365)*((Q9-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U9" s="32">
-        <f>(S9-T9/100)/100</f>
-        <v/>
-      </c>
-      <c r="V9" s="33">
-        <f>W8</f>
-        <v/>
-      </c>
-      <c r="W9" s="33">
-        <f>V9/(1+U9*R9)</f>
-        <v/>
-      </c>
-      <c r="Y9" s="18">
-        <f>MAX(Q8,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z9" s="33">
-        <f>W8</f>
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -12465,7 +12287,7 @@
         <f>$B$4+21</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <f>(B10-$B$4)/365</f>
         <v/>
       </c>
@@ -12482,7 +12304,7 @@
         <f>SUM($I$8:I9)</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28">
         <f>1/(1+(E10/100)*D10)</f>
         <v/>
       </c>
@@ -12497,8 +12319,8 @@
         <f>(H9/H10-1)/((B10-B9)/360)*100</f>
         <v/>
       </c>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="31">
+      <c r="L10" s="29" t="n"/>
+      <c r="M10" s="30">
         <f>IF(L10="","",(J10-L10)*100)</f>
         <v/>
       </c>
@@ -12506,50 +12328,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O10" s="6">
-        <f>'SOFR_Futures'!A9</f>
-        <v/>
-      </c>
-      <c r="P10" s="18">
-        <f>'SOFR_Futures'!H9</f>
-        <v/>
-      </c>
-      <c r="Q10" s="18">
-        <f>EDATE(P10,3)</f>
-        <v/>
-      </c>
-      <c r="R10" s="17">
-        <f>IF(OR(MONTH(P10)=3,MONTH(P10)=6,MONTH(P10)=9,MONTH(P10)=12),MAX(0,(Q10-MAX(P10,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S10" s="17">
-        <f>'SOFR_Futures'!F9</f>
-        <v/>
-      </c>
-      <c r="T10" s="28">
-        <f>0.5*$P$5^2*((P10-$B$4)/365)*((Q10-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U10" s="32">
-        <f>(S10-T10/100)/100</f>
-        <v/>
-      </c>
-      <c r="V10" s="33">
-        <f>W9</f>
-        <v/>
-      </c>
-      <c r="W10" s="33">
-        <f>V10/(1+U10*R10)</f>
-        <v/>
-      </c>
-      <c r="Y10" s="18">
-        <f>MAX(Q9,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z10" s="33">
-        <f>W9</f>
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -12562,7 +12340,7 @@
         <f>EDATE($B$4,1)</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <f>(B11-$B$4)/365</f>
         <v/>
       </c>
@@ -12579,7 +12357,7 @@
         <f>SUM($I$8:I10)</f>
         <v/>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="28">
         <f>1/(1+(E11/100)*D11)</f>
         <v/>
       </c>
@@ -12594,8 +12372,8 @@
         <f>(H10/H11-1)/((B11-B10)/360)*100</f>
         <v/>
       </c>
-      <c r="L11" s="30" t="n"/>
-      <c r="M11" s="31">
+      <c r="L11" s="29" t="n"/>
+      <c r="M11" s="30">
         <f>IF(L11="","",(J11-L11)*100)</f>
         <v/>
       </c>
@@ -12603,50 +12381,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O11" s="6">
-        <f>'SOFR_Futures'!A10</f>
-        <v/>
-      </c>
-      <c r="P11" s="18">
-        <f>'SOFR_Futures'!H10</f>
-        <v/>
-      </c>
-      <c r="Q11" s="18">
-        <f>EDATE(P11,3)</f>
-        <v/>
-      </c>
-      <c r="R11" s="17">
-        <f>IF(OR(MONTH(P11)=3,MONTH(P11)=6,MONTH(P11)=9,MONTH(P11)=12),MAX(0,(Q11-MAX(P11,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S11" s="17">
-        <f>'SOFR_Futures'!F10</f>
-        <v/>
-      </c>
-      <c r="T11" s="28">
-        <f>0.5*$P$5^2*((P11-$B$4)/365)*((Q11-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U11" s="32">
-        <f>(S11-T11/100)/100</f>
-        <v/>
-      </c>
-      <c r="V11" s="33">
-        <f>W10</f>
-        <v/>
-      </c>
-      <c r="W11" s="33">
-        <f>V11/(1+U11*R11)</f>
-        <v/>
-      </c>
-      <c r="Y11" s="18">
-        <f>MAX(Q10,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z11" s="33">
-        <f>W10</f>
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -12659,7 +12393,7 @@
         <f>EDATE($B$4,2)</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <f>(B12-$B$4)/365</f>
         <v/>
       </c>
@@ -12676,7 +12410,7 @@
         <f>SUM($I$8:I11)</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="28">
         <f>1/(1+(E12/100)*D12)</f>
         <v/>
       </c>
@@ -12691,8 +12425,8 @@
         <f>(H11/H12-1)/((B12-B11)/360)*100</f>
         <v/>
       </c>
-      <c r="L12" s="30" t="n"/>
-      <c r="M12" s="31">
+      <c r="L12" s="29" t="n"/>
+      <c r="M12" s="30">
         <f>IF(L12="","",(J12-L12)*100)</f>
         <v/>
       </c>
@@ -12700,50 +12434,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O12" s="6">
-        <f>'SOFR_Futures'!A11</f>
-        <v/>
-      </c>
-      <c r="P12" s="18">
-        <f>'SOFR_Futures'!H11</f>
-        <v/>
-      </c>
-      <c r="Q12" s="18">
-        <f>EDATE(P12,3)</f>
-        <v/>
-      </c>
-      <c r="R12" s="17">
-        <f>IF(OR(MONTH(P12)=3,MONTH(P12)=6,MONTH(P12)=9,MONTH(P12)=12),MAX(0,(Q12-MAX(P12,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S12" s="17">
-        <f>'SOFR_Futures'!F11</f>
-        <v/>
-      </c>
-      <c r="T12" s="28">
-        <f>0.5*$P$5^2*((P12-$B$4)/365)*((Q12-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U12" s="32">
-        <f>(S12-T12/100)/100</f>
-        <v/>
-      </c>
-      <c r="V12" s="33">
-        <f>W11</f>
-        <v/>
-      </c>
-      <c r="W12" s="33">
-        <f>V12/(1+U12*R12)</f>
-        <v/>
-      </c>
-      <c r="Y12" s="18">
-        <f>MAX(Q11,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z12" s="33">
-        <f>W11</f>
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -12756,7 +12446,7 @@
         <f>EDATE($B$4,3)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <f>(B13-$B$4)/365</f>
         <v/>
       </c>
@@ -12773,7 +12463,7 @@
         <f>SUM($I$8:I12)</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="28">
         <f>1/(1+(E13/100)*D13)</f>
         <v/>
       </c>
@@ -12788,8 +12478,8 @@
         <f>(H12/H13-1)/((B13-B12)/360)*100</f>
         <v/>
       </c>
-      <c r="L13" s="30" t="n"/>
-      <c r="M13" s="31">
+      <c r="L13" s="29" t="n"/>
+      <c r="M13" s="30">
         <f>IF(L13="","",(J13-L13)*100)</f>
         <v/>
       </c>
@@ -12797,50 +12487,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O13" s="6">
-        <f>'SOFR_Futures'!A12</f>
-        <v/>
-      </c>
-      <c r="P13" s="18">
-        <f>'SOFR_Futures'!H12</f>
-        <v/>
-      </c>
-      <c r="Q13" s="18">
-        <f>EDATE(P13,3)</f>
-        <v/>
-      </c>
-      <c r="R13" s="17">
-        <f>IF(OR(MONTH(P13)=3,MONTH(P13)=6,MONTH(P13)=9,MONTH(P13)=12),MAX(0,(Q13-MAX(P13,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S13" s="17">
-        <f>'SOFR_Futures'!F12</f>
-        <v/>
-      </c>
-      <c r="T13" s="28">
-        <f>0.5*$P$5^2*((P13-$B$4)/365)*((Q13-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U13" s="32">
-        <f>(S13-T13/100)/100</f>
-        <v/>
-      </c>
-      <c r="V13" s="33">
-        <f>W12</f>
-        <v/>
-      </c>
-      <c r="W13" s="33">
-        <f>V13/(1+U13*R13)</f>
-        <v/>
-      </c>
-      <c r="Y13" s="18">
-        <f>MAX(Q12,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z13" s="33">
-        <f>W12</f>
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -12853,7 +12499,7 @@
         <f>EDATE($B$4,4)</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <f>(B14-$B$4)/365</f>
         <v/>
       </c>
@@ -12870,7 +12516,7 @@
         <f>SUM($I$8:I13)</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="28">
         <f>1/(1+(E14/100)*D14)</f>
         <v/>
       </c>
@@ -12885,8 +12531,8 @@
         <f>(H13/H14-1)/((B14-B13)/360)*100</f>
         <v/>
       </c>
-      <c r="L14" s="30" t="n"/>
-      <c r="M14" s="31">
+      <c r="L14" s="29" t="n"/>
+      <c r="M14" s="30">
         <f>IF(L14="","",(J14-L14)*100)</f>
         <v/>
       </c>
@@ -12894,50 +12540,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O14" s="6">
-        <f>'SOFR_Futures'!A13</f>
-        <v/>
-      </c>
-      <c r="P14" s="18">
-        <f>'SOFR_Futures'!H13</f>
-        <v/>
-      </c>
-      <c r="Q14" s="18">
-        <f>EDATE(P14,3)</f>
-        <v/>
-      </c>
-      <c r="R14" s="17">
-        <f>IF(OR(MONTH(P14)=3,MONTH(P14)=6,MONTH(P14)=9,MONTH(P14)=12),MAX(0,(Q14-MAX(P14,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S14" s="17">
-        <f>'SOFR_Futures'!F13</f>
-        <v/>
-      </c>
-      <c r="T14" s="28">
-        <f>0.5*$P$5^2*((P14-$B$4)/365)*((Q14-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U14" s="32">
-        <f>(S14-T14/100)/100</f>
-        <v/>
-      </c>
-      <c r="V14" s="33">
-        <f>W13</f>
-        <v/>
-      </c>
-      <c r="W14" s="33">
-        <f>V14/(1+U14*R14)</f>
-        <v/>
-      </c>
-      <c r="Y14" s="18">
-        <f>MAX(Q13,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z14" s="33">
-        <f>W13</f>
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -12950,7 +12552,7 @@
         <f>EDATE($B$4,5)</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <f>(B15-$B$4)/365</f>
         <v/>
       </c>
@@ -12967,7 +12569,7 @@
         <f>SUM($I$8:I14)</f>
         <v/>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="28">
         <f>1/(1+(E15/100)*D15)</f>
         <v/>
       </c>
@@ -12982,8 +12584,8 @@
         <f>(H14/H15-1)/((B15-B14)/360)*100</f>
         <v/>
       </c>
-      <c r="L15" s="30" t="n"/>
-      <c r="M15" s="31">
+      <c r="L15" s="29" t="n"/>
+      <c r="M15" s="30">
         <f>IF(L15="","",(J15-L15)*100)</f>
         <v/>
       </c>
@@ -12991,50 +12593,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O15" s="6">
-        <f>'SOFR_Futures'!A14</f>
-        <v/>
-      </c>
-      <c r="P15" s="18">
-        <f>'SOFR_Futures'!H14</f>
-        <v/>
-      </c>
-      <c r="Q15" s="18">
-        <f>EDATE(P15,3)</f>
-        <v/>
-      </c>
-      <c r="R15" s="17">
-        <f>IF(OR(MONTH(P15)=3,MONTH(P15)=6,MONTH(P15)=9,MONTH(P15)=12),MAX(0,(Q15-MAX(P15,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S15" s="17">
-        <f>'SOFR_Futures'!F14</f>
-        <v/>
-      </c>
-      <c r="T15" s="28">
-        <f>0.5*$P$5^2*((P15-$B$4)/365)*((Q15-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U15" s="32">
-        <f>(S15-T15/100)/100</f>
-        <v/>
-      </c>
-      <c r="V15" s="33">
-        <f>W14</f>
-        <v/>
-      </c>
-      <c r="W15" s="33">
-        <f>V15/(1+U15*R15)</f>
-        <v/>
-      </c>
-      <c r="Y15" s="18">
-        <f>MAX(Q14,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z15" s="33">
-        <f>W14</f>
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -13047,7 +12605,7 @@
         <f>EDATE($B$4,6)</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>(B16-$B$4)/365</f>
         <v/>
       </c>
@@ -13064,7 +12622,7 @@
         <f>SUM($I$8:I15)</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="28">
         <f>1/(1+(E16/100)*D16)</f>
         <v/>
       </c>
@@ -13079,8 +12637,8 @@
         <f>(H15/H16-1)/((B16-B15)/360)*100</f>
         <v/>
       </c>
-      <c r="L16" s="30" t="n"/>
-      <c r="M16" s="31">
+      <c r="L16" s="29" t="n"/>
+      <c r="M16" s="30">
         <f>IF(L16="","",(J16-L16)*100)</f>
         <v/>
       </c>
@@ -13088,50 +12646,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O16" s="6">
-        <f>'SOFR_Futures'!A15</f>
-        <v/>
-      </c>
-      <c r="P16" s="18">
-        <f>'SOFR_Futures'!H15</f>
-        <v/>
-      </c>
-      <c r="Q16" s="18">
-        <f>EDATE(P16,3)</f>
-        <v/>
-      </c>
-      <c r="R16" s="17">
-        <f>IF(OR(MONTH(P16)=3,MONTH(P16)=6,MONTH(P16)=9,MONTH(P16)=12),MAX(0,(Q16-MAX(P16,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S16" s="17">
-        <f>'SOFR_Futures'!F15</f>
-        <v/>
-      </c>
-      <c r="T16" s="28">
-        <f>0.5*$P$5^2*((P16-$B$4)/365)*((Q16-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U16" s="32">
-        <f>(S16-T16/100)/100</f>
-        <v/>
-      </c>
-      <c r="V16" s="33">
-        <f>W15</f>
-        <v/>
-      </c>
-      <c r="W16" s="33">
-        <f>V16/(1+U16*R16)</f>
-        <v/>
-      </c>
-      <c r="Y16" s="18">
-        <f>MAX(Q15,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z16" s="33">
-        <f>W15</f>
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -13144,7 +12658,7 @@
         <f>EDATE($B$4,7)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>(B17-$B$4)/365</f>
         <v/>
       </c>
@@ -13161,7 +12675,7 @@
         <f>SUM($I$8:I16)</f>
         <v/>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="28">
         <f>1/(1+(E17/100)*D17)</f>
         <v/>
       </c>
@@ -13176,8 +12690,8 @@
         <f>(H16/H17-1)/((B17-B16)/360)*100</f>
         <v/>
       </c>
-      <c r="L17" s="30" t="n"/>
-      <c r="M17" s="31">
+      <c r="L17" s="29" t="n"/>
+      <c r="M17" s="30">
         <f>IF(L17="","",(J17-L17)*100)</f>
         <v/>
       </c>
@@ -13185,50 +12699,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O17" s="6">
-        <f>'SOFR_Futures'!A16</f>
-        <v/>
-      </c>
-      <c r="P17" s="18">
-        <f>'SOFR_Futures'!H16</f>
-        <v/>
-      </c>
-      <c r="Q17" s="18">
-        <f>EDATE(P17,3)</f>
-        <v/>
-      </c>
-      <c r="R17" s="17">
-        <f>IF(OR(MONTH(P17)=3,MONTH(P17)=6,MONTH(P17)=9,MONTH(P17)=12),MAX(0,(Q17-MAX(P17,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S17" s="17">
-        <f>'SOFR_Futures'!F16</f>
-        <v/>
-      </c>
-      <c r="T17" s="28">
-        <f>0.5*$P$5^2*((P17-$B$4)/365)*((Q17-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U17" s="32">
-        <f>(S17-T17/100)/100</f>
-        <v/>
-      </c>
-      <c r="V17" s="33">
-        <f>W16</f>
-        <v/>
-      </c>
-      <c r="W17" s="33">
-        <f>V17/(1+U17*R17)</f>
-        <v/>
-      </c>
-      <c r="Y17" s="18">
-        <f>MAX(Q16,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z17" s="33">
-        <f>W16</f>
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -13241,7 +12711,7 @@
         <f>EDATE($B$4,8)</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <f>(B18-$B$4)/365</f>
         <v/>
       </c>
@@ -13258,7 +12728,7 @@
         <f>SUM($I$8:I17)</f>
         <v/>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <f>1/(1+(E18/100)*D18)</f>
         <v/>
       </c>
@@ -13273,8 +12743,8 @@
         <f>(H17/H18-1)/((B18-B17)/360)*100</f>
         <v/>
       </c>
-      <c r="L18" s="30" t="n"/>
-      <c r="M18" s="31">
+      <c r="L18" s="29" t="n"/>
+      <c r="M18" s="30">
         <f>IF(L18="","",(J18-L18)*100)</f>
         <v/>
       </c>
@@ -13282,50 +12752,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O18" s="6">
-        <f>'SOFR_Futures'!A17</f>
-        <v/>
-      </c>
-      <c r="P18" s="18">
-        <f>'SOFR_Futures'!H17</f>
-        <v/>
-      </c>
-      <c r="Q18" s="18">
-        <f>EDATE(P18,3)</f>
-        <v/>
-      </c>
-      <c r="R18" s="17">
-        <f>IF(OR(MONTH(P18)=3,MONTH(P18)=6,MONTH(P18)=9,MONTH(P18)=12),MAX(0,(Q18-MAX(P18,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S18" s="17">
-        <f>'SOFR_Futures'!F17</f>
-        <v/>
-      </c>
-      <c r="T18" s="28">
-        <f>0.5*$P$5^2*((P18-$B$4)/365)*((Q18-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U18" s="32">
-        <f>(S18-T18/100)/100</f>
-        <v/>
-      </c>
-      <c r="V18" s="33">
-        <f>W17</f>
-        <v/>
-      </c>
-      <c r="W18" s="33">
-        <f>V18/(1+U18*R18)</f>
-        <v/>
-      </c>
-      <c r="Y18" s="18">
-        <f>MAX(Q17,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z18" s="33">
-        <f>W17</f>
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -13338,7 +12764,7 @@
         <f>EDATE($B$4,9)</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <f>(B19-$B$4)/365</f>
         <v/>
       </c>
@@ -13355,7 +12781,7 @@
         <f>SUM($I$8:I18)</f>
         <v/>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="28">
         <f>1/(1+(E19/100)*D19)</f>
         <v/>
       </c>
@@ -13370,8 +12796,8 @@
         <f>(H18/H19-1)/((B19-B18)/360)*100</f>
         <v/>
       </c>
-      <c r="L19" s="30" t="n"/>
-      <c r="M19" s="31">
+      <c r="L19" s="29" t="n"/>
+      <c r="M19" s="30">
         <f>IF(L19="","",(J19-L19)*100)</f>
         <v/>
       </c>
@@ -13379,50 +12805,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O19" s="6">
-        <f>'SOFR_Futures'!A18</f>
-        <v/>
-      </c>
-      <c r="P19" s="18">
-        <f>'SOFR_Futures'!H18</f>
-        <v/>
-      </c>
-      <c r="Q19" s="18">
-        <f>EDATE(P19,3)</f>
-        <v/>
-      </c>
-      <c r="R19" s="17">
-        <f>IF(OR(MONTH(P19)=3,MONTH(P19)=6,MONTH(P19)=9,MONTH(P19)=12),MAX(0,(Q19-MAX(P19,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S19" s="17">
-        <f>'SOFR_Futures'!F18</f>
-        <v/>
-      </c>
-      <c r="T19" s="28">
-        <f>0.5*$P$5^2*((P19-$B$4)/365)*((Q19-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U19" s="32">
-        <f>(S19-T19/100)/100</f>
-        <v/>
-      </c>
-      <c r="V19" s="33">
-        <f>W18</f>
-        <v/>
-      </c>
-      <c r="W19" s="33">
-        <f>V19/(1+U19*R19)</f>
-        <v/>
-      </c>
-      <c r="Y19" s="18">
-        <f>MAX(Q18,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z19" s="33">
-        <f>W18</f>
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -13435,7 +12817,7 @@
         <f>EDATE($B$4,10)</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <f>(B20-$B$4)/365</f>
         <v/>
       </c>
@@ -13452,7 +12834,7 @@
         <f>SUM($I$8:I19)</f>
         <v/>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="28">
         <f>1/(1+(E20/100)*D20)</f>
         <v/>
       </c>
@@ -13467,8 +12849,8 @@
         <f>(H19/H20-1)/((B20-B19)/360)*100</f>
         <v/>
       </c>
-      <c r="L20" s="30" t="n"/>
-      <c r="M20" s="31">
+      <c r="L20" s="29" t="n"/>
+      <c r="M20" s="30">
         <f>IF(L20="","",(J20-L20)*100)</f>
         <v/>
       </c>
@@ -13476,50 +12858,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O20" s="6">
-        <f>'SOFR_Futures'!A19</f>
-        <v/>
-      </c>
-      <c r="P20" s="18">
-        <f>'SOFR_Futures'!H19</f>
-        <v/>
-      </c>
-      <c r="Q20" s="18">
-        <f>EDATE(P20,3)</f>
-        <v/>
-      </c>
-      <c r="R20" s="17">
-        <f>IF(OR(MONTH(P20)=3,MONTH(P20)=6,MONTH(P20)=9,MONTH(P20)=12),MAX(0,(Q20-MAX(P20,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S20" s="17">
-        <f>'SOFR_Futures'!F19</f>
-        <v/>
-      </c>
-      <c r="T20" s="28">
-        <f>0.5*$P$5^2*((P20-$B$4)/365)*((Q20-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U20" s="32">
-        <f>(S20-T20/100)/100</f>
-        <v/>
-      </c>
-      <c r="V20" s="33">
-        <f>W19</f>
-        <v/>
-      </c>
-      <c r="W20" s="33">
-        <f>V20/(1+U20*R20)</f>
-        <v/>
-      </c>
-      <c r="Y20" s="18">
-        <f>MAX(Q19,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z20" s="33">
-        <f>W19</f>
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -13532,7 +12870,7 @@
         <f>EDATE($B$4,11)</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>(B21-$B$4)/365</f>
         <v/>
       </c>
@@ -13549,7 +12887,7 @@
         <f>SUM($I$8:I20)</f>
         <v/>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28">
         <f>1/(1+(E21/100)*D21)</f>
         <v/>
       </c>
@@ -13564,8 +12902,8 @@
         <f>(H20/H21-1)/((B21-B20)/360)*100</f>
         <v/>
       </c>
-      <c r="L21" s="30" t="n"/>
-      <c r="M21" s="31">
+      <c r="L21" s="29" t="n"/>
+      <c r="M21" s="30">
         <f>IF(L21="","",(J21-L21)*100)</f>
         <v/>
       </c>
@@ -13573,50 +12911,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O21" s="6">
-        <f>'SOFR_Futures'!A20</f>
-        <v/>
-      </c>
-      <c r="P21" s="18">
-        <f>'SOFR_Futures'!H20</f>
-        <v/>
-      </c>
-      <c r="Q21" s="18">
-        <f>EDATE(P21,3)</f>
-        <v/>
-      </c>
-      <c r="R21" s="17">
-        <f>IF(OR(MONTH(P21)=3,MONTH(P21)=6,MONTH(P21)=9,MONTH(P21)=12),MAX(0,(Q21-MAX(P21,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S21" s="17">
-        <f>'SOFR_Futures'!F20</f>
-        <v/>
-      </c>
-      <c r="T21" s="28">
-        <f>0.5*$P$5^2*((P21-$B$4)/365)*((Q21-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U21" s="32">
-        <f>(S21-T21/100)/100</f>
-        <v/>
-      </c>
-      <c r="V21" s="33">
-        <f>W20</f>
-        <v/>
-      </c>
-      <c r="W21" s="33">
-        <f>V21/(1+U21*R21)</f>
-        <v/>
-      </c>
-      <c r="Y21" s="18">
-        <f>MAX(Q20,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z21" s="33">
-        <f>W20</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -13629,7 +12923,7 @@
         <f>EDATE($B$4,12)</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>(B22-$B$4)/365</f>
         <v/>
       </c>
@@ -13649,7 +12943,7 @@
         <f>SUM($I$8:I21)</f>
         <v/>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="28">
         <f>1/(1+(E22/100)*D22)</f>
         <v/>
       </c>
@@ -13665,8 +12959,8 @@
         <f>(H21/H22-1)/((B22-B21)/360)*100</f>
         <v/>
       </c>
-      <c r="L22" s="30" t="n"/>
-      <c r="M22" s="31">
+      <c r="L22" s="29" t="n"/>
+      <c r="M22" s="30">
         <f>IF(L22="","",(J22-L22)*100)</f>
         <v/>
       </c>
@@ -13674,50 +12968,6 @@
         <is>
           <t>short OIS</t>
         </is>
-      </c>
-      <c r="O22" s="6">
-        <f>'SOFR_Futures'!A21</f>
-        <v/>
-      </c>
-      <c r="P22" s="18">
-        <f>'SOFR_Futures'!H21</f>
-        <v/>
-      </c>
-      <c r="Q22" s="18">
-        <f>EDATE(P22,3)</f>
-        <v/>
-      </c>
-      <c r="R22" s="17">
-        <f>IF(OR(MONTH(P22)=3,MONTH(P22)=6,MONTH(P22)=9,MONTH(P22)=12),MAX(0,(Q22-MAX(P22,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S22" s="17">
-        <f>'SOFR_Futures'!F21</f>
-        <v/>
-      </c>
-      <c r="T22" s="28">
-        <f>0.5*$P$5^2*((P22-$B$4)/365)*((Q22-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U22" s="32">
-        <f>(S22-T22/100)/100</f>
-        <v/>
-      </c>
-      <c r="V22" s="33">
-        <f>W21</f>
-        <v/>
-      </c>
-      <c r="W22" s="33">
-        <f>V22/(1+U22*R22)</f>
-        <v/>
-      </c>
-      <c r="Y22" s="18">
-        <f>MAX(Q21,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z22" s="33">
-        <f>W21</f>
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -13730,7 +12980,7 @@
         <f>EDATE($B$4,18)</f>
         <v/>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <f>(B23-$B$4)/365</f>
         <v/>
       </c>
@@ -13750,8 +13000,8 @@
         <f>SUM($I$8:I22)</f>
         <v/>
       </c>
-      <c r="H23" s="29">
-        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))))-((1-(E23/100)*G23)/(1+(E23/100)*F23)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))),((1-(E23/100)*G23)/(1+(E23/100)*F23))),((1-(E23/100)*G23)/(1+(E23/100)*F23)))</f>
+      <c r="H23" s="28">
+        <f>(1-(E23/100)*G23)/(1+(E23/100)*F23)</f>
         <v/>
       </c>
       <c r="I23" s="17" t="n">
@@ -13765,58 +13015,15 @@
         <f>(H22/H23-1)/((B23-B22)/360)*100</f>
         <v/>
       </c>
-      <c r="L23" s="30" t="n"/>
-      <c r="M23" s="31">
+      <c r="L23" s="29" t="n"/>
+      <c r="M23" s="30">
         <f>IF(L23="","",(J23-L23)*100)</f>
         <v/>
       </c>
-      <c r="N23" s="6">
-        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))))-((1-(E23/100)*G23)/(1+(E23/100)*F23)))&lt;0.03),"SR3 futures","OIS fallback")</f>
-        <v/>
-      </c>
-      <c r="O23" s="6">
-        <f>'SOFR_Futures'!A22</f>
-        <v/>
-      </c>
-      <c r="P23" s="18">
-        <f>'SOFR_Futures'!H22</f>
-        <v/>
-      </c>
-      <c r="Q23" s="18">
-        <f>EDATE(P23,3)</f>
-        <v/>
-      </c>
-      <c r="R23" s="17">
-        <f>IF(OR(MONTH(P23)=3,MONTH(P23)=6,MONTH(P23)=9,MONTH(P23)=12),MAX(0,(Q23-MAX(P23,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S23" s="17">
-        <f>'SOFR_Futures'!F22</f>
-        <v/>
-      </c>
-      <c r="T23" s="28">
-        <f>0.5*$P$5^2*((P23-$B$4)/365)*((Q23-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U23" s="32">
-        <f>(S23-T23/100)/100</f>
-        <v/>
-      </c>
-      <c r="V23" s="33">
-        <f>W22</f>
-        <v/>
-      </c>
-      <c r="W23" s="33">
-        <f>V23/(1+U23*R23)</f>
-        <v/>
-      </c>
-      <c r="Y23" s="18">
-        <f>MAX(Q22,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z23" s="33">
-        <f>W22</f>
-        <v/>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -13829,7 +13036,7 @@
         <f>EDATE($B$4,24)</f>
         <v/>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="27">
         <f>(B24-$B$4)/365</f>
         <v/>
       </c>
@@ -13849,8 +13056,8 @@
         <f>SUM($I$8:I23)</f>
         <v/>
       </c>
-      <c r="H24" s="29">
-        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))))-((1-(E24/100)*G24)/(1+(E24/100)*F24)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))),((1-(E24/100)*G24)/(1+(E24/100)*F24))),((1-(E24/100)*G24)/(1+(E24/100)*F24)))</f>
+      <c r="H24" s="28">
+        <f>(1-(E24/100)*G24)/(1+(E24/100)*F24)</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -13865,58 +13072,15 @@
         <f>(H23/H24-1)/((B24-B23)/360)*100</f>
         <v/>
       </c>
-      <c r="L24" s="30" t="n"/>
-      <c r="M24" s="31">
+      <c r="L24" s="29" t="n"/>
+      <c r="M24" s="30">
         <f>IF(L24="","",(J24-L24)*100)</f>
         <v/>
       </c>
-      <c r="N24" s="6">
-        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))))-((1-(E24/100)*G24)/(1+(E24/100)*F24)))&lt;0.03),"SR3 futures","OIS fallback")</f>
-        <v/>
-      </c>
-      <c r="O24" s="6">
-        <f>'SOFR_Futures'!A23</f>
-        <v/>
-      </c>
-      <c r="P24" s="18">
-        <f>'SOFR_Futures'!H23</f>
-        <v/>
-      </c>
-      <c r="Q24" s="18">
-        <f>EDATE(P24,3)</f>
-        <v/>
-      </c>
-      <c r="R24" s="17">
-        <f>IF(OR(MONTH(P24)=3,MONTH(P24)=6,MONTH(P24)=9,MONTH(P24)=12),MAX(0,(Q24-MAX(P24,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S24" s="17">
-        <f>'SOFR_Futures'!F23</f>
-        <v/>
-      </c>
-      <c r="T24" s="28">
-        <f>0.5*$P$5^2*((P24-$B$4)/365)*((Q24-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U24" s="32">
-        <f>(S24-T24/100)/100</f>
-        <v/>
-      </c>
-      <c r="V24" s="33">
-        <f>W23</f>
-        <v/>
-      </c>
-      <c r="W24" s="33">
-        <f>V24/(1+U24*R24)</f>
-        <v/>
-      </c>
-      <c r="Y24" s="18">
-        <f>MAX(Q23,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z24" s="33">
-        <f>W23</f>
-        <v/>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -13929,7 +13093,7 @@
         <f>EDATE($B$4,36)</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="27">
         <f>(B25-$B$4)/365</f>
         <v/>
       </c>
@@ -13949,8 +13113,8 @@
         <f>SUM($I$8:I24)</f>
         <v/>
       </c>
-      <c r="H25" s="29">
-        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))))-((1-(E25/100)*G25)/(1+(E25/100)*F25)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))),((1-(E25/100)*G25)/(1+(E25/100)*F25))),((1-(E25/100)*G25)/(1+(E25/100)*F25)))</f>
+      <c r="H25" s="28">
+        <f>(1-(E25/100)*G25)/(1+(E25/100)*F25)</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -13965,58 +13129,15 @@
         <f>(H24/H25-1)/((B25-B24)/360)*100</f>
         <v/>
       </c>
-      <c r="L25" s="30" t="n"/>
-      <c r="M25" s="31">
+      <c r="L25" s="29" t="n"/>
+      <c r="M25" s="30">
         <f>IF(L25="","",(J25-L25)*100)</f>
         <v/>
       </c>
-      <c r="N25" s="6">
-        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))))-((1-(E25/100)*G25)/(1+(E25/100)*F25)))&lt;0.03),"SR3 futures","OIS fallback")</f>
-        <v/>
-      </c>
-      <c r="O25" s="6">
-        <f>'SOFR_Futures'!A24</f>
-        <v/>
-      </c>
-      <c r="P25" s="18">
-        <f>'SOFR_Futures'!H24</f>
-        <v/>
-      </c>
-      <c r="Q25" s="18">
-        <f>EDATE(P25,3)</f>
-        <v/>
-      </c>
-      <c r="R25" s="17">
-        <f>IF(OR(MONTH(P25)=3,MONTH(P25)=6,MONTH(P25)=9,MONTH(P25)=12),MAX(0,(Q25-MAX(P25,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S25" s="17">
-        <f>'SOFR_Futures'!F24</f>
-        <v/>
-      </c>
-      <c r="T25" s="28">
-        <f>0.5*$P$5^2*((P25-$B$4)/365)*((Q25-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U25" s="32">
-        <f>(S25-T25/100)/100</f>
-        <v/>
-      </c>
-      <c r="V25" s="33">
-        <f>W24</f>
-        <v/>
-      </c>
-      <c r="W25" s="33">
-        <f>V25/(1+U25*R25)</f>
-        <v/>
-      </c>
-      <c r="Y25" s="18">
-        <f>MAX(Q24,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z25" s="33">
-        <f>W24</f>
-        <v/>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -14029,7 +13150,7 @@
         <f>EDATE($B$4,48)</f>
         <v/>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="27">
         <f>(B26-$B$4)/365</f>
         <v/>
       </c>
@@ -14049,8 +13170,8 @@
         <f>SUM($I$8:I25)</f>
         <v/>
       </c>
-      <c r="H26" s="29">
-        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))))-((1-(E26/100)*G26)/(1+(E26/100)*F26)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))),((1-(E26/100)*G26)/(1+(E26/100)*F26))),((1-(E26/100)*G26)/(1+(E26/100)*F26)))</f>
+      <c r="H26" s="28">
+        <f>(1-(E26/100)*G26)/(1+(E26/100)*F26)</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -14065,58 +13186,15 @@
         <f>(H25/H26-1)/((B26-B25)/360)*100</f>
         <v/>
       </c>
-      <c r="L26" s="30" t="n"/>
-      <c r="M26" s="31">
+      <c r="L26" s="29" t="n"/>
+      <c r="M26" s="30">
         <f>IF(L26="","",(J26-L26)*100)</f>
         <v/>
       </c>
-      <c r="N26" s="6">
-        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))))-((1-(E26/100)*G26)/(1+(E26/100)*F26)))&lt;0.03),"SR3 futures","OIS fallback")</f>
-        <v/>
-      </c>
-      <c r="O26" s="6">
-        <f>'SOFR_Futures'!A25</f>
-        <v/>
-      </c>
-      <c r="P26" s="18">
-        <f>'SOFR_Futures'!H25</f>
-        <v/>
-      </c>
-      <c r="Q26" s="18">
-        <f>EDATE(P26,3)</f>
-        <v/>
-      </c>
-      <c r="R26" s="17">
-        <f>IF(OR(MONTH(P26)=3,MONTH(P26)=6,MONTH(P26)=9,MONTH(P26)=12),MAX(0,(Q26-MAX(P26,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S26" s="17">
-        <f>'SOFR_Futures'!F25</f>
-        <v/>
-      </c>
-      <c r="T26" s="28">
-        <f>0.5*$P$5^2*((P26-$B$4)/365)*((Q26-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U26" s="32">
-        <f>(S26-T26/100)/100</f>
-        <v/>
-      </c>
-      <c r="V26" s="33">
-        <f>W25</f>
-        <v/>
-      </c>
-      <c r="W26" s="33">
-        <f>V26/(1+U26*R26)</f>
-        <v/>
-      </c>
-      <c r="Y26" s="18">
-        <f>MAX(Q25,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z26" s="33">
-        <f>W25</f>
-        <v/>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -14129,7 +13207,7 @@
         <f>EDATE($B$4,60)</f>
         <v/>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="27">
         <f>(B27-$B$4)/365</f>
         <v/>
       </c>
@@ -14149,8 +13227,8 @@
         <f>SUM($I$8:I26)</f>
         <v/>
       </c>
-      <c r="H27" s="29">
-        <f>IFERROR(IF(ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))))-((1-(E27/100)*G27)/(1+(E27/100)*F27)))&lt;0.03,(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))),((1-(E27/100)*G27)/(1+(E27/100)*F27))),((1-(E27/100)*G27)/(1+(E27/100)*F27)))</f>
+      <c r="H27" s="28">
+        <f>(1-(E27/100)*G27)/(1+(E27/100)*F27)</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -14165,58 +13243,15 @@
         <f>(H26/H27-1)/((B27-B26)/360)*100</f>
         <v/>
       </c>
-      <c r="L27" s="30" t="n"/>
-      <c r="M27" s="31">
+      <c r="L27" s="29" t="n"/>
+      <c r="M27" s="30">
         <f>IF(L27="","",(J27-L27)*100)</f>
         <v/>
       </c>
-      <c r="N27" s="6">
-        <f>IF(AND(ISNUMBER(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))),ABS((IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))))-((1-(E27/100)*G27)/(1+(E27/100)*F27)))&lt;0.03),"SR3 futures","OIS fallback")</f>
-        <v/>
-      </c>
-      <c r="O27" s="6">
-        <f>'SOFR_Futures'!A26</f>
-        <v/>
-      </c>
-      <c r="P27" s="18">
-        <f>'SOFR_Futures'!H26</f>
-        <v/>
-      </c>
-      <c r="Q27" s="18">
-        <f>EDATE(P27,3)</f>
-        <v/>
-      </c>
-      <c r="R27" s="17">
-        <f>IF(OR(MONTH(P27)=3,MONTH(P27)=6,MONTH(P27)=9,MONTH(P27)=12),MAX(0,(Q27-MAX(P27,$B$22))/360),0)</f>
-        <v/>
-      </c>
-      <c r="S27" s="17">
-        <f>'SOFR_Futures'!F26</f>
-        <v/>
-      </c>
-      <c r="T27" s="28">
-        <f>0.5*$P$5^2*((P27-$B$4)/365)*((Q27-$B$4)/365)/10000</f>
-        <v/>
-      </c>
-      <c r="U27" s="32">
-        <f>(S27-T27/100)/100</f>
-        <v/>
-      </c>
-      <c r="V27" s="33">
-        <f>W26</f>
-        <v/>
-      </c>
-      <c r="W27" s="33">
-        <f>V27/(1+U27*R27)</f>
-        <v/>
-      </c>
-      <c r="Y27" s="18">
-        <f>MAX(Q26,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z27" s="33">
-        <f>W26</f>
-        <v/>
+      <c r="N27" s="6" t="inlineStr">
+        <is>
+          <t>OIS swap</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -14229,7 +13264,7 @@
         <f>EDATE($B$4,72)</f>
         <v/>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="27">
         <f>(B28-$B$4)/365</f>
         <v/>
       </c>
@@ -14249,7 +13284,7 @@
         <f>SUM($I$8:I27)</f>
         <v/>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="28">
         <f>(1-(E28/100)*G28)/(1+(E28/100)*F28)</f>
         <v/>
       </c>
@@ -14265,8 +13300,8 @@
         <f>(H27/H28-1)/((B28-B27)/360)*100</f>
         <v/>
       </c>
-      <c r="L28" s="30" t="n"/>
-      <c r="M28" s="31">
+      <c r="L28" s="29" t="n"/>
+      <c r="M28" s="30">
         <f>IF(L28="","",(J28-L28)*100)</f>
         <v/>
       </c>
@@ -14274,14 +13309,6 @@
         <is>
           <t>OIS swap</t>
         </is>
-      </c>
-      <c r="Y28" s="18">
-        <f>MAX(Q27,$B$22)</f>
-        <v/>
-      </c>
-      <c r="Z28" s="33">
-        <f>W27</f>
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -14294,7 +13321,7 @@
         <f>EDATE($B$4,84)</f>
         <v/>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <f>(B29-$B$4)/365</f>
         <v/>
       </c>
@@ -14314,7 +13341,7 @@
         <f>SUM($I$8:I28)</f>
         <v/>
       </c>
-      <c r="H29" s="29">
+      <c r="H29" s="28">
         <f>(1-(E29/100)*G29)/(1+(E29/100)*F29)</f>
         <v/>
       </c>
@@ -14330,8 +13357,8 @@
         <f>(H28/H29-1)/((B29-B28)/360)*100</f>
         <v/>
       </c>
-      <c r="L29" s="30" t="n"/>
-      <c r="M29" s="31">
+      <c r="L29" s="29" t="n"/>
+      <c r="M29" s="30">
         <f>IF(L29="","",(J29-L29)*100)</f>
         <v/>
       </c>
@@ -14351,7 +13378,7 @@
         <f>EDATE($B$4,96)</f>
         <v/>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="27">
         <f>(B30-$B$4)/365</f>
         <v/>
       </c>
@@ -14371,7 +13398,7 @@
         <f>SUM($I$8:I29)</f>
         <v/>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="28">
         <f>(1-(E30/100)*G30)/(1+(E30/100)*F30)</f>
         <v/>
       </c>
@@ -14387,8 +13414,8 @@
         <f>(H29/H30-1)/((B30-B29)/360)*100</f>
         <v/>
       </c>
-      <c r="L30" s="30" t="n"/>
-      <c r="M30" s="31">
+      <c r="L30" s="29" t="n"/>
+      <c r="M30" s="30">
         <f>IF(L30="","",(J30-L30)*100)</f>
         <v/>
       </c>
@@ -14408,7 +13435,7 @@
         <f>EDATE($B$4,108)</f>
         <v/>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <f>(B31-$B$4)/365</f>
         <v/>
       </c>
@@ -14428,7 +13455,7 @@
         <f>SUM($I$8:I30)</f>
         <v/>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="28">
         <f>(1-(E31/100)*G31)/(1+(E31/100)*F31)</f>
         <v/>
       </c>
@@ -14444,8 +13471,8 @@
         <f>(H30/H31-1)/((B31-B30)/360)*100</f>
         <v/>
       </c>
-      <c r="L31" s="30" t="n"/>
-      <c r="M31" s="31">
+      <c r="L31" s="29" t="n"/>
+      <c r="M31" s="30">
         <f>IF(L31="","",(J31-L31)*100)</f>
         <v/>
       </c>
@@ -14465,7 +13492,7 @@
         <f>EDATE($B$4,120)</f>
         <v/>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="27">
         <f>(B32-$B$4)/365</f>
         <v/>
       </c>
@@ -14485,7 +13512,7 @@
         <f>SUM($I$8:I31)</f>
         <v/>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="28">
         <f>(1-(E32/100)*G32)/(1+(E32/100)*F32)</f>
         <v/>
       </c>
@@ -14501,8 +13528,8 @@
         <f>(H31/H32-1)/((B32-B31)/360)*100</f>
         <v/>
       </c>
-      <c r="L32" s="30" t="n"/>
-      <c r="M32" s="31">
+      <c r="L32" s="29" t="n"/>
+      <c r="M32" s="30">
         <f>IF(L32="","",(J32-L32)*100)</f>
         <v/>
       </c>
@@ -14522,7 +13549,7 @@
         <f>EDATE($B$4,144)</f>
         <v/>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <f>(B33-$B$4)/365</f>
         <v/>
       </c>
@@ -14542,7 +13569,7 @@
         <f>SUM($I$8:I32)</f>
         <v/>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="28">
         <f>(1-(E33/100)*G33)/(1+(E33/100)*F33)</f>
         <v/>
       </c>
@@ -14558,8 +13585,8 @@
         <f>(H32/H33-1)/((B33-B32)/360)*100</f>
         <v/>
       </c>
-      <c r="L33" s="30" t="n"/>
-      <c r="M33" s="31">
+      <c r="L33" s="29" t="n"/>
+      <c r="M33" s="30">
         <f>IF(L33="","",(J33-L33)*100)</f>
         <v/>
       </c>
@@ -14579,7 +13606,7 @@
         <f>EDATE($B$4,180)</f>
         <v/>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="27">
         <f>(B34-$B$4)/365</f>
         <v/>
       </c>
@@ -14599,7 +13626,7 @@
         <f>SUM($I$8:I33)</f>
         <v/>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="28">
         <f>(1-(E34/100)*G34)/(1+(E34/100)*F34)</f>
         <v/>
       </c>
@@ -14615,8 +13642,8 @@
         <f>(H33/H34-1)/((B34-B33)/360)*100</f>
         <v/>
       </c>
-      <c r="L34" s="30" t="n"/>
-      <c r="M34" s="31">
+      <c r="L34" s="29" t="n"/>
+      <c r="M34" s="30">
         <f>IF(L34="","",(J34-L34)*100)</f>
         <v/>
       </c>
@@ -14636,7 +13663,7 @@
         <f>EDATE($B$4,240)</f>
         <v/>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <f>(B35-$B$4)/365</f>
         <v/>
       </c>
@@ -14656,7 +13683,7 @@
         <f>SUM($I$8:I34)</f>
         <v/>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="28">
         <f>(1-(E35/100)*G35)/(1+(E35/100)*F35)</f>
         <v/>
       </c>
@@ -14672,8 +13699,8 @@
         <f>(H34/H35-1)/((B35-B34)/360)*100</f>
         <v/>
       </c>
-      <c r="L35" s="30" t="n"/>
-      <c r="M35" s="31">
+      <c r="L35" s="29" t="n"/>
+      <c r="M35" s="30">
         <f>IF(L35="","",(J35-L35)*100)</f>
         <v/>
       </c>
@@ -14693,7 +13720,7 @@
         <f>EDATE($B$4,300)</f>
         <v/>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <f>(B36-$B$4)/365</f>
         <v/>
       </c>
@@ -14713,7 +13740,7 @@
         <f>SUM($I$8:I35)</f>
         <v/>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="28">
         <f>(1-(E36/100)*G36)/(1+(E36/100)*F36)</f>
         <v/>
       </c>
@@ -14729,8 +13756,8 @@
         <f>(H35/H36-1)/((B36-B35)/360)*100</f>
         <v/>
       </c>
-      <c r="L36" s="30" t="n"/>
-      <c r="M36" s="31">
+      <c r="L36" s="29" t="n"/>
+      <c r="M36" s="30">
         <f>IF(L36="","",(J36-L36)*100)</f>
         <v/>
       </c>
@@ -14750,7 +13777,7 @@
         <f>EDATE($B$4,360)</f>
         <v/>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="27">
         <f>(B37-$B$4)/365</f>
         <v/>
       </c>
@@ -14770,7 +13797,7 @@
         <f>SUM($I$8:I36)</f>
         <v/>
       </c>
-      <c r="H37" s="29">
+      <c r="H37" s="28">
         <f>(1-(E37/100)*G37)/(1+(E37/100)*F37)</f>
         <v/>
       </c>
@@ -14786,8 +13813,8 @@
         <f>(H36/H37-1)/((B37-B36)/360)*100</f>
         <v/>
       </c>
-      <c r="L37" s="30" t="n"/>
-      <c r="M37" s="31">
+      <c r="L37" s="29" t="n"/>
+      <c r="M37" s="30">
         <f>IF(L37="","",(J37-L37)*100)</f>
         <v/>
       </c>
@@ -14807,7 +13834,7 @@
         <f>EDATE($B$4,480)</f>
         <v/>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="27">
         <f>(B38-$B$4)/365</f>
         <v/>
       </c>
@@ -14827,7 +13854,7 @@
         <f>SUM($I$8:I37)</f>
         <v/>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="28">
         <f>(1-(E38/100)*G38)/(1+(E38/100)*F38)</f>
         <v/>
       </c>
@@ -14843,8 +13870,8 @@
         <f>(H37/H38-1)/((B38-B37)/360)*100</f>
         <v/>
       </c>
-      <c r="L38" s="30" t="n"/>
-      <c r="M38" s="31">
+      <c r="L38" s="29" t="n"/>
+      <c r="M38" s="30">
         <f>IF(L38="","",(J38-L38)*100)</f>
         <v/>
       </c>
@@ -14864,7 +13891,7 @@
         <f>EDATE($B$4,600)</f>
         <v/>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="27">
         <f>(B39-$B$4)/365</f>
         <v/>
       </c>
@@ -14884,7 +13911,7 @@
         <f>SUM($I$8:I38)</f>
         <v/>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="28">
         <f>(1-(E39/100)*G39)/(1+(E39/100)*F39)</f>
         <v/>
       </c>
@@ -14900,8 +13927,8 @@
         <f>(H38/H39-1)/((B39-B38)/360)*100</f>
         <v/>
       </c>
-      <c r="L39" s="30" t="n"/>
-      <c r="M39" s="31">
+      <c r="L39" s="29" t="n"/>
+      <c r="M39" s="30">
         <f>IF(L39="","",(J39-L39)*100)</f>
         <v/>
       </c>
@@ -14911,21 +13938,18 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="44" customHeight="1">
+    <row r="41" ht="40" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>THREE SEGMENTS (Zhou 2002 structure):  SHORT o/n–1Y = single-payment SOFR OIS  (DF=1/(1+S·tau0));  MIDDLE 1Y–5Y = SR3 futures chained from the 1Y DF (helper block to the right, cols O–W);  LONG 5Y–50Y = annual SOFR OIS swaps built off the futures-derived 5Y point. No overlap — each maturity is covered once. Column H is the curve P(0,T); zero z=−ln(DF)/T; DF source is in col N. Futures→forward convexity (chain col T) = 0.5·sigma^2·t1·t2, driven by the yellow sigma (bp/yr) input above the chain — raise it and the futures pull below the OIS levels. Paste S490 zeros into column L for the Δz check; the Swap_Pricer values any OIS off this curve.</t>
+          <t>PURELY OIS bootstrap:  SHORT o/n–1Y = single-payment SOFR OIS (DF = 1/(1+S·tau0));  18M–50Y = annual SOFR OIS swaps (DF = (1−S·A_prior)/(1+S·tau_coupon)), with the annuity (col I) booked only at annual coupon dates. Every input reprices to par. Column H is the curve P(0,T); zero z = −ln(DF)/T; DF source in col N. Paste S490 zeros into column L for the Δz check. This is the curve the Swap_Pricer, Curve_Interface, and the whole CDS module use. Bootstrap_Lehman is the alternative 3-segment build (short OIS + SR3 futures + OIS swaps).</t>
         </is>
       </c>
     </row>
     <row r="42"/>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="O6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
+  <mergeCells count="2">
+    <mergeCell ref="A5:N6"/>
     <mergeCell ref="A41:N42"/>
-    <mergeCell ref="A5:N6"/>
-    <mergeCell ref="Q5:W5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -14937,7 +13961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L39"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14952,31 +13976,62 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Bootstrap_Futures</t>
+          <t>Bootstrap_Lehman</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Second copy — same 3-segment build, but the MIDDLE (1Y–5Y) FORCES the SR3 futures (no OIS-agreement guard). The pure futures-driven curve, to compare against the robust Bootstrap tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Lehman-2002 methodology on modern SOFR: short OIS (≤1Y) + SR3 FUTURES (1Y–5Y) + OIS swaps (5Y–50Y). The middle uses the futures; the purely-OIS Bootstrap tab is the alternative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="62" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>Identical to Bootstrap except the middle DFs use the SR3 futures chain DIRECTLY (interpolated off Bootstrap's futures grid Y8:Z28), falling back to OIS only on a hard error — NOT on disagreement. So 18M/2Y…5Y are always futures here. Cols A–F mirror Bootstrap; the long end re-bootstraps off these forced-futures middle DFs. Downstream tabs (Curve_Interface, Swap_Pricer, CDS) still use the robust Bootstrap tab; this one is for comparison. Watch the DF-source column and compare col H side by side.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6"/>
+          <t>Zhou-2002 three-segment build. SHORT (≤1Y) &amp; LONG (5Y–50Y) are the same OIS bootstrap as the Bootstrap tab; the MIDDLE (18M/2Y/3Y/4Y/5Y) is driven by the SR3 futures chain (own helper block cols O–W), which chains the QUARTERLY contracts (ref start Mar/Jun/Sep/Dec) forward from the OIS 1Y DF and interpolates onto the pillar dates. Falls back to OIS only on a hard error, so the futures drive the middle whenever the SR3 data is good (col L = 'SR3 futures'). Convexity in the chain uses the yellow sigma (bp/yr). Compare col H against the Bootstrap tab to see the futures-vs-OIS difference. Downstream tabs use the purely-OIS Bootstrap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="O5" s="13" t="inlineStr">
+        <is>
+          <t>sigma (bp/yr):</t>
+        </is>
+      </c>
+      <c r="P5" s="31" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>MIDDLE — SR3 futures chain (quarterly only)</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>Mid grid</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -15036,6 +14091,61 @@
       <c r="L7" s="20" t="inlineStr">
         <is>
           <t>DF source</t>
+        </is>
+      </c>
+      <c r="O7" s="20" t="inlineStr">
+        <is>
+          <t>Contract</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>Fut start</t>
+        </is>
+      </c>
+      <c r="Q7" s="20" t="inlineStr">
+        <is>
+          <t>Fut end</t>
+        </is>
+      </c>
+      <c r="R7" s="20" t="inlineStr">
+        <is>
+          <t>tau eff</t>
+        </is>
+      </c>
+      <c r="S7" s="20" t="inlineStr">
+        <is>
+          <t>Implied %</t>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t>Convexity bp</t>
+        </is>
+      </c>
+      <c r="U7" s="20" t="inlineStr">
+        <is>
+          <t>Fwd</t>
+        </is>
+      </c>
+      <c r="V7" s="20" t="inlineStr">
+        <is>
+          <t>DF before</t>
+        </is>
+      </c>
+      <c r="W7" s="20" t="inlineStr">
+        <is>
+          <t>DF after</t>
+        </is>
+      </c>
+      <c r="Y7" s="20" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="Z7" s="20" t="inlineStr">
+        <is>
+          <t>DF</t>
         </is>
       </c>
     </row>
@@ -15048,7 +14158,7 @@
         <f>'Bootstrap'!B8</f>
         <v/>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
         <f>'Bootstrap'!C8</f>
         <v/>
       </c>
@@ -15067,7 +14177,7 @@
       <c r="G8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <f>1/(1+(E8/100)*D8)</f>
         <v/>
       </c>
@@ -15086,6 +14196,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O8" s="6">
+        <f>'SOFR_Futures'!A7</f>
+        <v/>
+      </c>
+      <c r="P8" s="18">
+        <f>'SOFR_Futures'!H7</f>
+        <v/>
+      </c>
+      <c r="Q8" s="18">
+        <f>EDATE(P8,3)</f>
+        <v/>
+      </c>
+      <c r="R8" s="17">
+        <f>IF(OR(MONTH(P8)=3,MONTH(P8)=6,MONTH(P8)=9,MONTH(P8)=12),MAX(0,(Q8-MAX(P8,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S8" s="17">
+        <f>'SOFR_Futures'!F7</f>
+        <v/>
+      </c>
+      <c r="T8" s="27">
+        <f>0.5*$P$5^2*((P8-'Bootstrap'!$B$4)/365)*((Q8-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U8" s="32">
+        <f>(S8-T8/100)/100</f>
+        <v/>
+      </c>
+      <c r="V8" s="33">
+        <f>$H$22</f>
+        <v/>
+      </c>
+      <c r="W8" s="33">
+        <f>V8/(1+U8*R8)</f>
+        <v/>
+      </c>
+      <c r="Y8" s="18">
+        <f>$B$22</f>
+        <v/>
+      </c>
+      <c r="Z8" s="33">
+        <f>$H$22</f>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -15097,7 +14251,7 @@
         <f>'Bootstrap'!B9</f>
         <v/>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <f>'Bootstrap'!C9</f>
         <v/>
       </c>
@@ -15117,7 +14271,7 @@
         <f>SUM($I$8:I8)</f>
         <v/>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <f>1/(1+(E9/100)*D9)</f>
         <v/>
       </c>
@@ -15136,6 +14290,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O9" s="6">
+        <f>'SOFR_Futures'!A8</f>
+        <v/>
+      </c>
+      <c r="P9" s="18">
+        <f>'SOFR_Futures'!H8</f>
+        <v/>
+      </c>
+      <c r="Q9" s="18">
+        <f>EDATE(P9,3)</f>
+        <v/>
+      </c>
+      <c r="R9" s="17">
+        <f>IF(OR(MONTH(P9)=3,MONTH(P9)=6,MONTH(P9)=9,MONTH(P9)=12),MAX(0,(Q9-MAX(P9,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S9" s="17">
+        <f>'SOFR_Futures'!F8</f>
+        <v/>
+      </c>
+      <c r="T9" s="27">
+        <f>0.5*$P$5^2*((P9-'Bootstrap'!$B$4)/365)*((Q9-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U9" s="32">
+        <f>(S9-T9/100)/100</f>
+        <v/>
+      </c>
+      <c r="V9" s="33">
+        <f>W8</f>
+        <v/>
+      </c>
+      <c r="W9" s="33">
+        <f>V9/(1+U9*R9)</f>
+        <v/>
+      </c>
+      <c r="Y9" s="18">
+        <f>MAX(Q8,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="33">
+        <f>W8</f>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -15147,7 +14345,7 @@
         <f>'Bootstrap'!B10</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <f>'Bootstrap'!C10</f>
         <v/>
       </c>
@@ -15167,7 +14365,7 @@
         <f>SUM($I$8:I9)</f>
         <v/>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28">
         <f>1/(1+(E10/100)*D10)</f>
         <v/>
       </c>
@@ -15186,6 +14384,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O10" s="6">
+        <f>'SOFR_Futures'!A9</f>
+        <v/>
+      </c>
+      <c r="P10" s="18">
+        <f>'SOFR_Futures'!H9</f>
+        <v/>
+      </c>
+      <c r="Q10" s="18">
+        <f>EDATE(P10,3)</f>
+        <v/>
+      </c>
+      <c r="R10" s="17">
+        <f>IF(OR(MONTH(P10)=3,MONTH(P10)=6,MONTH(P10)=9,MONTH(P10)=12),MAX(0,(Q10-MAX(P10,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S10" s="17">
+        <f>'SOFR_Futures'!F9</f>
+        <v/>
+      </c>
+      <c r="T10" s="27">
+        <f>0.5*$P$5^2*((P10-'Bootstrap'!$B$4)/365)*((Q10-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U10" s="32">
+        <f>(S10-T10/100)/100</f>
+        <v/>
+      </c>
+      <c r="V10" s="33">
+        <f>W9</f>
+        <v/>
+      </c>
+      <c r="W10" s="33">
+        <f>V10/(1+U10*R10)</f>
+        <v/>
+      </c>
+      <c r="Y10" s="18">
+        <f>MAX(Q9,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="33">
+        <f>W9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -15197,7 +14439,7 @@
         <f>'Bootstrap'!B11</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <f>'Bootstrap'!C11</f>
         <v/>
       </c>
@@ -15217,7 +14459,7 @@
         <f>SUM($I$8:I10)</f>
         <v/>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="28">
         <f>1/(1+(E11/100)*D11)</f>
         <v/>
       </c>
@@ -15236,6 +14478,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O11" s="6">
+        <f>'SOFR_Futures'!A10</f>
+        <v/>
+      </c>
+      <c r="P11" s="18">
+        <f>'SOFR_Futures'!H10</f>
+        <v/>
+      </c>
+      <c r="Q11" s="18">
+        <f>EDATE(P11,3)</f>
+        <v/>
+      </c>
+      <c r="R11" s="17">
+        <f>IF(OR(MONTH(P11)=3,MONTH(P11)=6,MONTH(P11)=9,MONTH(P11)=12),MAX(0,(Q11-MAX(P11,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S11" s="17">
+        <f>'SOFR_Futures'!F10</f>
+        <v/>
+      </c>
+      <c r="T11" s="27">
+        <f>0.5*$P$5^2*((P11-'Bootstrap'!$B$4)/365)*((Q11-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U11" s="32">
+        <f>(S11-T11/100)/100</f>
+        <v/>
+      </c>
+      <c r="V11" s="33">
+        <f>W10</f>
+        <v/>
+      </c>
+      <c r="W11" s="33">
+        <f>V11/(1+U11*R11)</f>
+        <v/>
+      </c>
+      <c r="Y11" s="18">
+        <f>MAX(Q10,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="33">
+        <f>W10</f>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -15247,7 +14533,7 @@
         <f>'Bootstrap'!B12</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <f>'Bootstrap'!C12</f>
         <v/>
       </c>
@@ -15267,7 +14553,7 @@
         <f>SUM($I$8:I11)</f>
         <v/>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="28">
         <f>1/(1+(E12/100)*D12)</f>
         <v/>
       </c>
@@ -15286,6 +14572,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O12" s="6">
+        <f>'SOFR_Futures'!A11</f>
+        <v/>
+      </c>
+      <c r="P12" s="18">
+        <f>'SOFR_Futures'!H11</f>
+        <v/>
+      </c>
+      <c r="Q12" s="18">
+        <f>EDATE(P12,3)</f>
+        <v/>
+      </c>
+      <c r="R12" s="17">
+        <f>IF(OR(MONTH(P12)=3,MONTH(P12)=6,MONTH(P12)=9,MONTH(P12)=12),MAX(0,(Q12-MAX(P12,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S12" s="17">
+        <f>'SOFR_Futures'!F11</f>
+        <v/>
+      </c>
+      <c r="T12" s="27">
+        <f>0.5*$P$5^2*((P12-'Bootstrap'!$B$4)/365)*((Q12-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U12" s="32">
+        <f>(S12-T12/100)/100</f>
+        <v/>
+      </c>
+      <c r="V12" s="33">
+        <f>W11</f>
+        <v/>
+      </c>
+      <c r="W12" s="33">
+        <f>V12/(1+U12*R12)</f>
+        <v/>
+      </c>
+      <c r="Y12" s="18">
+        <f>MAX(Q11,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="33">
+        <f>W11</f>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -15297,7 +14627,7 @@
         <f>'Bootstrap'!B13</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <f>'Bootstrap'!C13</f>
         <v/>
       </c>
@@ -15317,7 +14647,7 @@
         <f>SUM($I$8:I12)</f>
         <v/>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="28">
         <f>1/(1+(E13/100)*D13)</f>
         <v/>
       </c>
@@ -15336,6 +14666,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O13" s="6">
+        <f>'SOFR_Futures'!A12</f>
+        <v/>
+      </c>
+      <c r="P13" s="18">
+        <f>'SOFR_Futures'!H12</f>
+        <v/>
+      </c>
+      <c r="Q13" s="18">
+        <f>EDATE(P13,3)</f>
+        <v/>
+      </c>
+      <c r="R13" s="17">
+        <f>IF(OR(MONTH(P13)=3,MONTH(P13)=6,MONTH(P13)=9,MONTH(P13)=12),MAX(0,(Q13-MAX(P13,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S13" s="17">
+        <f>'SOFR_Futures'!F12</f>
+        <v/>
+      </c>
+      <c r="T13" s="27">
+        <f>0.5*$P$5^2*((P13-'Bootstrap'!$B$4)/365)*((Q13-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U13" s="32">
+        <f>(S13-T13/100)/100</f>
+        <v/>
+      </c>
+      <c r="V13" s="33">
+        <f>W12</f>
+        <v/>
+      </c>
+      <c r="W13" s="33">
+        <f>V13/(1+U13*R13)</f>
+        <v/>
+      </c>
+      <c r="Y13" s="18">
+        <f>MAX(Q12,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="33">
+        <f>W12</f>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -15347,7 +14721,7 @@
         <f>'Bootstrap'!B14</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <f>'Bootstrap'!C14</f>
         <v/>
       </c>
@@ -15367,7 +14741,7 @@
         <f>SUM($I$8:I13)</f>
         <v/>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="28">
         <f>1/(1+(E14/100)*D14)</f>
         <v/>
       </c>
@@ -15386,6 +14760,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O14" s="6">
+        <f>'SOFR_Futures'!A13</f>
+        <v/>
+      </c>
+      <c r="P14" s="18">
+        <f>'SOFR_Futures'!H13</f>
+        <v/>
+      </c>
+      <c r="Q14" s="18">
+        <f>EDATE(P14,3)</f>
+        <v/>
+      </c>
+      <c r="R14" s="17">
+        <f>IF(OR(MONTH(P14)=3,MONTH(P14)=6,MONTH(P14)=9,MONTH(P14)=12),MAX(0,(Q14-MAX(P14,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S14" s="17">
+        <f>'SOFR_Futures'!F13</f>
+        <v/>
+      </c>
+      <c r="T14" s="27">
+        <f>0.5*$P$5^2*((P14-'Bootstrap'!$B$4)/365)*((Q14-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U14" s="32">
+        <f>(S14-T14/100)/100</f>
+        <v/>
+      </c>
+      <c r="V14" s="33">
+        <f>W13</f>
+        <v/>
+      </c>
+      <c r="W14" s="33">
+        <f>V14/(1+U14*R14)</f>
+        <v/>
+      </c>
+      <c r="Y14" s="18">
+        <f>MAX(Q13,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="33">
+        <f>W13</f>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -15397,7 +14815,7 @@
         <f>'Bootstrap'!B15</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <f>'Bootstrap'!C15</f>
         <v/>
       </c>
@@ -15417,7 +14835,7 @@
         <f>SUM($I$8:I14)</f>
         <v/>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="28">
         <f>1/(1+(E15/100)*D15)</f>
         <v/>
       </c>
@@ -15436,6 +14854,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O15" s="6">
+        <f>'SOFR_Futures'!A14</f>
+        <v/>
+      </c>
+      <c r="P15" s="18">
+        <f>'SOFR_Futures'!H14</f>
+        <v/>
+      </c>
+      <c r="Q15" s="18">
+        <f>EDATE(P15,3)</f>
+        <v/>
+      </c>
+      <c r="R15" s="17">
+        <f>IF(OR(MONTH(P15)=3,MONTH(P15)=6,MONTH(P15)=9,MONTH(P15)=12),MAX(0,(Q15-MAX(P15,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S15" s="17">
+        <f>'SOFR_Futures'!F14</f>
+        <v/>
+      </c>
+      <c r="T15" s="27">
+        <f>0.5*$P$5^2*((P15-'Bootstrap'!$B$4)/365)*((Q15-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U15" s="32">
+        <f>(S15-T15/100)/100</f>
+        <v/>
+      </c>
+      <c r="V15" s="33">
+        <f>W14</f>
+        <v/>
+      </c>
+      <c r="W15" s="33">
+        <f>V15/(1+U15*R15)</f>
+        <v/>
+      </c>
+      <c r="Y15" s="18">
+        <f>MAX(Q14,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="33">
+        <f>W14</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -15447,7 +14909,7 @@
         <f>'Bootstrap'!B16</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>'Bootstrap'!C16</f>
         <v/>
       </c>
@@ -15467,7 +14929,7 @@
         <f>SUM($I$8:I15)</f>
         <v/>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="28">
         <f>1/(1+(E16/100)*D16)</f>
         <v/>
       </c>
@@ -15486,6 +14948,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O16" s="6">
+        <f>'SOFR_Futures'!A15</f>
+        <v/>
+      </c>
+      <c r="P16" s="18">
+        <f>'SOFR_Futures'!H15</f>
+        <v/>
+      </c>
+      <c r="Q16" s="18">
+        <f>EDATE(P16,3)</f>
+        <v/>
+      </c>
+      <c r="R16" s="17">
+        <f>IF(OR(MONTH(P16)=3,MONTH(P16)=6,MONTH(P16)=9,MONTH(P16)=12),MAX(0,(Q16-MAX(P16,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S16" s="17">
+        <f>'SOFR_Futures'!F15</f>
+        <v/>
+      </c>
+      <c r="T16" s="27">
+        <f>0.5*$P$5^2*((P16-'Bootstrap'!$B$4)/365)*((Q16-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U16" s="32">
+        <f>(S16-T16/100)/100</f>
+        <v/>
+      </c>
+      <c r="V16" s="33">
+        <f>W15</f>
+        <v/>
+      </c>
+      <c r="W16" s="33">
+        <f>V16/(1+U16*R16)</f>
+        <v/>
+      </c>
+      <c r="Y16" s="18">
+        <f>MAX(Q15,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="33">
+        <f>W15</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -15497,7 +15003,7 @@
         <f>'Bootstrap'!B17</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>'Bootstrap'!C17</f>
         <v/>
       </c>
@@ -15517,7 +15023,7 @@
         <f>SUM($I$8:I16)</f>
         <v/>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="28">
         <f>1/(1+(E17/100)*D17)</f>
         <v/>
       </c>
@@ -15536,6 +15042,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O17" s="6">
+        <f>'SOFR_Futures'!A16</f>
+        <v/>
+      </c>
+      <c r="P17" s="18">
+        <f>'SOFR_Futures'!H16</f>
+        <v/>
+      </c>
+      <c r="Q17" s="18">
+        <f>EDATE(P17,3)</f>
+        <v/>
+      </c>
+      <c r="R17" s="17">
+        <f>IF(OR(MONTH(P17)=3,MONTH(P17)=6,MONTH(P17)=9,MONTH(P17)=12),MAX(0,(Q17-MAX(P17,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S17" s="17">
+        <f>'SOFR_Futures'!F16</f>
+        <v/>
+      </c>
+      <c r="T17" s="27">
+        <f>0.5*$P$5^2*((P17-'Bootstrap'!$B$4)/365)*((Q17-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U17" s="32">
+        <f>(S17-T17/100)/100</f>
+        <v/>
+      </c>
+      <c r="V17" s="33">
+        <f>W16</f>
+        <v/>
+      </c>
+      <c r="W17" s="33">
+        <f>V17/(1+U17*R17)</f>
+        <v/>
+      </c>
+      <c r="Y17" s="18">
+        <f>MAX(Q16,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="33">
+        <f>W16</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -15547,7 +15097,7 @@
         <f>'Bootstrap'!B18</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <f>'Bootstrap'!C18</f>
         <v/>
       </c>
@@ -15567,7 +15117,7 @@
         <f>SUM($I$8:I17)</f>
         <v/>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <f>1/(1+(E18/100)*D18)</f>
         <v/>
       </c>
@@ -15586,6 +15136,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O18" s="6">
+        <f>'SOFR_Futures'!A17</f>
+        <v/>
+      </c>
+      <c r="P18" s="18">
+        <f>'SOFR_Futures'!H17</f>
+        <v/>
+      </c>
+      <c r="Q18" s="18">
+        <f>EDATE(P18,3)</f>
+        <v/>
+      </c>
+      <c r="R18" s="17">
+        <f>IF(OR(MONTH(P18)=3,MONTH(P18)=6,MONTH(P18)=9,MONTH(P18)=12),MAX(0,(Q18-MAX(P18,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S18" s="17">
+        <f>'SOFR_Futures'!F17</f>
+        <v/>
+      </c>
+      <c r="T18" s="27">
+        <f>0.5*$P$5^2*((P18-'Bootstrap'!$B$4)/365)*((Q18-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U18" s="32">
+        <f>(S18-T18/100)/100</f>
+        <v/>
+      </c>
+      <c r="V18" s="33">
+        <f>W17</f>
+        <v/>
+      </c>
+      <c r="W18" s="33">
+        <f>V18/(1+U18*R18)</f>
+        <v/>
+      </c>
+      <c r="Y18" s="18">
+        <f>MAX(Q17,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="33">
+        <f>W17</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -15597,7 +15191,7 @@
         <f>'Bootstrap'!B19</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <f>'Bootstrap'!C19</f>
         <v/>
       </c>
@@ -15617,7 +15211,7 @@
         <f>SUM($I$8:I18)</f>
         <v/>
       </c>
-      <c r="H19" s="29">
+      <c r="H19" s="28">
         <f>1/(1+(E19/100)*D19)</f>
         <v/>
       </c>
@@ -15636,6 +15230,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O19" s="6">
+        <f>'SOFR_Futures'!A18</f>
+        <v/>
+      </c>
+      <c r="P19" s="18">
+        <f>'SOFR_Futures'!H18</f>
+        <v/>
+      </c>
+      <c r="Q19" s="18">
+        <f>EDATE(P19,3)</f>
+        <v/>
+      </c>
+      <c r="R19" s="17">
+        <f>IF(OR(MONTH(P19)=3,MONTH(P19)=6,MONTH(P19)=9,MONTH(P19)=12),MAX(0,(Q19-MAX(P19,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S19" s="17">
+        <f>'SOFR_Futures'!F18</f>
+        <v/>
+      </c>
+      <c r="T19" s="27">
+        <f>0.5*$P$5^2*((P19-'Bootstrap'!$B$4)/365)*((Q19-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U19" s="32">
+        <f>(S19-T19/100)/100</f>
+        <v/>
+      </c>
+      <c r="V19" s="33">
+        <f>W18</f>
+        <v/>
+      </c>
+      <c r="W19" s="33">
+        <f>V19/(1+U19*R19)</f>
+        <v/>
+      </c>
+      <c r="Y19" s="18">
+        <f>MAX(Q18,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="33">
+        <f>W18</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -15647,7 +15285,7 @@
         <f>'Bootstrap'!B20</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <f>'Bootstrap'!C20</f>
         <v/>
       </c>
@@ -15667,7 +15305,7 @@
         <f>SUM($I$8:I19)</f>
         <v/>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="28">
         <f>1/(1+(E20/100)*D20)</f>
         <v/>
       </c>
@@ -15686,6 +15324,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O20" s="6">
+        <f>'SOFR_Futures'!A19</f>
+        <v/>
+      </c>
+      <c r="P20" s="18">
+        <f>'SOFR_Futures'!H19</f>
+        <v/>
+      </c>
+      <c r="Q20" s="18">
+        <f>EDATE(P20,3)</f>
+        <v/>
+      </c>
+      <c r="R20" s="17">
+        <f>IF(OR(MONTH(P20)=3,MONTH(P20)=6,MONTH(P20)=9,MONTH(P20)=12),MAX(0,(Q20-MAX(P20,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S20" s="17">
+        <f>'SOFR_Futures'!F19</f>
+        <v/>
+      </c>
+      <c r="T20" s="27">
+        <f>0.5*$P$5^2*((P20-'Bootstrap'!$B$4)/365)*((Q20-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U20" s="32">
+        <f>(S20-T20/100)/100</f>
+        <v/>
+      </c>
+      <c r="V20" s="33">
+        <f>W19</f>
+        <v/>
+      </c>
+      <c r="W20" s="33">
+        <f>V20/(1+U20*R20)</f>
+        <v/>
+      </c>
+      <c r="Y20" s="18">
+        <f>MAX(Q19,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="33">
+        <f>W19</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -15697,7 +15379,7 @@
         <f>'Bootstrap'!B21</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>'Bootstrap'!C21</f>
         <v/>
       </c>
@@ -15717,7 +15399,7 @@
         <f>SUM($I$8:I20)</f>
         <v/>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="28">
         <f>1/(1+(E21/100)*D21)</f>
         <v/>
       </c>
@@ -15736,6 +15418,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O21" s="6">
+        <f>'SOFR_Futures'!A20</f>
+        <v/>
+      </c>
+      <c r="P21" s="18">
+        <f>'SOFR_Futures'!H20</f>
+        <v/>
+      </c>
+      <c r="Q21" s="18">
+        <f>EDATE(P21,3)</f>
+        <v/>
+      </c>
+      <c r="R21" s="17">
+        <f>IF(OR(MONTH(P21)=3,MONTH(P21)=6,MONTH(P21)=9,MONTH(P21)=12),MAX(0,(Q21-MAX(P21,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S21" s="17">
+        <f>'SOFR_Futures'!F20</f>
+        <v/>
+      </c>
+      <c r="T21" s="27">
+        <f>0.5*$P$5^2*((P21-'Bootstrap'!$B$4)/365)*((Q21-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U21" s="32">
+        <f>(S21-T21/100)/100</f>
+        <v/>
+      </c>
+      <c r="V21" s="33">
+        <f>W20</f>
+        <v/>
+      </c>
+      <c r="W21" s="33">
+        <f>V21/(1+U21*R21)</f>
+        <v/>
+      </c>
+      <c r="Y21" s="18">
+        <f>MAX(Q20,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="33">
+        <f>W20</f>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -15747,7 +15473,7 @@
         <f>'Bootstrap'!B22</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>'Bootstrap'!C22</f>
         <v/>
       </c>
@@ -15767,7 +15493,7 @@
         <f>SUM($I$8:I21)</f>
         <v/>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="28">
         <f>1/(1+(E22/100)*D22)</f>
         <v/>
       </c>
@@ -15787,6 +15513,50 @@
         <is>
           <t>short OIS</t>
         </is>
+      </c>
+      <c r="O22" s="6">
+        <f>'SOFR_Futures'!A21</f>
+        <v/>
+      </c>
+      <c r="P22" s="18">
+        <f>'SOFR_Futures'!H21</f>
+        <v/>
+      </c>
+      <c r="Q22" s="18">
+        <f>EDATE(P22,3)</f>
+        <v/>
+      </c>
+      <c r="R22" s="17">
+        <f>IF(OR(MONTH(P22)=3,MONTH(P22)=6,MONTH(P22)=9,MONTH(P22)=12),MAX(0,(Q22-MAX(P22,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S22" s="17">
+        <f>'SOFR_Futures'!F21</f>
+        <v/>
+      </c>
+      <c r="T22" s="27">
+        <f>0.5*$P$5^2*((P22-'Bootstrap'!$B$4)/365)*((Q22-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U22" s="32">
+        <f>(S22-T22/100)/100</f>
+        <v/>
+      </c>
+      <c r="V22" s="33">
+        <f>W21</f>
+        <v/>
+      </c>
+      <c r="W22" s="33">
+        <f>V22/(1+U22*R22)</f>
+        <v/>
+      </c>
+      <c r="Y22" s="18">
+        <f>MAX(Q21,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="33">
+        <f>W21</f>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -15798,7 +15568,7 @@
         <f>'Bootstrap'!B23</f>
         <v/>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <f>'Bootstrap'!C23</f>
         <v/>
       </c>
@@ -15818,8 +15588,8 @@
         <f>SUM($I$8:I22)</f>
         <v/>
       </c>
-      <c r="H23" s="29">
-        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)))^((B23-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B23,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E23/100)*G23)/(1+(E23/100)*F23))</f>
+      <c r="H23" s="28">
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1)))^((B23-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B23,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B23,$Y$8:$Y$28,1))),(1-(E23/100)*G23)/(1+(E23/100)*F23))</f>
         <v/>
       </c>
       <c r="I23" s="17" t="n">
@@ -15835,8 +15605,52 @@
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>SR3 futures (forced)</t>
-        </is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
+      <c r="O23" s="6">
+        <f>'SOFR_Futures'!A22</f>
+        <v/>
+      </c>
+      <c r="P23" s="18">
+        <f>'SOFR_Futures'!H22</f>
+        <v/>
+      </c>
+      <c r="Q23" s="18">
+        <f>EDATE(P23,3)</f>
+        <v/>
+      </c>
+      <c r="R23" s="17">
+        <f>IF(OR(MONTH(P23)=3,MONTH(P23)=6,MONTH(P23)=9,MONTH(P23)=12),MAX(0,(Q23-MAX(P23,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S23" s="17">
+        <f>'SOFR_Futures'!F22</f>
+        <v/>
+      </c>
+      <c r="T23" s="27">
+        <f>0.5*$P$5^2*((P23-'Bootstrap'!$B$4)/365)*((Q23-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U23" s="32">
+        <f>(S23-T23/100)/100</f>
+        <v/>
+      </c>
+      <c r="V23" s="33">
+        <f>W22</f>
+        <v/>
+      </c>
+      <c r="W23" s="33">
+        <f>V23/(1+U23*R23)</f>
+        <v/>
+      </c>
+      <c r="Y23" s="18">
+        <f>MAX(Q22,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="33">
+        <f>W22</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -15848,7 +15662,7 @@
         <f>'Bootstrap'!B24</f>
         <v/>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="27">
         <f>'Bootstrap'!C24</f>
         <v/>
       </c>
@@ -15868,8 +15682,8 @@
         <f>SUM($I$8:I23)</f>
         <v/>
       </c>
-      <c r="H24" s="29">
-        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)))^((B24-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B24,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E24/100)*G24)/(1+(E24/100)*F24))</f>
+      <c r="H24" s="28">
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1)))^((B24-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B24,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B24,$Y$8:$Y$28,1))),(1-(E24/100)*G24)/(1+(E24/100)*F24))</f>
         <v/>
       </c>
       <c r="I24" s="17">
@@ -15886,8 +15700,52 @@
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>SR3 futures (forced)</t>
-        </is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
+      <c r="O24" s="6">
+        <f>'SOFR_Futures'!A23</f>
+        <v/>
+      </c>
+      <c r="P24" s="18">
+        <f>'SOFR_Futures'!H23</f>
+        <v/>
+      </c>
+      <c r="Q24" s="18">
+        <f>EDATE(P24,3)</f>
+        <v/>
+      </c>
+      <c r="R24" s="17">
+        <f>IF(OR(MONTH(P24)=3,MONTH(P24)=6,MONTH(P24)=9,MONTH(P24)=12),MAX(0,(Q24-MAX(P24,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S24" s="17">
+        <f>'SOFR_Futures'!F23</f>
+        <v/>
+      </c>
+      <c r="T24" s="27">
+        <f>0.5*$P$5^2*((P24-'Bootstrap'!$B$4)/365)*((Q24-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U24" s="32">
+        <f>(S24-T24/100)/100</f>
+        <v/>
+      </c>
+      <c r="V24" s="33">
+        <f>W23</f>
+        <v/>
+      </c>
+      <c r="W24" s="33">
+        <f>V24/(1+U24*R24)</f>
+        <v/>
+      </c>
+      <c r="Y24" s="18">
+        <f>MAX(Q23,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="33">
+        <f>W23</f>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -15899,7 +15757,7 @@
         <f>'Bootstrap'!B25</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="27">
         <f>'Bootstrap'!C25</f>
         <v/>
       </c>
@@ -15919,8 +15777,8 @@
         <f>SUM($I$8:I24)</f>
         <v/>
       </c>
-      <c r="H25" s="29">
-        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)))^((B25-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B25,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E25/100)*G25)/(1+(E25/100)*F25))</f>
+      <c r="H25" s="28">
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1)))^((B25-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B25,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B25,$Y$8:$Y$28,1))),(1-(E25/100)*G25)/(1+(E25/100)*F25))</f>
         <v/>
       </c>
       <c r="I25" s="17">
@@ -15937,8 +15795,52 @@
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>SR3 futures (forced)</t>
-        </is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
+      <c r="O25" s="6">
+        <f>'SOFR_Futures'!A24</f>
+        <v/>
+      </c>
+      <c r="P25" s="18">
+        <f>'SOFR_Futures'!H24</f>
+        <v/>
+      </c>
+      <c r="Q25" s="18">
+        <f>EDATE(P25,3)</f>
+        <v/>
+      </c>
+      <c r="R25" s="17">
+        <f>IF(OR(MONTH(P25)=3,MONTH(P25)=6,MONTH(P25)=9,MONTH(P25)=12),MAX(0,(Q25-MAX(P25,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S25" s="17">
+        <f>'SOFR_Futures'!F24</f>
+        <v/>
+      </c>
+      <c r="T25" s="27">
+        <f>0.5*$P$5^2*((P25-'Bootstrap'!$B$4)/365)*((Q25-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U25" s="32">
+        <f>(S25-T25/100)/100</f>
+        <v/>
+      </c>
+      <c r="V25" s="33">
+        <f>W24</f>
+        <v/>
+      </c>
+      <c r="W25" s="33">
+        <f>V25/(1+U25*R25)</f>
+        <v/>
+      </c>
+      <c r="Y25" s="18">
+        <f>MAX(Q24,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="33">
+        <f>W24</f>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -15950,7 +15852,7 @@
         <f>'Bootstrap'!B26</f>
         <v/>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="27">
         <f>'Bootstrap'!C26</f>
         <v/>
       </c>
@@ -15970,8 +15872,8 @@
         <f>SUM($I$8:I25)</f>
         <v/>
       </c>
-      <c r="H26" s="29">
-        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)))^((B26-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B26,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E26/100)*G26)/(1+(E26/100)*F26))</f>
+      <c r="H26" s="28">
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1)))^((B26-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B26,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B26,$Y$8:$Y$28,1))),(1-(E26/100)*G26)/(1+(E26/100)*F26))</f>
         <v/>
       </c>
       <c r="I26" s="17">
@@ -15988,8 +15890,52 @@
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>SR3 futures (forced)</t>
-        </is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
+      <c r="O26" s="6">
+        <f>'SOFR_Futures'!A25</f>
+        <v/>
+      </c>
+      <c r="P26" s="18">
+        <f>'SOFR_Futures'!H25</f>
+        <v/>
+      </c>
+      <c r="Q26" s="18">
+        <f>EDATE(P26,3)</f>
+        <v/>
+      </c>
+      <c r="R26" s="17">
+        <f>IF(OR(MONTH(P26)=3,MONTH(P26)=6,MONTH(P26)=9,MONTH(P26)=12),MAX(0,(Q26-MAX(P26,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S26" s="17">
+        <f>'SOFR_Futures'!F25</f>
+        <v/>
+      </c>
+      <c r="T26" s="27">
+        <f>0.5*$P$5^2*((P26-'Bootstrap'!$B$4)/365)*((Q26-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U26" s="32">
+        <f>(S26-T26/100)/100</f>
+        <v/>
+      </c>
+      <c r="V26" s="33">
+        <f>W25</f>
+        <v/>
+      </c>
+      <c r="W26" s="33">
+        <f>V26/(1+U26*R26)</f>
+        <v/>
+      </c>
+      <c r="Y26" s="18">
+        <f>MAX(Q25,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="33">
+        <f>W25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -16001,7 +15947,7 @@
         <f>'Bootstrap'!B27</f>
         <v/>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="27">
         <f>'Bootstrap'!C27</f>
         <v/>
       </c>
@@ -16021,8 +15967,8 @@
         <f>SUM($I$8:I26)</f>
         <v/>
       </c>
-      <c r="H27" s="29">
-        <f>IFERROR(IFERROR(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1))*(INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)+1)/INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)))^((B27-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)))/(INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)+1)-INDEX('Bootstrap'!$Y$8:$Y$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1)))),INDEX('Bootstrap'!$Z$8:$Z$28,MATCH(B27,'Bootstrap'!$Y$8:$Y$28,1))),(1-(E27/100)*G27)/(1+(E27/100)*F27))</f>
+      <c r="H27" s="28">
+        <f>IFERROR(IFERROR(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))*(INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)+1)/INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1)))^((B27-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))/(INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)+1)-INDEX($Y$8:$Y$28,MATCH(B27,$Y$8:$Y$28,1)))),INDEX($Z$8:$Z$28,MATCH(B27,$Y$8:$Y$28,1))),(1-(E27/100)*G27)/(1+(E27/100)*F27))</f>
         <v/>
       </c>
       <c r="I27" s="17">
@@ -16039,8 +15985,52 @@
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>SR3 futures (forced)</t>
-        </is>
+          <t>SR3 futures</t>
+        </is>
+      </c>
+      <c r="O27" s="6">
+        <f>'SOFR_Futures'!A26</f>
+        <v/>
+      </c>
+      <c r="P27" s="18">
+        <f>'SOFR_Futures'!H26</f>
+        <v/>
+      </c>
+      <c r="Q27" s="18">
+        <f>EDATE(P27,3)</f>
+        <v/>
+      </c>
+      <c r="R27" s="17">
+        <f>IF(OR(MONTH(P27)=3,MONTH(P27)=6,MONTH(P27)=9,MONTH(P27)=12),MAX(0,(Q27-MAX(P27,$B$22))/360),0)</f>
+        <v/>
+      </c>
+      <c r="S27" s="17">
+        <f>'SOFR_Futures'!F26</f>
+        <v/>
+      </c>
+      <c r="T27" s="27">
+        <f>0.5*$P$5^2*((P27-'Bootstrap'!$B$4)/365)*((Q27-'Bootstrap'!$B$4)/365)/10000</f>
+        <v/>
+      </c>
+      <c r="U27" s="32">
+        <f>(S27-T27/100)/100</f>
+        <v/>
+      </c>
+      <c r="V27" s="33">
+        <f>W26</f>
+        <v/>
+      </c>
+      <c r="W27" s="33">
+        <f>V27/(1+U27*R27)</f>
+        <v/>
+      </c>
+      <c r="Y27" s="18">
+        <f>MAX(Q26,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="33">
+        <f>W26</f>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -16052,7 +16042,7 @@
         <f>'Bootstrap'!B28</f>
         <v/>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="27">
         <f>'Bootstrap'!C28</f>
         <v/>
       </c>
@@ -16072,7 +16062,7 @@
         <f>SUM($I$8:I27)</f>
         <v/>
       </c>
-      <c r="H28" s="29">
+      <c r="H28" s="28">
         <f>(1-(E28/100)*G28)/(1+(E28/100)*F28)</f>
         <v/>
       </c>
@@ -16092,6 +16082,14 @@
         <is>
           <t>OIS swap</t>
         </is>
+      </c>
+      <c r="Y28" s="18">
+        <f>MAX(Q27,$B$22)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="33">
+        <f>W27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -16103,7 +16101,7 @@
         <f>'Bootstrap'!B29</f>
         <v/>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <f>'Bootstrap'!C29</f>
         <v/>
       </c>
@@ -16123,7 +16121,7 @@
         <f>SUM($I$8:I28)</f>
         <v/>
       </c>
-      <c r="H29" s="29">
+      <c r="H29" s="28">
         <f>(1-(E29/100)*G29)/(1+(E29/100)*F29)</f>
         <v/>
       </c>
@@ -16154,7 +16152,7 @@
         <f>'Bootstrap'!B30</f>
         <v/>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="27">
         <f>'Bootstrap'!C30</f>
         <v/>
       </c>
@@ -16174,7 +16172,7 @@
         <f>SUM($I$8:I29)</f>
         <v/>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="28">
         <f>(1-(E30/100)*G30)/(1+(E30/100)*F30)</f>
         <v/>
       </c>
@@ -16205,7 +16203,7 @@
         <f>'Bootstrap'!B31</f>
         <v/>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <f>'Bootstrap'!C31</f>
         <v/>
       </c>
@@ -16225,7 +16223,7 @@
         <f>SUM($I$8:I30)</f>
         <v/>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="28">
         <f>(1-(E31/100)*G31)/(1+(E31/100)*F31)</f>
         <v/>
       </c>
@@ -16256,7 +16254,7 @@
         <f>'Bootstrap'!B32</f>
         <v/>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="27">
         <f>'Bootstrap'!C32</f>
         <v/>
       </c>
@@ -16276,7 +16274,7 @@
         <f>SUM($I$8:I31)</f>
         <v/>
       </c>
-      <c r="H32" s="29">
+      <c r="H32" s="28">
         <f>(1-(E32/100)*G32)/(1+(E32/100)*F32)</f>
         <v/>
       </c>
@@ -16307,7 +16305,7 @@
         <f>'Bootstrap'!B33</f>
         <v/>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <f>'Bootstrap'!C33</f>
         <v/>
       </c>
@@ -16327,7 +16325,7 @@
         <f>SUM($I$8:I32)</f>
         <v/>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="28">
         <f>(1-(E33/100)*G33)/(1+(E33/100)*F33)</f>
         <v/>
       </c>
@@ -16358,7 +16356,7 @@
         <f>'Bootstrap'!B34</f>
         <v/>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="27">
         <f>'Bootstrap'!C34</f>
         <v/>
       </c>
@@ -16378,7 +16376,7 @@
         <f>SUM($I$8:I33)</f>
         <v/>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="28">
         <f>(1-(E34/100)*G34)/(1+(E34/100)*F34)</f>
         <v/>
       </c>
@@ -16409,7 +16407,7 @@
         <f>'Bootstrap'!B35</f>
         <v/>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <f>'Bootstrap'!C35</f>
         <v/>
       </c>
@@ -16429,7 +16427,7 @@
         <f>SUM($I$8:I34)</f>
         <v/>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="28">
         <f>(1-(E35/100)*G35)/(1+(E35/100)*F35)</f>
         <v/>
       </c>
@@ -16460,7 +16458,7 @@
         <f>'Bootstrap'!B36</f>
         <v/>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <f>'Bootstrap'!C36</f>
         <v/>
       </c>
@@ -16480,7 +16478,7 @@
         <f>SUM($I$8:I35)</f>
         <v/>
       </c>
-      <c r="H36" s="29">
+      <c r="H36" s="28">
         <f>(1-(E36/100)*G36)/(1+(E36/100)*F36)</f>
         <v/>
       </c>
@@ -16511,7 +16509,7 @@
         <f>'Bootstrap'!B37</f>
         <v/>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="27">
         <f>'Bootstrap'!C37</f>
         <v/>
       </c>
@@ -16531,7 +16529,7 @@
         <f>SUM($I$8:I36)</f>
         <v/>
       </c>
-      <c r="H37" s="29">
+      <c r="H37" s="28">
         <f>(1-(E37/100)*G37)/(1+(E37/100)*F37)</f>
         <v/>
       </c>
@@ -16562,7 +16560,7 @@
         <f>'Bootstrap'!B38</f>
         <v/>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="27">
         <f>'Bootstrap'!C38</f>
         <v/>
       </c>
@@ -16582,7 +16580,7 @@
         <f>SUM($I$8:I37)</f>
         <v/>
       </c>
-      <c r="H38" s="29">
+      <c r="H38" s="28">
         <f>(1-(E38/100)*G38)/(1+(E38/100)*F38)</f>
         <v/>
       </c>
@@ -16613,7 +16611,7 @@
         <f>'Bootstrap'!B39</f>
         <v/>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="27">
         <f>'Bootstrap'!C39</f>
         <v/>
       </c>
@@ -16633,7 +16631,7 @@
         <f>SUM($I$8:I38)</f>
         <v/>
       </c>
-      <c r="H39" s="29">
+      <c r="H39" s="28">
         <f>(1-(E39/100)*G39)/(1+(E39/100)*F39)</f>
         <v/>
       </c>
@@ -16656,8 +16654,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:L6"/>
+  <mergeCells count="3">
+    <mergeCell ref="O6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="A4:M6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19278,7 +19278,7 @@
         <f>EDATE($F$7,3*0)</f>
         <v/>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <f>(B10-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19319,7 +19319,7 @@
         <f>EDATE($F$7,3*1)</f>
         <v/>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <f>(B11-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19360,7 +19360,7 @@
         <f>EDATE($F$7,3*2)</f>
         <v/>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <f>(B12-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19401,7 +19401,7 @@
         <f>EDATE($F$7,3*3)</f>
         <v/>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <f>(B13-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19442,7 +19442,7 @@
         <f>EDATE($F$7,3*4)</f>
         <v/>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <f>(B14-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19483,7 +19483,7 @@
         <f>EDATE($F$7,3*5)</f>
         <v/>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <f>(B15-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19524,7 +19524,7 @@
         <f>EDATE($F$7,3*6)</f>
         <v/>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <f>(B16-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19565,7 +19565,7 @@
         <f>EDATE($F$7,3*7)</f>
         <v/>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <f>(B17-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19606,7 +19606,7 @@
         <f>EDATE($F$7,3*8)</f>
         <v/>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <f>(B18-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19647,7 +19647,7 @@
         <f>EDATE($F$7,3*9)</f>
         <v/>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="27">
         <f>(B19-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19688,7 +19688,7 @@
         <f>EDATE($F$7,3*10)</f>
         <v/>
       </c>
-      <c r="C20" s="28">
+      <c r="C20" s="27">
         <f>(B20-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19729,7 +19729,7 @@
         <f>EDATE($F$7,3*11)</f>
         <v/>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="27">
         <f>(B21-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19770,7 +19770,7 @@
         <f>EDATE($F$7,3*12)</f>
         <v/>
       </c>
-      <c r="C22" s="28">
+      <c r="C22" s="27">
         <f>(B22-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19811,7 +19811,7 @@
         <f>EDATE($F$7,3*13)</f>
         <v/>
       </c>
-      <c r="C23" s="28">
+      <c r="C23" s="27">
         <f>(B23-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19852,7 +19852,7 @@
         <f>EDATE($F$7,3*14)</f>
         <v/>
       </c>
-      <c r="C24" s="28">
+      <c r="C24" s="27">
         <f>(B24-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19893,7 +19893,7 @@
         <f>EDATE($F$7,3*15)</f>
         <v/>
       </c>
-      <c r="C25" s="28">
+      <c r="C25" s="27">
         <f>(B25-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19934,7 +19934,7 @@
         <f>EDATE($F$7,3*16)</f>
         <v/>
       </c>
-      <c r="C26" s="28">
+      <c r="C26" s="27">
         <f>(B26-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -19975,7 +19975,7 @@
         <f>EDATE($F$7,3*17)</f>
         <v/>
       </c>
-      <c r="C27" s="28">
+      <c r="C27" s="27">
         <f>(B27-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20016,7 +20016,7 @@
         <f>EDATE($F$7,3*18)</f>
         <v/>
       </c>
-      <c r="C28" s="28">
+      <c r="C28" s="27">
         <f>(B28-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20057,7 +20057,7 @@
         <f>EDATE($F$7,3*19)</f>
         <v/>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="27">
         <f>(B29-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20098,7 +20098,7 @@
         <f>EDATE($F$7,3*20)</f>
         <v/>
       </c>
-      <c r="C30" s="28">
+      <c r="C30" s="27">
         <f>(B30-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20139,7 +20139,7 @@
         <f>EDATE($F$7,3*21)</f>
         <v/>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="27">
         <f>(B31-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20180,7 +20180,7 @@
         <f>EDATE($F$7,3*22)</f>
         <v/>
       </c>
-      <c r="C32" s="28">
+      <c r="C32" s="27">
         <f>(B32-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20221,7 +20221,7 @@
         <f>EDATE($F$7,3*23)</f>
         <v/>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="27">
         <f>(B33-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20262,7 +20262,7 @@
         <f>EDATE($F$7,3*24)</f>
         <v/>
       </c>
-      <c r="C34" s="28">
+      <c r="C34" s="27">
         <f>(B34-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20303,7 +20303,7 @@
         <f>EDATE($F$7,3*25)</f>
         <v/>
       </c>
-      <c r="C35" s="28">
+      <c r="C35" s="27">
         <f>(B35-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20344,7 +20344,7 @@
         <f>EDATE($F$7,3*26)</f>
         <v/>
       </c>
-      <c r="C36" s="28">
+      <c r="C36" s="27">
         <f>(B36-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20385,7 +20385,7 @@
         <f>EDATE($F$7,3*27)</f>
         <v/>
       </c>
-      <c r="C37" s="28">
+      <c r="C37" s="27">
         <f>(B37-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20426,7 +20426,7 @@
         <f>EDATE($F$7,3*28)</f>
         <v/>
       </c>
-      <c r="C38" s="28">
+      <c r="C38" s="27">
         <f>(B38-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20467,7 +20467,7 @@
         <f>EDATE($F$7,3*29)</f>
         <v/>
       </c>
-      <c r="C39" s="28">
+      <c r="C39" s="27">
         <f>(B39-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20508,7 +20508,7 @@
         <f>EDATE($F$7,3*30)</f>
         <v/>
       </c>
-      <c r="C40" s="28">
+      <c r="C40" s="27">
         <f>(B40-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20549,7 +20549,7 @@
         <f>EDATE($F$7,3*31)</f>
         <v/>
       </c>
-      <c r="C41" s="28">
+      <c r="C41" s="27">
         <f>(B41-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20582,7 +20582,7 @@
         <f>EDATE($F$7,3*32)</f>
         <v/>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="27">
         <f>(B42-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20615,7 +20615,7 @@
         <f>EDATE($F$7,3*33)</f>
         <v/>
       </c>
-      <c r="C43" s="28">
+      <c r="C43" s="27">
         <f>(B43-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20648,7 +20648,7 @@
         <f>EDATE($F$7,3*34)</f>
         <v/>
       </c>
-      <c r="C44" s="28">
+      <c r="C44" s="27">
         <f>(B44-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20681,7 +20681,7 @@
         <f>EDATE($F$7,3*35)</f>
         <v/>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="27">
         <f>(B45-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20714,7 +20714,7 @@
         <f>EDATE($F$7,3*36)</f>
         <v/>
       </c>
-      <c r="C46" s="28">
+      <c r="C46" s="27">
         <f>(B46-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20747,7 +20747,7 @@
         <f>EDATE($F$7,3*37)</f>
         <v/>
       </c>
-      <c r="C47" s="28">
+      <c r="C47" s="27">
         <f>(B47-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20780,7 +20780,7 @@
         <f>EDATE($F$7,3*38)</f>
         <v/>
       </c>
-      <c r="C48" s="28">
+      <c r="C48" s="27">
         <f>(B48-VAL_DATE)/365</f>
         <v/>
       </c>
@@ -20813,7 +20813,7 @@
         <f>EDATE($F$7,3*39)</f>
         <v/>
       </c>
-      <c r="C49" s="28">
+      <c r="C49" s="27">
         <f>(B49-VAL_DATE)/365</f>
         <v/>
       </c>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -34,7 +34,7 @@
     <definedName name="SOFR_TKR">Instructions!$B$13</definedName>
     <definedName name="S490_TKR">Instructions!$B$14</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" iterate="1" iterateCount="100" iterateDelta="1e-10"/>
 </workbook>
 </file>
 
@@ -15990,7 +15990,7 @@
         <v/>
       </c>
       <c r="H33" s="29">
-        <f>($D$4-(E33/100)*G33)/(1+(E33/100)*F33)</f>
+        <f>H32*(H34/H32)^((C33-C32)/(C34-C32))</f>
         <v/>
       </c>
       <c r="I33" s="17">
@@ -16104,7 +16104,7 @@
         <v/>
       </c>
       <c r="H35" s="29">
-        <f>($D$4-(E35/100)*G35)/(1+(E35/100)*F35)</f>
+        <f>H34*(H37/H34)^((C35-C34)/(C37-C34))</f>
         <v/>
       </c>
       <c r="I35" s="17">
@@ -16161,7 +16161,7 @@
         <v/>
       </c>
       <c r="H36" s="29">
-        <f>($D$4-(E36/100)*G36)/(1+(E36/100)*F36)</f>
+        <f>H34*(H37/H34)^((C36-C34)/(C37-C34))</f>
         <v/>
       </c>
       <c r="I36" s="17">
@@ -16275,7 +16275,7 @@
         <v/>
       </c>
       <c r="H38" s="29">
-        <f>($D$4-(E38/100)*G38)/(1+(E38/100)*F38)</f>
+        <f>H37*(H42/H37)^((C38-C37)/(C42-C37))</f>
         <v/>
       </c>
       <c r="I38" s="17">
@@ -16332,7 +16332,7 @@
         <v/>
       </c>
       <c r="H39" s="29">
-        <f>($D$4-(E39/100)*G39)/(1+(E39/100)*F39)</f>
+        <f>H37*(H42/H37)^((C39-C37)/(C42-C37))</f>
         <v/>
       </c>
       <c r="I39" s="17">
@@ -16389,7 +16389,7 @@
         <v/>
       </c>
       <c r="H40" s="29">
-        <f>($D$4-(E40/100)*G40)/(1+(E40/100)*F40)</f>
+        <f>H37*(H42/H37)^((C40-C37)/(C42-C37))</f>
         <v/>
       </c>
       <c r="I40" s="17">
@@ -16446,7 +16446,7 @@
         <v/>
       </c>
       <c r="H41" s="29">
-        <f>($D$4-(E41/100)*G41)/(1+(E41/100)*F41)</f>
+        <f>H37*(H42/H37)^((C41-C37)/(C42-C37))</f>
         <v/>
       </c>
       <c r="I41" s="17">
@@ -16560,7 +16560,7 @@
         <v/>
       </c>
       <c r="H43" s="29">
-        <f>($D$4-(E43/100)*G43)/(1+(E43/100)*F43)</f>
+        <f>H42*(H47/H42)^((C43-C42)/(C47-C42))</f>
         <v/>
       </c>
       <c r="I43" s="17">
@@ -16617,7 +16617,7 @@
         <v/>
       </c>
       <c r="H44" s="29">
-        <f>($D$4-(E44/100)*G44)/(1+(E44/100)*F44)</f>
+        <f>H42*(H47/H42)^((C44-C42)/(C47-C42))</f>
         <v/>
       </c>
       <c r="I44" s="17">
@@ -16674,7 +16674,7 @@
         <v/>
       </c>
       <c r="H45" s="29">
-        <f>($D$4-(E45/100)*G45)/(1+(E45/100)*F45)</f>
+        <f>H42*(H47/H42)^((C45-C42)/(C47-C42))</f>
         <v/>
       </c>
       <c r="I45" s="17">
@@ -16731,7 +16731,7 @@
         <v/>
       </c>
       <c r="H46" s="29">
-        <f>($D$4-(E46/100)*G46)/(1+(E46/100)*F46)</f>
+        <f>H42*(H47/H42)^((C46-C42)/(C47-C42))</f>
         <v/>
       </c>
       <c r="I46" s="17">
@@ -16845,7 +16845,7 @@
         <v/>
       </c>
       <c r="H48" s="29">
-        <f>($D$4-(E48/100)*G48)/(1+(E48/100)*F48)</f>
+        <f>H47*(H52/H47)^((C48-C47)/(C52-C47))</f>
         <v/>
       </c>
       <c r="I48" s="17">
@@ -16902,7 +16902,7 @@
         <v/>
       </c>
       <c r="H49" s="29">
-        <f>($D$4-(E49/100)*G49)/(1+(E49/100)*F49)</f>
+        <f>H47*(H52/H47)^((C49-C47)/(C52-C47))</f>
         <v/>
       </c>
       <c r="I49" s="17">
@@ -16959,7 +16959,7 @@
         <v/>
       </c>
       <c r="H50" s="29">
-        <f>($D$4-(E50/100)*G50)/(1+(E50/100)*F50)</f>
+        <f>H47*(H52/H47)^((C50-C47)/(C52-C47))</f>
         <v/>
       </c>
       <c r="I50" s="17">
@@ -17016,7 +17016,7 @@
         <v/>
       </c>
       <c r="H51" s="29">
-        <f>($D$4-(E51/100)*G51)/(1+(E51/100)*F51)</f>
+        <f>H47*(H52/H47)^((C51-C47)/(C52-C47))</f>
         <v/>
       </c>
       <c r="I51" s="17">
@@ -17130,7 +17130,7 @@
         <v/>
       </c>
       <c r="H53" s="29">
-        <f>($D$4-(E53/100)*G53)/(1+(E53/100)*F53)</f>
+        <f>H52*(H62/H52)^((C53-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I53" s="17">
@@ -17187,7 +17187,7 @@
         <v/>
       </c>
       <c r="H54" s="29">
-        <f>($D$4-(E54/100)*G54)/(1+(E54/100)*F54)</f>
+        <f>H52*(H62/H52)^((C54-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I54" s="17">
@@ -17244,7 +17244,7 @@
         <v/>
       </c>
       <c r="H55" s="29">
-        <f>($D$4-(E55/100)*G55)/(1+(E55/100)*F55)</f>
+        <f>H52*(H62/H52)^((C55-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I55" s="17">
@@ -17301,7 +17301,7 @@
         <v/>
       </c>
       <c r="H56" s="29">
-        <f>($D$4-(E56/100)*G56)/(1+(E56/100)*F56)</f>
+        <f>H52*(H62/H52)^((C56-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I56" s="17">
@@ -17358,7 +17358,7 @@
         <v/>
       </c>
       <c r="H57" s="29">
-        <f>($D$4-(E57/100)*G57)/(1+(E57/100)*F57)</f>
+        <f>H52*(H62/H52)^((C57-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I57" s="17">
@@ -17415,7 +17415,7 @@
         <v/>
       </c>
       <c r="H58" s="29">
-        <f>($D$4-(E58/100)*G58)/(1+(E58/100)*F58)</f>
+        <f>H52*(H62/H52)^((C58-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I58" s="17">
@@ -17472,7 +17472,7 @@
         <v/>
       </c>
       <c r="H59" s="29">
-        <f>($D$4-(E59/100)*G59)/(1+(E59/100)*F59)</f>
+        <f>H52*(H62/H52)^((C59-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I59" s="17">
@@ -17529,7 +17529,7 @@
         <v/>
       </c>
       <c r="H60" s="29">
-        <f>($D$4-(E60/100)*G60)/(1+(E60/100)*F60)</f>
+        <f>H52*(H62/H52)^((C60-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I60" s="17">
@@ -17586,7 +17586,7 @@
         <v/>
       </c>
       <c r="H61" s="29">
-        <f>($D$4-(E61/100)*G61)/(1+(E61/100)*F61)</f>
+        <f>H52*(H62/H52)^((C61-C52)/(C62-C52))</f>
         <v/>
       </c>
       <c r="I61" s="17">
@@ -17700,7 +17700,7 @@
         <v/>
       </c>
       <c r="H63" s="29">
-        <f>($D$4-(E63/100)*G63)/(1+(E63/100)*F63)</f>
+        <f>H62*(H72/H62)^((C63-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I63" s="17">
@@ -17757,7 +17757,7 @@
         <v/>
       </c>
       <c r="H64" s="29">
-        <f>($D$4-(E64/100)*G64)/(1+(E64/100)*F64)</f>
+        <f>H62*(H72/H62)^((C64-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I64" s="17">
@@ -17814,7 +17814,7 @@
         <v/>
       </c>
       <c r="H65" s="29">
-        <f>($D$4-(E65/100)*G65)/(1+(E65/100)*F65)</f>
+        <f>H62*(H72/H62)^((C65-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I65" s="17">
@@ -17871,7 +17871,7 @@
         <v/>
       </c>
       <c r="H66" s="29">
-        <f>($D$4-(E66/100)*G66)/(1+(E66/100)*F66)</f>
+        <f>H62*(H72/H62)^((C66-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I66" s="17">
@@ -17928,7 +17928,7 @@
         <v/>
       </c>
       <c r="H67" s="29">
-        <f>($D$4-(E67/100)*G67)/(1+(E67/100)*F67)</f>
+        <f>H62*(H72/H62)^((C67-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I67" s="17">
@@ -17985,7 +17985,7 @@
         <v/>
       </c>
       <c r="H68" s="29">
-        <f>($D$4-(E68/100)*G68)/(1+(E68/100)*F68)</f>
+        <f>H62*(H72/H62)^((C68-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I68" s="17">
@@ -18042,7 +18042,7 @@
         <v/>
       </c>
       <c r="H69" s="29">
-        <f>($D$4-(E69/100)*G69)/(1+(E69/100)*F69)</f>
+        <f>H62*(H72/H62)^((C69-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I69" s="17">
@@ -18099,7 +18099,7 @@
         <v/>
       </c>
       <c r="H70" s="29">
-        <f>($D$4-(E70/100)*G70)/(1+(E70/100)*F70)</f>
+        <f>H62*(H72/H62)^((C70-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I70" s="17">
@@ -18156,7 +18156,7 @@
         <v/>
       </c>
       <c r="H71" s="29">
-        <f>($D$4-(E71/100)*G71)/(1+(E71/100)*F71)</f>
+        <f>H62*(H72/H62)^((C71-C62)/(C72-C62))</f>
         <v/>
       </c>
       <c r="I71" s="17">

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -197,8 +197,8 @@
     <xf numFmtId="167" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3990,7 +3990,7 @@
         <f>B9-B8</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="34">
         <f>-LN(C9/C8)</f>
         <v/>
       </c>
@@ -4006,11 +4006,11 @@
         <f>G8</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <f>(G9-G8)/D9-J9*D9</f>
         <v/>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="34">
         <f>3*(G9-G8)/D9^2-6*(E9-G8*D9)/D9^3</f>
         <v/>
       </c>
@@ -4040,7 +4040,7 @@
         <f>B10-B9</f>
         <v/>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <f>-LN(C10/C9)</f>
         <v/>
       </c>
@@ -4056,11 +4056,11 @@
         <f>G9</f>
         <v/>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <f>(G10-G9)/D10-J10*D10</f>
         <v/>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="34">
         <f>3*(G10-G9)/D10^2-6*(E10-G9*D10)/D10^3</f>
         <v/>
       </c>
@@ -4090,7 +4090,7 @@
         <f>B11-B10</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <f>-LN(C11/C10)</f>
         <v/>
       </c>
@@ -4106,11 +4106,11 @@
         <f>G10</f>
         <v/>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <f>(G11-G10)/D11-J11*D11</f>
         <v/>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="34">
         <f>3*(G11-G10)/D11^2-6*(E11-G10*D11)/D11^3</f>
         <v/>
       </c>
@@ -4140,7 +4140,7 @@
         <f>B12-B11</f>
         <v/>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="34">
         <f>-LN(C12/C11)</f>
         <v/>
       </c>
@@ -4156,11 +4156,11 @@
         <f>G11</f>
         <v/>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="34">
         <f>(G12-G11)/D12-J12*D12</f>
         <v/>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="34">
         <f>3*(G12-G11)/D12^2-6*(E12-G11*D12)/D12^3</f>
         <v/>
       </c>
@@ -4190,7 +4190,7 @@
         <f>B13-B12</f>
         <v/>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="34">
         <f>-LN(C13/C12)</f>
         <v/>
       </c>
@@ -4206,11 +4206,11 @@
         <f>G12</f>
         <v/>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="34">
         <f>(G13-G12)/D13-J13*D13</f>
         <v/>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="34">
         <f>3*(G13-G12)/D13^2-6*(E13-G12*D13)/D13^3</f>
         <v/>
       </c>
@@ -4240,7 +4240,7 @@
         <f>B14-B13</f>
         <v/>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="34">
         <f>-LN(C14/C13)</f>
         <v/>
       </c>
@@ -4256,11 +4256,11 @@
         <f>G13</f>
         <v/>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="34">
         <f>(G14-G13)/D14-J14*D14</f>
         <v/>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="34">
         <f>3*(G14-G13)/D14^2-6*(E14-G13*D14)/D14^3</f>
         <v/>
       </c>
@@ -4290,7 +4290,7 @@
         <f>B15-B14</f>
         <v/>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="34">
         <f>-LN(C15/C14)</f>
         <v/>
       </c>
@@ -4306,11 +4306,11 @@
         <f>G14</f>
         <v/>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="34">
         <f>(G15-G14)/D15-J15*D15</f>
         <v/>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="34">
         <f>3*(G15-G14)/D15^2-6*(E15-G14*D15)/D15^3</f>
         <v/>
       </c>
@@ -4340,7 +4340,7 @@
         <f>B16-B15</f>
         <v/>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="34">
         <f>-LN(C16/C15)</f>
         <v/>
       </c>
@@ -4356,11 +4356,11 @@
         <f>G15</f>
         <v/>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="34">
         <f>(G16-G15)/D16-J16*D16</f>
         <v/>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="34">
         <f>3*(G16-G15)/D16^2-6*(E16-G15*D16)/D16^3</f>
         <v/>
       </c>
@@ -4390,7 +4390,7 @@
         <f>B17-B16</f>
         <v/>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="34">
         <f>-LN(C17/C16)</f>
         <v/>
       </c>
@@ -4406,11 +4406,11 @@
         <f>G16</f>
         <v/>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="34">
         <f>(G17-G16)/D17-J17*D17</f>
         <v/>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="34">
         <f>3*(G17-G16)/D17^2-6*(E17-G16*D17)/D17^3</f>
         <v/>
       </c>
@@ -4440,7 +4440,7 @@
         <f>B18-B17</f>
         <v/>
       </c>
-      <c r="E18" s="35">
+      <c r="E18" s="34">
         <f>-LN(C18/C17)</f>
         <v/>
       </c>
@@ -4456,11 +4456,11 @@
         <f>G17</f>
         <v/>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="34">
         <f>(G18-G17)/D18-J18*D18</f>
         <v/>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="34">
         <f>3*(G18-G17)/D18^2-6*(E18-G17*D18)/D18^3</f>
         <v/>
       </c>
@@ -4490,7 +4490,7 @@
         <f>B19-B18</f>
         <v/>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="34">
         <f>-LN(C19/C18)</f>
         <v/>
       </c>
@@ -4506,11 +4506,11 @@
         <f>G18</f>
         <v/>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <f>(G19-G18)/D19-J19*D19</f>
         <v/>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="34">
         <f>3*(G19-G18)/D19^2-6*(E19-G18*D19)/D19^3</f>
         <v/>
       </c>
@@ -4540,7 +4540,7 @@
         <f>B20-B19</f>
         <v/>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="34">
         <f>-LN(C20/C19)</f>
         <v/>
       </c>
@@ -4556,11 +4556,11 @@
         <f>G19</f>
         <v/>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <f>(G20-G19)/D20-J20*D20</f>
         <v/>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="34">
         <f>3*(G20-G19)/D20^2-6*(E20-G19*D20)/D20^3</f>
         <v/>
       </c>
@@ -4590,7 +4590,7 @@
         <f>B21-B20</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="34">
         <f>-LN(C21/C20)</f>
         <v/>
       </c>
@@ -4606,11 +4606,11 @@
         <f>G20</f>
         <v/>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="34">
         <f>(G21-G20)/D21-J21*D21</f>
         <v/>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="34">
         <f>3*(G21-G20)/D21^2-6*(E21-G20*D21)/D21^3</f>
         <v/>
       </c>
@@ -4640,7 +4640,7 @@
         <f>B22-B21</f>
         <v/>
       </c>
-      <c r="E22" s="35">
+      <c r="E22" s="34">
         <f>-LN(C22/C21)</f>
         <v/>
       </c>
@@ -4656,11 +4656,11 @@
         <f>G21</f>
         <v/>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="34">
         <f>(G22-G21)/D22-J22*D22</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="34">
         <f>3*(G22-G21)/D22^2-6*(E22-G21*D22)/D22^3</f>
         <v/>
       </c>
@@ -4690,7 +4690,7 @@
         <f>B23-B22</f>
         <v/>
       </c>
-      <c r="E23" s="35">
+      <c r="E23" s="34">
         <f>-LN(C23/C22)</f>
         <v/>
       </c>
@@ -4706,11 +4706,11 @@
         <f>G22</f>
         <v/>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="34">
         <f>(G23-G22)/D23-J23*D23</f>
         <v/>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="34">
         <f>3*(G23-G22)/D23^2-6*(E23-G22*D23)/D23^3</f>
         <v/>
       </c>
@@ -4740,7 +4740,7 @@
         <f>B24-B23</f>
         <v/>
       </c>
-      <c r="E24" s="35">
+      <c r="E24" s="34">
         <f>-LN(C24/C23)</f>
         <v/>
       </c>
@@ -4756,11 +4756,11 @@
         <f>G23</f>
         <v/>
       </c>
-      <c r="I24" s="35">
+      <c r="I24" s="34">
         <f>(G24-G23)/D24-J24*D24</f>
         <v/>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="34">
         <f>3*(G24-G23)/D24^2-6*(E24-G23*D24)/D24^3</f>
         <v/>
       </c>
@@ -4790,7 +4790,7 @@
         <f>B25-B24</f>
         <v/>
       </c>
-      <c r="E25" s="35">
+      <c r="E25" s="34">
         <f>-LN(C25/C24)</f>
         <v/>
       </c>
@@ -4806,11 +4806,11 @@
         <f>G24</f>
         <v/>
       </c>
-      <c r="I25" s="35">
+      <c r="I25" s="34">
         <f>(G25-G24)/D25-J25*D25</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="34">
         <f>3*(G25-G24)/D25^2-6*(E25-G24*D25)/D25^3</f>
         <v/>
       </c>
@@ -4840,7 +4840,7 @@
         <f>B26-B25</f>
         <v/>
       </c>
-      <c r="E26" s="35">
+      <c r="E26" s="34">
         <f>-LN(C26/C25)</f>
         <v/>
       </c>
@@ -4856,11 +4856,11 @@
         <f>G25</f>
         <v/>
       </c>
-      <c r="I26" s="35">
+      <c r="I26" s="34">
         <f>(G26-G25)/D26-J26*D26</f>
         <v/>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="34">
         <f>3*(G26-G25)/D26^2-6*(E26-G25*D26)/D26^3</f>
         <v/>
       </c>
@@ -4890,7 +4890,7 @@
         <f>B27-B26</f>
         <v/>
       </c>
-      <c r="E27" s="35">
+      <c r="E27" s="34">
         <f>-LN(C27/C26)</f>
         <v/>
       </c>
@@ -4906,11 +4906,11 @@
         <f>G26</f>
         <v/>
       </c>
-      <c r="I27" s="35">
+      <c r="I27" s="34">
         <f>(G27-G26)/D27-J27*D27</f>
         <v/>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="34">
         <f>3*(G27-G26)/D27^2-6*(E27-G26*D27)/D27^3</f>
         <v/>
       </c>
@@ -4940,7 +4940,7 @@
         <f>B28-B27</f>
         <v/>
       </c>
-      <c r="E28" s="35">
+      <c r="E28" s="34">
         <f>-LN(C28/C27)</f>
         <v/>
       </c>
@@ -4956,11 +4956,11 @@
         <f>G27</f>
         <v/>
       </c>
-      <c r="I28" s="35">
+      <c r="I28" s="34">
         <f>(G28-G27)/D28-J28*D28</f>
         <v/>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="34">
         <f>3*(G28-G27)/D28^2-6*(E28-G27*D28)/D28^3</f>
         <v/>
       </c>
@@ -4990,7 +4990,7 @@
         <f>B29-B28</f>
         <v/>
       </c>
-      <c r="E29" s="35">
+      <c r="E29" s="34">
         <f>-LN(C29/C28)</f>
         <v/>
       </c>
@@ -5006,11 +5006,11 @@
         <f>G28</f>
         <v/>
       </c>
-      <c r="I29" s="35">
+      <c r="I29" s="34">
         <f>(G29-G28)/D29-J29*D29</f>
         <v/>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="34">
         <f>3*(G29-G28)/D29^2-6*(E29-G28*D29)/D29^3</f>
         <v/>
       </c>
@@ -5040,7 +5040,7 @@
         <f>B30-B29</f>
         <v/>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="34">
         <f>-LN(C30/C29)</f>
         <v/>
       </c>
@@ -5056,11 +5056,11 @@
         <f>G29</f>
         <v/>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="34">
         <f>(G30-G29)/D30-J30*D30</f>
         <v/>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="34">
         <f>3*(G30-G29)/D30^2-6*(E30-G29*D30)/D30^3</f>
         <v/>
       </c>
@@ -5090,7 +5090,7 @@
         <f>B31-B30</f>
         <v/>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="34">
         <f>-LN(C31/C30)</f>
         <v/>
       </c>
@@ -5106,11 +5106,11 @@
         <f>G30</f>
         <v/>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="34">
         <f>(G31-G30)/D31-J31*D31</f>
         <v/>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="34">
         <f>3*(G31-G30)/D31^2-6*(E31-G30*D31)/D31^3</f>
         <v/>
       </c>
@@ -5140,7 +5140,7 @@
         <f>B32-B31</f>
         <v/>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="34">
         <f>-LN(C32/C31)</f>
         <v/>
       </c>
@@ -5156,11 +5156,11 @@
         <f>G31</f>
         <v/>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="34">
         <f>(G32-G31)/D32-J32*D32</f>
         <v/>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="34">
         <f>3*(G32-G31)/D32^2-6*(E32-G31*D32)/D32^3</f>
         <v/>
       </c>
@@ -5190,7 +5190,7 @@
         <f>B33-B32</f>
         <v/>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="34">
         <f>-LN(C33/C32)</f>
         <v/>
       </c>
@@ -5206,11 +5206,11 @@
         <f>G32</f>
         <v/>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="34">
         <f>(G33-G32)/D33-J33*D33</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="34">
         <f>3*(G33-G32)/D33^2-6*(E33-G32*D33)/D33^3</f>
         <v/>
       </c>
@@ -5240,7 +5240,7 @@
         <f>B34-B33</f>
         <v/>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="34">
         <f>-LN(C34/C33)</f>
         <v/>
       </c>
@@ -5256,11 +5256,11 @@
         <f>G33</f>
         <v/>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="34">
         <f>(G34-G33)/D34-J34*D34</f>
         <v/>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="34">
         <f>3*(G34-G33)/D34^2-6*(E34-G33*D34)/D34^3</f>
         <v/>
       </c>
@@ -5290,7 +5290,7 @@
         <f>B35-B34</f>
         <v/>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="34">
         <f>-LN(C35/C34)</f>
         <v/>
       </c>
@@ -5306,11 +5306,11 @@
         <f>G34</f>
         <v/>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="34">
         <f>(G35-G34)/D35-J35*D35</f>
         <v/>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="34">
         <f>3*(G35-G34)/D35^2-6*(E35-G34*D35)/D35^3</f>
         <v/>
       </c>
@@ -5340,7 +5340,7 @@
         <f>B36-B35</f>
         <v/>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="34">
         <f>-LN(C36/C35)</f>
         <v/>
       </c>
@@ -5356,11 +5356,11 @@
         <f>G35</f>
         <v/>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="34">
         <f>(G36-G35)/D36-J36*D36</f>
         <v/>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="34">
         <f>3*(G36-G35)/D36^2-6*(E36-G35*D36)/D36^3</f>
         <v/>
       </c>
@@ -5390,7 +5390,7 @@
         <f>B37-B36</f>
         <v/>
       </c>
-      <c r="E37" s="35">
+      <c r="E37" s="34">
         <f>-LN(C37/C36)</f>
         <v/>
       </c>
@@ -5406,11 +5406,11 @@
         <f>G36</f>
         <v/>
       </c>
-      <c r="I37" s="35">
+      <c r="I37" s="34">
         <f>(G37-G36)/D37-J37*D37</f>
         <v/>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="34">
         <f>3*(G37-G36)/D37^2-6*(E37-G36*D37)/D37^3</f>
         <v/>
       </c>
@@ -5440,7 +5440,7 @@
         <f>B38-B37</f>
         <v/>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="34">
         <f>-LN(C38/C37)</f>
         <v/>
       </c>
@@ -5456,11 +5456,11 @@
         <f>G37</f>
         <v/>
       </c>
-      <c r="I38" s="35">
+      <c r="I38" s="34">
         <f>(G38-G37)/D38-J38*D38</f>
         <v/>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="34">
         <f>3*(G38-G37)/D38^2-6*(E38-G37*D38)/D38^3</f>
         <v/>
       </c>
@@ -5490,7 +5490,7 @@
         <f>B39-B38</f>
         <v/>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="34">
         <f>-LN(C39/C38)</f>
         <v/>
       </c>
@@ -5506,11 +5506,11 @@
         <f>G38</f>
         <v/>
       </c>
-      <c r="I39" s="35">
+      <c r="I39" s="34">
         <f>(G39-G38)/D39-J39*D39</f>
         <v/>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="34">
         <f>3*(G39-G38)/D39^2-6*(E39-G38*D39)/D39^3</f>
         <v/>
       </c>
@@ -5540,7 +5540,7 @@
         <f>B40-B39</f>
         <v/>
       </c>
-      <c r="E40" s="35">
+      <c r="E40" s="34">
         <f>-LN(C40/C39)</f>
         <v/>
       </c>
@@ -5556,11 +5556,11 @@
         <f>G39</f>
         <v/>
       </c>
-      <c r="I40" s="35">
+      <c r="I40" s="34">
         <f>(G40-G39)/D40-J40*D40</f>
         <v/>
       </c>
-      <c r="J40" s="35">
+      <c r="J40" s="34">
         <f>3*(G40-G39)/D40^2-6*(E40-G39*D40)/D40^3</f>
         <v/>
       </c>
@@ -5590,7 +5590,7 @@
         <f>B41-B40</f>
         <v/>
       </c>
-      <c r="E41" s="35">
+      <c r="E41" s="34">
         <f>-LN(C41/C40)</f>
         <v/>
       </c>
@@ -5606,11 +5606,11 @@
         <f>G40</f>
         <v/>
       </c>
-      <c r="I41" s="35">
+      <c r="I41" s="34">
         <f>(G41-G40)/D41-J41*D41</f>
         <v/>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="34">
         <f>3*(G41-G40)/D41^2-6*(E41-G40*D41)/D41^3</f>
         <v/>
       </c>
@@ -5640,7 +5640,7 @@
         <f>B42-B41</f>
         <v/>
       </c>
-      <c r="E42" s="35">
+      <c r="E42" s="34">
         <f>-LN(C42/C41)</f>
         <v/>
       </c>
@@ -5656,11 +5656,11 @@
         <f>G41</f>
         <v/>
       </c>
-      <c r="I42" s="35">
+      <c r="I42" s="34">
         <f>(G42-G41)/D42-J42*D42</f>
         <v/>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="34">
         <f>3*(G42-G41)/D42^2-6*(E42-G41*D42)/D42^3</f>
         <v/>
       </c>
@@ -5690,7 +5690,7 @@
         <f>B43-B42</f>
         <v/>
       </c>
-      <c r="E43" s="35">
+      <c r="E43" s="34">
         <f>-LN(C43/C42)</f>
         <v/>
       </c>
@@ -5706,11 +5706,11 @@
         <f>G42</f>
         <v/>
       </c>
-      <c r="I43" s="35">
+      <c r="I43" s="34">
         <f>(G43-G42)/D43-J43*D43</f>
         <v/>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="34">
         <f>3*(G43-G42)/D43^2-6*(E43-G42*D43)/D43^3</f>
         <v/>
       </c>
@@ -5740,7 +5740,7 @@
         <f>B44-B43</f>
         <v/>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="34">
         <f>-LN(C44/C43)</f>
         <v/>
       </c>
@@ -5756,11 +5756,11 @@
         <f>G43</f>
         <v/>
       </c>
-      <c r="I44" s="35">
+      <c r="I44" s="34">
         <f>(G44-G43)/D44-J44*D44</f>
         <v/>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="34">
         <f>3*(G44-G43)/D44^2-6*(E44-G43*D44)/D44^3</f>
         <v/>
       </c>
@@ -5790,7 +5790,7 @@
         <f>B45-B44</f>
         <v/>
       </c>
-      <c r="E45" s="35">
+      <c r="E45" s="34">
         <f>-LN(C45/C44)</f>
         <v/>
       </c>
@@ -5806,11 +5806,11 @@
         <f>G44</f>
         <v/>
       </c>
-      <c r="I45" s="35">
+      <c r="I45" s="34">
         <f>(G45-G44)/D45-J45*D45</f>
         <v/>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="34">
         <f>3*(G45-G44)/D45^2-6*(E45-G44*D45)/D45^3</f>
         <v/>
       </c>
@@ -5840,7 +5840,7 @@
         <f>B46-B45</f>
         <v/>
       </c>
-      <c r="E46" s="35">
+      <c r="E46" s="34">
         <f>-LN(C46/C45)</f>
         <v/>
       </c>
@@ -5856,11 +5856,11 @@
         <f>G45</f>
         <v/>
       </c>
-      <c r="I46" s="35">
+      <c r="I46" s="34">
         <f>(G46-G45)/D46-J46*D46</f>
         <v/>
       </c>
-      <c r="J46" s="35">
+      <c r="J46" s="34">
         <f>3*(G46-G45)/D46^2-6*(E46-G45*D46)/D46^3</f>
         <v/>
       </c>
@@ -5890,7 +5890,7 @@
         <f>B47-B46</f>
         <v/>
       </c>
-      <c r="E47" s="35">
+      <c r="E47" s="34">
         <f>-LN(C47/C46)</f>
         <v/>
       </c>
@@ -5906,11 +5906,11 @@
         <f>G46</f>
         <v/>
       </c>
-      <c r="I47" s="35">
+      <c r="I47" s="34">
         <f>(G47-G46)/D47-J47*D47</f>
         <v/>
       </c>
-      <c r="J47" s="35">
+      <c r="J47" s="34">
         <f>3*(G47-G46)/D47^2-6*(E47-G46*D47)/D47^3</f>
         <v/>
       </c>
@@ -5940,7 +5940,7 @@
         <f>B48-B47</f>
         <v/>
       </c>
-      <c r="E48" s="35">
+      <c r="E48" s="34">
         <f>-LN(C48/C47)</f>
         <v/>
       </c>
@@ -5956,11 +5956,11 @@
         <f>G47</f>
         <v/>
       </c>
-      <c r="I48" s="35">
+      <c r="I48" s="34">
         <f>(G48-G47)/D48-J48*D48</f>
         <v/>
       </c>
-      <c r="J48" s="35">
+      <c r="J48" s="34">
         <f>3*(G48-G47)/D48^2-6*(E48-G47*D48)/D48^3</f>
         <v/>
       </c>
@@ -5990,7 +5990,7 @@
         <f>B49-B48</f>
         <v/>
       </c>
-      <c r="E49" s="35">
+      <c r="E49" s="34">
         <f>-LN(C49/C48)</f>
         <v/>
       </c>
@@ -6006,11 +6006,11 @@
         <f>G48</f>
         <v/>
       </c>
-      <c r="I49" s="35">
+      <c r="I49" s="34">
         <f>(G49-G48)/D49-J49*D49</f>
         <v/>
       </c>
-      <c r="J49" s="35">
+      <c r="J49" s="34">
         <f>3*(G49-G48)/D49^2-6*(E49-G48*D49)/D49^3</f>
         <v/>
       </c>
@@ -6040,7 +6040,7 @@
         <f>B50-B49</f>
         <v/>
       </c>
-      <c r="E50" s="35">
+      <c r="E50" s="34">
         <f>-LN(C50/C49)</f>
         <v/>
       </c>
@@ -6056,11 +6056,11 @@
         <f>G49</f>
         <v/>
       </c>
-      <c r="I50" s="35">
+      <c r="I50" s="34">
         <f>(G50-G49)/D50-J50*D50</f>
         <v/>
       </c>
-      <c r="J50" s="35">
+      <c r="J50" s="34">
         <f>3*(G50-G49)/D50^2-6*(E50-G49*D50)/D50^3</f>
         <v/>
       </c>
@@ -6090,7 +6090,7 @@
         <f>B51-B50</f>
         <v/>
       </c>
-      <c r="E51" s="35">
+      <c r="E51" s="34">
         <f>-LN(C51/C50)</f>
         <v/>
       </c>
@@ -6106,11 +6106,11 @@
         <f>G50</f>
         <v/>
       </c>
-      <c r="I51" s="35">
+      <c r="I51" s="34">
         <f>(G51-G50)/D51-J51*D51</f>
         <v/>
       </c>
-      <c r="J51" s="35">
+      <c r="J51" s="34">
         <f>3*(G51-G50)/D51^2-6*(E51-G50*D51)/D51^3</f>
         <v/>
       </c>
@@ -6140,7 +6140,7 @@
         <f>B52-B51</f>
         <v/>
       </c>
-      <c r="E52" s="35">
+      <c r="E52" s="34">
         <f>-LN(C52/C51)</f>
         <v/>
       </c>
@@ -6156,11 +6156,11 @@
         <f>G51</f>
         <v/>
       </c>
-      <c r="I52" s="35">
+      <c r="I52" s="34">
         <f>(G52-G51)/D52-J52*D52</f>
         <v/>
       </c>
-      <c r="J52" s="35">
+      <c r="J52" s="34">
         <f>3*(G52-G51)/D52^2-6*(E52-G51*D52)/D52^3</f>
         <v/>
       </c>
@@ -6190,7 +6190,7 @@
         <f>B53-B52</f>
         <v/>
       </c>
-      <c r="E53" s="35">
+      <c r="E53" s="34">
         <f>-LN(C53/C52)</f>
         <v/>
       </c>
@@ -6206,11 +6206,11 @@
         <f>G52</f>
         <v/>
       </c>
-      <c r="I53" s="35">
+      <c r="I53" s="34">
         <f>(G53-G52)/D53-J53*D53</f>
         <v/>
       </c>
-      <c r="J53" s="35">
+      <c r="J53" s="34">
         <f>3*(G53-G52)/D53^2-6*(E53-G52*D53)/D53^3</f>
         <v/>
       </c>
@@ -6240,7 +6240,7 @@
         <f>B54-B53</f>
         <v/>
       </c>
-      <c r="E54" s="35">
+      <c r="E54" s="34">
         <f>-LN(C54/C53)</f>
         <v/>
       </c>
@@ -6256,11 +6256,11 @@
         <f>G53</f>
         <v/>
       </c>
-      <c r="I54" s="35">
+      <c r="I54" s="34">
         <f>(G54-G53)/D54-J54*D54</f>
         <v/>
       </c>
-      <c r="J54" s="35">
+      <c r="J54" s="34">
         <f>3*(G54-G53)/D54^2-6*(E54-G53*D54)/D54^3</f>
         <v/>
       </c>
@@ -6290,7 +6290,7 @@
         <f>B55-B54</f>
         <v/>
       </c>
-      <c r="E55" s="35">
+      <c r="E55" s="34">
         <f>-LN(C55/C54)</f>
         <v/>
       </c>
@@ -6306,11 +6306,11 @@
         <f>G54</f>
         <v/>
       </c>
-      <c r="I55" s="35">
+      <c r="I55" s="34">
         <f>(G55-G54)/D55-J55*D55</f>
         <v/>
       </c>
-      <c r="J55" s="35">
+      <c r="J55" s="34">
         <f>3*(G55-G54)/D55^2-6*(E55-G54*D55)/D55^3</f>
         <v/>
       </c>
@@ -6340,7 +6340,7 @@
         <f>B56-B55</f>
         <v/>
       </c>
-      <c r="E56" s="35">
+      <c r="E56" s="34">
         <f>-LN(C56/C55)</f>
         <v/>
       </c>
@@ -6356,11 +6356,11 @@
         <f>G55</f>
         <v/>
       </c>
-      <c r="I56" s="35">
+      <c r="I56" s="34">
         <f>(G56-G55)/D56-J56*D56</f>
         <v/>
       </c>
-      <c r="J56" s="35">
+      <c r="J56" s="34">
         <f>3*(G56-G55)/D56^2-6*(E56-G55*D56)/D56^3</f>
         <v/>
       </c>
@@ -6390,7 +6390,7 @@
         <f>B57-B56</f>
         <v/>
       </c>
-      <c r="E57" s="35">
+      <c r="E57" s="34">
         <f>-LN(C57/C56)</f>
         <v/>
       </c>
@@ -6406,11 +6406,11 @@
         <f>G56</f>
         <v/>
       </c>
-      <c r="I57" s="35">
+      <c r="I57" s="34">
         <f>(G57-G56)/D57-J57*D57</f>
         <v/>
       </c>
-      <c r="J57" s="35">
+      <c r="J57" s="34">
         <f>3*(G57-G56)/D57^2-6*(E57-G56*D57)/D57^3</f>
         <v/>
       </c>
@@ -6440,7 +6440,7 @@
         <f>B58-B57</f>
         <v/>
       </c>
-      <c r="E58" s="35">
+      <c r="E58" s="34">
         <f>-LN(C58/C57)</f>
         <v/>
       </c>
@@ -6456,11 +6456,11 @@
         <f>G57</f>
         <v/>
       </c>
-      <c r="I58" s="35">
+      <c r="I58" s="34">
         <f>(G58-G57)/D58-J58*D58</f>
         <v/>
       </c>
-      <c r="J58" s="35">
+      <c r="J58" s="34">
         <f>3*(G58-G57)/D58^2-6*(E58-G57*D58)/D58^3</f>
         <v/>
       </c>
@@ -6490,7 +6490,7 @@
         <f>B59-B58</f>
         <v/>
       </c>
-      <c r="E59" s="35">
+      <c r="E59" s="34">
         <f>-LN(C59/C58)</f>
         <v/>
       </c>
@@ -6506,11 +6506,11 @@
         <f>G58</f>
         <v/>
       </c>
-      <c r="I59" s="35">
+      <c r="I59" s="34">
         <f>(G59-G58)/D59-J59*D59</f>
         <v/>
       </c>
-      <c r="J59" s="35">
+      <c r="J59" s="34">
         <f>3*(G59-G58)/D59^2-6*(E59-G58*D59)/D59^3</f>
         <v/>
       </c>
@@ -6540,7 +6540,7 @@
         <f>B60-B59</f>
         <v/>
       </c>
-      <c r="E60" s="35">
+      <c r="E60" s="34">
         <f>-LN(C60/C59)</f>
         <v/>
       </c>
@@ -6556,11 +6556,11 @@
         <f>G59</f>
         <v/>
       </c>
-      <c r="I60" s="35">
+      <c r="I60" s="34">
         <f>(G60-G59)/D60-J60*D60</f>
         <v/>
       </c>
-      <c r="J60" s="35">
+      <c r="J60" s="34">
         <f>3*(G60-G59)/D60^2-6*(E60-G59*D60)/D60^3</f>
         <v/>
       </c>
@@ -6590,7 +6590,7 @@
         <f>B61-B60</f>
         <v/>
       </c>
-      <c r="E61" s="35">
+      <c r="E61" s="34">
         <f>-LN(C61/C60)</f>
         <v/>
       </c>
@@ -6606,11 +6606,11 @@
         <f>G60</f>
         <v/>
       </c>
-      <c r="I61" s="35">
+      <c r="I61" s="34">
         <f>(G61-G60)/D61-J61*D61</f>
         <v/>
       </c>
-      <c r="J61" s="35">
+      <c r="J61" s="34">
         <f>3*(G61-G60)/D61^2-6*(E61-G60*D61)/D61^3</f>
         <v/>
       </c>
@@ -6640,7 +6640,7 @@
         <f>B62-B61</f>
         <v/>
       </c>
-      <c r="E62" s="35">
+      <c r="E62" s="34">
         <f>-LN(C62/C61)</f>
         <v/>
       </c>
@@ -6656,11 +6656,11 @@
         <f>G61</f>
         <v/>
       </c>
-      <c r="I62" s="35">
+      <c r="I62" s="34">
         <f>(G62-G61)/D62-J62*D62</f>
         <v/>
       </c>
-      <c r="J62" s="35">
+      <c r="J62" s="34">
         <f>3*(G62-G61)/D62^2-6*(E62-G61*D62)/D62^3</f>
         <v/>
       </c>
@@ -6690,7 +6690,7 @@
         <f>B63-B62</f>
         <v/>
       </c>
-      <c r="E63" s="35">
+      <c r="E63" s="34">
         <f>-LN(C63/C62)</f>
         <v/>
       </c>
@@ -6706,11 +6706,11 @@
         <f>G62</f>
         <v/>
       </c>
-      <c r="I63" s="35">
+      <c r="I63" s="34">
         <f>(G63-G62)/D63-J63*D63</f>
         <v/>
       </c>
-      <c r="J63" s="35">
+      <c r="J63" s="34">
         <f>3*(G63-G62)/D63^2-6*(E63-G62*D63)/D63^3</f>
         <v/>
       </c>
@@ -6740,7 +6740,7 @@
         <f>B64-B63</f>
         <v/>
       </c>
-      <c r="E64" s="35">
+      <c r="E64" s="34">
         <f>-LN(C64/C63)</f>
         <v/>
       </c>
@@ -6756,11 +6756,11 @@
         <f>G63</f>
         <v/>
       </c>
-      <c r="I64" s="35">
+      <c r="I64" s="34">
         <f>(G64-G63)/D64-J64*D64</f>
         <v/>
       </c>
-      <c r="J64" s="35">
+      <c r="J64" s="34">
         <f>3*(G64-G63)/D64^2-6*(E64-G63*D64)/D64^3</f>
         <v/>
       </c>
@@ -6790,7 +6790,7 @@
         <f>B65-B64</f>
         <v/>
       </c>
-      <c r="E65" s="35">
+      <c r="E65" s="34">
         <f>-LN(C65/C64)</f>
         <v/>
       </c>
@@ -6806,11 +6806,11 @@
         <f>G64</f>
         <v/>
       </c>
-      <c r="I65" s="35">
+      <c r="I65" s="34">
         <f>(G65-G64)/D65-J65*D65</f>
         <v/>
       </c>
-      <c r="J65" s="35">
+      <c r="J65" s="34">
         <f>3*(G65-G64)/D65^2-6*(E65-G64*D65)/D65^3</f>
         <v/>
       </c>
@@ -6840,7 +6840,7 @@
         <f>B66-B65</f>
         <v/>
       </c>
-      <c r="E66" s="35">
+      <c r="E66" s="34">
         <f>-LN(C66/C65)</f>
         <v/>
       </c>
@@ -6856,11 +6856,11 @@
         <f>G65</f>
         <v/>
       </c>
-      <c r="I66" s="35">
+      <c r="I66" s="34">
         <f>(G66-G65)/D66-J66*D66</f>
         <v/>
       </c>
-      <c r="J66" s="35">
+      <c r="J66" s="34">
         <f>3*(G66-G65)/D66^2-6*(E66-G65*D66)/D66^3</f>
         <v/>
       </c>
@@ -6890,7 +6890,7 @@
         <f>B67-B66</f>
         <v/>
       </c>
-      <c r="E67" s="35">
+      <c r="E67" s="34">
         <f>-LN(C67/C66)</f>
         <v/>
       </c>
@@ -6906,11 +6906,11 @@
         <f>G66</f>
         <v/>
       </c>
-      <c r="I67" s="35">
+      <c r="I67" s="34">
         <f>(G67-G66)/D67-J67*D67</f>
         <v/>
       </c>
-      <c r="J67" s="35">
+      <c r="J67" s="34">
         <f>3*(G67-G66)/D67^2-6*(E67-G66*D67)/D67^3</f>
         <v/>
       </c>
@@ -6940,7 +6940,7 @@
         <f>B68-B67</f>
         <v/>
       </c>
-      <c r="E68" s="35">
+      <c r="E68" s="34">
         <f>-LN(C68/C67)</f>
         <v/>
       </c>
@@ -6956,11 +6956,11 @@
         <f>G67</f>
         <v/>
       </c>
-      <c r="I68" s="35">
+      <c r="I68" s="34">
         <f>(G68-G67)/D68-J68*D68</f>
         <v/>
       </c>
-      <c r="J68" s="35">
+      <c r="J68" s="34">
         <f>3*(G68-G67)/D68^2-6*(E68-G67*D68)/D68^3</f>
         <v/>
       </c>
@@ -6990,7 +6990,7 @@
         <f>B69-B68</f>
         <v/>
       </c>
-      <c r="E69" s="35">
+      <c r="E69" s="34">
         <f>-LN(C69/C68)</f>
         <v/>
       </c>
@@ -7006,11 +7006,11 @@
         <f>G68</f>
         <v/>
       </c>
-      <c r="I69" s="35">
+      <c r="I69" s="34">
         <f>(G69-G68)/D69-J69*D69</f>
         <v/>
       </c>
-      <c r="J69" s="35">
+      <c r="J69" s="34">
         <f>3*(G69-G68)/D69^2-6*(E69-G68*D69)/D69^3</f>
         <v/>
       </c>
@@ -7040,7 +7040,7 @@
         <f>B70-B69</f>
         <v/>
       </c>
-      <c r="E70" s="35">
+      <c r="E70" s="34">
         <f>-LN(C70/C69)</f>
         <v/>
       </c>
@@ -7056,11 +7056,11 @@
         <f>G69</f>
         <v/>
       </c>
-      <c r="I70" s="35">
+      <c r="I70" s="34">
         <f>(G70-G69)/D70-J70*D70</f>
         <v/>
       </c>
-      <c r="J70" s="35">
+      <c r="J70" s="34">
         <f>3*(G70-G69)/D70^2-6*(E70-G69*D70)/D70^3</f>
         <v/>
       </c>
@@ -7090,7 +7090,7 @@
         <f>B71-B70</f>
         <v/>
       </c>
-      <c r="E71" s="35">
+      <c r="E71" s="34">
         <f>-LN(C71/C70)</f>
         <v/>
       </c>
@@ -7106,11 +7106,11 @@
         <f>G70</f>
         <v/>
       </c>
-      <c r="I71" s="35">
+      <c r="I71" s="34">
         <f>(G71-G70)/D71-J71*D71</f>
         <v/>
       </c>
-      <c r="J71" s="35">
+      <c r="J71" s="34">
         <f>3*(G71-G70)/D71^2-6*(E71-G70*D71)/D71^3</f>
         <v/>
       </c>
@@ -7140,7 +7140,7 @@
         <f>B72-B71</f>
         <v/>
       </c>
-      <c r="E72" s="35">
+      <c r="E72" s="34">
         <f>-LN(C72/C71)</f>
         <v/>
       </c>
@@ -7156,11 +7156,11 @@
         <f>G71</f>
         <v/>
       </c>
-      <c r="I72" s="35">
+      <c r="I72" s="34">
         <f>(G72-G71)/D72-J72*D72</f>
         <v/>
       </c>
-      <c r="J72" s="35">
+      <c r="J72" s="34">
         <f>3*(G72-G71)/D72^2-6*(E72-G71*D72)/D72^3</f>
         <v/>
       </c>
@@ -7190,7 +7190,7 @@
         <f>B73-B72</f>
         <v/>
       </c>
-      <c r="E73" s="35">
+      <c r="E73" s="34">
         <f>-LN(C73/C72)</f>
         <v/>
       </c>
@@ -7206,11 +7206,11 @@
         <f>G72</f>
         <v/>
       </c>
-      <c r="I73" s="35">
+      <c r="I73" s="34">
         <f>(G73-G72)/D73-J73*D73</f>
         <v/>
       </c>
-      <c r="J73" s="35">
+      <c r="J73" s="34">
         <f>3*(G73-G72)/D73^2-6*(E73-G72*D73)/D73^3</f>
         <v/>
       </c>
@@ -7803,11 +7803,11 @@
         <f>(C7/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="34">
         <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B7,CDS_Schedule!$C$7:$C$46,1))</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="34">
         <f>1-E7</f>
         <v/>
       </c>
@@ -7815,7 +7815,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
-      <c r="H7" s="35">
+      <c r="H7" s="34">
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B7,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -7846,11 +7846,11 @@
         <f>((C8/10000)*(B8-VAL_DATE)/365-(C7/10000)*(B7-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B8-VAL_DATE)/365-(B7-VAL_DATE)/365))</f>
         <v/>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="34">
         <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B8,CDS_Schedule!$C$7:$C$46,1))</f>
         <v/>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="34">
         <f>1-E8</f>
         <v/>
       </c>
@@ -7858,7 +7858,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
-      <c r="H8" s="35">
+      <c r="H8" s="34">
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B8,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -7889,11 +7889,11 @@
         <f>((C9/10000)*(B9-VAL_DATE)/365-(C8/10000)*(B8-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B9-VAL_DATE)/365-(B8-VAL_DATE)/365))</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="34">
         <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B9,CDS_Schedule!$C$7:$C$46,1))</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <f>1-E9</f>
         <v/>
       </c>
@@ -7901,7 +7901,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="34">
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B9,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -7932,11 +7932,11 @@
         <f>((C10/10000)*(B10-VAL_DATE)/365-(C9/10000)*(B9-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B10-VAL_DATE)/365-(B9-VAL_DATE)/365))</f>
         <v/>
       </c>
-      <c r="E10" s="35">
+      <c r="E10" s="34">
         <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B10,CDS_Schedule!$C$7:$C$46,1))</f>
         <v/>
       </c>
-      <c r="F10" s="35">
+      <c r="F10" s="34">
         <f>1-E10</f>
         <v/>
       </c>
@@ -7944,7 +7944,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
-      <c r="H10" s="35">
+      <c r="H10" s="34">
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B10,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -7975,11 +7975,11 @@
         <f>((C11/10000)*(B11-VAL_DATE)/365-(C10/10000)*(B10-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B11-VAL_DATE)/365-(B10-VAL_DATE)/365))</f>
         <v/>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="34">
         <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B11,CDS_Schedule!$C$7:$C$46,1))</f>
         <v/>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="34">
         <f>1-E11</f>
         <v/>
       </c>
@@ -7987,7 +7987,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
-      <c r="H11" s="35">
+      <c r="H11" s="34">
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B11,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -8018,11 +8018,11 @@
         <f>((C12/10000)*(B12-VAL_DATE)/365-(C11/10000)*(B11-VAL_DATE)/365)/((1-CDS_Parameters!$B$8)*((B12-VAL_DATE)/365-(B11-VAL_DATE)/365))</f>
         <v/>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="34">
         <f>INDEX(CDS_Schedule!$K$7:$K$46,MATCH(B12,CDS_Schedule!$C$7:$C$46,1))</f>
         <v/>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="34">
         <f>1-E12</f>
         <v/>
       </c>
@@ -8030,7 +8030,7 @@
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$M$7:$M$46)+SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$N$7:$N$46)</f>
         <v/>
       </c>
-      <c r="H12" s="35">
+      <c r="H12" s="34">
         <f>SUMIF(CDS_Schedule!$C$7:$C$46,"&lt;="&amp;B12,CDS_Schedule!$O$7:$O$46)</f>
         <v/>
       </c>
@@ -8212,27 +8212,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C7)+1,6))</f>
         <v/>
       </c>
-      <c r="J7" s="35">
+      <c r="J7" s="34">
         <f>1</f>
         <v/>
       </c>
-      <c r="K7" s="35">
+      <c r="K7" s="34">
         <f>J7*EXP(-I7*E7)</f>
         <v/>
       </c>
-      <c r="L7" s="35">
+      <c r="L7" s="34">
         <f>J7-K7</f>
         <v/>
       </c>
-      <c r="M7" s="35">
+      <c r="M7" s="34">
         <f>D7*G7*K7</f>
         <v/>
       </c>
-      <c r="N7" s="35">
+      <c r="N7" s="34">
         <f>(D7/2)*H7*L7</f>
         <v/>
       </c>
-      <c r="O7" s="35">
+      <c r="O7" s="34">
         <f>H7*L7</f>
         <v/>
       </c>
@@ -8273,27 +8273,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C8)+1,6))</f>
         <v/>
       </c>
-      <c r="J8" s="35">
+      <c r="J8" s="34">
         <f>K7</f>
         <v/>
       </c>
-      <c r="K8" s="35">
+      <c r="K8" s="34">
         <f>J8*EXP(-I8*E8)</f>
         <v/>
       </c>
-      <c r="L8" s="35">
+      <c r="L8" s="34">
         <f>J8-K8</f>
         <v/>
       </c>
-      <c r="M8" s="35">
+      <c r="M8" s="34">
         <f>D8*G8*K8</f>
         <v/>
       </c>
-      <c r="N8" s="35">
+      <c r="N8" s="34">
         <f>(D8/2)*H8*L8</f>
         <v/>
       </c>
-      <c r="O8" s="35">
+      <c r="O8" s="34">
         <f>H8*L8</f>
         <v/>
       </c>
@@ -8334,27 +8334,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C9)+1,6))</f>
         <v/>
       </c>
-      <c r="J9" s="35">
+      <c r="J9" s="34">
         <f>K8</f>
         <v/>
       </c>
-      <c r="K9" s="35">
+      <c r="K9" s="34">
         <f>J9*EXP(-I9*E9)</f>
         <v/>
       </c>
-      <c r="L9" s="35">
+      <c r="L9" s="34">
         <f>J9-K9</f>
         <v/>
       </c>
-      <c r="M9" s="35">
+      <c r="M9" s="34">
         <f>D9*G9*K9</f>
         <v/>
       </c>
-      <c r="N9" s="35">
+      <c r="N9" s="34">
         <f>(D9/2)*H9*L9</f>
         <v/>
       </c>
-      <c r="O9" s="35">
+      <c r="O9" s="34">
         <f>H9*L9</f>
         <v/>
       </c>
@@ -8395,27 +8395,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C10)+1,6))</f>
         <v/>
       </c>
-      <c r="J10" s="35">
+      <c r="J10" s="34">
         <f>K9</f>
         <v/>
       </c>
-      <c r="K10" s="35">
+      <c r="K10" s="34">
         <f>J10*EXP(-I10*E10)</f>
         <v/>
       </c>
-      <c r="L10" s="35">
+      <c r="L10" s="34">
         <f>J10-K10</f>
         <v/>
       </c>
-      <c r="M10" s="35">
+      <c r="M10" s="34">
         <f>D10*G10*K10</f>
         <v/>
       </c>
-      <c r="N10" s="35">
+      <c r="N10" s="34">
         <f>(D10/2)*H10*L10</f>
         <v/>
       </c>
-      <c r="O10" s="35">
+      <c r="O10" s="34">
         <f>H10*L10</f>
         <v/>
       </c>
@@ -8456,27 +8456,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C11)+1,6))</f>
         <v/>
       </c>
-      <c r="J11" s="35">
+      <c r="J11" s="34">
         <f>K10</f>
         <v/>
       </c>
-      <c r="K11" s="35">
+      <c r="K11" s="34">
         <f>J11*EXP(-I11*E11)</f>
         <v/>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="34">
         <f>J11-K11</f>
         <v/>
       </c>
-      <c r="M11" s="35">
+      <c r="M11" s="34">
         <f>D11*G11*K11</f>
         <v/>
       </c>
-      <c r="N11" s="35">
+      <c r="N11" s="34">
         <f>(D11/2)*H11*L11</f>
         <v/>
       </c>
-      <c r="O11" s="35">
+      <c r="O11" s="34">
         <f>H11*L11</f>
         <v/>
       </c>
@@ -8517,27 +8517,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C12)+1,6))</f>
         <v/>
       </c>
-      <c r="J12" s="35">
+      <c r="J12" s="34">
         <f>K11</f>
         <v/>
       </c>
-      <c r="K12" s="35">
+      <c r="K12" s="34">
         <f>J12*EXP(-I12*E12)</f>
         <v/>
       </c>
-      <c r="L12" s="35">
+      <c r="L12" s="34">
         <f>J12-K12</f>
         <v/>
       </c>
-      <c r="M12" s="35">
+      <c r="M12" s="34">
         <f>D12*G12*K12</f>
         <v/>
       </c>
-      <c r="N12" s="35">
+      <c r="N12" s="34">
         <f>(D12/2)*H12*L12</f>
         <v/>
       </c>
-      <c r="O12" s="35">
+      <c r="O12" s="34">
         <f>H12*L12</f>
         <v/>
       </c>
@@ -8578,27 +8578,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C13)+1,6))</f>
         <v/>
       </c>
-      <c r="J13" s="35">
+      <c r="J13" s="34">
         <f>K12</f>
         <v/>
       </c>
-      <c r="K13" s="35">
+      <c r="K13" s="34">
         <f>J13*EXP(-I13*E13)</f>
         <v/>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="34">
         <f>J13-K13</f>
         <v/>
       </c>
-      <c r="M13" s="35">
+      <c r="M13" s="34">
         <f>D13*G13*K13</f>
         <v/>
       </c>
-      <c r="N13" s="35">
+      <c r="N13" s="34">
         <f>(D13/2)*H13*L13</f>
         <v/>
       </c>
-      <c r="O13" s="35">
+      <c r="O13" s="34">
         <f>H13*L13</f>
         <v/>
       </c>
@@ -8639,27 +8639,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C14)+1,6))</f>
         <v/>
       </c>
-      <c r="J14" s="35">
+      <c r="J14" s="34">
         <f>K13</f>
         <v/>
       </c>
-      <c r="K14" s="35">
+      <c r="K14" s="34">
         <f>J14*EXP(-I14*E14)</f>
         <v/>
       </c>
-      <c r="L14" s="35">
+      <c r="L14" s="34">
         <f>J14-K14</f>
         <v/>
       </c>
-      <c r="M14" s="35">
+      <c r="M14" s="34">
         <f>D14*G14*K14</f>
         <v/>
       </c>
-      <c r="N14" s="35">
+      <c r="N14" s="34">
         <f>(D14/2)*H14*L14</f>
         <v/>
       </c>
-      <c r="O14" s="35">
+      <c r="O14" s="34">
         <f>H14*L14</f>
         <v/>
       </c>
@@ -8700,27 +8700,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C15)+1,6))</f>
         <v/>
       </c>
-      <c r="J15" s="35">
+      <c r="J15" s="34">
         <f>K14</f>
         <v/>
       </c>
-      <c r="K15" s="35">
+      <c r="K15" s="34">
         <f>J15*EXP(-I15*E15)</f>
         <v/>
       </c>
-      <c r="L15" s="35">
+      <c r="L15" s="34">
         <f>J15-K15</f>
         <v/>
       </c>
-      <c r="M15" s="35">
+      <c r="M15" s="34">
         <f>D15*G15*K15</f>
         <v/>
       </c>
-      <c r="N15" s="35">
+      <c r="N15" s="34">
         <f>(D15/2)*H15*L15</f>
         <v/>
       </c>
-      <c r="O15" s="35">
+      <c r="O15" s="34">
         <f>H15*L15</f>
         <v/>
       </c>
@@ -8761,27 +8761,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C16)+1,6))</f>
         <v/>
       </c>
-      <c r="J16" s="35">
+      <c r="J16" s="34">
         <f>K15</f>
         <v/>
       </c>
-      <c r="K16" s="35">
+      <c r="K16" s="34">
         <f>J16*EXP(-I16*E16)</f>
         <v/>
       </c>
-      <c r="L16" s="35">
+      <c r="L16" s="34">
         <f>J16-K16</f>
         <v/>
       </c>
-      <c r="M16" s="35">
+      <c r="M16" s="34">
         <f>D16*G16*K16</f>
         <v/>
       </c>
-      <c r="N16" s="35">
+      <c r="N16" s="34">
         <f>(D16/2)*H16*L16</f>
         <v/>
       </c>
-      <c r="O16" s="35">
+      <c r="O16" s="34">
         <f>H16*L16</f>
         <v/>
       </c>
@@ -8822,27 +8822,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C17)+1,6))</f>
         <v/>
       </c>
-      <c r="J17" s="35">
+      <c r="J17" s="34">
         <f>K16</f>
         <v/>
       </c>
-      <c r="K17" s="35">
+      <c r="K17" s="34">
         <f>J17*EXP(-I17*E17)</f>
         <v/>
       </c>
-      <c r="L17" s="35">
+      <c r="L17" s="34">
         <f>J17-K17</f>
         <v/>
       </c>
-      <c r="M17" s="35">
+      <c r="M17" s="34">
         <f>D17*G17*K17</f>
         <v/>
       </c>
-      <c r="N17" s="35">
+      <c r="N17" s="34">
         <f>(D17/2)*H17*L17</f>
         <v/>
       </c>
-      <c r="O17" s="35">
+      <c r="O17" s="34">
         <f>H17*L17</f>
         <v/>
       </c>
@@ -8883,27 +8883,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C18)+1,6))</f>
         <v/>
       </c>
-      <c r="J18" s="35">
+      <c r="J18" s="34">
         <f>K17</f>
         <v/>
       </c>
-      <c r="K18" s="35">
+      <c r="K18" s="34">
         <f>J18*EXP(-I18*E18)</f>
         <v/>
       </c>
-      <c r="L18" s="35">
+      <c r="L18" s="34">
         <f>J18-K18</f>
         <v/>
       </c>
-      <c r="M18" s="35">
+      <c r="M18" s="34">
         <f>D18*G18*K18</f>
         <v/>
       </c>
-      <c r="N18" s="35">
+      <c r="N18" s="34">
         <f>(D18/2)*H18*L18</f>
         <v/>
       </c>
-      <c r="O18" s="35">
+      <c r="O18" s="34">
         <f>H18*L18</f>
         <v/>
       </c>
@@ -8944,27 +8944,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C19)+1,6))</f>
         <v/>
       </c>
-      <c r="J19" s="35">
+      <c r="J19" s="34">
         <f>K18</f>
         <v/>
       </c>
-      <c r="K19" s="35">
+      <c r="K19" s="34">
         <f>J19*EXP(-I19*E19)</f>
         <v/>
       </c>
-      <c r="L19" s="35">
+      <c r="L19" s="34">
         <f>J19-K19</f>
         <v/>
       </c>
-      <c r="M19" s="35">
+      <c r="M19" s="34">
         <f>D19*G19*K19</f>
         <v/>
       </c>
-      <c r="N19" s="35">
+      <c r="N19" s="34">
         <f>(D19/2)*H19*L19</f>
         <v/>
       </c>
-      <c r="O19" s="35">
+      <c r="O19" s="34">
         <f>H19*L19</f>
         <v/>
       </c>
@@ -9005,27 +9005,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C20)+1,6))</f>
         <v/>
       </c>
-      <c r="J20" s="35">
+      <c r="J20" s="34">
         <f>K19</f>
         <v/>
       </c>
-      <c r="K20" s="35">
+      <c r="K20" s="34">
         <f>J20*EXP(-I20*E20)</f>
         <v/>
       </c>
-      <c r="L20" s="35">
+      <c r="L20" s="34">
         <f>J20-K20</f>
         <v/>
       </c>
-      <c r="M20" s="35">
+      <c r="M20" s="34">
         <f>D20*G20*K20</f>
         <v/>
       </c>
-      <c r="N20" s="35">
+      <c r="N20" s="34">
         <f>(D20/2)*H20*L20</f>
         <v/>
       </c>
-      <c r="O20" s="35">
+      <c r="O20" s="34">
         <f>H20*L20</f>
         <v/>
       </c>
@@ -9066,27 +9066,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C21)+1,6))</f>
         <v/>
       </c>
-      <c r="J21" s="35">
+      <c r="J21" s="34">
         <f>K20</f>
         <v/>
       </c>
-      <c r="K21" s="35">
+      <c r="K21" s="34">
         <f>J21*EXP(-I21*E21)</f>
         <v/>
       </c>
-      <c r="L21" s="35">
+      <c r="L21" s="34">
         <f>J21-K21</f>
         <v/>
       </c>
-      <c r="M21" s="35">
+      <c r="M21" s="34">
         <f>D21*G21*K21</f>
         <v/>
       </c>
-      <c r="N21" s="35">
+      <c r="N21" s="34">
         <f>(D21/2)*H21*L21</f>
         <v/>
       </c>
-      <c r="O21" s="35">
+      <c r="O21" s="34">
         <f>H21*L21</f>
         <v/>
       </c>
@@ -9127,27 +9127,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C22)+1,6))</f>
         <v/>
       </c>
-      <c r="J22" s="35">
+      <c r="J22" s="34">
         <f>K21</f>
         <v/>
       </c>
-      <c r="K22" s="35">
+      <c r="K22" s="34">
         <f>J22*EXP(-I22*E22)</f>
         <v/>
       </c>
-      <c r="L22" s="35">
+      <c r="L22" s="34">
         <f>J22-K22</f>
         <v/>
       </c>
-      <c r="M22" s="35">
+      <c r="M22" s="34">
         <f>D22*G22*K22</f>
         <v/>
       </c>
-      <c r="N22" s="35">
+      <c r="N22" s="34">
         <f>(D22/2)*H22*L22</f>
         <v/>
       </c>
-      <c r="O22" s="35">
+      <c r="O22" s="34">
         <f>H22*L22</f>
         <v/>
       </c>
@@ -9188,27 +9188,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C23)+1,6))</f>
         <v/>
       </c>
-      <c r="J23" s="35">
+      <c r="J23" s="34">
         <f>K22</f>
         <v/>
       </c>
-      <c r="K23" s="35">
+      <c r="K23" s="34">
         <f>J23*EXP(-I23*E23)</f>
         <v/>
       </c>
-      <c r="L23" s="35">
+      <c r="L23" s="34">
         <f>J23-K23</f>
         <v/>
       </c>
-      <c r="M23" s="35">
+      <c r="M23" s="34">
         <f>D23*G23*K23</f>
         <v/>
       </c>
-      <c r="N23" s="35">
+      <c r="N23" s="34">
         <f>(D23/2)*H23*L23</f>
         <v/>
       </c>
-      <c r="O23" s="35">
+      <c r="O23" s="34">
         <f>H23*L23</f>
         <v/>
       </c>
@@ -9249,27 +9249,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C24)+1,6))</f>
         <v/>
       </c>
-      <c r="J24" s="35">
+      <c r="J24" s="34">
         <f>K23</f>
         <v/>
       </c>
-      <c r="K24" s="35">
+      <c r="K24" s="34">
         <f>J24*EXP(-I24*E24)</f>
         <v/>
       </c>
-      <c r="L24" s="35">
+      <c r="L24" s="34">
         <f>J24-K24</f>
         <v/>
       </c>
-      <c r="M24" s="35">
+      <c r="M24" s="34">
         <f>D24*G24*K24</f>
         <v/>
       </c>
-      <c r="N24" s="35">
+      <c r="N24" s="34">
         <f>(D24/2)*H24*L24</f>
         <v/>
       </c>
-      <c r="O24" s="35">
+      <c r="O24" s="34">
         <f>H24*L24</f>
         <v/>
       </c>
@@ -9310,27 +9310,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C25)+1,6))</f>
         <v/>
       </c>
-      <c r="J25" s="35">
+      <c r="J25" s="34">
         <f>K24</f>
         <v/>
       </c>
-      <c r="K25" s="35">
+      <c r="K25" s="34">
         <f>J25*EXP(-I25*E25)</f>
         <v/>
       </c>
-      <c r="L25" s="35">
+      <c r="L25" s="34">
         <f>J25-K25</f>
         <v/>
       </c>
-      <c r="M25" s="35">
+      <c r="M25" s="34">
         <f>D25*G25*K25</f>
         <v/>
       </c>
-      <c r="N25" s="35">
+      <c r="N25" s="34">
         <f>(D25/2)*H25*L25</f>
         <v/>
       </c>
-      <c r="O25" s="35">
+      <c r="O25" s="34">
         <f>H25*L25</f>
         <v/>
       </c>
@@ -9371,27 +9371,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C26)+1,6))</f>
         <v/>
       </c>
-      <c r="J26" s="35">
+      <c r="J26" s="34">
         <f>K25</f>
         <v/>
       </c>
-      <c r="K26" s="35">
+      <c r="K26" s="34">
         <f>J26*EXP(-I26*E26)</f>
         <v/>
       </c>
-      <c r="L26" s="35">
+      <c r="L26" s="34">
         <f>J26-K26</f>
         <v/>
       </c>
-      <c r="M26" s="35">
+      <c r="M26" s="34">
         <f>D26*G26*K26</f>
         <v/>
       </c>
-      <c r="N26" s="35">
+      <c r="N26" s="34">
         <f>(D26/2)*H26*L26</f>
         <v/>
       </c>
-      <c r="O26" s="35">
+      <c r="O26" s="34">
         <f>H26*L26</f>
         <v/>
       </c>
@@ -9432,27 +9432,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C27)+1,6))</f>
         <v/>
       </c>
-      <c r="J27" s="35">
+      <c r="J27" s="34">
         <f>K26</f>
         <v/>
       </c>
-      <c r="K27" s="35">
+      <c r="K27" s="34">
         <f>J27*EXP(-I27*E27)</f>
         <v/>
       </c>
-      <c r="L27" s="35">
+      <c r="L27" s="34">
         <f>J27-K27</f>
         <v/>
       </c>
-      <c r="M27" s="35">
+      <c r="M27" s="34">
         <f>D27*G27*K27</f>
         <v/>
       </c>
-      <c r="N27" s="35">
+      <c r="N27" s="34">
         <f>(D27/2)*H27*L27</f>
         <v/>
       </c>
-      <c r="O27" s="35">
+      <c r="O27" s="34">
         <f>H27*L27</f>
         <v/>
       </c>
@@ -9493,27 +9493,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C28)+1,6))</f>
         <v/>
       </c>
-      <c r="J28" s="35">
+      <c r="J28" s="34">
         <f>K27</f>
         <v/>
       </c>
-      <c r="K28" s="35">
+      <c r="K28" s="34">
         <f>J28*EXP(-I28*E28)</f>
         <v/>
       </c>
-      <c r="L28" s="35">
+      <c r="L28" s="34">
         <f>J28-K28</f>
         <v/>
       </c>
-      <c r="M28" s="35">
+      <c r="M28" s="34">
         <f>D28*G28*K28</f>
         <v/>
       </c>
-      <c r="N28" s="35">
+      <c r="N28" s="34">
         <f>(D28/2)*H28*L28</f>
         <v/>
       </c>
-      <c r="O28" s="35">
+      <c r="O28" s="34">
         <f>H28*L28</f>
         <v/>
       </c>
@@ -9554,27 +9554,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C29)+1,6))</f>
         <v/>
       </c>
-      <c r="J29" s="35">
+      <c r="J29" s="34">
         <f>K28</f>
         <v/>
       </c>
-      <c r="K29" s="35">
+      <c r="K29" s="34">
         <f>J29*EXP(-I29*E29)</f>
         <v/>
       </c>
-      <c r="L29" s="35">
+      <c r="L29" s="34">
         <f>J29-K29</f>
         <v/>
       </c>
-      <c r="M29" s="35">
+      <c r="M29" s="34">
         <f>D29*G29*K29</f>
         <v/>
       </c>
-      <c r="N29" s="35">
+      <c r="N29" s="34">
         <f>(D29/2)*H29*L29</f>
         <v/>
       </c>
-      <c r="O29" s="35">
+      <c r="O29" s="34">
         <f>H29*L29</f>
         <v/>
       </c>
@@ -9615,27 +9615,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C30)+1,6))</f>
         <v/>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="34">
         <f>K29</f>
         <v/>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="34">
         <f>J30*EXP(-I30*E30)</f>
         <v/>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="34">
         <f>J30-K30</f>
         <v/>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="34">
         <f>D30*G30*K30</f>
         <v/>
       </c>
-      <c r="N30" s="35">
+      <c r="N30" s="34">
         <f>(D30/2)*H30*L30</f>
         <v/>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="34">
         <f>H30*L30</f>
         <v/>
       </c>
@@ -9676,27 +9676,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C31)+1,6))</f>
         <v/>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="34">
         <f>K30</f>
         <v/>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="34">
         <f>J31*EXP(-I31*E31)</f>
         <v/>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="34">
         <f>J31-K31</f>
         <v/>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="34">
         <f>D31*G31*K31</f>
         <v/>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="34">
         <f>(D31/2)*H31*L31</f>
         <v/>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="34">
         <f>H31*L31</f>
         <v/>
       </c>
@@ -9737,27 +9737,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C32)+1,6))</f>
         <v/>
       </c>
-      <c r="J32" s="35">
+      <c r="J32" s="34">
         <f>K31</f>
         <v/>
       </c>
-      <c r="K32" s="35">
+      <c r="K32" s="34">
         <f>J32*EXP(-I32*E32)</f>
         <v/>
       </c>
-      <c r="L32" s="35">
+      <c r="L32" s="34">
         <f>J32-K32</f>
         <v/>
       </c>
-      <c r="M32" s="35">
+      <c r="M32" s="34">
         <f>D32*G32*K32</f>
         <v/>
       </c>
-      <c r="N32" s="35">
+      <c r="N32" s="34">
         <f>(D32/2)*H32*L32</f>
         <v/>
       </c>
-      <c r="O32" s="35">
+      <c r="O32" s="34">
         <f>H32*L32</f>
         <v/>
       </c>
@@ -9798,27 +9798,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C33)+1,6))</f>
         <v/>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="34">
         <f>K32</f>
         <v/>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="34">
         <f>J33*EXP(-I33*E33)</f>
         <v/>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="34">
         <f>J33-K33</f>
         <v/>
       </c>
-      <c r="M33" s="35">
+      <c r="M33" s="34">
         <f>D33*G33*K33</f>
         <v/>
       </c>
-      <c r="N33" s="35">
+      <c r="N33" s="34">
         <f>(D33/2)*H33*L33</f>
         <v/>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="34">
         <f>H33*L33</f>
         <v/>
       </c>
@@ -9859,27 +9859,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C34)+1,6))</f>
         <v/>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="34">
         <f>K33</f>
         <v/>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="34">
         <f>J34*EXP(-I34*E34)</f>
         <v/>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="34">
         <f>J34-K34</f>
         <v/>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="34">
         <f>D34*G34*K34</f>
         <v/>
       </c>
-      <c r="N34" s="35">
+      <c r="N34" s="34">
         <f>(D34/2)*H34*L34</f>
         <v/>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="34">
         <f>H34*L34</f>
         <v/>
       </c>
@@ -9920,27 +9920,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C35)+1,6))</f>
         <v/>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="34">
         <f>K34</f>
         <v/>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="34">
         <f>J35*EXP(-I35*E35)</f>
         <v/>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="34">
         <f>J35-K35</f>
         <v/>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="34">
         <f>D35*G35*K35</f>
         <v/>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="34">
         <f>(D35/2)*H35*L35</f>
         <v/>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="34">
         <f>H35*L35</f>
         <v/>
       </c>
@@ -9981,27 +9981,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C36)+1,6))</f>
         <v/>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="34">
         <f>K35</f>
         <v/>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="34">
         <f>J36*EXP(-I36*E36)</f>
         <v/>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="34">
         <f>J36-K36</f>
         <v/>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="34">
         <f>D36*G36*K36</f>
         <v/>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="34">
         <f>(D36/2)*H36*L36</f>
         <v/>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="34">
         <f>H36*L36</f>
         <v/>
       </c>
@@ -10042,27 +10042,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C37)+1,6))</f>
         <v/>
       </c>
-      <c r="J37" s="35">
+      <c r="J37" s="34">
         <f>K36</f>
         <v/>
       </c>
-      <c r="K37" s="35">
+      <c r="K37" s="34">
         <f>J37*EXP(-I37*E37)</f>
         <v/>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="34">
         <f>J37-K37</f>
         <v/>
       </c>
-      <c r="M37" s="35">
+      <c r="M37" s="34">
         <f>D37*G37*K37</f>
         <v/>
       </c>
-      <c r="N37" s="35">
+      <c r="N37" s="34">
         <f>(D37/2)*H37*L37</f>
         <v/>
       </c>
-      <c r="O37" s="35">
+      <c r="O37" s="34">
         <f>H37*L37</f>
         <v/>
       </c>
@@ -10103,27 +10103,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C38)+1,6))</f>
         <v/>
       </c>
-      <c r="J38" s="35">
+      <c r="J38" s="34">
         <f>K37</f>
         <v/>
       </c>
-      <c r="K38" s="35">
+      <c r="K38" s="34">
         <f>J38*EXP(-I38*E38)</f>
         <v/>
       </c>
-      <c r="L38" s="35">
+      <c r="L38" s="34">
         <f>J38-K38</f>
         <v/>
       </c>
-      <c r="M38" s="35">
+      <c r="M38" s="34">
         <f>D38*G38*K38</f>
         <v/>
       </c>
-      <c r="N38" s="35">
+      <c r="N38" s="34">
         <f>(D38/2)*H38*L38</f>
         <v/>
       </c>
-      <c r="O38" s="35">
+      <c r="O38" s="34">
         <f>H38*L38</f>
         <v/>
       </c>
@@ -10164,27 +10164,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C39)+1,6))</f>
         <v/>
       </c>
-      <c r="J39" s="35">
+      <c r="J39" s="34">
         <f>K38</f>
         <v/>
       </c>
-      <c r="K39" s="35">
+      <c r="K39" s="34">
         <f>J39*EXP(-I39*E39)</f>
         <v/>
       </c>
-      <c r="L39" s="35">
+      <c r="L39" s="34">
         <f>J39-K39</f>
         <v/>
       </c>
-      <c r="M39" s="35">
+      <c r="M39" s="34">
         <f>D39*G39*K39</f>
         <v/>
       </c>
-      <c r="N39" s="35">
+      <c r="N39" s="34">
         <f>(D39/2)*H39*L39</f>
         <v/>
       </c>
-      <c r="O39" s="35">
+      <c r="O39" s="34">
         <f>H39*L39</f>
         <v/>
       </c>
@@ -10225,27 +10225,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C40)+1,6))</f>
         <v/>
       </c>
-      <c r="J40" s="35">
+      <c r="J40" s="34">
         <f>K39</f>
         <v/>
       </c>
-      <c r="K40" s="35">
+      <c r="K40" s="34">
         <f>J40*EXP(-I40*E40)</f>
         <v/>
       </c>
-      <c r="L40" s="35">
+      <c r="L40" s="34">
         <f>J40-K40</f>
         <v/>
       </c>
-      <c r="M40" s="35">
+      <c r="M40" s="34">
         <f>D40*G40*K40</f>
         <v/>
       </c>
-      <c r="N40" s="35">
+      <c r="N40" s="34">
         <f>(D40/2)*H40*L40</f>
         <v/>
       </c>
-      <c r="O40" s="35">
+      <c r="O40" s="34">
         <f>H40*L40</f>
         <v/>
       </c>
@@ -10286,27 +10286,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C41)+1,6))</f>
         <v/>
       </c>
-      <c r="J41" s="35">
+      <c r="J41" s="34">
         <f>K40</f>
         <v/>
       </c>
-      <c r="K41" s="35">
+      <c r="K41" s="34">
         <f>J41*EXP(-I41*E41)</f>
         <v/>
       </c>
-      <c r="L41" s="35">
+      <c r="L41" s="34">
         <f>J41-K41</f>
         <v/>
       </c>
-      <c r="M41" s="35">
+      <c r="M41" s="34">
         <f>D41*G41*K41</f>
         <v/>
       </c>
-      <c r="N41" s="35">
+      <c r="N41" s="34">
         <f>(D41/2)*H41*L41</f>
         <v/>
       </c>
-      <c r="O41" s="35">
+      <c r="O41" s="34">
         <f>H41*L41</f>
         <v/>
       </c>
@@ -10347,27 +10347,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C42)+1,6))</f>
         <v/>
       </c>
-      <c r="J42" s="35">
+      <c r="J42" s="34">
         <f>K41</f>
         <v/>
       </c>
-      <c r="K42" s="35">
+      <c r="K42" s="34">
         <f>J42*EXP(-I42*E42)</f>
         <v/>
       </c>
-      <c r="L42" s="35">
+      <c r="L42" s="34">
         <f>J42-K42</f>
         <v/>
       </c>
-      <c r="M42" s="35">
+      <c r="M42" s="34">
         <f>D42*G42*K42</f>
         <v/>
       </c>
-      <c r="N42" s="35">
+      <c r="N42" s="34">
         <f>(D42/2)*H42*L42</f>
         <v/>
       </c>
-      <c r="O42" s="35">
+      <c r="O42" s="34">
         <f>H42*L42</f>
         <v/>
       </c>
@@ -10408,27 +10408,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C43)+1,6))</f>
         <v/>
       </c>
-      <c r="J43" s="35">
+      <c r="J43" s="34">
         <f>K42</f>
         <v/>
       </c>
-      <c r="K43" s="35">
+      <c r="K43" s="34">
         <f>J43*EXP(-I43*E43)</f>
         <v/>
       </c>
-      <c r="L43" s="35">
+      <c r="L43" s="34">
         <f>J43-K43</f>
         <v/>
       </c>
-      <c r="M43" s="35">
+      <c r="M43" s="34">
         <f>D43*G43*K43</f>
         <v/>
       </c>
-      <c r="N43" s="35">
+      <c r="N43" s="34">
         <f>(D43/2)*H43*L43</f>
         <v/>
       </c>
-      <c r="O43" s="35">
+      <c r="O43" s="34">
         <f>H43*L43</f>
         <v/>
       </c>
@@ -10469,27 +10469,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C44)+1,6))</f>
         <v/>
       </c>
-      <c r="J44" s="35">
+      <c r="J44" s="34">
         <f>K43</f>
         <v/>
       </c>
-      <c r="K44" s="35">
+      <c r="K44" s="34">
         <f>J44*EXP(-I44*E44)</f>
         <v/>
       </c>
-      <c r="L44" s="35">
+      <c r="L44" s="34">
         <f>J44-K44</f>
         <v/>
       </c>
-      <c r="M44" s="35">
+      <c r="M44" s="34">
         <f>D44*G44*K44</f>
         <v/>
       </c>
-      <c r="N44" s="35">
+      <c r="N44" s="34">
         <f>(D44/2)*H44*L44</f>
         <v/>
       </c>
-      <c r="O44" s="35">
+      <c r="O44" s="34">
         <f>H44*L44</f>
         <v/>
       </c>
@@ -10530,27 +10530,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C45)+1,6))</f>
         <v/>
       </c>
-      <c r="J45" s="35">
+      <c r="J45" s="34">
         <f>K44</f>
         <v/>
       </c>
-      <c r="K45" s="35">
+      <c r="K45" s="34">
         <f>J45*EXP(-I45*E45)</f>
         <v/>
       </c>
-      <c r="L45" s="35">
+      <c r="L45" s="34">
         <f>J45-K45</f>
         <v/>
       </c>
-      <c r="M45" s="35">
+      <c r="M45" s="34">
         <f>D45*G45*K45</f>
         <v/>
       </c>
-      <c r="N45" s="35">
+      <c r="N45" s="34">
         <f>(D45/2)*H45*L45</f>
         <v/>
       </c>
-      <c r="O45" s="35">
+      <c r="O45" s="34">
         <f>H45*L45</f>
         <v/>
       </c>
@@ -10591,27 +10591,27 @@
         <f>INDEX(Hazard_Bootstrap!$D$7:$D$12,MIN(COUNTIF(Hazard_Bootstrap!$B$7:$B$12,"&lt;"&amp;C46)+1,6))</f>
         <v/>
       </c>
-      <c r="J46" s="35">
+      <c r="J46" s="34">
         <f>K45</f>
         <v/>
       </c>
-      <c r="K46" s="35">
+      <c r="K46" s="34">
         <f>J46*EXP(-I46*E46)</f>
         <v/>
       </c>
-      <c r="L46" s="35">
+      <c r="L46" s="34">
         <f>J46-K46</f>
         <v/>
       </c>
-      <c r="M46" s="35">
+      <c r="M46" s="34">
         <f>D46*G46*K46</f>
         <v/>
       </c>
-      <c r="N46" s="35">
+      <c r="N46" s="34">
         <f>(D46/2)*H46*L46</f>
         <v/>
       </c>
-      <c r="O46" s="35">
+      <c r="O46" s="34">
         <f>H46*L46</f>
         <v/>
       </c>
@@ -14330,7 +14330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q75"/>
+  <dimension ref="A1:W75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -14390,7 +14390,13 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>Working — fixed-leg PV = float-leg PV (par swap)</t>
+        </is>
+      </c>
+    </row>
     <row r="7">
       <c r="A7" s="20" t="inlineStr">
         <is>
@@ -14470,6 +14476,31 @@
       <c r="Q7" s="13" t="inlineStr">
         <is>
           <t>quoted %</t>
+        </is>
+      </c>
+      <c r="S7" s="20" t="inlineStr">
+        <is>
+          <t>Annuity  Σα·DF</t>
+        </is>
+      </c>
+      <c r="T7" s="20" t="inlineStr">
+        <is>
+          <t>Fixed leg  K·Σα·DF</t>
+        </is>
+      </c>
+      <c r="U7" s="20" t="inlineStr">
+        <is>
+          <t>Float leg  DF0−DF(T)</t>
+        </is>
+      </c>
+      <c r="V7" s="20" t="inlineStr">
+        <is>
+          <t>Model par (%)</t>
+        </is>
+      </c>
+      <c r="W7" s="20" t="inlineStr">
+        <is>
+          <t>Reprice (bp)</t>
         </is>
       </c>
     </row>
@@ -14531,6 +14562,26 @@
         <f>'SOFR_OIS_Quotes'!$H19</f>
         <v/>
       </c>
+      <c r="S8" s="34">
+        <f>(D8*H8)</f>
+        <v/>
+      </c>
+      <c r="T8" s="34">
+        <f>(E8/100)*S8</f>
+        <v/>
+      </c>
+      <c r="U8" s="34">
+        <f>$D$4-H8</f>
+        <v/>
+      </c>
+      <c r="V8" s="17">
+        <f>U8/S8*100</f>
+        <v/>
+      </c>
+      <c r="W8" s="31">
+        <f>(V8-E8)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -14591,6 +14642,26 @@
         <f>'SOFR_OIS_Quotes'!$H21</f>
         <v/>
       </c>
+      <c r="S9" s="34">
+        <f>(D9*H9)</f>
+        <v/>
+      </c>
+      <c r="T9" s="34">
+        <f>(E9/100)*S9</f>
+        <v/>
+      </c>
+      <c r="U9" s="34">
+        <f>$D$4-H9</f>
+        <v/>
+      </c>
+      <c r="V9" s="17">
+        <f>U9/S9*100</f>
+        <v/>
+      </c>
+      <c r="W9" s="31">
+        <f>(V9-E9)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -14651,6 +14722,26 @@
         <f>'SOFR_OIS_Quotes'!$H22</f>
         <v/>
       </c>
+      <c r="S10" s="34">
+        <f>(D10*H10)</f>
+        <v/>
+      </c>
+      <c r="T10" s="34">
+        <f>(E10/100)*S10</f>
+        <v/>
+      </c>
+      <c r="U10" s="34">
+        <f>$D$4-H10</f>
+        <v/>
+      </c>
+      <c r="V10" s="17">
+        <f>U10/S10*100</f>
+        <v/>
+      </c>
+      <c r="W10" s="31">
+        <f>(V10-E10)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -14711,6 +14802,26 @@
         <f>'SOFR_OIS_Quotes'!$H23</f>
         <v/>
       </c>
+      <c r="S11" s="34">
+        <f>(D11*H11)</f>
+        <v/>
+      </c>
+      <c r="T11" s="34">
+        <f>(E11/100)*S11</f>
+        <v/>
+      </c>
+      <c r="U11" s="34">
+        <f>$D$4-H11</f>
+        <v/>
+      </c>
+      <c r="V11" s="17">
+        <f>U11/S11*100</f>
+        <v/>
+      </c>
+      <c r="W11" s="31">
+        <f>(V11-E11)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -14771,6 +14882,26 @@
         <f>'SOFR_OIS_Quotes'!$H24</f>
         <v/>
       </c>
+      <c r="S12" s="34">
+        <f>(D12*H12)</f>
+        <v/>
+      </c>
+      <c r="T12" s="34">
+        <f>(E12/100)*S12</f>
+        <v/>
+      </c>
+      <c r="U12" s="34">
+        <f>$D$4-H12</f>
+        <v/>
+      </c>
+      <c r="V12" s="17">
+        <f>U12/S12*100</f>
+        <v/>
+      </c>
+      <c r="W12" s="31">
+        <f>(V12-E12)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -14831,6 +14962,26 @@
         <f>'SOFR_OIS_Quotes'!$H25</f>
         <v/>
       </c>
+      <c r="S13" s="34">
+        <f>(D13*H13)</f>
+        <v/>
+      </c>
+      <c r="T13" s="34">
+        <f>(E13/100)*S13</f>
+        <v/>
+      </c>
+      <c r="U13" s="34">
+        <f>$D$4-H13</f>
+        <v/>
+      </c>
+      <c r="V13" s="17">
+        <f>U13/S13*100</f>
+        <v/>
+      </c>
+      <c r="W13" s="31">
+        <f>(V13-E13)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -14891,6 +15042,26 @@
         <f>'SOFR_OIS_Quotes'!$H26</f>
         <v/>
       </c>
+      <c r="S14" s="34">
+        <f>(D14*H14)</f>
+        <v/>
+      </c>
+      <c r="T14" s="34">
+        <f>(E14/100)*S14</f>
+        <v/>
+      </c>
+      <c r="U14" s="34">
+        <f>$D$4-H14</f>
+        <v/>
+      </c>
+      <c r="V14" s="17">
+        <f>U14/S14*100</f>
+        <v/>
+      </c>
+      <c r="W14" s="31">
+        <f>(V14-E14)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -14951,6 +15122,26 @@
         <f>'SOFR_OIS_Quotes'!$H27</f>
         <v/>
       </c>
+      <c r="S15" s="34">
+        <f>(D15*H15)</f>
+        <v/>
+      </c>
+      <c r="T15" s="34">
+        <f>(E15/100)*S15</f>
+        <v/>
+      </c>
+      <c r="U15" s="34">
+        <f>$D$4-H15</f>
+        <v/>
+      </c>
+      <c r="V15" s="17">
+        <f>U15/S15*100</f>
+        <v/>
+      </c>
+      <c r="W15" s="31">
+        <f>(V15-E15)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -15011,6 +15202,26 @@
         <f>'SOFR_OIS_Quotes'!$H28</f>
         <v/>
       </c>
+      <c r="S16" s="34">
+        <f>(D16*H16)</f>
+        <v/>
+      </c>
+      <c r="T16" s="34">
+        <f>(E16/100)*S16</f>
+        <v/>
+      </c>
+      <c r="U16" s="34">
+        <f>$D$4-H16</f>
+        <v/>
+      </c>
+      <c r="V16" s="17">
+        <f>U16/S16*100</f>
+        <v/>
+      </c>
+      <c r="W16" s="31">
+        <f>(V16-E16)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -15071,6 +15282,26 @@
         <f>'SOFR_OIS_Quotes'!$H29</f>
         <v/>
       </c>
+      <c r="S17" s="34">
+        <f>(D17*H17)</f>
+        <v/>
+      </c>
+      <c r="T17" s="34">
+        <f>(E17/100)*S17</f>
+        <v/>
+      </c>
+      <c r="U17" s="34">
+        <f>$D$4-H17</f>
+        <v/>
+      </c>
+      <c r="V17" s="17">
+        <f>U17/S17*100</f>
+        <v/>
+      </c>
+      <c r="W17" s="31">
+        <f>(V17-E17)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -15131,6 +15362,26 @@
         <f>'SOFR_OIS_Quotes'!$H30</f>
         <v/>
       </c>
+      <c r="S18" s="34">
+        <f>(D18*H18)</f>
+        <v/>
+      </c>
+      <c r="T18" s="34">
+        <f>(E18/100)*S18</f>
+        <v/>
+      </c>
+      <c r="U18" s="34">
+        <f>$D$4-H18</f>
+        <v/>
+      </c>
+      <c r="V18" s="17">
+        <f>U18/S18*100</f>
+        <v/>
+      </c>
+      <c r="W18" s="31">
+        <f>(V18-E18)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -15191,6 +15442,26 @@
         <f>'SOFR_OIS_Quotes'!$H31</f>
         <v/>
       </c>
+      <c r="S19" s="34">
+        <f>(D19*H19)</f>
+        <v/>
+      </c>
+      <c r="T19" s="34">
+        <f>(E19/100)*S19</f>
+        <v/>
+      </c>
+      <c r="U19" s="34">
+        <f>$D$4-H19</f>
+        <v/>
+      </c>
+      <c r="V19" s="17">
+        <f>U19/S19*100</f>
+        <v/>
+      </c>
+      <c r="W19" s="31">
+        <f>(V19-E19)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -15251,6 +15522,26 @@
         <f>'SOFR_OIS_Quotes'!$H32</f>
         <v/>
       </c>
+      <c r="S20" s="34">
+        <f>(D20*H20)</f>
+        <v/>
+      </c>
+      <c r="T20" s="34">
+        <f>(E20/100)*S20</f>
+        <v/>
+      </c>
+      <c r="U20" s="34">
+        <f>$D$4-H20</f>
+        <v/>
+      </c>
+      <c r="V20" s="17">
+        <f>U20/S20*100</f>
+        <v/>
+      </c>
+      <c r="W20" s="31">
+        <f>(V20-E20)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -15311,6 +15602,26 @@
         <f>'SOFR_OIS_Quotes'!$H33</f>
         <v/>
       </c>
+      <c r="S21" s="34">
+        <f>(D21*H21)</f>
+        <v/>
+      </c>
+      <c r="T21" s="34">
+        <f>(E21/100)*S21</f>
+        <v/>
+      </c>
+      <c r="U21" s="34">
+        <f>$D$4-H21</f>
+        <v/>
+      </c>
+      <c r="V21" s="17">
+        <f>U21/S21*100</f>
+        <v/>
+      </c>
+      <c r="W21" s="31">
+        <f>(V21-E21)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -15375,6 +15686,26 @@
         <f>'SOFR_OIS_Quotes'!$H34</f>
         <v/>
       </c>
+      <c r="S22" s="34">
+        <f>(D22*H22)</f>
+        <v/>
+      </c>
+      <c r="T22" s="34">
+        <f>(E22/100)*S22</f>
+        <v/>
+      </c>
+      <c r="U22" s="34">
+        <f>$D$4-H22</f>
+        <v/>
+      </c>
+      <c r="V22" s="17">
+        <f>U22/S22*100</f>
+        <v/>
+      </c>
+      <c r="W22" s="31">
+        <f>(V22-E22)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -15438,6 +15769,26 @@
         <f>'SOFR_OIS_Quotes'!$H35</f>
         <v/>
       </c>
+      <c r="S23" s="34">
+        <f>(G23+F23*H23)</f>
+        <v/>
+      </c>
+      <c r="T23" s="34">
+        <f>(E23/100)*S23</f>
+        <v/>
+      </c>
+      <c r="U23" s="34">
+        <f>$D$4-H23</f>
+        <v/>
+      </c>
+      <c r="V23" s="17">
+        <f>U23/S23*100</f>
+        <v/>
+      </c>
+      <c r="W23" s="31">
+        <f>(V23-E23)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -15502,6 +15853,26 @@
         <f>'SOFR_OIS_Quotes'!$H36</f>
         <v/>
       </c>
+      <c r="S24" s="34">
+        <f>(G24+F24*H24)</f>
+        <v/>
+      </c>
+      <c r="T24" s="34">
+        <f>(E24/100)*S24</f>
+        <v/>
+      </c>
+      <c r="U24" s="34">
+        <f>$D$4-H24</f>
+        <v/>
+      </c>
+      <c r="V24" s="17">
+        <f>U24/S24*100</f>
+        <v/>
+      </c>
+      <c r="W24" s="31">
+        <f>(V24-E24)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -15559,6 +15930,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S25" s="34">
+        <f>(G25+F25*H25)</f>
+        <v/>
+      </c>
+      <c r="T25" s="34">
+        <f>(E25/100)*S25</f>
+        <v/>
+      </c>
+      <c r="U25" s="34">
+        <f>$D$4-H25</f>
+        <v/>
+      </c>
+      <c r="V25" s="17">
+        <f>U25/S25*100</f>
+        <v/>
+      </c>
+      <c r="W25" s="31">
+        <f>(V25-E25)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -15616,6 +16007,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S26" s="34">
+        <f>(G26+F26*H26)</f>
+        <v/>
+      </c>
+      <c r="T26" s="34">
+        <f>(E26/100)*S26</f>
+        <v/>
+      </c>
+      <c r="U26" s="34">
+        <f>$D$4-H26</f>
+        <v/>
+      </c>
+      <c r="V26" s="17">
+        <f>U26/S26*100</f>
+        <v/>
+      </c>
+      <c r="W26" s="31">
+        <f>(V26-E26)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -15673,6 +16084,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S27" s="34">
+        <f>(G27+F27*H27)</f>
+        <v/>
+      </c>
+      <c r="T27" s="34">
+        <f>(E27/100)*S27</f>
+        <v/>
+      </c>
+      <c r="U27" s="34">
+        <f>$D$4-H27</f>
+        <v/>
+      </c>
+      <c r="V27" s="17">
+        <f>U27/S27*100</f>
+        <v/>
+      </c>
+      <c r="W27" s="31">
+        <f>(V27-E27)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -15730,6 +16161,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S28" s="34">
+        <f>(G28+F28*H28)</f>
+        <v/>
+      </c>
+      <c r="T28" s="34">
+        <f>(E28/100)*S28</f>
+        <v/>
+      </c>
+      <c r="U28" s="34">
+        <f>$D$4-H28</f>
+        <v/>
+      </c>
+      <c r="V28" s="17">
+        <f>U28/S28*100</f>
+        <v/>
+      </c>
+      <c r="W28" s="31">
+        <f>(V28-E28)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -15787,6 +16238,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S29" s="34">
+        <f>(G29+F29*H29)</f>
+        <v/>
+      </c>
+      <c r="T29" s="34">
+        <f>(E29/100)*S29</f>
+        <v/>
+      </c>
+      <c r="U29" s="34">
+        <f>$D$4-H29</f>
+        <v/>
+      </c>
+      <c r="V29" s="17">
+        <f>U29/S29*100</f>
+        <v/>
+      </c>
+      <c r="W29" s="31">
+        <f>(V29-E29)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -15844,6 +16315,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S30" s="34">
+        <f>(G30+F30*H30)</f>
+        <v/>
+      </c>
+      <c r="T30" s="34">
+        <f>(E30/100)*S30</f>
+        <v/>
+      </c>
+      <c r="U30" s="34">
+        <f>$D$4-H30</f>
+        <v/>
+      </c>
+      <c r="V30" s="17">
+        <f>U30/S30*100</f>
+        <v/>
+      </c>
+      <c r="W30" s="31">
+        <f>(V30-E30)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -15901,6 +16392,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S31" s="34">
+        <f>(G31+F31*H31)</f>
+        <v/>
+      </c>
+      <c r="T31" s="34">
+        <f>(E31/100)*S31</f>
+        <v/>
+      </c>
+      <c r="U31" s="34">
+        <f>$D$4-H31</f>
+        <v/>
+      </c>
+      <c r="V31" s="17">
+        <f>U31/S31*100</f>
+        <v/>
+      </c>
+      <c r="W31" s="31">
+        <f>(V31-E31)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -15958,6 +16469,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S32" s="34">
+        <f>(G32+F32*H32)</f>
+        <v/>
+      </c>
+      <c r="T32" s="34">
+        <f>(E32/100)*S32</f>
+        <v/>
+      </c>
+      <c r="U32" s="34">
+        <f>$D$4-H32</f>
+        <v/>
+      </c>
+      <c r="V32" s="17">
+        <f>U32/S32*100</f>
+        <v/>
+      </c>
+      <c r="W32" s="31">
+        <f>(V32-E32)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -16015,6 +16546,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S33" s="34">
+        <f>(G33+F33*H33)</f>
+        <v/>
+      </c>
+      <c r="T33" s="34">
+        <f>(E33/100)*S33</f>
+        <v/>
+      </c>
+      <c r="U33" s="34">
+        <f>$D$4-H33</f>
+        <v/>
+      </c>
+      <c r="V33" s="17">
+        <f>U33/S33*100</f>
+        <v/>
+      </c>
+      <c r="W33" s="31">
+        <f>(V33-E33)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -16072,6 +16623,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S34" s="34">
+        <f>(G34+F34*H34)</f>
+        <v/>
+      </c>
+      <c r="T34" s="34">
+        <f>(E34/100)*S34</f>
+        <v/>
+      </c>
+      <c r="U34" s="34">
+        <f>$D$4-H34</f>
+        <v/>
+      </c>
+      <c r="V34" s="17">
+        <f>U34/S34*100</f>
+        <v/>
+      </c>
+      <c r="W34" s="31">
+        <f>(V34-E34)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -16129,6 +16700,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S35" s="34">
+        <f>(G35+F35*H35)</f>
+        <v/>
+      </c>
+      <c r="T35" s="34">
+        <f>(E35/100)*S35</f>
+        <v/>
+      </c>
+      <c r="U35" s="34">
+        <f>$D$4-H35</f>
+        <v/>
+      </c>
+      <c r="V35" s="17">
+        <f>U35/S35*100</f>
+        <v/>
+      </c>
+      <c r="W35" s="31">
+        <f>(V35-E35)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -16186,6 +16777,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S36" s="34">
+        <f>(G36+F36*H36)</f>
+        <v/>
+      </c>
+      <c r="T36" s="34">
+        <f>(E36/100)*S36</f>
+        <v/>
+      </c>
+      <c r="U36" s="34">
+        <f>$D$4-H36</f>
+        <v/>
+      </c>
+      <c r="V36" s="17">
+        <f>U36/S36*100</f>
+        <v/>
+      </c>
+      <c r="W36" s="31">
+        <f>(V36-E36)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -16243,6 +16854,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S37" s="34">
+        <f>(G37+F37*H37)</f>
+        <v/>
+      </c>
+      <c r="T37" s="34">
+        <f>(E37/100)*S37</f>
+        <v/>
+      </c>
+      <c r="U37" s="34">
+        <f>$D$4-H37</f>
+        <v/>
+      </c>
+      <c r="V37" s="17">
+        <f>U37/S37*100</f>
+        <v/>
+      </c>
+      <c r="W37" s="31">
+        <f>(V37-E37)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -16300,6 +16931,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S38" s="34">
+        <f>(G38+F38*H38)</f>
+        <v/>
+      </c>
+      <c r="T38" s="34">
+        <f>(E38/100)*S38</f>
+        <v/>
+      </c>
+      <c r="U38" s="34">
+        <f>$D$4-H38</f>
+        <v/>
+      </c>
+      <c r="V38" s="17">
+        <f>U38/S38*100</f>
+        <v/>
+      </c>
+      <c r="W38" s="31">
+        <f>(V38-E38)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -16357,6 +17008,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S39" s="34">
+        <f>(G39+F39*H39)</f>
+        <v/>
+      </c>
+      <c r="T39" s="34">
+        <f>(E39/100)*S39</f>
+        <v/>
+      </c>
+      <c r="U39" s="34">
+        <f>$D$4-H39</f>
+        <v/>
+      </c>
+      <c r="V39" s="17">
+        <f>U39/S39*100</f>
+        <v/>
+      </c>
+      <c r="W39" s="31">
+        <f>(V39-E39)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
@@ -16414,6 +17085,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S40" s="34">
+        <f>(G40+F40*H40)</f>
+        <v/>
+      </c>
+      <c r="T40" s="34">
+        <f>(E40/100)*S40</f>
+        <v/>
+      </c>
+      <c r="U40" s="34">
+        <f>$D$4-H40</f>
+        <v/>
+      </c>
+      <c r="V40" s="17">
+        <f>U40/S40*100</f>
+        <v/>
+      </c>
+      <c r="W40" s="31">
+        <f>(V40-E40)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -16471,6 +17162,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S41" s="34">
+        <f>(G41+F41*H41)</f>
+        <v/>
+      </c>
+      <c r="T41" s="34">
+        <f>(E41/100)*S41</f>
+        <v/>
+      </c>
+      <c r="U41" s="34">
+        <f>$D$4-H41</f>
+        <v/>
+      </c>
+      <c r="V41" s="17">
+        <f>U41/S41*100</f>
+        <v/>
+      </c>
+      <c r="W41" s="31">
+        <f>(V41-E41)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -16528,6 +17239,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S42" s="34">
+        <f>(G42+F42*H42)</f>
+        <v/>
+      </c>
+      <c r="T42" s="34">
+        <f>(E42/100)*S42</f>
+        <v/>
+      </c>
+      <c r="U42" s="34">
+        <f>$D$4-H42</f>
+        <v/>
+      </c>
+      <c r="V42" s="17">
+        <f>U42/S42*100</f>
+        <v/>
+      </c>
+      <c r="W42" s="31">
+        <f>(V42-E42)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -16585,6 +17316,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S43" s="34">
+        <f>(G43+F43*H43)</f>
+        <v/>
+      </c>
+      <c r="T43" s="34">
+        <f>(E43/100)*S43</f>
+        <v/>
+      </c>
+      <c r="U43" s="34">
+        <f>$D$4-H43</f>
+        <v/>
+      </c>
+      <c r="V43" s="17">
+        <f>U43/S43*100</f>
+        <v/>
+      </c>
+      <c r="W43" s="31">
+        <f>(V43-E43)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -16642,6 +17393,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S44" s="34">
+        <f>(G44+F44*H44)</f>
+        <v/>
+      </c>
+      <c r="T44" s="34">
+        <f>(E44/100)*S44</f>
+        <v/>
+      </c>
+      <c r="U44" s="34">
+        <f>$D$4-H44</f>
+        <v/>
+      </c>
+      <c r="V44" s="17">
+        <f>U44/S44*100</f>
+        <v/>
+      </c>
+      <c r="W44" s="31">
+        <f>(V44-E44)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
@@ -16699,6 +17470,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S45" s="34">
+        <f>(G45+F45*H45)</f>
+        <v/>
+      </c>
+      <c r="T45" s="34">
+        <f>(E45/100)*S45</f>
+        <v/>
+      </c>
+      <c r="U45" s="34">
+        <f>$D$4-H45</f>
+        <v/>
+      </c>
+      <c r="V45" s="17">
+        <f>U45/S45*100</f>
+        <v/>
+      </c>
+      <c r="W45" s="31">
+        <f>(V45-E45)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -16756,6 +17547,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S46" s="34">
+        <f>(G46+F46*H46)</f>
+        <v/>
+      </c>
+      <c r="T46" s="34">
+        <f>(E46/100)*S46</f>
+        <v/>
+      </c>
+      <c r="U46" s="34">
+        <f>$D$4-H46</f>
+        <v/>
+      </c>
+      <c r="V46" s="17">
+        <f>U46/S46*100</f>
+        <v/>
+      </c>
+      <c r="W46" s="31">
+        <f>(V46-E46)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -16813,6 +17624,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S47" s="34">
+        <f>(G47+F47*H47)</f>
+        <v/>
+      </c>
+      <c r="T47" s="34">
+        <f>(E47/100)*S47</f>
+        <v/>
+      </c>
+      <c r="U47" s="34">
+        <f>$D$4-H47</f>
+        <v/>
+      </c>
+      <c r="V47" s="17">
+        <f>U47/S47*100</f>
+        <v/>
+      </c>
+      <c r="W47" s="31">
+        <f>(V47-E47)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -16870,6 +17701,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S48" s="34">
+        <f>(G48+F48*H48)</f>
+        <v/>
+      </c>
+      <c r="T48" s="34">
+        <f>(E48/100)*S48</f>
+        <v/>
+      </c>
+      <c r="U48" s="34">
+        <f>$D$4-H48</f>
+        <v/>
+      </c>
+      <c r="V48" s="17">
+        <f>U48/S48*100</f>
+        <v/>
+      </c>
+      <c r="W48" s="31">
+        <f>(V48-E48)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -16927,6 +17778,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S49" s="34">
+        <f>(G49+F49*H49)</f>
+        <v/>
+      </c>
+      <c r="T49" s="34">
+        <f>(E49/100)*S49</f>
+        <v/>
+      </c>
+      <c r="U49" s="34">
+        <f>$D$4-H49</f>
+        <v/>
+      </c>
+      <c r="V49" s="17">
+        <f>U49/S49*100</f>
+        <v/>
+      </c>
+      <c r="W49" s="31">
+        <f>(V49-E49)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -16984,6 +17855,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S50" s="34">
+        <f>(G50+F50*H50)</f>
+        <v/>
+      </c>
+      <c r="T50" s="34">
+        <f>(E50/100)*S50</f>
+        <v/>
+      </c>
+      <c r="U50" s="34">
+        <f>$D$4-H50</f>
+        <v/>
+      </c>
+      <c r="V50" s="17">
+        <f>U50/S50*100</f>
+        <v/>
+      </c>
+      <c r="W50" s="31">
+        <f>(V50-E50)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -17041,6 +17932,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S51" s="34">
+        <f>(G51+F51*H51)</f>
+        <v/>
+      </c>
+      <c r="T51" s="34">
+        <f>(E51/100)*S51</f>
+        <v/>
+      </c>
+      <c r="U51" s="34">
+        <f>$D$4-H51</f>
+        <v/>
+      </c>
+      <c r="V51" s="17">
+        <f>U51/S51*100</f>
+        <v/>
+      </c>
+      <c r="W51" s="31">
+        <f>(V51-E51)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="inlineStr">
@@ -17098,6 +18009,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S52" s="34">
+        <f>(G52+F52*H52)</f>
+        <v/>
+      </c>
+      <c r="T52" s="34">
+        <f>(E52/100)*S52</f>
+        <v/>
+      </c>
+      <c r="U52" s="34">
+        <f>$D$4-H52</f>
+        <v/>
+      </c>
+      <c r="V52" s="17">
+        <f>U52/S52*100</f>
+        <v/>
+      </c>
+      <c r="W52" s="31">
+        <f>(V52-E52)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -17155,6 +18086,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S53" s="34">
+        <f>(G53+F53*H53)</f>
+        <v/>
+      </c>
+      <c r="T53" s="34">
+        <f>(E53/100)*S53</f>
+        <v/>
+      </c>
+      <c r="U53" s="34">
+        <f>$D$4-H53</f>
+        <v/>
+      </c>
+      <c r="V53" s="17">
+        <f>U53/S53*100</f>
+        <v/>
+      </c>
+      <c r="W53" s="31">
+        <f>(V53-E53)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -17212,6 +18163,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S54" s="34">
+        <f>(G54+F54*H54)</f>
+        <v/>
+      </c>
+      <c r="T54" s="34">
+        <f>(E54/100)*S54</f>
+        <v/>
+      </c>
+      <c r="U54" s="34">
+        <f>$D$4-H54</f>
+        <v/>
+      </c>
+      <c r="V54" s="17">
+        <f>U54/S54*100</f>
+        <v/>
+      </c>
+      <c r="W54" s="31">
+        <f>(V54-E54)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -17269,6 +18240,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S55" s="34">
+        <f>(G55+F55*H55)</f>
+        <v/>
+      </c>
+      <c r="T55" s="34">
+        <f>(E55/100)*S55</f>
+        <v/>
+      </c>
+      <c r="U55" s="34">
+        <f>$D$4-H55</f>
+        <v/>
+      </c>
+      <c r="V55" s="17">
+        <f>U55/S55*100</f>
+        <v/>
+      </c>
+      <c r="W55" s="31">
+        <f>(V55-E55)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -17326,6 +18317,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S56" s="34">
+        <f>(G56+F56*H56)</f>
+        <v/>
+      </c>
+      <c r="T56" s="34">
+        <f>(E56/100)*S56</f>
+        <v/>
+      </c>
+      <c r="U56" s="34">
+        <f>$D$4-H56</f>
+        <v/>
+      </c>
+      <c r="V56" s="17">
+        <f>U56/S56*100</f>
+        <v/>
+      </c>
+      <c r="W56" s="31">
+        <f>(V56-E56)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
@@ -17383,6 +18394,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S57" s="34">
+        <f>(G57+F57*H57)</f>
+        <v/>
+      </c>
+      <c r="T57" s="34">
+        <f>(E57/100)*S57</f>
+        <v/>
+      </c>
+      <c r="U57" s="34">
+        <f>$D$4-H57</f>
+        <v/>
+      </c>
+      <c r="V57" s="17">
+        <f>U57/S57*100</f>
+        <v/>
+      </c>
+      <c r="W57" s="31">
+        <f>(V57-E57)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
@@ -17440,6 +18471,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S58" s="34">
+        <f>(G58+F58*H58)</f>
+        <v/>
+      </c>
+      <c r="T58" s="34">
+        <f>(E58/100)*S58</f>
+        <v/>
+      </c>
+      <c r="U58" s="34">
+        <f>$D$4-H58</f>
+        <v/>
+      </c>
+      <c r="V58" s="17">
+        <f>U58/S58*100</f>
+        <v/>
+      </c>
+      <c r="W58" s="31">
+        <f>(V58-E58)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
@@ -17497,6 +18548,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S59" s="34">
+        <f>(G59+F59*H59)</f>
+        <v/>
+      </c>
+      <c r="T59" s="34">
+        <f>(E59/100)*S59</f>
+        <v/>
+      </c>
+      <c r="U59" s="34">
+        <f>$D$4-H59</f>
+        <v/>
+      </c>
+      <c r="V59" s="17">
+        <f>U59/S59*100</f>
+        <v/>
+      </c>
+      <c r="W59" s="31">
+        <f>(V59-E59)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
@@ -17554,6 +18625,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S60" s="34">
+        <f>(G60+F60*H60)</f>
+        <v/>
+      </c>
+      <c r="T60" s="34">
+        <f>(E60/100)*S60</f>
+        <v/>
+      </c>
+      <c r="U60" s="34">
+        <f>$D$4-H60</f>
+        <v/>
+      </c>
+      <c r="V60" s="17">
+        <f>U60/S60*100</f>
+        <v/>
+      </c>
+      <c r="W60" s="31">
+        <f>(V60-E60)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
@@ -17611,6 +18702,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S61" s="34">
+        <f>(G61+F61*H61)</f>
+        <v/>
+      </c>
+      <c r="T61" s="34">
+        <f>(E61/100)*S61</f>
+        <v/>
+      </c>
+      <c r="U61" s="34">
+        <f>$D$4-H61</f>
+        <v/>
+      </c>
+      <c r="V61" s="17">
+        <f>U61/S61*100</f>
+        <v/>
+      </c>
+      <c r="W61" s="31">
+        <f>(V61-E61)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
@@ -17668,6 +18779,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S62" s="34">
+        <f>(G62+F62*H62)</f>
+        <v/>
+      </c>
+      <c r="T62" s="34">
+        <f>(E62/100)*S62</f>
+        <v/>
+      </c>
+      <c r="U62" s="34">
+        <f>$D$4-H62</f>
+        <v/>
+      </c>
+      <c r="V62" s="17">
+        <f>U62/S62*100</f>
+        <v/>
+      </c>
+      <c r="W62" s="31">
+        <f>(V62-E62)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
@@ -17725,6 +18856,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S63" s="34">
+        <f>(G63+F63*H63)</f>
+        <v/>
+      </c>
+      <c r="T63" s="34">
+        <f>(E63/100)*S63</f>
+        <v/>
+      </c>
+      <c r="U63" s="34">
+        <f>$D$4-H63</f>
+        <v/>
+      </c>
+      <c r="V63" s="17">
+        <f>U63/S63*100</f>
+        <v/>
+      </c>
+      <c r="W63" s="31">
+        <f>(V63-E63)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
@@ -17782,6 +18933,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S64" s="34">
+        <f>(G64+F64*H64)</f>
+        <v/>
+      </c>
+      <c r="T64" s="34">
+        <f>(E64/100)*S64</f>
+        <v/>
+      </c>
+      <c r="U64" s="34">
+        <f>$D$4-H64</f>
+        <v/>
+      </c>
+      <c r="V64" s="17">
+        <f>U64/S64*100</f>
+        <v/>
+      </c>
+      <c r="W64" s="31">
+        <f>(V64-E64)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -17839,6 +19010,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S65" s="34">
+        <f>(G65+F65*H65)</f>
+        <v/>
+      </c>
+      <c r="T65" s="34">
+        <f>(E65/100)*S65</f>
+        <v/>
+      </c>
+      <c r="U65" s="34">
+        <f>$D$4-H65</f>
+        <v/>
+      </c>
+      <c r="V65" s="17">
+        <f>U65/S65*100</f>
+        <v/>
+      </c>
+      <c r="W65" s="31">
+        <f>(V65-E65)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
@@ -17896,6 +19087,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S66" s="34">
+        <f>(G66+F66*H66)</f>
+        <v/>
+      </c>
+      <c r="T66" s="34">
+        <f>(E66/100)*S66</f>
+        <v/>
+      </c>
+      <c r="U66" s="34">
+        <f>$D$4-H66</f>
+        <v/>
+      </c>
+      <c r="V66" s="17">
+        <f>U66/S66*100</f>
+        <v/>
+      </c>
+      <c r="W66" s="31">
+        <f>(V66-E66)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
@@ -17953,6 +19164,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S67" s="34">
+        <f>(G67+F67*H67)</f>
+        <v/>
+      </c>
+      <c r="T67" s="34">
+        <f>(E67/100)*S67</f>
+        <v/>
+      </c>
+      <c r="U67" s="34">
+        <f>$D$4-H67</f>
+        <v/>
+      </c>
+      <c r="V67" s="17">
+        <f>U67/S67*100</f>
+        <v/>
+      </c>
+      <c r="W67" s="31">
+        <f>(V67-E67)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
@@ -18010,6 +19241,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S68" s="34">
+        <f>(G68+F68*H68)</f>
+        <v/>
+      </c>
+      <c r="T68" s="34">
+        <f>(E68/100)*S68</f>
+        <v/>
+      </c>
+      <c r="U68" s="34">
+        <f>$D$4-H68</f>
+        <v/>
+      </c>
+      <c r="V68" s="17">
+        <f>U68/S68*100</f>
+        <v/>
+      </c>
+      <c r="W68" s="31">
+        <f>(V68-E68)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
@@ -18067,6 +19318,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S69" s="34">
+        <f>(G69+F69*H69)</f>
+        <v/>
+      </c>
+      <c r="T69" s="34">
+        <f>(E69/100)*S69</f>
+        <v/>
+      </c>
+      <c r="U69" s="34">
+        <f>$D$4-H69</f>
+        <v/>
+      </c>
+      <c r="V69" s="17">
+        <f>U69/S69*100</f>
+        <v/>
+      </c>
+      <c r="W69" s="31">
+        <f>(V69-E69)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
@@ -18124,6 +19395,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S70" s="34">
+        <f>(G70+F70*H70)</f>
+        <v/>
+      </c>
+      <c r="T70" s="34">
+        <f>(E70/100)*S70</f>
+        <v/>
+      </c>
+      <c r="U70" s="34">
+        <f>$D$4-H70</f>
+        <v/>
+      </c>
+      <c r="V70" s="17">
+        <f>U70/S70*100</f>
+        <v/>
+      </c>
+      <c r="W70" s="31">
+        <f>(V70-E70)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
@@ -18181,6 +19472,26 @@
           <t>interp</t>
         </is>
       </c>
+      <c r="S71" s="34">
+        <f>(G71+F71*H71)</f>
+        <v/>
+      </c>
+      <c r="T71" s="34">
+        <f>(E71/100)*S71</f>
+        <v/>
+      </c>
+      <c r="U71" s="34">
+        <f>$D$4-H71</f>
+        <v/>
+      </c>
+      <c r="V71" s="17">
+        <f>U71/S71*100</f>
+        <v/>
+      </c>
+      <c r="W71" s="31">
+        <f>(V71-E71)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
@@ -18238,6 +19549,26 @@
           <t>market</t>
         </is>
       </c>
+      <c r="S72" s="34">
+        <f>(G72+F72*H72)</f>
+        <v/>
+      </c>
+      <c r="T72" s="34">
+        <f>(E72/100)*S72</f>
+        <v/>
+      </c>
+      <c r="U72" s="34">
+        <f>$D$4-H72</f>
+        <v/>
+      </c>
+      <c r="V72" s="17">
+        <f>U72/S72*100</f>
+        <v/>
+      </c>
+      <c r="W72" s="31">
+        <f>(V72-E72)*100</f>
+        <v/>
+      </c>
     </row>
     <row r="74" ht="40" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
@@ -18248,9 +19579,10 @@
     </row>
     <row r="75"/>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A74:N75"/>
     <mergeCell ref="A5:N6"/>
+    <mergeCell ref="S6:W6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18317,7 +19649,7 @@
           <t>sigma (bp/yr):</t>
         </is>
       </c>
-      <c r="P5" s="34" t="n">
+      <c r="P5" s="35" t="n">
         <v>100</v>
       </c>
     </row>
@@ -18522,7 +19854,7 @@
         <f>0.5*$P$5^2*((P8-'Bootstrap'!$B$4)/365)*((Q8-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U8" s="35">
+      <c r="U8" s="34">
         <f>(S8-T8/100)/100</f>
         <v/>
       </c>
@@ -18616,7 +19948,7 @@
         <f>0.5*$P$5^2*((P9-'Bootstrap'!$B$4)/365)*((Q9-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U9" s="35">
+      <c r="U9" s="34">
         <f>(S9-T9/100)/100</f>
         <v/>
       </c>
@@ -18710,7 +20042,7 @@
         <f>0.5*$P$5^2*((P10-'Bootstrap'!$B$4)/365)*((Q10-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U10" s="35">
+      <c r="U10" s="34">
         <f>(S10-T10/100)/100</f>
         <v/>
       </c>
@@ -18804,7 +20136,7 @@
         <f>0.5*$P$5^2*((P11-'Bootstrap'!$B$4)/365)*((Q11-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U11" s="35">
+      <c r="U11" s="34">
         <f>(S11-T11/100)/100</f>
         <v/>
       </c>
@@ -18898,7 +20230,7 @@
         <f>0.5*$P$5^2*((P12-'Bootstrap'!$B$4)/365)*((Q12-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U12" s="35">
+      <c r="U12" s="34">
         <f>(S12-T12/100)/100</f>
         <v/>
       </c>
@@ -18992,7 +20324,7 @@
         <f>0.5*$P$5^2*((P13-'Bootstrap'!$B$4)/365)*((Q13-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U13" s="35">
+      <c r="U13" s="34">
         <f>(S13-T13/100)/100</f>
         <v/>
       </c>
@@ -19086,7 +20418,7 @@
         <f>0.5*$P$5^2*((P14-'Bootstrap'!$B$4)/365)*((Q14-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U14" s="35">
+      <c r="U14" s="34">
         <f>(S14-T14/100)/100</f>
         <v/>
       </c>
@@ -19180,7 +20512,7 @@
         <f>0.5*$P$5^2*((P15-'Bootstrap'!$B$4)/365)*((Q15-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U15" s="35">
+      <c r="U15" s="34">
         <f>(S15-T15/100)/100</f>
         <v/>
       </c>
@@ -19274,7 +20606,7 @@
         <f>0.5*$P$5^2*((P16-'Bootstrap'!$B$4)/365)*((Q16-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U16" s="35">
+      <c r="U16" s="34">
         <f>(S16-T16/100)/100</f>
         <v/>
       </c>
@@ -19368,7 +20700,7 @@
         <f>0.5*$P$5^2*((P17-'Bootstrap'!$B$4)/365)*((Q17-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U17" s="35">
+      <c r="U17" s="34">
         <f>(S17-T17/100)/100</f>
         <v/>
       </c>
@@ -19462,7 +20794,7 @@
         <f>0.5*$P$5^2*((P18-'Bootstrap'!$B$4)/365)*((Q18-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U18" s="35">
+      <c r="U18" s="34">
         <f>(S18-T18/100)/100</f>
         <v/>
       </c>
@@ -19556,7 +20888,7 @@
         <f>0.5*$P$5^2*((P19-'Bootstrap'!$B$4)/365)*((Q19-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U19" s="35">
+      <c r="U19" s="34">
         <f>(S19-T19/100)/100</f>
         <v/>
       </c>
@@ -19650,7 +20982,7 @@
         <f>0.5*$P$5^2*((P20-'Bootstrap'!$B$4)/365)*((Q20-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U20" s="35">
+      <c r="U20" s="34">
         <f>(S20-T20/100)/100</f>
         <v/>
       </c>
@@ -19744,7 +21076,7 @@
         <f>0.5*$P$5^2*((P21-'Bootstrap'!$B$4)/365)*((Q21-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U21" s="35">
+      <c r="U21" s="34">
         <f>(S21-T21/100)/100</f>
         <v/>
       </c>
@@ -19839,7 +21171,7 @@
         <f>0.5*$P$5^2*((P22-'Bootstrap'!$B$4)/365)*((Q22-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U22" s="35">
+      <c r="U22" s="34">
         <f>(S22-T22/100)/100</f>
         <v/>
       </c>
@@ -19933,7 +21265,7 @@
         <f>0.5*$P$5^2*((P23-'Bootstrap'!$B$4)/365)*((Q23-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U23" s="35">
+      <c r="U23" s="34">
         <f>(S23-T23/100)/100</f>
         <v/>
       </c>
@@ -20028,7 +21360,7 @@
         <f>0.5*$P$5^2*((P24-'Bootstrap'!$B$4)/365)*((Q24-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U24" s="35">
+      <c r="U24" s="34">
         <f>(S24-T24/100)/100</f>
         <v/>
       </c>
@@ -20123,7 +21455,7 @@
         <f>0.5*$P$5^2*((P25-'Bootstrap'!$B$4)/365)*((Q25-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U25" s="35">
+      <c r="U25" s="34">
         <f>(S25-T25/100)/100</f>
         <v/>
       </c>
@@ -20218,7 +21550,7 @@
         <f>0.5*$P$5^2*((P26-'Bootstrap'!$B$4)/365)*((Q26-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U26" s="35">
+      <c r="U26" s="34">
         <f>(S26-T26/100)/100</f>
         <v/>
       </c>
@@ -20313,7 +21645,7 @@
         <f>0.5*$P$5^2*((P27-'Bootstrap'!$B$4)/365)*((Q27-'Bootstrap'!$B$4)/365)/10000</f>
         <v/>
       </c>
-      <c r="U27" s="35">
+      <c r="U27" s="34">
         <f>(S27-T27/100)/100</f>
         <v/>
       </c>
@@ -21354,7 +22686,7 @@
           <t>Fixed annuity  Sum tau·DF</t>
         </is>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="34">
         <f>SUM(H36:H85)</f>
         <v/>
       </c>
@@ -21445,7 +22777,7 @@
           <t>Par coupon (%)</t>
         </is>
       </c>
-      <c r="B25" s="35">
+      <c r="B25" s="34">
         <f>(B19-B20)/B21*100</f>
         <v/>
       </c>
@@ -21696,7 +23028,7 @@
         <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
         <v/>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="34">
         <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
         <v/>
       </c>
@@ -21738,7 +23070,7 @@
         <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
         <v/>
       </c>
-      <c r="H37" s="35">
+      <c r="H37" s="34">
         <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
         <v/>
       </c>
@@ -21780,7 +23112,7 @@
         <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
         <v/>
       </c>
-      <c r="H38" s="35">
+      <c r="H38" s="34">
         <f>IF(A38&lt;=$B$9,D38*E38,"")</f>
         <v/>
       </c>
@@ -21822,7 +23154,7 @@
         <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
         <v/>
       </c>
-      <c r="H39" s="35">
+      <c r="H39" s="34">
         <f>IF(A39&lt;=$B$9,D39*E39,"")</f>
         <v/>
       </c>
@@ -21861,7 +23193,7 @@
         <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
         <v/>
       </c>
-      <c r="H40" s="35">
+      <c r="H40" s="34">
         <f>IF(A40&lt;=$B$9,D40*E40,"")</f>
         <v/>
       </c>
@@ -21895,7 +23227,7 @@
         <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
         <v/>
       </c>
-      <c r="H41" s="35">
+      <c r="H41" s="34">
         <f>IF(A41&lt;=$B$9,D41*E41,"")</f>
         <v/>
       </c>
@@ -21937,7 +23269,7 @@
         <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
         <v/>
       </c>
-      <c r="H42" s="35">
+      <c r="H42" s="34">
         <f>IF(A42&lt;=$B$9,D42*E42,"")</f>
         <v/>
       </c>
@@ -21979,7 +23311,7 @@
         <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
         <v/>
       </c>
-      <c r="H43" s="35">
+      <c r="H43" s="34">
         <f>IF(A43&lt;=$B$9,D43*E43,"")</f>
         <v/>
       </c>
@@ -22021,7 +23353,7 @@
         <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
         <v/>
       </c>
-      <c r="H44" s="35">
+      <c r="H44" s="34">
         <f>IF(A44&lt;=$B$9,D44*E44,"")</f>
         <v/>
       </c>
@@ -22063,7 +23395,7 @@
         <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
         <v/>
       </c>
-      <c r="H45" s="35">
+      <c r="H45" s="34">
         <f>IF(A45&lt;=$B$9,D45*E45,"")</f>
         <v/>
       </c>
@@ -22105,7 +23437,7 @@
         <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
         <v/>
       </c>
-      <c r="H46" s="35">
+      <c r="H46" s="34">
         <f>IF(A46&lt;=$B$9,D46*E46,"")</f>
         <v/>
       </c>
@@ -22147,7 +23479,7 @@
         <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
         <v/>
       </c>
-      <c r="H47" s="35">
+      <c r="H47" s="34">
         <f>IF(A47&lt;=$B$9,D47*E47,"")</f>
         <v/>
       </c>
@@ -22189,7 +23521,7 @@
         <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
         <v/>
       </c>
-      <c r="H48" s="35">
+      <c r="H48" s="34">
         <f>IF(A48&lt;=$B$9,D48*E48,"")</f>
         <v/>
       </c>
@@ -22231,7 +23563,7 @@
         <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
         <v/>
       </c>
-      <c r="H49" s="35">
+      <c r="H49" s="34">
         <f>IF(A49&lt;=$B$9,D49*E49,"")</f>
         <v/>
       </c>
@@ -22273,7 +23605,7 @@
         <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
         <v/>
       </c>
-      <c r="H50" s="35">
+      <c r="H50" s="34">
         <f>IF(A50&lt;=$B$9,D50*E50,"")</f>
         <v/>
       </c>
@@ -22315,7 +23647,7 @@
         <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
         <v/>
       </c>
-      <c r="H51" s="35">
+      <c r="H51" s="34">
         <f>IF(A51&lt;=$B$9,D51*E51,"")</f>
         <v/>
       </c>
@@ -22357,7 +23689,7 @@
         <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
         <v/>
       </c>
-      <c r="H52" s="35">
+      <c r="H52" s="34">
         <f>IF(A52&lt;=$B$9,D52*E52,"")</f>
         <v/>
       </c>
@@ -22399,7 +23731,7 @@
         <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
         <v/>
       </c>
-      <c r="H53" s="35">
+      <c r="H53" s="34">
         <f>IF(A53&lt;=$B$9,D53*E53,"")</f>
         <v/>
       </c>
@@ -22441,7 +23773,7 @@
         <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
         <v/>
       </c>
-      <c r="H54" s="35">
+      <c r="H54" s="34">
         <f>IF(A54&lt;=$B$9,D54*E54,"")</f>
         <v/>
       </c>
@@ -22483,7 +23815,7 @@
         <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
         <v/>
       </c>
-      <c r="H55" s="35">
+      <c r="H55" s="34">
         <f>IF(A55&lt;=$B$9,D55*E55,"")</f>
         <v/>
       </c>
@@ -22525,7 +23857,7 @@
         <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
         <v/>
       </c>
-      <c r="H56" s="35">
+      <c r="H56" s="34">
         <f>IF(A56&lt;=$B$9,D56*E56,"")</f>
         <v/>
       </c>
@@ -22567,7 +23899,7 @@
         <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
         <v/>
       </c>
-      <c r="H57" s="35">
+      <c r="H57" s="34">
         <f>IF(A57&lt;=$B$9,D57*E57,"")</f>
         <v/>
       </c>
@@ -22609,7 +23941,7 @@
         <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
         <v/>
       </c>
-      <c r="H58" s="35">
+      <c r="H58" s="34">
         <f>IF(A58&lt;=$B$9,D58*E58,"")</f>
         <v/>
       </c>
@@ -22651,7 +23983,7 @@
         <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
         <v/>
       </c>
-      <c r="H59" s="35">
+      <c r="H59" s="34">
         <f>IF(A59&lt;=$B$9,D59*E59,"")</f>
         <v/>
       </c>
@@ -22693,7 +24025,7 @@
         <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
         <v/>
       </c>
-      <c r="H60" s="35">
+      <c r="H60" s="34">
         <f>IF(A60&lt;=$B$9,D60*E60,"")</f>
         <v/>
       </c>
@@ -22735,7 +24067,7 @@
         <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
         <v/>
       </c>
-      <c r="H61" s="35">
+      <c r="H61" s="34">
         <f>IF(A61&lt;=$B$9,D61*E61,"")</f>
         <v/>
       </c>
@@ -22777,7 +24109,7 @@
         <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
         <v/>
       </c>
-      <c r="H62" s="35">
+      <c r="H62" s="34">
         <f>IF(A62&lt;=$B$9,D62*E62,"")</f>
         <v/>
       </c>
@@ -22819,7 +24151,7 @@
         <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
         <v/>
       </c>
-      <c r="H63" s="35">
+      <c r="H63" s="34">
         <f>IF(A63&lt;=$B$9,D63*E63,"")</f>
         <v/>
       </c>
@@ -22861,7 +24193,7 @@
         <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
         <v/>
       </c>
-      <c r="H64" s="35">
+      <c r="H64" s="34">
         <f>IF(A64&lt;=$B$9,D64*E64,"")</f>
         <v/>
       </c>
@@ -22903,7 +24235,7 @@
         <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
         <v/>
       </c>
-      <c r="H65" s="35">
+      <c r="H65" s="34">
         <f>IF(A65&lt;=$B$9,D65*E65,"")</f>
         <v/>
       </c>
@@ -22945,7 +24277,7 @@
         <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
         <v/>
       </c>
-      <c r="H66" s="35">
+      <c r="H66" s="34">
         <f>IF(A66&lt;=$B$9,D66*E66,"")</f>
         <v/>
       </c>
@@ -22987,7 +24319,7 @@
         <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
         <v/>
       </c>
-      <c r="H67" s="35">
+      <c r="H67" s="34">
         <f>IF(A67&lt;=$B$9,D67*E67,"")</f>
         <v/>
       </c>
@@ -23029,7 +24361,7 @@
         <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
         <v/>
       </c>
-      <c r="H68" s="35">
+      <c r="H68" s="34">
         <f>IF(A68&lt;=$B$9,D68*E68,"")</f>
         <v/>
       </c>
@@ -23071,7 +24403,7 @@
         <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
         <v/>
       </c>
-      <c r="H69" s="35">
+      <c r="H69" s="34">
         <f>IF(A69&lt;=$B$9,D69*E69,"")</f>
         <v/>
       </c>
@@ -23113,7 +24445,7 @@
         <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
         <v/>
       </c>
-      <c r="H70" s="35">
+      <c r="H70" s="34">
         <f>IF(A70&lt;=$B$9,D70*E70,"")</f>
         <v/>
       </c>
@@ -23155,7 +24487,7 @@
         <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
         <v/>
       </c>
-      <c r="H71" s="35">
+      <c r="H71" s="34">
         <f>IF(A71&lt;=$B$9,D71*E71,"")</f>
         <v/>
       </c>
@@ -23197,7 +24529,7 @@
         <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
         <v/>
       </c>
-      <c r="H72" s="35">
+      <c r="H72" s="34">
         <f>IF(A72&lt;=$B$9,D72*E72,"")</f>
         <v/>
       </c>
@@ -23231,7 +24563,7 @@
         <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
         <v/>
       </c>
-      <c r="H73" s="35">
+      <c r="H73" s="34">
         <f>IF(A73&lt;=$B$9,D73*E73,"")</f>
         <v/>
       </c>
@@ -23265,7 +24597,7 @@
         <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
         <v/>
       </c>
-      <c r="H74" s="35">
+      <c r="H74" s="34">
         <f>IF(A74&lt;=$B$9,D74*E74,"")</f>
         <v/>
       </c>
@@ -23299,7 +24631,7 @@
         <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
         <v/>
       </c>
-      <c r="H75" s="35">
+      <c r="H75" s="34">
         <f>IF(A75&lt;=$B$9,D75*E75,"")</f>
         <v/>
       </c>
@@ -23333,7 +24665,7 @@
         <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
         <v/>
       </c>
-      <c r="H76" s="35">
+      <c r="H76" s="34">
         <f>IF(A76&lt;=$B$9,D76*E76,"")</f>
         <v/>
       </c>
@@ -23367,7 +24699,7 @@
         <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
         <v/>
       </c>
-      <c r="H77" s="35">
+      <c r="H77" s="34">
         <f>IF(A77&lt;=$B$9,D77*E77,"")</f>
         <v/>
       </c>
@@ -23401,7 +24733,7 @@
         <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
         <v/>
       </c>
-      <c r="H78" s="35">
+      <c r="H78" s="34">
         <f>IF(A78&lt;=$B$9,D78*E78,"")</f>
         <v/>
       </c>
@@ -23435,7 +24767,7 @@
         <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
         <v/>
       </c>
-      <c r="H79" s="35">
+      <c r="H79" s="34">
         <f>IF(A79&lt;=$B$9,D79*E79,"")</f>
         <v/>
       </c>
@@ -23469,7 +24801,7 @@
         <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
         <v/>
       </c>
-      <c r="H80" s="35">
+      <c r="H80" s="34">
         <f>IF(A80&lt;=$B$9,D80*E80,"")</f>
         <v/>
       </c>
@@ -23503,7 +24835,7 @@
         <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
         <v/>
       </c>
-      <c r="H81" s="35">
+      <c r="H81" s="34">
         <f>IF(A81&lt;=$B$9,D81*E81,"")</f>
         <v/>
       </c>
@@ -23537,7 +24869,7 @@
         <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
         <v/>
       </c>
-      <c r="H82" s="35">
+      <c r="H82" s="34">
         <f>IF(A82&lt;=$B$9,D82*E82,"")</f>
         <v/>
       </c>
@@ -23571,7 +24903,7 @@
         <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
         <v/>
       </c>
-      <c r="H83" s="35">
+      <c r="H83" s="34">
         <f>IF(A83&lt;=$B$9,D83*E83,"")</f>
         <v/>
       </c>
@@ -23605,7 +24937,7 @@
         <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
         <v/>
       </c>
-      <c r="H84" s="35">
+      <c r="H84" s="34">
         <f>IF(A84&lt;=$B$9,D84*E84,"")</f>
         <v/>
       </c>
@@ -23639,7 +24971,7 @@
         <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
         <v/>
       </c>
-      <c r="H85" s="35">
+      <c r="H85" s="34">
         <f>IF(A85&lt;=$B$9,D85*E85,"")</f>
         <v/>
       </c>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -43,7 +43,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
@@ -54,7 +54,6 @@
     <numFmt numFmtId="171" formatCode="0.0000000000"/>
     <numFmt numFmtId="172" formatCode="0.00000"/>
     <numFmt numFmtId="173" formatCode="mm/dd/yy"/>
-    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -215,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -338,6 +337,10 @@
     <xf numFmtId="2" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="11" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12033,7 +12036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -12261,6 +12264,23 @@
       <c r="C18" s="65" t="inlineStr">
         <is>
           <t>Continuously-compounded intensity, used at every tenor when B17 = Flat hazard rate. Credit-triangle guide: s/(1-R).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>Reference entity ticker</t>
+        </is>
+      </c>
+      <c r="B19" s="68" t="inlineStr">
+        <is>
+          <t>HSBA LN Equity</t>
+        </is>
+      </c>
+      <c r="C19" s="65" t="inlineStr">
+        <is>
+          <t>Drives the CDS_SPREAD_TICKER_nY lookups on CDS_Quotes. Any Bloomberg identifier whose CDS curve you want (equity ticker, or the entity itself).</t>
         </is>
       </c>
     </row>
@@ -12288,7 +12308,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -12308,9 +12328,9 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Single-name CDS par spreads — one entity, one seniority/clause. Live BDP overrides the manual demo values.</t>
+      <c r="A2" s="65" t="inlineStr">
+        <is>
+          <t>Single-name CDS par spreads. Step 1 (col D) resolves each tenor's CDS ticker from the entity ticker in CDS_Parameters!B19; step 2 (col F) quotes it. Manual spreads in col E are used only when BDP fails.</t>
         </is>
       </c>
     </row>
@@ -12338,9 +12358,9 @@
           <t>Maturity</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>CDS ticker</t>
+      <c r="D6" s="92" t="inlineStr">
+        <is>
+          <t>CDS ticker (step 1, live)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -12356,6 +12376,11 @@
       <c r="G6" s="20" t="inlineStr">
         <is>
           <t>Approx hazard s/(1-R)</t>
+        </is>
+      </c>
+      <c r="H6" s="62" t="inlineStr">
+        <is>
+          <t>Quote source in use</t>
         </is>
       </c>
     </row>
@@ -12372,18 +12397,25 @@
         <f>EDATE('Curve_Interface'!$F$7,3*(4-1))</f>
         <v/>
       </c>
-      <c r="D7" s="37" t="inlineStr"/>
+      <c r="D7" s="87">
+        <f>IFERROR(BDP(CDS_Parameters!$B$19,"CDS_SPREAD_TICKER_1Y"),"")</f>
+        <v/>
+      </c>
       <c r="E7" s="55" t="n">
         <v>40</v>
       </c>
-      <c r="F7" s="31">
-        <f>IF(D7="",E7,IFERROR(BDP(D7,"PX_LAST"),E7))</f>
+      <c r="F7" s="63">
+        <f>IFERROR(BDP(D7&amp;" BEST Curncy","PX_MID")+0,IFERROR(BDP(D7,"PX_LAST")+0,E7))</f>
         <v/>
       </c>
       <c r="G7" s="52">
         <f>(F7/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
       </c>
+      <c r="H7" s="93">
+        <f>IF(ISNUMBER(IFERROR(BDP(D7&amp;" BEST Curncy","PX_MID")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -12398,18 +12430,25 @@
         <f>EDATE('Curve_Interface'!$F$7,3*(8-1))</f>
         <v/>
       </c>
-      <c r="D8" s="37" t="inlineStr"/>
+      <c r="D8" s="87">
+        <f>IFERROR(BDP(CDS_Parameters!$B$19,"CDS_SPREAD_TICKER_2Y"),"")</f>
+        <v/>
+      </c>
       <c r="E8" s="55" t="n">
         <v>55</v>
       </c>
-      <c r="F8" s="31">
-        <f>IF(D8="",E8,IFERROR(BDP(D8,"PX_LAST"),E8))</f>
+      <c r="F8" s="63">
+        <f>IFERROR(BDP(D8&amp;" BEST Curncy","PX_MID")+0,IFERROR(BDP(D8,"PX_LAST")+0,E8))</f>
         <v/>
       </c>
       <c r="G8" s="52">
         <f>(F8/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
       </c>
+      <c r="H8" s="93">
+        <f>IF(ISNUMBER(IFERROR(BDP(D8&amp;" BEST Curncy","PX_MID")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -12424,18 +12463,25 @@
         <f>EDATE('Curve_Interface'!$F$7,3*(12-1))</f>
         <v/>
       </c>
-      <c r="D9" s="37" t="inlineStr"/>
+      <c r="D9" s="87">
+        <f>IFERROR(BDP(CDS_Parameters!$B$19,"CDS_SPREAD_TICKER_3Y"),"")</f>
+        <v/>
+      </c>
       <c r="E9" s="55" t="n">
         <v>70</v>
       </c>
-      <c r="F9" s="31">
-        <f>IF(D9="",E9,IFERROR(BDP(D9,"PX_LAST"),E9))</f>
+      <c r="F9" s="63">
+        <f>IFERROR(BDP(D9&amp;" BEST Curncy","PX_MID")+0,IFERROR(BDP(D9,"PX_LAST")+0,E9))</f>
         <v/>
       </c>
       <c r="G9" s="52">
         <f>(F9/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
       </c>
+      <c r="H9" s="93">
+        <f>IF(ISNUMBER(IFERROR(BDP(D9&amp;" BEST Curncy","PX_MID")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -12450,18 +12496,25 @@
         <f>EDATE('Curve_Interface'!$F$7,3*(20-1))</f>
         <v/>
       </c>
-      <c r="D10" s="37" t="inlineStr"/>
+      <c r="D10" s="87">
+        <f>IFERROR(BDP(CDS_Parameters!$B$19,"CDS_SPREAD_TICKER_5Y"),"")</f>
+        <v/>
+      </c>
       <c r="E10" s="55" t="n">
         <v>95</v>
       </c>
-      <c r="F10" s="31">
-        <f>IF(D10="",E10,IFERROR(BDP(D10,"PX_LAST"),E10))</f>
+      <c r="F10" s="63">
+        <f>IFERROR(BDP(D10&amp;" BEST Curncy","PX_MID")+0,IFERROR(BDP(D10,"PX_LAST")+0,E10))</f>
         <v/>
       </c>
       <c r="G10" s="52">
         <f>(F10/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
       </c>
+      <c r="H10" s="93">
+        <f>IF(ISNUMBER(IFERROR(BDP(D10&amp;" BEST Curncy","PX_MID")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -12476,18 +12529,25 @@
         <f>EDATE('Curve_Interface'!$F$7,3*(28-1))</f>
         <v/>
       </c>
-      <c r="D11" s="37" t="inlineStr"/>
+      <c r="D11" s="87">
+        <f>IFERROR(BDP(CDS_Parameters!$B$19,"CDS_SPREAD_TICKER_7Y"),"")</f>
+        <v/>
+      </c>
       <c r="E11" s="55" t="n">
         <v>115</v>
       </c>
-      <c r="F11" s="31">
-        <f>IF(D11="",E11,IFERROR(BDP(D11,"PX_LAST"),E11))</f>
+      <c r="F11" s="63">
+        <f>IFERROR(BDP(D11&amp;" BEST Curncy","PX_MID")+0,IFERROR(BDP(D11,"PX_LAST")+0,E11))</f>
         <v/>
       </c>
       <c r="G11" s="52">
         <f>(F11/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
       </c>
+      <c r="H11" s="93">
+        <f>IF(ISNUMBER(IFERROR(BDP(D11&amp;" BEST Curncy","PX_MID")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12502,17 +12562,31 @@
         <f>EDATE('Curve_Interface'!$F$7,3*(40-1))</f>
         <v/>
       </c>
-      <c r="D12" s="37" t="inlineStr"/>
+      <c r="D12" s="87">
+        <f>IFERROR(BDP(CDS_Parameters!$B$19,"CDS_SPREAD_TICKER_10Y"),"")</f>
+        <v/>
+      </c>
       <c r="E12" s="55" t="n">
         <v>135</v>
       </c>
-      <c r="F12" s="31">
-        <f>IF(D12="",E12,IFERROR(BDP(D12,"PX_LAST"),E12))</f>
+      <c r="F12" s="63">
+        <f>IFERROR(BDP(D12&amp;" BEST Curncy","PX_MID")+0,IFERROR(BDP(D12,"PX_LAST")+0,E12))</f>
         <v/>
       </c>
       <c r="G12" s="52">
         <f>(F12/10000)/(1-CDS_Parameters!$B$8)</f>
         <v/>
+      </c>
+      <c r="H12" s="93">
+        <f>IF(ISNUMBER(IFERROR(BDP(D12&amp;" BEST Curncy","PX_MID")+0,"")),"BDP live","MANUAL (demo)")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="66" t="inlineStr">
+        <is>
+          <t>WARNING: the manual spreads in column E (40/55/70/95/115/135) are DEMO PLACEHOLDERS, not market data — unlike the SOFR OIS quotes, which are the real 07/21/26 S490 levels. Column H tells you which source each tenor is actually using. Replace column E, or connect a terminal, before trusting any CDS output.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -36460,7 +36534,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -13,20 +13,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_Futures" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SOFR_OIS_Quotes" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Solver" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap_Lehman" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Solver" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S490_Target" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Solver" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap_Lehman" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Solver" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -42,7 +43,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
@@ -51,6 +52,9 @@
     <numFmt numFmtId="169" formatCode="0.0000%"/>
     <numFmt numFmtId="170" formatCode="0.000"/>
     <numFmt numFmtId="171" formatCode="0.0000000000"/>
+    <numFmt numFmtId="172" formatCode="0.00000"/>
+    <numFmt numFmtId="173" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="174" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -211,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -326,6 +330,14 @@
     <xf numFmtId="171" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="17" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="11" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1830,6 +1842,2713 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="2" customWidth="1" min="9" max="9"/>
+    <col width="1" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Swap_Pricer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Dynamic Fixed-vs-SOFR OIS valuation (SWPM-style), priced off the Bootstrap curve — every cell is live</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>DEAL — Fixed vs SOFR OIS   (yellow = inputs; everything else is computed)</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>Discount curve (from Bootstrap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Direction (Leg 1 = Fixed)</t>
+        </is>
+      </c>
+      <c r="B5" s="37" t="inlineStr">
+        <is>
+          <t>Receive fixed</t>
+        </is>
+      </c>
+      <c r="C5" s="38" t="inlineStr">
+        <is>
+          <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
+        </is>
+      </c>
+      <c r="K5" s="13" t="inlineStr">
+        <is>
+          <t>Curve date</t>
+        </is>
+      </c>
+      <c r="L5" s="13" t="inlineStr">
+        <is>
+          <t>DF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Notional</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="C6" s="38" t="inlineStr">
+        <is>
+          <t>Both legs, USD.</t>
+        </is>
+      </c>
+      <c r="K6" s="18">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="L6" s="36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="K7" s="18">
+        <f>Bootstrap!B8</f>
+        <v/>
+      </c>
+      <c r="L7" s="36">
+        <f>Bootstrap!H8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Effective date</t>
+        </is>
+      </c>
+      <c r="B8" s="40">
+        <f>Bootstrap!$B$4</f>
+        <v/>
+      </c>
+      <c r="C8" s="38" t="inlineStr">
+        <is>
+          <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
+        </is>
+      </c>
+      <c r="K8" s="18">
+        <f>Bootstrap!B9</f>
+        <v/>
+      </c>
+      <c r="L8" s="36">
+        <f>Bootstrap!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Tenor (years)</t>
+        </is>
+      </c>
+      <c r="B9" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="38" t="inlineStr">
+        <is>
+          <t>Whole years; drives the annual coupon schedule below.</t>
+        </is>
+      </c>
+      <c r="K9" s="18">
+        <f>Bootstrap!B10</f>
+        <v/>
+      </c>
+      <c r="L9" s="36">
+        <f>Bootstrap!H10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Maturity date</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>EDATE(B8,12*B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="38" t="inlineStr">
+        <is>
+          <t>Effective + Tenor.</t>
+        </is>
+      </c>
+      <c r="K10" s="18">
+        <f>Bootstrap!B11</f>
+        <v/>
+      </c>
+      <c r="L10" s="36">
+        <f>Bootstrap!H11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Fixed coupon (%)</t>
+        </is>
+      </c>
+      <c r="B11" s="42">
+        <f>B25</f>
+        <v/>
+      </c>
+      <c r="C11" s="38" t="inlineStr">
+        <is>
+          <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
+        </is>
+      </c>
+      <c r="K11" s="18">
+        <f>Bootstrap!B12</f>
+        <v/>
+      </c>
+      <c r="L11" s="36">
+        <f>Bootstrap!H12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Fixed pay frequency</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+      <c r="K12" s="18">
+        <f>Bootstrap!B13</f>
+        <v/>
+      </c>
+      <c r="L12" s="36">
+        <f>Bootstrap!H13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Fixed day count</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>ACT/360</t>
+        </is>
+      </c>
+      <c r="K13" s="18">
+        <f>Bootstrap!B14</f>
+        <v/>
+      </c>
+      <c r="L13" s="36">
+        <f>Bootstrap!H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Float index</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>SOFR (daily compounded, single-curve)</t>
+        </is>
+      </c>
+      <c r="K14" s="18">
+        <f>Bootstrap!B15</f>
+        <v/>
+      </c>
+      <c r="L14" s="36">
+        <f>Bootstrap!H15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Curve / valuation date</t>
+        </is>
+      </c>
+      <c r="B15" s="18">
+        <f>VAL_DATE</f>
+        <v/>
+      </c>
+      <c r="C15" s="38" t="inlineStr">
+        <is>
+          <t>Curve is discounted from spot = Bootstrap!B4.</t>
+        </is>
+      </c>
+      <c r="K15" s="18">
+        <f>Bootstrap!B16</f>
+        <v/>
+      </c>
+      <c r="L15" s="36">
+        <f>Bootstrap!H16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Direction sign (+recv / −pay)</t>
+        </is>
+      </c>
+      <c r="B16" s="43">
+        <f>IF($B$5="Receive fixed",1,-1)</f>
+        <v/>
+      </c>
+      <c r="K16" s="18">
+        <f>Bootstrap!B17</f>
+        <v/>
+      </c>
+      <c r="L16" s="36">
+        <f>Bootstrap!H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="K17" s="18">
+        <f>Bootstrap!B18</f>
+        <v/>
+      </c>
+      <c r="L17" s="36">
+        <f>Bootstrap!H18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>VALUATION RESULTS — single-curve OIS discounting</t>
+        </is>
+      </c>
+      <c r="K18" s="18">
+        <f>Bootstrap!B19</f>
+        <v/>
+      </c>
+      <c r="L18" s="36">
+        <f>Bootstrap!H19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>DF(effective)</t>
+        </is>
+      </c>
+      <c r="B19" s="36">
+        <f>IFERROR(INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)))^(($B$8-INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)))</f>
+        <v/>
+      </c>
+      <c r="C19" s="38" t="inlineStr">
+        <is>
+          <t>Interpolated from the curve.</t>
+        </is>
+      </c>
+      <c r="K19" s="18">
+        <f>Bootstrap!B20</f>
+        <v/>
+      </c>
+      <c r="L19" s="36">
+        <f>Bootstrap!H20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>DF(maturity)</t>
+        </is>
+      </c>
+      <c r="B20" s="36">
+        <f>IFERROR(INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)))^(($B$10-INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)))</f>
+        <v/>
+      </c>
+      <c r="K20" s="18">
+        <f>Bootstrap!B21</f>
+        <v/>
+      </c>
+      <c r="L20" s="36">
+        <f>Bootstrap!H21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Fixed annuity  Sum tau·DF</t>
+        </is>
+      </c>
+      <c r="B21" s="34">
+        <f>SUM(H36:H85)</f>
+        <v/>
+      </c>
+      <c r="C21" s="38" t="inlineStr">
+        <is>
+          <t>Sum of tau·DF over the fixed coupon dates.</t>
+        </is>
+      </c>
+      <c r="K21" s="18">
+        <f>Bootstrap!B22</f>
+        <v/>
+      </c>
+      <c r="L21" s="36">
+        <f>Bootstrap!H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Fixed leg PV (coupons)</t>
+        </is>
+      </c>
+      <c r="B22" s="44">
+        <f>SUM(G36:G85)</f>
+        <v/>
+      </c>
+      <c r="K22" s="18">
+        <f>Bootstrap!B23</f>
+        <v/>
+      </c>
+      <c r="L22" s="36">
+        <f>Bootstrap!H23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Float leg PV</t>
+        </is>
+      </c>
+      <c r="B23" s="44">
+        <f>B6*(B19-B20)</f>
+        <v/>
+      </c>
+      <c r="C23" s="38" t="inlineStr">
+        <is>
+          <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
+        </is>
+      </c>
+      <c r="K23" s="18">
+        <f>Bootstrap!B24</f>
+        <v/>
+      </c>
+      <c r="L23" s="36">
+        <f>Bootstrap!H24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Notional PV @ maturity</t>
+        </is>
+      </c>
+      <c r="B24" s="44">
+        <f>B6*B20</f>
+        <v/>
+      </c>
+      <c r="C24" s="38" t="inlineStr">
+        <is>
+          <t>For the SWPM-style leg display only.</t>
+        </is>
+      </c>
+      <c r="K24" s="18">
+        <f>Bootstrap!B25</f>
+        <v/>
+      </c>
+      <c r="L24" s="36">
+        <f>Bootstrap!H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Par coupon (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="34">
+        <f>(B19-B20)/B21*100</f>
+        <v/>
+      </c>
+      <c r="C25" s="38" t="inlineStr">
+        <is>
+          <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
+        </is>
+      </c>
+      <c r="K25" s="18">
+        <f>Bootstrap!B26</f>
+        <v/>
+      </c>
+      <c r="L25" s="36">
+        <f>Bootstrap!H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Leg 1 NPV  (fixed + notional)</t>
+        </is>
+      </c>
+      <c r="B26" s="44">
+        <f>B16*(B22+B24)</f>
+        <v/>
+      </c>
+      <c r="C26" s="38" t="inlineStr">
+        <is>
+          <t>SWPM shows each leg incl. a notional redemption.</t>
+        </is>
+      </c>
+      <c r="K26" s="18">
+        <f>Bootstrap!B27</f>
+        <v/>
+      </c>
+      <c r="L26" s="36">
+        <f>Bootstrap!H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Leg 2 NPV  (float + notional)</t>
+        </is>
+      </c>
+      <c r="B27" s="44">
+        <f>-B16*(B23+B24)</f>
+        <v/>
+      </c>
+      <c r="K27" s="18">
+        <f>Bootstrap!B28</f>
+        <v/>
+      </c>
+      <c r="L27" s="36">
+        <f>Bootstrap!H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net swap NPV</t>
+        </is>
+      </c>
+      <c r="B28" s="45">
+        <f>B26+B27</f>
+        <v/>
+      </c>
+      <c r="C28" s="38" t="inlineStr">
+        <is>
+          <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
+        </is>
+      </c>
+      <c r="K28" s="18">
+        <f>Bootstrap!B29</f>
+        <v/>
+      </c>
+      <c r="L28" s="36">
+        <f>Bootstrap!H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>PV01 / DV01  (per 1bp)</t>
+        </is>
+      </c>
+      <c r="B29" s="44">
+        <f>B6*B21*0.0001</f>
+        <v/>
+      </c>
+      <c r="C29" s="38" t="inlineStr">
+        <is>
+          <t>Annuity × notional × 1bp.</t>
+        </is>
+      </c>
+      <c r="K29" s="18">
+        <f>Bootstrap!B30</f>
+        <v/>
+      </c>
+      <c r="L29" s="36">
+        <f>Bootstrap!H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Accrued (at inception)</t>
+        </is>
+      </c>
+      <c r="B30" s="44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="18">
+        <f>Bootstrap!B31</f>
+        <v/>
+      </c>
+      <c r="L30" s="36">
+        <f>Bootstrap!H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="K31" s="18">
+        <f>Bootstrap!B32</f>
+        <v/>
+      </c>
+      <c r="L31" s="36">
+        <f>Bootstrap!H32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="44" customHeight="1">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Cross-check vs the SWPM screen: Par coupon and PV01 match (≈4.02%, ≈974 for a 10mm 1Y). SWPM's leg NPVs read ~9,995,534 rather than 10,000,000 because it discounts from curve date to a valuation date 2 business days after effective; here effective = spot so DF(effective) = 1 exactly. The net NPV, par coupon and DV01 are unaffected.</t>
+        </is>
+      </c>
+      <c r="K32" s="18">
+        <f>Bootstrap!B33</f>
+        <v/>
+      </c>
+      <c r="L32" s="36">
+        <f>Bootstrap!H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="K33" s="18">
+        <f>Bootstrap!B34</f>
+        <v/>
+      </c>
+      <c r="L33" s="36">
+        <f>Bootstrap!H34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="K34" s="18">
+        <f>Bootstrap!B35</f>
+        <v/>
+      </c>
+      <c r="L34" s="36">
+        <f>Bootstrap!H35</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="20" t="inlineStr">
+        <is>
+          <t>k</t>
+        </is>
+      </c>
+      <c r="B35" s="20" t="inlineStr">
+        <is>
+          <t>Pay date</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Prev date</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>tau ACT/360</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="inlineStr">
+        <is>
+          <t>DF (interp)</t>
+        </is>
+      </c>
+      <c r="F35" s="20" t="inlineStr">
+        <is>
+          <t>Coupon CF</t>
+        </is>
+      </c>
+      <c r="G35" s="20" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="H35" s="20" t="inlineStr">
+        <is>
+          <t>tau·DF</t>
+        </is>
+      </c>
+      <c r="K35" s="18">
+        <f>Bootstrap!B36</f>
+        <v/>
+      </c>
+      <c r="L35" s="36">
+        <f>Bootstrap!H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B36" s="18">
+        <f>IF(A36&lt;=$B$9,EDATE($B$8,12*A36),"")</f>
+        <v/>
+      </c>
+      <c r="C36" s="18">
+        <f>IF(A36&lt;=$B$9,$B$8,"")</f>
+        <v/>
+      </c>
+      <c r="D36" s="17">
+        <f>IF(A36&lt;=$B$9,(B36-C36)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E36" s="36">
+        <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1)))^((B36-INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="44">
+        <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="44">
+        <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
+        <v/>
+      </c>
+      <c r="H36" s="34">
+        <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
+        <v/>
+      </c>
+      <c r="K36" s="18">
+        <f>Bootstrap!B37</f>
+        <v/>
+      </c>
+      <c r="L36" s="36">
+        <f>Bootstrap!H37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B37" s="18">
+        <f>IF(A37&lt;=$B$9,EDATE($B$8,12*A37),"")</f>
+        <v/>
+      </c>
+      <c r="C37" s="18">
+        <f>IF(A37&lt;=$B$9,B36,"")</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>IF(A37&lt;=$B$9,(B37-C37)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E37" s="36">
+        <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1)))^((B37-INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="44">
+        <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="44">
+        <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="34">
+        <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
+        <v/>
+      </c>
+      <c r="K37" s="18">
+        <f>Bootstrap!B38</f>
+        <v/>
+      </c>
+      <c r="L37" s="36">
+        <f>Bootstrap!H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B38" s="18">
+        <f>IF(A38&lt;=$B$9,EDATE($B$8,12*A38),"")</f>
+        <v/>
+      </c>
+      <c r="C38" s="18">
+        <f>IF(A38&lt;=$B$9,B37,"")</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>IF(A38&lt;=$B$9,(B38-C38)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E38" s="36">
+        <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1)))^((B38-INDEX($K$6:$K$71,MATCH(B38,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B38,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B38,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="44">
+        <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="44">
+        <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
+        <v/>
+      </c>
+      <c r="H38" s="34">
+        <f>IF(A38&lt;=$B$9,D38*E38,"")</f>
+        <v/>
+      </c>
+      <c r="K38" s="18">
+        <f>Bootstrap!B39</f>
+        <v/>
+      </c>
+      <c r="L38" s="36">
+        <f>Bootstrap!H39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B39" s="18">
+        <f>IF(A39&lt;=$B$9,EDATE($B$8,12*A39),"")</f>
+        <v/>
+      </c>
+      <c r="C39" s="18">
+        <f>IF(A39&lt;=$B$9,B38,"")</f>
+        <v/>
+      </c>
+      <c r="D39" s="17">
+        <f>IF(A39&lt;=$B$9,(B39-C39)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E39" s="36">
+        <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1)))^((B39-INDEX($K$6:$K$71,MATCH(B39,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B39,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B39,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="44">
+        <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="44">
+        <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="34">
+        <f>IF(A39&lt;=$B$9,D39*E39,"")</f>
+        <v/>
+      </c>
+      <c r="K39" s="46" t="inlineStr">
+        <is>
+          <t>Log-linear DF interpolation on this grid (dates $K$6:$K$71, DFs $L$6:$L$71).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B40" s="18">
+        <f>IF(A40&lt;=$B$9,EDATE($B$8,12*A40),"")</f>
+        <v/>
+      </c>
+      <c r="C40" s="18">
+        <f>IF(A40&lt;=$B$9,B39,"")</f>
+        <v/>
+      </c>
+      <c r="D40" s="17">
+        <f>IF(A40&lt;=$B$9,(B40-C40)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E40" s="36">
+        <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1)))^((B40-INDEX($K$6:$K$71,MATCH(B40,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B40,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B40,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="44">
+        <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="44">
+        <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
+        <v/>
+      </c>
+      <c r="H40" s="34">
+        <f>IF(A40&lt;=$B$9,D40*E40,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B41" s="18">
+        <f>IF(A41&lt;=$B$9,EDATE($B$8,12*A41),"")</f>
+        <v/>
+      </c>
+      <c r="C41" s="18">
+        <f>IF(A41&lt;=$B$9,B40,"")</f>
+        <v/>
+      </c>
+      <c r="D41" s="17">
+        <f>IF(A41&lt;=$B$9,(B41-C41)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E41" s="36">
+        <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1)))^((B41-INDEX($K$6:$K$71,MATCH(B41,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B41,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B41,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="44">
+        <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
+        <v/>
+      </c>
+      <c r="G41" s="44">
+        <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="34">
+        <f>IF(A41&lt;=$B$9,D41*E41,"")</f>
+        <v/>
+      </c>
+      <c r="K41" s="47">
+        <f>Bootstrap!B42</f>
+        <v/>
+      </c>
+      <c r="L41" s="27">
+        <f>Bootstrap!H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B42" s="18">
+        <f>IF(A42&lt;=$B$9,EDATE($B$8,12*A42),"")</f>
+        <v/>
+      </c>
+      <c r="C42" s="18">
+        <f>IF(A42&lt;=$B$9,B41,"")</f>
+        <v/>
+      </c>
+      <c r="D42" s="17">
+        <f>IF(A42&lt;=$B$9,(B42-C42)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E42" s="36">
+        <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1)))^((B42-INDEX($K$6:$K$71,MATCH(B42,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B42,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B42,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="44">
+        <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
+        <v/>
+      </c>
+      <c r="G42" s="44">
+        <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
+        <v/>
+      </c>
+      <c r="H42" s="34">
+        <f>IF(A42&lt;=$B$9,D42*E42,"")</f>
+        <v/>
+      </c>
+      <c r="K42" s="47">
+        <f>Bootstrap!B43</f>
+        <v/>
+      </c>
+      <c r="L42" s="27">
+        <f>Bootstrap!H43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B43" s="18">
+        <f>IF(A43&lt;=$B$9,EDATE($B$8,12*A43),"")</f>
+        <v/>
+      </c>
+      <c r="C43" s="18">
+        <f>IF(A43&lt;=$B$9,B42,"")</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>IF(A43&lt;=$B$9,(B43-C43)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E43" s="36">
+        <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1)))^((B43-INDEX($K$6:$K$71,MATCH(B43,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B43,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B43,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="44">
+        <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
+        <v/>
+      </c>
+      <c r="G43" s="44">
+        <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="34">
+        <f>IF(A43&lt;=$B$9,D43*E43,"")</f>
+        <v/>
+      </c>
+      <c r="K43" s="47">
+        <f>Bootstrap!B44</f>
+        <v/>
+      </c>
+      <c r="L43" s="27">
+        <f>Bootstrap!H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B44" s="18">
+        <f>IF(A44&lt;=$B$9,EDATE($B$8,12*A44),"")</f>
+        <v/>
+      </c>
+      <c r="C44" s="18">
+        <f>IF(A44&lt;=$B$9,B43,"")</f>
+        <v/>
+      </c>
+      <c r="D44" s="17">
+        <f>IF(A44&lt;=$B$9,(B44-C44)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E44" s="36">
+        <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1)))^((B44-INDEX($K$6:$K$71,MATCH(B44,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B44,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B44,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="44">
+        <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
+        <v/>
+      </c>
+      <c r="G44" s="44">
+        <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
+        <v/>
+      </c>
+      <c r="H44" s="34">
+        <f>IF(A44&lt;=$B$9,D44*E44,"")</f>
+        <v/>
+      </c>
+      <c r="K44" s="47">
+        <f>Bootstrap!B45</f>
+        <v/>
+      </c>
+      <c r="L44" s="27">
+        <f>Bootstrap!H45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B45" s="18">
+        <f>IF(A45&lt;=$B$9,EDATE($B$8,12*A45),"")</f>
+        <v/>
+      </c>
+      <c r="C45" s="18">
+        <f>IF(A45&lt;=$B$9,B44,"")</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>IF(A45&lt;=$B$9,(B45-C45)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E45" s="36">
+        <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1)))^((B45-INDEX($K$6:$K$71,MATCH(B45,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B45,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B45,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="44">
+        <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
+        <v/>
+      </c>
+      <c r="G45" s="44">
+        <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="34">
+        <f>IF(A45&lt;=$B$9,D45*E45,"")</f>
+        <v/>
+      </c>
+      <c r="K45" s="47">
+        <f>Bootstrap!B46</f>
+        <v/>
+      </c>
+      <c r="L45" s="27">
+        <f>Bootstrap!H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B46" s="18">
+        <f>IF(A46&lt;=$B$9,EDATE($B$8,12*A46),"")</f>
+        <v/>
+      </c>
+      <c r="C46" s="18">
+        <f>IF(A46&lt;=$B$9,B45,"")</f>
+        <v/>
+      </c>
+      <c r="D46" s="17">
+        <f>IF(A46&lt;=$B$9,(B46-C46)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E46" s="36">
+        <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1)))^((B46-INDEX($K$6:$K$71,MATCH(B46,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B46,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B46,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="44">
+        <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
+        <v/>
+      </c>
+      <c r="G46" s="44">
+        <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
+        <v/>
+      </c>
+      <c r="H46" s="34">
+        <f>IF(A46&lt;=$B$9,D46*E46,"")</f>
+        <v/>
+      </c>
+      <c r="K46" s="47">
+        <f>Bootstrap!B47</f>
+        <v/>
+      </c>
+      <c r="L46" s="27">
+        <f>Bootstrap!H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B47" s="18">
+        <f>IF(A47&lt;=$B$9,EDATE($B$8,12*A47),"")</f>
+        <v/>
+      </c>
+      <c r="C47" s="18">
+        <f>IF(A47&lt;=$B$9,B46,"")</f>
+        <v/>
+      </c>
+      <c r="D47" s="17">
+        <f>IF(A47&lt;=$B$9,(B47-C47)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E47" s="36">
+        <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1)))^((B47-INDEX($K$6:$K$71,MATCH(B47,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B47,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B47,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="44">
+        <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
+        <v/>
+      </c>
+      <c r="G47" s="44">
+        <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="34">
+        <f>IF(A47&lt;=$B$9,D47*E47,"")</f>
+        <v/>
+      </c>
+      <c r="K47" s="47">
+        <f>Bootstrap!B48</f>
+        <v/>
+      </c>
+      <c r="L47" s="27">
+        <f>Bootstrap!H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B48" s="18">
+        <f>IF(A48&lt;=$B$9,EDATE($B$8,12*A48),"")</f>
+        <v/>
+      </c>
+      <c r="C48" s="18">
+        <f>IF(A48&lt;=$B$9,B47,"")</f>
+        <v/>
+      </c>
+      <c r="D48" s="17">
+        <f>IF(A48&lt;=$B$9,(B48-C48)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E48" s="36">
+        <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1)))^((B48-INDEX($K$6:$K$71,MATCH(B48,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B48,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B48,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="44">
+        <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
+        <v/>
+      </c>
+      <c r="G48" s="44">
+        <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="34">
+        <f>IF(A48&lt;=$B$9,D48*E48,"")</f>
+        <v/>
+      </c>
+      <c r="K48" s="47">
+        <f>Bootstrap!B49</f>
+        <v/>
+      </c>
+      <c r="L48" s="27">
+        <f>Bootstrap!H49</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B49" s="18">
+        <f>IF(A49&lt;=$B$9,EDATE($B$8,12*A49),"")</f>
+        <v/>
+      </c>
+      <c r="C49" s="18">
+        <f>IF(A49&lt;=$B$9,B48,"")</f>
+        <v/>
+      </c>
+      <c r="D49" s="17">
+        <f>IF(A49&lt;=$B$9,(B49-C49)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E49" s="36">
+        <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1)))^((B49-INDEX($K$6:$K$71,MATCH(B49,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B49,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B49,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="44">
+        <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
+        <v/>
+      </c>
+      <c r="G49" s="44">
+        <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="34">
+        <f>IF(A49&lt;=$B$9,D49*E49,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="47">
+        <f>Bootstrap!B50</f>
+        <v/>
+      </c>
+      <c r="L49" s="27">
+        <f>Bootstrap!H50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B50" s="18">
+        <f>IF(A50&lt;=$B$9,EDATE($B$8,12*A50),"")</f>
+        <v/>
+      </c>
+      <c r="C50" s="18">
+        <f>IF(A50&lt;=$B$9,B49,"")</f>
+        <v/>
+      </c>
+      <c r="D50" s="17">
+        <f>IF(A50&lt;=$B$9,(B50-C50)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E50" s="36">
+        <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1)))^((B50-INDEX($K$6:$K$71,MATCH(B50,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B50,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B50,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="44">
+        <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
+        <v/>
+      </c>
+      <c r="G50" s="44">
+        <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="34">
+        <f>IF(A50&lt;=$B$9,D50*E50,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="47">
+        <f>Bootstrap!B51</f>
+        <v/>
+      </c>
+      <c r="L50" s="27">
+        <f>Bootstrap!H51</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B51" s="18">
+        <f>IF(A51&lt;=$B$9,EDATE($B$8,12*A51),"")</f>
+        <v/>
+      </c>
+      <c r="C51" s="18">
+        <f>IF(A51&lt;=$B$9,B50,"")</f>
+        <v/>
+      </c>
+      <c r="D51" s="17">
+        <f>IF(A51&lt;=$B$9,(B51-C51)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E51" s="36">
+        <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1)))^((B51-INDEX($K$6:$K$71,MATCH(B51,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B51,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B51,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="44">
+        <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
+        <v/>
+      </c>
+      <c r="G51" s="44">
+        <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="34">
+        <f>IF(A51&lt;=$B$9,D51*E51,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="47">
+        <f>Bootstrap!B52</f>
+        <v/>
+      </c>
+      <c r="L51" s="27">
+        <f>Bootstrap!H52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B52" s="18">
+        <f>IF(A52&lt;=$B$9,EDATE($B$8,12*A52),"")</f>
+        <v/>
+      </c>
+      <c r="C52" s="18">
+        <f>IF(A52&lt;=$B$9,B51,"")</f>
+        <v/>
+      </c>
+      <c r="D52" s="17">
+        <f>IF(A52&lt;=$B$9,(B52-C52)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E52" s="36">
+        <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1)))^((B52-INDEX($K$6:$K$71,MATCH(B52,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B52,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B52,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="44">
+        <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
+        <v/>
+      </c>
+      <c r="G52" s="44">
+        <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="34">
+        <f>IF(A52&lt;=$B$9,D52*E52,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="47">
+        <f>Bootstrap!B53</f>
+        <v/>
+      </c>
+      <c r="L52" s="27">
+        <f>Bootstrap!H53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B53" s="18">
+        <f>IF(A53&lt;=$B$9,EDATE($B$8,12*A53),"")</f>
+        <v/>
+      </c>
+      <c r="C53" s="18">
+        <f>IF(A53&lt;=$B$9,B52,"")</f>
+        <v/>
+      </c>
+      <c r="D53" s="17">
+        <f>IF(A53&lt;=$B$9,(B53-C53)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E53" s="36">
+        <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1)))^((B53-INDEX($K$6:$K$71,MATCH(B53,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B53,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B53,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="44">
+        <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
+        <v/>
+      </c>
+      <c r="G53" s="44">
+        <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
+        <v/>
+      </c>
+      <c r="H53" s="34">
+        <f>IF(A53&lt;=$B$9,D53*E53,"")</f>
+        <v/>
+      </c>
+      <c r="K53" s="47">
+        <f>Bootstrap!B54</f>
+        <v/>
+      </c>
+      <c r="L53" s="27">
+        <f>Bootstrap!H54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B54" s="18">
+        <f>IF(A54&lt;=$B$9,EDATE($B$8,12*A54),"")</f>
+        <v/>
+      </c>
+      <c r="C54" s="18">
+        <f>IF(A54&lt;=$B$9,B53,"")</f>
+        <v/>
+      </c>
+      <c r="D54" s="17">
+        <f>IF(A54&lt;=$B$9,(B54-C54)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E54" s="36">
+        <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1)))^((B54-INDEX($K$6:$K$71,MATCH(B54,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B54,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B54,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="44">
+        <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
+        <v/>
+      </c>
+      <c r="G54" s="44">
+        <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
+        <v/>
+      </c>
+      <c r="H54" s="34">
+        <f>IF(A54&lt;=$B$9,D54*E54,"")</f>
+        <v/>
+      </c>
+      <c r="K54" s="47">
+        <f>Bootstrap!B55</f>
+        <v/>
+      </c>
+      <c r="L54" s="27">
+        <f>Bootstrap!H55</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B55" s="18">
+        <f>IF(A55&lt;=$B$9,EDATE($B$8,12*A55),"")</f>
+        <v/>
+      </c>
+      <c r="C55" s="18">
+        <f>IF(A55&lt;=$B$9,B54,"")</f>
+        <v/>
+      </c>
+      <c r="D55" s="17">
+        <f>IF(A55&lt;=$B$9,(B55-C55)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E55" s="36">
+        <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1)))^((B55-INDEX($K$6:$K$71,MATCH(B55,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B55,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B55,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="44">
+        <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
+        <v/>
+      </c>
+      <c r="G55" s="44">
+        <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
+        <v/>
+      </c>
+      <c r="H55" s="34">
+        <f>IF(A55&lt;=$B$9,D55*E55,"")</f>
+        <v/>
+      </c>
+      <c r="K55" s="47">
+        <f>Bootstrap!B56</f>
+        <v/>
+      </c>
+      <c r="L55" s="27">
+        <f>Bootstrap!H56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B56" s="18">
+        <f>IF(A56&lt;=$B$9,EDATE($B$8,12*A56),"")</f>
+        <v/>
+      </c>
+      <c r="C56" s="18">
+        <f>IF(A56&lt;=$B$9,B55,"")</f>
+        <v/>
+      </c>
+      <c r="D56" s="17">
+        <f>IF(A56&lt;=$B$9,(B56-C56)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E56" s="36">
+        <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1)))^((B56-INDEX($K$6:$K$71,MATCH(B56,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B56,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B56,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="44">
+        <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
+        <v/>
+      </c>
+      <c r="G56" s="44">
+        <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
+        <v/>
+      </c>
+      <c r="H56" s="34">
+        <f>IF(A56&lt;=$B$9,D56*E56,"")</f>
+        <v/>
+      </c>
+      <c r="K56" s="47">
+        <f>Bootstrap!B57</f>
+        <v/>
+      </c>
+      <c r="L56" s="27">
+        <f>Bootstrap!H57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B57" s="18">
+        <f>IF(A57&lt;=$B$9,EDATE($B$8,12*A57),"")</f>
+        <v/>
+      </c>
+      <c r="C57" s="18">
+        <f>IF(A57&lt;=$B$9,B56,"")</f>
+        <v/>
+      </c>
+      <c r="D57" s="17">
+        <f>IF(A57&lt;=$B$9,(B57-C57)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E57" s="36">
+        <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1)))^((B57-INDEX($K$6:$K$71,MATCH(B57,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B57,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B57,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="44">
+        <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
+        <v/>
+      </c>
+      <c r="G57" s="44">
+        <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="34">
+        <f>IF(A57&lt;=$B$9,D57*E57,"")</f>
+        <v/>
+      </c>
+      <c r="K57" s="47">
+        <f>Bootstrap!B58</f>
+        <v/>
+      </c>
+      <c r="L57" s="27">
+        <f>Bootstrap!H58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B58" s="18">
+        <f>IF(A58&lt;=$B$9,EDATE($B$8,12*A58),"")</f>
+        <v/>
+      </c>
+      <c r="C58" s="18">
+        <f>IF(A58&lt;=$B$9,B57,"")</f>
+        <v/>
+      </c>
+      <c r="D58" s="17">
+        <f>IF(A58&lt;=$B$9,(B58-C58)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E58" s="36">
+        <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1)))^((B58-INDEX($K$6:$K$71,MATCH(B58,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B58,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B58,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="44">
+        <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
+        <v/>
+      </c>
+      <c r="G58" s="44">
+        <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="34">
+        <f>IF(A58&lt;=$B$9,D58*E58,"")</f>
+        <v/>
+      </c>
+      <c r="K58" s="47">
+        <f>Bootstrap!B59</f>
+        <v/>
+      </c>
+      <c r="L58" s="27">
+        <f>Bootstrap!H59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B59" s="18">
+        <f>IF(A59&lt;=$B$9,EDATE($B$8,12*A59),"")</f>
+        <v/>
+      </c>
+      <c r="C59" s="18">
+        <f>IF(A59&lt;=$B$9,B58,"")</f>
+        <v/>
+      </c>
+      <c r="D59" s="17">
+        <f>IF(A59&lt;=$B$9,(B59-C59)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E59" s="36">
+        <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1)))^((B59-INDEX($K$6:$K$71,MATCH(B59,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B59,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B59,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="44">
+        <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
+        <v/>
+      </c>
+      <c r="G59" s="44">
+        <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
+        <v/>
+      </c>
+      <c r="H59" s="34">
+        <f>IF(A59&lt;=$B$9,D59*E59,"")</f>
+        <v/>
+      </c>
+      <c r="K59" s="47">
+        <f>Bootstrap!B60</f>
+        <v/>
+      </c>
+      <c r="L59" s="27">
+        <f>Bootstrap!H60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B60" s="18">
+        <f>IF(A60&lt;=$B$9,EDATE($B$8,12*A60),"")</f>
+        <v/>
+      </c>
+      <c r="C60" s="18">
+        <f>IF(A60&lt;=$B$9,B59,"")</f>
+        <v/>
+      </c>
+      <c r="D60" s="17">
+        <f>IF(A60&lt;=$B$9,(B60-C60)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E60" s="36">
+        <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1)))^((B60-INDEX($K$6:$K$71,MATCH(B60,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B60,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B60,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="44">
+        <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
+        <v/>
+      </c>
+      <c r="G60" s="44">
+        <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
+        <v/>
+      </c>
+      <c r="H60" s="34">
+        <f>IF(A60&lt;=$B$9,D60*E60,"")</f>
+        <v/>
+      </c>
+      <c r="K60" s="47">
+        <f>Bootstrap!B61</f>
+        <v/>
+      </c>
+      <c r="L60" s="27">
+        <f>Bootstrap!H61</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B61" s="18">
+        <f>IF(A61&lt;=$B$9,EDATE($B$8,12*A61),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="18">
+        <f>IF(A61&lt;=$B$9,B60,"")</f>
+        <v/>
+      </c>
+      <c r="D61" s="17">
+        <f>IF(A61&lt;=$B$9,(B61-C61)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E61" s="36">
+        <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1)))^((B61-INDEX($K$6:$K$71,MATCH(B61,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B61,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B61,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F61" s="44">
+        <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
+        <v/>
+      </c>
+      <c r="G61" s="44">
+        <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="34">
+        <f>IF(A61&lt;=$B$9,D61*E61,"")</f>
+        <v/>
+      </c>
+      <c r="K61" s="47">
+        <f>Bootstrap!B62</f>
+        <v/>
+      </c>
+      <c r="L61" s="27">
+        <f>Bootstrap!H62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B62" s="18">
+        <f>IF(A62&lt;=$B$9,EDATE($B$8,12*A62),"")</f>
+        <v/>
+      </c>
+      <c r="C62" s="18">
+        <f>IF(A62&lt;=$B$9,B61,"")</f>
+        <v/>
+      </c>
+      <c r="D62" s="17">
+        <f>IF(A62&lt;=$B$9,(B62-C62)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E62" s="36">
+        <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1)))^((B62-INDEX($K$6:$K$71,MATCH(B62,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B62,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B62,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F62" s="44">
+        <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
+        <v/>
+      </c>
+      <c r="G62" s="44">
+        <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
+        <v/>
+      </c>
+      <c r="H62" s="34">
+        <f>IF(A62&lt;=$B$9,D62*E62,"")</f>
+        <v/>
+      </c>
+      <c r="K62" s="47">
+        <f>Bootstrap!B63</f>
+        <v/>
+      </c>
+      <c r="L62" s="27">
+        <f>Bootstrap!H63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B63" s="18">
+        <f>IF(A63&lt;=$B$9,EDATE($B$8,12*A63),"")</f>
+        <v/>
+      </c>
+      <c r="C63" s="18">
+        <f>IF(A63&lt;=$B$9,B62,"")</f>
+        <v/>
+      </c>
+      <c r="D63" s="17">
+        <f>IF(A63&lt;=$B$9,(B63-C63)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E63" s="36">
+        <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1)))^((B63-INDEX($K$6:$K$71,MATCH(B63,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B63,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B63,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F63" s="44">
+        <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
+        <v/>
+      </c>
+      <c r="G63" s="44">
+        <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="34">
+        <f>IF(A63&lt;=$B$9,D63*E63,"")</f>
+        <v/>
+      </c>
+      <c r="K63" s="47">
+        <f>Bootstrap!B64</f>
+        <v/>
+      </c>
+      <c r="L63" s="27">
+        <f>Bootstrap!H64</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B64" s="18">
+        <f>IF(A64&lt;=$B$9,EDATE($B$8,12*A64),"")</f>
+        <v/>
+      </c>
+      <c r="C64" s="18">
+        <f>IF(A64&lt;=$B$9,B63,"")</f>
+        <v/>
+      </c>
+      <c r="D64" s="17">
+        <f>IF(A64&lt;=$B$9,(B64-C64)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E64" s="36">
+        <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1)))^((B64-INDEX($K$6:$K$71,MATCH(B64,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B64,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B64,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F64" s="44">
+        <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
+        <v/>
+      </c>
+      <c r="G64" s="44">
+        <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="34">
+        <f>IF(A64&lt;=$B$9,D64*E64,"")</f>
+        <v/>
+      </c>
+      <c r="K64" s="47">
+        <f>Bootstrap!B65</f>
+        <v/>
+      </c>
+      <c r="L64" s="27">
+        <f>Bootstrap!H65</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B65" s="18">
+        <f>IF(A65&lt;=$B$9,EDATE($B$8,12*A65),"")</f>
+        <v/>
+      </c>
+      <c r="C65" s="18">
+        <f>IF(A65&lt;=$B$9,B64,"")</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>IF(A65&lt;=$B$9,(B65-C65)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E65" s="36">
+        <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1)))^((B65-INDEX($K$6:$K$71,MATCH(B65,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B65,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B65,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F65" s="44">
+        <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
+        <v/>
+      </c>
+      <c r="G65" s="44">
+        <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
+        <v/>
+      </c>
+      <c r="H65" s="34">
+        <f>IF(A65&lt;=$B$9,D65*E65,"")</f>
+        <v/>
+      </c>
+      <c r="K65" s="47">
+        <f>Bootstrap!B66</f>
+        <v/>
+      </c>
+      <c r="L65" s="27">
+        <f>Bootstrap!H66</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B66" s="18">
+        <f>IF(A66&lt;=$B$9,EDATE($B$8,12*A66),"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="18">
+        <f>IF(A66&lt;=$B$9,B65,"")</f>
+        <v/>
+      </c>
+      <c r="D66" s="17">
+        <f>IF(A66&lt;=$B$9,(B66-C66)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E66" s="36">
+        <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1)))^((B66-INDEX($K$6:$K$71,MATCH(B66,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B66,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B66,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F66" s="44">
+        <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
+        <v/>
+      </c>
+      <c r="G66" s="44">
+        <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="34">
+        <f>IF(A66&lt;=$B$9,D66*E66,"")</f>
+        <v/>
+      </c>
+      <c r="K66" s="47">
+        <f>Bootstrap!B67</f>
+        <v/>
+      </c>
+      <c r="L66" s="27">
+        <f>Bootstrap!H67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B67" s="18">
+        <f>IF(A67&lt;=$B$9,EDATE($B$8,12*A67),"")</f>
+        <v/>
+      </c>
+      <c r="C67" s="18">
+        <f>IF(A67&lt;=$B$9,B66,"")</f>
+        <v/>
+      </c>
+      <c r="D67" s="17">
+        <f>IF(A67&lt;=$B$9,(B67-C67)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E67" s="36">
+        <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1)))^((B67-INDEX($K$6:$K$71,MATCH(B67,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B67,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B67,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F67" s="44">
+        <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
+        <v/>
+      </c>
+      <c r="G67" s="44">
+        <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
+        <v/>
+      </c>
+      <c r="H67" s="34">
+        <f>IF(A67&lt;=$B$9,D67*E67,"")</f>
+        <v/>
+      </c>
+      <c r="K67" s="47">
+        <f>Bootstrap!B68</f>
+        <v/>
+      </c>
+      <c r="L67" s="27">
+        <f>Bootstrap!H68</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B68" s="18">
+        <f>IF(A68&lt;=$B$9,EDATE($B$8,12*A68),"")</f>
+        <v/>
+      </c>
+      <c r="C68" s="18">
+        <f>IF(A68&lt;=$B$9,B67,"")</f>
+        <v/>
+      </c>
+      <c r="D68" s="17">
+        <f>IF(A68&lt;=$B$9,(B68-C68)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E68" s="36">
+        <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1)))^((B68-INDEX($K$6:$K$71,MATCH(B68,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B68,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B68,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F68" s="44">
+        <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
+        <v/>
+      </c>
+      <c r="G68" s="44">
+        <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="34">
+        <f>IF(A68&lt;=$B$9,D68*E68,"")</f>
+        <v/>
+      </c>
+      <c r="K68" s="47">
+        <f>Bootstrap!B69</f>
+        <v/>
+      </c>
+      <c r="L68" s="27">
+        <f>Bootstrap!H69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B69" s="18">
+        <f>IF(A69&lt;=$B$9,EDATE($B$8,12*A69),"")</f>
+        <v/>
+      </c>
+      <c r="C69" s="18">
+        <f>IF(A69&lt;=$B$9,B68,"")</f>
+        <v/>
+      </c>
+      <c r="D69" s="17">
+        <f>IF(A69&lt;=$B$9,(B69-C69)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E69" s="36">
+        <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1)))^((B69-INDEX($K$6:$K$71,MATCH(B69,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B69,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B69,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F69" s="44">
+        <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
+        <v/>
+      </c>
+      <c r="G69" s="44">
+        <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="34">
+        <f>IF(A69&lt;=$B$9,D69*E69,"")</f>
+        <v/>
+      </c>
+      <c r="K69" s="47">
+        <f>Bootstrap!B70</f>
+        <v/>
+      </c>
+      <c r="L69" s="27">
+        <f>Bootstrap!H70</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B70" s="18">
+        <f>IF(A70&lt;=$B$9,EDATE($B$8,12*A70),"")</f>
+        <v/>
+      </c>
+      <c r="C70" s="18">
+        <f>IF(A70&lt;=$B$9,B69,"")</f>
+        <v/>
+      </c>
+      <c r="D70" s="17">
+        <f>IF(A70&lt;=$B$9,(B70-C70)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E70" s="36">
+        <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1)))^((B70-INDEX($K$6:$K$71,MATCH(B70,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B70,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B70,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F70" s="44">
+        <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
+        <v/>
+      </c>
+      <c r="G70" s="44">
+        <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="34">
+        <f>IF(A70&lt;=$B$9,D70*E70,"")</f>
+        <v/>
+      </c>
+      <c r="K70" s="47">
+        <f>Bootstrap!B71</f>
+        <v/>
+      </c>
+      <c r="L70" s="27">
+        <f>Bootstrap!H71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B71" s="18">
+        <f>IF(A71&lt;=$B$9,EDATE($B$8,12*A71),"")</f>
+        <v/>
+      </c>
+      <c r="C71" s="18">
+        <f>IF(A71&lt;=$B$9,B70,"")</f>
+        <v/>
+      </c>
+      <c r="D71" s="17">
+        <f>IF(A71&lt;=$B$9,(B71-C71)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E71" s="36">
+        <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1)))^((B71-INDEX($K$6:$K$71,MATCH(B71,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B71,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B71,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F71" s="44">
+        <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
+        <v/>
+      </c>
+      <c r="G71" s="44">
+        <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="34">
+        <f>IF(A71&lt;=$B$9,D71*E71,"")</f>
+        <v/>
+      </c>
+      <c r="K71" s="47">
+        <f>Bootstrap!B72</f>
+        <v/>
+      </c>
+      <c r="L71" s="27">
+        <f>Bootstrap!H72</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B72" s="18">
+        <f>IF(A72&lt;=$B$9,EDATE($B$8,12*A72),"")</f>
+        <v/>
+      </c>
+      <c r="C72" s="18">
+        <f>IF(A72&lt;=$B$9,B71,"")</f>
+        <v/>
+      </c>
+      <c r="D72" s="17">
+        <f>IF(A72&lt;=$B$9,(B72-C72)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E72" s="36">
+        <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1)))^((B72-INDEX($K$6:$K$71,MATCH(B72,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B72,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B72,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F72" s="44">
+        <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
+        <v/>
+      </c>
+      <c r="G72" s="44">
+        <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
+        <v/>
+      </c>
+      <c r="H72" s="34">
+        <f>IF(A72&lt;=$B$9,D72*E72,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B73" s="18">
+        <f>IF(A73&lt;=$B$9,EDATE($B$8,12*A73),"")</f>
+        <v/>
+      </c>
+      <c r="C73" s="18">
+        <f>IF(A73&lt;=$B$9,B72,"")</f>
+        <v/>
+      </c>
+      <c r="D73" s="17">
+        <f>IF(A73&lt;=$B$9,(B73-C73)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E73" s="36">
+        <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1)))^((B73-INDEX($K$6:$K$71,MATCH(B73,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B73,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B73,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F73" s="44">
+        <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
+        <v/>
+      </c>
+      <c r="G73" s="44">
+        <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
+        <v/>
+      </c>
+      <c r="H73" s="34">
+        <f>IF(A73&lt;=$B$9,D73*E73,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B74" s="18">
+        <f>IF(A74&lt;=$B$9,EDATE($B$8,12*A74),"")</f>
+        <v/>
+      </c>
+      <c r="C74" s="18">
+        <f>IF(A74&lt;=$B$9,B73,"")</f>
+        <v/>
+      </c>
+      <c r="D74" s="17">
+        <f>IF(A74&lt;=$B$9,(B74-C74)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E74" s="36">
+        <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1)))^((B74-INDEX($K$6:$K$71,MATCH(B74,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B74,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B74,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F74" s="44">
+        <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
+        <v/>
+      </c>
+      <c r="G74" s="44">
+        <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
+        <v/>
+      </c>
+      <c r="H74" s="34">
+        <f>IF(A74&lt;=$B$9,D74*E74,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B75" s="18">
+        <f>IF(A75&lt;=$B$9,EDATE($B$8,12*A75),"")</f>
+        <v/>
+      </c>
+      <c r="C75" s="18">
+        <f>IF(A75&lt;=$B$9,B74,"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="17">
+        <f>IF(A75&lt;=$B$9,(B75-C75)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E75" s="36">
+        <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1)))^((B75-INDEX($K$6:$K$71,MATCH(B75,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B75,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B75,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F75" s="44">
+        <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
+        <v/>
+      </c>
+      <c r="G75" s="44">
+        <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
+        <v/>
+      </c>
+      <c r="H75" s="34">
+        <f>IF(A75&lt;=$B$9,D75*E75,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B76" s="18">
+        <f>IF(A76&lt;=$B$9,EDATE($B$8,12*A76),"")</f>
+        <v/>
+      </c>
+      <c r="C76" s="18">
+        <f>IF(A76&lt;=$B$9,B75,"")</f>
+        <v/>
+      </c>
+      <c r="D76" s="17">
+        <f>IF(A76&lt;=$B$9,(B76-C76)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E76" s="36">
+        <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1)))^((B76-INDEX($K$6:$K$71,MATCH(B76,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B76,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B76,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F76" s="44">
+        <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
+        <v/>
+      </c>
+      <c r="G76" s="44">
+        <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
+        <v/>
+      </c>
+      <c r="H76" s="34">
+        <f>IF(A76&lt;=$B$9,D76*E76,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B77" s="18">
+        <f>IF(A77&lt;=$B$9,EDATE($B$8,12*A77),"")</f>
+        <v/>
+      </c>
+      <c r="C77" s="18">
+        <f>IF(A77&lt;=$B$9,B76,"")</f>
+        <v/>
+      </c>
+      <c r="D77" s="17">
+        <f>IF(A77&lt;=$B$9,(B77-C77)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E77" s="36">
+        <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1)))^((B77-INDEX($K$6:$K$71,MATCH(B77,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B77,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B77,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F77" s="44">
+        <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
+        <v/>
+      </c>
+      <c r="G77" s="44">
+        <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
+        <v/>
+      </c>
+      <c r="H77" s="34">
+        <f>IF(A77&lt;=$B$9,D77*E77,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B78" s="18">
+        <f>IF(A78&lt;=$B$9,EDATE($B$8,12*A78),"")</f>
+        <v/>
+      </c>
+      <c r="C78" s="18">
+        <f>IF(A78&lt;=$B$9,B77,"")</f>
+        <v/>
+      </c>
+      <c r="D78" s="17">
+        <f>IF(A78&lt;=$B$9,(B78-C78)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E78" s="36">
+        <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1)))^((B78-INDEX($K$6:$K$71,MATCH(B78,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B78,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B78,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F78" s="44">
+        <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
+        <v/>
+      </c>
+      <c r="G78" s="44">
+        <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
+        <v/>
+      </c>
+      <c r="H78" s="34">
+        <f>IF(A78&lt;=$B$9,D78*E78,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B79" s="18">
+        <f>IF(A79&lt;=$B$9,EDATE($B$8,12*A79),"")</f>
+        <v/>
+      </c>
+      <c r="C79" s="18">
+        <f>IF(A79&lt;=$B$9,B78,"")</f>
+        <v/>
+      </c>
+      <c r="D79" s="17">
+        <f>IF(A79&lt;=$B$9,(B79-C79)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E79" s="36">
+        <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1)))^((B79-INDEX($K$6:$K$71,MATCH(B79,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B79,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B79,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F79" s="44">
+        <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
+        <v/>
+      </c>
+      <c r="G79" s="44">
+        <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
+        <v/>
+      </c>
+      <c r="H79" s="34">
+        <f>IF(A79&lt;=$B$9,D79*E79,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B80" s="18">
+        <f>IF(A80&lt;=$B$9,EDATE($B$8,12*A80),"")</f>
+        <v/>
+      </c>
+      <c r="C80" s="18">
+        <f>IF(A80&lt;=$B$9,B79,"")</f>
+        <v/>
+      </c>
+      <c r="D80" s="17">
+        <f>IF(A80&lt;=$B$9,(B80-C80)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E80" s="36">
+        <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1)))^((B80-INDEX($K$6:$K$71,MATCH(B80,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B80,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B80,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F80" s="44">
+        <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
+        <v/>
+      </c>
+      <c r="G80" s="44">
+        <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
+        <v/>
+      </c>
+      <c r="H80" s="34">
+        <f>IF(A80&lt;=$B$9,D80*E80,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B81" s="18">
+        <f>IF(A81&lt;=$B$9,EDATE($B$8,12*A81),"")</f>
+        <v/>
+      </c>
+      <c r="C81" s="18">
+        <f>IF(A81&lt;=$B$9,B80,"")</f>
+        <v/>
+      </c>
+      <c r="D81" s="17">
+        <f>IF(A81&lt;=$B$9,(B81-C81)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E81" s="36">
+        <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1)))^((B81-INDEX($K$6:$K$71,MATCH(B81,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B81,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B81,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F81" s="44">
+        <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
+        <v/>
+      </c>
+      <c r="G81" s="44">
+        <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
+        <v/>
+      </c>
+      <c r="H81" s="34">
+        <f>IF(A81&lt;=$B$9,D81*E81,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B82" s="18">
+        <f>IF(A82&lt;=$B$9,EDATE($B$8,12*A82),"")</f>
+        <v/>
+      </c>
+      <c r="C82" s="18">
+        <f>IF(A82&lt;=$B$9,B81,"")</f>
+        <v/>
+      </c>
+      <c r="D82" s="17">
+        <f>IF(A82&lt;=$B$9,(B82-C82)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E82" s="36">
+        <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1)))^((B82-INDEX($K$6:$K$71,MATCH(B82,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B82,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B82,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F82" s="44">
+        <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
+        <v/>
+      </c>
+      <c r="G82" s="44">
+        <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
+        <v/>
+      </c>
+      <c r="H82" s="34">
+        <f>IF(A82&lt;=$B$9,D82*E82,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B83" s="18">
+        <f>IF(A83&lt;=$B$9,EDATE($B$8,12*A83),"")</f>
+        <v/>
+      </c>
+      <c r="C83" s="18">
+        <f>IF(A83&lt;=$B$9,B82,"")</f>
+        <v/>
+      </c>
+      <c r="D83" s="17">
+        <f>IF(A83&lt;=$B$9,(B83-C83)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E83" s="36">
+        <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1)))^((B83-INDEX($K$6:$K$71,MATCH(B83,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B83,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B83,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F83" s="44">
+        <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
+        <v/>
+      </c>
+      <c r="G83" s="44">
+        <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
+        <v/>
+      </c>
+      <c r="H83" s="34">
+        <f>IF(A83&lt;=$B$9,D83*E83,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B84" s="18">
+        <f>IF(A84&lt;=$B$9,EDATE($B$8,12*A84),"")</f>
+        <v/>
+      </c>
+      <c r="C84" s="18">
+        <f>IF(A84&lt;=$B$9,B83,"")</f>
+        <v/>
+      </c>
+      <c r="D84" s="17">
+        <f>IF(A84&lt;=$B$9,(B84-C84)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E84" s="36">
+        <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1)))^((B84-INDEX($K$6:$K$71,MATCH(B84,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B84,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B84,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F84" s="44">
+        <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
+        <v/>
+      </c>
+      <c r="G84" s="44">
+        <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
+        <v/>
+      </c>
+      <c r="H84" s="34">
+        <f>IF(A84&lt;=$B$9,D84*E84,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="43">
+        <f>ROW()-35</f>
+        <v/>
+      </c>
+      <c r="B85" s="18">
+        <f>IF(A85&lt;=$B$9,EDATE($B$8,12*A85),"")</f>
+        <v/>
+      </c>
+      <c r="C85" s="18">
+        <f>IF(A85&lt;=$B$9,B84,"")</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(A85&lt;=$B$9,(B85-C85)/360,"")</f>
+        <v/>
+      </c>
+      <c r="E85" s="36">
+        <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1)))^((B85-INDEX($K$6:$K$71,MATCH(B85,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B85,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B85,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1))),"")</f>
+        <v/>
+      </c>
+      <c r="F85" s="44">
+        <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
+        <v/>
+      </c>
+      <c r="G85" s="44">
+        <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
+        <v/>
+      </c>
+      <c r="H85" s="34">
+        <f>IF(A85&lt;=$B$9,D85*E85,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="C23:I23"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="C19:I19"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C24:I24"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="C26:I26"/>
+    <mergeCell ref="C29:I29"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="C21:I21"/>
+    <mergeCell ref="A32:I33"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="C11:I11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3861,7 +6580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5201,7 +7920,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5925,7 +8644,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9308,7 +12027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9563,7 +12282,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9804,7 +12523,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10194,7 +12913,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12767,7 +15486,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13059,7 +15778,39 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Curve visuals</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Charts read live from the Bootstrap and Fwd_Interp tabs — they populate once Bloomberg fills the data. Bootstrap columns: T (C), Discount factor (H), Zero (J); Fwd_Interp: T (B), flat fwd V1 (F), quadratic V2 (K).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13336,39 +16087,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Curve visuals</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="16" t="inlineStr">
-        <is>
-          <t>Charts read live from the Bootstrap and Fwd_Interp tabs — they populate once Bloomberg fills the data. Bootstrap columns: T (C), Discount factor (H), Zero (J); Fwd_Interp: T (B), flat fwd V1 (F), quadratic V2 (K).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001565C0"/>
@@ -30328,7 +33047,7 @@
       </c>
       <c r="E5" s="62" t="inlineStr">
         <is>
-          <t>Manual o/n (%)</t>
+          <t>O/N stub (%)</t>
         </is>
       </c>
     </row>
@@ -30342,7 +33061,7 @@
           <t>PX_LAST</t>
         </is>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="84">
         <f>IFERROR(BDP(SOFR_TKR,"PX_LAST")+0,E6)</f>
         <v/>
       </c>
@@ -30350,12 +33069,12 @@
         <f>IFERROR(BDP(SOFR_TKR,"LAST_UPDATE_DT"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="E6" s="64" t="n">
-        <v>4.06</v>
+      <c r="E6" s="85" t="n">
+        <v>3.64055</v>
       </c>
       <c r="F6" s="65" t="inlineStr">
         <is>
-          <t>PLACEHOLDER — used only if BDP fails. Sets DFspot.</t>
+          <t>FITTED, not an observed fixing: 3.64055% is the overnight rate that makes DFspot reproduce the screen's discount column (spot lag T+2, ACT/360). Replace with the real SOFR fixing if you prefer observed inputs - it moves the whole curve by ~1e-6 in DF.</t>
         </is>
       </c>
     </row>
@@ -32021,7 +34740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:L39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -32043,7 +34762,7 @@
       </c>
       <c r="J1" s="66" t="inlineStr">
         <is>
-          <t>MANUAL FALLBACK — PLACEHOLDER RATES, NOT MARKET DATA</t>
+          <t>REAL MARKET DATA — Bloomberg YCSW0490 USD SOFR, curve date 07/21/2026, PCS BGN</t>
         </is>
       </c>
     </row>
@@ -32055,7 +34774,7 @@
       </c>
       <c r="J2" s="65" t="inlineStr">
         <is>
-          <t>Column J is used only when BDP fails. These are a plausible Jul-2026 SOFR OIS shape so the curve computes off-terminal — they are invented, not observed. Overwrite with real quotes before using any output for anything real. On a terminal, BDP takes precedence automatically and column J is ignored.</t>
+          <t>Source: S490 Curve Construction screen (user-supplied photo, 07/21/26). Mid = (bid+ask)/2 reproduces Bloomberg's Market Rate column for all 32 pillars. Used only when BDP fails; on a terminal BDP takes precedence.</t>
         </is>
       </c>
     </row>
@@ -32123,10 +34842,15 @@
       </c>
       <c r="J4" s="62" t="inlineStr">
         <is>
-          <t>Manual quote (%)</t>
+          <t>Manual BID (%)</t>
         </is>
       </c>
       <c r="K4" s="62" t="inlineStr">
+        <is>
+          <t>Manual ASK (%)</t>
+        </is>
+      </c>
+      <c r="L4" s="62" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
@@ -32163,8 +34887,8 @@
         <f>IFERROR(BDP(A5&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H5" s="63">
-        <f>IFERROR((E5+F5)/2,IFERROR(G5+0,J5))</f>
+      <c r="H5" s="84">
+        <f>IFERROR((E5+F5)/2,IFERROR(G5+0,(J5+K5)/2))</f>
         <v/>
       </c>
       <c r="I5" s="26" t="inlineStr">
@@ -32172,12 +34896,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J5" s="64" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K5" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J5" s="85" t="n">
+        <v>3.62682</v>
+      </c>
+      <c r="K5" s="85" t="n">
+        <v>3.63318</v>
+      </c>
+      <c r="L5" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32212,17 +34939,20 @@
         <f>IFERROR(BDP(A6&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H6" s="63">
-        <f>IFERROR((E6+F6)/2,IFERROR(G6+0,J6))</f>
+      <c r="H6" s="84">
+        <f>IFERROR((E6+F6)/2,IFERROR(G6+0,(J6+K6)/2))</f>
         <v/>
       </c>
       <c r="I6" s="26" t="inlineStr"/>
-      <c r="J6" s="64" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K6" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J6" s="85" t="n">
+        <v>3.66879</v>
+      </c>
+      <c r="K6" s="85" t="n">
+        <v>3.67521</v>
+      </c>
+      <c r="L6" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32257,17 +34987,20 @@
         <f>IFERROR(BDP(A7&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H7" s="63">
-        <f>IFERROR((E7+F7)/2,IFERROR(G7+0,J7))</f>
+      <c r="H7" s="84">
+        <f>IFERROR((E7+F7)/2,IFERROR(G7+0,(J7+K7)/2))</f>
         <v/>
       </c>
       <c r="I7" s="26" t="inlineStr"/>
-      <c r="J7" s="64" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="K7" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J7" s="85" t="n">
+        <v>3.66701</v>
+      </c>
+      <c r="K7" s="85" t="n">
+        <v>3.67279</v>
+      </c>
+      <c r="L7" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32302,8 +35035,8 @@
         <f>IFERROR(BDP(A8&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H8" s="63">
-        <f>IFERROR((E8+F8)/2,IFERROR(G8+0,J8))</f>
+      <c r="H8" s="84">
+        <f>IFERROR((E8+F8)/2,IFERROR(G8+0,(J8+K8)/2))</f>
         <v/>
       </c>
       <c r="I8" s="26" t="inlineStr">
@@ -32311,12 +35044,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J8" s="64" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="K8" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J8" s="85" t="n">
+        <v>3.67722</v>
+      </c>
+      <c r="K8" s="85" t="n">
+        <v>3.68058</v>
+      </c>
+      <c r="L8" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32351,17 +35087,20 @@
         <f>IFERROR(BDP(A9&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H9" s="63">
-        <f>IFERROR((E9+F9)/2,IFERROR(G9+0,J9))</f>
+      <c r="H9" s="84">
+        <f>IFERROR((E9+F9)/2,IFERROR(G9+0,(J9+K9)/2))</f>
         <v/>
       </c>
       <c r="I9" s="26" t="inlineStr"/>
-      <c r="J9" s="64" t="n">
-        <v>4</v>
-      </c>
-      <c r="K9" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J9" s="85" t="n">
+        <v>3.70154</v>
+      </c>
+      <c r="K9" s="85" t="n">
+        <v>3.70535</v>
+      </c>
+      <c r="L9" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32396,8 +35135,8 @@
         <f>IFERROR(BDP(A10&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H10" s="63">
-        <f>IFERROR((E10+F10)/2,IFERROR(G10+0,J10))</f>
+      <c r="H10" s="84">
+        <f>IFERROR((E10+F10)/2,IFERROR(G10+0,(J10+K10)/2))</f>
         <v/>
       </c>
       <c r="I10" s="26" t="inlineStr">
@@ -32405,12 +35144,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J10" s="64" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="K10" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J10" s="85" t="n">
+        <v>3.7508</v>
+      </c>
+      <c r="K10" s="85" t="n">
+        <v>3.7549</v>
+      </c>
+      <c r="L10" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32445,17 +35187,20 @@
         <f>IFERROR(BDP(A11&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H11" s="63">
-        <f>IFERROR((E11+F11)/2,IFERROR(G11+0,J11))</f>
+      <c r="H11" s="84">
+        <f>IFERROR((E11+F11)/2,IFERROR(G11+0,(J11+K11)/2))</f>
         <v/>
       </c>
       <c r="I11" s="26" t="inlineStr"/>
-      <c r="J11" s="64" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="K11" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J11" s="85" t="n">
+        <v>3.79361</v>
+      </c>
+      <c r="K11" s="85" t="n">
+        <v>3.79789</v>
+      </c>
+      <c r="L11" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32490,17 +35235,20 @@
         <f>IFERROR(BDP(A12&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H12" s="63">
-        <f>IFERROR((E12+F12)/2,IFERROR(G12+0,J12))</f>
+      <c r="H12" s="84">
+        <f>IFERROR((E12+F12)/2,IFERROR(G12+0,(J12+K12)/2))</f>
         <v/>
       </c>
       <c r="I12" s="26" t="inlineStr"/>
-      <c r="J12" s="64" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="K12" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J12" s="85" t="n">
+        <v>3.83196</v>
+      </c>
+      <c r="K12" s="85" t="n">
+        <v>3.83674</v>
+      </c>
+      <c r="L12" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32535,8 +35283,8 @@
         <f>IFERROR(BDP(A13&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H13" s="63">
-        <f>IFERROR((E13+F13)/2,IFERROR(G13+0,J13))</f>
+      <c r="H13" s="84">
+        <f>IFERROR((E13+F13)/2,IFERROR(G13+0,(J13+K13)/2))</f>
         <v/>
       </c>
       <c r="I13" s="26" t="inlineStr">
@@ -32544,12 +35292,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J13" s="64" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K13" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J13" s="85" t="n">
+        <v>3.87501</v>
+      </c>
+      <c r="K13" s="85" t="n">
+        <v>3.87949</v>
+      </c>
+      <c r="L13" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32584,17 +35335,20 @@
         <f>IFERROR(BDP(A14&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H14" s="63">
-        <f>IFERROR((E14+F14)/2,IFERROR(G14+0,J14))</f>
+      <c r="H14" s="84">
+        <f>IFERROR((E14+F14)/2,IFERROR(G14+0,(J14+K14)/2))</f>
         <v/>
       </c>
       <c r="I14" s="26" t="inlineStr"/>
-      <c r="J14" s="64" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="K14" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J14" s="85" t="n">
+        <v>3.90612</v>
+      </c>
+      <c r="K14" s="85" t="n">
+        <v>3.91028</v>
+      </c>
+      <c r="L14" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32629,17 +35383,20 @@
         <f>IFERROR(BDP(A15&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H15" s="63">
-        <f>IFERROR((E15+F15)/2,IFERROR(G15+0,J15))</f>
+      <c r="H15" s="84">
+        <f>IFERROR((E15+F15)/2,IFERROR(G15+0,(J15+K15)/2))</f>
         <v/>
       </c>
       <c r="I15" s="26" t="inlineStr"/>
-      <c r="J15" s="64" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="K15" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J15" s="85" t="n">
+        <v>3.93252</v>
+      </c>
+      <c r="K15" s="85" t="n">
+        <v>3.93648</v>
+      </c>
+      <c r="L15" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32674,17 +35431,20 @@
         <f>IFERROR(BDP(A16&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H16" s="63">
-        <f>IFERROR((E16+F16)/2,IFERROR(G16+0,J16))</f>
+      <c r="H16" s="84">
+        <f>IFERROR((E16+F16)/2,IFERROR(G16+0,(J16+K16)/2))</f>
         <v/>
       </c>
       <c r="I16" s="26" t="inlineStr"/>
-      <c r="J16" s="64" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="K16" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J16" s="85" t="n">
+        <v>3.96102</v>
+      </c>
+      <c r="K16" s="85" t="n">
+        <v>3.96488</v>
+      </c>
+      <c r="L16" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32719,17 +35479,20 @@
         <f>IFERROR(BDP(A17&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H17" s="63">
-        <f>IFERROR((E17+F17)/2,IFERROR(G17+0,J17))</f>
+      <c r="H17" s="84">
+        <f>IFERROR((E17+F17)/2,IFERROR(G17+0,(J17+K17)/2))</f>
         <v/>
       </c>
       <c r="I17" s="26" t="inlineStr"/>
-      <c r="J17" s="64" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K17" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J17" s="85" t="n">
+        <v>3.98669</v>
+      </c>
+      <c r="K17" s="85" t="n">
+        <v>3.99051</v>
+      </c>
+      <c r="L17" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32764,17 +35527,20 @@
         <f>IFERROR(BDP(A18&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H18" s="63">
-        <f>IFERROR((E18+F18)/2,IFERROR(G18+0,J18))</f>
+      <c r="H18" s="84">
+        <f>IFERROR((E18+F18)/2,IFERROR(G18+0,(J18+K18)/2))</f>
         <v/>
       </c>
       <c r="I18" s="26" t="inlineStr"/>
-      <c r="J18" s="64" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="K18" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J18" s="85" t="n">
+        <v>4.00898</v>
+      </c>
+      <c r="K18" s="85" t="n">
+        <v>4.01272</v>
+      </c>
+      <c r="L18" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32809,17 +35575,20 @@
         <f>IFERROR(BDP(A19&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H19" s="63">
-        <f>IFERROR((E19+F19)/2,IFERROR(G19+0,J19))</f>
+      <c r="H19" s="84">
+        <f>IFERROR((E19+F19)/2,IFERROR(G19+0,(J19+K19)/2))</f>
         <v/>
       </c>
       <c r="I19" s="26" t="inlineStr"/>
-      <c r="J19" s="64" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="K19" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J19" s="85" t="n">
+        <v>4.02869</v>
+      </c>
+      <c r="K19" s="85" t="n">
+        <v>4.03192</v>
+      </c>
+      <c r="L19" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32854,17 +35623,20 @@
         <f>IFERROR(BDP(A20&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H20" s="63">
-        <f>IFERROR((E20+F20)/2,IFERROR(G20+0,J20))</f>
+      <c r="H20" s="84">
+        <f>IFERROR((E20+F20)/2,IFERROR(G20+0,(J20+K20)/2))</f>
         <v/>
       </c>
       <c r="I20" s="26" t="inlineStr"/>
-      <c r="J20" s="64" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="K20" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J20" s="85" t="n">
+        <v>4.04401</v>
+      </c>
+      <c r="K20" s="85" t="n">
+        <v>4.04717</v>
+      </c>
+      <c r="L20" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32899,17 +35671,20 @@
         <f>IFERROR(BDP(A21&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H21" s="63">
-        <f>IFERROR((E21+F21)/2,IFERROR(G21+0,J21))</f>
+      <c r="H21" s="84">
+        <f>IFERROR((E21+F21)/2,IFERROR(G21+0,(J21+K21)/2))</f>
         <v/>
       </c>
       <c r="I21" s="26" t="inlineStr"/>
-      <c r="J21" s="64" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K21" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J21" s="85" t="n">
+        <v>4.0498</v>
+      </c>
+      <c r="K21" s="85" t="n">
+        <v>4.0524</v>
+      </c>
+      <c r="L21" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32944,17 +35719,20 @@
         <f>IFERROR(BDP(A22&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H22" s="63">
-        <f>IFERROR((E22+F22)/2,IFERROR(G22+0,J22))</f>
+      <c r="H22" s="84">
+        <f>IFERROR((E22+F22)/2,IFERROR(G22+0,(J22+K22)/2))</f>
         <v/>
       </c>
       <c r="I22" s="26" t="inlineStr"/>
-      <c r="J22" s="64" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="K22" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J22" s="85" t="n">
+        <v>4.0302</v>
+      </c>
+      <c r="K22" s="85" t="n">
+        <v>4.0327</v>
+      </c>
+      <c r="L22" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -32989,17 +35767,20 @@
         <f>IFERROR(BDP(A23&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H23" s="63">
-        <f>IFERROR((E23+F23)/2,IFERROR(G23+0,J23))</f>
+      <c r="H23" s="84">
+        <f>IFERROR((E23+F23)/2,IFERROR(G23+0,(J23+K23)/2))</f>
         <v/>
       </c>
       <c r="I23" s="26" t="inlineStr"/>
-      <c r="J23" s="64" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="K23" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J23" s="85" t="n">
+        <v>4.02235</v>
+      </c>
+      <c r="K23" s="85" t="n">
+        <v>4.02486</v>
+      </c>
+      <c r="L23" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33034,8 +35815,8 @@
         <f>IFERROR(BDP(A24&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H24" s="63">
-        <f>IFERROR((E24+F24)/2,IFERROR(G24+0,J24))</f>
+      <c r="H24" s="84">
+        <f>IFERROR((E24+F24)/2,IFERROR(G24+0,(J24+K24)/2))</f>
         <v/>
       </c>
       <c r="I24" s="26" t="inlineStr">
@@ -33043,12 +35824,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J24" s="64" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="K24" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J24" s="85" t="n">
+        <v>4.03007</v>
+      </c>
+      <c r="K24" s="85" t="n">
+        <v>4.03273</v>
+      </c>
+      <c r="L24" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33083,8 +35867,8 @@
         <f>IFERROR(BDP(A25&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H25" s="63">
-        <f>IFERROR((E25+F25)/2,IFERROR(G25+0,J25))</f>
+      <c r="H25" s="84">
+        <f>IFERROR((E25+F25)/2,IFERROR(G25+0,(J25+K25)/2))</f>
         <v/>
       </c>
       <c r="I25" s="26" t="inlineStr">
@@ -33092,12 +35876,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J25" s="64" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="K25" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J25" s="85" t="n">
+        <v>4.0507</v>
+      </c>
+      <c r="K25" s="85" t="n">
+        <v>4.05283</v>
+      </c>
+      <c r="L25" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33132,8 +35919,8 @@
         <f>IFERROR(BDP(A26&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H26" s="63">
-        <f>IFERROR((E26+F26)/2,IFERROR(G26+0,J26))</f>
+      <c r="H26" s="84">
+        <f>IFERROR((E26+F26)/2,IFERROR(G26+0,(J26+K26)/2))</f>
         <v/>
       </c>
       <c r="I26" s="26" t="inlineStr">
@@ -33141,12 +35928,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J26" s="64" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="K26" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J26" s="85" t="n">
+        <v>4.07677</v>
+      </c>
+      <c r="K26" s="85" t="n">
+        <v>4.07909</v>
+      </c>
+      <c r="L26" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33181,8 +35971,8 @@
         <f>IFERROR(BDP(A27&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H27" s="63">
-        <f>IFERROR((E27+F27)/2,IFERROR(G27+0,J27))</f>
+      <c r="H27" s="84">
+        <f>IFERROR((E27+F27)/2,IFERROR(G27+0,(J27+K27)/2))</f>
         <v/>
       </c>
       <c r="I27" s="26" t="inlineStr">
@@ -33190,12 +35980,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J27" s="64" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K27" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J27" s="85" t="n">
+        <v>4.10574</v>
+      </c>
+      <c r="K27" s="85" t="n">
+        <v>4.10816</v>
+      </c>
+      <c r="L27" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33230,8 +36023,8 @@
         <f>IFERROR(BDP(A28&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H28" s="63">
-        <f>IFERROR((E28+F28)/2,IFERROR(G28+0,J28))</f>
+      <c r="H28" s="84">
+        <f>IFERROR((E28+F28)/2,IFERROR(G28+0,(J28+K28)/2))</f>
         <v/>
       </c>
       <c r="I28" s="26" t="inlineStr">
@@ -33239,12 +36032,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J28" s="64" t="n">
-        <v>3.93</v>
-      </c>
-      <c r="K28" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J28" s="85" t="n">
+        <v>4.13691</v>
+      </c>
+      <c r="K28" s="85" t="n">
+        <v>4.13959</v>
+      </c>
+      <c r="L28" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33279,8 +36075,8 @@
         <f>IFERROR(BDP(A29&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H29" s="63">
-        <f>IFERROR((E29+F29)/2,IFERROR(G29+0,J29))</f>
+      <c r="H29" s="84">
+        <f>IFERROR((E29+F29)/2,IFERROR(G29+0,(J29+K29)/2))</f>
         <v/>
       </c>
       <c r="I29" s="26" t="inlineStr">
@@ -33288,12 +36084,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J29" s="64" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="K29" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J29" s="85" t="n">
+        <v>4.17029</v>
+      </c>
+      <c r="K29" s="85" t="n">
+        <v>4.17301</v>
+      </c>
+      <c r="L29" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33328,8 +36127,8 @@
         <f>IFERROR(BDP(A30&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H30" s="63">
-        <f>IFERROR((E30+F30)/2,IFERROR(G30+0,J30))</f>
+      <c r="H30" s="84">
+        <f>IFERROR((E30+F30)/2,IFERROR(G30+0,(J30+K30)/2))</f>
         <v/>
       </c>
       <c r="I30" s="26" t="inlineStr">
@@ -33337,12 +36136,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J30" s="64" t="n">
-        <v>4.01</v>
-      </c>
-      <c r="K30" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J30" s="85" t="n">
+        <v>4.23713</v>
+      </c>
+      <c r="K30" s="85" t="n">
+        <v>4.23995</v>
+      </c>
+      <c r="L30" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33377,8 +36179,8 @@
         <f>IFERROR(BDP(A31&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H31" s="63">
-        <f>IFERROR((E31+F31)/2,IFERROR(G31+0,J31))</f>
+      <c r="H31" s="84">
+        <f>IFERROR((E31+F31)/2,IFERROR(G31+0,(J31+K31)/2))</f>
         <v/>
       </c>
       <c r="I31" s="26" t="inlineStr">
@@ -33386,12 +36188,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J31" s="64" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="K31" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J31" s="85" t="n">
+        <v>4.32475</v>
+      </c>
+      <c r="K31" s="85" t="n">
+        <v>4.32801</v>
+      </c>
+      <c r="L31" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33426,8 +36231,8 @@
         <f>IFERROR(BDP(A32&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H32" s="63">
-        <f>IFERROR((E32+F32)/2,IFERROR(G32+0,J32))</f>
+      <c r="H32" s="84">
+        <f>IFERROR((E32+F32)/2,IFERROR(G32+0,(J32+K32)/2))</f>
         <v/>
       </c>
       <c r="I32" s="26" t="inlineStr">
@@ -33435,12 +36240,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J32" s="64" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="K32" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J32" s="85" t="n">
+        <v>4.39966</v>
+      </c>
+      <c r="K32" s="85" t="n">
+        <v>4.40294</v>
+      </c>
+      <c r="L32" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33475,8 +36283,8 @@
         <f>IFERROR(BDP(A33&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H33" s="63">
-        <f>IFERROR((E33+F33)/2,IFERROR(G33+0,J33))</f>
+      <c r="H33" s="84">
+        <f>IFERROR((E33+F33)/2,IFERROR(G33+0,(J33+K33)/2))</f>
         <v/>
       </c>
       <c r="I33" s="26" t="inlineStr">
@@ -33484,12 +36292,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J33" s="64" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="K33" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J33" s="85" t="n">
+        <v>4.39842</v>
+      </c>
+      <c r="K33" s="85" t="n">
+        <v>4.40168</v>
+      </c>
+      <c r="L33" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33524,8 +36335,8 @@
         <f>IFERROR(BDP(A34&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H34" s="63">
-        <f>IFERROR((E34+F34)/2,IFERROR(G34+0,J34))</f>
+      <c r="H34" s="84">
+        <f>IFERROR((E34+F34)/2,IFERROR(G34+0,(J34+K34)/2))</f>
         <v/>
       </c>
       <c r="I34" s="26" t="inlineStr">
@@ -33533,12 +36344,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J34" s="64" t="n">
-        <v>3.97</v>
-      </c>
-      <c r="K34" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J34" s="85" t="n">
+        <v>4.36132</v>
+      </c>
+      <c r="K34" s="85" t="n">
+        <v>4.36422</v>
+      </c>
+      <c r="L34" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33573,8 +36387,8 @@
         <f>IFERROR(BDP(A35&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H35" s="63">
-        <f>IFERROR((E35+F35)/2,IFERROR(G35+0,J35))</f>
+      <c r="H35" s="84">
+        <f>IFERROR((E35+F35)/2,IFERROR(G35+0,(J35+K35)/2))</f>
         <v/>
       </c>
       <c r="I35" s="26" t="inlineStr">
@@ -33582,12 +36396,15 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J35" s="64" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K35" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
+      <c r="J35" s="85" t="n">
+        <v>4.23695</v>
+      </c>
+      <c r="K35" s="85" t="n">
+        <v>4.25025</v>
+      </c>
+      <c r="L35" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
         </is>
       </c>
     </row>
@@ -33622,8 +36439,8 @@
         <f>IFERROR(BDP(A36&amp;" "&amp;PX_SRC&amp;" Curncy","PX_LAST"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
-      <c r="H36" s="63">
-        <f>IFERROR((E36+F36)/2,IFERROR(G36+0,J36))</f>
+      <c r="H36" s="84">
+        <f>IFERROR((E36+F36)/2,IFERROR(G36+0,(J36+K36)/2))</f>
         <v/>
       </c>
       <c r="I36" s="26" t="inlineStr">
@@ -33631,15 +36448,19 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="J36" s="64" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="K36" s="65" t="inlineStr">
-        <is>
-          <t>PLACEHOLDER</t>
-        </is>
-      </c>
-    </row>
+      <c r="J36" s="85" t="n">
+        <v>4.09924</v>
+      </c>
+      <c r="K36" s="85" t="n">
+        <v>4.1213</v>
+      </c>
+      <c r="L36" s="65" t="inlineStr">
+        <is>
+          <t>S490 07/21/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
@@ -33688,6 +36509,11 @@
           <t>Bootstrap</t>
         </is>
       </c>
+      <c r="R1" s="65" t="inlineStr">
+        <is>
+          <t>Pillar dates are modified-following business-day adjusted (weekends only, no holiday calendar). Bloomberg rolls 07/23/2033-&gt;07/25/2033 and 07/23/2028-&gt;07/24/2028; plain EDATE did not, which shifted the curve.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -33860,8 +36686,8 @@
           <t>1W</t>
         </is>
       </c>
-      <c r="B8" s="18">
-        <f>$B$4+7</f>
+      <c r="B8" s="86">
+        <f>IF(MONTH((($B$4+7)+IF(WEEKDAY(($B$4+7),2)=6,2,IF(WEEKDAY(($B$4+7),2)=7,1,0))))&lt;&gt;MONTH(($B$4+7)),(($B$4+7)-IF(WEEKDAY(($B$4+7),2)=6,1,IF(WEEKDAY(($B$4+7),2)=7,2,0))),(($B$4+7)+IF(WEEKDAY(($B$4+7),2)=6,2,IF(WEEKDAY(($B$4+7),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C8" s="28">
@@ -33939,8 +36765,8 @@
           <t>2W</t>
         </is>
       </c>
-      <c r="B9" s="18">
-        <f>$B$4+14</f>
+      <c r="B9" s="86">
+        <f>IF(MONTH((($B$4+14)+IF(WEEKDAY(($B$4+14),2)=6,2,IF(WEEKDAY(($B$4+14),2)=7,1,0))))&lt;&gt;MONTH(($B$4+14)),(($B$4+14)-IF(WEEKDAY(($B$4+14),2)=6,1,IF(WEEKDAY(($B$4+14),2)=7,2,0))),(($B$4+14)+IF(WEEKDAY(($B$4+14),2)=6,2,IF(WEEKDAY(($B$4+14),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C9" s="28">
@@ -34019,8 +36845,8 @@
           <t>3W</t>
         </is>
       </c>
-      <c r="B10" s="18">
-        <f>$B$4+21</f>
+      <c r="B10" s="86">
+        <f>IF(MONTH((($B$4+21)+IF(WEEKDAY(($B$4+21),2)=6,2,IF(WEEKDAY(($B$4+21),2)=7,1,0))))&lt;&gt;MONTH(($B$4+21)),(($B$4+21)-IF(WEEKDAY(($B$4+21),2)=6,1,IF(WEEKDAY(($B$4+21),2)=7,2,0))),(($B$4+21)+IF(WEEKDAY(($B$4+21),2)=6,2,IF(WEEKDAY(($B$4+21),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C10" s="28">
@@ -34099,8 +36925,8 @@
           <t>1M</t>
         </is>
       </c>
-      <c r="B11" s="18">
-        <f>EDATE($B$4,1)</f>
+      <c r="B11" s="86">
+        <f>IF(MONTH(((EDATE($B$4,1))+IF(WEEKDAY((EDATE($B$4,1)),2)=6,2,IF(WEEKDAY((EDATE($B$4,1)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,1))),((EDATE($B$4,1))-IF(WEEKDAY((EDATE($B$4,1)),2)=6,1,IF(WEEKDAY((EDATE($B$4,1)),2)=7,2,0))),((EDATE($B$4,1))+IF(WEEKDAY((EDATE($B$4,1)),2)=6,2,IF(WEEKDAY((EDATE($B$4,1)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C11" s="28">
@@ -34179,8 +37005,8 @@
           <t>2M</t>
         </is>
       </c>
-      <c r="B12" s="18">
-        <f>EDATE($B$4,2)</f>
+      <c r="B12" s="86">
+        <f>IF(MONTH(((EDATE($B$4,2))+IF(WEEKDAY((EDATE($B$4,2)),2)=6,2,IF(WEEKDAY((EDATE($B$4,2)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,2))),((EDATE($B$4,2))-IF(WEEKDAY((EDATE($B$4,2)),2)=6,1,IF(WEEKDAY((EDATE($B$4,2)),2)=7,2,0))),((EDATE($B$4,2))+IF(WEEKDAY((EDATE($B$4,2)),2)=6,2,IF(WEEKDAY((EDATE($B$4,2)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C12" s="28">
@@ -34259,8 +37085,8 @@
           <t>3M</t>
         </is>
       </c>
-      <c r="B13" s="18">
-        <f>EDATE($B$4,3)</f>
+      <c r="B13" s="86">
+        <f>IF(MONTH(((EDATE($B$4,3))+IF(WEEKDAY((EDATE($B$4,3)),2)=6,2,IF(WEEKDAY((EDATE($B$4,3)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,3))),((EDATE($B$4,3))-IF(WEEKDAY((EDATE($B$4,3)),2)=6,1,IF(WEEKDAY((EDATE($B$4,3)),2)=7,2,0))),((EDATE($B$4,3))+IF(WEEKDAY((EDATE($B$4,3)),2)=6,2,IF(WEEKDAY((EDATE($B$4,3)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C13" s="28">
@@ -34339,8 +37165,8 @@
           <t>4M</t>
         </is>
       </c>
-      <c r="B14" s="18">
-        <f>EDATE($B$4,4)</f>
+      <c r="B14" s="86">
+        <f>IF(MONTH(((EDATE($B$4,4))+IF(WEEKDAY((EDATE($B$4,4)),2)=6,2,IF(WEEKDAY((EDATE($B$4,4)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,4))),((EDATE($B$4,4))-IF(WEEKDAY((EDATE($B$4,4)),2)=6,1,IF(WEEKDAY((EDATE($B$4,4)),2)=7,2,0))),((EDATE($B$4,4))+IF(WEEKDAY((EDATE($B$4,4)),2)=6,2,IF(WEEKDAY((EDATE($B$4,4)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C14" s="28">
@@ -34419,8 +37245,8 @@
           <t>5M</t>
         </is>
       </c>
-      <c r="B15" s="18">
-        <f>EDATE($B$4,5)</f>
+      <c r="B15" s="86">
+        <f>IF(MONTH(((EDATE($B$4,5))+IF(WEEKDAY((EDATE($B$4,5)),2)=6,2,IF(WEEKDAY((EDATE($B$4,5)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,5))),((EDATE($B$4,5))-IF(WEEKDAY((EDATE($B$4,5)),2)=6,1,IF(WEEKDAY((EDATE($B$4,5)),2)=7,2,0))),((EDATE($B$4,5))+IF(WEEKDAY((EDATE($B$4,5)),2)=6,2,IF(WEEKDAY((EDATE($B$4,5)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C15" s="28">
@@ -34499,8 +37325,8 @@
           <t>6M</t>
         </is>
       </c>
-      <c r="B16" s="18">
-        <f>EDATE($B$4,6)</f>
+      <c r="B16" s="86">
+        <f>IF(MONTH(((EDATE($B$4,6))+IF(WEEKDAY((EDATE($B$4,6)),2)=6,2,IF(WEEKDAY((EDATE($B$4,6)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,6))),((EDATE($B$4,6))-IF(WEEKDAY((EDATE($B$4,6)),2)=6,1,IF(WEEKDAY((EDATE($B$4,6)),2)=7,2,0))),((EDATE($B$4,6))+IF(WEEKDAY((EDATE($B$4,6)),2)=6,2,IF(WEEKDAY((EDATE($B$4,6)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C16" s="28">
@@ -34579,8 +37405,8 @@
           <t>7M</t>
         </is>
       </c>
-      <c r="B17" s="18">
-        <f>EDATE($B$4,7)</f>
+      <c r="B17" s="86">
+        <f>IF(MONTH(((EDATE($B$4,7))+IF(WEEKDAY((EDATE($B$4,7)),2)=6,2,IF(WEEKDAY((EDATE($B$4,7)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,7))),((EDATE($B$4,7))-IF(WEEKDAY((EDATE($B$4,7)),2)=6,1,IF(WEEKDAY((EDATE($B$4,7)),2)=7,2,0))),((EDATE($B$4,7))+IF(WEEKDAY((EDATE($B$4,7)),2)=6,2,IF(WEEKDAY((EDATE($B$4,7)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C17" s="28">
@@ -34659,8 +37485,8 @@
           <t>8M</t>
         </is>
       </c>
-      <c r="B18" s="18">
-        <f>EDATE($B$4,8)</f>
+      <c r="B18" s="86">
+        <f>IF(MONTH(((EDATE($B$4,8))+IF(WEEKDAY((EDATE($B$4,8)),2)=6,2,IF(WEEKDAY((EDATE($B$4,8)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,8))),((EDATE($B$4,8))-IF(WEEKDAY((EDATE($B$4,8)),2)=6,1,IF(WEEKDAY((EDATE($B$4,8)),2)=7,2,0))),((EDATE($B$4,8))+IF(WEEKDAY((EDATE($B$4,8)),2)=6,2,IF(WEEKDAY((EDATE($B$4,8)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C18" s="28">
@@ -34739,8 +37565,8 @@
           <t>9M</t>
         </is>
       </c>
-      <c r="B19" s="18">
-        <f>EDATE($B$4,9)</f>
+      <c r="B19" s="86">
+        <f>IF(MONTH(((EDATE($B$4,9))+IF(WEEKDAY((EDATE($B$4,9)),2)=6,2,IF(WEEKDAY((EDATE($B$4,9)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,9))),((EDATE($B$4,9))-IF(WEEKDAY((EDATE($B$4,9)),2)=6,1,IF(WEEKDAY((EDATE($B$4,9)),2)=7,2,0))),((EDATE($B$4,9))+IF(WEEKDAY((EDATE($B$4,9)),2)=6,2,IF(WEEKDAY((EDATE($B$4,9)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C19" s="28">
@@ -34819,8 +37645,8 @@
           <t>10M</t>
         </is>
       </c>
-      <c r="B20" s="18">
-        <f>EDATE($B$4,10)</f>
+      <c r="B20" s="86">
+        <f>IF(MONTH(((EDATE($B$4,10))+IF(WEEKDAY((EDATE($B$4,10)),2)=6,2,IF(WEEKDAY((EDATE($B$4,10)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,10))),((EDATE($B$4,10))-IF(WEEKDAY((EDATE($B$4,10)),2)=6,1,IF(WEEKDAY((EDATE($B$4,10)),2)=7,2,0))),((EDATE($B$4,10))+IF(WEEKDAY((EDATE($B$4,10)),2)=6,2,IF(WEEKDAY((EDATE($B$4,10)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C20" s="28">
@@ -34899,8 +37725,8 @@
           <t>11M</t>
         </is>
       </c>
-      <c r="B21" s="18">
-        <f>EDATE($B$4,11)</f>
+      <c r="B21" s="86">
+        <f>IF(MONTH(((EDATE($B$4,11))+IF(WEEKDAY((EDATE($B$4,11)),2)=6,2,IF(WEEKDAY((EDATE($B$4,11)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,11))),((EDATE($B$4,11))-IF(WEEKDAY((EDATE($B$4,11)),2)=6,1,IF(WEEKDAY((EDATE($B$4,11)),2)=7,2,0))),((EDATE($B$4,11))+IF(WEEKDAY((EDATE($B$4,11)),2)=6,2,IF(WEEKDAY((EDATE($B$4,11)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C21" s="28">
@@ -34979,8 +37805,8 @@
           <t>1Y</t>
         </is>
       </c>
-      <c r="B22" s="18">
-        <f>EDATE($B$4,12)</f>
+      <c r="B22" s="86">
+        <f>IF(MONTH(((EDATE($B$4,12))+IF(WEEKDAY((EDATE($B$4,12)),2)=6,2,IF(WEEKDAY((EDATE($B$4,12)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,12))),((EDATE($B$4,12))-IF(WEEKDAY((EDATE($B$4,12)),2)=6,1,IF(WEEKDAY((EDATE($B$4,12)),2)=7,2,0))),((EDATE($B$4,12))+IF(WEEKDAY((EDATE($B$4,12)),2)=6,2,IF(WEEKDAY((EDATE($B$4,12)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C22" s="28">
@@ -35063,8 +37889,8 @@
           <t>18M</t>
         </is>
       </c>
-      <c r="B23" s="18">
-        <f>EDATE($B$4,18)</f>
+      <c r="B23" s="86">
+        <f>IF(MONTH(((EDATE($B$4,18))+IF(WEEKDAY((EDATE($B$4,18)),2)=6,2,IF(WEEKDAY((EDATE($B$4,18)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,18))),((EDATE($B$4,18))-IF(WEEKDAY((EDATE($B$4,18)),2)=6,1,IF(WEEKDAY((EDATE($B$4,18)),2)=7,2,0))),((EDATE($B$4,18))+IF(WEEKDAY((EDATE($B$4,18)),2)=6,2,IF(WEEKDAY((EDATE($B$4,18)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C23" s="28">
@@ -35146,8 +37972,8 @@
           <t>2Y</t>
         </is>
       </c>
-      <c r="B24" s="18">
-        <f>EDATE($B$4,24)</f>
+      <c r="B24" s="86">
+        <f>IF(MONTH(((EDATE($B$4,24))+IF(WEEKDAY((EDATE($B$4,24)),2)=6,2,IF(WEEKDAY((EDATE($B$4,24)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,24))),((EDATE($B$4,24))-IF(WEEKDAY((EDATE($B$4,24)),2)=6,1,IF(WEEKDAY((EDATE($B$4,24)),2)=7,2,0))),((EDATE($B$4,24))+IF(WEEKDAY((EDATE($B$4,24)),2)=6,2,IF(WEEKDAY((EDATE($B$4,24)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C24" s="28">
@@ -35230,8 +38056,8 @@
           <t>3Y</t>
         </is>
       </c>
-      <c r="B25" s="18">
-        <f>EDATE($B$4,36)</f>
+      <c r="B25" s="86">
+        <f>IF(MONTH(((EDATE($B$4,36))+IF(WEEKDAY((EDATE($B$4,36)),2)=6,2,IF(WEEKDAY((EDATE($B$4,36)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,36))),((EDATE($B$4,36))-IF(WEEKDAY((EDATE($B$4,36)),2)=6,1,IF(WEEKDAY((EDATE($B$4,36)),2)=7,2,0))),((EDATE($B$4,36))+IF(WEEKDAY((EDATE($B$4,36)),2)=6,2,IF(WEEKDAY((EDATE($B$4,36)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C25" s="28">
@@ -35307,8 +38133,8 @@
           <t>4Y</t>
         </is>
       </c>
-      <c r="B26" s="18">
-        <f>EDATE($B$4,48)</f>
+      <c r="B26" s="86">
+        <f>IF(MONTH(((EDATE($B$4,48))+IF(WEEKDAY((EDATE($B$4,48)),2)=6,2,IF(WEEKDAY((EDATE($B$4,48)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,48))),((EDATE($B$4,48))-IF(WEEKDAY((EDATE($B$4,48)),2)=6,1,IF(WEEKDAY((EDATE($B$4,48)),2)=7,2,0))),((EDATE($B$4,48))+IF(WEEKDAY((EDATE($B$4,48)),2)=6,2,IF(WEEKDAY((EDATE($B$4,48)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C26" s="28">
@@ -35384,8 +38210,8 @@
           <t>5Y</t>
         </is>
       </c>
-      <c r="B27" s="18">
-        <f>EDATE($B$4,60)</f>
+      <c r="B27" s="86">
+        <f>IF(MONTH(((EDATE($B$4,60))+IF(WEEKDAY((EDATE($B$4,60)),2)=6,2,IF(WEEKDAY((EDATE($B$4,60)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,60))),((EDATE($B$4,60))-IF(WEEKDAY((EDATE($B$4,60)),2)=6,1,IF(WEEKDAY((EDATE($B$4,60)),2)=7,2,0))),((EDATE($B$4,60))+IF(WEEKDAY((EDATE($B$4,60)),2)=6,2,IF(WEEKDAY((EDATE($B$4,60)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C27" s="28">
@@ -35461,8 +38287,8 @@
           <t>6Y</t>
         </is>
       </c>
-      <c r="B28" s="18">
-        <f>EDATE($B$4,72)</f>
+      <c r="B28" s="86">
+        <f>IF(MONTH(((EDATE($B$4,72))+IF(WEEKDAY((EDATE($B$4,72)),2)=6,2,IF(WEEKDAY((EDATE($B$4,72)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,72))),((EDATE($B$4,72))-IF(WEEKDAY((EDATE($B$4,72)),2)=6,1,IF(WEEKDAY((EDATE($B$4,72)),2)=7,2,0))),((EDATE($B$4,72))+IF(WEEKDAY((EDATE($B$4,72)),2)=6,2,IF(WEEKDAY((EDATE($B$4,72)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C28" s="28">
@@ -35538,8 +38364,8 @@
           <t>7Y</t>
         </is>
       </c>
-      <c r="B29" s="18">
-        <f>EDATE($B$4,84)</f>
+      <c r="B29" s="86">
+        <f>IF(MONTH(((EDATE($B$4,84))+IF(WEEKDAY((EDATE($B$4,84)),2)=6,2,IF(WEEKDAY((EDATE($B$4,84)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,84))),((EDATE($B$4,84))-IF(WEEKDAY((EDATE($B$4,84)),2)=6,1,IF(WEEKDAY((EDATE($B$4,84)),2)=7,2,0))),((EDATE($B$4,84))+IF(WEEKDAY((EDATE($B$4,84)),2)=6,2,IF(WEEKDAY((EDATE($B$4,84)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C29" s="28">
@@ -35615,8 +38441,8 @@
           <t>8Y</t>
         </is>
       </c>
-      <c r="B30" s="18">
-        <f>EDATE($B$4,96)</f>
+      <c r="B30" s="86">
+        <f>IF(MONTH(((EDATE($B$4,96))+IF(WEEKDAY((EDATE($B$4,96)),2)=6,2,IF(WEEKDAY((EDATE($B$4,96)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,96))),((EDATE($B$4,96))-IF(WEEKDAY((EDATE($B$4,96)),2)=6,1,IF(WEEKDAY((EDATE($B$4,96)),2)=7,2,0))),((EDATE($B$4,96))+IF(WEEKDAY((EDATE($B$4,96)),2)=6,2,IF(WEEKDAY((EDATE($B$4,96)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C30" s="28">
@@ -35692,8 +38518,8 @@
           <t>9Y</t>
         </is>
       </c>
-      <c r="B31" s="18">
-        <f>EDATE($B$4,108)</f>
+      <c r="B31" s="86">
+        <f>IF(MONTH(((EDATE($B$4,108))+IF(WEEKDAY((EDATE($B$4,108)),2)=6,2,IF(WEEKDAY((EDATE($B$4,108)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,108))),((EDATE($B$4,108))-IF(WEEKDAY((EDATE($B$4,108)),2)=6,1,IF(WEEKDAY((EDATE($B$4,108)),2)=7,2,0))),((EDATE($B$4,108))+IF(WEEKDAY((EDATE($B$4,108)),2)=6,2,IF(WEEKDAY((EDATE($B$4,108)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C31" s="28">
@@ -35769,8 +38595,8 @@
           <t>10Y</t>
         </is>
       </c>
-      <c r="B32" s="18">
-        <f>EDATE($B$4,120)</f>
+      <c r="B32" s="86">
+        <f>IF(MONTH(((EDATE($B$4,120))+IF(WEEKDAY((EDATE($B$4,120)),2)=6,2,IF(WEEKDAY((EDATE($B$4,120)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,120))),((EDATE($B$4,120))-IF(WEEKDAY((EDATE($B$4,120)),2)=6,1,IF(WEEKDAY((EDATE($B$4,120)),2)=7,2,0))),((EDATE($B$4,120))+IF(WEEKDAY((EDATE($B$4,120)),2)=6,2,IF(WEEKDAY((EDATE($B$4,120)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C32" s="28">
@@ -35846,8 +38672,8 @@
           <t>11Y</t>
         </is>
       </c>
-      <c r="B33" s="18">
-        <f>EDATE($B$4,132)</f>
+      <c r="B33" s="86">
+        <f>IF(MONTH(((EDATE($B$4,132))+IF(WEEKDAY((EDATE($B$4,132)),2)=6,2,IF(WEEKDAY((EDATE($B$4,132)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,132))),((EDATE($B$4,132))-IF(WEEKDAY((EDATE($B$4,132)),2)=6,1,IF(WEEKDAY((EDATE($B$4,132)),2)=7,2,0))),((EDATE($B$4,132))+IF(WEEKDAY((EDATE($B$4,132)),2)=6,2,IF(WEEKDAY((EDATE($B$4,132)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C33" s="28">
@@ -35923,8 +38749,8 @@
           <t>12Y</t>
         </is>
       </c>
-      <c r="B34" s="18">
-        <f>EDATE($B$4,144)</f>
+      <c r="B34" s="86">
+        <f>IF(MONTH(((EDATE($B$4,144))+IF(WEEKDAY((EDATE($B$4,144)),2)=6,2,IF(WEEKDAY((EDATE($B$4,144)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,144))),((EDATE($B$4,144))-IF(WEEKDAY((EDATE($B$4,144)),2)=6,1,IF(WEEKDAY((EDATE($B$4,144)),2)=7,2,0))),((EDATE($B$4,144))+IF(WEEKDAY((EDATE($B$4,144)),2)=6,2,IF(WEEKDAY((EDATE($B$4,144)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C34" s="28">
@@ -36004,8 +38830,8 @@
           <t>13Y</t>
         </is>
       </c>
-      <c r="B35" s="18">
-        <f>EDATE($B$4,156)</f>
+      <c r="B35" s="86">
+        <f>IF(MONTH(((EDATE($B$4,156))+IF(WEEKDAY((EDATE($B$4,156)),2)=6,2,IF(WEEKDAY((EDATE($B$4,156)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,156))),((EDATE($B$4,156))-IF(WEEKDAY((EDATE($B$4,156)),2)=6,1,IF(WEEKDAY((EDATE($B$4,156)),2)=7,2,0))),((EDATE($B$4,156))+IF(WEEKDAY((EDATE($B$4,156)),2)=6,2,IF(WEEKDAY((EDATE($B$4,156)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C35" s="28">
@@ -36081,8 +38907,8 @@
           <t>14Y</t>
         </is>
       </c>
-      <c r="B36" s="18">
-        <f>EDATE($B$4,168)</f>
+      <c r="B36" s="86">
+        <f>IF(MONTH(((EDATE($B$4,168))+IF(WEEKDAY((EDATE($B$4,168)),2)=6,2,IF(WEEKDAY((EDATE($B$4,168)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,168))),((EDATE($B$4,168))-IF(WEEKDAY((EDATE($B$4,168)),2)=6,1,IF(WEEKDAY((EDATE($B$4,168)),2)=7,2,0))),((EDATE($B$4,168))+IF(WEEKDAY((EDATE($B$4,168)),2)=6,2,IF(WEEKDAY((EDATE($B$4,168)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C36" s="28">
@@ -36158,8 +38984,8 @@
           <t>15Y</t>
         </is>
       </c>
-      <c r="B37" s="18">
-        <f>EDATE($B$4,180)</f>
+      <c r="B37" s="86">
+        <f>IF(MONTH(((EDATE($B$4,180))+IF(WEEKDAY((EDATE($B$4,180)),2)=6,2,IF(WEEKDAY((EDATE($B$4,180)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,180))),((EDATE($B$4,180))-IF(WEEKDAY((EDATE($B$4,180)),2)=6,1,IF(WEEKDAY((EDATE($B$4,180)),2)=7,2,0))),((EDATE($B$4,180))+IF(WEEKDAY((EDATE($B$4,180)),2)=6,2,IF(WEEKDAY((EDATE($B$4,180)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C37" s="28">
@@ -36239,8 +39065,8 @@
           <t>16Y</t>
         </is>
       </c>
-      <c r="B38" s="18">
-        <f>EDATE($B$4,192)</f>
+      <c r="B38" s="86">
+        <f>IF(MONTH(((EDATE($B$4,192))+IF(WEEKDAY((EDATE($B$4,192)),2)=6,2,IF(WEEKDAY((EDATE($B$4,192)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,192))),((EDATE($B$4,192))-IF(WEEKDAY((EDATE($B$4,192)),2)=6,1,IF(WEEKDAY((EDATE($B$4,192)),2)=7,2,0))),((EDATE($B$4,192))+IF(WEEKDAY((EDATE($B$4,192)),2)=6,2,IF(WEEKDAY((EDATE($B$4,192)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C38" s="28">
@@ -36316,8 +39142,8 @@
           <t>17Y</t>
         </is>
       </c>
-      <c r="B39" s="18">
-        <f>EDATE($B$4,204)</f>
+      <c r="B39" s="86">
+        <f>IF(MONTH(((EDATE($B$4,204))+IF(WEEKDAY((EDATE($B$4,204)),2)=6,2,IF(WEEKDAY((EDATE($B$4,204)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,204))),((EDATE($B$4,204))-IF(WEEKDAY((EDATE($B$4,204)),2)=6,1,IF(WEEKDAY((EDATE($B$4,204)),2)=7,2,0))),((EDATE($B$4,204))+IF(WEEKDAY((EDATE($B$4,204)),2)=6,2,IF(WEEKDAY((EDATE($B$4,204)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C39" s="28">
@@ -36393,8 +39219,8 @@
           <t>18Y</t>
         </is>
       </c>
-      <c r="B40" s="18">
-        <f>EDATE($B$4,216)</f>
+      <c r="B40" s="86">
+        <f>IF(MONTH(((EDATE($B$4,216))+IF(WEEKDAY((EDATE($B$4,216)),2)=6,2,IF(WEEKDAY((EDATE($B$4,216)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,216))),((EDATE($B$4,216))-IF(WEEKDAY((EDATE($B$4,216)),2)=6,1,IF(WEEKDAY((EDATE($B$4,216)),2)=7,2,0))),((EDATE($B$4,216))+IF(WEEKDAY((EDATE($B$4,216)),2)=6,2,IF(WEEKDAY((EDATE($B$4,216)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C40" s="28">
@@ -36470,8 +39296,8 @@
           <t>19Y</t>
         </is>
       </c>
-      <c r="B41" s="18">
-        <f>EDATE($B$4,228)</f>
+      <c r="B41" s="86">
+        <f>IF(MONTH(((EDATE($B$4,228))+IF(WEEKDAY((EDATE($B$4,228)),2)=6,2,IF(WEEKDAY((EDATE($B$4,228)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,228))),((EDATE($B$4,228))-IF(WEEKDAY((EDATE($B$4,228)),2)=6,1,IF(WEEKDAY((EDATE($B$4,228)),2)=7,2,0))),((EDATE($B$4,228))+IF(WEEKDAY((EDATE($B$4,228)),2)=6,2,IF(WEEKDAY((EDATE($B$4,228)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C41" s="28">
@@ -36547,8 +39373,8 @@
           <t>20Y</t>
         </is>
       </c>
-      <c r="B42" s="18">
-        <f>EDATE($B$4,240)</f>
+      <c r="B42" s="86">
+        <f>IF(MONTH(((EDATE($B$4,240))+IF(WEEKDAY((EDATE($B$4,240)),2)=6,2,IF(WEEKDAY((EDATE($B$4,240)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,240))),((EDATE($B$4,240))-IF(WEEKDAY((EDATE($B$4,240)),2)=6,1,IF(WEEKDAY((EDATE($B$4,240)),2)=7,2,0))),((EDATE($B$4,240))+IF(WEEKDAY((EDATE($B$4,240)),2)=6,2,IF(WEEKDAY((EDATE($B$4,240)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C42" s="28">
@@ -36628,8 +39454,8 @@
           <t>21Y</t>
         </is>
       </c>
-      <c r="B43" s="18">
-        <f>EDATE($B$4,252)</f>
+      <c r="B43" s="86">
+        <f>IF(MONTH(((EDATE($B$4,252))+IF(WEEKDAY((EDATE($B$4,252)),2)=6,2,IF(WEEKDAY((EDATE($B$4,252)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,252))),((EDATE($B$4,252))-IF(WEEKDAY((EDATE($B$4,252)),2)=6,1,IF(WEEKDAY((EDATE($B$4,252)),2)=7,2,0))),((EDATE($B$4,252))+IF(WEEKDAY((EDATE($B$4,252)),2)=6,2,IF(WEEKDAY((EDATE($B$4,252)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C43" s="28">
@@ -36705,8 +39531,8 @@
           <t>22Y</t>
         </is>
       </c>
-      <c r="B44" s="18">
-        <f>EDATE($B$4,264)</f>
+      <c r="B44" s="86">
+        <f>IF(MONTH(((EDATE($B$4,264))+IF(WEEKDAY((EDATE($B$4,264)),2)=6,2,IF(WEEKDAY((EDATE($B$4,264)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,264))),((EDATE($B$4,264))-IF(WEEKDAY((EDATE($B$4,264)),2)=6,1,IF(WEEKDAY((EDATE($B$4,264)),2)=7,2,0))),((EDATE($B$4,264))+IF(WEEKDAY((EDATE($B$4,264)),2)=6,2,IF(WEEKDAY((EDATE($B$4,264)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C44" s="28">
@@ -36782,8 +39608,8 @@
           <t>23Y</t>
         </is>
       </c>
-      <c r="B45" s="18">
-        <f>EDATE($B$4,276)</f>
+      <c r="B45" s="86">
+        <f>IF(MONTH(((EDATE($B$4,276))+IF(WEEKDAY((EDATE($B$4,276)),2)=6,2,IF(WEEKDAY((EDATE($B$4,276)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,276))),((EDATE($B$4,276))-IF(WEEKDAY((EDATE($B$4,276)),2)=6,1,IF(WEEKDAY((EDATE($B$4,276)),2)=7,2,0))),((EDATE($B$4,276))+IF(WEEKDAY((EDATE($B$4,276)),2)=6,2,IF(WEEKDAY((EDATE($B$4,276)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C45" s="28">
@@ -36859,8 +39685,8 @@
           <t>24Y</t>
         </is>
       </c>
-      <c r="B46" s="18">
-        <f>EDATE($B$4,288)</f>
+      <c r="B46" s="86">
+        <f>IF(MONTH(((EDATE($B$4,288))+IF(WEEKDAY((EDATE($B$4,288)),2)=6,2,IF(WEEKDAY((EDATE($B$4,288)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,288))),((EDATE($B$4,288))-IF(WEEKDAY((EDATE($B$4,288)),2)=6,1,IF(WEEKDAY((EDATE($B$4,288)),2)=7,2,0))),((EDATE($B$4,288))+IF(WEEKDAY((EDATE($B$4,288)),2)=6,2,IF(WEEKDAY((EDATE($B$4,288)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C46" s="28">
@@ -36936,8 +39762,8 @@
           <t>25Y</t>
         </is>
       </c>
-      <c r="B47" s="18">
-        <f>EDATE($B$4,300)</f>
+      <c r="B47" s="86">
+        <f>IF(MONTH(((EDATE($B$4,300))+IF(WEEKDAY((EDATE($B$4,300)),2)=6,2,IF(WEEKDAY((EDATE($B$4,300)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,300))),((EDATE($B$4,300))-IF(WEEKDAY((EDATE($B$4,300)),2)=6,1,IF(WEEKDAY((EDATE($B$4,300)),2)=7,2,0))),((EDATE($B$4,300))+IF(WEEKDAY((EDATE($B$4,300)),2)=6,2,IF(WEEKDAY((EDATE($B$4,300)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C47" s="28">
@@ -37017,8 +39843,8 @@
           <t>26Y</t>
         </is>
       </c>
-      <c r="B48" s="18">
-        <f>EDATE($B$4,312)</f>
+      <c r="B48" s="86">
+        <f>IF(MONTH(((EDATE($B$4,312))+IF(WEEKDAY((EDATE($B$4,312)),2)=6,2,IF(WEEKDAY((EDATE($B$4,312)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,312))),((EDATE($B$4,312))-IF(WEEKDAY((EDATE($B$4,312)),2)=6,1,IF(WEEKDAY((EDATE($B$4,312)),2)=7,2,0))),((EDATE($B$4,312))+IF(WEEKDAY((EDATE($B$4,312)),2)=6,2,IF(WEEKDAY((EDATE($B$4,312)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C48" s="28">
@@ -37094,8 +39920,8 @@
           <t>27Y</t>
         </is>
       </c>
-      <c r="B49" s="18">
-        <f>EDATE($B$4,324)</f>
+      <c r="B49" s="86">
+        <f>IF(MONTH(((EDATE($B$4,324))+IF(WEEKDAY((EDATE($B$4,324)),2)=6,2,IF(WEEKDAY((EDATE($B$4,324)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,324))),((EDATE($B$4,324))-IF(WEEKDAY((EDATE($B$4,324)),2)=6,1,IF(WEEKDAY((EDATE($B$4,324)),2)=7,2,0))),((EDATE($B$4,324))+IF(WEEKDAY((EDATE($B$4,324)),2)=6,2,IF(WEEKDAY((EDATE($B$4,324)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C49" s="28">
@@ -37171,8 +39997,8 @@
           <t>28Y</t>
         </is>
       </c>
-      <c r="B50" s="18">
-        <f>EDATE($B$4,336)</f>
+      <c r="B50" s="86">
+        <f>IF(MONTH(((EDATE($B$4,336))+IF(WEEKDAY((EDATE($B$4,336)),2)=6,2,IF(WEEKDAY((EDATE($B$4,336)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,336))),((EDATE($B$4,336))-IF(WEEKDAY((EDATE($B$4,336)),2)=6,1,IF(WEEKDAY((EDATE($B$4,336)),2)=7,2,0))),((EDATE($B$4,336))+IF(WEEKDAY((EDATE($B$4,336)),2)=6,2,IF(WEEKDAY((EDATE($B$4,336)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C50" s="28">
@@ -37248,8 +40074,8 @@
           <t>29Y</t>
         </is>
       </c>
-      <c r="B51" s="18">
-        <f>EDATE($B$4,348)</f>
+      <c r="B51" s="86">
+        <f>IF(MONTH(((EDATE($B$4,348))+IF(WEEKDAY((EDATE($B$4,348)),2)=6,2,IF(WEEKDAY((EDATE($B$4,348)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,348))),((EDATE($B$4,348))-IF(WEEKDAY((EDATE($B$4,348)),2)=6,1,IF(WEEKDAY((EDATE($B$4,348)),2)=7,2,0))),((EDATE($B$4,348))+IF(WEEKDAY((EDATE($B$4,348)),2)=6,2,IF(WEEKDAY((EDATE($B$4,348)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C51" s="28">
@@ -37325,8 +40151,8 @@
           <t>30Y</t>
         </is>
       </c>
-      <c r="B52" s="18">
-        <f>EDATE($B$4,360)</f>
+      <c r="B52" s="86">
+        <f>IF(MONTH(((EDATE($B$4,360))+IF(WEEKDAY((EDATE($B$4,360)),2)=6,2,IF(WEEKDAY((EDATE($B$4,360)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,360))),((EDATE($B$4,360))-IF(WEEKDAY((EDATE($B$4,360)),2)=6,1,IF(WEEKDAY((EDATE($B$4,360)),2)=7,2,0))),((EDATE($B$4,360))+IF(WEEKDAY((EDATE($B$4,360)),2)=6,2,IF(WEEKDAY((EDATE($B$4,360)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C52" s="28">
@@ -37406,8 +40232,8 @@
           <t>31Y</t>
         </is>
       </c>
-      <c r="B53" s="18">
-        <f>EDATE($B$4,372)</f>
+      <c r="B53" s="86">
+        <f>IF(MONTH(((EDATE($B$4,372))+IF(WEEKDAY((EDATE($B$4,372)),2)=6,2,IF(WEEKDAY((EDATE($B$4,372)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,372))),((EDATE($B$4,372))-IF(WEEKDAY((EDATE($B$4,372)),2)=6,1,IF(WEEKDAY((EDATE($B$4,372)),2)=7,2,0))),((EDATE($B$4,372))+IF(WEEKDAY((EDATE($B$4,372)),2)=6,2,IF(WEEKDAY((EDATE($B$4,372)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C53" s="28">
@@ -37483,8 +40309,8 @@
           <t>32Y</t>
         </is>
       </c>
-      <c r="B54" s="18">
-        <f>EDATE($B$4,384)</f>
+      <c r="B54" s="86">
+        <f>IF(MONTH(((EDATE($B$4,384))+IF(WEEKDAY((EDATE($B$4,384)),2)=6,2,IF(WEEKDAY((EDATE($B$4,384)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,384))),((EDATE($B$4,384))-IF(WEEKDAY((EDATE($B$4,384)),2)=6,1,IF(WEEKDAY((EDATE($B$4,384)),2)=7,2,0))),((EDATE($B$4,384))+IF(WEEKDAY((EDATE($B$4,384)),2)=6,2,IF(WEEKDAY((EDATE($B$4,384)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C54" s="28">
@@ -37560,8 +40386,8 @@
           <t>33Y</t>
         </is>
       </c>
-      <c r="B55" s="18">
-        <f>EDATE($B$4,396)</f>
+      <c r="B55" s="86">
+        <f>IF(MONTH(((EDATE($B$4,396))+IF(WEEKDAY((EDATE($B$4,396)),2)=6,2,IF(WEEKDAY((EDATE($B$4,396)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,396))),((EDATE($B$4,396))-IF(WEEKDAY((EDATE($B$4,396)),2)=6,1,IF(WEEKDAY((EDATE($B$4,396)),2)=7,2,0))),((EDATE($B$4,396))+IF(WEEKDAY((EDATE($B$4,396)),2)=6,2,IF(WEEKDAY((EDATE($B$4,396)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C55" s="28">
@@ -37637,8 +40463,8 @@
           <t>34Y</t>
         </is>
       </c>
-      <c r="B56" s="18">
-        <f>EDATE($B$4,408)</f>
+      <c r="B56" s="86">
+        <f>IF(MONTH(((EDATE($B$4,408))+IF(WEEKDAY((EDATE($B$4,408)),2)=6,2,IF(WEEKDAY((EDATE($B$4,408)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,408))),((EDATE($B$4,408))-IF(WEEKDAY((EDATE($B$4,408)),2)=6,1,IF(WEEKDAY((EDATE($B$4,408)),2)=7,2,0))),((EDATE($B$4,408))+IF(WEEKDAY((EDATE($B$4,408)),2)=6,2,IF(WEEKDAY((EDATE($B$4,408)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C56" s="28">
@@ -37714,8 +40540,8 @@
           <t>35Y</t>
         </is>
       </c>
-      <c r="B57" s="18">
-        <f>EDATE($B$4,420)</f>
+      <c r="B57" s="86">
+        <f>IF(MONTH(((EDATE($B$4,420))+IF(WEEKDAY((EDATE($B$4,420)),2)=6,2,IF(WEEKDAY((EDATE($B$4,420)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,420))),((EDATE($B$4,420))-IF(WEEKDAY((EDATE($B$4,420)),2)=6,1,IF(WEEKDAY((EDATE($B$4,420)),2)=7,2,0))),((EDATE($B$4,420))+IF(WEEKDAY((EDATE($B$4,420)),2)=6,2,IF(WEEKDAY((EDATE($B$4,420)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C57" s="28">
@@ -37791,8 +40617,8 @@
           <t>36Y</t>
         </is>
       </c>
-      <c r="B58" s="18">
-        <f>EDATE($B$4,432)</f>
+      <c r="B58" s="86">
+        <f>IF(MONTH(((EDATE($B$4,432))+IF(WEEKDAY((EDATE($B$4,432)),2)=6,2,IF(WEEKDAY((EDATE($B$4,432)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,432))),((EDATE($B$4,432))-IF(WEEKDAY((EDATE($B$4,432)),2)=6,1,IF(WEEKDAY((EDATE($B$4,432)),2)=7,2,0))),((EDATE($B$4,432))+IF(WEEKDAY((EDATE($B$4,432)),2)=6,2,IF(WEEKDAY((EDATE($B$4,432)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C58" s="28">
@@ -37868,8 +40694,8 @@
           <t>37Y</t>
         </is>
       </c>
-      <c r="B59" s="18">
-        <f>EDATE($B$4,444)</f>
+      <c r="B59" s="86">
+        <f>IF(MONTH(((EDATE($B$4,444))+IF(WEEKDAY((EDATE($B$4,444)),2)=6,2,IF(WEEKDAY((EDATE($B$4,444)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,444))),((EDATE($B$4,444))-IF(WEEKDAY((EDATE($B$4,444)),2)=6,1,IF(WEEKDAY((EDATE($B$4,444)),2)=7,2,0))),((EDATE($B$4,444))+IF(WEEKDAY((EDATE($B$4,444)),2)=6,2,IF(WEEKDAY((EDATE($B$4,444)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C59" s="28">
@@ -37945,8 +40771,8 @@
           <t>38Y</t>
         </is>
       </c>
-      <c r="B60" s="18">
-        <f>EDATE($B$4,456)</f>
+      <c r="B60" s="86">
+        <f>IF(MONTH(((EDATE($B$4,456))+IF(WEEKDAY((EDATE($B$4,456)),2)=6,2,IF(WEEKDAY((EDATE($B$4,456)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,456))),((EDATE($B$4,456))-IF(WEEKDAY((EDATE($B$4,456)),2)=6,1,IF(WEEKDAY((EDATE($B$4,456)),2)=7,2,0))),((EDATE($B$4,456))+IF(WEEKDAY((EDATE($B$4,456)),2)=6,2,IF(WEEKDAY((EDATE($B$4,456)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C60" s="28">
@@ -38022,8 +40848,8 @@
           <t>39Y</t>
         </is>
       </c>
-      <c r="B61" s="18">
-        <f>EDATE($B$4,468)</f>
+      <c r="B61" s="86">
+        <f>IF(MONTH(((EDATE($B$4,468))+IF(WEEKDAY((EDATE($B$4,468)),2)=6,2,IF(WEEKDAY((EDATE($B$4,468)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,468))),((EDATE($B$4,468))-IF(WEEKDAY((EDATE($B$4,468)),2)=6,1,IF(WEEKDAY((EDATE($B$4,468)),2)=7,2,0))),((EDATE($B$4,468))+IF(WEEKDAY((EDATE($B$4,468)),2)=6,2,IF(WEEKDAY((EDATE($B$4,468)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C61" s="28">
@@ -38099,8 +40925,8 @@
           <t>40Y</t>
         </is>
       </c>
-      <c r="B62" s="18">
-        <f>EDATE($B$4,480)</f>
+      <c r="B62" s="86">
+        <f>IF(MONTH(((EDATE($B$4,480))+IF(WEEKDAY((EDATE($B$4,480)),2)=6,2,IF(WEEKDAY((EDATE($B$4,480)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,480))),((EDATE($B$4,480))-IF(WEEKDAY((EDATE($B$4,480)),2)=6,1,IF(WEEKDAY((EDATE($B$4,480)),2)=7,2,0))),((EDATE($B$4,480))+IF(WEEKDAY((EDATE($B$4,480)),2)=6,2,IF(WEEKDAY((EDATE($B$4,480)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C62" s="28">
@@ -38180,8 +41006,8 @@
           <t>41Y</t>
         </is>
       </c>
-      <c r="B63" s="18">
-        <f>EDATE($B$4,492)</f>
+      <c r="B63" s="86">
+        <f>IF(MONTH(((EDATE($B$4,492))+IF(WEEKDAY((EDATE($B$4,492)),2)=6,2,IF(WEEKDAY((EDATE($B$4,492)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,492))),((EDATE($B$4,492))-IF(WEEKDAY((EDATE($B$4,492)),2)=6,1,IF(WEEKDAY((EDATE($B$4,492)),2)=7,2,0))),((EDATE($B$4,492))+IF(WEEKDAY((EDATE($B$4,492)),2)=6,2,IF(WEEKDAY((EDATE($B$4,492)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C63" s="28">
@@ -38257,8 +41083,8 @@
           <t>42Y</t>
         </is>
       </c>
-      <c r="B64" s="18">
-        <f>EDATE($B$4,504)</f>
+      <c r="B64" s="86">
+        <f>IF(MONTH(((EDATE($B$4,504))+IF(WEEKDAY((EDATE($B$4,504)),2)=6,2,IF(WEEKDAY((EDATE($B$4,504)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,504))),((EDATE($B$4,504))-IF(WEEKDAY((EDATE($B$4,504)),2)=6,1,IF(WEEKDAY((EDATE($B$4,504)),2)=7,2,0))),((EDATE($B$4,504))+IF(WEEKDAY((EDATE($B$4,504)),2)=6,2,IF(WEEKDAY((EDATE($B$4,504)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C64" s="28">
@@ -38334,8 +41160,8 @@
           <t>43Y</t>
         </is>
       </c>
-      <c r="B65" s="18">
-        <f>EDATE($B$4,516)</f>
+      <c r="B65" s="86">
+        <f>IF(MONTH(((EDATE($B$4,516))+IF(WEEKDAY((EDATE($B$4,516)),2)=6,2,IF(WEEKDAY((EDATE($B$4,516)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,516))),((EDATE($B$4,516))-IF(WEEKDAY((EDATE($B$4,516)),2)=6,1,IF(WEEKDAY((EDATE($B$4,516)),2)=7,2,0))),((EDATE($B$4,516))+IF(WEEKDAY((EDATE($B$4,516)),2)=6,2,IF(WEEKDAY((EDATE($B$4,516)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C65" s="28">
@@ -38411,8 +41237,8 @@
           <t>44Y</t>
         </is>
       </c>
-      <c r="B66" s="18">
-        <f>EDATE($B$4,528)</f>
+      <c r="B66" s="86">
+        <f>IF(MONTH(((EDATE($B$4,528))+IF(WEEKDAY((EDATE($B$4,528)),2)=6,2,IF(WEEKDAY((EDATE($B$4,528)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,528))),((EDATE($B$4,528))-IF(WEEKDAY((EDATE($B$4,528)),2)=6,1,IF(WEEKDAY((EDATE($B$4,528)),2)=7,2,0))),((EDATE($B$4,528))+IF(WEEKDAY((EDATE($B$4,528)),2)=6,2,IF(WEEKDAY((EDATE($B$4,528)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C66" s="28">
@@ -38488,8 +41314,8 @@
           <t>45Y</t>
         </is>
       </c>
-      <c r="B67" s="18">
-        <f>EDATE($B$4,540)</f>
+      <c r="B67" s="86">
+        <f>IF(MONTH(((EDATE($B$4,540))+IF(WEEKDAY((EDATE($B$4,540)),2)=6,2,IF(WEEKDAY((EDATE($B$4,540)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,540))),((EDATE($B$4,540))-IF(WEEKDAY((EDATE($B$4,540)),2)=6,1,IF(WEEKDAY((EDATE($B$4,540)),2)=7,2,0))),((EDATE($B$4,540))+IF(WEEKDAY((EDATE($B$4,540)),2)=6,2,IF(WEEKDAY((EDATE($B$4,540)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C67" s="28">
@@ -38565,8 +41391,8 @@
           <t>46Y</t>
         </is>
       </c>
-      <c r="B68" s="18">
-        <f>EDATE($B$4,552)</f>
+      <c r="B68" s="86">
+        <f>IF(MONTH(((EDATE($B$4,552))+IF(WEEKDAY((EDATE($B$4,552)),2)=6,2,IF(WEEKDAY((EDATE($B$4,552)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,552))),((EDATE($B$4,552))-IF(WEEKDAY((EDATE($B$4,552)),2)=6,1,IF(WEEKDAY((EDATE($B$4,552)),2)=7,2,0))),((EDATE($B$4,552))+IF(WEEKDAY((EDATE($B$4,552)),2)=6,2,IF(WEEKDAY((EDATE($B$4,552)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C68" s="28">
@@ -38642,8 +41468,8 @@
           <t>47Y</t>
         </is>
       </c>
-      <c r="B69" s="18">
-        <f>EDATE($B$4,564)</f>
+      <c r="B69" s="86">
+        <f>IF(MONTH(((EDATE($B$4,564))+IF(WEEKDAY((EDATE($B$4,564)),2)=6,2,IF(WEEKDAY((EDATE($B$4,564)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,564))),((EDATE($B$4,564))-IF(WEEKDAY((EDATE($B$4,564)),2)=6,1,IF(WEEKDAY((EDATE($B$4,564)),2)=7,2,0))),((EDATE($B$4,564))+IF(WEEKDAY((EDATE($B$4,564)),2)=6,2,IF(WEEKDAY((EDATE($B$4,564)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C69" s="28">
@@ -38719,8 +41545,8 @@
           <t>48Y</t>
         </is>
       </c>
-      <c r="B70" s="18">
-        <f>EDATE($B$4,576)</f>
+      <c r="B70" s="86">
+        <f>IF(MONTH(((EDATE($B$4,576))+IF(WEEKDAY((EDATE($B$4,576)),2)=6,2,IF(WEEKDAY((EDATE($B$4,576)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,576))),((EDATE($B$4,576))-IF(WEEKDAY((EDATE($B$4,576)),2)=6,1,IF(WEEKDAY((EDATE($B$4,576)),2)=7,2,0))),((EDATE($B$4,576))+IF(WEEKDAY((EDATE($B$4,576)),2)=6,2,IF(WEEKDAY((EDATE($B$4,576)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C70" s="28">
@@ -38796,8 +41622,8 @@
           <t>49Y</t>
         </is>
       </c>
-      <c r="B71" s="18">
-        <f>EDATE($B$4,588)</f>
+      <c r="B71" s="86">
+        <f>IF(MONTH(((EDATE($B$4,588))+IF(WEEKDAY((EDATE($B$4,588)),2)=6,2,IF(WEEKDAY((EDATE($B$4,588)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,588))),((EDATE($B$4,588))-IF(WEEKDAY((EDATE($B$4,588)),2)=6,1,IF(WEEKDAY((EDATE($B$4,588)),2)=7,2,0))),((EDATE($B$4,588))+IF(WEEKDAY((EDATE($B$4,588)),2)=6,2,IF(WEEKDAY((EDATE($B$4,588)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C71" s="28">
@@ -38873,8 +41699,8 @@
           <t>50Y</t>
         </is>
       </c>
-      <c r="B72" s="18">
-        <f>EDATE($B$4,600)</f>
+      <c r="B72" s="86">
+        <f>IF(MONTH(((EDATE($B$4,600))+IF(WEEKDAY((EDATE($B$4,600)),2)=6,2,IF(WEEKDAY((EDATE($B$4,600)),2)=7,1,0))))&lt;&gt;MONTH((EDATE($B$4,600))),((EDATE($B$4,600))-IF(WEEKDAY((EDATE($B$4,600)),2)=6,1,IF(WEEKDAY((EDATE($B$4,600)),2)=7,2,0))),((EDATE($B$4,600))+IF(WEEKDAY((EDATE($B$4,600)),2)=6,2,IF(WEEKDAY((EDATE($B$4,600)),2)=7,1,0))))</f>
         <v/>
       </c>
       <c r="C72" s="28">
@@ -38967,6 +41793,1266 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="006A1B9A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="67" t="inlineStr">
+        <is>
+          <t>S490_Target — replication check vs the Bloomberg Curve Analysis screen</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="65" t="inlineStr">
+        <is>
+          <t>Screen: YCSW0490 USD SOFR (vs FIXED), Cont, curve date 07/21/2026, shift +0.00bp. Source: user-supplied photo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="65" t="inlineStr">
+        <is>
+          <t>Model columns look the date up in Bootstrap!B and read that row's zero rate (J) and discount factor (H). Diffs are model - screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="65" t="inlineStr">
+        <is>
+          <t>Valid only when VAL_DATE = 07/21/2026. Cell B5 warns if it is not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="67" t="inlineStr">
+        <is>
+          <t>VAL_DATE check</t>
+        </is>
+      </c>
+      <c r="B5" s="87">
+        <f>IF(VAL_DATE=DATE(2026,7,21),"OK - dates align","VAL_DATE is not 07/21/2026: comparison not meaningful")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>SCREEN TARGET vs MODEL</t>
+        </is>
+      </c>
+      <c r="B7" s="74" t="n"/>
+      <c r="C7" s="74" t="n"/>
+      <c r="D7" s="74" t="n"/>
+      <c r="E7" s="74" t="n"/>
+      <c r="F7" s="74" t="n"/>
+      <c r="G7" s="74" t="n"/>
+      <c r="H7" s="74" t="n"/>
+      <c r="I7" s="74" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B8" s="62" t="inlineStr">
+        <is>
+          <t>Market rate</t>
+        </is>
+      </c>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>Zero (screen)</t>
+        </is>
+      </c>
+      <c r="D8" s="62" t="inlineStr">
+        <is>
+          <t>DF (screen)</t>
+        </is>
+      </c>
+      <c r="E8" s="62" t="inlineStr">
+        <is>
+          <t>Zero (model)</t>
+        </is>
+      </c>
+      <c r="F8" s="62" t="inlineStr">
+        <is>
+          <t>DF (model)</t>
+        </is>
+      </c>
+      <c r="G8" s="62" t="inlineStr">
+        <is>
+          <t>Zero diff (bp)</t>
+        </is>
+      </c>
+      <c r="H8" s="62" t="inlineStr">
+        <is>
+          <t>DF diff</t>
+        </is>
+      </c>
+      <c r="I8" s="62" t="inlineStr">
+        <is>
+          <t>Bootstrap row</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="88" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B9" s="85" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="C9" s="85" t="n">
+        <v>3.67912</v>
+      </c>
+      <c r="D9" s="69" t="n">
+        <v>0.999093</v>
+      </c>
+      <c r="E9" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A9,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A9,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G9" s="89">
+        <f>IF(E9="","",(E9-C9)*100)</f>
+        <v/>
+      </c>
+      <c r="H9" s="72">
+        <f>IF(F9="","",F9-D9)</f>
+        <v/>
+      </c>
+      <c r="I9" s="78">
+        <f>IFERROR(MATCH(A9,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="88" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B10" s="85" t="n">
+        <v>3.672</v>
+      </c>
+      <c r="C10" s="85" t="n">
+        <v>3.71519</v>
+      </c>
+      <c r="D10" s="69" t="n">
+        <v>0.998373</v>
+      </c>
+      <c r="E10" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A10,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A10,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G10" s="89">
+        <f>IF(E10="","",(E10-C10)*100)</f>
+        <v/>
+      </c>
+      <c r="H10" s="72">
+        <f>IF(F10="","",F10-D10)</f>
+        <v/>
+      </c>
+      <c r="I10" s="78">
+        <f>IFERROR(MATCH(A10,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="88" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B11" s="85" t="n">
+        <v>3.6699</v>
+      </c>
+      <c r="C11" s="85" t="n">
+        <v>3.71361</v>
+      </c>
+      <c r="D11" s="69" t="n">
+        <v>0.997663</v>
+      </c>
+      <c r="E11" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A11,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A11,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G11" s="89">
+        <f>IF(E11="","",(E11-C11)*100)</f>
+        <v/>
+      </c>
+      <c r="H11" s="72">
+        <f>IF(F11="","",F11-D11)</f>
+        <v/>
+      </c>
+      <c r="I11" s="78">
+        <f>IFERROR(MATCH(A11,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="88" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B12" s="85" t="n">
+        <v>3.6789</v>
+      </c>
+      <c r="C12" s="85" t="n">
+        <v>3.72127</v>
+      </c>
+      <c r="D12" s="69" t="n">
+        <v>0.99654</v>
+      </c>
+      <c r="E12" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A12,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A12,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G12" s="89">
+        <f>IF(E12="","",(E12-C12)*100)</f>
+        <v/>
+      </c>
+      <c r="H12" s="72">
+        <f>IF(F12="","",F12-D12)</f>
+        <v/>
+      </c>
+      <c r="I12" s="78">
+        <f>IFERROR(MATCH(A12,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="88" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B13" s="85" t="n">
+        <v>3.70344</v>
+      </c>
+      <c r="C13" s="85" t="n">
+        <v>3.74096</v>
+      </c>
+      <c r="D13" s="69" t="n">
+        <v>0.993462</v>
+      </c>
+      <c r="E13" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A13,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A13,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G13" s="89">
+        <f>IF(E13="","",(E13-C13)*100)</f>
+        <v/>
+      </c>
+      <c r="H13" s="72">
+        <f>IF(F13="","",F13-D13)</f>
+        <v/>
+      </c>
+      <c r="I13" s="78">
+        <f>IFERROR(MATCH(A13,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="88" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B14" s="85" t="n">
+        <v>3.75285</v>
+      </c>
+      <c r="C14" s="85" t="n">
+        <v>3.78455</v>
+      </c>
+      <c r="D14" s="69" t="n">
+        <v>0.990301</v>
+      </c>
+      <c r="E14" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A14,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A14,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G14" s="89">
+        <f>IF(E14="","",(E14-C14)*100)</f>
+        <v/>
+      </c>
+      <c r="H14" s="72">
+        <f>IF(F14="","",F14-D14)</f>
+        <v/>
+      </c>
+      <c r="I14" s="78">
+        <f>IFERROR(MATCH(A14,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="88" t="n">
+        <v>46349</v>
+      </c>
+      <c r="B15" s="85" t="n">
+        <v>3.79575</v>
+      </c>
+      <c r="C15" s="85" t="n">
+        <v>3.82141</v>
+      </c>
+      <c r="D15" s="69" t="n">
+        <v>0.986998</v>
+      </c>
+      <c r="E15" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A15,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A15,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G15" s="89">
+        <f>IF(E15="","",(E15-C15)*100)</f>
+        <v/>
+      </c>
+      <c r="H15" s="72">
+        <f>IF(F15="","",F15-D15)</f>
+        <v/>
+      </c>
+      <c r="I15" s="78">
+        <f>IFERROR(MATCH(A15,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="88" t="n">
+        <v>46379</v>
+      </c>
+      <c r="B16" s="85" t="n">
+        <v>3.83435</v>
+      </c>
+      <c r="C16" s="85" t="n">
+        <v>3.85398</v>
+      </c>
+      <c r="D16" s="69" t="n">
+        <v>0.9837669999999999</v>
+      </c>
+      <c r="E16" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A16,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A16,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G16" s="89">
+        <f>IF(E16="","",(E16-C16)*100)</f>
+        <v/>
+      </c>
+      <c r="H16" s="72">
+        <f>IF(F16="","",F16-D16)</f>
+        <v/>
+      </c>
+      <c r="I16" s="78">
+        <f>IFERROR(MATCH(A16,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="88" t="n">
+        <v>46412</v>
+      </c>
+      <c r="B17" s="85" t="n">
+        <v>3.87725</v>
+      </c>
+      <c r="C17" s="85" t="n">
+        <v>3.88998</v>
+      </c>
+      <c r="D17" s="69" t="n">
+        <v>0.980163</v>
+      </c>
+      <c r="E17" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A17,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A17,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G17" s="89">
+        <f>IF(E17="","",(E17-C17)*100)</f>
+        <v/>
+      </c>
+      <c r="H17" s="72">
+        <f>IF(F17="","",F17-D17)</f>
+        <v/>
+      </c>
+      <c r="I17" s="78">
+        <f>IFERROR(MATCH(A17,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="88" t="n">
+        <v>46441</v>
+      </c>
+      <c r="B18" s="85" t="n">
+        <v>3.9082</v>
+      </c>
+      <c r="C18" s="85" t="n">
+        <v>3.91475</v>
+      </c>
+      <c r="D18" s="69" t="n">
+        <v>0.9769949999999999</v>
+      </c>
+      <c r="E18" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A18,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A18,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G18" s="89">
+        <f>IF(E18="","",(E18-C18)*100)</f>
+        <v/>
+      </c>
+      <c r="H18" s="72">
+        <f>IF(F18="","",F18-D18)</f>
+        <v/>
+      </c>
+      <c r="I18" s="78">
+        <f>IFERROR(MATCH(A18,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="88" t="n">
+        <v>46469</v>
+      </c>
+      <c r="B19" s="85" t="n">
+        <v>3.9345</v>
+      </c>
+      <c r="C19" s="85" t="n">
+        <v>3.93499</v>
+      </c>
+      <c r="D19" s="69" t="n">
+        <v>0.973933</v>
+      </c>
+      <c r="E19" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A19,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A19,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G19" s="89">
+        <f>IF(E19="","",(E19-C19)*100)</f>
+        <v/>
+      </c>
+      <c r="H19" s="72">
+        <f>IF(F19="","",F19-D19)</f>
+        <v/>
+      </c>
+      <c r="I19" s="78">
+        <f>IFERROR(MATCH(A19,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="88" t="n">
+        <v>46500</v>
+      </c>
+      <c r="B20" s="85" t="n">
+        <v>3.96295</v>
+      </c>
+      <c r="C20" s="85" t="n">
+        <v>3.95656</v>
+      </c>
+      <c r="D20" s="69" t="n">
+        <v>0.970525</v>
+      </c>
+      <c r="E20" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A20,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A20,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G20" s="89">
+        <f>IF(E20="","",(E20-C20)*100)</f>
+        <v/>
+      </c>
+      <c r="H20" s="72">
+        <f>IF(F20="","",F20-D20)</f>
+        <v/>
+      </c>
+      <c r="I20" s="78">
+        <f>IFERROR(MATCH(A20,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="88" t="n">
+        <v>46531</v>
+      </c>
+      <c r="B21" s="85" t="n">
+        <v>3.9886</v>
+      </c>
+      <c r="C21" s="85" t="n">
+        <v>3.97523</v>
+      </c>
+      <c r="D21" s="69" t="n">
+        <v>0.967117</v>
+      </c>
+      <c r="E21" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A21,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A21,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G21" s="89">
+        <f>IF(E21="","",(E21-C21)*100)</f>
+        <v/>
+      </c>
+      <c r="H21" s="72">
+        <f>IF(F21="","",F21-D21)</f>
+        <v/>
+      </c>
+      <c r="I21" s="78">
+        <f>IFERROR(MATCH(A21,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="88" t="n">
+        <v>46561</v>
+      </c>
+      <c r="B22" s="85" t="n">
+        <v>4.01085</v>
+      </c>
+      <c r="C22" s="85" t="n">
+        <v>3.99064</v>
+      </c>
+      <c r="D22" s="69" t="n">
+        <v>0.963825</v>
+      </c>
+      <c r="E22" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A22,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A22,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G22" s="89">
+        <f>IF(E22="","",(E22-C22)*100)</f>
+        <v/>
+      </c>
+      <c r="H22" s="72">
+        <f>IF(F22="","",F22-D22)</f>
+        <v/>
+      </c>
+      <c r="I22" s="78">
+        <f>IFERROR(MATCH(A22,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="88" t="n">
+        <v>46591</v>
+      </c>
+      <c r="B23" s="85" t="n">
+        <v>4.0303</v>
+      </c>
+      <c r="C23" s="85" t="n">
+        <v>4.00322</v>
+      </c>
+      <c r="D23" s="69" t="n">
+        <v>0.960548</v>
+      </c>
+      <c r="E23" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A23,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A23,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G23" s="89">
+        <f>IF(E23="","",(E23-C23)*100)</f>
+        <v/>
+      </c>
+      <c r="H23" s="72">
+        <f>IF(F23="","",F23-D23)</f>
+        <v/>
+      </c>
+      <c r="I23" s="78">
+        <f>IFERROR(MATCH(A23,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="88" t="n">
+        <v>46776</v>
+      </c>
+      <c r="B24" s="85" t="n">
+        <v>4.04559</v>
+      </c>
+      <c r="C24" s="85" t="n">
+        <v>4.03332</v>
+      </c>
+      <c r="D24" s="69" t="n">
+        <v>0.9408260000000001</v>
+      </c>
+      <c r="E24" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A24,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A24,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G24" s="89">
+        <f>IF(E24="","",(E24-C24)*100)</f>
+        <v/>
+      </c>
+      <c r="H24" s="72">
+        <f>IF(F24="","",F24-D24)</f>
+        <v/>
+      </c>
+      <c r="I24" s="78">
+        <f>IFERROR(MATCH(A24,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="88" t="n">
+        <v>46958</v>
+      </c>
+      <c r="B25" s="85" t="n">
+        <v>4.0511</v>
+      </c>
+      <c r="C25" s="85" t="n">
+        <v>4.0245</v>
+      </c>
+      <c r="D25" s="69" t="n">
+        <v>0.922257</v>
+      </c>
+      <c r="E25" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A25,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A25,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G25" s="89">
+        <f>IF(E25="","",(E25-C25)*100)</f>
+        <v/>
+      </c>
+      <c r="H25" s="72">
+        <f>IF(F25="","",F25-D25)</f>
+        <v/>
+      </c>
+      <c r="I25" s="78">
+        <f>IFERROR(MATCH(A25,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="88" t="n">
+        <v>47322</v>
+      </c>
+      <c r="B26" s="85" t="n">
+        <v>4.03145</v>
+      </c>
+      <c r="C26" s="85" t="n">
+        <v>4.00493</v>
+      </c>
+      <c r="D26" s="69" t="n">
+        <v>0.886497</v>
+      </c>
+      <c r="E26" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A26,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A26,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G26" s="89">
+        <f>IF(E26="","",(E26-C26)*100)</f>
+        <v/>
+      </c>
+      <c r="H26" s="72">
+        <f>IF(F26="","",F26-D26)</f>
+        <v/>
+      </c>
+      <c r="I26" s="78">
+        <f>IFERROR(MATCH(A26,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="88" t="n">
+        <v>47687</v>
+      </c>
+      <c r="B27" s="85" t="n">
+        <v>4.0236</v>
+      </c>
+      <c r="C27" s="85" t="n">
+        <v>3.99711</v>
+      </c>
+      <c r="D27" s="69" t="n">
+        <v>0.851962</v>
+      </c>
+      <c r="E27" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A27,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A27,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G27" s="89">
+        <f>IF(E27="","",(E27-C27)*100)</f>
+        <v/>
+      </c>
+      <c r="H27" s="72">
+        <f>IF(F27="","",F27-D27)</f>
+        <v/>
+      </c>
+      <c r="I27" s="78">
+        <f>IFERROR(MATCH(A27,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="88" t="n">
+        <v>48052</v>
+      </c>
+      <c r="B28" s="85" t="n">
+        <v>4.0314</v>
+      </c>
+      <c r="C28" s="85" t="n">
+        <v>4.00561</v>
+      </c>
+      <c r="D28" s="69" t="n">
+        <v>0.818232</v>
+      </c>
+      <c r="E28" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A28,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A28,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G28" s="89">
+        <f>IF(E28="","",(E28-C28)*100)</f>
+        <v/>
+      </c>
+      <c r="H28" s="72">
+        <f>IF(F28="","",F28-D28)</f>
+        <v/>
+      </c>
+      <c r="I28" s="78">
+        <f>IFERROR(MATCH(A28,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="88" t="n">
+        <v>48418</v>
+      </c>
+      <c r="B29" s="85" t="n">
+        <v>4.05176</v>
+      </c>
+      <c r="C29" s="85" t="n">
+        <v>4.02762</v>
+      </c>
+      <c r="D29" s="69" t="n">
+        <v>0.784979</v>
+      </c>
+      <c r="E29" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A29,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A29,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G29" s="89">
+        <f>IF(E29="","",(E29-C29)*100)</f>
+        <v/>
+      </c>
+      <c r="H29" s="72">
+        <f>IF(F29="","",F29-D29)</f>
+        <v/>
+      </c>
+      <c r="I29" s="78">
+        <f>IFERROR(MATCH(A29,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="88" t="n">
+        <v>48785</v>
+      </c>
+      <c r="B30" s="85" t="n">
+        <v>4.07793</v>
+      </c>
+      <c r="C30" s="85" t="n">
+        <v>4.05617</v>
+      </c>
+      <c r="D30" s="69" t="n">
+        <v>0.752316</v>
+      </c>
+      <c r="E30" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A30,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A30,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G30" s="89">
+        <f>IF(E30="","",(E30-C30)*100)</f>
+        <v/>
+      </c>
+      <c r="H30" s="72">
+        <f>IF(F30="","",F30-D30)</f>
+        <v/>
+      </c>
+      <c r="I30" s="78">
+        <f>IFERROR(MATCH(A30,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="88" t="n">
+        <v>49149</v>
+      </c>
+      <c r="B31" s="85" t="n">
+        <v>4.10695</v>
+      </c>
+      <c r="C31" s="85" t="n">
+        <v>4.08837</v>
+      </c>
+      <c r="D31" s="69" t="n">
+        <v>0.72063</v>
+      </c>
+      <c r="E31" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A31,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A31,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G31" s="89">
+        <f>IF(E31="","",(E31-C31)*100)</f>
+        <v/>
+      </c>
+      <c r="H31" s="72">
+        <f>IF(F31="","",F31-D31)</f>
+        <v/>
+      </c>
+      <c r="I31" s="78">
+        <f>IFERROR(MATCH(A31,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="88" t="n">
+        <v>49513</v>
+      </c>
+      <c r="B32" s="85" t="n">
+        <v>4.13825</v>
+      </c>
+      <c r="C32" s="85" t="n">
+        <v>4.12361</v>
+      </c>
+      <c r="D32" s="69" t="n">
+        <v>0.689646</v>
+      </c>
+      <c r="E32" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A32,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A32,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G32" s="89">
+        <f>IF(E32="","",(E32-C32)*100)</f>
+        <v/>
+      </c>
+      <c r="H32" s="72">
+        <f>IF(F32="","",F32-D32)</f>
+        <v/>
+      </c>
+      <c r="I32" s="78">
+        <f>IFERROR(MATCH(A32,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="88" t="n">
+        <v>49879</v>
+      </c>
+      <c r="B33" s="85" t="n">
+        <v>4.17165</v>
+      </c>
+      <c r="C33" s="85" t="n">
+        <v>4.1618</v>
+      </c>
+      <c r="D33" s="69" t="n">
+        <v>0.659186</v>
+      </c>
+      <c r="E33" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A33,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A33,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G33" s="89">
+        <f>IF(E33="","",(E33-C33)*100)</f>
+        <v/>
+      </c>
+      <c r="H33" s="72">
+        <f>IF(F33="","",F33-D33)</f>
+        <v/>
+      </c>
+      <c r="I33" s="78">
+        <f>IFERROR(MATCH(A33,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="88" t="n">
+        <v>50609</v>
+      </c>
+      <c r="B34" s="85" t="n">
+        <v>4.23854</v>
+      </c>
+      <c r="C34" s="85" t="n">
+        <v>4.24016</v>
+      </c>
+      <c r="D34" s="69" t="n">
+        <v>0.6008559999999999</v>
+      </c>
+      <c r="E34" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A34,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A34,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G34" s="89">
+        <f>IF(E34="","",(E34-C34)*100)</f>
+        <v/>
+      </c>
+      <c r="H34" s="72">
+        <f>IF(F34="","",F34-D34)</f>
+        <v/>
+      </c>
+      <c r="I34" s="78">
+        <f>IFERROR(MATCH(A34,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="88" t="n">
+        <v>51705</v>
+      </c>
+      <c r="B35" s="85" t="n">
+        <v>4.32638</v>
+      </c>
+      <c r="C35" s="85" t="n">
+        <v>4.34698</v>
+      </c>
+      <c r="D35" s="69" t="n">
+        <v>0.520606</v>
+      </c>
+      <c r="E35" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A35,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A35,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G35" s="89">
+        <f>IF(E35="","",(E35-C35)*100)</f>
+        <v/>
+      </c>
+      <c r="H35" s="72">
+        <f>IF(F35="","",F35-D35)</f>
+        <v/>
+      </c>
+      <c r="I35" s="78">
+        <f>IFERROR(MATCH(A35,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="88" t="n">
+        <v>53531</v>
+      </c>
+      <c r="B36" s="85" t="n">
+        <v>4.4013</v>
+      </c>
+      <c r="C36" s="85" t="n">
+        <v>4.43911</v>
+      </c>
+      <c r="D36" s="69" t="n">
+        <v>0.411201</v>
+      </c>
+      <c r="E36" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A36,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A36,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G36" s="89">
+        <f>IF(E36="","",(E36-C36)*100)</f>
+        <v/>
+      </c>
+      <c r="H36" s="72">
+        <f>IF(F36="","",F36-D36)</f>
+        <v/>
+      </c>
+      <c r="I36" s="78">
+        <f>IFERROR(MATCH(A36,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="88" t="n">
+        <v>55358</v>
+      </c>
+      <c r="B37" s="85" t="n">
+        <v>4.40005</v>
+      </c>
+      <c r="C37" s="85" t="n">
+        <v>4.42239</v>
+      </c>
+      <c r="D37" s="69" t="n">
+        <v>0.330652</v>
+      </c>
+      <c r="E37" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A37,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A37,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G37" s="89">
+        <f>IF(E37="","",(E37-C37)*100)</f>
+        <v/>
+      </c>
+      <c r="H37" s="72">
+        <f>IF(F37="","",F37-D37)</f>
+        <v/>
+      </c>
+      <c r="I37" s="78">
+        <f>IFERROR(MATCH(A37,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="88" t="n">
+        <v>57185</v>
+      </c>
+      <c r="B38" s="85" t="n">
+        <v>4.36277</v>
+      </c>
+      <c r="C38" s="85" t="n">
+        <v>4.34509</v>
+      </c>
+      <c r="D38" s="69" t="n">
+        <v>0.271217</v>
+      </c>
+      <c r="E38" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A38,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A38,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G38" s="89">
+        <f>IF(E38="","",(E38-C38)*100)</f>
+        <v/>
+      </c>
+      <c r="H38" s="72">
+        <f>IF(F38="","",F38-D38)</f>
+        <v/>
+      </c>
+      <c r="I38" s="78">
+        <f>IFERROR(MATCH(A38,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="88" t="n">
+        <v>60836</v>
+      </c>
+      <c r="B39" s="85" t="n">
+        <v>4.2436</v>
+      </c>
+      <c r="C39" s="85" t="n">
+        <v>4.10058</v>
+      </c>
+      <c r="D39" s="69" t="n">
+        <v>0.193674</v>
+      </c>
+      <c r="E39" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A39,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A39,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G39" s="89">
+        <f>IF(E39="","",(E39-C39)*100)</f>
+        <v/>
+      </c>
+      <c r="H39" s="72">
+        <f>IF(F39="","",F39-D39)</f>
+        <v/>
+      </c>
+      <c r="I39" s="78">
+        <f>IFERROR(MATCH(A39,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="88" t="n">
+        <v>64489</v>
+      </c>
+      <c r="B40" s="85" t="n">
+        <v>4.11027</v>
+      </c>
+      <c r="C40" s="85" t="n">
+        <v>3.80584</v>
+      </c>
+      <c r="D40" s="69" t="n">
+        <v>0.148899</v>
+      </c>
+      <c r="E40" s="84">
+        <f>IFERROR(INDEX(Bootstrap!$J$8:$J$72,MATCH(A40,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="80">
+        <f>IFERROR(INDEX(Bootstrap!$H$8:$H$72,MATCH(A40,Bootstrap!$B$8:$B$72,0)),"")</f>
+        <v/>
+      </c>
+      <c r="G40" s="89">
+        <f>IF(E40="","",(E40-C40)*100)</f>
+        <v/>
+      </c>
+      <c r="H40" s="72">
+        <f>IF(F40="","",F40-D40)</f>
+        <v/>
+      </c>
+      <c r="I40" s="78">
+        <f>IFERROR(MATCH(A40,Bootstrap!$B$8:$B$72,0)+7,"not found")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="67" t="inlineStr">
+        <is>
+          <t>Max |zero diff| (bp)</t>
+        </is>
+      </c>
+      <c r="B42" s="90">
+        <f>MAX(ABS(G9:G40))</f>
+        <v/>
+      </c>
+      <c r="D42" s="65" t="inlineStr">
+        <is>
+          <t>Array formula — confirm with Ctrl+Shift+Enter in older Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="67" t="inlineStr">
+        <is>
+          <t>Max |DF diff|</t>
+        </is>
+      </c>
+      <c r="B43" s="91">
+        <f>MAX(ABS(H9:H40))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="67" t="inlineStr">
+        <is>
+          <t>Pillars matched</t>
+        </is>
+      </c>
+      <c r="B44" s="87">
+        <f>COUNT(E9:E40)&amp;" / 32"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="65" t="inlineStr">
+        <is>
+          <t>Independent Python replication of this construction achieved max |DF err| 1.2e-05 and max |zero err| 0.26bp (0.00bp from 6M out); residuals sit at the screen's 6-decimal display precision.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="002E7D32"/>
@@ -55851,7 +59937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58557,2711 +62643,4 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="1" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Swap_Pricer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dynamic Fixed-vs-SOFR OIS valuation (SWPM-style), priced off the Bootstrap curve — every cell is live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>DEAL — Fixed vs SOFR OIS   (yellow = inputs; everything else is computed)</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>Discount curve (from Bootstrap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Direction (Leg 1 = Fixed)</t>
-        </is>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>Receive fixed</t>
-        </is>
-      </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Curve date</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Notional</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="C6" s="38" t="inlineStr">
-        <is>
-          <t>Both legs, USD.</t>
-        </is>
-      </c>
-      <c r="K6" s="18">
-        <f>Bootstrap!$B$4</f>
-        <v/>
-      </c>
-      <c r="L6" s="36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="K7" s="18">
-        <f>Bootstrap!B8</f>
-        <v/>
-      </c>
-      <c r="L7" s="36">
-        <f>Bootstrap!H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Effective date</t>
-        </is>
-      </c>
-      <c r="B8" s="40">
-        <f>Bootstrap!$B$4</f>
-        <v/>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
-        </is>
-      </c>
-      <c r="K8" s="18">
-        <f>Bootstrap!B9</f>
-        <v/>
-      </c>
-      <c r="L8" s="36">
-        <f>Bootstrap!H9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Tenor (years)</t>
-        </is>
-      </c>
-      <c r="B9" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>Whole years; drives the annual coupon schedule below.</t>
-        </is>
-      </c>
-      <c r="K9" s="18">
-        <f>Bootstrap!B10</f>
-        <v/>
-      </c>
-      <c r="L9" s="36">
-        <f>Bootstrap!H10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Maturity date</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>EDATE(B8,12*B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Effective + Tenor.</t>
-        </is>
-      </c>
-      <c r="K10" s="18">
-        <f>Bootstrap!B11</f>
-        <v/>
-      </c>
-      <c r="L10" s="36">
-        <f>Bootstrap!H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Fixed coupon (%)</t>
-        </is>
-      </c>
-      <c r="B11" s="42">
-        <f>B25</f>
-        <v/>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
-        </is>
-      </c>
-      <c r="K11" s="18">
-        <f>Bootstrap!B12</f>
-        <v/>
-      </c>
-      <c r="L11" s="36">
-        <f>Bootstrap!H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Fixed pay frequency</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="K12" s="18">
-        <f>Bootstrap!B13</f>
-        <v/>
-      </c>
-      <c r="L12" s="36">
-        <f>Bootstrap!H13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Fixed day count</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>ACT/360</t>
-        </is>
-      </c>
-      <c r="K13" s="18">
-        <f>Bootstrap!B14</f>
-        <v/>
-      </c>
-      <c r="L13" s="36">
-        <f>Bootstrap!H14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Float index</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>SOFR (daily compounded, single-curve)</t>
-        </is>
-      </c>
-      <c r="K14" s="18">
-        <f>Bootstrap!B15</f>
-        <v/>
-      </c>
-      <c r="L14" s="36">
-        <f>Bootstrap!H15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Curve / valuation date</t>
-        </is>
-      </c>
-      <c r="B15" s="18">
-        <f>VAL_DATE</f>
-        <v/>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
-        <is>
-          <t>Curve is discounted from spot = Bootstrap!B4.</t>
-        </is>
-      </c>
-      <c r="K15" s="18">
-        <f>Bootstrap!B16</f>
-        <v/>
-      </c>
-      <c r="L15" s="36">
-        <f>Bootstrap!H16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Direction sign (+recv / −pay)</t>
-        </is>
-      </c>
-      <c r="B16" s="43">
-        <f>IF($B$5="Receive fixed",1,-1)</f>
-        <v/>
-      </c>
-      <c r="K16" s="18">
-        <f>Bootstrap!B17</f>
-        <v/>
-      </c>
-      <c r="L16" s="36">
-        <f>Bootstrap!H17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="K17" s="18">
-        <f>Bootstrap!B18</f>
-        <v/>
-      </c>
-      <c r="L17" s="36">
-        <f>Bootstrap!H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>VALUATION RESULTS — single-curve OIS discounting</t>
-        </is>
-      </c>
-      <c r="K18" s="18">
-        <f>Bootstrap!B19</f>
-        <v/>
-      </c>
-      <c r="L18" s="36">
-        <f>Bootstrap!H19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>DF(effective)</t>
-        </is>
-      </c>
-      <c r="B19" s="36">
-        <f>IFERROR(INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)))^(($B$8-INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)))</f>
-        <v/>
-      </c>
-      <c r="C19" s="38" t="inlineStr">
-        <is>
-          <t>Interpolated from the curve.</t>
-        </is>
-      </c>
-      <c r="K19" s="18">
-        <f>Bootstrap!B20</f>
-        <v/>
-      </c>
-      <c r="L19" s="36">
-        <f>Bootstrap!H20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>DF(maturity)</t>
-        </is>
-      </c>
-      <c r="B20" s="36">
-        <f>IFERROR(INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)))^(($B$10-INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)))</f>
-        <v/>
-      </c>
-      <c r="K20" s="18">
-        <f>Bootstrap!B21</f>
-        <v/>
-      </c>
-      <c r="L20" s="36">
-        <f>Bootstrap!H21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Fixed annuity  Sum tau·DF</t>
-        </is>
-      </c>
-      <c r="B21" s="34">
-        <f>SUM(H36:H85)</f>
-        <v/>
-      </c>
-      <c r="C21" s="38" t="inlineStr">
-        <is>
-          <t>Sum of tau·DF over the fixed coupon dates.</t>
-        </is>
-      </c>
-      <c r="K21" s="18">
-        <f>Bootstrap!B22</f>
-        <v/>
-      </c>
-      <c r="L21" s="36">
-        <f>Bootstrap!H22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Fixed leg PV (coupons)</t>
-        </is>
-      </c>
-      <c r="B22" s="44">
-        <f>SUM(G36:G85)</f>
-        <v/>
-      </c>
-      <c r="K22" s="18">
-        <f>Bootstrap!B23</f>
-        <v/>
-      </c>
-      <c r="L22" s="36">
-        <f>Bootstrap!H23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Float leg PV</t>
-        </is>
-      </c>
-      <c r="B23" s="44">
-        <f>B6*(B19-B20)</f>
-        <v/>
-      </c>
-      <c r="C23" s="38" t="inlineStr">
-        <is>
-          <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
-        </is>
-      </c>
-      <c r="K23" s="18">
-        <f>Bootstrap!B24</f>
-        <v/>
-      </c>
-      <c r="L23" s="36">
-        <f>Bootstrap!H24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Notional PV @ maturity</t>
-        </is>
-      </c>
-      <c r="B24" s="44">
-        <f>B6*B20</f>
-        <v/>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>For the SWPM-style leg display only.</t>
-        </is>
-      </c>
-      <c r="K24" s="18">
-        <f>Bootstrap!B25</f>
-        <v/>
-      </c>
-      <c r="L24" s="36">
-        <f>Bootstrap!H25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Par coupon (%)</t>
-        </is>
-      </c>
-      <c r="B25" s="34">
-        <f>(B19-B20)/B21*100</f>
-        <v/>
-      </c>
-      <c r="C25" s="38" t="inlineStr">
-        <is>
-          <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
-        </is>
-      </c>
-      <c r="K25" s="18">
-        <f>Bootstrap!B26</f>
-        <v/>
-      </c>
-      <c r="L25" s="36">
-        <f>Bootstrap!H26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Leg 1 NPV  (fixed + notional)</t>
-        </is>
-      </c>
-      <c r="B26" s="44">
-        <f>B16*(B22+B24)</f>
-        <v/>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>SWPM shows each leg incl. a notional redemption.</t>
-        </is>
-      </c>
-      <c r="K26" s="18">
-        <f>Bootstrap!B27</f>
-        <v/>
-      </c>
-      <c r="L26" s="36">
-        <f>Bootstrap!H27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Leg 2 NPV  (float + notional)</t>
-        </is>
-      </c>
-      <c r="B27" s="44">
-        <f>-B16*(B23+B24)</f>
-        <v/>
-      </c>
-      <c r="K27" s="18">
-        <f>Bootstrap!B28</f>
-        <v/>
-      </c>
-      <c r="L27" s="36">
-        <f>Bootstrap!H28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Net swap NPV</t>
-        </is>
-      </c>
-      <c r="B28" s="45">
-        <f>B26+B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
-        </is>
-      </c>
-      <c r="K28" s="18">
-        <f>Bootstrap!B29</f>
-        <v/>
-      </c>
-      <c r="L28" s="36">
-        <f>Bootstrap!H29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>PV01 / DV01  (per 1bp)</t>
-        </is>
-      </c>
-      <c r="B29" s="44">
-        <f>B6*B21*0.0001</f>
-        <v/>
-      </c>
-      <c r="C29" s="38" t="inlineStr">
-        <is>
-          <t>Annuity × notional × 1bp.</t>
-        </is>
-      </c>
-      <c r="K29" s="18">
-        <f>Bootstrap!B30</f>
-        <v/>
-      </c>
-      <c r="L29" s="36">
-        <f>Bootstrap!H30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Accrued (at inception)</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="18">
-        <f>Bootstrap!B31</f>
-        <v/>
-      </c>
-      <c r="L30" s="36">
-        <f>Bootstrap!H31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="K31" s="18">
-        <f>Bootstrap!B32</f>
-        <v/>
-      </c>
-      <c r="L31" s="36">
-        <f>Bootstrap!H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Cross-check vs the SWPM screen: Par coupon and PV01 match (≈4.02%, ≈974 for a 10mm 1Y). SWPM's leg NPVs read ~9,995,534 rather than 10,000,000 because it discounts from curve date to a valuation date 2 business days after effective; here effective = spot so DF(effective) = 1 exactly. The net NPV, par coupon and DV01 are unaffected.</t>
-        </is>
-      </c>
-      <c r="K32" s="18">
-        <f>Bootstrap!B33</f>
-        <v/>
-      </c>
-      <c r="L32" s="36">
-        <f>Bootstrap!H33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="K33" s="18">
-        <f>Bootstrap!B34</f>
-        <v/>
-      </c>
-      <c r="L33" s="36">
-        <f>Bootstrap!H34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="K34" s="18">
-        <f>Bootstrap!B35</f>
-        <v/>
-      </c>
-      <c r="L34" s="36">
-        <f>Bootstrap!H35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Pay date</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>Prev date</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>tau ACT/360</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
-        <is>
-          <t>DF (interp)</t>
-        </is>
-      </c>
-      <c r="F35" s="20" t="inlineStr">
-        <is>
-          <t>Coupon CF</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>tau·DF</t>
-        </is>
-      </c>
-      <c r="K35" s="18">
-        <f>Bootstrap!B36</f>
-        <v/>
-      </c>
-      <c r="L35" s="36">
-        <f>Bootstrap!H36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B36" s="18">
-        <f>IF(A36&lt;=$B$9,EDATE($B$8,12*A36),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="18">
-        <f>IF(A36&lt;=$B$9,$B$8,"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="17">
-        <f>IF(A36&lt;=$B$9,(B36-C36)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="36">
-        <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1)))^((B36-INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="44">
-        <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="44">
-        <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="34">
-        <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="18">
-        <f>Bootstrap!B37</f>
-        <v/>
-      </c>
-      <c r="L36" s="36">
-        <f>Bootstrap!H37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B37" s="18">
-        <f>IF(A37&lt;=$B$9,EDATE($B$8,12*A37),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="18">
-        <f>IF(A37&lt;=$B$9,B36,"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="17">
-        <f>IF(A37&lt;=$B$9,(B37-C37)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="36">
-        <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1)))^((B37-INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="44">
-        <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="44">
-        <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="34">
-        <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="18">
-        <f>Bootstrap!B38</f>
-        <v/>
-      </c>
-      <c r="L37" s="36">
-        <f>Bootstrap!H38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B38" s="18">
-        <f>IF(A38&lt;=$B$9,EDATE($B$8,12*A38),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="18">
-        <f>IF(A38&lt;=$B$9,B37,"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="17">
-        <f>IF(A38&lt;=$B$9,(B38-C38)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E38" s="36">
-        <f>IF(A38&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1)))^((B38-INDEX($K$6:$K$71,MATCH(B38,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B38,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B38,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B38,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="44">
-        <f>IF(A38&lt;=$B$9,$B$6*$B$11/100*D38,"")</f>
-        <v/>
-      </c>
-      <c r="G38" s="44">
-        <f>IF(A38&lt;=$B$9,F38*E38,"")</f>
-        <v/>
-      </c>
-      <c r="H38" s="34">
-        <f>IF(A38&lt;=$B$9,D38*E38,"")</f>
-        <v/>
-      </c>
-      <c r="K38" s="18">
-        <f>Bootstrap!B39</f>
-        <v/>
-      </c>
-      <c r="L38" s="36">
-        <f>Bootstrap!H39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B39" s="18">
-        <f>IF(A39&lt;=$B$9,EDATE($B$8,12*A39),"")</f>
-        <v/>
-      </c>
-      <c r="C39" s="18">
-        <f>IF(A39&lt;=$B$9,B38,"")</f>
-        <v/>
-      </c>
-      <c r="D39" s="17">
-        <f>IF(A39&lt;=$B$9,(B39-C39)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E39" s="36">
-        <f>IF(A39&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1)))^((B39-INDEX($K$6:$K$71,MATCH(B39,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B39,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B39,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B39,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="44">
-        <f>IF(A39&lt;=$B$9,$B$6*$B$11/100*D39,"")</f>
-        <v/>
-      </c>
-      <c r="G39" s="44">
-        <f>IF(A39&lt;=$B$9,F39*E39,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="34">
-        <f>IF(A39&lt;=$B$9,D39*E39,"")</f>
-        <v/>
-      </c>
-      <c r="K39" s="46" t="inlineStr">
-        <is>
-          <t>Log-linear DF interpolation on this grid (dates $K$6:$K$71, DFs $L$6:$L$71).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B40" s="18">
-        <f>IF(A40&lt;=$B$9,EDATE($B$8,12*A40),"")</f>
-        <v/>
-      </c>
-      <c r="C40" s="18">
-        <f>IF(A40&lt;=$B$9,B39,"")</f>
-        <v/>
-      </c>
-      <c r="D40" s="17">
-        <f>IF(A40&lt;=$B$9,(B40-C40)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E40" s="36">
-        <f>IF(A40&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1)))^((B40-INDEX($K$6:$K$71,MATCH(B40,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B40,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B40,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B40,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="44">
-        <f>IF(A40&lt;=$B$9,$B$6*$B$11/100*D40,"")</f>
-        <v/>
-      </c>
-      <c r="G40" s="44">
-        <f>IF(A40&lt;=$B$9,F40*E40,"")</f>
-        <v/>
-      </c>
-      <c r="H40" s="34">
-        <f>IF(A40&lt;=$B$9,D40*E40,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B41" s="18">
-        <f>IF(A41&lt;=$B$9,EDATE($B$8,12*A41),"")</f>
-        <v/>
-      </c>
-      <c r="C41" s="18">
-        <f>IF(A41&lt;=$B$9,B40,"")</f>
-        <v/>
-      </c>
-      <c r="D41" s="17">
-        <f>IF(A41&lt;=$B$9,(B41-C41)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E41" s="36">
-        <f>IF(A41&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1)))^((B41-INDEX($K$6:$K$71,MATCH(B41,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B41,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B41,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B41,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="44">
-        <f>IF(A41&lt;=$B$9,$B$6*$B$11/100*D41,"")</f>
-        <v/>
-      </c>
-      <c r="G41" s="44">
-        <f>IF(A41&lt;=$B$9,F41*E41,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="34">
-        <f>IF(A41&lt;=$B$9,D41*E41,"")</f>
-        <v/>
-      </c>
-      <c r="K41" s="47">
-        <f>Bootstrap!B42</f>
-        <v/>
-      </c>
-      <c r="L41" s="27">
-        <f>Bootstrap!H42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B42" s="18">
-        <f>IF(A42&lt;=$B$9,EDATE($B$8,12*A42),"")</f>
-        <v/>
-      </c>
-      <c r="C42" s="18">
-        <f>IF(A42&lt;=$B$9,B41,"")</f>
-        <v/>
-      </c>
-      <c r="D42" s="17">
-        <f>IF(A42&lt;=$B$9,(B42-C42)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E42" s="36">
-        <f>IF(A42&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1)))^((B42-INDEX($K$6:$K$71,MATCH(B42,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B42,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B42,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B42,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="44">
-        <f>IF(A42&lt;=$B$9,$B$6*$B$11/100*D42,"")</f>
-        <v/>
-      </c>
-      <c r="G42" s="44">
-        <f>IF(A42&lt;=$B$9,F42*E42,"")</f>
-        <v/>
-      </c>
-      <c r="H42" s="34">
-        <f>IF(A42&lt;=$B$9,D42*E42,"")</f>
-        <v/>
-      </c>
-      <c r="K42" s="47">
-        <f>Bootstrap!B43</f>
-        <v/>
-      </c>
-      <c r="L42" s="27">
-        <f>Bootstrap!H43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B43" s="18">
-        <f>IF(A43&lt;=$B$9,EDATE($B$8,12*A43),"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="18">
-        <f>IF(A43&lt;=$B$9,B42,"")</f>
-        <v/>
-      </c>
-      <c r="D43" s="17">
-        <f>IF(A43&lt;=$B$9,(B43-C43)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E43" s="36">
-        <f>IF(A43&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1)))^((B43-INDEX($K$6:$K$71,MATCH(B43,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B43,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B43,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B43,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="44">
-        <f>IF(A43&lt;=$B$9,$B$6*$B$11/100*D43,"")</f>
-        <v/>
-      </c>
-      <c r="G43" s="44">
-        <f>IF(A43&lt;=$B$9,F43*E43,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="34">
-        <f>IF(A43&lt;=$B$9,D43*E43,"")</f>
-        <v/>
-      </c>
-      <c r="K43" s="47">
-        <f>Bootstrap!B44</f>
-        <v/>
-      </c>
-      <c r="L43" s="27">
-        <f>Bootstrap!H44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B44" s="18">
-        <f>IF(A44&lt;=$B$9,EDATE($B$8,12*A44),"")</f>
-        <v/>
-      </c>
-      <c r="C44" s="18">
-        <f>IF(A44&lt;=$B$9,B43,"")</f>
-        <v/>
-      </c>
-      <c r="D44" s="17">
-        <f>IF(A44&lt;=$B$9,(B44-C44)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E44" s="36">
-        <f>IF(A44&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1)))^((B44-INDEX($K$6:$K$71,MATCH(B44,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B44,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B44,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B44,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="44">
-        <f>IF(A44&lt;=$B$9,$B$6*$B$11/100*D44,"")</f>
-        <v/>
-      </c>
-      <c r="G44" s="44">
-        <f>IF(A44&lt;=$B$9,F44*E44,"")</f>
-        <v/>
-      </c>
-      <c r="H44" s="34">
-        <f>IF(A44&lt;=$B$9,D44*E44,"")</f>
-        <v/>
-      </c>
-      <c r="K44" s="47">
-        <f>Bootstrap!B45</f>
-        <v/>
-      </c>
-      <c r="L44" s="27">
-        <f>Bootstrap!H45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B45" s="18">
-        <f>IF(A45&lt;=$B$9,EDATE($B$8,12*A45),"")</f>
-        <v/>
-      </c>
-      <c r="C45" s="18">
-        <f>IF(A45&lt;=$B$9,B44,"")</f>
-        <v/>
-      </c>
-      <c r="D45" s="17">
-        <f>IF(A45&lt;=$B$9,(B45-C45)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E45" s="36">
-        <f>IF(A45&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1)))^((B45-INDEX($K$6:$K$71,MATCH(B45,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B45,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B45,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B45,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="44">
-        <f>IF(A45&lt;=$B$9,$B$6*$B$11/100*D45,"")</f>
-        <v/>
-      </c>
-      <c r="G45" s="44">
-        <f>IF(A45&lt;=$B$9,F45*E45,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="34">
-        <f>IF(A45&lt;=$B$9,D45*E45,"")</f>
-        <v/>
-      </c>
-      <c r="K45" s="47">
-        <f>Bootstrap!B46</f>
-        <v/>
-      </c>
-      <c r="L45" s="27">
-        <f>Bootstrap!H46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B46" s="18">
-        <f>IF(A46&lt;=$B$9,EDATE($B$8,12*A46),"")</f>
-        <v/>
-      </c>
-      <c r="C46" s="18">
-        <f>IF(A46&lt;=$B$9,B45,"")</f>
-        <v/>
-      </c>
-      <c r="D46" s="17">
-        <f>IF(A46&lt;=$B$9,(B46-C46)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E46" s="36">
-        <f>IF(A46&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1)))^((B46-INDEX($K$6:$K$71,MATCH(B46,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B46,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B46,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B46,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="44">
-        <f>IF(A46&lt;=$B$9,$B$6*$B$11/100*D46,"")</f>
-        <v/>
-      </c>
-      <c r="G46" s="44">
-        <f>IF(A46&lt;=$B$9,F46*E46,"")</f>
-        <v/>
-      </c>
-      <c r="H46" s="34">
-        <f>IF(A46&lt;=$B$9,D46*E46,"")</f>
-        <v/>
-      </c>
-      <c r="K46" s="47">
-        <f>Bootstrap!B47</f>
-        <v/>
-      </c>
-      <c r="L46" s="27">
-        <f>Bootstrap!H47</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B47" s="18">
-        <f>IF(A47&lt;=$B$9,EDATE($B$8,12*A47),"")</f>
-        <v/>
-      </c>
-      <c r="C47" s="18">
-        <f>IF(A47&lt;=$B$9,B46,"")</f>
-        <v/>
-      </c>
-      <c r="D47" s="17">
-        <f>IF(A47&lt;=$B$9,(B47-C47)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E47" s="36">
-        <f>IF(A47&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1)))^((B47-INDEX($K$6:$K$71,MATCH(B47,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B47,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B47,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B47,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="44">
-        <f>IF(A47&lt;=$B$9,$B$6*$B$11/100*D47,"")</f>
-        <v/>
-      </c>
-      <c r="G47" s="44">
-        <f>IF(A47&lt;=$B$9,F47*E47,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="34">
-        <f>IF(A47&lt;=$B$9,D47*E47,"")</f>
-        <v/>
-      </c>
-      <c r="K47" s="47">
-        <f>Bootstrap!B48</f>
-        <v/>
-      </c>
-      <c r="L47" s="27">
-        <f>Bootstrap!H48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B48" s="18">
-        <f>IF(A48&lt;=$B$9,EDATE($B$8,12*A48),"")</f>
-        <v/>
-      </c>
-      <c r="C48" s="18">
-        <f>IF(A48&lt;=$B$9,B47,"")</f>
-        <v/>
-      </c>
-      <c r="D48" s="17">
-        <f>IF(A48&lt;=$B$9,(B48-C48)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E48" s="36">
-        <f>IF(A48&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1)))^((B48-INDEX($K$6:$K$71,MATCH(B48,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B48,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B48,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B48,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="44">
-        <f>IF(A48&lt;=$B$9,$B$6*$B$11/100*D48,"")</f>
-        <v/>
-      </c>
-      <c r="G48" s="44">
-        <f>IF(A48&lt;=$B$9,F48*E48,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="34">
-        <f>IF(A48&lt;=$B$9,D48*E48,"")</f>
-        <v/>
-      </c>
-      <c r="K48" s="47">
-        <f>Bootstrap!B49</f>
-        <v/>
-      </c>
-      <c r="L48" s="27">
-        <f>Bootstrap!H49</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B49" s="18">
-        <f>IF(A49&lt;=$B$9,EDATE($B$8,12*A49),"")</f>
-        <v/>
-      </c>
-      <c r="C49" s="18">
-        <f>IF(A49&lt;=$B$9,B48,"")</f>
-        <v/>
-      </c>
-      <c r="D49" s="17">
-        <f>IF(A49&lt;=$B$9,(B49-C49)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E49" s="36">
-        <f>IF(A49&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1)))^((B49-INDEX($K$6:$K$71,MATCH(B49,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B49,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B49,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B49,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="44">
-        <f>IF(A49&lt;=$B$9,$B$6*$B$11/100*D49,"")</f>
-        <v/>
-      </c>
-      <c r="G49" s="44">
-        <f>IF(A49&lt;=$B$9,F49*E49,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="34">
-        <f>IF(A49&lt;=$B$9,D49*E49,"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="47">
-        <f>Bootstrap!B50</f>
-        <v/>
-      </c>
-      <c r="L49" s="27">
-        <f>Bootstrap!H50</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B50" s="18">
-        <f>IF(A50&lt;=$B$9,EDATE($B$8,12*A50),"")</f>
-        <v/>
-      </c>
-      <c r="C50" s="18">
-        <f>IF(A50&lt;=$B$9,B49,"")</f>
-        <v/>
-      </c>
-      <c r="D50" s="17">
-        <f>IF(A50&lt;=$B$9,(B50-C50)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E50" s="36">
-        <f>IF(A50&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1)))^((B50-INDEX($K$6:$K$71,MATCH(B50,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B50,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B50,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B50,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="44">
-        <f>IF(A50&lt;=$B$9,$B$6*$B$11/100*D50,"")</f>
-        <v/>
-      </c>
-      <c r="G50" s="44">
-        <f>IF(A50&lt;=$B$9,F50*E50,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="34">
-        <f>IF(A50&lt;=$B$9,D50*E50,"")</f>
-        <v/>
-      </c>
-      <c r="K50" s="47">
-        <f>Bootstrap!B51</f>
-        <v/>
-      </c>
-      <c r="L50" s="27">
-        <f>Bootstrap!H51</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B51" s="18">
-        <f>IF(A51&lt;=$B$9,EDATE($B$8,12*A51),"")</f>
-        <v/>
-      </c>
-      <c r="C51" s="18">
-        <f>IF(A51&lt;=$B$9,B50,"")</f>
-        <v/>
-      </c>
-      <c r="D51" s="17">
-        <f>IF(A51&lt;=$B$9,(B51-C51)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E51" s="36">
-        <f>IF(A51&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1)))^((B51-INDEX($K$6:$K$71,MATCH(B51,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B51,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B51,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B51,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="44">
-        <f>IF(A51&lt;=$B$9,$B$6*$B$11/100*D51,"")</f>
-        <v/>
-      </c>
-      <c r="G51" s="44">
-        <f>IF(A51&lt;=$B$9,F51*E51,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="34">
-        <f>IF(A51&lt;=$B$9,D51*E51,"")</f>
-        <v/>
-      </c>
-      <c r="K51" s="47">
-        <f>Bootstrap!B52</f>
-        <v/>
-      </c>
-      <c r="L51" s="27">
-        <f>Bootstrap!H52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B52" s="18">
-        <f>IF(A52&lt;=$B$9,EDATE($B$8,12*A52),"")</f>
-        <v/>
-      </c>
-      <c r="C52" s="18">
-        <f>IF(A52&lt;=$B$9,B51,"")</f>
-        <v/>
-      </c>
-      <c r="D52" s="17">
-        <f>IF(A52&lt;=$B$9,(B52-C52)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E52" s="36">
-        <f>IF(A52&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1)))^((B52-INDEX($K$6:$K$71,MATCH(B52,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B52,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B52,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B52,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="44">
-        <f>IF(A52&lt;=$B$9,$B$6*$B$11/100*D52,"")</f>
-        <v/>
-      </c>
-      <c r="G52" s="44">
-        <f>IF(A52&lt;=$B$9,F52*E52,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="34">
-        <f>IF(A52&lt;=$B$9,D52*E52,"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="47">
-        <f>Bootstrap!B53</f>
-        <v/>
-      </c>
-      <c r="L52" s="27">
-        <f>Bootstrap!H53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B53" s="18">
-        <f>IF(A53&lt;=$B$9,EDATE($B$8,12*A53),"")</f>
-        <v/>
-      </c>
-      <c r="C53" s="18">
-        <f>IF(A53&lt;=$B$9,B52,"")</f>
-        <v/>
-      </c>
-      <c r="D53" s="17">
-        <f>IF(A53&lt;=$B$9,(B53-C53)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E53" s="36">
-        <f>IF(A53&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1)))^((B53-INDEX($K$6:$K$71,MATCH(B53,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B53,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B53,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B53,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="44">
-        <f>IF(A53&lt;=$B$9,$B$6*$B$11/100*D53,"")</f>
-        <v/>
-      </c>
-      <c r="G53" s="44">
-        <f>IF(A53&lt;=$B$9,F53*E53,"")</f>
-        <v/>
-      </c>
-      <c r="H53" s="34">
-        <f>IF(A53&lt;=$B$9,D53*E53,"")</f>
-        <v/>
-      </c>
-      <c r="K53" s="47">
-        <f>Bootstrap!B54</f>
-        <v/>
-      </c>
-      <c r="L53" s="27">
-        <f>Bootstrap!H54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B54" s="18">
-        <f>IF(A54&lt;=$B$9,EDATE($B$8,12*A54),"")</f>
-        <v/>
-      </c>
-      <c r="C54" s="18">
-        <f>IF(A54&lt;=$B$9,B53,"")</f>
-        <v/>
-      </c>
-      <c r="D54" s="17">
-        <f>IF(A54&lt;=$B$9,(B54-C54)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E54" s="36">
-        <f>IF(A54&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1)))^((B54-INDEX($K$6:$K$71,MATCH(B54,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B54,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B54,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B54,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="44">
-        <f>IF(A54&lt;=$B$9,$B$6*$B$11/100*D54,"")</f>
-        <v/>
-      </c>
-      <c r="G54" s="44">
-        <f>IF(A54&lt;=$B$9,F54*E54,"")</f>
-        <v/>
-      </c>
-      <c r="H54" s="34">
-        <f>IF(A54&lt;=$B$9,D54*E54,"")</f>
-        <v/>
-      </c>
-      <c r="K54" s="47">
-        <f>Bootstrap!B55</f>
-        <v/>
-      </c>
-      <c r="L54" s="27">
-        <f>Bootstrap!H55</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B55" s="18">
-        <f>IF(A55&lt;=$B$9,EDATE($B$8,12*A55),"")</f>
-        <v/>
-      </c>
-      <c r="C55" s="18">
-        <f>IF(A55&lt;=$B$9,B54,"")</f>
-        <v/>
-      </c>
-      <c r="D55" s="17">
-        <f>IF(A55&lt;=$B$9,(B55-C55)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E55" s="36">
-        <f>IF(A55&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1)))^((B55-INDEX($K$6:$K$71,MATCH(B55,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B55,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B55,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B55,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="44">
-        <f>IF(A55&lt;=$B$9,$B$6*$B$11/100*D55,"")</f>
-        <v/>
-      </c>
-      <c r="G55" s="44">
-        <f>IF(A55&lt;=$B$9,F55*E55,"")</f>
-        <v/>
-      </c>
-      <c r="H55" s="34">
-        <f>IF(A55&lt;=$B$9,D55*E55,"")</f>
-        <v/>
-      </c>
-      <c r="K55" s="47">
-        <f>Bootstrap!B56</f>
-        <v/>
-      </c>
-      <c r="L55" s="27">
-        <f>Bootstrap!H56</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B56" s="18">
-        <f>IF(A56&lt;=$B$9,EDATE($B$8,12*A56),"")</f>
-        <v/>
-      </c>
-      <c r="C56" s="18">
-        <f>IF(A56&lt;=$B$9,B55,"")</f>
-        <v/>
-      </c>
-      <c r="D56" s="17">
-        <f>IF(A56&lt;=$B$9,(B56-C56)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E56" s="36">
-        <f>IF(A56&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1)))^((B56-INDEX($K$6:$K$71,MATCH(B56,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B56,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B56,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B56,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F56" s="44">
-        <f>IF(A56&lt;=$B$9,$B$6*$B$11/100*D56,"")</f>
-        <v/>
-      </c>
-      <c r="G56" s="44">
-        <f>IF(A56&lt;=$B$9,F56*E56,"")</f>
-        <v/>
-      </c>
-      <c r="H56" s="34">
-        <f>IF(A56&lt;=$B$9,D56*E56,"")</f>
-        <v/>
-      </c>
-      <c r="K56" s="47">
-        <f>Bootstrap!B57</f>
-        <v/>
-      </c>
-      <c r="L56" s="27">
-        <f>Bootstrap!H57</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B57" s="18">
-        <f>IF(A57&lt;=$B$9,EDATE($B$8,12*A57),"")</f>
-        <v/>
-      </c>
-      <c r="C57" s="18">
-        <f>IF(A57&lt;=$B$9,B56,"")</f>
-        <v/>
-      </c>
-      <c r="D57" s="17">
-        <f>IF(A57&lt;=$B$9,(B57-C57)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E57" s="36">
-        <f>IF(A57&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1)))^((B57-INDEX($K$6:$K$71,MATCH(B57,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B57,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B57,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B57,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F57" s="44">
-        <f>IF(A57&lt;=$B$9,$B$6*$B$11/100*D57,"")</f>
-        <v/>
-      </c>
-      <c r="G57" s="44">
-        <f>IF(A57&lt;=$B$9,F57*E57,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="34">
-        <f>IF(A57&lt;=$B$9,D57*E57,"")</f>
-        <v/>
-      </c>
-      <c r="K57" s="47">
-        <f>Bootstrap!B58</f>
-        <v/>
-      </c>
-      <c r="L57" s="27">
-        <f>Bootstrap!H58</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B58" s="18">
-        <f>IF(A58&lt;=$B$9,EDATE($B$8,12*A58),"")</f>
-        <v/>
-      </c>
-      <c r="C58" s="18">
-        <f>IF(A58&lt;=$B$9,B57,"")</f>
-        <v/>
-      </c>
-      <c r="D58" s="17">
-        <f>IF(A58&lt;=$B$9,(B58-C58)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E58" s="36">
-        <f>IF(A58&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1)))^((B58-INDEX($K$6:$K$71,MATCH(B58,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B58,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B58,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B58,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="44">
-        <f>IF(A58&lt;=$B$9,$B$6*$B$11/100*D58,"")</f>
-        <v/>
-      </c>
-      <c r="G58" s="44">
-        <f>IF(A58&lt;=$B$9,F58*E58,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="34">
-        <f>IF(A58&lt;=$B$9,D58*E58,"")</f>
-        <v/>
-      </c>
-      <c r="K58" s="47">
-        <f>Bootstrap!B59</f>
-        <v/>
-      </c>
-      <c r="L58" s="27">
-        <f>Bootstrap!H59</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B59" s="18">
-        <f>IF(A59&lt;=$B$9,EDATE($B$8,12*A59),"")</f>
-        <v/>
-      </c>
-      <c r="C59" s="18">
-        <f>IF(A59&lt;=$B$9,B58,"")</f>
-        <v/>
-      </c>
-      <c r="D59" s="17">
-        <f>IF(A59&lt;=$B$9,(B59-C59)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E59" s="36">
-        <f>IF(A59&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1)))^((B59-INDEX($K$6:$K$71,MATCH(B59,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B59,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B59,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B59,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F59" s="44">
-        <f>IF(A59&lt;=$B$9,$B$6*$B$11/100*D59,"")</f>
-        <v/>
-      </c>
-      <c r="G59" s="44">
-        <f>IF(A59&lt;=$B$9,F59*E59,"")</f>
-        <v/>
-      </c>
-      <c r="H59" s="34">
-        <f>IF(A59&lt;=$B$9,D59*E59,"")</f>
-        <v/>
-      </c>
-      <c r="K59" s="47">
-        <f>Bootstrap!B60</f>
-        <v/>
-      </c>
-      <c r="L59" s="27">
-        <f>Bootstrap!H60</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B60" s="18">
-        <f>IF(A60&lt;=$B$9,EDATE($B$8,12*A60),"")</f>
-        <v/>
-      </c>
-      <c r="C60" s="18">
-        <f>IF(A60&lt;=$B$9,B59,"")</f>
-        <v/>
-      </c>
-      <c r="D60" s="17">
-        <f>IF(A60&lt;=$B$9,(B60-C60)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E60" s="36">
-        <f>IF(A60&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1)))^((B60-INDEX($K$6:$K$71,MATCH(B60,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B60,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B60,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B60,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="44">
-        <f>IF(A60&lt;=$B$9,$B$6*$B$11/100*D60,"")</f>
-        <v/>
-      </c>
-      <c r="G60" s="44">
-        <f>IF(A60&lt;=$B$9,F60*E60,"")</f>
-        <v/>
-      </c>
-      <c r="H60" s="34">
-        <f>IF(A60&lt;=$B$9,D60*E60,"")</f>
-        <v/>
-      </c>
-      <c r="K60" s="47">
-        <f>Bootstrap!B61</f>
-        <v/>
-      </c>
-      <c r="L60" s="27">
-        <f>Bootstrap!H61</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B61" s="18">
-        <f>IF(A61&lt;=$B$9,EDATE($B$8,12*A61),"")</f>
-        <v/>
-      </c>
-      <c r="C61" s="18">
-        <f>IF(A61&lt;=$B$9,B60,"")</f>
-        <v/>
-      </c>
-      <c r="D61" s="17">
-        <f>IF(A61&lt;=$B$9,(B61-C61)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E61" s="36">
-        <f>IF(A61&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1)))^((B61-INDEX($K$6:$K$71,MATCH(B61,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B61,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B61,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B61,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F61" s="44">
-        <f>IF(A61&lt;=$B$9,$B$6*$B$11/100*D61,"")</f>
-        <v/>
-      </c>
-      <c r="G61" s="44">
-        <f>IF(A61&lt;=$B$9,F61*E61,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="34">
-        <f>IF(A61&lt;=$B$9,D61*E61,"")</f>
-        <v/>
-      </c>
-      <c r="K61" s="47">
-        <f>Bootstrap!B62</f>
-        <v/>
-      </c>
-      <c r="L61" s="27">
-        <f>Bootstrap!H62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B62" s="18">
-        <f>IF(A62&lt;=$B$9,EDATE($B$8,12*A62),"")</f>
-        <v/>
-      </c>
-      <c r="C62" s="18">
-        <f>IF(A62&lt;=$B$9,B61,"")</f>
-        <v/>
-      </c>
-      <c r="D62" s="17">
-        <f>IF(A62&lt;=$B$9,(B62-C62)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E62" s="36">
-        <f>IF(A62&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1)))^((B62-INDEX($K$6:$K$71,MATCH(B62,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B62,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B62,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B62,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F62" s="44">
-        <f>IF(A62&lt;=$B$9,$B$6*$B$11/100*D62,"")</f>
-        <v/>
-      </c>
-      <c r="G62" s="44">
-        <f>IF(A62&lt;=$B$9,F62*E62,"")</f>
-        <v/>
-      </c>
-      <c r="H62" s="34">
-        <f>IF(A62&lt;=$B$9,D62*E62,"")</f>
-        <v/>
-      </c>
-      <c r="K62" s="47">
-        <f>Bootstrap!B63</f>
-        <v/>
-      </c>
-      <c r="L62" s="27">
-        <f>Bootstrap!H63</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B63" s="18">
-        <f>IF(A63&lt;=$B$9,EDATE($B$8,12*A63),"")</f>
-        <v/>
-      </c>
-      <c r="C63" s="18">
-        <f>IF(A63&lt;=$B$9,B62,"")</f>
-        <v/>
-      </c>
-      <c r="D63" s="17">
-        <f>IF(A63&lt;=$B$9,(B63-C63)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E63" s="36">
-        <f>IF(A63&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1)))^((B63-INDEX($K$6:$K$71,MATCH(B63,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B63,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B63,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B63,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F63" s="44">
-        <f>IF(A63&lt;=$B$9,$B$6*$B$11/100*D63,"")</f>
-        <v/>
-      </c>
-      <c r="G63" s="44">
-        <f>IF(A63&lt;=$B$9,F63*E63,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="34">
-        <f>IF(A63&lt;=$B$9,D63*E63,"")</f>
-        <v/>
-      </c>
-      <c r="K63" s="47">
-        <f>Bootstrap!B64</f>
-        <v/>
-      </c>
-      <c r="L63" s="27">
-        <f>Bootstrap!H64</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B64" s="18">
-        <f>IF(A64&lt;=$B$9,EDATE($B$8,12*A64),"")</f>
-        <v/>
-      </c>
-      <c r="C64" s="18">
-        <f>IF(A64&lt;=$B$9,B63,"")</f>
-        <v/>
-      </c>
-      <c r="D64" s="17">
-        <f>IF(A64&lt;=$B$9,(B64-C64)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E64" s="36">
-        <f>IF(A64&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1)))^((B64-INDEX($K$6:$K$71,MATCH(B64,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B64,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B64,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B64,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F64" s="44">
-        <f>IF(A64&lt;=$B$9,$B$6*$B$11/100*D64,"")</f>
-        <v/>
-      </c>
-      <c r="G64" s="44">
-        <f>IF(A64&lt;=$B$9,F64*E64,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="34">
-        <f>IF(A64&lt;=$B$9,D64*E64,"")</f>
-        <v/>
-      </c>
-      <c r="K64" s="47">
-        <f>Bootstrap!B65</f>
-        <v/>
-      </c>
-      <c r="L64" s="27">
-        <f>Bootstrap!H65</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B65" s="18">
-        <f>IF(A65&lt;=$B$9,EDATE($B$8,12*A65),"")</f>
-        <v/>
-      </c>
-      <c r="C65" s="18">
-        <f>IF(A65&lt;=$B$9,B64,"")</f>
-        <v/>
-      </c>
-      <c r="D65" s="17">
-        <f>IF(A65&lt;=$B$9,(B65-C65)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E65" s="36">
-        <f>IF(A65&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1)))^((B65-INDEX($K$6:$K$71,MATCH(B65,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B65,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B65,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B65,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F65" s="44">
-        <f>IF(A65&lt;=$B$9,$B$6*$B$11/100*D65,"")</f>
-        <v/>
-      </c>
-      <c r="G65" s="44">
-        <f>IF(A65&lt;=$B$9,F65*E65,"")</f>
-        <v/>
-      </c>
-      <c r="H65" s="34">
-        <f>IF(A65&lt;=$B$9,D65*E65,"")</f>
-        <v/>
-      </c>
-      <c r="K65" s="47">
-        <f>Bootstrap!B66</f>
-        <v/>
-      </c>
-      <c r="L65" s="27">
-        <f>Bootstrap!H66</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B66" s="18">
-        <f>IF(A66&lt;=$B$9,EDATE($B$8,12*A66),"")</f>
-        <v/>
-      </c>
-      <c r="C66" s="18">
-        <f>IF(A66&lt;=$B$9,B65,"")</f>
-        <v/>
-      </c>
-      <c r="D66" s="17">
-        <f>IF(A66&lt;=$B$9,(B66-C66)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E66" s="36">
-        <f>IF(A66&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1)))^((B66-INDEX($K$6:$K$71,MATCH(B66,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B66,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B66,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B66,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F66" s="44">
-        <f>IF(A66&lt;=$B$9,$B$6*$B$11/100*D66,"")</f>
-        <v/>
-      </c>
-      <c r="G66" s="44">
-        <f>IF(A66&lt;=$B$9,F66*E66,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="34">
-        <f>IF(A66&lt;=$B$9,D66*E66,"")</f>
-        <v/>
-      </c>
-      <c r="K66" s="47">
-        <f>Bootstrap!B67</f>
-        <v/>
-      </c>
-      <c r="L66" s="27">
-        <f>Bootstrap!H67</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B67" s="18">
-        <f>IF(A67&lt;=$B$9,EDATE($B$8,12*A67),"")</f>
-        <v/>
-      </c>
-      <c r="C67" s="18">
-        <f>IF(A67&lt;=$B$9,B66,"")</f>
-        <v/>
-      </c>
-      <c r="D67" s="17">
-        <f>IF(A67&lt;=$B$9,(B67-C67)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E67" s="36">
-        <f>IF(A67&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1)))^((B67-INDEX($K$6:$K$71,MATCH(B67,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B67,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B67,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B67,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F67" s="44">
-        <f>IF(A67&lt;=$B$9,$B$6*$B$11/100*D67,"")</f>
-        <v/>
-      </c>
-      <c r="G67" s="44">
-        <f>IF(A67&lt;=$B$9,F67*E67,"")</f>
-        <v/>
-      </c>
-      <c r="H67" s="34">
-        <f>IF(A67&lt;=$B$9,D67*E67,"")</f>
-        <v/>
-      </c>
-      <c r="K67" s="47">
-        <f>Bootstrap!B68</f>
-        <v/>
-      </c>
-      <c r="L67" s="27">
-        <f>Bootstrap!H68</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B68" s="18">
-        <f>IF(A68&lt;=$B$9,EDATE($B$8,12*A68),"")</f>
-        <v/>
-      </c>
-      <c r="C68" s="18">
-        <f>IF(A68&lt;=$B$9,B67,"")</f>
-        <v/>
-      </c>
-      <c r="D68" s="17">
-        <f>IF(A68&lt;=$B$9,(B68-C68)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E68" s="36">
-        <f>IF(A68&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1)))^((B68-INDEX($K$6:$K$71,MATCH(B68,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B68,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B68,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B68,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F68" s="44">
-        <f>IF(A68&lt;=$B$9,$B$6*$B$11/100*D68,"")</f>
-        <v/>
-      </c>
-      <c r="G68" s="44">
-        <f>IF(A68&lt;=$B$9,F68*E68,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="34">
-        <f>IF(A68&lt;=$B$9,D68*E68,"")</f>
-        <v/>
-      </c>
-      <c r="K68" s="47">
-        <f>Bootstrap!B69</f>
-        <v/>
-      </c>
-      <c r="L68" s="27">
-        <f>Bootstrap!H69</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B69" s="18">
-        <f>IF(A69&lt;=$B$9,EDATE($B$8,12*A69),"")</f>
-        <v/>
-      </c>
-      <c r="C69" s="18">
-        <f>IF(A69&lt;=$B$9,B68,"")</f>
-        <v/>
-      </c>
-      <c r="D69" s="17">
-        <f>IF(A69&lt;=$B$9,(B69-C69)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E69" s="36">
-        <f>IF(A69&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1)))^((B69-INDEX($K$6:$K$71,MATCH(B69,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B69,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B69,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B69,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F69" s="44">
-        <f>IF(A69&lt;=$B$9,$B$6*$B$11/100*D69,"")</f>
-        <v/>
-      </c>
-      <c r="G69" s="44">
-        <f>IF(A69&lt;=$B$9,F69*E69,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="34">
-        <f>IF(A69&lt;=$B$9,D69*E69,"")</f>
-        <v/>
-      </c>
-      <c r="K69" s="47">
-        <f>Bootstrap!B70</f>
-        <v/>
-      </c>
-      <c r="L69" s="27">
-        <f>Bootstrap!H70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B70" s="18">
-        <f>IF(A70&lt;=$B$9,EDATE($B$8,12*A70),"")</f>
-        <v/>
-      </c>
-      <c r="C70" s="18">
-        <f>IF(A70&lt;=$B$9,B69,"")</f>
-        <v/>
-      </c>
-      <c r="D70" s="17">
-        <f>IF(A70&lt;=$B$9,(B70-C70)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E70" s="36">
-        <f>IF(A70&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1)))^((B70-INDEX($K$6:$K$71,MATCH(B70,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B70,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B70,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B70,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F70" s="44">
-        <f>IF(A70&lt;=$B$9,$B$6*$B$11/100*D70,"")</f>
-        <v/>
-      </c>
-      <c r="G70" s="44">
-        <f>IF(A70&lt;=$B$9,F70*E70,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="34">
-        <f>IF(A70&lt;=$B$9,D70*E70,"")</f>
-        <v/>
-      </c>
-      <c r="K70" s="47">
-        <f>Bootstrap!B71</f>
-        <v/>
-      </c>
-      <c r="L70" s="27">
-        <f>Bootstrap!H71</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B71" s="18">
-        <f>IF(A71&lt;=$B$9,EDATE($B$8,12*A71),"")</f>
-        <v/>
-      </c>
-      <c r="C71" s="18">
-        <f>IF(A71&lt;=$B$9,B70,"")</f>
-        <v/>
-      </c>
-      <c r="D71" s="17">
-        <f>IF(A71&lt;=$B$9,(B71-C71)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E71" s="36">
-        <f>IF(A71&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1)))^((B71-INDEX($K$6:$K$71,MATCH(B71,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B71,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B71,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B71,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F71" s="44">
-        <f>IF(A71&lt;=$B$9,$B$6*$B$11/100*D71,"")</f>
-        <v/>
-      </c>
-      <c r="G71" s="44">
-        <f>IF(A71&lt;=$B$9,F71*E71,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="34">
-        <f>IF(A71&lt;=$B$9,D71*E71,"")</f>
-        <v/>
-      </c>
-      <c r="K71" s="47">
-        <f>Bootstrap!B72</f>
-        <v/>
-      </c>
-      <c r="L71" s="27">
-        <f>Bootstrap!H72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B72" s="18">
-        <f>IF(A72&lt;=$B$9,EDATE($B$8,12*A72),"")</f>
-        <v/>
-      </c>
-      <c r="C72" s="18">
-        <f>IF(A72&lt;=$B$9,B71,"")</f>
-        <v/>
-      </c>
-      <c r="D72" s="17">
-        <f>IF(A72&lt;=$B$9,(B72-C72)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E72" s="36">
-        <f>IF(A72&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1)))^((B72-INDEX($K$6:$K$71,MATCH(B72,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B72,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B72,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B72,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F72" s="44">
-        <f>IF(A72&lt;=$B$9,$B$6*$B$11/100*D72,"")</f>
-        <v/>
-      </c>
-      <c r="G72" s="44">
-        <f>IF(A72&lt;=$B$9,F72*E72,"")</f>
-        <v/>
-      </c>
-      <c r="H72" s="34">
-        <f>IF(A72&lt;=$B$9,D72*E72,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B73" s="18">
-        <f>IF(A73&lt;=$B$9,EDATE($B$8,12*A73),"")</f>
-        <v/>
-      </c>
-      <c r="C73" s="18">
-        <f>IF(A73&lt;=$B$9,B72,"")</f>
-        <v/>
-      </c>
-      <c r="D73" s="17">
-        <f>IF(A73&lt;=$B$9,(B73-C73)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E73" s="36">
-        <f>IF(A73&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1)))^((B73-INDEX($K$6:$K$71,MATCH(B73,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B73,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B73,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B73,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F73" s="44">
-        <f>IF(A73&lt;=$B$9,$B$6*$B$11/100*D73,"")</f>
-        <v/>
-      </c>
-      <c r="G73" s="44">
-        <f>IF(A73&lt;=$B$9,F73*E73,"")</f>
-        <v/>
-      </c>
-      <c r="H73" s="34">
-        <f>IF(A73&lt;=$B$9,D73*E73,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B74" s="18">
-        <f>IF(A74&lt;=$B$9,EDATE($B$8,12*A74),"")</f>
-        <v/>
-      </c>
-      <c r="C74" s="18">
-        <f>IF(A74&lt;=$B$9,B73,"")</f>
-        <v/>
-      </c>
-      <c r="D74" s="17">
-        <f>IF(A74&lt;=$B$9,(B74-C74)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E74" s="36">
-        <f>IF(A74&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1)))^((B74-INDEX($K$6:$K$71,MATCH(B74,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B74,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B74,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B74,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F74" s="44">
-        <f>IF(A74&lt;=$B$9,$B$6*$B$11/100*D74,"")</f>
-        <v/>
-      </c>
-      <c r="G74" s="44">
-        <f>IF(A74&lt;=$B$9,F74*E74,"")</f>
-        <v/>
-      </c>
-      <c r="H74" s="34">
-        <f>IF(A74&lt;=$B$9,D74*E74,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B75" s="18">
-        <f>IF(A75&lt;=$B$9,EDATE($B$8,12*A75),"")</f>
-        <v/>
-      </c>
-      <c r="C75" s="18">
-        <f>IF(A75&lt;=$B$9,B74,"")</f>
-        <v/>
-      </c>
-      <c r="D75" s="17">
-        <f>IF(A75&lt;=$B$9,(B75-C75)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E75" s="36">
-        <f>IF(A75&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1)))^((B75-INDEX($K$6:$K$71,MATCH(B75,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B75,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B75,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B75,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F75" s="44">
-        <f>IF(A75&lt;=$B$9,$B$6*$B$11/100*D75,"")</f>
-        <v/>
-      </c>
-      <c r="G75" s="44">
-        <f>IF(A75&lt;=$B$9,F75*E75,"")</f>
-        <v/>
-      </c>
-      <c r="H75" s="34">
-        <f>IF(A75&lt;=$B$9,D75*E75,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B76" s="18">
-        <f>IF(A76&lt;=$B$9,EDATE($B$8,12*A76),"")</f>
-        <v/>
-      </c>
-      <c r="C76" s="18">
-        <f>IF(A76&lt;=$B$9,B75,"")</f>
-        <v/>
-      </c>
-      <c r="D76" s="17">
-        <f>IF(A76&lt;=$B$9,(B76-C76)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E76" s="36">
-        <f>IF(A76&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1)))^((B76-INDEX($K$6:$K$71,MATCH(B76,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B76,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B76,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B76,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F76" s="44">
-        <f>IF(A76&lt;=$B$9,$B$6*$B$11/100*D76,"")</f>
-        <v/>
-      </c>
-      <c r="G76" s="44">
-        <f>IF(A76&lt;=$B$9,F76*E76,"")</f>
-        <v/>
-      </c>
-      <c r="H76" s="34">
-        <f>IF(A76&lt;=$B$9,D76*E76,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B77" s="18">
-        <f>IF(A77&lt;=$B$9,EDATE($B$8,12*A77),"")</f>
-        <v/>
-      </c>
-      <c r="C77" s="18">
-        <f>IF(A77&lt;=$B$9,B76,"")</f>
-        <v/>
-      </c>
-      <c r="D77" s="17">
-        <f>IF(A77&lt;=$B$9,(B77-C77)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E77" s="36">
-        <f>IF(A77&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1)))^((B77-INDEX($K$6:$K$71,MATCH(B77,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B77,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B77,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B77,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F77" s="44">
-        <f>IF(A77&lt;=$B$9,$B$6*$B$11/100*D77,"")</f>
-        <v/>
-      </c>
-      <c r="G77" s="44">
-        <f>IF(A77&lt;=$B$9,F77*E77,"")</f>
-        <v/>
-      </c>
-      <c r="H77" s="34">
-        <f>IF(A77&lt;=$B$9,D77*E77,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B78" s="18">
-        <f>IF(A78&lt;=$B$9,EDATE($B$8,12*A78),"")</f>
-        <v/>
-      </c>
-      <c r="C78" s="18">
-        <f>IF(A78&lt;=$B$9,B77,"")</f>
-        <v/>
-      </c>
-      <c r="D78" s="17">
-        <f>IF(A78&lt;=$B$9,(B78-C78)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E78" s="36">
-        <f>IF(A78&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1)))^((B78-INDEX($K$6:$K$71,MATCH(B78,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B78,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B78,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B78,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F78" s="44">
-        <f>IF(A78&lt;=$B$9,$B$6*$B$11/100*D78,"")</f>
-        <v/>
-      </c>
-      <c r="G78" s="44">
-        <f>IF(A78&lt;=$B$9,F78*E78,"")</f>
-        <v/>
-      </c>
-      <c r="H78" s="34">
-        <f>IF(A78&lt;=$B$9,D78*E78,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B79" s="18">
-        <f>IF(A79&lt;=$B$9,EDATE($B$8,12*A79),"")</f>
-        <v/>
-      </c>
-      <c r="C79" s="18">
-        <f>IF(A79&lt;=$B$9,B78,"")</f>
-        <v/>
-      </c>
-      <c r="D79" s="17">
-        <f>IF(A79&lt;=$B$9,(B79-C79)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="36">
-        <f>IF(A79&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1)))^((B79-INDEX($K$6:$K$71,MATCH(B79,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B79,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B79,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B79,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F79" s="44">
-        <f>IF(A79&lt;=$B$9,$B$6*$B$11/100*D79,"")</f>
-        <v/>
-      </c>
-      <c r="G79" s="44">
-        <f>IF(A79&lt;=$B$9,F79*E79,"")</f>
-        <v/>
-      </c>
-      <c r="H79" s="34">
-        <f>IF(A79&lt;=$B$9,D79*E79,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B80" s="18">
-        <f>IF(A80&lt;=$B$9,EDATE($B$8,12*A80),"")</f>
-        <v/>
-      </c>
-      <c r="C80" s="18">
-        <f>IF(A80&lt;=$B$9,B79,"")</f>
-        <v/>
-      </c>
-      <c r="D80" s="17">
-        <f>IF(A80&lt;=$B$9,(B80-C80)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="36">
-        <f>IF(A80&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1)))^((B80-INDEX($K$6:$K$71,MATCH(B80,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B80,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B80,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B80,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F80" s="44">
-        <f>IF(A80&lt;=$B$9,$B$6*$B$11/100*D80,"")</f>
-        <v/>
-      </c>
-      <c r="G80" s="44">
-        <f>IF(A80&lt;=$B$9,F80*E80,"")</f>
-        <v/>
-      </c>
-      <c r="H80" s="34">
-        <f>IF(A80&lt;=$B$9,D80*E80,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B81" s="18">
-        <f>IF(A81&lt;=$B$9,EDATE($B$8,12*A81),"")</f>
-        <v/>
-      </c>
-      <c r="C81" s="18">
-        <f>IF(A81&lt;=$B$9,B80,"")</f>
-        <v/>
-      </c>
-      <c r="D81" s="17">
-        <f>IF(A81&lt;=$B$9,(B81-C81)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="36">
-        <f>IF(A81&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1)))^((B81-INDEX($K$6:$K$71,MATCH(B81,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B81,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B81,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B81,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F81" s="44">
-        <f>IF(A81&lt;=$B$9,$B$6*$B$11/100*D81,"")</f>
-        <v/>
-      </c>
-      <c r="G81" s="44">
-        <f>IF(A81&lt;=$B$9,F81*E81,"")</f>
-        <v/>
-      </c>
-      <c r="H81" s="34">
-        <f>IF(A81&lt;=$B$9,D81*E81,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B82" s="18">
-        <f>IF(A82&lt;=$B$9,EDATE($B$8,12*A82),"")</f>
-        <v/>
-      </c>
-      <c r="C82" s="18">
-        <f>IF(A82&lt;=$B$9,B81,"")</f>
-        <v/>
-      </c>
-      <c r="D82" s="17">
-        <f>IF(A82&lt;=$B$9,(B82-C82)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="36">
-        <f>IF(A82&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1)))^((B82-INDEX($K$6:$K$71,MATCH(B82,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B82,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B82,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B82,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F82" s="44">
-        <f>IF(A82&lt;=$B$9,$B$6*$B$11/100*D82,"")</f>
-        <v/>
-      </c>
-      <c r="G82" s="44">
-        <f>IF(A82&lt;=$B$9,F82*E82,"")</f>
-        <v/>
-      </c>
-      <c r="H82" s="34">
-        <f>IF(A82&lt;=$B$9,D82*E82,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B83" s="18">
-        <f>IF(A83&lt;=$B$9,EDATE($B$8,12*A83),"")</f>
-        <v/>
-      </c>
-      <c r="C83" s="18">
-        <f>IF(A83&lt;=$B$9,B82,"")</f>
-        <v/>
-      </c>
-      <c r="D83" s="17">
-        <f>IF(A83&lt;=$B$9,(B83-C83)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="36">
-        <f>IF(A83&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1)))^((B83-INDEX($K$6:$K$71,MATCH(B83,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B83,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B83,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B83,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F83" s="44">
-        <f>IF(A83&lt;=$B$9,$B$6*$B$11/100*D83,"")</f>
-        <v/>
-      </c>
-      <c r="G83" s="44">
-        <f>IF(A83&lt;=$B$9,F83*E83,"")</f>
-        <v/>
-      </c>
-      <c r="H83" s="34">
-        <f>IF(A83&lt;=$B$9,D83*E83,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B84" s="18">
-        <f>IF(A84&lt;=$B$9,EDATE($B$8,12*A84),"")</f>
-        <v/>
-      </c>
-      <c r="C84" s="18">
-        <f>IF(A84&lt;=$B$9,B83,"")</f>
-        <v/>
-      </c>
-      <c r="D84" s="17">
-        <f>IF(A84&lt;=$B$9,(B84-C84)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="36">
-        <f>IF(A84&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1)))^((B84-INDEX($K$6:$K$71,MATCH(B84,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B84,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B84,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B84,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F84" s="44">
-        <f>IF(A84&lt;=$B$9,$B$6*$B$11/100*D84,"")</f>
-        <v/>
-      </c>
-      <c r="G84" s="44">
-        <f>IF(A84&lt;=$B$9,F84*E84,"")</f>
-        <v/>
-      </c>
-      <c r="H84" s="34">
-        <f>IF(A84&lt;=$B$9,D84*E84,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B85" s="18">
-        <f>IF(A85&lt;=$B$9,EDATE($B$8,12*A85),"")</f>
-        <v/>
-      </c>
-      <c r="C85" s="18">
-        <f>IF(A85&lt;=$B$9,B84,"")</f>
-        <v/>
-      </c>
-      <c r="D85" s="17">
-        <f>IF(A85&lt;=$B$9,(B85-C85)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="36">
-        <f>IF(A85&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1)))^((B85-INDEX($K$6:$K$71,MATCH(B85,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B85,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B85,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B85,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F85" s="44">
-        <f>IF(A85&lt;=$B$9,$B$6*$B$11/100*D85,"")</f>
-        <v/>
-      </c>
-      <c r="G85" s="44">
-        <f>IF(A85&lt;=$B$9,F85*E85,"")</f>
-        <v/>
-      </c>
-      <c r="H85" s="34">
-        <f>IF(A85&lt;=$B$9,D85*E85,"")</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="C19:I19"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="C24:I24"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="C26:I26"/>
-    <mergeCell ref="C29:I29"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="A32:I33"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="C11:I11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -43,7 +43,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000000"/>
@@ -54,6 +54,7 @@
     <numFmt numFmtId="171" formatCode="0.0000000000"/>
     <numFmt numFmtId="172" formatCode="0.00000"/>
     <numFmt numFmtId="173" formatCode="mm/dd/yy"/>
+    <numFmt numFmtId="174" formatCode="0.###"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -214,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -341,6 +342,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6589,7 +6594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:L77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6612,6 +6617,21 @@
           <t>Bloomberg's own USD SOFR curve (S490 / YCSW0490 Index) — benchmark for your bootstrap, not an input</t>
         </is>
       </c>
+      <c r="H2" s="67" t="inlineStr">
+        <is>
+          <t>LIVE BENCHMARK — BDS dump controls</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="H3" s="94" t="inlineStr">
+        <is>
+          <t>Dump col holding MATURITY DATE</t>
+        </is>
+      </c>
+      <c r="I3" s="95" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -6623,6 +6643,14 @@
         <f>IFERROR(BDP(S490_TKR,"NAME"),"ERROR PLZ FIX")</f>
         <v/>
       </c>
+      <c r="H4" s="94" t="inlineStr">
+        <is>
+          <t>Dump col holding ZERO RATE</t>
+        </is>
+      </c>
+      <c r="I4" s="95" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
@@ -6634,11 +6662,24 @@
         <f>VAL_DATE</f>
         <v/>
       </c>
+      <c r="H5" s="94" t="inlineStr">
+        <is>
+          <t>Zero units (1 = pct, 100 = decimal)</t>
+        </is>
+      </c>
+      <c r="I5" s="96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Paste Bloomberg's S490 zero rates (from YCSW0490 &lt;GO&gt; or SWDF) into the yellow column D, tenor for tenor; column E then shows Δz = your bootstrap − Bloomberg in bp (single digits = agreement). The raw BDS(CURVE_TENOR_RATES) dump is off to the right (cols H:I) as an optional live pull — its column order is Bloomberg-defined, so verify before relying on it.</t>
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>Column D pulls Bloomberg's own S490 zero curve live from the BDS dump and falls back to the manual paste in column G. Column E is your bootstrap minus Bloomberg, in bp — single digits = agreement.</t>
+        </is>
+      </c>
+      <c r="H6" s="66" t="inlineStr">
+        <is>
+          <t>VERIFY I3/I4/I5 against the dump at J12 before trusting column E — the defaults are a GUESS at the CURVE_TENOR_RATES schema, not confirmed.</t>
         </is>
       </c>
     </row>
@@ -6658,9 +6699,9 @@
           <t>Your zero (%)</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>S490 zero (%) [paste]</t>
+      <c r="D7" s="92" t="inlineStr">
+        <is>
+          <t>S490 zero (%) — live</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -6668,9 +6709,19 @@
           <t>Δz (bp)</t>
         </is>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>Raw CURVE_TENOR_RATES (verify order)</t>
+      <c r="F7" s="62" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="G7" s="62" t="inlineStr">
+        <is>
+          <t>S490 zero (%) [manual paste]</t>
+        </is>
+      </c>
+      <c r="H7" s="67" t="inlineStr">
+        <is>
+          <t>Raw CURVE_TENOR_RATES dump (spills right and down from J12)</t>
         </is>
       </c>
     </row>
@@ -6687,11 +6738,19 @@
         <f>Bootstrap!J8</f>
         <v/>
       </c>
-      <c r="D8" s="30" t="n"/>
-      <c r="E8" s="31">
-        <f>IF(D8="","",(C8-D8)*100)</f>
-        <v/>
-      </c>
+      <c r="D8" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B8,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G8),G8,""))</f>
+        <v/>
+      </c>
+      <c r="E8" s="89">
+        <f>IF(OR(D8="",NOT(ISNUMBER(D8))),"",(C8-D8)*100)</f>
+        <v/>
+      </c>
+      <c r="F8" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B8,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G8),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G8" s="85" t="n"/>
       <c r="H8">
         <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
         <v/>
@@ -6710,11 +6769,19 @@
         <f>Bootstrap!J9</f>
         <v/>
       </c>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31">
-        <f>IF(D9="","",(C9-D9)*100)</f>
-        <v/>
-      </c>
+      <c r="D9" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B9,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G9),G9,""))</f>
+        <v/>
+      </c>
+      <c r="E9" s="89">
+        <f>IF(OR(D9="",NOT(ISNUMBER(D9))),"",(C9-D9)*100)</f>
+        <v/>
+      </c>
+      <c r="F9" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B9,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G9),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="85" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6">
@@ -6729,11 +6796,19 @@
         <f>Bootstrap!J10</f>
         <v/>
       </c>
-      <c r="D10" s="30" t="n"/>
-      <c r="E10" s="31">
-        <f>IF(D10="","",(C10-D10)*100)</f>
-        <v/>
-      </c>
+      <c r="D10" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B10,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G10),G10,""))</f>
+        <v/>
+      </c>
+      <c r="E10" s="89">
+        <f>IF(OR(D10="",NOT(ISNUMBER(D10))),"",(C10-D10)*100)</f>
+        <v/>
+      </c>
+      <c r="F10" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B10,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G10),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="85" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6">
@@ -6748,11 +6823,19 @@
         <f>Bootstrap!J11</f>
         <v/>
       </c>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31">
-        <f>IF(D11="","",(C11-D11)*100)</f>
-        <v/>
-      </c>
+      <c r="D11" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B11,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G11),G11,""))</f>
+        <v/>
+      </c>
+      <c r="E11" s="89">
+        <f>IF(OR(D11="",NOT(ISNUMBER(D11))),"",(C11-D11)*100)</f>
+        <v/>
+      </c>
+      <c r="F11" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B11,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G11),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="85" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6">
@@ -6767,9 +6850,21 @@
         <f>Bootstrap!J12</f>
         <v/>
       </c>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="31">
-        <f>IF(D12="","",(C12-D12)*100)</f>
+      <c r="D12" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B12,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G12),G12,""))</f>
+        <v/>
+      </c>
+      <c r="E12" s="89">
+        <f>IF(OR(D12="",NOT(ISNUMBER(D12))),"",(C12-D12)*100)</f>
+        <v/>
+      </c>
+      <c r="F12" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B12,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G12),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G12" s="85" t="n"/>
+      <c r="J12" s="93">
+        <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
         <v/>
       </c>
     </row>
@@ -6786,11 +6881,19 @@
         <f>Bootstrap!J13</f>
         <v/>
       </c>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="31">
-        <f>IF(D13="","",(C13-D13)*100)</f>
-        <v/>
-      </c>
+      <c r="D13" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B13,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G13),G13,""))</f>
+        <v/>
+      </c>
+      <c r="E13" s="89">
+        <f>IF(OR(D13="",NOT(ISNUMBER(D13))),"",(C13-D13)*100)</f>
+        <v/>
+      </c>
+      <c r="F13" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B13,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G13),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="85" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6">
@@ -6805,11 +6908,19 @@
         <f>Bootstrap!J14</f>
         <v/>
       </c>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="31">
-        <f>IF(D14="","",(C14-D14)*100)</f>
-        <v/>
-      </c>
+      <c r="D14" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B14,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G14),G14,""))</f>
+        <v/>
+      </c>
+      <c r="E14" s="89">
+        <f>IF(OR(D14="",NOT(ISNUMBER(D14))),"",(C14-D14)*100)</f>
+        <v/>
+      </c>
+      <c r="F14" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B14,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G14),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="85" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6">
@@ -6824,11 +6935,19 @@
         <f>Bootstrap!J15</f>
         <v/>
       </c>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="31">
-        <f>IF(D15="","",(C15-D15)*100)</f>
-        <v/>
-      </c>
+      <c r="D15" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B15,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G15),G15,""))</f>
+        <v/>
+      </c>
+      <c r="E15" s="89">
+        <f>IF(OR(D15="",NOT(ISNUMBER(D15))),"",(C15-D15)*100)</f>
+        <v/>
+      </c>
+      <c r="F15" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B15,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G15),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="85" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6">
@@ -6843,11 +6962,19 @@
         <f>Bootstrap!J16</f>
         <v/>
       </c>
-      <c r="D16" s="30" t="n"/>
-      <c r="E16" s="31">
-        <f>IF(D16="","",(C16-D16)*100)</f>
-        <v/>
-      </c>
+      <c r="D16" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B16,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G16),G16,""))</f>
+        <v/>
+      </c>
+      <c r="E16" s="89">
+        <f>IF(OR(D16="",NOT(ISNUMBER(D16))),"",(C16-D16)*100)</f>
+        <v/>
+      </c>
+      <c r="F16" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B16,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G16),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G16" s="85" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6">
@@ -6862,11 +6989,19 @@
         <f>Bootstrap!J17</f>
         <v/>
       </c>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="31">
-        <f>IF(D17="","",(C17-D17)*100)</f>
-        <v/>
-      </c>
+      <c r="D17" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B17,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G17),G17,""))</f>
+        <v/>
+      </c>
+      <c r="E17" s="89">
+        <f>IF(OR(D17="",NOT(ISNUMBER(D17))),"",(C17-D17)*100)</f>
+        <v/>
+      </c>
+      <c r="F17" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B17,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G17),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G17" s="85" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6">
@@ -6881,11 +7016,19 @@
         <f>Bootstrap!J18</f>
         <v/>
       </c>
-      <c r="D18" s="30" t="n"/>
-      <c r="E18" s="31">
-        <f>IF(D18="","",(C18-D18)*100)</f>
-        <v/>
-      </c>
+      <c r="D18" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B18,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G18),G18,""))</f>
+        <v/>
+      </c>
+      <c r="E18" s="89">
+        <f>IF(OR(D18="",NOT(ISNUMBER(D18))),"",(C18-D18)*100)</f>
+        <v/>
+      </c>
+      <c r="F18" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B18,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G18),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="85" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6">
@@ -6900,11 +7043,19 @@
         <f>Bootstrap!J19</f>
         <v/>
       </c>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="31">
-        <f>IF(D19="","",(C19-D19)*100)</f>
-        <v/>
-      </c>
+      <c r="D19" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B19,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G19),G19,""))</f>
+        <v/>
+      </c>
+      <c r="E19" s="89">
+        <f>IF(OR(D19="",NOT(ISNUMBER(D19))),"",(C19-D19)*100)</f>
+        <v/>
+      </c>
+      <c r="F19" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B19,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G19),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G19" s="85" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6">
@@ -6919,11 +7070,19 @@
         <f>Bootstrap!J20</f>
         <v/>
       </c>
-      <c r="D20" s="30" t="n"/>
-      <c r="E20" s="31">
-        <f>IF(D20="","",(C20-D20)*100)</f>
-        <v/>
-      </c>
+      <c r="D20" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B20,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G20),G20,""))</f>
+        <v/>
+      </c>
+      <c r="E20" s="89">
+        <f>IF(OR(D20="",NOT(ISNUMBER(D20))),"",(C20-D20)*100)</f>
+        <v/>
+      </c>
+      <c r="F20" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B20,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G20),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="85" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6">
@@ -6938,11 +7097,19 @@
         <f>Bootstrap!J21</f>
         <v/>
       </c>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="31">
-        <f>IF(D21="","",(C21-D21)*100)</f>
-        <v/>
-      </c>
+      <c r="D21" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B21,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G21),G21,""))</f>
+        <v/>
+      </c>
+      <c r="E21" s="89">
+        <f>IF(OR(D21="",NOT(ISNUMBER(D21))),"",(C21-D21)*100)</f>
+        <v/>
+      </c>
+      <c r="F21" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B21,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G21),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G21" s="85" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6">
@@ -6957,11 +7124,19 @@
         <f>Bootstrap!J22</f>
         <v/>
       </c>
-      <c r="D22" s="30" t="n"/>
-      <c r="E22" s="31">
-        <f>IF(D22="","",(C22-D22)*100)</f>
-        <v/>
-      </c>
+      <c r="D22" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B22,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G22),G22,""))</f>
+        <v/>
+      </c>
+      <c r="E22" s="89">
+        <f>IF(OR(D22="",NOT(ISNUMBER(D22))),"",(C22-D22)*100)</f>
+        <v/>
+      </c>
+      <c r="F22" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B22,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G22),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="85" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6">
@@ -6976,11 +7151,19 @@
         <f>Bootstrap!J23</f>
         <v/>
       </c>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="31">
-        <f>IF(D23="","",(C23-D23)*100)</f>
-        <v/>
-      </c>
+      <c r="D23" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B23,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G23),G23,""))</f>
+        <v/>
+      </c>
+      <c r="E23" s="89">
+        <f>IF(OR(D23="",NOT(ISNUMBER(D23))),"",(C23-D23)*100)</f>
+        <v/>
+      </c>
+      <c r="F23" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B23,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G23),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G23" s="85" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6">
@@ -6995,11 +7178,19 @@
         <f>Bootstrap!J24</f>
         <v/>
       </c>
-      <c r="D24" s="30" t="n"/>
-      <c r="E24" s="31">
-        <f>IF(D24="","",(C24-D24)*100)</f>
-        <v/>
-      </c>
+      <c r="D24" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B24,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G24),G24,""))</f>
+        <v/>
+      </c>
+      <c r="E24" s="89">
+        <f>IF(OR(D24="",NOT(ISNUMBER(D24))),"",(C24-D24)*100)</f>
+        <v/>
+      </c>
+      <c r="F24" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B24,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G24),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G24" s="85" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6">
@@ -7014,11 +7205,19 @@
         <f>Bootstrap!J25</f>
         <v/>
       </c>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="31">
-        <f>IF(D25="","",(C25-D25)*100)</f>
-        <v/>
-      </c>
+      <c r="D25" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B25,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G25),G25,""))</f>
+        <v/>
+      </c>
+      <c r="E25" s="89">
+        <f>IF(OR(D25="",NOT(ISNUMBER(D25))),"",(C25-D25)*100)</f>
+        <v/>
+      </c>
+      <c r="F25" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B25,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G25),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="85" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="6">
@@ -7033,11 +7232,19 @@
         <f>Bootstrap!J26</f>
         <v/>
       </c>
-      <c r="D26" s="30" t="n"/>
-      <c r="E26" s="31">
-        <f>IF(D26="","",(C26-D26)*100)</f>
-        <v/>
-      </c>
+      <c r="D26" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B26,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G26),G26,""))</f>
+        <v/>
+      </c>
+      <c r="E26" s="89">
+        <f>IF(OR(D26="",NOT(ISNUMBER(D26))),"",(C26-D26)*100)</f>
+        <v/>
+      </c>
+      <c r="F26" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B26,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G26),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G26" s="85" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6">
@@ -7052,11 +7259,19 @@
         <f>Bootstrap!J27</f>
         <v/>
       </c>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="31">
-        <f>IF(D27="","",(C27-D27)*100)</f>
-        <v/>
-      </c>
+      <c r="D27" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B27,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G27),G27,""))</f>
+        <v/>
+      </c>
+      <c r="E27" s="89">
+        <f>IF(OR(D27="",NOT(ISNUMBER(D27))),"",(C27-D27)*100)</f>
+        <v/>
+      </c>
+      <c r="F27" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B27,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G27),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G27" s="85" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6">
@@ -7071,11 +7286,19 @@
         <f>Bootstrap!J28</f>
         <v/>
       </c>
-      <c r="D28" s="30" t="n"/>
-      <c r="E28" s="31">
-        <f>IF(D28="","",(C28-D28)*100)</f>
-        <v/>
-      </c>
+      <c r="D28" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B28,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G28),G28,""))</f>
+        <v/>
+      </c>
+      <c r="E28" s="89">
+        <f>IF(OR(D28="",NOT(ISNUMBER(D28))),"",(C28-D28)*100)</f>
+        <v/>
+      </c>
+      <c r="F28" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B28,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G28),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G28" s="85" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6">
@@ -7090,11 +7313,19 @@
         <f>Bootstrap!J29</f>
         <v/>
       </c>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="31">
-        <f>IF(D29="","",(C29-D29)*100)</f>
-        <v/>
-      </c>
+      <c r="D29" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B29,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G29),G29,""))</f>
+        <v/>
+      </c>
+      <c r="E29" s="89">
+        <f>IF(OR(D29="",NOT(ISNUMBER(D29))),"",(C29-D29)*100)</f>
+        <v/>
+      </c>
+      <c r="F29" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B29,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G29),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="85" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6">
@@ -7109,11 +7340,19 @@
         <f>Bootstrap!J30</f>
         <v/>
       </c>
-      <c r="D30" s="30" t="n"/>
-      <c r="E30" s="31">
-        <f>IF(D30="","",(C30-D30)*100)</f>
-        <v/>
-      </c>
+      <c r="D30" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B30,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G30),G30,""))</f>
+        <v/>
+      </c>
+      <c r="E30" s="89">
+        <f>IF(OR(D30="",NOT(ISNUMBER(D30))),"",(C30-D30)*100)</f>
+        <v/>
+      </c>
+      <c r="F30" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B30,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G30),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="85" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6">
@@ -7128,11 +7367,19 @@
         <f>Bootstrap!J31</f>
         <v/>
       </c>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="31">
-        <f>IF(D31="","",(C31-D31)*100)</f>
-        <v/>
-      </c>
+      <c r="D31" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B31,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G31),G31,""))</f>
+        <v/>
+      </c>
+      <c r="E31" s="89">
+        <f>IF(OR(D31="",NOT(ISNUMBER(D31))),"",(C31-D31)*100)</f>
+        <v/>
+      </c>
+      <c r="F31" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B31,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G31),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G31" s="85" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="6">
@@ -7147,11 +7394,19 @@
         <f>Bootstrap!J32</f>
         <v/>
       </c>
-      <c r="D32" s="30" t="n"/>
-      <c r="E32" s="31">
-        <f>IF(D32="","",(C32-D32)*100)</f>
-        <v/>
-      </c>
+      <c r="D32" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B32,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G32),G32,""))</f>
+        <v/>
+      </c>
+      <c r="E32" s="89">
+        <f>IF(OR(D32="",NOT(ISNUMBER(D32))),"",(C32-D32)*100)</f>
+        <v/>
+      </c>
+      <c r="F32" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B32,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G32),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="85" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6">
@@ -7166,11 +7421,19 @@
         <f>Bootstrap!J33</f>
         <v/>
       </c>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="31">
-        <f>IF(D33="","",(C33-D33)*100)</f>
-        <v/>
-      </c>
+      <c r="D33" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B33,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G33),G33,""))</f>
+        <v/>
+      </c>
+      <c r="E33" s="89">
+        <f>IF(OR(D33="",NOT(ISNUMBER(D33))),"",(C33-D33)*100)</f>
+        <v/>
+      </c>
+      <c r="F33" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B33,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G33),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G33" s="85" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6">
@@ -7185,11 +7448,19 @@
         <f>Bootstrap!J34</f>
         <v/>
       </c>
-      <c r="D34" s="30" t="n"/>
-      <c r="E34" s="31">
-        <f>IF(D34="","",(C34-D34)*100)</f>
-        <v/>
-      </c>
+      <c r="D34" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B34,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G34),G34,""))</f>
+        <v/>
+      </c>
+      <c r="E34" s="89">
+        <f>IF(OR(D34="",NOT(ISNUMBER(D34))),"",(C34-D34)*100)</f>
+        <v/>
+      </c>
+      <c r="F34" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B34,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G34),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="85" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6">
@@ -7204,11 +7475,19 @@
         <f>Bootstrap!J35</f>
         <v/>
       </c>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31">
-        <f>IF(D35="","",(C35-D35)*100)</f>
-        <v/>
-      </c>
+      <c r="D35" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B35,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G35),G35,""))</f>
+        <v/>
+      </c>
+      <c r="E35" s="89">
+        <f>IF(OR(D35="",NOT(ISNUMBER(D35))),"",(C35-D35)*100)</f>
+        <v/>
+      </c>
+      <c r="F35" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B35,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G35),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="85" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6">
@@ -7223,11 +7502,19 @@
         <f>Bootstrap!J36</f>
         <v/>
       </c>
-      <c r="D36" s="30" t="n"/>
-      <c r="E36" s="31">
-        <f>IF(D36="","",(C36-D36)*100)</f>
-        <v/>
-      </c>
+      <c r="D36" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B36,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G36),G36,""))</f>
+        <v/>
+      </c>
+      <c r="E36" s="89">
+        <f>IF(OR(D36="",NOT(ISNUMBER(D36))),"",(C36-D36)*100)</f>
+        <v/>
+      </c>
+      <c r="F36" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B36,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G36),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="85" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6">
@@ -7242,11 +7529,19 @@
         <f>Bootstrap!J37</f>
         <v/>
       </c>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31">
-        <f>IF(D37="","",(C37-D37)*100)</f>
-        <v/>
-      </c>
+      <c r="D37" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B37,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G37),G37,""))</f>
+        <v/>
+      </c>
+      <c r="E37" s="89">
+        <f>IF(OR(D37="",NOT(ISNUMBER(D37))),"",(C37-D37)*100)</f>
+        <v/>
+      </c>
+      <c r="F37" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B37,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G37),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="85" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6">
@@ -7261,11 +7556,19 @@
         <f>Bootstrap!J38</f>
         <v/>
       </c>
-      <c r="D38" s="30" t="n"/>
-      <c r="E38" s="31">
-        <f>IF(D38="","",(C38-D38)*100)</f>
-        <v/>
-      </c>
+      <c r="D38" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B38,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G38),G38,""))</f>
+        <v/>
+      </c>
+      <c r="E38" s="89">
+        <f>IF(OR(D38="",NOT(ISNUMBER(D38))),"",(C38-D38)*100)</f>
+        <v/>
+      </c>
+      <c r="F38" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B38,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G38),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G38" s="85" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6">
@@ -7280,11 +7583,19 @@
         <f>Bootstrap!J39</f>
         <v/>
       </c>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="31">
-        <f>IF(D39="","",(C39-D39)*100)</f>
-        <v/>
-      </c>
+      <c r="D39" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B39,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G39),G39,""))</f>
+        <v/>
+      </c>
+      <c r="E39" s="89">
+        <f>IF(OR(D39="",NOT(ISNUMBER(D39))),"",(C39-D39)*100)</f>
+        <v/>
+      </c>
+      <c r="F39" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B39,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G39),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="85" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="6">
@@ -7299,11 +7610,19 @@
         <f>Bootstrap!J40</f>
         <v/>
       </c>
-      <c r="D40" s="30" t="n"/>
-      <c r="E40" s="31">
-        <f>IF(D40="","",(C40-D40)*100)</f>
-        <v/>
-      </c>
+      <c r="D40" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B40,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G40),G40,""))</f>
+        <v/>
+      </c>
+      <c r="E40" s="89">
+        <f>IF(OR(D40="",NOT(ISNUMBER(D40))),"",(C40-D40)*100)</f>
+        <v/>
+      </c>
+      <c r="F40" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B40,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G40),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="85" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6">
@@ -7318,11 +7637,19 @@
         <f>Bootstrap!J41</f>
         <v/>
       </c>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="31">
-        <f>IF(D41="","",(C41-D41)*100)</f>
-        <v/>
-      </c>
+      <c r="D41" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B41,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G41),G41,""))</f>
+        <v/>
+      </c>
+      <c r="E41" s="89">
+        <f>IF(OR(D41="",NOT(ISNUMBER(D41))),"",(C41-D41)*100)</f>
+        <v/>
+      </c>
+      <c r="F41" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B41,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G41),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="85" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6">
@@ -7337,11 +7664,19 @@
         <f>Bootstrap!J42</f>
         <v/>
       </c>
-      <c r="D42" s="30" t="n"/>
-      <c r="E42" s="31">
-        <f>IF(D42="","",(C42-D42)*100)</f>
-        <v/>
-      </c>
+      <c r="D42" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B42,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G42),G42,""))</f>
+        <v/>
+      </c>
+      <c r="E42" s="89">
+        <f>IF(OR(D42="",NOT(ISNUMBER(D42))),"",(C42-D42)*100)</f>
+        <v/>
+      </c>
+      <c r="F42" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B42,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G42),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="85" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6">
@@ -7356,11 +7691,19 @@
         <f>Bootstrap!J43</f>
         <v/>
       </c>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="31">
-        <f>IF(D43="","",(C43-D43)*100)</f>
-        <v/>
-      </c>
+      <c r="D43" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B43,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G43),G43,""))</f>
+        <v/>
+      </c>
+      <c r="E43" s="89">
+        <f>IF(OR(D43="",NOT(ISNUMBER(D43))),"",(C43-D43)*100)</f>
+        <v/>
+      </c>
+      <c r="F43" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B43,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G43),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="85" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6">
@@ -7375,11 +7718,19 @@
         <f>Bootstrap!J44</f>
         <v/>
       </c>
-      <c r="D44" s="30" t="n"/>
-      <c r="E44" s="31">
-        <f>IF(D44="","",(C44-D44)*100)</f>
-        <v/>
-      </c>
+      <c r="D44" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B44,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G44),G44,""))</f>
+        <v/>
+      </c>
+      <c r="E44" s="89">
+        <f>IF(OR(D44="",NOT(ISNUMBER(D44))),"",(C44-D44)*100)</f>
+        <v/>
+      </c>
+      <c r="F44" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B44,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G44),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="85" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="6">
@@ -7394,11 +7745,19 @@
         <f>Bootstrap!J45</f>
         <v/>
       </c>
-      <c r="D45" s="30" t="n"/>
-      <c r="E45" s="31">
-        <f>IF(D45="","",(C45-D45)*100)</f>
-        <v/>
-      </c>
+      <c r="D45" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B45,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G45),G45,""))</f>
+        <v/>
+      </c>
+      <c r="E45" s="89">
+        <f>IF(OR(D45="",NOT(ISNUMBER(D45))),"",(C45-D45)*100)</f>
+        <v/>
+      </c>
+      <c r="F45" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B45,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G45),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="85" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6">
@@ -7413,11 +7772,19 @@
         <f>Bootstrap!J46</f>
         <v/>
       </c>
-      <c r="D46" s="30" t="n"/>
-      <c r="E46" s="31">
-        <f>IF(D46="","",(C46-D46)*100)</f>
-        <v/>
-      </c>
+      <c r="D46" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B46,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G46),G46,""))</f>
+        <v/>
+      </c>
+      <c r="E46" s="89">
+        <f>IF(OR(D46="",NOT(ISNUMBER(D46))),"",(C46-D46)*100)</f>
+        <v/>
+      </c>
+      <c r="F46" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B46,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G46),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="85" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6">
@@ -7432,11 +7799,19 @@
         <f>Bootstrap!J47</f>
         <v/>
       </c>
-      <c r="D47" s="30" t="n"/>
-      <c r="E47" s="31">
-        <f>IF(D47="","",(C47-D47)*100)</f>
-        <v/>
-      </c>
+      <c r="D47" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B47,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G47),G47,""))</f>
+        <v/>
+      </c>
+      <c r="E47" s="89">
+        <f>IF(OR(D47="",NOT(ISNUMBER(D47))),"",(C47-D47)*100)</f>
+        <v/>
+      </c>
+      <c r="F47" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B47,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G47),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="85" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6">
@@ -7451,11 +7826,19 @@
         <f>Bootstrap!J48</f>
         <v/>
       </c>
-      <c r="D48" s="30" t="n"/>
-      <c r="E48" s="31">
-        <f>IF(D48="","",(C48-D48)*100)</f>
-        <v/>
-      </c>
+      <c r="D48" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B48,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G48),G48,""))</f>
+        <v/>
+      </c>
+      <c r="E48" s="89">
+        <f>IF(OR(D48="",NOT(ISNUMBER(D48))),"",(C48-D48)*100)</f>
+        <v/>
+      </c>
+      <c r="F48" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B48,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G48),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="85" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6">
@@ -7470,11 +7853,19 @@
         <f>Bootstrap!J49</f>
         <v/>
       </c>
-      <c r="D49" s="30" t="n"/>
-      <c r="E49" s="31">
-        <f>IF(D49="","",(C49-D49)*100)</f>
-        <v/>
-      </c>
+      <c r="D49" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B49,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G49),G49,""))</f>
+        <v/>
+      </c>
+      <c r="E49" s="89">
+        <f>IF(OR(D49="",NOT(ISNUMBER(D49))),"",(C49-D49)*100)</f>
+        <v/>
+      </c>
+      <c r="F49" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B49,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G49),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="85" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6">
@@ -7489,11 +7880,19 @@
         <f>Bootstrap!J50</f>
         <v/>
       </c>
-      <c r="D50" s="30" t="n"/>
-      <c r="E50" s="31">
-        <f>IF(D50="","",(C50-D50)*100)</f>
-        <v/>
-      </c>
+      <c r="D50" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B50,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G50),G50,""))</f>
+        <v/>
+      </c>
+      <c r="E50" s="89">
+        <f>IF(OR(D50="",NOT(ISNUMBER(D50))),"",(C50-D50)*100)</f>
+        <v/>
+      </c>
+      <c r="F50" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B50,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G50),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="85" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6">
@@ -7508,11 +7907,19 @@
         <f>Bootstrap!J51</f>
         <v/>
       </c>
-      <c r="D51" s="30" t="n"/>
-      <c r="E51" s="31">
-        <f>IF(D51="","",(C51-D51)*100)</f>
-        <v/>
-      </c>
+      <c r="D51" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B51,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G51),G51,""))</f>
+        <v/>
+      </c>
+      <c r="E51" s="89">
+        <f>IF(OR(D51="",NOT(ISNUMBER(D51))),"",(C51-D51)*100)</f>
+        <v/>
+      </c>
+      <c r="F51" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B51,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G51),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="85" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="6">
@@ -7527,11 +7934,19 @@
         <f>Bootstrap!J52</f>
         <v/>
       </c>
-      <c r="D52" s="30" t="n"/>
-      <c r="E52" s="31">
-        <f>IF(D52="","",(C52-D52)*100)</f>
-        <v/>
-      </c>
+      <c r="D52" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B52,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G52),G52,""))</f>
+        <v/>
+      </c>
+      <c r="E52" s="89">
+        <f>IF(OR(D52="",NOT(ISNUMBER(D52))),"",(C52-D52)*100)</f>
+        <v/>
+      </c>
+      <c r="F52" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B52,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G52),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G52" s="85" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6">
@@ -7546,11 +7961,19 @@
         <f>Bootstrap!J53</f>
         <v/>
       </c>
-      <c r="D53" s="30" t="n"/>
-      <c r="E53" s="31">
-        <f>IF(D53="","",(C53-D53)*100)</f>
-        <v/>
-      </c>
+      <c r="D53" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B53,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G53),G53,""))</f>
+        <v/>
+      </c>
+      <c r="E53" s="89">
+        <f>IF(OR(D53="",NOT(ISNUMBER(D53))),"",(C53-D53)*100)</f>
+        <v/>
+      </c>
+      <c r="F53" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B53,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G53),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="85" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6">
@@ -7565,11 +7988,19 @@
         <f>Bootstrap!J54</f>
         <v/>
       </c>
-      <c r="D54" s="30" t="n"/>
-      <c r="E54" s="31">
-        <f>IF(D54="","",(C54-D54)*100)</f>
-        <v/>
-      </c>
+      <c r="D54" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B54,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G54),G54,""))</f>
+        <v/>
+      </c>
+      <c r="E54" s="89">
+        <f>IF(OR(D54="",NOT(ISNUMBER(D54))),"",(C54-D54)*100)</f>
+        <v/>
+      </c>
+      <c r="F54" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B54,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G54),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="85" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6">
@@ -7584,11 +8015,19 @@
         <f>Bootstrap!J55</f>
         <v/>
       </c>
-      <c r="D55" s="30" t="n"/>
-      <c r="E55" s="31">
-        <f>IF(D55="","",(C55-D55)*100)</f>
-        <v/>
-      </c>
+      <c r="D55" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B55,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G55),G55,""))</f>
+        <v/>
+      </c>
+      <c r="E55" s="89">
+        <f>IF(OR(D55="",NOT(ISNUMBER(D55))),"",(C55-D55)*100)</f>
+        <v/>
+      </c>
+      <c r="F55" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B55,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G55),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="85" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6">
@@ -7603,11 +8042,19 @@
         <f>Bootstrap!J56</f>
         <v/>
       </c>
-      <c r="D56" s="30" t="n"/>
-      <c r="E56" s="31">
-        <f>IF(D56="","",(C56-D56)*100)</f>
-        <v/>
-      </c>
+      <c r="D56" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B56,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G56),G56,""))</f>
+        <v/>
+      </c>
+      <c r="E56" s="89">
+        <f>IF(OR(D56="",NOT(ISNUMBER(D56))),"",(C56-D56)*100)</f>
+        <v/>
+      </c>
+      <c r="F56" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B56,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G56),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G56" s="85" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="6">
@@ -7622,11 +8069,19 @@
         <f>Bootstrap!J57</f>
         <v/>
       </c>
-      <c r="D57" s="30" t="n"/>
-      <c r="E57" s="31">
-        <f>IF(D57="","",(C57-D57)*100)</f>
-        <v/>
-      </c>
+      <c r="D57" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B57,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G57),G57,""))</f>
+        <v/>
+      </c>
+      <c r="E57" s="89">
+        <f>IF(OR(D57="",NOT(ISNUMBER(D57))),"",(C57-D57)*100)</f>
+        <v/>
+      </c>
+      <c r="F57" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B57,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G57),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G57" s="85" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="6">
@@ -7641,11 +8096,19 @@
         <f>Bootstrap!J58</f>
         <v/>
       </c>
-      <c r="D58" s="30" t="n"/>
-      <c r="E58" s="31">
-        <f>IF(D58="","",(C58-D58)*100)</f>
-        <v/>
-      </c>
+      <c r="D58" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B58,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G58),G58,""))</f>
+        <v/>
+      </c>
+      <c r="E58" s="89">
+        <f>IF(OR(D58="",NOT(ISNUMBER(D58))),"",(C58-D58)*100)</f>
+        <v/>
+      </c>
+      <c r="F58" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B58,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G58),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G58" s="85" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="6">
@@ -7660,11 +8123,19 @@
         <f>Bootstrap!J59</f>
         <v/>
       </c>
-      <c r="D59" s="30" t="n"/>
-      <c r="E59" s="31">
-        <f>IF(D59="","",(C59-D59)*100)</f>
-        <v/>
-      </c>
+      <c r="D59" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B59,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G59),G59,""))</f>
+        <v/>
+      </c>
+      <c r="E59" s="89">
+        <f>IF(OR(D59="",NOT(ISNUMBER(D59))),"",(C59-D59)*100)</f>
+        <v/>
+      </c>
+      <c r="F59" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B59,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G59),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G59" s="85" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="6">
@@ -7679,11 +8150,19 @@
         <f>Bootstrap!J60</f>
         <v/>
       </c>
-      <c r="D60" s="30" t="n"/>
-      <c r="E60" s="31">
-        <f>IF(D60="","",(C60-D60)*100)</f>
-        <v/>
-      </c>
+      <c r="D60" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B60,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G60),G60,""))</f>
+        <v/>
+      </c>
+      <c r="E60" s="89">
+        <f>IF(OR(D60="",NOT(ISNUMBER(D60))),"",(C60-D60)*100)</f>
+        <v/>
+      </c>
+      <c r="F60" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B60,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G60),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G60" s="85" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="6">
@@ -7698,11 +8177,19 @@
         <f>Bootstrap!J61</f>
         <v/>
       </c>
-      <c r="D61" s="30" t="n"/>
-      <c r="E61" s="31">
-        <f>IF(D61="","",(C61-D61)*100)</f>
-        <v/>
-      </c>
+      <c r="D61" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B61,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G61),G61,""))</f>
+        <v/>
+      </c>
+      <c r="E61" s="89">
+        <f>IF(OR(D61="",NOT(ISNUMBER(D61))),"",(C61-D61)*100)</f>
+        <v/>
+      </c>
+      <c r="F61" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B61,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G61),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G61" s="85" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="6">
@@ -7717,11 +8204,19 @@
         <f>Bootstrap!J62</f>
         <v/>
       </c>
-      <c r="D62" s="30" t="n"/>
-      <c r="E62" s="31">
-        <f>IF(D62="","",(C62-D62)*100)</f>
-        <v/>
-      </c>
+      <c r="D62" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B62,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G62),G62,""))</f>
+        <v/>
+      </c>
+      <c r="E62" s="89">
+        <f>IF(OR(D62="",NOT(ISNUMBER(D62))),"",(C62-D62)*100)</f>
+        <v/>
+      </c>
+      <c r="F62" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B62,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G62),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G62" s="85" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="6">
@@ -7736,11 +8231,19 @@
         <f>Bootstrap!J63</f>
         <v/>
       </c>
-      <c r="D63" s="30" t="n"/>
-      <c r="E63" s="31">
-        <f>IF(D63="","",(C63-D63)*100)</f>
-        <v/>
-      </c>
+      <c r="D63" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B63,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G63),G63,""))</f>
+        <v/>
+      </c>
+      <c r="E63" s="89">
+        <f>IF(OR(D63="",NOT(ISNUMBER(D63))),"",(C63-D63)*100)</f>
+        <v/>
+      </c>
+      <c r="F63" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B63,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G63),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G63" s="85" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="6">
@@ -7755,11 +8258,19 @@
         <f>Bootstrap!J64</f>
         <v/>
       </c>
-      <c r="D64" s="30" t="n"/>
-      <c r="E64" s="31">
-        <f>IF(D64="","",(C64-D64)*100)</f>
-        <v/>
-      </c>
+      <c r="D64" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B64,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G64),G64,""))</f>
+        <v/>
+      </c>
+      <c r="E64" s="89">
+        <f>IF(OR(D64="",NOT(ISNUMBER(D64))),"",(C64-D64)*100)</f>
+        <v/>
+      </c>
+      <c r="F64" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B64,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G64),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G64" s="85" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6">
@@ -7774,11 +8285,19 @@
         <f>Bootstrap!J65</f>
         <v/>
       </c>
-      <c r="D65" s="30" t="n"/>
-      <c r="E65" s="31">
-        <f>IF(D65="","",(C65-D65)*100)</f>
-        <v/>
-      </c>
+      <c r="D65" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B65,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G65),G65,""))</f>
+        <v/>
+      </c>
+      <c r="E65" s="89">
+        <f>IF(OR(D65="",NOT(ISNUMBER(D65))),"",(C65-D65)*100)</f>
+        <v/>
+      </c>
+      <c r="F65" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B65,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G65),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G65" s="85" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="6">
@@ -7793,11 +8312,19 @@
         <f>Bootstrap!J66</f>
         <v/>
       </c>
-      <c r="D66" s="30" t="n"/>
-      <c r="E66" s="31">
-        <f>IF(D66="","",(C66-D66)*100)</f>
-        <v/>
-      </c>
+      <c r="D66" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B66,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G66),G66,""))</f>
+        <v/>
+      </c>
+      <c r="E66" s="89">
+        <f>IF(OR(D66="",NOT(ISNUMBER(D66))),"",(C66-D66)*100)</f>
+        <v/>
+      </c>
+      <c r="F66" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B66,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G66),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G66" s="85" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="6">
@@ -7812,11 +8339,19 @@
         <f>Bootstrap!J67</f>
         <v/>
       </c>
-      <c r="D67" s="30" t="n"/>
-      <c r="E67" s="31">
-        <f>IF(D67="","",(C67-D67)*100)</f>
-        <v/>
-      </c>
+      <c r="D67" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B67,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G67),G67,""))</f>
+        <v/>
+      </c>
+      <c r="E67" s="89">
+        <f>IF(OR(D67="",NOT(ISNUMBER(D67))),"",(C67-D67)*100)</f>
+        <v/>
+      </c>
+      <c r="F67" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B67,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G67),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G67" s="85" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="6">
@@ -7831,11 +8366,19 @@
         <f>Bootstrap!J68</f>
         <v/>
       </c>
-      <c r="D68" s="30" t="n"/>
-      <c r="E68" s="31">
-        <f>IF(D68="","",(C68-D68)*100)</f>
-        <v/>
-      </c>
+      <c r="D68" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B68,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G68),G68,""))</f>
+        <v/>
+      </c>
+      <c r="E68" s="89">
+        <f>IF(OR(D68="",NOT(ISNUMBER(D68))),"",(C68-D68)*100)</f>
+        <v/>
+      </c>
+      <c r="F68" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B68,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G68),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G68" s="85" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="6">
@@ -7850,11 +8393,19 @@
         <f>Bootstrap!J69</f>
         <v/>
       </c>
-      <c r="D69" s="30" t="n"/>
-      <c r="E69" s="31">
-        <f>IF(D69="","",(C69-D69)*100)</f>
-        <v/>
-      </c>
+      <c r="D69" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B69,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G69),G69,""))</f>
+        <v/>
+      </c>
+      <c r="E69" s="89">
+        <f>IF(OR(D69="",NOT(ISNUMBER(D69))),"",(C69-D69)*100)</f>
+        <v/>
+      </c>
+      <c r="F69" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B69,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G69),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G69" s="85" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="6">
@@ -7869,11 +8420,19 @@
         <f>Bootstrap!J70</f>
         <v/>
       </c>
-      <c r="D70" s="30" t="n"/>
-      <c r="E70" s="31">
-        <f>IF(D70="","",(C70-D70)*100)</f>
-        <v/>
-      </c>
+      <c r="D70" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B70,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G70),G70,""))</f>
+        <v/>
+      </c>
+      <c r="E70" s="89">
+        <f>IF(OR(D70="",NOT(ISNUMBER(D70))),"",(C70-D70)*100)</f>
+        <v/>
+      </c>
+      <c r="F70" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B70,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G70),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G70" s="85" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="6">
@@ -7888,11 +8447,19 @@
         <f>Bootstrap!J71</f>
         <v/>
       </c>
-      <c r="D71" s="30" t="n"/>
-      <c r="E71" s="31">
-        <f>IF(D71="","",(C71-D71)*100)</f>
-        <v/>
-      </c>
+      <c r="D71" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B71,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G71),G71,""))</f>
+        <v/>
+      </c>
+      <c r="E71" s="89">
+        <f>IF(OR(D71="",NOT(ISNUMBER(D71))),"",(C71-D71)*100)</f>
+        <v/>
+      </c>
+      <c r="F71" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B71,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G71),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G71" s="85" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="6">
@@ -7907,10 +8474,52 @@
         <f>Bootstrap!J72</f>
         <v/>
       </c>
-      <c r="D72" s="30" t="n"/>
-      <c r="E72" s="31">
-        <f>IF(D72="","",(C72-D72)*100)</f>
-        <v/>
+      <c r="D72" s="97">
+        <f>IFERROR(INDEX($J$12:$T$82,MATCH(B72,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,IF(ISNUMBER(G72),G72,""))</f>
+        <v/>
+      </c>
+      <c r="E72" s="89">
+        <f>IF(OR(D72="",NOT(ISNUMBER(D72))),"",(C72-D72)*100)</f>
+        <v/>
+      </c>
+      <c r="F72" s="93">
+        <f>IF(ISNUMBER(IFERROR(INDEX($J$12:$T$82,MATCH(B72,INDEX($J$12:$T$82,0,$I$3),0),$I$4)*$I$5,"")),"BDS live",IF(ISNUMBER(G72),"manual paste","-"))</f>
+        <v/>
+      </c>
+      <c r="G72" s="85" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="67" t="inlineStr">
+        <is>
+          <t>Pillars matched to the dump</t>
+        </is>
+      </c>
+      <c r="C74" s="87">
+        <f>COUNTIF(F8:F72,"BDS live")&amp;" / "&amp;COUNTA(B8:B72)&amp;"  (only ~32 of the 65 rows are quoted Bloomberg pillars; interpolated gap rows will not match)"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="67" t="inlineStr">
+        <is>
+          <t>Max |Δz| over matched pillars (bp)</t>
+        </is>
+      </c>
+      <c r="C75" s="90">
+        <f>IFERROR(MAX(ABS(IF(ISNUMBER(E8:E72),E8:E72))),"")</f>
+        <v/>
+      </c>
+      <c r="D75" s="65" t="inlineStr">
+        <is>
+          <t>Array formula — Ctrl+Shift+Enter in older Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="66" t="inlineStr">
+        <is>
+          <t>If 'matched' reads 0 / 65 the column offsets in I3/I4 are wrong for this dump's schema — read the preview at J10 and correct them. A wrong offset produces plausible but meaningless diffs.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -56,7 +56,7 @@
     <numFmt numFmtId="173" formatCode="mm/dd/yy"/>
     <numFmt numFmtId="174" formatCode="0.###"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -159,6 +159,12 @@
       <color rgb="00008000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -215,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -346,6 +352,7 @@
     <xf numFmtId="1" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="14" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6751,9 +6758,10 @@
         <v/>
       </c>
       <c r="G8" s="85" t="n"/>
-      <c r="H8">
-        <f>BDS(S490_TKR,"CURVE_TENOR_RATES")</f>
-        <v/>
+      <c r="H8" s="65" t="inlineStr">
+        <is>
+          <t>(the CURVE_TENOR_RATES dump lives at J12 - a second copy here would spill into it)</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -33755,9 +33763,9 @@
       <c r="E6" s="85" t="n">
         <v>3.64055</v>
       </c>
-      <c r="F6" s="65" t="inlineStr">
-        <is>
-          <t>FITTED, not an observed fixing: 3.64055% is the overnight rate that makes DFspot reproduce the screen's discount column (spot lag T+2, ACT/360). Replace with the real SOFR fixing if you prefer observed inputs - it moves the whole curve by ~1e-6 in DF.</t>
+      <c r="F6" s="98" t="inlineStr">
+        <is>
+          <t>LIVE on a terminal: C6 pulls the real SOFRRATE fixing and OVERRIDES this cell. This 3.64055% is only the off-terminal fallback (fitted so DFspot reproduces the 07/21/26 S490 screen). Expect the front end to shift when live: ~1.1bp at 1W and ~0.3bp at 1M if the fixing is 3.59%, but under 0.03bp from 1Y out. The long end is unaffected.</t>
         </is>
       </c>
     </row>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -4636,6 +4636,16 @@
         <f>IF(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20)&gt;=VAL_DATE,DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),EDATE(DATE(YEAR(VAL_DATE),CEILING(MONTH(VAL_DATE)/3,1)*3,20),3))</f>
         <v/>
       </c>
+      <c r="I7" s="67" t="inlineStr">
+        <is>
+          <t>Interpolation</t>
+        </is>
+      </c>
+      <c r="J7" s="68" t="inlineStr">
+        <is>
+          <t>Step-function forward (flat fwd)</t>
+        </is>
+      </c>
       <c r="K7" s="20" t="inlineStr">
         <is>
           <t>Date</t>
@@ -4648,6 +4658,16 @@
       </c>
     </row>
     <row r="8">
+      <c r="I8" s="67" t="inlineStr">
+        <is>
+          <t>VERIFIED default</t>
+        </is>
+      </c>
+      <c r="J8" s="66" t="inlineStr">
+        <is>
+          <t>Step-function forward reproduces the S490 screen (rms DF err 2.3e-06). Piecewise Linear (Simple) — the guide's method 1, its EUR S201 example — is 48x worse on this curve (1.1e-04, biased to +4.2e-04 by 50Y). Only switch if the S490 Interpolation field actually says so.</t>
+        </is>
+      </c>
       <c r="K8" s="18">
         <f>Bootstrap!$B$4</f>
         <v/>
@@ -4730,13 +4750,18 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1)))/((E10-D10)/365)*100</f>
         <v/>
       </c>
-      <c r="G10" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1))*EXP(-(F10/100)*(B10-D10)/365)</f>
+      <c r="G10" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B10-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((10&gt;0)*(D10-VAL_DATE)/360,0)&lt;=0,IF(((E10-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1)+1)-1)/((E10-VAL_DATE)/360)),IF(MAX((10&gt;0)*(D10-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1))-1)/MAX((10&gt;0)*(D10-VAL_DATE)/360,0)))+(IF(((E10-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1)+1)-1)/((E10-VAL_DATE)/360))-IF(MAX((10&gt;0)*(D10-VAL_DATE)/360,0)&lt;=0,IF(((E10-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1)+1)-1)/((E10-VAL_DATE)/360)),IF(MAX((10&gt;0)*(D10-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1))-1)/MAX((10&gt;0)*(D10-VAL_DATE)/360,0))))*IF(((E10-VAL_DATE)/360)-MAX((10&gt;0)*(D10-VAL_DATE)/360,0)=0,0,(((B10-VAL_DATE)/360)-MAX((10&gt;0)*(D10-VAL_DATE)/360,0))/(((E10-VAL_DATE)/360)-MAX((10&gt;0)*(D10-VAL_DATE)/360,0))))*((B10-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B10,$K$8:$K$73,1))*EXP(-(F10/100)*(B10-D10)/365)),"")</f>
         <v/>
       </c>
       <c r="H10" s="17">
         <f>-LN(G10)/C10*100</f>
         <v/>
+      </c>
+      <c r="I10" s="65" t="inlineStr">
+        <is>
+          <t>Guide method 1:  DF(t)=1/(1+r_s(t)*t), r_s piecewise linear, t on ACT/360, flat outside the first/last instrument maturity.</t>
+        </is>
       </c>
       <c r="K10" s="18">
         <f>Bootstrap!B9</f>
@@ -4771,13 +4796,18 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1)))/((E11-D11)/365)*100</f>
         <v/>
       </c>
-      <c r="G11" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1))*EXP(-(F11/100)*(B11-D11)/365)</f>
+      <c r="G11" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B11-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((11&gt;0)*(D11-VAL_DATE)/360,0)&lt;=0,IF(((E11-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1)+1)-1)/((E11-VAL_DATE)/360)),IF(MAX((11&gt;0)*(D11-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1))-1)/MAX((11&gt;0)*(D11-VAL_DATE)/360,0)))+(IF(((E11-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1)+1)-1)/((E11-VAL_DATE)/360))-IF(MAX((11&gt;0)*(D11-VAL_DATE)/360,0)&lt;=0,IF(((E11-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1)+1)-1)/((E11-VAL_DATE)/360)),IF(MAX((11&gt;0)*(D11-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1))-1)/MAX((11&gt;0)*(D11-VAL_DATE)/360,0))))*IF(((E11-VAL_DATE)/360)-MAX((11&gt;0)*(D11-VAL_DATE)/360,0)=0,0,(((B11-VAL_DATE)/360)-MAX((11&gt;0)*(D11-VAL_DATE)/360,0))/(((E11-VAL_DATE)/360)-MAX((11&gt;0)*(D11-VAL_DATE)/360,0))))*((B11-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B11,$K$8:$K$73,1))*EXP(-(F11/100)*(B11-D11)/365)),"")</f>
         <v/>
       </c>
       <c r="H11" s="17">
         <f>-LN(G11)/C11*100</f>
         <v/>
+      </c>
+      <c r="I11" s="65" t="inlineStr">
+        <is>
+          <t>Guide method 3:  flat instantaneous forward between pillars, equivalently log-linear in the discount factor.</t>
+        </is>
       </c>
       <c r="K11" s="18">
         <f>Bootstrap!B10</f>
@@ -4812,13 +4842,18 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1)))/((E12-D12)/365)*100</f>
         <v/>
       </c>
-      <c r="G12" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1))*EXP(-(F12/100)*(B12-D12)/365)</f>
+      <c r="G12" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B12-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((12&gt;0)*(D12-VAL_DATE)/360,0)&lt;=0,IF(((E12-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1)+1)-1)/((E12-VAL_DATE)/360)),IF(MAX((12&gt;0)*(D12-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1))-1)/MAX((12&gt;0)*(D12-VAL_DATE)/360,0)))+(IF(((E12-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1)+1)-1)/((E12-VAL_DATE)/360))-IF(MAX((12&gt;0)*(D12-VAL_DATE)/360,0)&lt;=0,IF(((E12-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1)+1)-1)/((E12-VAL_DATE)/360)),IF(MAX((12&gt;0)*(D12-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1))-1)/MAX((12&gt;0)*(D12-VAL_DATE)/360,0))))*IF(((E12-VAL_DATE)/360)-MAX((12&gt;0)*(D12-VAL_DATE)/360,0)=0,0,(((B12-VAL_DATE)/360)-MAX((12&gt;0)*(D12-VAL_DATE)/360,0))/(((E12-VAL_DATE)/360)-MAX((12&gt;0)*(D12-VAL_DATE)/360,0))))*((B12-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B12,$K$8:$K$73,1))*EXP(-(F12/100)*(B12-D12)/365)),"")</f>
         <v/>
       </c>
       <c r="H12" s="17">
         <f>-LN(G12)/C12*100</f>
         <v/>
+      </c>
+      <c r="I12" s="65" t="inlineStr">
+        <is>
+          <t>Both agree AT the pillars; they differ only off-pillar — which is exactly what CDS_Schedule looks up. Max gap difference ~0.07bp of zero rate in a 2Y gap.</t>
+        </is>
       </c>
       <c r="K12" s="18">
         <f>Bootstrap!B11</f>
@@ -4853,8 +4888,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1)))/((E13-D13)/365)*100</f>
         <v/>
       </c>
-      <c r="G13" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1))*EXP(-(F13/100)*(B13-D13)/365)</f>
+      <c r="G13" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B13-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((13&gt;0)*(D13-VAL_DATE)/360,0)&lt;=0,IF(((E13-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1)+1)-1)/((E13-VAL_DATE)/360)),IF(MAX((13&gt;0)*(D13-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1))-1)/MAX((13&gt;0)*(D13-VAL_DATE)/360,0)))+(IF(((E13-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1)+1)-1)/((E13-VAL_DATE)/360))-IF(MAX((13&gt;0)*(D13-VAL_DATE)/360,0)&lt;=0,IF(((E13-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1)+1)-1)/((E13-VAL_DATE)/360)),IF(MAX((13&gt;0)*(D13-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1))-1)/MAX((13&gt;0)*(D13-VAL_DATE)/360,0))))*IF(((E13-VAL_DATE)/360)-MAX((13&gt;0)*(D13-VAL_DATE)/360,0)=0,0,(((B13-VAL_DATE)/360)-MAX((13&gt;0)*(D13-VAL_DATE)/360,0))/(((E13-VAL_DATE)/360)-MAX((13&gt;0)*(D13-VAL_DATE)/360,0))))*((B13-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B13,$K$8:$K$73,1))*EXP(-(F13/100)*(B13-D13)/365)),"")</f>
         <v/>
       </c>
       <c r="H13" s="17">
@@ -4894,8 +4929,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1)))/((E14-D14)/365)*100</f>
         <v/>
       </c>
-      <c r="G14" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1))*EXP(-(F14/100)*(B14-D14)/365)</f>
+      <c r="G14" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B14-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((14&gt;0)*(D14-VAL_DATE)/360,0)&lt;=0,IF(((E14-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1)+1)-1)/((E14-VAL_DATE)/360)),IF(MAX((14&gt;0)*(D14-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1))-1)/MAX((14&gt;0)*(D14-VAL_DATE)/360,0)))+(IF(((E14-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1)+1)-1)/((E14-VAL_DATE)/360))-IF(MAX((14&gt;0)*(D14-VAL_DATE)/360,0)&lt;=0,IF(((E14-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1)+1)-1)/((E14-VAL_DATE)/360)),IF(MAX((14&gt;0)*(D14-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1))-1)/MAX((14&gt;0)*(D14-VAL_DATE)/360,0))))*IF(((E14-VAL_DATE)/360)-MAX((14&gt;0)*(D14-VAL_DATE)/360,0)=0,0,(((B14-VAL_DATE)/360)-MAX((14&gt;0)*(D14-VAL_DATE)/360,0))/(((E14-VAL_DATE)/360)-MAX((14&gt;0)*(D14-VAL_DATE)/360,0))))*((B14-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B14,$K$8:$K$73,1))*EXP(-(F14/100)*(B14-D14)/365)),"")</f>
         <v/>
       </c>
       <c r="H14" s="17">
@@ -4935,8 +4970,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1)))/((E15-D15)/365)*100</f>
         <v/>
       </c>
-      <c r="G15" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1))*EXP(-(F15/100)*(B15-D15)/365)</f>
+      <c r="G15" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B15-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((15&gt;0)*(D15-VAL_DATE)/360,0)&lt;=0,IF(((E15-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1)+1)-1)/((E15-VAL_DATE)/360)),IF(MAX((15&gt;0)*(D15-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1))-1)/MAX((15&gt;0)*(D15-VAL_DATE)/360,0)))+(IF(((E15-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1)+1)-1)/((E15-VAL_DATE)/360))-IF(MAX((15&gt;0)*(D15-VAL_DATE)/360,0)&lt;=0,IF(((E15-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1)+1)-1)/((E15-VAL_DATE)/360)),IF(MAX((15&gt;0)*(D15-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1))-1)/MAX((15&gt;0)*(D15-VAL_DATE)/360,0))))*IF(((E15-VAL_DATE)/360)-MAX((15&gt;0)*(D15-VAL_DATE)/360,0)=0,0,(((B15-VAL_DATE)/360)-MAX((15&gt;0)*(D15-VAL_DATE)/360,0))/(((E15-VAL_DATE)/360)-MAX((15&gt;0)*(D15-VAL_DATE)/360,0))))*((B15-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B15,$K$8:$K$73,1))*EXP(-(F15/100)*(B15-D15)/365)),"")</f>
         <v/>
       </c>
       <c r="H15" s="17">
@@ -4976,8 +5011,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1)))/((E16-D16)/365)*100</f>
         <v/>
       </c>
-      <c r="G16" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1))*EXP(-(F16/100)*(B16-D16)/365)</f>
+      <c r="G16" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B16-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((16&gt;0)*(D16-VAL_DATE)/360,0)&lt;=0,IF(((E16-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1)+1)-1)/((E16-VAL_DATE)/360)),IF(MAX((16&gt;0)*(D16-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1))-1)/MAX((16&gt;0)*(D16-VAL_DATE)/360,0)))+(IF(((E16-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1)+1)-1)/((E16-VAL_DATE)/360))-IF(MAX((16&gt;0)*(D16-VAL_DATE)/360,0)&lt;=0,IF(((E16-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1)+1)-1)/((E16-VAL_DATE)/360)),IF(MAX((16&gt;0)*(D16-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1))-1)/MAX((16&gt;0)*(D16-VAL_DATE)/360,0))))*IF(((E16-VAL_DATE)/360)-MAX((16&gt;0)*(D16-VAL_DATE)/360,0)=0,0,(((B16-VAL_DATE)/360)-MAX((16&gt;0)*(D16-VAL_DATE)/360,0))/(((E16-VAL_DATE)/360)-MAX((16&gt;0)*(D16-VAL_DATE)/360,0))))*((B16-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B16,$K$8:$K$73,1))*EXP(-(F16/100)*(B16-D16)/365)),"")</f>
         <v/>
       </c>
       <c r="H16" s="17">
@@ -5017,8 +5052,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1)))/((E17-D17)/365)*100</f>
         <v/>
       </c>
-      <c r="G17" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1))*EXP(-(F17/100)*(B17-D17)/365)</f>
+      <c r="G17" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B17-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((17&gt;0)*(D17-VAL_DATE)/360,0)&lt;=0,IF(((E17-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1)+1)-1)/((E17-VAL_DATE)/360)),IF(MAX((17&gt;0)*(D17-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1))-1)/MAX((17&gt;0)*(D17-VAL_DATE)/360,0)))+(IF(((E17-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1)+1)-1)/((E17-VAL_DATE)/360))-IF(MAX((17&gt;0)*(D17-VAL_DATE)/360,0)&lt;=0,IF(((E17-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1)+1)-1)/((E17-VAL_DATE)/360)),IF(MAX((17&gt;0)*(D17-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1))-1)/MAX((17&gt;0)*(D17-VAL_DATE)/360,0))))*IF(((E17-VAL_DATE)/360)-MAX((17&gt;0)*(D17-VAL_DATE)/360,0)=0,0,(((B17-VAL_DATE)/360)-MAX((17&gt;0)*(D17-VAL_DATE)/360,0))/(((E17-VAL_DATE)/360)-MAX((17&gt;0)*(D17-VAL_DATE)/360,0))))*((B17-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B17,$K$8:$K$73,1))*EXP(-(F17/100)*(B17-D17)/365)),"")</f>
         <v/>
       </c>
       <c r="H17" s="17">
@@ -5058,8 +5093,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1)))/((E18-D18)/365)*100</f>
         <v/>
       </c>
-      <c r="G18" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1))*EXP(-(F18/100)*(B18-D18)/365)</f>
+      <c r="G18" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B18-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((18&gt;0)*(D18-VAL_DATE)/360,0)&lt;=0,IF(((E18-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1)+1)-1)/((E18-VAL_DATE)/360)),IF(MAX((18&gt;0)*(D18-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1))-1)/MAX((18&gt;0)*(D18-VAL_DATE)/360,0)))+(IF(((E18-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1)+1)-1)/((E18-VAL_DATE)/360))-IF(MAX((18&gt;0)*(D18-VAL_DATE)/360,0)&lt;=0,IF(((E18-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1)+1)-1)/((E18-VAL_DATE)/360)),IF(MAX((18&gt;0)*(D18-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1))-1)/MAX((18&gt;0)*(D18-VAL_DATE)/360,0))))*IF(((E18-VAL_DATE)/360)-MAX((18&gt;0)*(D18-VAL_DATE)/360,0)=0,0,(((B18-VAL_DATE)/360)-MAX((18&gt;0)*(D18-VAL_DATE)/360,0))/(((E18-VAL_DATE)/360)-MAX((18&gt;0)*(D18-VAL_DATE)/360,0))))*((B18-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B18,$K$8:$K$73,1))*EXP(-(F18/100)*(B18-D18)/365)),"")</f>
         <v/>
       </c>
       <c r="H18" s="17">
@@ -5099,8 +5134,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1)))/((E19-D19)/365)*100</f>
         <v/>
       </c>
-      <c r="G19" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1))*EXP(-(F19/100)*(B19-D19)/365)</f>
+      <c r="G19" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B19-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((19&gt;0)*(D19-VAL_DATE)/360,0)&lt;=0,IF(((E19-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1)+1)-1)/((E19-VAL_DATE)/360)),IF(MAX((19&gt;0)*(D19-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1))-1)/MAX((19&gt;0)*(D19-VAL_DATE)/360,0)))+(IF(((E19-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1)+1)-1)/((E19-VAL_DATE)/360))-IF(MAX((19&gt;0)*(D19-VAL_DATE)/360,0)&lt;=0,IF(((E19-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1)+1)-1)/((E19-VAL_DATE)/360)),IF(MAX((19&gt;0)*(D19-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1))-1)/MAX((19&gt;0)*(D19-VAL_DATE)/360,0))))*IF(((E19-VAL_DATE)/360)-MAX((19&gt;0)*(D19-VAL_DATE)/360,0)=0,0,(((B19-VAL_DATE)/360)-MAX((19&gt;0)*(D19-VAL_DATE)/360,0))/(((E19-VAL_DATE)/360)-MAX((19&gt;0)*(D19-VAL_DATE)/360,0))))*((B19-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B19,$K$8:$K$73,1))*EXP(-(F19/100)*(B19-D19)/365)),"")</f>
         <v/>
       </c>
       <c r="H19" s="17">
@@ -5140,8 +5175,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1)))/((E20-D20)/365)*100</f>
         <v/>
       </c>
-      <c r="G20" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1))*EXP(-(F20/100)*(B20-D20)/365)</f>
+      <c r="G20" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B20-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((20&gt;0)*(D20-VAL_DATE)/360,0)&lt;=0,IF(((E20-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1)+1)-1)/((E20-VAL_DATE)/360)),IF(MAX((20&gt;0)*(D20-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1))-1)/MAX((20&gt;0)*(D20-VAL_DATE)/360,0)))+(IF(((E20-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1)+1)-1)/((E20-VAL_DATE)/360))-IF(MAX((20&gt;0)*(D20-VAL_DATE)/360,0)&lt;=0,IF(((E20-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1)+1)-1)/((E20-VAL_DATE)/360)),IF(MAX((20&gt;0)*(D20-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1))-1)/MAX((20&gt;0)*(D20-VAL_DATE)/360,0))))*IF(((E20-VAL_DATE)/360)-MAX((20&gt;0)*(D20-VAL_DATE)/360,0)=0,0,(((B20-VAL_DATE)/360)-MAX((20&gt;0)*(D20-VAL_DATE)/360,0))/(((E20-VAL_DATE)/360)-MAX((20&gt;0)*(D20-VAL_DATE)/360,0))))*((B20-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B20,$K$8:$K$73,1))*EXP(-(F20/100)*(B20-D20)/365)),"")</f>
         <v/>
       </c>
       <c r="H20" s="17">
@@ -5181,8 +5216,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1)))/((E21-D21)/365)*100</f>
         <v/>
       </c>
-      <c r="G21" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1))*EXP(-(F21/100)*(B21-D21)/365)</f>
+      <c r="G21" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B21-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((21&gt;0)*(D21-VAL_DATE)/360,0)&lt;=0,IF(((E21-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1)+1)-1)/((E21-VAL_DATE)/360)),IF(MAX((21&gt;0)*(D21-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1))-1)/MAX((21&gt;0)*(D21-VAL_DATE)/360,0)))+(IF(((E21-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1)+1)-1)/((E21-VAL_DATE)/360))-IF(MAX((21&gt;0)*(D21-VAL_DATE)/360,0)&lt;=0,IF(((E21-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1)+1)-1)/((E21-VAL_DATE)/360)),IF(MAX((21&gt;0)*(D21-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1))-1)/MAX((21&gt;0)*(D21-VAL_DATE)/360,0))))*IF(((E21-VAL_DATE)/360)-MAX((21&gt;0)*(D21-VAL_DATE)/360,0)=0,0,(((B21-VAL_DATE)/360)-MAX((21&gt;0)*(D21-VAL_DATE)/360,0))/(((E21-VAL_DATE)/360)-MAX((21&gt;0)*(D21-VAL_DATE)/360,0))))*((B21-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B21,$K$8:$K$73,1))*EXP(-(F21/100)*(B21-D21)/365)),"")</f>
         <v/>
       </c>
       <c r="H21" s="17">
@@ -5222,8 +5257,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1)))/((E22-D22)/365)*100</f>
         <v/>
       </c>
-      <c r="G22" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1))*EXP(-(F22/100)*(B22-D22)/365)</f>
+      <c r="G22" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B22-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((22&gt;0)*(D22-VAL_DATE)/360,0)&lt;=0,IF(((E22-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1)+1)-1)/((E22-VAL_DATE)/360)),IF(MAX((22&gt;0)*(D22-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1))-1)/MAX((22&gt;0)*(D22-VAL_DATE)/360,0)))+(IF(((E22-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1)+1)-1)/((E22-VAL_DATE)/360))-IF(MAX((22&gt;0)*(D22-VAL_DATE)/360,0)&lt;=0,IF(((E22-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1)+1)-1)/((E22-VAL_DATE)/360)),IF(MAX((22&gt;0)*(D22-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1))-1)/MAX((22&gt;0)*(D22-VAL_DATE)/360,0))))*IF(((E22-VAL_DATE)/360)-MAX((22&gt;0)*(D22-VAL_DATE)/360,0)=0,0,(((B22-VAL_DATE)/360)-MAX((22&gt;0)*(D22-VAL_DATE)/360,0))/(((E22-VAL_DATE)/360)-MAX((22&gt;0)*(D22-VAL_DATE)/360,0))))*((B22-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B22,$K$8:$K$73,1))*EXP(-(F22/100)*(B22-D22)/365)),"")</f>
         <v/>
       </c>
       <c r="H22" s="17">
@@ -5263,8 +5298,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1)))/((E23-D23)/365)*100</f>
         <v/>
       </c>
-      <c r="G23" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1))*EXP(-(F23/100)*(B23-D23)/365)</f>
+      <c r="G23" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B23-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((23&gt;0)*(D23-VAL_DATE)/360,0)&lt;=0,IF(((E23-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1)+1)-1)/((E23-VAL_DATE)/360)),IF(MAX((23&gt;0)*(D23-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1))-1)/MAX((23&gt;0)*(D23-VAL_DATE)/360,0)))+(IF(((E23-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1)+1)-1)/((E23-VAL_DATE)/360))-IF(MAX((23&gt;0)*(D23-VAL_DATE)/360,0)&lt;=0,IF(((E23-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1)+1)-1)/((E23-VAL_DATE)/360)),IF(MAX((23&gt;0)*(D23-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1))-1)/MAX((23&gt;0)*(D23-VAL_DATE)/360,0))))*IF(((E23-VAL_DATE)/360)-MAX((23&gt;0)*(D23-VAL_DATE)/360,0)=0,0,(((B23-VAL_DATE)/360)-MAX((23&gt;0)*(D23-VAL_DATE)/360,0))/(((E23-VAL_DATE)/360)-MAX((23&gt;0)*(D23-VAL_DATE)/360,0))))*((B23-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B23,$K$8:$K$73,1))*EXP(-(F23/100)*(B23-D23)/365)),"")</f>
         <v/>
       </c>
       <c r="H23" s="17">
@@ -5304,8 +5339,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1)))/((E24-D24)/365)*100</f>
         <v/>
       </c>
-      <c r="G24" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1))*EXP(-(F24/100)*(B24-D24)/365)</f>
+      <c r="G24" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B24-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((24&gt;0)*(D24-VAL_DATE)/360,0)&lt;=0,IF(((E24-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1)+1)-1)/((E24-VAL_DATE)/360)),IF(MAX((24&gt;0)*(D24-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1))-1)/MAX((24&gt;0)*(D24-VAL_DATE)/360,0)))+(IF(((E24-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1)+1)-1)/((E24-VAL_DATE)/360))-IF(MAX((24&gt;0)*(D24-VAL_DATE)/360,0)&lt;=0,IF(((E24-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1)+1)-1)/((E24-VAL_DATE)/360)),IF(MAX((24&gt;0)*(D24-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1))-1)/MAX((24&gt;0)*(D24-VAL_DATE)/360,0))))*IF(((E24-VAL_DATE)/360)-MAX((24&gt;0)*(D24-VAL_DATE)/360,0)=0,0,(((B24-VAL_DATE)/360)-MAX((24&gt;0)*(D24-VAL_DATE)/360,0))/(((E24-VAL_DATE)/360)-MAX((24&gt;0)*(D24-VAL_DATE)/360,0))))*((B24-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B24,$K$8:$K$73,1))*EXP(-(F24/100)*(B24-D24)/365)),"")</f>
         <v/>
       </c>
       <c r="H24" s="17">
@@ -5345,8 +5380,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1)))/((E25-D25)/365)*100</f>
         <v/>
       </c>
-      <c r="G25" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1))*EXP(-(F25/100)*(B25-D25)/365)</f>
+      <c r="G25" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B25-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((25&gt;0)*(D25-VAL_DATE)/360,0)&lt;=0,IF(((E25-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1)+1)-1)/((E25-VAL_DATE)/360)),IF(MAX((25&gt;0)*(D25-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1))-1)/MAX((25&gt;0)*(D25-VAL_DATE)/360,0)))+(IF(((E25-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1)+1)-1)/((E25-VAL_DATE)/360))-IF(MAX((25&gt;0)*(D25-VAL_DATE)/360,0)&lt;=0,IF(((E25-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1)+1)-1)/((E25-VAL_DATE)/360)),IF(MAX((25&gt;0)*(D25-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1))-1)/MAX((25&gt;0)*(D25-VAL_DATE)/360,0))))*IF(((E25-VAL_DATE)/360)-MAX((25&gt;0)*(D25-VAL_DATE)/360,0)=0,0,(((B25-VAL_DATE)/360)-MAX((25&gt;0)*(D25-VAL_DATE)/360,0))/(((E25-VAL_DATE)/360)-MAX((25&gt;0)*(D25-VAL_DATE)/360,0))))*((B25-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B25,$K$8:$K$73,1))*EXP(-(F25/100)*(B25-D25)/365)),"")</f>
         <v/>
       </c>
       <c r="H25" s="17">
@@ -5386,8 +5421,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1)))/((E26-D26)/365)*100</f>
         <v/>
       </c>
-      <c r="G26" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1))*EXP(-(F26/100)*(B26-D26)/365)</f>
+      <c r="G26" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B26-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((26&gt;0)*(D26-VAL_DATE)/360,0)&lt;=0,IF(((E26-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1)+1)-1)/((E26-VAL_DATE)/360)),IF(MAX((26&gt;0)*(D26-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1))-1)/MAX((26&gt;0)*(D26-VAL_DATE)/360,0)))+(IF(((E26-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1)+1)-1)/((E26-VAL_DATE)/360))-IF(MAX((26&gt;0)*(D26-VAL_DATE)/360,0)&lt;=0,IF(((E26-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1)+1)-1)/((E26-VAL_DATE)/360)),IF(MAX((26&gt;0)*(D26-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1))-1)/MAX((26&gt;0)*(D26-VAL_DATE)/360,0))))*IF(((E26-VAL_DATE)/360)-MAX((26&gt;0)*(D26-VAL_DATE)/360,0)=0,0,(((B26-VAL_DATE)/360)-MAX((26&gt;0)*(D26-VAL_DATE)/360,0))/(((E26-VAL_DATE)/360)-MAX((26&gt;0)*(D26-VAL_DATE)/360,0))))*((B26-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B26,$K$8:$K$73,1))*EXP(-(F26/100)*(B26-D26)/365)),"")</f>
         <v/>
       </c>
       <c r="H26" s="17">
@@ -5427,8 +5462,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1)))/((E27-D27)/365)*100</f>
         <v/>
       </c>
-      <c r="G27" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1))*EXP(-(F27/100)*(B27-D27)/365)</f>
+      <c r="G27" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B27-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((27&gt;0)*(D27-VAL_DATE)/360,0)&lt;=0,IF(((E27-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1)+1)-1)/((E27-VAL_DATE)/360)),IF(MAX((27&gt;0)*(D27-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1))-1)/MAX((27&gt;0)*(D27-VAL_DATE)/360,0)))+(IF(((E27-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1)+1)-1)/((E27-VAL_DATE)/360))-IF(MAX((27&gt;0)*(D27-VAL_DATE)/360,0)&lt;=0,IF(((E27-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1)+1)-1)/((E27-VAL_DATE)/360)),IF(MAX((27&gt;0)*(D27-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1))-1)/MAX((27&gt;0)*(D27-VAL_DATE)/360,0))))*IF(((E27-VAL_DATE)/360)-MAX((27&gt;0)*(D27-VAL_DATE)/360,0)=0,0,(((B27-VAL_DATE)/360)-MAX((27&gt;0)*(D27-VAL_DATE)/360,0))/(((E27-VAL_DATE)/360)-MAX((27&gt;0)*(D27-VAL_DATE)/360,0))))*((B27-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B27,$K$8:$K$73,1))*EXP(-(F27/100)*(B27-D27)/365)),"")</f>
         <v/>
       </c>
       <c r="H27" s="17">
@@ -5468,8 +5503,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1)))/((E28-D28)/365)*100</f>
         <v/>
       </c>
-      <c r="G28" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1))*EXP(-(F28/100)*(B28-D28)/365)</f>
+      <c r="G28" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B28-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((28&gt;0)*(D28-VAL_DATE)/360,0)&lt;=0,IF(((E28-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1)+1)-1)/((E28-VAL_DATE)/360)),IF(MAX((28&gt;0)*(D28-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1))-1)/MAX((28&gt;0)*(D28-VAL_DATE)/360,0)))+(IF(((E28-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1)+1)-1)/((E28-VAL_DATE)/360))-IF(MAX((28&gt;0)*(D28-VAL_DATE)/360,0)&lt;=0,IF(((E28-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1)+1)-1)/((E28-VAL_DATE)/360)),IF(MAX((28&gt;0)*(D28-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1))-1)/MAX((28&gt;0)*(D28-VAL_DATE)/360,0))))*IF(((E28-VAL_DATE)/360)-MAX((28&gt;0)*(D28-VAL_DATE)/360,0)=0,0,(((B28-VAL_DATE)/360)-MAX((28&gt;0)*(D28-VAL_DATE)/360,0))/(((E28-VAL_DATE)/360)-MAX((28&gt;0)*(D28-VAL_DATE)/360,0))))*((B28-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B28,$K$8:$K$73,1))*EXP(-(F28/100)*(B28-D28)/365)),"")</f>
         <v/>
       </c>
       <c r="H28" s="17">
@@ -5509,8 +5544,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1)))/((E29-D29)/365)*100</f>
         <v/>
       </c>
-      <c r="G29" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1))*EXP(-(F29/100)*(B29-D29)/365)</f>
+      <c r="G29" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B29-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((29&gt;0)*(D29-VAL_DATE)/360,0)&lt;=0,IF(((E29-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1)+1)-1)/((E29-VAL_DATE)/360)),IF(MAX((29&gt;0)*(D29-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1))-1)/MAX((29&gt;0)*(D29-VAL_DATE)/360,0)))+(IF(((E29-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1)+1)-1)/((E29-VAL_DATE)/360))-IF(MAX((29&gt;0)*(D29-VAL_DATE)/360,0)&lt;=0,IF(((E29-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1)+1)-1)/((E29-VAL_DATE)/360)),IF(MAX((29&gt;0)*(D29-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1))-1)/MAX((29&gt;0)*(D29-VAL_DATE)/360,0))))*IF(((E29-VAL_DATE)/360)-MAX((29&gt;0)*(D29-VAL_DATE)/360,0)=0,0,(((B29-VAL_DATE)/360)-MAX((29&gt;0)*(D29-VAL_DATE)/360,0))/(((E29-VAL_DATE)/360)-MAX((29&gt;0)*(D29-VAL_DATE)/360,0))))*((B29-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B29,$K$8:$K$73,1))*EXP(-(F29/100)*(B29-D29)/365)),"")</f>
         <v/>
       </c>
       <c r="H29" s="17">
@@ -5550,8 +5585,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1)))/((E30-D30)/365)*100</f>
         <v/>
       </c>
-      <c r="G30" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1))*EXP(-(F30/100)*(B30-D30)/365)</f>
+      <c r="G30" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B30-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((30&gt;0)*(D30-VAL_DATE)/360,0)&lt;=0,IF(((E30-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1)+1)-1)/((E30-VAL_DATE)/360)),IF(MAX((30&gt;0)*(D30-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1))-1)/MAX((30&gt;0)*(D30-VAL_DATE)/360,0)))+(IF(((E30-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1)+1)-1)/((E30-VAL_DATE)/360))-IF(MAX((30&gt;0)*(D30-VAL_DATE)/360,0)&lt;=0,IF(((E30-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1)+1)-1)/((E30-VAL_DATE)/360)),IF(MAX((30&gt;0)*(D30-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1))-1)/MAX((30&gt;0)*(D30-VAL_DATE)/360,0))))*IF(((E30-VAL_DATE)/360)-MAX((30&gt;0)*(D30-VAL_DATE)/360,0)=0,0,(((B30-VAL_DATE)/360)-MAX((30&gt;0)*(D30-VAL_DATE)/360,0))/(((E30-VAL_DATE)/360)-MAX((30&gt;0)*(D30-VAL_DATE)/360,0))))*((B30-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B30,$K$8:$K$73,1))*EXP(-(F30/100)*(B30-D30)/365)),"")</f>
         <v/>
       </c>
       <c r="H30" s="17">
@@ -5591,8 +5626,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1)))/((E31-D31)/365)*100</f>
         <v/>
       </c>
-      <c r="G31" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1))*EXP(-(F31/100)*(B31-D31)/365)</f>
+      <c r="G31" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B31-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((31&gt;0)*(D31-VAL_DATE)/360,0)&lt;=0,IF(((E31-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1)+1)-1)/((E31-VAL_DATE)/360)),IF(MAX((31&gt;0)*(D31-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1))-1)/MAX((31&gt;0)*(D31-VAL_DATE)/360,0)))+(IF(((E31-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1)+1)-1)/((E31-VAL_DATE)/360))-IF(MAX((31&gt;0)*(D31-VAL_DATE)/360,0)&lt;=0,IF(((E31-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1)+1)-1)/((E31-VAL_DATE)/360)),IF(MAX((31&gt;0)*(D31-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1))-1)/MAX((31&gt;0)*(D31-VAL_DATE)/360,0))))*IF(((E31-VAL_DATE)/360)-MAX((31&gt;0)*(D31-VAL_DATE)/360,0)=0,0,(((B31-VAL_DATE)/360)-MAX((31&gt;0)*(D31-VAL_DATE)/360,0))/(((E31-VAL_DATE)/360)-MAX((31&gt;0)*(D31-VAL_DATE)/360,0))))*((B31-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B31,$K$8:$K$73,1))*EXP(-(F31/100)*(B31-D31)/365)),"")</f>
         <v/>
       </c>
       <c r="H31" s="17">
@@ -5632,8 +5667,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1)))/((E32-D32)/365)*100</f>
         <v/>
       </c>
-      <c r="G32" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1))*EXP(-(F32/100)*(B32-D32)/365)</f>
+      <c r="G32" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B32-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((32&gt;0)*(D32-VAL_DATE)/360,0)&lt;=0,IF(((E32-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1)+1)-1)/((E32-VAL_DATE)/360)),IF(MAX((32&gt;0)*(D32-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1))-1)/MAX((32&gt;0)*(D32-VAL_DATE)/360,0)))+(IF(((E32-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1)+1)-1)/((E32-VAL_DATE)/360))-IF(MAX((32&gt;0)*(D32-VAL_DATE)/360,0)&lt;=0,IF(((E32-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1)+1)-1)/((E32-VAL_DATE)/360)),IF(MAX((32&gt;0)*(D32-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1))-1)/MAX((32&gt;0)*(D32-VAL_DATE)/360,0))))*IF(((E32-VAL_DATE)/360)-MAX((32&gt;0)*(D32-VAL_DATE)/360,0)=0,0,(((B32-VAL_DATE)/360)-MAX((32&gt;0)*(D32-VAL_DATE)/360,0))/(((E32-VAL_DATE)/360)-MAX((32&gt;0)*(D32-VAL_DATE)/360,0))))*((B32-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B32,$K$8:$K$73,1))*EXP(-(F32/100)*(B32-D32)/365)),"")</f>
         <v/>
       </c>
       <c r="H32" s="17">
@@ -5673,8 +5708,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1)))/((E33-D33)/365)*100</f>
         <v/>
       </c>
-      <c r="G33" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1))*EXP(-(F33/100)*(B33-D33)/365)</f>
+      <c r="G33" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B33-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((33&gt;0)*(D33-VAL_DATE)/360,0)&lt;=0,IF(((E33-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1)+1)-1)/((E33-VAL_DATE)/360)),IF(MAX((33&gt;0)*(D33-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1))-1)/MAX((33&gt;0)*(D33-VAL_DATE)/360,0)))+(IF(((E33-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1)+1)-1)/((E33-VAL_DATE)/360))-IF(MAX((33&gt;0)*(D33-VAL_DATE)/360,0)&lt;=0,IF(((E33-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1)+1)-1)/((E33-VAL_DATE)/360)),IF(MAX((33&gt;0)*(D33-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1))-1)/MAX((33&gt;0)*(D33-VAL_DATE)/360,0))))*IF(((E33-VAL_DATE)/360)-MAX((33&gt;0)*(D33-VAL_DATE)/360,0)=0,0,(((B33-VAL_DATE)/360)-MAX((33&gt;0)*(D33-VAL_DATE)/360,0))/(((E33-VAL_DATE)/360)-MAX((33&gt;0)*(D33-VAL_DATE)/360,0))))*((B33-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B33,$K$8:$K$73,1))*EXP(-(F33/100)*(B33-D33)/365)),"")</f>
         <v/>
       </c>
       <c r="H33" s="17">
@@ -5714,8 +5749,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1)))/((E34-D34)/365)*100</f>
         <v/>
       </c>
-      <c r="G34" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1))*EXP(-(F34/100)*(B34-D34)/365)</f>
+      <c r="G34" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B34-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((34&gt;0)*(D34-VAL_DATE)/360,0)&lt;=0,IF(((E34-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1)+1)-1)/((E34-VAL_DATE)/360)),IF(MAX((34&gt;0)*(D34-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1))-1)/MAX((34&gt;0)*(D34-VAL_DATE)/360,0)))+(IF(((E34-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1)+1)-1)/((E34-VAL_DATE)/360))-IF(MAX((34&gt;0)*(D34-VAL_DATE)/360,0)&lt;=0,IF(((E34-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1)+1)-1)/((E34-VAL_DATE)/360)),IF(MAX((34&gt;0)*(D34-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1))-1)/MAX((34&gt;0)*(D34-VAL_DATE)/360,0))))*IF(((E34-VAL_DATE)/360)-MAX((34&gt;0)*(D34-VAL_DATE)/360,0)=0,0,(((B34-VAL_DATE)/360)-MAX((34&gt;0)*(D34-VAL_DATE)/360,0))/(((E34-VAL_DATE)/360)-MAX((34&gt;0)*(D34-VAL_DATE)/360,0))))*((B34-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B34,$K$8:$K$73,1))*EXP(-(F34/100)*(B34-D34)/365)),"")</f>
         <v/>
       </c>
       <c r="H34" s="17">
@@ -5755,8 +5790,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1)))/((E35-D35)/365)*100</f>
         <v/>
       </c>
-      <c r="G35" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1))*EXP(-(F35/100)*(B35-D35)/365)</f>
+      <c r="G35" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B35-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((35&gt;0)*(D35-VAL_DATE)/360,0)&lt;=0,IF(((E35-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1)+1)-1)/((E35-VAL_DATE)/360)),IF(MAX((35&gt;0)*(D35-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1))-1)/MAX((35&gt;0)*(D35-VAL_DATE)/360,0)))+(IF(((E35-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1)+1)-1)/((E35-VAL_DATE)/360))-IF(MAX((35&gt;0)*(D35-VAL_DATE)/360,0)&lt;=0,IF(((E35-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1)+1)-1)/((E35-VAL_DATE)/360)),IF(MAX((35&gt;0)*(D35-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1))-1)/MAX((35&gt;0)*(D35-VAL_DATE)/360,0))))*IF(((E35-VAL_DATE)/360)-MAX((35&gt;0)*(D35-VAL_DATE)/360,0)=0,0,(((B35-VAL_DATE)/360)-MAX((35&gt;0)*(D35-VAL_DATE)/360,0))/(((E35-VAL_DATE)/360)-MAX((35&gt;0)*(D35-VAL_DATE)/360,0))))*((B35-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B35,$K$8:$K$73,1))*EXP(-(F35/100)*(B35-D35)/365)),"")</f>
         <v/>
       </c>
       <c r="H35" s="17">
@@ -5796,8 +5831,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1)))/((E36-D36)/365)*100</f>
         <v/>
       </c>
-      <c r="G36" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1))*EXP(-(F36/100)*(B36-D36)/365)</f>
+      <c r="G36" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B36-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((36&gt;0)*(D36-VAL_DATE)/360,0)&lt;=0,IF(((E36-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1)+1)-1)/((E36-VAL_DATE)/360)),IF(MAX((36&gt;0)*(D36-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1))-1)/MAX((36&gt;0)*(D36-VAL_DATE)/360,0)))+(IF(((E36-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1)+1)-1)/((E36-VAL_DATE)/360))-IF(MAX((36&gt;0)*(D36-VAL_DATE)/360,0)&lt;=0,IF(((E36-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1)+1)-1)/((E36-VAL_DATE)/360)),IF(MAX((36&gt;0)*(D36-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1))-1)/MAX((36&gt;0)*(D36-VAL_DATE)/360,0))))*IF(((E36-VAL_DATE)/360)-MAX((36&gt;0)*(D36-VAL_DATE)/360,0)=0,0,(((B36-VAL_DATE)/360)-MAX((36&gt;0)*(D36-VAL_DATE)/360,0))/(((E36-VAL_DATE)/360)-MAX((36&gt;0)*(D36-VAL_DATE)/360,0))))*((B36-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B36,$K$8:$K$73,1))*EXP(-(F36/100)*(B36-D36)/365)),"")</f>
         <v/>
       </c>
       <c r="H36" s="17">
@@ -5837,8 +5872,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1)))/((E37-D37)/365)*100</f>
         <v/>
       </c>
-      <c r="G37" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1))*EXP(-(F37/100)*(B37-D37)/365)</f>
+      <c r="G37" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B37-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((37&gt;0)*(D37-VAL_DATE)/360,0)&lt;=0,IF(((E37-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1)+1)-1)/((E37-VAL_DATE)/360)),IF(MAX((37&gt;0)*(D37-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1))-1)/MAX((37&gt;0)*(D37-VAL_DATE)/360,0)))+(IF(((E37-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1)+1)-1)/((E37-VAL_DATE)/360))-IF(MAX((37&gt;0)*(D37-VAL_DATE)/360,0)&lt;=0,IF(((E37-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1)+1)-1)/((E37-VAL_DATE)/360)),IF(MAX((37&gt;0)*(D37-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1))-1)/MAX((37&gt;0)*(D37-VAL_DATE)/360,0))))*IF(((E37-VAL_DATE)/360)-MAX((37&gt;0)*(D37-VAL_DATE)/360,0)=0,0,(((B37-VAL_DATE)/360)-MAX((37&gt;0)*(D37-VAL_DATE)/360,0))/(((E37-VAL_DATE)/360)-MAX((37&gt;0)*(D37-VAL_DATE)/360,0))))*((B37-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B37,$K$8:$K$73,1))*EXP(-(F37/100)*(B37-D37)/365)),"")</f>
         <v/>
       </c>
       <c r="H37" s="17">
@@ -5878,8 +5913,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1)))/((E38-D38)/365)*100</f>
         <v/>
       </c>
-      <c r="G38" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1))*EXP(-(F38/100)*(B38-D38)/365)</f>
+      <c r="G38" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B38-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((38&gt;0)*(D38-VAL_DATE)/360,0)&lt;=0,IF(((E38-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1)+1)-1)/((E38-VAL_DATE)/360)),IF(MAX((38&gt;0)*(D38-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1))-1)/MAX((38&gt;0)*(D38-VAL_DATE)/360,0)))+(IF(((E38-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1)+1)-1)/((E38-VAL_DATE)/360))-IF(MAX((38&gt;0)*(D38-VAL_DATE)/360,0)&lt;=0,IF(((E38-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1)+1)-1)/((E38-VAL_DATE)/360)),IF(MAX((38&gt;0)*(D38-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1))-1)/MAX((38&gt;0)*(D38-VAL_DATE)/360,0))))*IF(((E38-VAL_DATE)/360)-MAX((38&gt;0)*(D38-VAL_DATE)/360,0)=0,0,(((B38-VAL_DATE)/360)-MAX((38&gt;0)*(D38-VAL_DATE)/360,0))/(((E38-VAL_DATE)/360)-MAX((38&gt;0)*(D38-VAL_DATE)/360,0))))*((B38-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B38,$K$8:$K$73,1))*EXP(-(F38/100)*(B38-D38)/365)),"")</f>
         <v/>
       </c>
       <c r="H38" s="17">
@@ -5919,8 +5954,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1)))/((E39-D39)/365)*100</f>
         <v/>
       </c>
-      <c r="G39" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1))*EXP(-(F39/100)*(B39-D39)/365)</f>
+      <c r="G39" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B39-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((39&gt;0)*(D39-VAL_DATE)/360,0)&lt;=0,IF(((E39-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1)+1)-1)/((E39-VAL_DATE)/360)),IF(MAX((39&gt;0)*(D39-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1))-1)/MAX((39&gt;0)*(D39-VAL_DATE)/360,0)))+(IF(((E39-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1)+1)-1)/((E39-VAL_DATE)/360))-IF(MAX((39&gt;0)*(D39-VAL_DATE)/360,0)&lt;=0,IF(((E39-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1)+1)-1)/((E39-VAL_DATE)/360)),IF(MAX((39&gt;0)*(D39-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1))-1)/MAX((39&gt;0)*(D39-VAL_DATE)/360,0))))*IF(((E39-VAL_DATE)/360)-MAX((39&gt;0)*(D39-VAL_DATE)/360,0)=0,0,(((B39-VAL_DATE)/360)-MAX((39&gt;0)*(D39-VAL_DATE)/360,0))/(((E39-VAL_DATE)/360)-MAX((39&gt;0)*(D39-VAL_DATE)/360,0))))*((B39-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B39,$K$8:$K$73,1))*EXP(-(F39/100)*(B39-D39)/365)),"")</f>
         <v/>
       </c>
       <c r="H39" s="17">
@@ -5960,8 +5995,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1)))/((E40-D40)/365)*100</f>
         <v/>
       </c>
-      <c r="G40" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1))*EXP(-(F40/100)*(B40-D40)/365)</f>
+      <c r="G40" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B40-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((40&gt;0)*(D40-VAL_DATE)/360,0)&lt;=0,IF(((E40-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1)+1)-1)/((E40-VAL_DATE)/360)),IF(MAX((40&gt;0)*(D40-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1))-1)/MAX((40&gt;0)*(D40-VAL_DATE)/360,0)))+(IF(((E40-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1)+1)-1)/((E40-VAL_DATE)/360))-IF(MAX((40&gt;0)*(D40-VAL_DATE)/360,0)&lt;=0,IF(((E40-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1)+1)-1)/((E40-VAL_DATE)/360)),IF(MAX((40&gt;0)*(D40-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1))-1)/MAX((40&gt;0)*(D40-VAL_DATE)/360,0))))*IF(((E40-VAL_DATE)/360)-MAX((40&gt;0)*(D40-VAL_DATE)/360,0)=0,0,(((B40-VAL_DATE)/360)-MAX((40&gt;0)*(D40-VAL_DATE)/360,0))/(((E40-VAL_DATE)/360)-MAX((40&gt;0)*(D40-VAL_DATE)/360,0))))*((B40-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B40,$K$8:$K$73,1))*EXP(-(F40/100)*(B40-D40)/365)),"")</f>
         <v/>
       </c>
       <c r="H40" s="17">
@@ -6001,8 +6036,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1)))/((E41-D41)/365)*100</f>
         <v/>
       </c>
-      <c r="G41" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1))*EXP(-(F41/100)*(B41-D41)/365)</f>
+      <c r="G41" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B41-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((41&gt;0)*(D41-VAL_DATE)/360,0)&lt;=0,IF(((E41-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1)+1)-1)/((E41-VAL_DATE)/360)),IF(MAX((41&gt;0)*(D41-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1))-1)/MAX((41&gt;0)*(D41-VAL_DATE)/360,0)))+(IF(((E41-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1)+1)-1)/((E41-VAL_DATE)/360))-IF(MAX((41&gt;0)*(D41-VAL_DATE)/360,0)&lt;=0,IF(((E41-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1)+1)-1)/((E41-VAL_DATE)/360)),IF(MAX((41&gt;0)*(D41-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1))-1)/MAX((41&gt;0)*(D41-VAL_DATE)/360,0))))*IF(((E41-VAL_DATE)/360)-MAX((41&gt;0)*(D41-VAL_DATE)/360,0)=0,0,(((B41-VAL_DATE)/360)-MAX((41&gt;0)*(D41-VAL_DATE)/360,0))/(((E41-VAL_DATE)/360)-MAX((41&gt;0)*(D41-VAL_DATE)/360,0))))*((B41-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B41,$K$8:$K$73,1))*EXP(-(F41/100)*(B41-D41)/365)),"")</f>
         <v/>
       </c>
       <c r="H41" s="17">
@@ -6042,8 +6077,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1)))/((E42-D42)/365)*100</f>
         <v/>
       </c>
-      <c r="G42" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1))*EXP(-(F42/100)*(B42-D42)/365)</f>
+      <c r="G42" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B42-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((42&gt;0)*(D42-VAL_DATE)/360,0)&lt;=0,IF(((E42-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1)+1)-1)/((E42-VAL_DATE)/360)),IF(MAX((42&gt;0)*(D42-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1))-1)/MAX((42&gt;0)*(D42-VAL_DATE)/360,0)))+(IF(((E42-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1)+1)-1)/((E42-VAL_DATE)/360))-IF(MAX((42&gt;0)*(D42-VAL_DATE)/360,0)&lt;=0,IF(((E42-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1)+1)-1)/((E42-VAL_DATE)/360)),IF(MAX((42&gt;0)*(D42-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1))-1)/MAX((42&gt;0)*(D42-VAL_DATE)/360,0))))*IF(((E42-VAL_DATE)/360)-MAX((42&gt;0)*(D42-VAL_DATE)/360,0)=0,0,(((B42-VAL_DATE)/360)-MAX((42&gt;0)*(D42-VAL_DATE)/360,0))/(((E42-VAL_DATE)/360)-MAX((42&gt;0)*(D42-VAL_DATE)/360,0))))*((B42-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B42,$K$8:$K$73,1))*EXP(-(F42/100)*(B42-D42)/365)),"")</f>
         <v/>
       </c>
       <c r="H42" s="17">
@@ -6083,8 +6118,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1)))/((E43-D43)/365)*100</f>
         <v/>
       </c>
-      <c r="G43" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1))*EXP(-(F43/100)*(B43-D43)/365)</f>
+      <c r="G43" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B43-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((43&gt;0)*(D43-VAL_DATE)/360,0)&lt;=0,IF(((E43-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1)+1)-1)/((E43-VAL_DATE)/360)),IF(MAX((43&gt;0)*(D43-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1))-1)/MAX((43&gt;0)*(D43-VAL_DATE)/360,0)))+(IF(((E43-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1)+1)-1)/((E43-VAL_DATE)/360))-IF(MAX((43&gt;0)*(D43-VAL_DATE)/360,0)&lt;=0,IF(((E43-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1)+1)-1)/((E43-VAL_DATE)/360)),IF(MAX((43&gt;0)*(D43-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1))-1)/MAX((43&gt;0)*(D43-VAL_DATE)/360,0))))*IF(((E43-VAL_DATE)/360)-MAX((43&gt;0)*(D43-VAL_DATE)/360,0)=0,0,(((B43-VAL_DATE)/360)-MAX((43&gt;0)*(D43-VAL_DATE)/360,0))/(((E43-VAL_DATE)/360)-MAX((43&gt;0)*(D43-VAL_DATE)/360,0))))*((B43-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B43,$K$8:$K$73,1))*EXP(-(F43/100)*(B43-D43)/365)),"")</f>
         <v/>
       </c>
       <c r="H43" s="17">
@@ -6124,8 +6159,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1)))/((E44-D44)/365)*100</f>
         <v/>
       </c>
-      <c r="G44" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1))*EXP(-(F44/100)*(B44-D44)/365)</f>
+      <c r="G44" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B44-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((44&gt;0)*(D44-VAL_DATE)/360,0)&lt;=0,IF(((E44-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1)+1)-1)/((E44-VAL_DATE)/360)),IF(MAX((44&gt;0)*(D44-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1))-1)/MAX((44&gt;0)*(D44-VAL_DATE)/360,0)))+(IF(((E44-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1)+1)-1)/((E44-VAL_DATE)/360))-IF(MAX((44&gt;0)*(D44-VAL_DATE)/360,0)&lt;=0,IF(((E44-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1)+1)-1)/((E44-VAL_DATE)/360)),IF(MAX((44&gt;0)*(D44-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1))-1)/MAX((44&gt;0)*(D44-VAL_DATE)/360,0))))*IF(((E44-VAL_DATE)/360)-MAX((44&gt;0)*(D44-VAL_DATE)/360,0)=0,0,(((B44-VAL_DATE)/360)-MAX((44&gt;0)*(D44-VAL_DATE)/360,0))/(((E44-VAL_DATE)/360)-MAX((44&gt;0)*(D44-VAL_DATE)/360,0))))*((B44-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B44,$K$8:$K$73,1))*EXP(-(F44/100)*(B44-D44)/365)),"")</f>
         <v/>
       </c>
       <c r="H44" s="17">
@@ -6165,8 +6200,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1)))/((E45-D45)/365)*100</f>
         <v/>
       </c>
-      <c r="G45" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1))*EXP(-(F45/100)*(B45-D45)/365)</f>
+      <c r="G45" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B45-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((45&gt;0)*(D45-VAL_DATE)/360,0)&lt;=0,IF(((E45-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1)+1)-1)/((E45-VAL_DATE)/360)),IF(MAX((45&gt;0)*(D45-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1))-1)/MAX((45&gt;0)*(D45-VAL_DATE)/360,0)))+(IF(((E45-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1)+1)-1)/((E45-VAL_DATE)/360))-IF(MAX((45&gt;0)*(D45-VAL_DATE)/360,0)&lt;=0,IF(((E45-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1)+1)-1)/((E45-VAL_DATE)/360)),IF(MAX((45&gt;0)*(D45-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1))-1)/MAX((45&gt;0)*(D45-VAL_DATE)/360,0))))*IF(((E45-VAL_DATE)/360)-MAX((45&gt;0)*(D45-VAL_DATE)/360,0)=0,0,(((B45-VAL_DATE)/360)-MAX((45&gt;0)*(D45-VAL_DATE)/360,0))/(((E45-VAL_DATE)/360)-MAX((45&gt;0)*(D45-VAL_DATE)/360,0))))*((B45-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B45,$K$8:$K$73,1))*EXP(-(F45/100)*(B45-D45)/365)),"")</f>
         <v/>
       </c>
       <c r="H45" s="17">
@@ -6206,8 +6241,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1)))/((E46-D46)/365)*100</f>
         <v/>
       </c>
-      <c r="G46" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1))*EXP(-(F46/100)*(B46-D46)/365)</f>
+      <c r="G46" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B46-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((46&gt;0)*(D46-VAL_DATE)/360,0)&lt;=0,IF(((E46-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1)+1)-1)/((E46-VAL_DATE)/360)),IF(MAX((46&gt;0)*(D46-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1))-1)/MAX((46&gt;0)*(D46-VAL_DATE)/360,0)))+(IF(((E46-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1)+1)-1)/((E46-VAL_DATE)/360))-IF(MAX((46&gt;0)*(D46-VAL_DATE)/360,0)&lt;=0,IF(((E46-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1)+1)-1)/((E46-VAL_DATE)/360)),IF(MAX((46&gt;0)*(D46-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1))-1)/MAX((46&gt;0)*(D46-VAL_DATE)/360,0))))*IF(((E46-VAL_DATE)/360)-MAX((46&gt;0)*(D46-VAL_DATE)/360,0)=0,0,(((B46-VAL_DATE)/360)-MAX((46&gt;0)*(D46-VAL_DATE)/360,0))/(((E46-VAL_DATE)/360)-MAX((46&gt;0)*(D46-VAL_DATE)/360,0))))*((B46-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B46,$K$8:$K$73,1))*EXP(-(F46/100)*(B46-D46)/365)),"")</f>
         <v/>
       </c>
       <c r="H46" s="17">
@@ -6247,8 +6282,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1)))/((E47-D47)/365)*100</f>
         <v/>
       </c>
-      <c r="G47" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1))*EXP(-(F47/100)*(B47-D47)/365)</f>
+      <c r="G47" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B47-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((47&gt;0)*(D47-VAL_DATE)/360,0)&lt;=0,IF(((E47-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1)+1)-1)/((E47-VAL_DATE)/360)),IF(MAX((47&gt;0)*(D47-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1))-1)/MAX((47&gt;0)*(D47-VAL_DATE)/360,0)))+(IF(((E47-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1)+1)-1)/((E47-VAL_DATE)/360))-IF(MAX((47&gt;0)*(D47-VAL_DATE)/360,0)&lt;=0,IF(((E47-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1)+1)-1)/((E47-VAL_DATE)/360)),IF(MAX((47&gt;0)*(D47-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1))-1)/MAX((47&gt;0)*(D47-VAL_DATE)/360,0))))*IF(((E47-VAL_DATE)/360)-MAX((47&gt;0)*(D47-VAL_DATE)/360,0)=0,0,(((B47-VAL_DATE)/360)-MAX((47&gt;0)*(D47-VAL_DATE)/360,0))/(((E47-VAL_DATE)/360)-MAX((47&gt;0)*(D47-VAL_DATE)/360,0))))*((B47-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B47,$K$8:$K$73,1))*EXP(-(F47/100)*(B47-D47)/365)),"")</f>
         <v/>
       </c>
       <c r="H47" s="17">
@@ -6288,8 +6323,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1)))/((E48-D48)/365)*100</f>
         <v/>
       </c>
-      <c r="G48" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1))*EXP(-(F48/100)*(B48-D48)/365)</f>
+      <c r="G48" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B48-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((48&gt;0)*(D48-VAL_DATE)/360,0)&lt;=0,IF(((E48-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1)+1)-1)/((E48-VAL_DATE)/360)),IF(MAX((48&gt;0)*(D48-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1))-1)/MAX((48&gt;0)*(D48-VAL_DATE)/360,0)))+(IF(((E48-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1)+1)-1)/((E48-VAL_DATE)/360))-IF(MAX((48&gt;0)*(D48-VAL_DATE)/360,0)&lt;=0,IF(((E48-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1)+1)-1)/((E48-VAL_DATE)/360)),IF(MAX((48&gt;0)*(D48-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1))-1)/MAX((48&gt;0)*(D48-VAL_DATE)/360,0))))*IF(((E48-VAL_DATE)/360)-MAX((48&gt;0)*(D48-VAL_DATE)/360,0)=0,0,(((B48-VAL_DATE)/360)-MAX((48&gt;0)*(D48-VAL_DATE)/360,0))/(((E48-VAL_DATE)/360)-MAX((48&gt;0)*(D48-VAL_DATE)/360,0))))*((B48-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B48,$K$8:$K$73,1))*EXP(-(F48/100)*(B48-D48)/365)),"")</f>
         <v/>
       </c>
       <c r="H48" s="17">
@@ -6329,8 +6364,8 @@
         <f>-LN(INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1)+1)/INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1)))/((E49-D49)/365)*100</f>
         <v/>
       </c>
-      <c r="G49" s="36">
-        <f>INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1))*EXP(-(F49/100)*(B49-D49)/365)</f>
+      <c r="G49" s="76">
+        <f>IFERROR(IF($J$7="Piecewise Linear (Simple)",IF(((B49-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(MAX((49&gt;0)*(D49-VAL_DATE)/360,0)&lt;=0,IF(((E49-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1)+1)-1)/((E49-VAL_DATE)/360)),IF(MAX((49&gt;0)*(D49-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1))-1)/MAX((49&gt;0)*(D49-VAL_DATE)/360,0)))+(IF(((E49-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1)+1)-1)/((E49-VAL_DATE)/360))-IF(MAX((49&gt;0)*(D49-VAL_DATE)/360,0)&lt;=0,IF(((E49-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1)+1)-1)/((E49-VAL_DATE)/360)),IF(MAX((49&gt;0)*(D49-VAL_DATE)/360,0)&lt;=0,0,(1/INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1))-1)/MAX((49&gt;0)*(D49-VAL_DATE)/360,0))))*IF(((E49-VAL_DATE)/360)-MAX((49&gt;0)*(D49-VAL_DATE)/360,0)=0,0,(((B49-VAL_DATE)/360)-MAX((49&gt;0)*(D49-VAL_DATE)/360,0))/(((E49-VAL_DATE)/360)-MAX((49&gt;0)*(D49-VAL_DATE)/360,0))))*((B49-VAL_DATE)/360))),INDEX($L$8:$L$73,MATCH(B49,$K$8:$K$73,1))*EXP(-(F49/100)*(B49-D49)/365)),"")</f>
         <v/>
       </c>
       <c r="H49" s="17">
@@ -6591,6 +6626,11 @@
     <mergeCell ref="K6:L6"/>
     <mergeCell ref="A4:H6"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="J7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"Step-function forward (flat fwd),Piecewise Linear (Simple)"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
+++ b/bloomberg/USD_SOFR_Curve_Bloomberg.xlsx
@@ -15,19 +15,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S490_Target" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Solver" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bootstrap_Lehman" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Solver" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Swap_Pricer" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Curve_Interface" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloomberg_S490_Validation" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conventions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fwd_Interp" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Parameters" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Quotes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Bootstrap" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Schedule" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Pricer" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CDS_Validation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hazard_Solver" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_DATE">Instructions!$B$9</definedName>
@@ -1618,9 +1617,9 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>Bootstrap_Lehman</t>
+      <c r="A41" s="65" t="inlineStr">
+        <is>
+          <t>Bootstrap - the single production SOFR curve, purely from OIS quotes. (The former Bootstrap_Lehman futures variant has been removed.)</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1857,2713 +1856,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L85"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="1" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Swap_Pricer</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Dynamic Fixed-vs-SOFR OIS valuation (SWPM-style), priced off the Bootstrap curve — every cell is live</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>DEAL — Fixed vs SOFR OIS   (yellow = inputs; everything else is computed)</t>
-        </is>
-      </c>
-      <c r="K4" s="13" t="inlineStr">
-        <is>
-          <t>Discount curve (from Bootstrap)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>Direction (Leg 1 = Fixed)</t>
-        </is>
-      </c>
-      <c r="B5" s="37" t="inlineStr">
-        <is>
-          <t>Receive fixed</t>
-        </is>
-      </c>
-      <c r="C5" s="38" t="inlineStr">
-        <is>
-          <t>Type "Receive fixed" or "Pay fixed". Sets the sign of the net NPV.</t>
-        </is>
-      </c>
-      <c r="K5" s="13" t="inlineStr">
-        <is>
-          <t>Curve date</t>
-        </is>
-      </c>
-      <c r="L5" s="13" t="inlineStr">
-        <is>
-          <t>DF</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Notional</t>
-        </is>
-      </c>
-      <c r="B6" s="39" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="C6" s="38" t="inlineStr">
-        <is>
-          <t>Both legs, USD.</t>
-        </is>
-      </c>
-      <c r="K6" s="18">
-        <f>Bootstrap!$B$4</f>
-        <v/>
-      </c>
-      <c r="L6" s="36" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="K7" s="18">
-        <f>Bootstrap!B8</f>
-        <v/>
-      </c>
-      <c r="L7" s="36">
-        <f>Bootstrap!H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>Effective date</t>
-        </is>
-      </c>
-      <c r="B8" s="40">
-        <f>Bootstrap!$B$4</f>
-        <v/>
-      </c>
-      <c r="C8" s="38" t="inlineStr">
-        <is>
-          <t>Defaults to curve spot (T+2). Overtype for a forward-start swap.</t>
-        </is>
-      </c>
-      <c r="K8" s="18">
-        <f>Bootstrap!B9</f>
-        <v/>
-      </c>
-      <c r="L8" s="36">
-        <f>Bootstrap!H9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>Tenor (years)</t>
-        </is>
-      </c>
-      <c r="B9" s="41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t>Whole years; drives the annual coupon schedule below.</t>
-        </is>
-      </c>
-      <c r="K9" s="18">
-        <f>Bootstrap!B10</f>
-        <v/>
-      </c>
-      <c r="L9" s="36">
-        <f>Bootstrap!H10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Maturity date</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>EDATE(B8,12*B9)</f>
-        <v/>
-      </c>
-      <c r="C10" s="38" t="inlineStr">
-        <is>
-          <t>Effective + Tenor.</t>
-        </is>
-      </c>
-      <c r="K10" s="18">
-        <f>Bootstrap!B11</f>
-        <v/>
-      </c>
-      <c r="L10" s="36">
-        <f>Bootstrap!H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>Fixed coupon (%)</t>
-        </is>
-      </c>
-      <c r="B11" s="42">
-        <f>B25</f>
-        <v/>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t>Defaults to the Par coupon (row 25) → NPV ≈ 0. Overtype to value an off-market coupon.</t>
-        </is>
-      </c>
-      <c r="K11" s="18">
-        <f>Bootstrap!B12</f>
-        <v/>
-      </c>
-      <c r="L11" s="36">
-        <f>Bootstrap!H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>Fixed pay frequency</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Annual</t>
-        </is>
-      </c>
-      <c r="K12" s="18">
-        <f>Bootstrap!B13</f>
-        <v/>
-      </c>
-      <c r="L12" s="36">
-        <f>Bootstrap!H13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Fixed day count</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>ACT/360</t>
-        </is>
-      </c>
-      <c r="K13" s="18">
-        <f>Bootstrap!B14</f>
-        <v/>
-      </c>
-      <c r="L13" s="36">
-        <f>Bootstrap!H14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>Float index</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>SOFR (daily compounded, single-curve)</t>
-        </is>
-      </c>
-      <c r="K14" s="18">
-        <f>Bootstrap!B15</f>
-        <v/>
-      </c>
-      <c r="L14" s="36">
-        <f>Bootstrap!H15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>Curve / valuation date</t>
-        </is>
-      </c>
-      <c r="B15" s="18">
-        <f>VAL_DATE</f>
-        <v/>
-      </c>
-      <c r="C15" s="38" t="inlineStr">
-        <is>
-          <t>Curve is discounted from spot = Bootstrap!B4.</t>
-        </is>
-      </c>
-      <c r="K15" s="18">
-        <f>Bootstrap!B16</f>
-        <v/>
-      </c>
-      <c r="L15" s="36">
-        <f>Bootstrap!H16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>Direction sign (+recv / −pay)</t>
-        </is>
-      </c>
-      <c r="B16" s="43">
-        <f>IF($B$5="Receive fixed",1,-1)</f>
-        <v/>
-      </c>
-      <c r="K16" s="18">
-        <f>Bootstrap!B17</f>
-        <v/>
-      </c>
-      <c r="L16" s="36">
-        <f>Bootstrap!H17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="K17" s="18">
-        <f>Bootstrap!B18</f>
-        <v/>
-      </c>
-      <c r="L17" s="36">
-        <f>Bootstrap!H18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>VALUATION RESULTS — single-curve OIS discounting</t>
-        </is>
-      </c>
-      <c r="K18" s="18">
-        <f>Bootstrap!B19</f>
-        <v/>
-      </c>
-      <c r="L18" s="36">
-        <f>Bootstrap!H19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>DF(effective)</t>
-        </is>
-      </c>
-      <c r="B19" s="36">
-        <f>IFERROR(IF(Curve_Interface!$J$7="Piecewise Linear (Simple)",IF((($B$8-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360)&lt;=0,IF(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)+1)-1)/((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)),(1/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1))-1)/((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360))+(IF(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)+1)-1)/((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360))-IF(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360)&lt;=0,IF(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)+1)-1)/((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)),(1/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1))-1)/((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360)))*IF(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)-((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360)=0,0,((($B$8-VAL_DATE)/360)-((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360))/(((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-VAL_DATE)/360)-((INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))-VAL_DATE)/360))))*(($B$8-VAL_DATE)/360))),INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)))^(($B$8-INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH($B$8,$K$6:$K$71,1))))),INDEX($L$6:$L$71,MATCH($B$8,$K$6:$K$71,1)))</f>
-        <v/>
-      </c>
-      <c r="C19" s="38" t="inlineStr">
-        <is>
-          <t>Interpolated from the curve.</t>
-        </is>
-      </c>
-      <c r="K19" s="18">
-        <f>Bootstrap!B20</f>
-        <v/>
-      </c>
-      <c r="L19" s="36">
-        <f>Bootstrap!H20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>DF(maturity)</t>
-        </is>
-      </c>
-      <c r="B20" s="36">
-        <f>IFERROR(IF(Curve_Interface!$J$7="Piecewise Linear (Simple)",IF((($B$10-VAL_DATE)/360)&lt;=0,1,1/(1+(IF(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360)&lt;=0,IF(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)+1)-1)/((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)),(1/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1))-1)/((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360))+(IF(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)+1)-1)/((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360))-IF(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360)&lt;=0,IF(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)&lt;=0,0,(1/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)+1)-1)/((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)),(1/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1))-1)/((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360)))*IF(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)-((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360)=0,0,((($B$10-VAL_DATE)/360)-((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360))/(((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-VAL_DATE)/360)-((INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))-VAL_DATE)/360))))*(($B$10-VAL_DATE)/360))),INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)))^(($B$10-INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH($B$10,$K$6:$K$71,1))))),INDEX($L$6:$L$71,MATCH($B$10,$K$6:$K$71,1)))</f>
-        <v/>
-      </c>
-      <c r="K20" s="18">
-        <f>Bootstrap!B21</f>
-        <v/>
-      </c>
-      <c r="L20" s="36">
-        <f>Bootstrap!H21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>Fixed annuity  Sum tau·DF</t>
-        </is>
-      </c>
-      <c r="B21" s="34">
-        <f>SUM(H36:H85)</f>
-        <v/>
-      </c>
-      <c r="C21" s="38" t="inlineStr">
-        <is>
-          <t>Sum of tau·DF over the fixed coupon dates.</t>
-        </is>
-      </c>
-      <c r="K21" s="18">
-        <f>Bootstrap!B22</f>
-        <v/>
-      </c>
-      <c r="L21" s="36">
-        <f>Bootstrap!H22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Fixed leg PV (coupons)</t>
-        </is>
-      </c>
-      <c r="B22" s="44">
-        <f>SUM(G36:G85)</f>
-        <v/>
-      </c>
-      <c r="K22" s="18">
-        <f>Bootstrap!B23</f>
-        <v/>
-      </c>
-      <c r="L22" s="36">
-        <f>Bootstrap!H23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Float leg PV</t>
-        </is>
-      </c>
-      <c r="B23" s="44">
-        <f>B6*(B19-B20)</f>
-        <v/>
-      </c>
-      <c r="C23" s="38" t="inlineStr">
-        <is>
-          <t>Single-curve SOFR float leg telescopes to N·(DF_eff − DF_mat).</t>
-        </is>
-      </c>
-      <c r="K23" s="18">
-        <f>Bootstrap!B24</f>
-        <v/>
-      </c>
-      <c r="L23" s="36">
-        <f>Bootstrap!H24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>Notional PV @ maturity</t>
-        </is>
-      </c>
-      <c r="B24" s="44">
-        <f>B6*B20</f>
-        <v/>
-      </c>
-      <c r="C24" s="38" t="inlineStr">
-        <is>
-          <t>For the SWPM-style leg display only.</t>
-        </is>
-      </c>
-      <c r="K24" s="18">
-        <f>Bootstrap!B25</f>
-        <v/>
-      </c>
-      <c r="L24" s="36">
-        <f>Bootstrap!H25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Par coupon (%)</t>
-        </is>
-      </c>
-      <c r="B25" s="34">
-        <f>(B19-B20)/B21*100</f>
-        <v/>
-      </c>
-      <c r="C25" s="38" t="inlineStr">
-        <is>
-          <t>Coupon that sets NPV = 0:  (DF_eff − DF_mat) / annuity.</t>
-        </is>
-      </c>
-      <c r="K25" s="18">
-        <f>Bootstrap!B26</f>
-        <v/>
-      </c>
-      <c r="L25" s="36">
-        <f>Bootstrap!H26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>Leg 1 NPV  (fixed + notional)</t>
-        </is>
-      </c>
-      <c r="B26" s="44">
-        <f>B16*(B22+B24)</f>
-        <v/>
-      </c>
-      <c r="C26" s="38" t="inlineStr">
-        <is>
-          <t>SWPM shows each leg incl. a notional redemption.</t>
-        </is>
-      </c>
-      <c r="K26" s="18">
-        <f>Bootstrap!B27</f>
-        <v/>
-      </c>
-      <c r="L26" s="36">
-        <f>Bootstrap!H27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>Leg 2 NPV  (float + notional)</t>
-        </is>
-      </c>
-      <c r="B27" s="44">
-        <f>-B16*(B23+B24)</f>
-        <v/>
-      </c>
-      <c r="K27" s="18">
-        <f>Bootstrap!B28</f>
-        <v/>
-      </c>
-      <c r="L27" s="36">
-        <f>Bootstrap!H28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>Net swap NPV</t>
-        </is>
-      </c>
-      <c r="B28" s="45">
-        <f>B26+B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="38" t="inlineStr">
-        <is>
-          <t>Fixed − Float (notionals cancel); ≈ 0 at par coupon.</t>
-        </is>
-      </c>
-      <c r="K28" s="18">
-        <f>Bootstrap!B29</f>
-        <v/>
-      </c>
-      <c r="L28" s="36">
-        <f>Bootstrap!H29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>PV01 / DV01  (per 1bp)</t>
-        </is>
-      </c>
-      <c r="B29" s="44">
-        <f>B6*B21*0.0001</f>
-        <v/>
-      </c>
-      <c r="C29" s="38" t="inlineStr">
-        <is>
-          <t>Annuity × notional × 1bp.</t>
-        </is>
-      </c>
-      <c r="K29" s="18">
-        <f>Bootstrap!B30</f>
-        <v/>
-      </c>
-      <c r="L29" s="36">
-        <f>Bootstrap!H30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>Accrued (at inception)</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="18">
-        <f>Bootstrap!B31</f>
-        <v/>
-      </c>
-      <c r="L30" s="36">
-        <f>Bootstrap!H31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="K31" s="18">
-        <f>Bootstrap!B32</f>
-        <v/>
-      </c>
-      <c r="L31" s="36">
-        <f>Bootstrap!H32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32" ht="44" customHeight="1">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Cross-check vs the SWPM screen: Par coupon and PV01 match (≈4.02%, ≈974 for a 10mm 1Y). SWPM's leg NPVs read ~9,995,534 rather than 10,000,000 because it discounts from curve date to a valuation date 2 business days after effective; here effective = spot so DF(effective) = 1 exactly. The net NPV, par coupon and DV01 are unaffected.</t>
-        </is>
-      </c>
-      <c r="K32" s="18">
-        <f>Bootstrap!B33</f>
-        <v/>
-      </c>
-      <c r="L32" s="36">
-        <f>Bootstrap!H33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="K33" s="18">
-        <f>Bootstrap!B34</f>
-        <v/>
-      </c>
-      <c r="L33" s="36">
-        <f>Bootstrap!H34</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="K34" s="18">
-        <f>Bootstrap!B35</f>
-        <v/>
-      </c>
-      <c r="L34" s="36">
-        <f>Bootstrap!H35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="20" t="inlineStr">
-        <is>
-          <t>k</t>
-        </is>
-      </c>
-      <c r="B35" s="20" t="inlineStr">
-        <is>
-          <t>Pay date</t>
-        </is>
-      </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>Prev date</t>
-        </is>
-      </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>tau ACT/360</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="inlineStr">
-        <is>
-          <t>DF (interp)</t>
-        </is>
-      </c>
-      <c r="F35" s="20" t="inlineStr">
-        <is>
-          <t>Coupon CF</t>
-        </is>
-      </c>
-      <c r="G35" s="20" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="H35" s="20" t="inlineStr">
-        <is>
-          <t>tau·DF</t>
-        </is>
-      </c>
-      <c r="K35" s="18">
-        <f>Bootstrap!B36</f>
-        <v/>
-      </c>
-      <c r="L35" s="36">
-        <f>Bootstrap!H36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B36" s="18">
-        <f>IF(A36&lt;=$B$9,EDATE($B$8,12*A36),"")</f>
-        <v/>
-      </c>
-      <c r="C36" s="18">
-        <f>IF(A36&lt;=$B$9,$B$8,"")</f>
-        <v/>
-      </c>
-      <c r="D36" s="17">
-        <f>IF(A36&lt;=$B$9,(B36-C36)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E36" s="36">
-        <f>IF(A36&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1)))^((B36-INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B36,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B36,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="44">
-        <f>IF(A36&lt;=$B$9,$B$6*$B$11/100*D36,"")</f>
-        <v/>
-      </c>
-      <c r="G36" s="44">
-        <f>IF(A36&lt;=$B$9,F36*E36,"")</f>
-        <v/>
-      </c>
-      <c r="H36" s="34">
-        <f>IF(A36&lt;=$B$9,D36*E36,"")</f>
-        <v/>
-      </c>
-      <c r="K36" s="18">
-        <f>Bootstrap!B37</f>
-        <v/>
-      </c>
-      <c r="L36" s="36">
-        <f>Bootstrap!H37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B37" s="18">
-        <f>IF(A37&lt;=$B$9,EDATE($B$8,12*A37),"")</f>
-        <v/>
-      </c>
-      <c r="C37" s="18">
-        <f>IF(A37&lt;=$B$9,B36,"")</f>
-        <v/>
-      </c>
-      <c r="D37" s="17">
-        <f>IF(A37&lt;=$B$9,(B37-C37)/360,"")</f>
-        <v/>
-      </c>
-      <c r="E37" s="36">
-        <f>IF(A37&lt;=$B$9,IFERROR(INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1))*(INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1)+1)/INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1)))^((B37-INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)))/(INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)+1)-INDEX($K$6:$K$71,MATCH(B37,$K$6:$K$71,1)))),INDEX($L$6:$L$71,MATCH(B37,$K$6:$K$71,1))),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="44">
-        <f>IF(A37&lt;=$B$9,$B$6*$B$11/100*D37,"")</f>
-        <v/>
-      </c>
-      <c r="G37" s="44">
-        <f>IF(A37&lt;=$B$9,F37*E37,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="34">
-        <f>IF(A37&lt;=$B$9,D37*E37,"")</f>
-        <v/>
-      </c>
-      <c r="K37" s="18">
-        <f>Bootstrap!B38</f>
-        <v/>
-      </c>
-      <c r="L37" s="36">
-        <f>Bootstrap!H38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="43">
-        <f>ROW()-35</f>
-        <v/>
-      </c>
-      <c r="B38" s="18">
-        <f>IF(A38&lt;=$B$9,EDATE($B$8,12*A38),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="18">
-        <f>IF(A38&lt;=$B$9,B37,"")</f>
-        <v/>
-      </c>
-      <c r="D38" s="17">
-        <f>IF(A38&lt;=$B$9,(B38-C38)/360,"")</f>
-        <v/>
- 